--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGames\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3296BBD-FA7F-4B37-BC23-77C76606EF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB9F988-D61A-4D1D-95B9-6F4332434E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="欄位定義" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -53,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2289" uniqueCount="997">
   <si>
     <t>群組ID</t>
   </si>
@@ -1240,9 +1239,6 @@
     <t>ground-tornado-fire</t>
   </si>
   <si>
-    <t>{"pct":60,"pctPer":6,"hits":5,"sec":2.5}</t>
-  </si>
-  <si>
     <t>在敵人腳下召喚一道火柱（射程 {castM} 米），對目標 {m} 米內的敵人連續造成 {hits} 段傷害，每段 {pct}% 火焰傷害（全程約 {sec} 秒）</t>
   </si>
   <si>
@@ -1270,9 +1266,6 @@
     <t>烈焰衝擊</t>
   </si>
   <si>
-    <t>火龍捲或火牆消失時，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
-  </si>
-  <si>
     <t>重生</t>
   </si>
   <si>
@@ -1282,18 +1275,6 @@
     <t>火柱消失後有 {chance}% 機率在我方 {m} 米內的敵人身上重生</t>
   </si>
   <si>
-    <t>無限火牆</t>
-  </si>
-  <si>
-    <t>ground-firewall</t>
-  </si>
-  <si>
-    <t>{"count":3,"hits":8,"pct":100,"pctPer":10,"respawn":1}</t>
-  </si>
-  <si>
-    <t>改為施放 {count} 道火牆（橫向 {len}×{wid} 米），每道造成 {hits} 段 {pct}% 火焰傷害；每道火牆消失後再召喚 1 道（僅能再觸發一次；第 2~6 階效果仍然生效）</t>
-  </si>
-  <si>
     <t>烈焰暴風</t>
   </si>
   <si>
@@ -1303,9 +1284,6 @@
     <t>{"mult":1.2,"multPer":0.8}</t>
   </si>
   <si>
-    <t>每次施放的火龍捲（火牆）數量變為 {mult} 倍（小數部分依機率補 1 道）</t>
-  </si>
-  <si>
     <t>永劫火獄</t>
   </si>
   <si>
@@ -1444,12 +1422,6 @@
     <t>ground-domain-fire</t>
   </si>
   <si>
-    <t>{"pct":300,"pctPer":30,"orbs":3,"orbsPer":0.3,"mps":24,"flyM":40}</t>
-  </si>
-  <si>
-    <t>你的身體被火焰包裹：每 {gap} 秒對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害；普攻同時朝目標射出 {orbs} 顆火狩星環，以 {mps} 米／秒貫穿飛行 {flyM} 米</t>
-  </si>
-  <si>
     <t>rockarmor</t>
   </si>
   <si>
@@ -1936,12 +1908,6 @@
     <t>ground-thunder-curtain</t>
   </si>
   <si>
-    <t>{"count":2,"countPer":0.2,"pct":300,"pctPer":30,"mps":30}</t>
-  </si>
-  <si>
-    <t>施放落雷術時同時召喚橫向與直向各 {count} 道雷幕橫掃全場（每道寬 {wid} 米、{mps} 米／秒，相鄰兩道由反方向交錯掃過），對掃過的所有敵人各造成 1 次 {pct}% 雷電傷害</t>
-  </si>
-  <si>
     <t>雷霆天劫</t>
   </si>
   <si>
@@ -1975,9 +1941,6 @@
     <t>6*6</t>
   </si>
   <si>
-    <t>{"pct":50,"pctPer":5,"count":2,"sec":2,"speed":6}</t>
-  </si>
-  <si>
     <t>召喚 {count} 個雷球緩慢飛向目標（射程 {castM} 米、飛行速度 {speed} 米/秒），途中每 {gap} 秒對半徑 {m} 米內的所有敵人造成 {pct}% 雷電傷害，抵達後停留 {sec} 秒才消散</t>
   </si>
   <si>
@@ -2026,9 +1989,6 @@
     <t>雷殞天落</t>
   </si>
   <si>
-    <t>proj-thunder-orb-fall</t>
-  </si>
-  <si>
     <t>mark-blue</t>
   </si>
   <si>
@@ -2092,9 +2052,6 @@
     <t>hit-ice</t>
   </si>
   <si>
-    <t>{"pct":250,"pctPer":25,"count":2,"speed":45}</t>
-  </si>
-  <si>
     <t>朝前方射出 {count} 支寒冰箭，每支箭夾角 {deg} 度（射程 {castM} 米、飛行速度 {speed} 米／秒），每支對 1 個敵人造成 {pct}% 寒冰傷害</t>
   </si>
   <si>
@@ -2125,9 +2082,6 @@
     <t>冰箭散射</t>
   </si>
   <si>
-    <t>ground-homing-ice-shard</t>
-  </si>
-  <si>
     <t>射出的寒冰箭數量額外 +{add} 支（不足 1 支的部分以機率觸發）</t>
   </si>
   <si>
@@ -2146,9 +2100,6 @@
     <t>0|750</t>
   </si>
   <si>
-    <t>burst-ice-blast</t>
-  </si>
-  <si>
     <t>{"pct":400,"pctPer":40,"sec":6,"chaseM":30,"bodyM":1.5,"waves":3,"waveGap":0.3}</t>
   </si>
   <si>
@@ -2200,15 +2151,9 @@
     <t>💧</t>
   </si>
   <si>
-    <t>proj-waterball</t>
-  </si>
-  <si>
     <t>{"pct":200,"pctPer":20,"arcM":8}</t>
   </si>
   <si>
-    <t>丟出一顆水彈砸向敵人（射程 {castM} 米、拋物線離地最高 {arcM} 米），造成 {pct}% 寒冰傷害</t>
-  </si>
-  <si>
     <t>寒冰逆轉</t>
   </si>
   <si>
@@ -2236,9 +2181,6 @@
     <t>{"bounce":2,"bouncePer":0.2}</t>
   </si>
   <si>
-    <t>水流彈改為範圍攻擊，對目標 {m} 米內的所有敵人造成傷害，並再彈射 {bounce} 次（不足 1 次的部分以機率觸發）</t>
-  </si>
-  <si>
     <t>寒霜擴散</t>
   </si>
   <si>
@@ -2429,9 +2371,6 @@
   </si>
   <si>
     <t>hit-wind</t>
-  </si>
-  <si>
-    <t>{"pct":200,"pctPer":20,"speed":18}</t>
   </si>
   <si>
     <t>朝前方射出一道弧形風刃（射程 {castM} 米、飛行速度 {speed} 米/秒），貫穿飛行路徑 {m} 米上的所有敵人，各造成 {pct}% 風系傷害</t>
@@ -3024,6 +2963,87 @@
   </si>
   <si>
     <t>field-water-tornado</t>
+  </si>
+  <si>
+    <t>飛行子彈速度（米／秒）</t>
+  </si>
+  <si>
+    <t>{"pct":60,"pctPer":6,"hits":6,"sec":3}</t>
+  </si>
+  <si>
+    <t>火龍捲消失時，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+  </si>
+  <si>
+    <t>無限火龍</t>
+  </si>
+  <si>
+    <t>fire-tornado-infinite</t>
+  </si>
+  <si>
+    <t>{"hitsAdd":6,"pct":100,"pctPer":10,"respawn":1,"sec":6}</t>
+  </si>
+  <si>
+    <t>火龍捲持續 {sec} 秒，傷害段數 +{hitsAdd} 段，每段 {pct}% 火焰傷害；以每秒 {speed} 米持續隨機追敵，單一敵人時在其附近移動；消散後再召喚 {respawn} 次（再召喚不可連鎖），火焰轉為暗紅色</t>
+  </si>
+  <si>
+    <t>每次施放的火龍捲數量變為 {mult} 倍（小數部分依機率補 1 道）</t>
+  </si>
+  <si>
+    <t>{"pct":300,"pctPer":30,"orbs":3,"orbsPer":0.3,"flyM":40}</t>
+  </si>
+  <si>
+    <t>你的身體被火焰包裹：每 {gap} 秒對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害；普攻同時朝目標射出 {orbs} 顆火狩星環，以 {speed} 米／秒貫穿飛行 {flyM} 米</t>
+  </si>
+  <si>
+    <t>bolt-thunderstrike-bluewhite</t>
+  </si>
+  <si>
+    <t>hit-thunderstrike-bluewhite</t>
+  </si>
+  <si>
+    <t>{"count":2,"countPer":0.2,"pct":300,"pctPer":30}</t>
+  </si>
+  <si>
+    <t>施放落雷術時同時召喚橫向與直向各 {count} 道雷幕橫掃全場（每道寬 {wid} 米、{speed} 米／秒，相鄰兩道由反方向交錯掃過），對掃過的所有敵人各造成 1 次 {pct}% 雷電傷害</t>
+  </si>
+  <si>
+    <t>{"pct":50,"pctPer":5,"count":2,"sec":2}</t>
+  </si>
+  <si>
+    <t>hit-thunderfall-impact</t>
+  </si>
+  <si>
+    <t>proj-thunderfall-sky</t>
+  </si>
+  <si>
+    <t>proj-icearrow-frost</t>
+  </si>
+  <si>
+    <t>hit-icearrow-shatter</t>
+  </si>
+  <si>
+    <t>{"pct":250,"pctPer":25,"count":2}</t>
+  </si>
+  <si>
+    <t>ground-icearrow-frost</t>
+  </si>
+  <si>
+    <t>burst-icearrow-crystal</t>
+  </si>
+  <si>
+    <t>proj-waterball-flow</t>
+  </si>
+  <si>
+    <t>hit-waterball-splash</t>
+  </si>
+  <si>
+    <t>朝敵人起飛時的座標拋出水彈（射程 {castM} 米、弧高 {arcM} 米），途中不追蹤；落地時對落點半徑 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
+  </si>
+  <si>
+    <t>水流彈落地後再彈射 {bounce} 次（不足 1 次以機率觸發）；每次起飛重新鎖定敵人當下座標，途中不追蹤，落地造成半徑 {m} 米範圍傷害</t>
+  </si>
+  <si>
+    <t>burst-vacuum-shockwave</t>
   </si>
 </sst>
 </file>
@@ -3899,6 +3919,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E75956C6-7D01-2B48-8FC4-16BDEF26F80D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4110,7 +4184,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ231"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4133,7 +4207,7 @@
     <col min="36" max="36" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4222,7 +4296,7 @@
         <v>28</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>968</v>
+        <v>948</v>
       </c>
       <c r="AE1" s="3" t="s">
         <v>29</v>
@@ -4239,13 +4313,11 @@
       <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="3" t="inlineStr">
-        <is>
-          <t>飛行子彈速度（米／秒）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ1" s="3" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>34</v>
       </c>
@@ -4298,7 +4370,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>34</v>
       </c>
@@ -4342,7 +4414,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>34</v>
       </c>
@@ -4392,7 +4464,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -4442,7 +4514,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>34</v>
       </c>
@@ -4492,7 +4564,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>34</v>
       </c>
@@ -4548,7 +4620,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -4598,7 +4670,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
@@ -4636,7 +4708,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>34</v>
       </c>
@@ -4668,7 +4740,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
@@ -4700,7 +4772,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>80</v>
       </c>
@@ -4750,7 +4822,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>80</v>
       </c>
@@ -4791,7 +4863,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>80</v>
       </c>
@@ -4832,7 +4904,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>80</v>
       </c>
@@ -4873,7 +4945,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>80</v>
       </c>
@@ -4917,7 +4989,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>80</v>
       </c>
@@ -4970,7 +5042,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>80</v>
       </c>
@@ -5017,7 +5089,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>80</v>
       </c>
@@ -5049,7 +5121,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>80</v>
       </c>
@@ -5090,7 +5162,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>80</v>
       </c>
@@ -5122,7 +5194,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>116</v>
       </c>
@@ -5175,7 +5247,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>116</v>
       </c>
@@ -5216,7 +5288,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>116</v>
       </c>
@@ -5266,7 +5338,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>116</v>
       </c>
@@ -5307,7 +5379,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>116</v>
       </c>
@@ -5348,7 +5420,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>116</v>
       </c>
@@ -5389,7 +5461,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>116</v>
       </c>
@@ -5430,7 +5502,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>116</v>
       </c>
@@ -5462,7 +5534,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>116</v>
       </c>
@@ -5494,7 +5566,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>116</v>
       </c>
@@ -5535,7 +5607,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>155</v>
       </c>
@@ -5831,7 +5903,7 @@
         <v>175</v>
       </c>
       <c r="AE38" s="5" t="s">
-        <v>972</v>
+        <v>952</v>
       </c>
       <c r="AF38">
         <v>5000000</v>
@@ -5983,7 +6055,7 @@
         <v>25</v>
       </c>
       <c r="Z42" t="s">
-        <v>973</v>
+        <v>953</v>
       </c>
       <c r="AB42" t="s">
         <v>192</v>
@@ -6845,7 +6917,7 @@
         <v>5</v>
       </c>
       <c r="AA62" t="s">
-        <v>974</v>
+        <v>954</v>
       </c>
       <c r="AB62" t="s">
         <v>40</v>
@@ -7595,7 +7667,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="81" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>310</v>
       </c>
@@ -7633,7 +7705,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="82" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>345</v>
       </c>
@@ -7674,13 +7746,13 @@
         <v>350</v>
       </c>
       <c r="Z82" t="s">
-        <v>975</v>
+        <v>955</v>
       </c>
       <c r="AA82" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="AB82" t="s">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="AE82" t="s">
         <v>354</v>
@@ -7701,7 +7773,7 @@
         <v>65.52</v>
       </c>
     </row>
-    <row r="83" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>345</v>
       </c>
@@ -7751,7 +7823,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="84" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>345</v>
       </c>
@@ -7786,13 +7858,13 @@
         <v>80</v>
       </c>
       <c r="Z84" t="s">
-        <v>975</v>
+        <v>955</v>
       </c>
       <c r="AA84" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="AB84" t="s">
-        <v>975</v>
+        <v>955</v>
       </c>
       <c r="AE84" t="s">
         <v>362</v>
@@ -7810,7 +7882,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="85" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>345</v>
       </c>
@@ -7863,7 +7935,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="86" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>345</v>
       </c>
@@ -7919,7 +7991,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="87" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>345</v>
       </c>
@@ -7969,7 +8041,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="88" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>345</v>
       </c>
@@ -8007,13 +8079,13 @@
         <v>320</v>
       </c>
       <c r="Z88" t="s">
-        <v>978</v>
+        <v>958</v>
       </c>
       <c r="AA88" t="s">
-        <v>979</v>
+        <v>959</v>
       </c>
       <c r="AB88" t="s">
-        <v>978</v>
+        <v>958</v>
       </c>
       <c r="AC88" t="s">
         <v>374</v>
@@ -8037,7 +8109,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="89" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>345</v>
       </c>
@@ -8069,7 +8141,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="90" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>345</v>
       </c>
@@ -8119,7 +8191,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="91" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>345</v>
       </c>
@@ -8157,7 +8229,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>391</v>
       </c>
@@ -8198,15 +8270,13 @@
         <v>353</v>
       </c>
       <c r="AC92" t="s">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="AD92" t="s">
-        <v>980</v>
-      </c>
-      <c r="AE92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"pct":60,"pctPer":6,"hits":6,"sec":3}</t>
-        </is>
+        <v>960</v>
+      </c>
+      <c r="AE92" t="s">
+        <v>971</v>
       </c>
       <c r="AF92">
         <v>100000</v>
@@ -8215,13 +8285,13 @@
         <v>1.5</v>
       </c>
       <c r="AH92" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AI92" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="93" spans="1:35" x14ac:dyDescent="0.3">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="93" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>391</v>
       </c>
@@ -8229,7 +8299,7 @@
         <v>392</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>393</v>
@@ -8262,13 +8332,13 @@
         <v>1.5</v>
       </c>
       <c r="AH93" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AI93" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="94" spans="1:35" x14ac:dyDescent="0.3">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="94" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>391</v>
       </c>
@@ -8276,7 +8346,7 @@
         <v>392</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>393</v>
@@ -8303,7 +8373,7 @@
         <v>80</v>
       </c>
       <c r="AE94" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AF94">
         <v>400000</v>
@@ -8312,13 +8382,13 @@
         <v>1.5</v>
       </c>
       <c r="AH94" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AI94" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="95" spans="1:35" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="95" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>391</v>
       </c>
@@ -8350,7 +8420,7 @@
         <v>100</v>
       </c>
       <c r="AE95" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AF95">
         <v>800000</v>
@@ -8359,13 +8429,13 @@
         <v>1.5</v>
       </c>
       <c r="AH95" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AI95" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="96" spans="1:35" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="96" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>391</v>
       </c>
@@ -8373,7 +8443,7 @@
         <v>392</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>393</v>
@@ -8414,18 +8484,14 @@
       <c r="AG96">
         <v>1.5</v>
       </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火龍捲消失時，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火龍捲消失時，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AH96" t="s">
+        <v>972</v>
+      </c>
+      <c r="AI96" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="97" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>391</v>
       </c>
@@ -8433,7 +8499,7 @@
         <v>392</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>393</v>
@@ -8460,7 +8526,7 @@
         <v>200</v>
       </c>
       <c r="AE97" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AF97">
         <v>3000000</v>
@@ -8469,23 +8535,21 @@
         <v>1.5</v>
       </c>
       <c r="AH97" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AI97" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="98" spans="1:35" x14ac:dyDescent="0.3">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="98" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>391</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無限火龍</t>
-        </is>
+      <c r="C98" s="2" t="s">
+        <v>973</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>393</v>
@@ -8496,8 +8560,6 @@
       <c r="F98" t="s">
         <v>139</v>
       </c>
-      <c r="O98" s="1"/>
-      <c r="Q98" s="1"/>
       <c r="U98" s="1" t="s">
         <v>348</v>
       </c>
@@ -8513,16 +8575,11 @@
       <c r="AB98" t="s">
         <v>353</v>
       </c>
-      <c r="AC98"/>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fire-tornado-infinite</t>
-        </is>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{"hitsAdd":6,"pct":100,"pctPer":10,"respawn":1,"sec":6}</t>
-        </is>
+      <c r="AD98" t="s">
+        <v>974</v>
+      </c>
+      <c r="AE98" t="s">
+        <v>975</v>
       </c>
       <c r="AF98">
         <v>5000000</v>
@@ -8530,38 +8587,34 @@
       <c r="AG98">
         <v>1.5</v>
       </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火龍捲持續 {sec} 秒，傷害段數 +{hitsAdd} 段，每段 {pct}% 火焰傷害；以每秒 {speed} 米持續隨機追敵，單一敵人時在其附近移動；消散後再召喚 {respawn} 次（再召喚不可連鎖），火焰轉為暗紅色</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火龍捲持續 {sec} 秒，傷害段數 +{hitsAdd} 段，每段 {pct}% 火焰傷害；以每秒 {speed} 米持續隨機追敵，單一敵人時在其附近移動；消散後再召喚 {respawn} 次（再召喚不可連鎖），火焰轉為暗紅色</t>
-        </is>
+      <c r="AH98" t="s">
+        <v>976</v>
+      </c>
+      <c r="AI98" t="s">
+        <v>976</v>
       </c>
       <c r="AJ98">
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>391</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="E99">
         <v>8</v>
       </c>
       <c r="G99" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="X99" s="1">
         <v>300</v>
       </c>
       <c r="AE99" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="AF99">
         <v>10000000</v>
@@ -8569,29 +8622,25 @@
       <c r="AG99">
         <v>1.5</v>
       </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">每次施放的火龍捲數量變為 {mult} 倍（小數部分依機率補 1 道）</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">每次施放的火龍捲數量變為 {mult} 倍（小數部分依機率補 1 道）</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AH99" t="s">
+        <v>977</v>
+      </c>
+      <c r="AI99" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="100" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>391</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="E100">
         <v>9</v>
       </c>
       <c r="G100" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="K100" s="1">
         <v>20</v>
@@ -8603,10 +8652,10 @@
         <v>300</v>
       </c>
       <c r="AC100" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="AE100" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AF100">
         <v>10000000</v>
@@ -8615,24 +8664,24 @@
         <v>1.5</v>
       </c>
       <c r="AH100" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="AI100" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="101" spans="1:35" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="101" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>391</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="E101">
         <v>10</v>
       </c>
       <c r="G101" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="K101" s="1">
         <v>30</v>
@@ -8641,7 +8690,7 @@
         <v>300</v>
       </c>
       <c r="AE101" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="AF101">
         <v>10000000</v>
@@ -8650,24 +8699,24 @@
         <v>1.5</v>
       </c>
       <c r="AH101" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="AI101" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="102" spans="1:35" x14ac:dyDescent="0.3">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="102" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E102">
         <v>1</v>
@@ -8676,7 +8725,7 @@
         <v>52</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="I102" s="1">
         <v>8</v>
@@ -8700,16 +8749,16 @@
         <v>351</v>
       </c>
       <c r="AA102" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="AB102" t="s">
         <v>361</v>
       </c>
       <c r="AC102" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="AE102" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="AF102">
         <v>100000</v>
@@ -8718,24 +8767,24 @@
         <v>1.5</v>
       </c>
       <c r="AH102" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="AI102" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="103" spans="1:35" x14ac:dyDescent="0.3">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="103" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>434</v>
-      </c>
       <c r="D103" s="1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E103">
         <v>2</v>
@@ -8744,7 +8793,7 @@
         <v>56</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="U103" s="1" t="s">
         <v>348</v>
@@ -8759,7 +8808,7 @@
         <v>60</v>
       </c>
       <c r="AE103" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="AF103">
         <v>200000</v>
@@ -8768,24 +8817,24 @@
         <v>1.5</v>
       </c>
       <c r="AH103" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="AI103" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="104" spans="1:35" x14ac:dyDescent="0.3">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="104" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E104">
         <v>3</v>
@@ -8794,7 +8843,7 @@
         <v>61</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="K104" s="1">
         <v>1</v>
@@ -8812,10 +8861,10 @@
         <v>80</v>
       </c>
       <c r="AA104" t="s">
-        <v>981</v>
+        <v>961</v>
       </c>
       <c r="AE104" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="AF104">
         <v>400000</v>
@@ -8824,24 +8873,24 @@
         <v>1.5</v>
       </c>
       <c r="AH104" t="s">
-        <v>982</v>
+        <v>962</v>
       </c>
       <c r="AI104" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="105" spans="1:35" x14ac:dyDescent="0.3">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="105" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E105">
         <v>4</v>
@@ -8850,7 +8899,7 @@
         <v>65</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="U105" s="1" t="s">
         <v>348</v>
@@ -8865,7 +8914,7 @@
         <v>100</v>
       </c>
       <c r="AE105" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="AF105">
         <v>800000</v>
@@ -8874,24 +8923,24 @@
         <v>1.5</v>
       </c>
       <c r="AH105" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="AI105" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="106" spans="1:35" x14ac:dyDescent="0.3">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="106" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E106">
         <v>5</v>
@@ -8900,7 +8949,7 @@
         <v>135</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="U106" s="1" t="s">
         <v>348</v>
@@ -8915,7 +8964,7 @@
         <v>140</v>
       </c>
       <c r="AE106" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="AF106">
         <v>1500000</v>
@@ -8924,24 +8973,24 @@
         <v>1.5</v>
       </c>
       <c r="AH106" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="AI106" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="107" spans="1:35" x14ac:dyDescent="0.3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="107" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E107">
         <v>6</v>
@@ -8950,7 +8999,7 @@
         <v>139</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="U107" s="1" t="s">
         <v>348</v>
@@ -8965,7 +9014,7 @@
         <v>200</v>
       </c>
       <c r="AE107" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="AF107">
         <v>3000000</v>
@@ -8974,24 +9023,24 @@
         <v>1.5</v>
       </c>
       <c r="AH107" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="AI107" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="108" spans="1:35" x14ac:dyDescent="0.3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="108" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E108">
         <v>7</v>
@@ -9000,7 +9049,7 @@
         <v>174</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="K108" s="1">
         <v>6</v>
@@ -9018,7 +9067,7 @@
         <v>320</v>
       </c>
       <c r="AE108" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="AF108">
         <v>5000000</v>
@@ -9027,30 +9076,30 @@
         <v>1.5</v>
       </c>
       <c r="AH108" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="AI108" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="109" spans="1:35" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="109" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="E109">
         <v>8</v>
       </c>
       <c r="G109" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="X109" s="1">
         <v>300</v>
       </c>
       <c r="AE109" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="AF109">
         <v>10000000</v>
@@ -9059,24 +9108,24 @@
         <v>1.5</v>
       </c>
       <c r="AH109" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="AI109" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="110" spans="1:35" x14ac:dyDescent="0.3">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="110" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="E110">
         <v>9</v>
       </c>
       <c r="G110" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="K110" s="1">
         <v>40</v>
@@ -9085,7 +9134,7 @@
         <v>300</v>
       </c>
       <c r="AE110" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="AF110">
         <v>10000000</v>
@@ -9094,24 +9143,24 @@
         <v>1.5</v>
       </c>
       <c r="AH110" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="AI110" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="111" spans="1:35" x14ac:dyDescent="0.3">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="111" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="E111">
         <v>10</v>
       </c>
       <c r="G111" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="K111" s="1">
         <v>6</v>
@@ -9123,18 +9172,16 @@
         <v>300</v>
       </c>
       <c r="AA111" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="AB111" t="s">
         <v>353</v>
       </c>
       <c r="AC111" t="s">
-        <v>462</v>
-      </c>
-      <c r="AE111" t="inlineStr">
-        <is>
-          <t>{"pct":300,"pctPer":30,"orbs":3,"orbsPer":0.3,"flyM":40}</t>
-        </is>
+        <v>455</v>
+      </c>
+      <c r="AE111" t="s">
+        <v>978</v>
       </c>
       <c r="AF111">
         <v>10000000</v>
@@ -9142,32 +9189,28 @@
       <c r="AG111">
         <v>1.5</v>
       </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>你的身體被火焰包裹：每 {gap} 秒對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害；普攻同時朝目標射出 {orbs} 顆火狩星環，以 {speed} 米／秒貫穿飛行 {flyM} 米</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>你的身體被火焰包裹：每 {gap} 秒對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害；普攻同時朝目標射出 {orbs} 顆火狩星環，以 {speed} 米／秒貫穿飛行 {flyM} 米</t>
-        </is>
+      <c r="AH111" t="s">
+        <v>979</v>
+      </c>
+      <c r="AI111" t="s">
+        <v>979</v>
       </c>
       <c r="AJ111">
         <v>24</v>
       </c>
     </row>
-    <row r="112" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="E112">
         <v>1</v>
@@ -9182,7 +9225,7 @@
         <v>348</v>
       </c>
       <c r="V112" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W112" s="1">
         <v>15</v>
@@ -9191,10 +9234,10 @@
         <v>40</v>
       </c>
       <c r="AC112" t="s">
-        <v>983</v>
+        <v>963</v>
       </c>
       <c r="AE112" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="AF112">
         <v>100000</v>
@@ -9203,24 +9246,24 @@
         <v>1.5</v>
       </c>
       <c r="AH112" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="AI112" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
     </row>
     <row r="113" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="E113">
         <v>2</v>
@@ -9232,7 +9275,7 @@
         <v>348</v>
       </c>
       <c r="V113" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W113" s="1">
         <v>15</v>
@@ -9250,24 +9293,24 @@
         <v>1.5</v>
       </c>
       <c r="AH113" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="AI113" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
     </row>
     <row r="114" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="E114">
         <v>3</v>
@@ -9279,7 +9322,7 @@
         <v>348</v>
       </c>
       <c r="V114" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W114" s="1">
         <v>15</v>
@@ -9291,7 +9334,7 @@
         <v>285</v>
       </c>
       <c r="AE114" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="AF114">
         <v>400000</v>
@@ -9300,24 +9343,24 @@
         <v>1.5</v>
       </c>
       <c r="AH114" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="AI114" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
     </row>
     <row r="115" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="E115">
         <v>4</v>
@@ -9329,7 +9372,7 @@
         <v>348</v>
       </c>
       <c r="V115" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W115" s="1">
         <v>15</v>
@@ -9338,7 +9381,7 @@
         <v>40</v>
       </c>
       <c r="AE115" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="AF115">
         <v>800000</v>
@@ -9347,24 +9390,24 @@
         <v>1.5</v>
       </c>
       <c r="AH115" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="AI115" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
     </row>
     <row r="116" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="E116">
         <v>5</v>
@@ -9376,7 +9419,7 @@
         <v>348</v>
       </c>
       <c r="V116" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W116" s="1">
         <v>15</v>
@@ -9394,24 +9437,24 @@
         <v>1.5</v>
       </c>
       <c r="AH116" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="AI116" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="117" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="E117">
         <v>6</v>
@@ -9423,7 +9466,7 @@
         <v>348</v>
       </c>
       <c r="V117" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W117" s="1">
         <v>15</v>
@@ -9432,7 +9475,7 @@
         <v>40</v>
       </c>
       <c r="AE117" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="AF117">
         <v>3000000</v>
@@ -9441,24 +9484,24 @@
         <v>1.5</v>
       </c>
       <c r="AH117" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="AI117" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="118" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="E118">
         <v>7</v>
@@ -9470,7 +9513,7 @@
         <v>348</v>
       </c>
       <c r="V118" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W118" s="1">
         <v>15</v>
@@ -9479,10 +9522,10 @@
         <v>40</v>
       </c>
       <c r="AC118" t="s">
-        <v>984</v>
+        <v>964</v>
       </c>
       <c r="AE118" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="AF118">
         <v>5000000</v>
@@ -9491,24 +9534,24 @@
         <v>1.5</v>
       </c>
       <c r="AH118" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AI118" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
     </row>
     <row r="119" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="E119">
         <v>8</v>
       </c>
       <c r="G119" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="K119" s="1">
         <v>24</v>
@@ -9517,16 +9560,16 @@
         <v>300</v>
       </c>
       <c r="Z119" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="AB119" t="s">
         <v>285</v>
       </c>
       <c r="AC119" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="AE119" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="AF119">
         <v>10000000</v>
@@ -9535,30 +9578,30 @@
         <v>1.5</v>
       </c>
       <c r="AH119" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="AI119" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
     </row>
     <row r="120" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="E120">
         <v>9</v>
       </c>
       <c r="G120" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="X120" s="1">
         <v>300</v>
       </c>
       <c r="AE120" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="AF120">
         <v>10000000</v>
@@ -9567,24 +9610,24 @@
         <v>1.5</v>
       </c>
       <c r="AH120" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="AI120" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
     </row>
     <row r="121" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="E121">
         <v>10</v>
       </c>
       <c r="G121" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="K121" s="1">
         <v>24</v>
@@ -9593,16 +9636,16 @@
         <v>300</v>
       </c>
       <c r="Z121" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="AB121" t="s">
         <v>285</v>
       </c>
       <c r="AC121" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="AE121" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="AF121">
         <v>10000000</v>
@@ -9611,24 +9654,24 @@
         <v>1.5</v>
       </c>
       <c r="AH121" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="AI121" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
     </row>
     <row r="122" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="E122">
         <v>1</v>
@@ -9637,7 +9680,7 @@
         <v>61</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="I122" s="1">
         <v>20</v>
@@ -9646,7 +9689,7 @@
         <v>348</v>
       </c>
       <c r="V122" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W122" s="1">
         <v>15</v>
@@ -9655,10 +9698,10 @@
         <v>40</v>
       </c>
       <c r="AC122" t="s">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="AE122" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="AF122">
         <v>100000</v>
@@ -9667,24 +9710,24 @@
         <v>1.5</v>
       </c>
       <c r="AH122" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="AI122" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="123" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>199</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="E123">
         <v>2</v>
@@ -9693,13 +9736,13 @@
         <v>65</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="U123" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V123" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W123" s="1">
         <v>15</v>
@@ -9708,7 +9751,7 @@
         <v>40</v>
       </c>
       <c r="AE123" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="AF123">
         <v>200000</v>
@@ -9717,24 +9760,24 @@
         <v>1.5</v>
       </c>
       <c r="AH123" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="AI123" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="124" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="E124">
         <v>3</v>
@@ -9743,13 +9786,13 @@
         <v>135</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="U124" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V124" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W124" s="1">
         <v>15</v>
@@ -9758,10 +9801,10 @@
         <v>40</v>
       </c>
       <c r="AC124" t="s">
-        <v>986</v>
+        <v>966</v>
       </c>
       <c r="AE124" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="AF124">
         <v>400000</v>
@@ -9770,24 +9813,24 @@
         <v>1.5</v>
       </c>
       <c r="AH124" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="AI124" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
     </row>
     <row r="125" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="B125" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>511</v>
-      </c>
       <c r="D125" s="1" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="E125">
         <v>4</v>
@@ -9796,7 +9839,7 @@
         <v>139</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="K125" s="1">
         <v>40</v>
@@ -9805,7 +9848,7 @@
         <v>348</v>
       </c>
       <c r="V125" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W125" s="1">
         <v>15</v>
@@ -9814,7 +9857,7 @@
         <v>40</v>
       </c>
       <c r="AE125" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AF125">
         <v>800000</v>
@@ -9823,24 +9866,24 @@
         <v>1.5</v>
       </c>
       <c r="AH125" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="AI125" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
     </row>
     <row r="126" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="E126">
         <v>5</v>
@@ -9849,13 +9892,13 @@
         <v>174</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="U126" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V126" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W126" s="1">
         <v>15</v>
@@ -9864,7 +9907,7 @@
         <v>40</v>
       </c>
       <c r="AE126" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="AF126">
         <v>1500000</v>
@@ -9873,24 +9916,24 @@
         <v>1.5</v>
       </c>
       <c r="AH126" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="AI126" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
     </row>
     <row r="127" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="E127">
         <v>6</v>
@@ -9899,13 +9942,13 @@
         <v>212</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="U127" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V127" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W127" s="1">
         <v>15</v>
@@ -9914,7 +9957,7 @@
         <v>40</v>
       </c>
       <c r="AE127" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="AF127">
         <v>3000000</v>
@@ -9923,24 +9966,24 @@
         <v>1.5</v>
       </c>
       <c r="AH127" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="AI127" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
     </row>
     <row r="128" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="E128">
         <v>7</v>
@@ -9949,13 +9992,13 @@
         <v>217</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="U128" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V128" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W128" s="1">
         <v>15</v>
@@ -9964,10 +10007,10 @@
         <v>40</v>
       </c>
       <c r="AC128" t="s">
-        <v>987</v>
+        <v>967</v>
       </c>
       <c r="AE128" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="AF128">
         <v>5000000</v>
@@ -9976,24 +10019,24 @@
         <v>1.5</v>
       </c>
       <c r="AH128" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="AI128" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
     </row>
     <row r="129" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="E129">
         <v>8</v>
       </c>
       <c r="G129" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="M129" s="1">
         <v>0.35</v>
@@ -10002,7 +10045,7 @@
         <v>300</v>
       </c>
       <c r="AE129" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="AF129">
         <v>10000000</v>
@@ -10011,24 +10054,24 @@
         <v>1.5</v>
       </c>
       <c r="AH129" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="AI129" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
     </row>
     <row r="130" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="E130">
         <v>9</v>
       </c>
       <c r="G130" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="K130" s="1">
         <v>6</v>
@@ -10046,7 +10089,7 @@
         <v>394</v>
       </c>
       <c r="AE130" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="AF130">
         <v>10000000</v>
@@ -10055,30 +10098,30 @@
         <v>1.5</v>
       </c>
       <c r="AH130" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="AI130" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
     </row>
     <row r="131" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="E131">
         <v>10</v>
       </c>
       <c r="G131" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="X131" s="1">
         <v>300</v>
       </c>
       <c r="AE131" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="AF131">
         <v>10000000</v>
@@ -10087,24 +10130,24 @@
         <v>1.5</v>
       </c>
       <c r="AH131" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="AI131" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
     </row>
     <row r="132" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="E132">
         <v>1</v>
@@ -10116,7 +10159,7 @@
         <v>348</v>
       </c>
       <c r="V132" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W132" s="1">
         <v>0</v>
@@ -10125,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="AE132" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="AF132">
         <v>100000</v>
@@ -10134,24 +10177,24 @@
         <v>1.5</v>
       </c>
       <c r="AH132" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="AI132" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
     </row>
     <row r="133" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="E133">
         <v>2</v>
@@ -10163,7 +10206,7 @@
         <v>348</v>
       </c>
       <c r="V133" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W133" s="1">
         <v>0</v>
@@ -10172,7 +10215,7 @@
         <v>25</v>
       </c>
       <c r="AE133" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="AF133">
         <v>200000</v>
@@ -10181,24 +10224,24 @@
         <v>1.5</v>
       </c>
       <c r="AH133" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="AI133" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
     </row>
     <row r="134" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="E134">
         <v>3</v>
@@ -10210,7 +10253,7 @@
         <v>348</v>
       </c>
       <c r="V134" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W134" s="1">
         <v>0</v>
@@ -10219,7 +10262,7 @@
         <v>25</v>
       </c>
       <c r="AE134" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="AF134">
         <v>400000</v>
@@ -10228,24 +10271,24 @@
         <v>1.5</v>
       </c>
       <c r="AH134" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="AI134" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
     </row>
     <row r="135" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B135" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C135" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="C135" s="2" t="s">
-        <v>545</v>
-      </c>
       <c r="D135" s="1" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="E135">
         <v>4</v>
@@ -10257,7 +10300,7 @@
         <v>348</v>
       </c>
       <c r="V135" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W135" s="1">
         <v>0</v>
@@ -10266,7 +10309,7 @@
         <v>25</v>
       </c>
       <c r="AE135" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="AF135">
         <v>800000</v>
@@ -10275,24 +10318,24 @@
         <v>1.5</v>
       </c>
       <c r="AH135" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="AI135" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
     </row>
     <row r="136" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="E136">
         <v>5</v>
@@ -10304,7 +10347,7 @@
         <v>348</v>
       </c>
       <c r="V136" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W136" s="1">
         <v>0</v>
@@ -10313,7 +10356,7 @@
         <v>25</v>
       </c>
       <c r="AE136" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="AF136">
         <v>1500000</v>
@@ -10322,24 +10365,24 @@
         <v>1.5</v>
       </c>
       <c r="AH136" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="AI136" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
     </row>
     <row r="137" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="E137">
         <v>6</v>
@@ -10354,7 +10397,7 @@
         <v>348</v>
       </c>
       <c r="V137" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W137" s="1">
         <v>0</v>
@@ -10363,13 +10406,13 @@
         <v>25</v>
       </c>
       <c r="Z137" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="AB137" t="s">
         <v>297</v>
       </c>
       <c r="AE137" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="AF137">
         <v>3000000</v>
@@ -10378,24 +10421,24 @@
         <v>1.5</v>
       </c>
       <c r="AH137" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="AI137" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
     </row>
     <row r="138" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="E138">
         <v>7</v>
@@ -10407,7 +10450,7 @@
         <v>348</v>
       </c>
       <c r="V138" s="1" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="W138" s="1">
         <v>0</v>
@@ -10416,13 +10459,13 @@
         <v>25</v>
       </c>
       <c r="Z138" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="AB138" t="s">
         <v>297</v>
       </c>
       <c r="AE138" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="AF138">
         <v>5000000</v>
@@ -10431,30 +10474,30 @@
         <v>1.5</v>
       </c>
       <c r="AH138" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="AI138" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
     </row>
     <row r="139" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="E139">
         <v>8</v>
       </c>
       <c r="G139" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="X139" s="1">
         <v>300</v>
       </c>
       <c r="AE139" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="AF139">
         <v>10000000</v>
@@ -10463,36 +10506,36 @@
         <v>1.5</v>
       </c>
       <c r="AH139" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="AI139" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
     </row>
     <row r="140" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="E140">
         <v>9</v>
       </c>
       <c r="G140" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="X140" s="1">
         <v>300</v>
       </c>
       <c r="Z140" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="AB140" t="s">
         <v>285</v>
       </c>
       <c r="AE140" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="AF140">
         <v>10000000</v>
@@ -10501,30 +10544,30 @@
         <v>1.5</v>
       </c>
       <c r="AH140" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="AI140" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="141" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="E141">
         <v>10</v>
       </c>
       <c r="G141" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="X141" s="1">
         <v>300</v>
       </c>
       <c r="AE141" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="AF141">
         <v>10000000</v>
@@ -10533,24 +10576,24 @@
         <v>1.5</v>
       </c>
       <c r="AH141" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="AI141" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
     </row>
     <row r="142" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="E142">
         <v>1</v>
@@ -10568,7 +10611,7 @@
         <v>348</v>
       </c>
       <c r="V142" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W142" s="1">
         <v>15</v>
@@ -10580,13 +10623,13 @@
         <v>350</v>
       </c>
       <c r="AA142" t="s">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="AB142" t="s">
         <v>153</v>
       </c>
       <c r="AE142" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="AF142">
         <v>100000</v>
@@ -10595,24 +10638,24 @@
         <v>1.5</v>
       </c>
       <c r="AH142" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="AI142" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
     </row>
     <row r="143" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="E143">
         <v>2</v>
@@ -10624,7 +10667,7 @@
         <v>348</v>
       </c>
       <c r="V143" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W143" s="1">
         <v>15</v>
@@ -10642,24 +10685,24 @@
         <v>1.5</v>
       </c>
       <c r="AH143" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="AI143" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
     </row>
     <row r="144" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>580</v>
-      </c>
       <c r="D144" s="1" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="E144">
         <v>3</v>
@@ -10671,7 +10714,7 @@
         <v>348</v>
       </c>
       <c r="V144" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W144" s="1">
         <v>15</v>
@@ -10680,7 +10723,7 @@
         <v>40</v>
       </c>
       <c r="AE144" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AF144">
         <v>400000</v>
@@ -10689,24 +10732,24 @@
         <v>1.5</v>
       </c>
       <c r="AH144" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="AI144" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="145" spans="1:35" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="145" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="E145">
         <v>4</v>
@@ -10718,7 +10761,7 @@
         <v>348</v>
       </c>
       <c r="V145" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W145" s="1">
         <v>15</v>
@@ -10736,24 +10779,24 @@
         <v>1.5</v>
       </c>
       <c r="AH145" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="AI145" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="146" spans="1:35" x14ac:dyDescent="0.3">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="146" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="E146">
         <v>5</v>
@@ -10768,7 +10811,7 @@
         <v>348</v>
       </c>
       <c r="V146" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W146" s="1">
         <v>15</v>
@@ -10780,7 +10823,7 @@
         <v>153</v>
       </c>
       <c r="AE146" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="AF146">
         <v>1500000</v>
@@ -10789,24 +10832,24 @@
         <v>1.5</v>
       </c>
       <c r="AH146" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="AI146" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="147" spans="1:35" x14ac:dyDescent="0.3">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="147" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="E147">
         <v>6</v>
@@ -10818,7 +10861,7 @@
         <v>348</v>
       </c>
       <c r="V147" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W147" s="1">
         <v>15</v>
@@ -10827,7 +10870,7 @@
         <v>40</v>
       </c>
       <c r="AC147" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="AE147" t="s">
         <v>89</v>
@@ -10839,24 +10882,24 @@
         <v>1.5</v>
       </c>
       <c r="AH147" t="s">
-        <v>988</v>
+        <v>968</v>
       </c>
       <c r="AI147" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="148" spans="1:35" x14ac:dyDescent="0.3">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="148" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="E148">
         <v>7</v>
@@ -10868,7 +10911,7 @@
         <v>348</v>
       </c>
       <c r="V148" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W148" s="1">
         <v>15</v>
@@ -10877,7 +10920,7 @@
         <v>40</v>
       </c>
       <c r="AE148" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="AF148">
         <v>5000000</v>
@@ -10886,24 +10929,24 @@
         <v>1.5</v>
       </c>
       <c r="AH148" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="AI148" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="149" spans="1:35" x14ac:dyDescent="0.3">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="149" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="E149">
         <v>8</v>
       </c>
       <c r="G149" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="M149" s="1">
         <v>1</v>
@@ -10924,24 +10967,24 @@
         <v>1.5</v>
       </c>
       <c r="AH149" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="AI149" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="150" spans="1:35" x14ac:dyDescent="0.3">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="150" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="E150">
         <v>9</v>
       </c>
       <c r="G150" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="K150" s="1">
         <v>30</v>
@@ -10950,16 +10993,16 @@
         <v>300</v>
       </c>
       <c r="AA150" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="AB150" t="s">
         <v>153</v>
       </c>
       <c r="AC150" t="s">
+        <v>579</v>
+      </c>
+      <c r="AE150" t="s">
         <v>588</v>
-      </c>
-      <c r="AE150" t="s">
-        <v>597</v>
       </c>
       <c r="AF150">
         <v>10000000</v>
@@ -10968,24 +11011,24 @@
         <v>1.5</v>
       </c>
       <c r="AH150" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="AI150" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="151" spans="1:35" x14ac:dyDescent="0.3">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="151" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="E151">
         <v>10</v>
       </c>
       <c r="G151" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="K151" s="1">
         <v>30</v>
@@ -10997,13 +11040,13 @@
         <v>300</v>
       </c>
       <c r="AA151" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="AB151" t="s">
         <v>153</v>
       </c>
       <c r="AE151" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="AF151">
         <v>10000000</v>
@@ -11012,24 +11055,24 @@
         <v>1.5</v>
       </c>
       <c r="AH151" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="AI151" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="152" spans="1:35" x14ac:dyDescent="0.3">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="152" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E152">
         <v>1</v>
@@ -11047,7 +11090,7 @@
         <v>348</v>
       </c>
       <c r="V152" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W152" s="1">
         <v>15</v>
@@ -11058,18 +11101,14 @@
       <c r="Y152" t="s">
         <v>350</v>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>bolt-thunderstrike-bluewhite</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>hit-thunderstrike-bluewhite</t>
-        </is>
+      <c r="Z152" t="s">
+        <v>980</v>
+      </c>
+      <c r="AB152" t="s">
+        <v>981</v>
       </c>
       <c r="AE152" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="AF152">
         <v>100000</v>
@@ -11078,24 +11117,24 @@
         <v>1.5</v>
       </c>
       <c r="AH152" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="AI152" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="153" spans="1:35" x14ac:dyDescent="0.3">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="153" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E153">
         <v>2</v>
@@ -11107,7 +11146,7 @@
         <v>348</v>
       </c>
       <c r="V153" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W153" s="1">
         <v>15</v>
@@ -11116,7 +11155,7 @@
         <v>40</v>
       </c>
       <c r="AE153" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AF153">
         <v>200000</v>
@@ -11125,24 +11164,24 @@
         <v>1.5</v>
       </c>
       <c r="AH153" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="AI153" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="154" spans="1:35" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="154" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E154">
         <v>3</v>
@@ -11154,7 +11193,7 @@
         <v>348</v>
       </c>
       <c r="V154" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W154" s="1">
         <v>15</v>
@@ -11163,7 +11202,7 @@
         <v>40</v>
       </c>
       <c r="AE154" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AF154">
         <v>400000</v>
@@ -11172,24 +11211,24 @@
         <v>1.5</v>
       </c>
       <c r="AH154" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="AI154" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="155" spans="1:35" x14ac:dyDescent="0.3">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="155" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>612</v>
-      </c>
       <c r="D155" s="1" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E155">
         <v>4</v>
@@ -11201,7 +11240,7 @@
         <v>348</v>
       </c>
       <c r="V155" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W155" s="1">
         <v>15</v>
@@ -11219,24 +11258,24 @@
         <v>1.5</v>
       </c>
       <c r="AH155" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="AI155" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="156" spans="1:35" x14ac:dyDescent="0.3">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="156" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E156">
         <v>5</v>
@@ -11251,7 +11290,7 @@
         <v>348</v>
       </c>
       <c r="V156" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W156" s="1">
         <v>15</v>
@@ -11260,7 +11299,7 @@
         <v>40</v>
       </c>
       <c r="AE156" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="AF156">
         <v>1500000</v>
@@ -11269,24 +11308,24 @@
         <v>1.5</v>
       </c>
       <c r="AH156" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="AI156" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="157" spans="1:35" x14ac:dyDescent="0.3">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="157" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E157">
         <v>6</v>
@@ -11298,7 +11337,7 @@
         <v>348</v>
       </c>
       <c r="V157" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W157" s="1">
         <v>15</v>
@@ -11307,7 +11346,7 @@
         <v>40</v>
       </c>
       <c r="AE157" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="AF157">
         <v>3000000</v>
@@ -11316,24 +11355,24 @@
         <v>1.5</v>
       </c>
       <c r="AH157" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="AI157" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="158" spans="1:35" x14ac:dyDescent="0.3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="158" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E158">
         <v>7</v>
@@ -11348,7 +11387,7 @@
         <v>348</v>
       </c>
       <c r="V158" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W158" s="1">
         <v>15</v>
@@ -11357,7 +11396,7 @@
         <v>40</v>
       </c>
       <c r="AE158" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="AF158">
         <v>5000000</v>
@@ -11366,24 +11405,24 @@
         <v>1.5</v>
       </c>
       <c r="AH158" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="AI158" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="159" spans="1:35" x14ac:dyDescent="0.3">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="159" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="E159">
         <v>8</v>
       </c>
       <c r="G159" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="Q159" s="1">
         <v>3</v>
@@ -11392,15 +11431,13 @@
         <v>300</v>
       </c>
       <c r="Z159" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="AC159" t="s">
-        <v>626</v>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>{"count":2,"countPer":0.2,"pct":300,"pctPer":30}</t>
-        </is>
+        <v>617</v>
+      </c>
+      <c r="AE159" t="s">
+        <v>982</v>
       </c>
       <c r="AF159">
         <v>10000000</v>
@@ -11408,32 +11445,28 @@
       <c r="AG159">
         <v>1.5</v>
       </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>施放落雷術時同時召喚橫向與直向各 {count} 道雷幕橫掃全場（每道寬 {wid} 米、{speed} 米／秒，相鄰兩道由反方向交錯掃過），對掃過的所有敵人各造成 1 次 {pct}% 雷電傷害</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>施放落雷術時同時召喚橫向與直向各 {count} 道雷幕橫掃全場（每道寬 {wid} 米、{speed} 米／秒，相鄰兩道由反方向交錯掃過），對掃過的所有敵人各造成 1 次 {pct}% 雷電傷害</t>
-        </is>
+      <c r="AH159" t="s">
+        <v>983</v>
+      </c>
+      <c r="AI159" t="s">
+        <v>983</v>
       </c>
       <c r="AJ159">
         <v>30</v>
       </c>
     </row>
-    <row r="160" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="E160">
         <v>9</v>
       </c>
       <c r="G160" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="K160" s="1">
         <v>30</v>
@@ -11451,7 +11484,7 @@
         <v>184</v>
       </c>
       <c r="AE160" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="AF160">
         <v>10000000</v>
@@ -11460,24 +11493,24 @@
         <v>1.5</v>
       </c>
       <c r="AH160" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="AI160" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="161" spans="1:35" x14ac:dyDescent="0.3">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="161" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="E161">
         <v>10</v>
       </c>
       <c r="G161" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="M161" s="1">
         <v>1</v>
@@ -11498,24 +11531,24 @@
         <v>1.5</v>
       </c>
       <c r="AH161" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="AI161" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="162" spans="1:35" x14ac:dyDescent="0.3">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="162" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="E162">
         <v>1</v>
@@ -11524,7 +11557,7 @@
         <v>174</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="I162" s="1">
         <v>30</v>
@@ -11539,7 +11572,7 @@
         <v>348</v>
       </c>
       <c r="V162" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W162" s="1">
         <v>15</v>
@@ -11554,12 +11587,10 @@
         <v>153</v>
       </c>
       <c r="AD162" t="s">
-        <v>971</v>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>{"pct":50,"pctPer":5,"count":2,"sec":2}</t>
-        </is>
+        <v>951</v>
+      </c>
+      <c r="AE162" t="s">
+        <v>984</v>
       </c>
       <c r="AF162">
         <v>100000</v>
@@ -11568,27 +11599,27 @@
         <v>1.5</v>
       </c>
       <c r="AH162" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="AI162" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="AJ162" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="E163">
         <v>2</v>
@@ -11597,13 +11628,13 @@
         <v>212</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="U163" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V163" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W163" s="1">
         <v>15</v>
@@ -11612,7 +11643,7 @@
         <v>40</v>
       </c>
       <c r="AE163" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="AF163">
         <v>200000</v>
@@ -11621,24 +11652,24 @@
         <v>1.5</v>
       </c>
       <c r="AH163" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="AI163" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="164" spans="1:35" x14ac:dyDescent="0.3">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="164" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="E164">
         <v>3</v>
@@ -11647,13 +11678,13 @@
         <v>217</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="U164" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V164" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W164" s="1">
         <v>15</v>
@@ -11662,7 +11693,7 @@
         <v>40</v>
       </c>
       <c r="AE164" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AF164">
         <v>400000</v>
@@ -11671,24 +11702,24 @@
         <v>1.5</v>
       </c>
       <c r="AH164" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="AI164" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="165" spans="1:35" x14ac:dyDescent="0.3">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="165" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="E165">
         <v>4</v>
@@ -11697,7 +11728,7 @@
         <v>255</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="K165" s="1">
         <v>8</v>
@@ -11706,7 +11737,7 @@
         <v>348</v>
       </c>
       <c r="V165" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W165" s="1">
         <v>15</v>
@@ -11715,16 +11746,16 @@
         <v>40</v>
       </c>
       <c r="AA165" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="AB165" t="s">
         <v>153</v>
       </c>
       <c r="AC165" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="AE165" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="AF165">
         <v>800000</v>
@@ -11733,24 +11764,24 @@
         <v>1.5</v>
       </c>
       <c r="AH165" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="AI165" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="166" spans="1:35" x14ac:dyDescent="0.3">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="166" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="E166">
         <v>5</v>
@@ -11759,13 +11790,13 @@
         <v>292</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="U166" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V166" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W166" s="1">
         <v>15</v>
@@ -11774,7 +11805,7 @@
         <v>40</v>
       </c>
       <c r="AE166" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="AF166">
         <v>1500000</v>
@@ -11783,24 +11814,24 @@
         <v>1.5</v>
       </c>
       <c r="AH166" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="AI166" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="167" spans="1:35" x14ac:dyDescent="0.3">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="167" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="E167">
         <v>6</v>
@@ -11809,13 +11840,13 @@
         <v>326</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="U167" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V167" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W167" s="1">
         <v>15</v>
@@ -11827,10 +11858,10 @@
         <v>153</v>
       </c>
       <c r="AD167" t="s">
-        <v>971</v>
+        <v>951</v>
       </c>
       <c r="AE167" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="AF167">
         <v>3000000</v>
@@ -11839,24 +11870,24 @@
         <v>1.5</v>
       </c>
       <c r="AH167" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="AI167" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="168" spans="1:35" x14ac:dyDescent="0.3">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="168" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="E168">
         <v>7</v>
@@ -11865,7 +11896,7 @@
         <v>330</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="K168" s="1">
         <v>15</v>
@@ -11874,7 +11905,7 @@
         <v>348</v>
       </c>
       <c r="V168" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="W168" s="1">
         <v>15</v>
@@ -11882,26 +11913,20 @@
       <c r="X168" s="1">
         <v>40</v>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>hit-thunderfall-impact</t>
-        </is>
-      </c>
-      <c r="AA168" t="inlineStr">
-        <is>
-          <t>proj-thunderfall-sky</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>hit-thunderfall-impact</t>
-        </is>
+      <c r="Z168" t="s">
+        <v>985</v>
+      </c>
+      <c r="AA168" t="s">
+        <v>986</v>
+      </c>
+      <c r="AB168" t="s">
+        <v>985</v>
       </c>
       <c r="AC168" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="AE168" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="AF168">
         <v>5000000</v>
@@ -11910,30 +11935,30 @@
         <v>1.5</v>
       </c>
       <c r="AH168" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="AI168" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="169" spans="1:35" x14ac:dyDescent="0.3">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="169" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="E169">
         <v>8</v>
       </c>
       <c r="G169" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="X169" s="1">
         <v>300</v>
       </c>
       <c r="AE169" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="AF169">
         <v>10000000</v>
@@ -11942,24 +11967,24 @@
         <v>1.5</v>
       </c>
       <c r="AH169" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="AI169" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="170" spans="1:35" x14ac:dyDescent="0.3">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="170" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="E170">
         <v>9</v>
       </c>
       <c r="G170" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="K170" s="1">
         <v>12</v>
@@ -11971,7 +11996,7 @@
         <v>153</v>
       </c>
       <c r="AE170" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="AF170">
         <v>10000000</v>
@@ -11980,24 +12005,24 @@
         <v>1.5</v>
       </c>
       <c r="AH170" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="AI170" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="171" spans="1:35" x14ac:dyDescent="0.3">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="171" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="E171">
         <v>10</v>
       </c>
       <c r="G171" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="M171" s="1">
         <v>1</v>
@@ -12006,7 +12031,7 @@
         <v>300</v>
       </c>
       <c r="AE171" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="AF171">
         <v>10000000</v>
@@ -12015,24 +12040,24 @@
         <v>1.5</v>
       </c>
       <c r="AH171" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="AI171" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="172" spans="1:35" x14ac:dyDescent="0.3">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="172" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="E172">
         <v>1</v>
@@ -12050,7 +12075,7 @@
         <v>348</v>
       </c>
       <c r="V172" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W172" s="1">
         <v>15</v>
@@ -12061,20 +12086,14 @@
       <c r="Y172" t="s">
         <v>350</v>
       </c>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t>proj-icearrow-frost</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>hit-icearrow-shatter</t>
-        </is>
-      </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t>{"pct":250,"pctPer":25,"count":2}</t>
-        </is>
+      <c r="AA172" t="s">
+        <v>987</v>
+      </c>
+      <c r="AB172" t="s">
+        <v>988</v>
+      </c>
+      <c r="AE172" t="s">
+        <v>989</v>
       </c>
       <c r="AF172">
         <v>100000</v>
@@ -12083,27 +12102,27 @@
         <v>1.5</v>
       </c>
       <c r="AH172" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="AI172" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="AJ172" s="1">
         <v>58.5</v>
       </c>
     </row>
-    <row r="173" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="E173">
         <v>2</v>
@@ -12115,7 +12134,7 @@
         <v>348</v>
       </c>
       <c r="V173" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W173" s="1">
         <v>15</v>
@@ -12124,10 +12143,10 @@
         <v>40</v>
       </c>
       <c r="AB173" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="AE173" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="AF173">
         <v>200000</v>
@@ -12136,24 +12155,24 @@
         <v>1.5</v>
       </c>
       <c r="AH173" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="AI173" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="174" spans="1:35" x14ac:dyDescent="0.3">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="174" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="E174">
         <v>3</v>
@@ -12165,7 +12184,7 @@
         <v>348</v>
       </c>
       <c r="V174" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W174" s="1">
         <v>15</v>
@@ -12183,24 +12202,24 @@
         <v>1.5</v>
       </c>
       <c r="AH174" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="AI174" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="175" spans="1:35" x14ac:dyDescent="0.3">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="175" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C175" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="B175" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>687</v>
-      </c>
       <c r="D175" s="1" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="E175">
         <v>4</v>
@@ -12218,7 +12237,7 @@
         <v>348</v>
       </c>
       <c r="V175" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W175" s="1">
         <v>15</v>
@@ -12226,15 +12245,11 @@
       <c r="X175" s="1">
         <v>40</v>
       </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>proj-icearrow-frost</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>hit-icearrow-shatter</t>
-        </is>
+      <c r="AA175" t="s">
+        <v>987</v>
+      </c>
+      <c r="AB175" t="s">
+        <v>988</v>
       </c>
       <c r="AE175" t="s">
         <v>62</v>
@@ -12246,24 +12261,24 @@
         <v>1.5</v>
       </c>
       <c r="AH175" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="AI175" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="176" spans="1:35" x14ac:dyDescent="0.3">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="176" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="E176">
         <v>5</v>
@@ -12275,7 +12290,7 @@
         <v>348</v>
       </c>
       <c r="V176" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W176" s="1">
         <v>15</v>
@@ -12283,13 +12298,8 @@
       <c r="X176" s="1">
         <v>40</v>
       </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>ground-icearrow-frost</t>
-        </is>
-      </c>
       <c r="AE176" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AF176">
         <v>1500000</v>
@@ -12298,24 +12308,24 @@
         <v>1.5</v>
       </c>
       <c r="AH176" t="s">
-        <v>691</v>
+        <v>676</v>
       </c>
       <c r="AI176" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="177" spans="1:35" x14ac:dyDescent="0.3">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="177" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="E177">
         <v>6</v>
@@ -12327,7 +12337,7 @@
         <v>348</v>
       </c>
       <c r="V177" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W177" s="1">
         <v>15</v>
@@ -12336,7 +12346,7 @@
         <v>40</v>
       </c>
       <c r="AE177" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="AF177">
         <v>3000000</v>
@@ -12345,30 +12355,30 @@
         <v>1.5</v>
       </c>
       <c r="AH177" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="AI177" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="178" spans="1:35" x14ac:dyDescent="0.3">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="178" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>695</v>
+        <v>680</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="E178">
         <v>7</v>
       </c>
       <c r="F178" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="K178" s="1">
         <v>6</v>
@@ -12380,7 +12390,7 @@
         <v>348</v>
       </c>
       <c r="V178" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W178" s="1">
         <v>15</v>
@@ -12388,16 +12398,17 @@
       <c r="X178" s="1">
         <v>40</v>
       </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>burst-icearrow-crystal</t>
-        </is>
+      <c r="Z178" t="s">
+        <v>991</v>
       </c>
       <c r="AB178" t="s">
-        <v>678</v>
+        <v>665</v>
+      </c>
+      <c r="AC178" t="s">
+        <v>990</v>
       </c>
       <c r="AE178" t="s">
-        <v>698</v>
+        <v>682</v>
       </c>
       <c r="AF178">
         <v>5000000</v>
@@ -12406,30 +12417,30 @@
         <v>1.5</v>
       </c>
       <c r="AH178" t="s">
-        <v>699</v>
+        <v>683</v>
       </c>
       <c r="AI178" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="179" spans="1:35" x14ac:dyDescent="0.3">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="179" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>700</v>
+        <v>684</v>
       </c>
       <c r="E179">
         <v>8</v>
       </c>
       <c r="G179" t="s">
-        <v>701</v>
+        <v>685</v>
       </c>
       <c r="X179" s="1">
         <v>300</v>
       </c>
       <c r="AE179" t="s">
-        <v>702</v>
+        <v>686</v>
       </c>
       <c r="AF179">
         <v>10000000</v>
@@ -12438,30 +12449,30 @@
         <v>1.5</v>
       </c>
       <c r="AH179" t="s">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="AI179" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="180" spans="1:35" x14ac:dyDescent="0.3">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="180" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>704</v>
+        <v>688</v>
       </c>
       <c r="E180">
         <v>9</v>
       </c>
       <c r="G180" t="s">
-        <v>705</v>
+        <v>689</v>
       </c>
       <c r="X180" s="1">
         <v>300</v>
       </c>
       <c r="AE180" t="s">
-        <v>706</v>
+        <v>690</v>
       </c>
       <c r="AF180">
         <v>10000000</v>
@@ -12470,24 +12481,24 @@
         <v>1.5</v>
       </c>
       <c r="AH180" t="s">
-        <v>707</v>
+        <v>691</v>
       </c>
       <c r="AI180" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="181" spans="1:35" x14ac:dyDescent="0.3">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="181" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>708</v>
+        <v>692</v>
       </c>
       <c r="E181">
         <v>10</v>
       </c>
       <c r="G181" t="s">
-        <v>709</v>
+        <v>693</v>
       </c>
       <c r="K181" s="1">
         <v>30</v>
@@ -12498,18 +12509,14 @@
       <c r="X181" s="1">
         <v>300</v>
       </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>proj-icearrow-frost</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>hit-icearrow-shatter</t>
-        </is>
+      <c r="AA181" t="s">
+        <v>987</v>
+      </c>
+      <c r="AB181" t="s">
+        <v>988</v>
       </c>
       <c r="AE181" t="s">
-        <v>710</v>
+        <v>694</v>
       </c>
       <c r="AF181">
         <v>10000000</v>
@@ -12518,24 +12525,24 @@
         <v>1.5</v>
       </c>
       <c r="AH181" t="s">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="AI181" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="182" spans="1:35" x14ac:dyDescent="0.3">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="182" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="E182">
         <v>1</v>
@@ -12546,14 +12553,14 @@
       <c r="I182" s="1">
         <v>30</v>
       </c>
-      <c r="K182" t="n">
+      <c r="K182">
         <v>6</v>
       </c>
       <c r="U182" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V182" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W182" s="1">
         <v>15</v>
@@ -12564,18 +12571,14 @@
       <c r="Y182" t="s">
         <v>350</v>
       </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>proj-waterball-flow</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>hit-waterball-splash</t>
-        </is>
+      <c r="AA182" t="s">
+        <v>992</v>
+      </c>
+      <c r="AB182" t="s">
+        <v>993</v>
       </c>
       <c r="AE182" t="s">
-        <v>716</v>
+        <v>699</v>
       </c>
       <c r="AF182">
         <v>100000</v>
@@ -12583,32 +12586,28 @@
       <c r="AG182">
         <v>1.5</v>
       </c>
-      <c r="AH182" t="inlineStr">
-        <is>
-          <t>朝敵人起飛時的座標拋出水彈（射程 {castM} 米、弧高 {arcM} 米），途中不追蹤；落地時對落點半徑 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
-        </is>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>朝敵人起飛時的座標拋出水彈（射程 {castM} 米、弧高 {arcM} 米），途中不追蹤；落地時對落點半徑 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
-        </is>
-      </c>
-      <c r="AJ182" s="1" t="n">
+      <c r="AH182" t="s">
+        <v>994</v>
+      </c>
+      <c r="AI182" t="s">
+        <v>994</v>
+      </c>
+      <c r="AJ182" s="1">
         <v>57.96</v>
       </c>
     </row>
-    <row r="183" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>718</v>
+        <v>700</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="E183">
         <v>2</v>
@@ -12620,7 +12619,7 @@
         <v>348</v>
       </c>
       <c r="V183" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W183" s="1">
         <v>15</v>
@@ -12629,7 +12628,7 @@
         <v>40</v>
       </c>
       <c r="AE183" t="s">
-        <v>719</v>
+        <v>701</v>
       </c>
       <c r="AF183">
         <v>200000</v>
@@ -12638,24 +12637,24 @@
         <v>1.5</v>
       </c>
       <c r="AH183" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="AI183" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="184" spans="1:35" x14ac:dyDescent="0.3">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="184" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="E184">
         <v>3</v>
@@ -12667,7 +12666,7 @@
         <v>348</v>
       </c>
       <c r="V184" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W184" s="1">
         <v>15</v>
@@ -12676,7 +12675,7 @@
         <v>40</v>
       </c>
       <c r="AE184" t="s">
-        <v>722</v>
+        <v>704</v>
       </c>
       <c r="AF184">
         <v>400000</v>
@@ -12685,24 +12684,24 @@
         <v>1.5</v>
       </c>
       <c r="AH184" t="s">
-        <v>723</v>
+        <v>705</v>
       </c>
       <c r="AI184" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="185" spans="1:35" x14ac:dyDescent="0.3">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="185" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="E185">
         <v>4</v>
@@ -12710,14 +12709,14 @@
       <c r="F185" t="s">
         <v>326</v>
       </c>
-      <c r="K185" s="1" t="n">
+      <c r="K185" s="1">
         <v>6</v>
       </c>
       <c r="U185" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V185" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W185" s="1">
         <v>15</v>
@@ -12726,20 +12725,16 @@
         <v>40</v>
       </c>
       <c r="Z185" t="s">
-        <v>725</v>
-      </c>
-      <c r="AA185" t="inlineStr">
-        <is>
-          <t>proj-waterball-flow</t>
-        </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>hit-waterball-splash</t>
-        </is>
+        <v>707</v>
+      </c>
+      <c r="AA185" t="s">
+        <v>992</v>
+      </c>
+      <c r="AB185" t="s">
+        <v>993</v>
       </c>
       <c r="AE185" t="s">
-        <v>726</v>
+        <v>708</v>
       </c>
       <c r="AF185">
         <v>800000</v>
@@ -12747,29 +12742,25 @@
       <c r="AG185">
         <v>1.5</v>
       </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>水流彈落地後再彈射 {bounce} 次（不足 1 次以機率觸發）；每次起飛重新鎖定敵人當下座標，途中不追蹤，落地造成半徑 {m} 米範圍傷害</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>水流彈落地後再彈射 {bounce} 次（不足 1 次以機率觸發）；每次起飛重新鎖定敵人當下座標，途中不追蹤，落地造成半徑 {m} 米範圍傷害</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AH185" t="s">
+        <v>995</v>
+      </c>
+      <c r="AI185" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="186" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>728</v>
+        <v>709</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="E186">
         <v>5</v>
@@ -12784,7 +12775,7 @@
         <v>348</v>
       </c>
       <c r="V186" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W186" s="1">
         <v>15</v>
@@ -12793,13 +12784,13 @@
         <v>40</v>
       </c>
       <c r="AA186" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="AB186" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="AE186" t="s">
-        <v>729</v>
+        <v>710</v>
       </c>
       <c r="AF186">
         <v>1500000</v>
@@ -12808,36 +12799,36 @@
         <v>1.5</v>
       </c>
       <c r="AH186" t="s">
-        <v>730</v>
+        <v>711</v>
       </c>
       <c r="AI186" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="187" spans="1:35" x14ac:dyDescent="0.3">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="187" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="B187" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>731</v>
-      </c>
       <c r="D187" s="1" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="E187">
         <v>6</v>
       </c>
       <c r="F187" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="U187" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V187" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W187" s="1">
         <v>15</v>
@@ -12855,30 +12846,30 @@
         <v>1.5</v>
       </c>
       <c r="AH187" t="s">
-        <v>732</v>
+        <v>713</v>
       </c>
       <c r="AI187" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="188" spans="1:35" x14ac:dyDescent="0.3">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="188" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>733</v>
+        <v>714</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="E188">
         <v>7</v>
       </c>
       <c r="F188" t="s">
-        <v>734</v>
+        <v>715</v>
       </c>
       <c r="K188" s="1">
         <v>5</v>
@@ -12890,7 +12881,7 @@
         <v>348</v>
       </c>
       <c r="V188" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W188" s="1">
         <v>15</v>
@@ -12899,10 +12890,10 @@
         <v>40</v>
       </c>
       <c r="AD188" t="s">
-        <v>989</v>
+        <v>969</v>
       </c>
       <c r="AE188" t="s">
-        <v>736</v>
+        <v>717</v>
       </c>
       <c r="AF188">
         <v>5000000</v>
@@ -12911,24 +12902,24 @@
         <v>1.5</v>
       </c>
       <c r="AH188" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="AI188" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="189" spans="1:35" x14ac:dyDescent="0.3">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="189" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>738</v>
+        <v>719</v>
       </c>
       <c r="E189">
         <v>8</v>
       </c>
       <c r="G189" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="K189" s="1">
         <v>20</v>
@@ -12937,10 +12928,10 @@
         <v>300</v>
       </c>
       <c r="AC189" t="s">
-        <v>740</v>
+        <v>721</v>
       </c>
       <c r="AE189" t="s">
-        <v>741</v>
+        <v>722</v>
       </c>
       <c r="AF189">
         <v>10000000</v>
@@ -12949,24 +12940,24 @@
         <v>1.5</v>
       </c>
       <c r="AH189" t="s">
-        <v>742</v>
+        <v>723</v>
       </c>
       <c r="AI189" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="190" spans="1:35" x14ac:dyDescent="0.3">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="190" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>743</v>
+        <v>724</v>
       </c>
       <c r="E190">
         <v>9</v>
       </c>
       <c r="G190" t="s">
-        <v>744</v>
+        <v>725</v>
       </c>
       <c r="K190" s="1">
         <v>20</v>
@@ -12975,10 +12966,10 @@
         <v>300</v>
       </c>
       <c r="AC190" t="s">
-        <v>735</v>
+        <v>716</v>
       </c>
       <c r="AE190" t="s">
-        <v>745</v>
+        <v>726</v>
       </c>
       <c r="AF190">
         <v>10000000</v>
@@ -12987,24 +12978,24 @@
         <v>1.5</v>
       </c>
       <c r="AH190" t="s">
-        <v>746</v>
+        <v>727</v>
       </c>
       <c r="AI190" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="191" spans="1:35" x14ac:dyDescent="0.3">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="191" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="E191">
         <v>10</v>
       </c>
       <c r="G191" t="s">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="K191" s="1">
         <v>30</v>
@@ -13016,13 +13007,13 @@
         <v>300</v>
       </c>
       <c r="AB191" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="AC191" t="s">
-        <v>740</v>
+        <v>721</v>
       </c>
       <c r="AE191" t="s">
-        <v>749</v>
+        <v>730</v>
       </c>
       <c r="AF191">
         <v>10000000</v>
@@ -13031,24 +13022,24 @@
         <v>1.5</v>
       </c>
       <c r="AH191" t="s">
-        <v>750</v>
+        <v>731</v>
       </c>
       <c r="AI191" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="192" spans="1:35" x14ac:dyDescent="0.3">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="192" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E192">
         <v>1</v>
@@ -13066,7 +13057,7 @@
         <v>348</v>
       </c>
       <c r="V192" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W192" s="1">
         <v>15</v>
@@ -13078,13 +13069,13 @@
         <v>350</v>
       </c>
       <c r="Z192" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="AB192" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="AE192" t="s">
-        <v>754</v>
+        <v>735</v>
       </c>
       <c r="AF192">
         <v>100000</v>
@@ -13093,24 +13084,24 @@
         <v>1.5</v>
       </c>
       <c r="AH192" t="s">
-        <v>755</v>
+        <v>736</v>
       </c>
       <c r="AI192" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="193" spans="1:35" x14ac:dyDescent="0.3">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="193" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>756</v>
+        <v>737</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E193">
         <v>2</v>
@@ -13134,7 +13125,7 @@
         <v>348</v>
       </c>
       <c r="V193" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W193" s="1">
         <v>15</v>
@@ -13152,24 +13143,24 @@
         <v>1.5</v>
       </c>
       <c r="AH193" t="s">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="AI193" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="194" spans="1:35" x14ac:dyDescent="0.3">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="194" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E194">
         <v>3</v>
@@ -13181,7 +13172,7 @@
         <v>348</v>
       </c>
       <c r="V194" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W194" s="1">
         <v>15</v>
@@ -13190,10 +13181,10 @@
         <v>40</v>
       </c>
       <c r="AB194" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="AE194" t="s">
-        <v>759</v>
+        <v>740</v>
       </c>
       <c r="AF194">
         <v>400000</v>
@@ -13202,24 +13193,24 @@
         <v>1.5</v>
       </c>
       <c r="AH194" t="s">
-        <v>760</v>
+        <v>741</v>
       </c>
       <c r="AI194" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="195" spans="1:35" x14ac:dyDescent="0.3">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="195" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E195">
         <v>4</v>
@@ -13231,7 +13222,7 @@
         <v>348</v>
       </c>
       <c r="V195" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W195" s="1">
         <v>15</v>
@@ -13240,13 +13231,13 @@
         <v>40</v>
       </c>
       <c r="Z195" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="AB195" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="AE195" t="s">
-        <v>763</v>
+        <v>744</v>
       </c>
       <c r="AF195">
         <v>800000</v>
@@ -13255,30 +13246,30 @@
         <v>1.5</v>
       </c>
       <c r="AH195" t="s">
-        <v>764</v>
+        <v>745</v>
       </c>
       <c r="AI195" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="196" spans="1:35" x14ac:dyDescent="0.3">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="196" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>765</v>
+        <v>746</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E196">
         <v>5</v>
       </c>
       <c r="F196" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="K196" s="1">
         <v>3</v>
@@ -13287,7 +13278,7 @@
         <v>348</v>
       </c>
       <c r="V196" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W196" s="1">
         <v>15</v>
@@ -13296,7 +13287,7 @@
         <v>40</v>
       </c>
       <c r="AE196" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="AF196">
         <v>1500000</v>
@@ -13305,36 +13296,36 @@
         <v>1.5</v>
       </c>
       <c r="AH196" t="s">
-        <v>766</v>
+        <v>747</v>
       </c>
       <c r="AI196" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="197" spans="1:35" x14ac:dyDescent="0.3">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="197" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>767</v>
+        <v>748</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E197">
         <v>6</v>
       </c>
       <c r="F197" t="s">
-        <v>734</v>
+        <v>715</v>
       </c>
       <c r="U197" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V197" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W197" s="1">
         <v>15</v>
@@ -13343,7 +13334,7 @@
         <v>40</v>
       </c>
       <c r="AE197" t="s">
-        <v>768</v>
+        <v>749</v>
       </c>
       <c r="AF197">
         <v>3000000</v>
@@ -13352,30 +13343,30 @@
         <v>1.5</v>
       </c>
       <c r="AH197" t="s">
-        <v>769</v>
+        <v>750</v>
       </c>
       <c r="AI197" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="198" spans="1:35" x14ac:dyDescent="0.3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="198" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="C198" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="B198" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>770</v>
-      </c>
       <c r="D198" s="1" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E198">
         <v>7</v>
       </c>
       <c r="F198" t="s">
-        <v>771</v>
+        <v>752</v>
       </c>
       <c r="M198" s="1">
         <v>0.4</v>
@@ -13384,7 +13375,7 @@
         <v>348</v>
       </c>
       <c r="V198" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="W198" s="1">
         <v>15</v>
@@ -13393,10 +13384,10 @@
         <v>40</v>
       </c>
       <c r="AC198" t="s">
-        <v>772</v>
+        <v>753</v>
       </c>
       <c r="AE198" t="s">
-        <v>773</v>
+        <v>754</v>
       </c>
       <c r="AF198">
         <v>5000000</v>
@@ -13405,24 +13396,24 @@
         <v>1.5</v>
       </c>
       <c r="AH198" t="s">
-        <v>774</v>
+        <v>755</v>
       </c>
       <c r="AI198" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="199" spans="1:35" x14ac:dyDescent="0.3">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="199" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>775</v>
+        <v>756</v>
       </c>
       <c r="E199">
         <v>8</v>
       </c>
       <c r="G199" t="s">
-        <v>776</v>
+        <v>757</v>
       </c>
       <c r="M199" s="1">
         <v>1</v>
@@ -13440,24 +13431,24 @@
         <v>1.5</v>
       </c>
       <c r="AH199" t="s">
-        <v>777</v>
+        <v>758</v>
       </c>
       <c r="AI199" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="200" spans="1:35" x14ac:dyDescent="0.3">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="200" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>778</v>
+        <v>759</v>
       </c>
       <c r="E200">
         <v>9</v>
       </c>
       <c r="G200" t="s">
-        <v>779</v>
+        <v>760</v>
       </c>
       <c r="K200" s="1">
         <v>8</v>
@@ -13469,10 +13460,10 @@
         <v>300</v>
       </c>
       <c r="AA200" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="AB200" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="AE200" t="s">
         <v>84</v>
@@ -13484,24 +13475,24 @@
         <v>1.5</v>
       </c>
       <c r="AH200" t="s">
-        <v>780</v>
+        <v>761</v>
       </c>
       <c r="AI200" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="201" spans="1:35" x14ac:dyDescent="0.3">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="201" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>781</v>
+        <v>762</v>
       </c>
       <c r="E201">
         <v>10</v>
       </c>
       <c r="G201" t="s">
-        <v>782</v>
+        <v>763</v>
       </c>
       <c r="K201" s="1">
         <v>8</v>
@@ -13513,10 +13504,10 @@
         <v>300</v>
       </c>
       <c r="AC201" t="s">
-        <v>735</v>
+        <v>716</v>
       </c>
       <c r="AE201" t="s">
-        <v>783</v>
+        <v>764</v>
       </c>
       <c r="AF201">
         <v>10000000</v>
@@ -13525,24 +13516,24 @@
         <v>1.5</v>
       </c>
       <c r="AH201" t="s">
-        <v>784</v>
+        <v>765</v>
       </c>
       <c r="AI201" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="202" spans="1:35" x14ac:dyDescent="0.3">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="202" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="E202">
         <v>1</v>
@@ -13551,7 +13542,7 @@
         <v>292</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="I202" s="1">
         <v>30</v>
@@ -13563,7 +13554,7 @@
         <v>348</v>
       </c>
       <c r="V202" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W202" s="1">
         <v>15</v>
@@ -13575,15 +13566,13 @@
         <v>350</v>
       </c>
       <c r="AA202" t="s">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="AB202" t="s">
-        <v>791</v>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>{"pct":200,"pctPer":20}</t>
-        </is>
+        <v>772</v>
+      </c>
+      <c r="AE202" t="s">
+        <v>84</v>
       </c>
       <c r="AF202">
         <v>100000</v>
@@ -13592,27 +13581,27 @@
         <v>1.5</v>
       </c>
       <c r="AH202" t="s">
-        <v>793</v>
+        <v>773</v>
       </c>
       <c r="AI202" t="s">
-        <v>793</v>
+        <v>773</v>
       </c>
       <c r="AJ202" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="E203">
         <v>2</v>
@@ -13621,13 +13610,13 @@
         <v>326</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="U203" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V203" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W203" s="1">
         <v>15</v>
@@ -13636,7 +13625,7 @@
         <v>40</v>
       </c>
       <c r="AE203" t="s">
-        <v>795</v>
+        <v>775</v>
       </c>
       <c r="AF203">
         <v>200000</v>
@@ -13645,24 +13634,24 @@
         <v>1.5</v>
       </c>
       <c r="AH203" t="s">
-        <v>796</v>
+        <v>776</v>
       </c>
       <c r="AI203" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="204" spans="1:35" x14ac:dyDescent="0.3">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="204" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>797</v>
+        <v>777</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="E204">
         <v>3</v>
@@ -13671,13 +13660,13 @@
         <v>330</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="U204" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V204" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W204" s="1">
         <v>15</v>
@@ -13686,7 +13675,7 @@
         <v>40</v>
       </c>
       <c r="AE204" t="s">
-        <v>798</v>
+        <v>778</v>
       </c>
       <c r="AF204">
         <v>400000</v>
@@ -13695,33 +13684,33 @@
         <v>1.5</v>
       </c>
       <c r="AH204" t="s">
-        <v>799</v>
+        <v>779</v>
       </c>
       <c r="AI204" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="205" spans="1:35" x14ac:dyDescent="0.3">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="205" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="E205">
         <v>4</v>
       </c>
       <c r="F205" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="S205" s="1">
         <v>30</v>
@@ -13730,7 +13719,7 @@
         <v>348</v>
       </c>
       <c r="V205" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W205" s="1">
         <v>15</v>
@@ -13739,13 +13728,13 @@
         <v>40</v>
       </c>
       <c r="AA205" t="s">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="AB205" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="AE205" t="s">
-        <v>801</v>
+        <v>781</v>
       </c>
       <c r="AF205">
         <v>800000</v>
@@ -13754,33 +13743,33 @@
         <v>1.5</v>
       </c>
       <c r="AH205" t="s">
-        <v>802</v>
+        <v>782</v>
       </c>
       <c r="AI205" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="206" spans="1:35" x14ac:dyDescent="0.3">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="206" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>803</v>
+        <v>783</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="E206">
         <v>5</v>
       </c>
       <c r="F206" t="s">
-        <v>734</v>
+        <v>715</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="M206" s="1">
         <v>0.1</v>
@@ -13789,7 +13778,7 @@
         <v>348</v>
       </c>
       <c r="V206" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W206" s="1">
         <v>15</v>
@@ -13798,13 +13787,13 @@
         <v>40</v>
       </c>
       <c r="AB206" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="AC206" t="s">
-        <v>804</v>
+        <v>784</v>
       </c>
       <c r="AE206" t="s">
-        <v>805</v>
+        <v>785</v>
       </c>
       <c r="AF206">
         <v>1500000</v>
@@ -13813,33 +13802,33 @@
         <v>1.5</v>
       </c>
       <c r="AH206" t="s">
-        <v>806</v>
+        <v>786</v>
       </c>
       <c r="AI206" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="207" spans="1:35" x14ac:dyDescent="0.3">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="207" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>807</v>
+        <v>787</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="E207">
         <v>6</v>
       </c>
       <c r="F207" t="s">
-        <v>771</v>
+        <v>752</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="K207" s="1">
         <v>6</v>
@@ -13854,7 +13843,7 @@
         <v>348</v>
       </c>
       <c r="V207" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W207" s="1">
         <v>15</v>
@@ -13863,13 +13852,13 @@
         <v>40</v>
       </c>
       <c r="Z207" t="s">
-        <v>808</v>
+        <v>788</v>
       </c>
       <c r="AB207" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="AE207" t="s">
-        <v>809</v>
+        <v>789</v>
       </c>
       <c r="AF207">
         <v>3000000</v>
@@ -13878,33 +13867,33 @@
         <v>1.5</v>
       </c>
       <c r="AH207" t="s">
-        <v>810</v>
+        <v>790</v>
       </c>
       <c r="AI207" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="208" spans="1:35" x14ac:dyDescent="0.3">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="208" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>811</v>
+        <v>791</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="E208">
         <v>7</v>
       </c>
       <c r="F208" t="s">
-        <v>812</v>
+        <v>792</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="M208" s="1">
         <v>0.2</v>
@@ -13913,7 +13902,7 @@
         <v>348</v>
       </c>
       <c r="V208" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W208" s="1">
         <v>15</v>
@@ -13922,7 +13911,7 @@
         <v>40</v>
       </c>
       <c r="AE208" t="s">
-        <v>813</v>
+        <v>793</v>
       </c>
       <c r="AF208">
         <v>5000000</v>
@@ -13931,36 +13920,36 @@
         <v>1.5</v>
       </c>
       <c r="AH208" t="s">
-        <v>814</v>
+        <v>794</v>
       </c>
       <c r="AI208" t="s">
-        <v>814</v>
+        <v>794</v>
       </c>
     </row>
     <row r="209" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>815</v>
+        <v>795</v>
       </c>
       <c r="E209">
         <v>8</v>
       </c>
       <c r="G209" t="s">
-        <v>816</v>
+        <v>796</v>
       </c>
       <c r="X209" s="1">
         <v>300</v>
       </c>
       <c r="AB209" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="AC209" t="s">
-        <v>804</v>
+        <v>784</v>
       </c>
       <c r="AE209" t="s">
-        <v>817</v>
+        <v>797</v>
       </c>
       <c r="AF209">
         <v>10000000</v>
@@ -13969,36 +13958,36 @@
         <v>1.5</v>
       </c>
       <c r="AH209" t="s">
-        <v>818</v>
+        <v>798</v>
       </c>
       <c r="AI209" t="s">
-        <v>818</v>
+        <v>798</v>
       </c>
     </row>
     <row r="210" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>819</v>
+        <v>799</v>
       </c>
       <c r="E210">
         <v>9</v>
       </c>
       <c r="G210" t="s">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="X210" s="1">
         <v>300</v>
       </c>
       <c r="AA210" t="s">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="AB210" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="AE210" t="s">
-        <v>821</v>
+        <v>801</v>
       </c>
       <c r="AF210">
         <v>10000000</v>
@@ -14007,30 +13996,30 @@
         <v>1.5</v>
       </c>
       <c r="AH210" t="s">
-        <v>822</v>
+        <v>802</v>
       </c>
       <c r="AI210" t="s">
-        <v>822</v>
+        <v>802</v>
       </c>
     </row>
     <row r="211" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>823</v>
+        <v>803</v>
       </c>
       <c r="E211">
         <v>10</v>
       </c>
       <c r="G211" t="s">
-        <v>824</v>
+        <v>804</v>
       </c>
       <c r="X211" s="1">
         <v>300</v>
       </c>
       <c r="AE211" t="s">
-        <v>825</v>
+        <v>805</v>
       </c>
       <c r="AF211">
         <v>10000000</v>
@@ -14039,24 +14028,24 @@
         <v>1.5</v>
       </c>
       <c r="AH211" t="s">
-        <v>826</v>
+        <v>806</v>
       </c>
       <c r="AI211" t="s">
-        <v>826</v>
+        <v>806</v>
       </c>
     </row>
     <row r="212" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>828</v>
+        <v>808</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>828</v>
+        <v>808</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>829</v>
+        <v>809</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -14074,7 +14063,7 @@
         <v>348</v>
       </c>
       <c r="V212" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W212" s="1">
         <v>15</v>
@@ -14086,10 +14075,10 @@
         <v>350</v>
       </c>
       <c r="Z212" t="s">
-        <v>830</v>
+        <v>810</v>
       </c>
       <c r="AB212" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="AE212" t="s">
         <v>375</v>
@@ -14101,24 +14090,24 @@
         <v>1.5</v>
       </c>
       <c r="AH212" t="s">
-        <v>831</v>
+        <v>811</v>
       </c>
       <c r="AI212" t="s">
-        <v>831</v>
+        <v>811</v>
       </c>
     </row>
     <row r="213" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>828</v>
+        <v>808</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>832</v>
+        <v>812</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>829</v>
+        <v>809</v>
       </c>
       <c r="E213">
         <v>2</v>
@@ -14130,7 +14119,7 @@
         <v>348</v>
       </c>
       <c r="V213" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W213" s="1">
         <v>15</v>
@@ -14138,13 +14127,11 @@
       <c r="X213" s="1">
         <v>40</v>
       </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>burst-vacuum-shockwave</t>
-        </is>
+      <c r="Z213" t="s">
+        <v>996</v>
       </c>
       <c r="AE213" t="s">
-        <v>833</v>
+        <v>813</v>
       </c>
       <c r="AF213">
         <v>200000</v>
@@ -14153,30 +14140,30 @@
         <v>1.5</v>
       </c>
       <c r="AH213" t="s">
-        <v>834</v>
+        <v>814</v>
       </c>
       <c r="AI213" t="s">
-        <v>834</v>
+        <v>814</v>
       </c>
     </row>
     <row r="214" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>828</v>
+        <v>808</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>835</v>
+        <v>815</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>829</v>
+        <v>809</v>
       </c>
       <c r="E214">
         <v>3</v>
       </c>
       <c r="F214" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="M214" s="1">
         <v>0.5</v>
@@ -14185,7 +14172,7 @@
         <v>348</v>
       </c>
       <c r="V214" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W214" s="1">
         <v>15</v>
@@ -14194,7 +14181,7 @@
         <v>40</v>
       </c>
       <c r="AE214" t="s">
-        <v>836</v>
+        <v>816</v>
       </c>
       <c r="AF214">
         <v>400000</v>
@@ -14203,30 +14190,30 @@
         <v>1.5</v>
       </c>
       <c r="AH214" t="s">
-        <v>837</v>
+        <v>817</v>
       </c>
       <c r="AI214" t="s">
-        <v>837</v>
+        <v>817</v>
       </c>
     </row>
     <row r="215" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>828</v>
+        <v>808</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>838</v>
+        <v>818</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>829</v>
+        <v>809</v>
       </c>
       <c r="E215">
         <v>4</v>
       </c>
       <c r="F215" t="s">
-        <v>734</v>
+        <v>715</v>
       </c>
       <c r="K215" s="1">
         <v>6</v>
@@ -14235,7 +14222,7 @@
         <v>348</v>
       </c>
       <c r="V215" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W215" s="1">
         <v>15</v>
@@ -14244,13 +14231,13 @@
         <v>40</v>
       </c>
       <c r="Z215" t="s">
-        <v>839</v>
+        <v>819</v>
       </c>
       <c r="AB215" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="AE215" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="AF215">
         <v>800000</v>
@@ -14259,30 +14246,30 @@
         <v>1.5</v>
       </c>
       <c r="AH215" t="s">
-        <v>840</v>
+        <v>820</v>
       </c>
       <c r="AI215" t="s">
-        <v>840</v>
+        <v>820</v>
       </c>
     </row>
     <row r="216" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>828</v>
+        <v>808</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>841</v>
+        <v>821</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>829</v>
+        <v>809</v>
       </c>
       <c r="E216">
         <v>5</v>
       </c>
       <c r="F216" t="s">
-        <v>771</v>
+        <v>752</v>
       </c>
       <c r="K216" s="1">
         <v>6</v>
@@ -14291,7 +14278,7 @@
         <v>348</v>
       </c>
       <c r="V216" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W216" s="1">
         <v>15</v>
@@ -14300,7 +14287,7 @@
         <v>40</v>
       </c>
       <c r="AE216" t="s">
-        <v>842</v>
+        <v>822</v>
       </c>
       <c r="AF216">
         <v>1500000</v>
@@ -14309,36 +14296,36 @@
         <v>1.5</v>
       </c>
       <c r="AH216" t="s">
-        <v>843</v>
+        <v>823</v>
       </c>
       <c r="AI216" t="s">
-        <v>843</v>
+        <v>823</v>
       </c>
     </row>
     <row r="217" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>828</v>
+        <v>808</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>844</v>
+        <v>824</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>829</v>
+        <v>809</v>
       </c>
       <c r="E217">
         <v>6</v>
       </c>
       <c r="F217" t="s">
-        <v>812</v>
+        <v>792</v>
       </c>
       <c r="U217" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V217" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W217" s="1">
         <v>15</v>
@@ -14347,7 +14334,7 @@
         <v>40</v>
       </c>
       <c r="AE217" t="s">
-        <v>845</v>
+        <v>825</v>
       </c>
       <c r="AF217">
         <v>3000000</v>
@@ -14356,30 +14343,30 @@
         <v>1.5</v>
       </c>
       <c r="AH217" t="s">
-        <v>846</v>
+        <v>826</v>
       </c>
       <c r="AI217" t="s">
-        <v>846</v>
+        <v>826</v>
       </c>
     </row>
     <row r="218" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C218" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>847</v>
-      </c>
       <c r="D218" s="1" t="s">
-        <v>829</v>
+        <v>809</v>
       </c>
       <c r="E218">
         <v>7</v>
       </c>
       <c r="F218" t="s">
-        <v>848</v>
+        <v>828</v>
       </c>
       <c r="K218" s="1">
         <v>6</v>
@@ -14388,7 +14375,7 @@
         <v>348</v>
       </c>
       <c r="V218" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W218" s="1">
         <v>15</v>
@@ -14397,19 +14384,19 @@
         <v>40</v>
       </c>
       <c r="Z218" t="s">
-        <v>808</v>
+        <v>788</v>
       </c>
       <c r="AA218" t="s">
-        <v>849</v>
+        <v>829</v>
       </c>
       <c r="AB218" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="AC218" t="s">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="AE218" t="s">
-        <v>851</v>
+        <v>831</v>
       </c>
       <c r="AF218">
         <v>5000000</v>
@@ -14418,24 +14405,24 @@
         <v>1.5</v>
       </c>
       <c r="AH218" t="s">
-        <v>852</v>
+        <v>832</v>
       </c>
       <c r="AI218" t="s">
-        <v>852</v>
+        <v>832</v>
       </c>
     </row>
     <row r="219" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>853</v>
+        <v>833</v>
       </c>
       <c r="E219">
         <v>8</v>
       </c>
       <c r="G219" t="s">
-        <v>854</v>
+        <v>834</v>
       </c>
       <c r="M219" s="1">
         <v>0.25</v>
@@ -14444,13 +14431,13 @@
         <v>300</v>
       </c>
       <c r="AB219" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="AC219" t="s">
-        <v>804</v>
+        <v>784</v>
       </c>
       <c r="AE219" t="s">
-        <v>855</v>
+        <v>835</v>
       </c>
       <c r="AF219">
         <v>10000000</v>
@@ -14459,24 +14446,24 @@
         <v>1.5</v>
       </c>
       <c r="AH219" t="s">
-        <v>856</v>
+        <v>836</v>
       </c>
       <c r="AI219" t="s">
-        <v>856</v>
+        <v>836</v>
       </c>
     </row>
     <row r="220" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>857</v>
+        <v>837</v>
       </c>
       <c r="E220">
         <v>9</v>
       </c>
       <c r="G220" t="s">
-        <v>858</v>
+        <v>838</v>
       </c>
       <c r="M220" s="1">
         <v>2</v>
@@ -14494,24 +14481,24 @@
         <v>1.5</v>
       </c>
       <c r="AH220" t="s">
-        <v>859</v>
+        <v>839</v>
       </c>
       <c r="AI220" t="s">
-        <v>859</v>
+        <v>839</v>
       </c>
     </row>
     <row r="221" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>860</v>
+        <v>840</v>
       </c>
       <c r="E221">
         <v>10</v>
       </c>
       <c r="G221" t="s">
-        <v>861</v>
+        <v>841</v>
       </c>
       <c r="K221" s="1">
         <v>12</v>
@@ -14529,24 +14516,24 @@
         <v>1.5</v>
       </c>
       <c r="AH221" t="s">
-        <v>862</v>
+        <v>842</v>
       </c>
       <c r="AI221" t="s">
-        <v>862</v>
+        <v>842</v>
       </c>
     </row>
     <row r="222" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>864</v>
+        <v>844</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>864</v>
+        <v>844</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>865</v>
+        <v>845</v>
       </c>
       <c r="E222">
         <v>1</v>
@@ -14564,7 +14551,7 @@
         <v>348</v>
       </c>
       <c r="V222" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W222" s="1">
         <v>15</v>
@@ -14573,10 +14560,10 @@
         <v>40</v>
       </c>
       <c r="AC222" t="s">
-        <v>866</v>
+        <v>846</v>
       </c>
       <c r="AE222" t="s">
-        <v>867</v>
+        <v>847</v>
       </c>
       <c r="AF222">
         <v>100000</v>
@@ -14585,30 +14572,30 @@
         <v>1.5</v>
       </c>
       <c r="AH222" t="s">
-        <v>868</v>
+        <v>848</v>
       </c>
       <c r="AI222" t="s">
-        <v>868</v>
+        <v>848</v>
       </c>
     </row>
     <row r="223" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>864</v>
+        <v>844</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>869</v>
+        <v>849</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>865</v>
+        <v>845</v>
       </c>
       <c r="E223">
         <v>2</v>
       </c>
       <c r="F223" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="K223" s="1">
         <v>8</v>
@@ -14617,7 +14604,7 @@
         <v>348</v>
       </c>
       <c r="V223" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W223" s="1">
         <v>15</v>
@@ -14626,10 +14613,10 @@
         <v>40</v>
       </c>
       <c r="AB223" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="AC223" t="s">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="AE223" t="s">
         <v>89</v>
@@ -14641,36 +14628,36 @@
         <v>1.5</v>
       </c>
       <c r="AH223" t="s">
-        <v>871</v>
+        <v>851</v>
       </c>
       <c r="AI223" t="s">
-        <v>871</v>
+        <v>851</v>
       </c>
     </row>
     <row r="224" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>864</v>
+        <v>844</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>872</v>
+        <v>852</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>865</v>
+        <v>845</v>
       </c>
       <c r="E224">
         <v>3</v>
       </c>
       <c r="F224" t="s">
-        <v>734</v>
+        <v>715</v>
       </c>
       <c r="U224" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V224" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W224" s="1">
         <v>15</v>
@@ -14679,10 +14666,10 @@
         <v>40</v>
       </c>
       <c r="AB224" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="AE224" t="s">
-        <v>873</v>
+        <v>853</v>
       </c>
       <c r="AF224">
         <v>400000</v>
@@ -14691,36 +14678,36 @@
         <v>1.5</v>
       </c>
       <c r="AH224" t="s">
-        <v>874</v>
+        <v>854</v>
       </c>
       <c r="AI224" t="s">
-        <v>874</v>
+        <v>854</v>
       </c>
     </row>
     <row r="225" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>864</v>
+        <v>844</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>875</v>
+        <v>855</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>865</v>
+        <v>845</v>
       </c>
       <c r="E225">
         <v>4</v>
       </c>
       <c r="F225" t="s">
-        <v>771</v>
+        <v>752</v>
       </c>
       <c r="U225" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V225" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W225" s="1">
         <v>15</v>
@@ -14729,13 +14716,13 @@
         <v>40</v>
       </c>
       <c r="AA225" t="s">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="AB225" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="AE225" t="s">
-        <v>876</v>
+        <v>856</v>
       </c>
       <c r="AF225">
         <v>800000</v>
@@ -14744,30 +14731,30 @@
         <v>1.5</v>
       </c>
       <c r="AH225" t="s">
-        <v>877</v>
+        <v>857</v>
       </c>
       <c r="AI225" t="s">
-        <v>877</v>
+        <v>857</v>
       </c>
     </row>
     <row r="226" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>864</v>
+        <v>844</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>878</v>
+        <v>858</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>865</v>
+        <v>845</v>
       </c>
       <c r="E226">
         <v>5</v>
       </c>
       <c r="F226" t="s">
-        <v>812</v>
+        <v>792</v>
       </c>
       <c r="K226" s="1">
         <v>10</v>
@@ -14776,7 +14763,7 @@
         <v>348</v>
       </c>
       <c r="V226" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W226" s="1">
         <v>15</v>
@@ -14785,13 +14772,13 @@
         <v>40</v>
       </c>
       <c r="AA226" t="s">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="AB226" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="AE226" t="s">
-        <v>873</v>
+        <v>853</v>
       </c>
       <c r="AF226">
         <v>1500000</v>
@@ -14800,36 +14787,36 @@
         <v>1.5</v>
       </c>
       <c r="AH226" t="s">
-        <v>879</v>
+        <v>859</v>
       </c>
       <c r="AI226" t="s">
-        <v>879</v>
+        <v>859</v>
       </c>
     </row>
     <row r="227" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>864</v>
+        <v>844</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>880</v>
+        <v>860</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>865</v>
+        <v>845</v>
       </c>
       <c r="E227">
         <v>6</v>
       </c>
       <c r="F227" t="s">
-        <v>848</v>
+        <v>828</v>
       </c>
       <c r="U227" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V227" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W227" s="1">
         <v>15</v>
@@ -14838,7 +14825,7 @@
         <v>40</v>
       </c>
       <c r="AE227" t="s">
-        <v>881</v>
+        <v>861</v>
       </c>
       <c r="AF227">
         <v>3000000</v>
@@ -14847,36 +14834,36 @@
         <v>1.5</v>
       </c>
       <c r="AH227" t="s">
-        <v>882</v>
+        <v>862</v>
       </c>
       <c r="AI227" t="s">
-        <v>882</v>
+        <v>862</v>
       </c>
     </row>
     <row r="228" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="C228" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="B228" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>883</v>
-      </c>
       <c r="D228" s="1" t="s">
-        <v>865</v>
+        <v>845</v>
       </c>
       <c r="E228">
         <v>7</v>
       </c>
       <c r="F228" t="s">
-        <v>884</v>
+        <v>864</v>
       </c>
       <c r="U228" s="1" t="s">
         <v>348</v>
       </c>
       <c r="V228" s="1" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="W228" s="1">
         <v>15</v>
@@ -14885,10 +14872,10 @@
         <v>40</v>
       </c>
       <c r="AC228" t="s">
-        <v>885</v>
+        <v>865</v>
       </c>
       <c r="AE228" t="s">
-        <v>886</v>
+        <v>866</v>
       </c>
       <c r="AF228">
         <v>5000000</v>
@@ -14897,30 +14884,30 @@
         <v>1.5</v>
       </c>
       <c r="AH228" t="s">
-        <v>887</v>
+        <v>867</v>
       </c>
       <c r="AI228" t="s">
-        <v>887</v>
+        <v>867</v>
       </c>
     </row>
     <row r="229" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>888</v>
+        <v>868</v>
       </c>
       <c r="E229">
         <v>8</v>
       </c>
       <c r="G229" t="s">
-        <v>889</v>
+        <v>869</v>
       </c>
       <c r="X229" s="1">
         <v>300</v>
       </c>
       <c r="AE229" t="s">
-        <v>890</v>
+        <v>870</v>
       </c>
       <c r="AF229">
         <v>10000000</v>
@@ -14929,24 +14916,24 @@
         <v>1.5</v>
       </c>
       <c r="AH229" t="s">
-        <v>891</v>
+        <v>871</v>
       </c>
       <c r="AI229" t="s">
-        <v>891</v>
+        <v>871</v>
       </c>
     </row>
     <row r="230" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>823</v>
+        <v>803</v>
       </c>
       <c r="E230">
         <v>9</v>
       </c>
       <c r="G230" t="s">
-        <v>892</v>
+        <v>872</v>
       </c>
       <c r="K230" s="1">
         <v>8</v>
@@ -14970,7 +14957,7 @@
         <v>374</v>
       </c>
       <c r="AE230" t="s">
-        <v>893</v>
+        <v>873</v>
       </c>
       <c r="AF230">
         <v>10000000</v>
@@ -14979,39 +14966,39 @@
         <v>1.5</v>
       </c>
       <c r="AH230" t="s">
-        <v>894</v>
+        <v>874</v>
       </c>
       <c r="AI230" t="s">
-        <v>894</v>
+        <v>874</v>
       </c>
     </row>
     <row r="231" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>895</v>
+        <v>875</v>
       </c>
       <c r="E231">
         <v>10</v>
       </c>
       <c r="G231" t="s">
-        <v>896</v>
+        <v>876</v>
       </c>
       <c r="X231" s="1">
         <v>300</v>
       </c>
       <c r="Z231" t="s">
-        <v>808</v>
+        <v>788</v>
       </c>
       <c r="AA231" t="s">
-        <v>849</v>
+        <v>829</v>
       </c>
       <c r="AB231" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="AC231" t="s">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="AE231" t="s">
         <v>89</v>
@@ -15023,10 +15010,10 @@
         <v>1.5</v>
       </c>
       <c r="AH231" t="s">
-        <v>897</v>
+        <v>877</v>
       </c>
       <c r="AI231" t="s">
-        <v>897</v>
+        <v>877</v>
       </c>
     </row>
   </sheetData>
@@ -15049,12 +15036,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>898</v>
+        <v>878</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>899</v>
+        <v>879</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
@@ -15064,27 +15051,27 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>901</v>
+        <v>881</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>902</v>
+        <v>882</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>903</v>
+        <v>883</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>904</v>
+        <v>884</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
@@ -15094,17 +15081,17 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>905</v>
+        <v>885</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>906</v>
+        <v>886</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>907</v>
+        <v>887</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
@@ -15114,62 +15101,62 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>908</v>
+        <v>888</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>909</v>
+        <v>889</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>910</v>
+        <v>890</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>911</v>
+        <v>891</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>912</v>
+        <v>892</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>913</v>
+        <v>893</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>914</v>
+        <v>894</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>915</v>
+        <v>895</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>916</v>
+        <v>896</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>917</v>
+        <v>897</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>918</v>
+        <v>898</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>919</v>
+        <v>899</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
@@ -15179,82 +15166,82 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>921</v>
+        <v>901</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>922</v>
+        <v>902</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>923</v>
+        <v>903</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>924</v>
+        <v>904</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>927</v>
+        <v>907</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>929</v>
+        <v>909</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>931</v>
+        <v>911</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>933</v>
+        <v>913</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>934</v>
+        <v>914</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>935</v>
+        <v>915</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
@@ -15264,27 +15251,27 @@
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>936</v>
+        <v>916</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>937</v>
+        <v>917</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>938</v>
+        <v>918</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>939</v>
+        <v>919</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
@@ -15294,147 +15281,147 @@
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>941</v>
+        <v>921</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>969</v>
+        <v>949</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>942</v>
+        <v>922</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>943</v>
+        <v>923</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>945</v>
+        <v>925</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>970</v>
+        <v>950</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>947</v>
+        <v>927</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>948</v>
+        <v>928</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>949</v>
+        <v>929</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>950</v>
+        <v>930</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>952</v>
+        <v>932</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>953</v>
+        <v>933</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>954</v>
+        <v>934</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>955</v>
+        <v>935</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>956</v>
+        <v>936</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>957</v>
+        <v>937</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>958</v>
+        <v>938</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>960</v>
+        <v>940</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>961</v>
+        <v>941</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>962</v>
+        <v>942</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>963</v>
+        <v>943</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>964</v>
+        <v>944</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>965</v>
+        <v>945</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>966</v>
+        <v>946</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>967</v>
+        <v>947</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGames\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB9F988-D61A-4D1D-95B9-6F4332434E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E0D6BB-F790-4259-B1E1-A14272BC7B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2289" uniqueCount="997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="998">
   <si>
     <t>群組ID</t>
   </si>
@@ -3044,6 +3044,10 @@
   </si>
   <si>
     <t>burst-vacuum-shockwave</t>
+  </si>
+  <si>
+    <t>slash-thrust-scatter-blue</t>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3973,6 +3977,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26AF238F-4FAE-90FF-3781-B2E28FB4E9E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4692,6 +4750,12 @@
       <c r="X9" s="1">
         <v>300</v>
       </c>
+      <c r="Z9" s="5" t="s">
+        <v>997</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>40</v>
+      </c>
       <c r="AE9" t="s">
         <v>70</v>
       </c>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGames\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E0D6BB-F790-4259-B1E1-A14272BC7B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463E67D7-1EAE-4EA9-9F87-3FFE21AF5EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="1000">
   <si>
     <t>群組ID</t>
   </si>
@@ -3047,6 +3047,14 @@
   </si>
   <si>
     <t>slash-thrust-scatter-blue</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>slash-thrust-scatter-red</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>slash-thrust-scatter-super</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -4031,6 +4039,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C7EF70A-2935-25D2-2B27-424B989A13DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4788,6 +4850,12 @@
       <c r="X10" s="1">
         <v>300</v>
       </c>
+      <c r="Z10" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>40</v>
+      </c>
       <c r="AE10" t="s">
         <v>74</v>
       </c>
@@ -4819,6 +4887,12 @@
       </c>
       <c r="X11" s="1">
         <v>300</v>
+      </c>
+      <c r="Z11" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>40</v>
       </c>
       <c r="AE11" t="s">
         <v>78</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -4929,20 +4929,30 @@
       <c r="F12" t="s">
         <v>37</v>
       </c>
+      <c r="I12" s="1">
+        <v>8</v>
+      </c>
+      <c r="K12" s="1">
+        <v>8</v>
+      </c>
       <c r="W12" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="X12" s="1">
         <v>25</v>
       </c>
-      <c r="Z12" t="s">
-        <v>83</v>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>slash-cleave-ring-warm</t>
+        </is>
       </c>
       <c r="AB12" t="s">
         <v>40</v>
       </c>
-      <c r="AE12" t="s">
-        <v>84</v>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>{"pct":200,"pctPer":20,"radiusCurve":[[0,0.12],[0.25,0.48],[0.65,0.86],[1,1]]}</t>
+        </is>
       </c>
       <c r="AF12">
         <v>100000</v>
@@ -4950,11 +4960,15 @@
       <c r="AG12">
         <v>1.5</v>
       </c>
-      <c r="AH12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>85</v>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>對自身周圍 {m} 米內的所有敵人造成 1 次 {pct}% 物理傷害</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>對自身周圍 {m} 米內的所有敵人造成 1 次 {pct}% 物理傷害</t>
+        </is>
       </c>
       <c r="AJ12">
         <v>24</v>
@@ -4967,8 +4981,10 @@
       <c r="B13" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>86</v>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>擴增</t>
+        </is>
       </c>
       <c r="D13" s="1" t="s">
         <v>82</v>
@@ -4980,7 +4996,7 @@
         <v>37</v>
       </c>
       <c r="W13" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="X13" s="1">
         <v>40</v>
@@ -4994,11 +5010,15 @@
       <c r="AG13">
         <v>1.5</v>
       </c>
-      <c r="AH13" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>88</v>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>斬擊範圍擴大 {range}%</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>斬擊範圍擴大 {range}%</t>
+        </is>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
@@ -5008,8 +5028,10 @@
       <c r="B14" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>46</v>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>強化</t>
+        </is>
       </c>
       <c r="D14" s="1" t="s">
         <v>82</v>
@@ -5021,13 +5043,20 @@
         <v>47</v>
       </c>
       <c r="W14" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="X14" s="1">
         <v>60</v>
       </c>
-      <c r="AE14" t="s">
-        <v>89</v>
+      <c r="Z14" s="0" t="inlineStr">
+        <is>
+          <t>slash-cleave-ring-blue</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>{"pct":20,"pctPer":8}</t>
+        </is>
       </c>
       <c r="AF14">
         <v>400000</v>
@@ -5062,13 +5091,15 @@
         <v>52</v>
       </c>
       <c r="W15" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="X15" s="1">
         <v>80</v>
       </c>
-      <c r="AE15" t="s">
-        <v>92</v>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>{"times":1,"timesPer":0.1}</t>
+        </is>
       </c>
       <c r="AF15">
         <v>800000</v>
@@ -5076,11 +5107,15 @@
       <c r="AG15">
         <v>1.5</v>
       </c>
-      <c r="AH15" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>93</v>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>額外劈出 {times} 次斬擊（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>額外劈出 {times} 次斬擊（不足 1 次的部分以機率觸發）</t>
+        </is>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
@@ -5103,14 +5138,12 @@
         <v>56</v>
       </c>
       <c r="W16" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="X16" s="1">
         <v>100</v>
       </c>
-      <c r="Z16" t="s">
-        <v>95</v>
-      </c>
+      <c r="Z16"/>
       <c r="AE16" t="s">
         <v>96</v>
       </c>
@@ -5153,13 +5186,16 @@
         <v>0.5</v>
       </c>
       <c r="W17" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="X17" s="1">
         <v>140</v>
       </c>
-      <c r="Z17" t="s">
-        <v>95</v>
+      <c r="Z17"/>
+      <c r="AA17" s="0" t="inlineStr">
+        <is>
+          <t>proj-cleave-ring-blue</t>
+        </is>
       </c>
       <c r="AB17" t="s">
         <v>40</v>
@@ -5173,11 +5209,15 @@
       <c r="AG17">
         <v>1.5</v>
       </c>
-      <c r="AH17" t="s">
-        <v>99</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>99</v>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>圓形刀波向外擴張至 {m} 米，對擴張路徑上的所有敵人造成傷害</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>圓形刀波向外擴張至 {m} 米，對擴張路徑上的所有敵人造成傷害</t>
+        </is>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.3">
@@ -5200,13 +5240,16 @@
         <v>65</v>
       </c>
       <c r="W18" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="X18" s="1">
         <v>240</v>
       </c>
-      <c r="Z18" t="s">
-        <v>95</v>
+      <c r="Z18"/>
+      <c r="AA18" s="0" t="inlineStr">
+        <is>
+          <t>proj-cleave-ring-tricolor</t>
+        </is>
       </c>
       <c r="AB18" t="s">
         <v>40</v>
@@ -5220,11 +5263,15 @@
       <c r="AG18">
         <v>1.5</v>
       </c>
-      <c r="AH18" t="s">
-        <v>102</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>102</v>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>額外使出 {times} 次圓形斬擊，且傷害額外 +{pct}%（與原有傷害乘法計算）</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>額外使出 {times} 次圓形斬擊，且傷害額外 +{pct}%（與原有傷害乘法計算）</t>
+        </is>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.3">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0641A473-A143-4658-9D23-0689502AC9D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABD7D6B-AA91-4F84-A758-62FD8D061855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3031,9 +3031,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>slash-cleave-ring-warm</t>
-  </si>
-  <si>
     <t>{"pct":200,"pctPer":20,"radiusCurve":[[0,0.12],[0.25,0.48],[0.65,0.86],[1,1]]}</t>
   </si>
   <si>
@@ -3069,6 +3066,10 @@
   </si>
   <si>
     <t>slash-cleave-ring-blue</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>slash-cleave-ring-warm</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -4161,6 +4162,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E099B606-74C2-D886-363C-37863425F54F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5009,14 +5064,14 @@
       <c r="X12" s="1">
         <v>25</v>
       </c>
-      <c r="Z12" t="s">
-        <v>991</v>
+      <c r="Z12" s="5" t="s">
+        <v>1003</v>
       </c>
       <c r="AB12" t="s">
         <v>40</v>
       </c>
       <c r="AE12" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AF12">
         <v>100000</v>
@@ -5025,10 +5080,10 @@
         <v>1.5</v>
       </c>
       <c r="AH12" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="AI12" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="AJ12">
         <v>24</v>
@@ -5042,7 +5097,7 @@
         <v>81</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>82</v>
@@ -5069,10 +5124,10 @@
         <v>1.5</v>
       </c>
       <c r="AH13" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="AI13" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
@@ -5083,7 +5138,7 @@
         <v>81</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>82</v>
@@ -5101,7 +5156,7 @@
         <v>60</v>
       </c>
       <c r="AE14" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="AF14">
         <v>400000</v>
@@ -5142,7 +5197,7 @@
         <v>80</v>
       </c>
       <c r="AE15" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AF15">
         <v>800000</v>
@@ -5151,10 +5206,10 @@
         <v>1.5</v>
       </c>
       <c r="AH15" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="AI15" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
@@ -5230,7 +5285,7 @@
         <v>140</v>
       </c>
       <c r="AA17" s="5" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="AB17" t="s">
         <v>40</v>
@@ -5245,10 +5300,10 @@
         <v>1.5</v>
       </c>
       <c r="AH17" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="AI17" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
@@ -5277,7 +5332,7 @@
         <v>240</v>
       </c>
       <c r="AA18" s="5" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="AB18" t="s">
         <v>40</v>
@@ -5292,10 +5347,10 @@
         <v>1.5</v>
       </c>
       <c r="AH18" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
@@ -5789,7 +5844,7 @@
         <v>142</v>
       </c>
       <c r="K31" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="X31" s="1">
         <v>300</v>
@@ -5800,8 +5855,10 @@
       <c r="AB31" t="s">
         <v>144</v>
       </c>
-      <c r="AE31" t="s">
-        <v>85</v>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>{"pct":4,"pctPer":0.4,"sec":10}</t>
+        </is>
       </c>
       <c r="AF31">
         <v>10000000</v>
@@ -5809,11 +5866,15 @@
       <c r="AG31">
         <v>1.5</v>
       </c>
-      <c r="AH31" t="s">
-        <v>145</v>
-      </c>
-      <c r="AI31" t="s">
-        <v>145</v>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>每次施放飛刀時額外射出 1 支無限飛刀，追擊自身周圍 {m} 米內的任意敵人。每次彈射使該支飛刀傷害額外提高 {pct}%（累加），最多存在 {sec} 秒。無敵人時在自身周圍環繞待機，單一敵人時飛離後折返攻擊</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>每次施放飛刀時額外射出 1 支無限飛刀，追擊自身周圍 {m} 米內的任意敵人。每次彈射使該支飛刀傷害額外提高 {pct}%（累加），最多存在 {sec} 秒。無敵人時在自身周圍環繞待機，單一敵人時飛離後折返攻擊</t>
+        </is>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGames\Idle-RPG\codex\tmp\skills2-repair\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGames\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5808F30-A2EF-4D42-A4F2-2EA2B1165AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1D4795-ED4A-4C72-9EB3-3CCBBAA62E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2300" uniqueCount="1013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2304" uniqueCount="1015">
   <si>
     <t>群組ID</t>
   </si>
@@ -3078,6 +3078,12 @@
   </si>
   <si>
     <t>整列留白：技能本體沿前階繼承；附加效果不播放。整條來源都無特效時不退回舊版畫法；換外觀可在 VFX 編輯器另存新檔名再填入。</t>
+  </si>
+  <si>
+    <t>proj-knife-gold-08-cri-rain</t>
+  </si>
+  <si>
+    <t>proj-knife-gold-09-die</t>
   </si>
 </sst>
 </file>
@@ -3707,422 +3713,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Text Box 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noGrp="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="9525000" cy="9525000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noGrp="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="9525000" cy="9525000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noGrp="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="9525000" cy="9525000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>403860</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noGrp="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="9525000" cy="9525000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>403860</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noGrp="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="9525000" cy="9525000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>403860</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noGrp="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="9525000" cy="9525000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>403860</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noGrp="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="9525000" cy="9525000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noGrp="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="9525000" cy="9525000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noGrp="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="9525000" cy="9525000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>403860</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noGrp="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="9525000" cy="9525000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -4165,6 +3755,60 @@
             <a:srgbClr val="000000"/>
           </a:solidFill>
           <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>167640</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B3C2D5D-F93A-0EAA-77D9-13B0298AF0CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
           <a:headEnd/>
           <a:tailEnd/>
         </a:ln>
@@ -6168,6 +5812,12 @@
       <c r="X29" s="1">
         <v>300</v>
       </c>
+      <c r="AA29" t="s">
+        <v>1013</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>113</v>
+      </c>
       <c r="AE29" t="s">
         <v>223</v>
       </c>
@@ -6218,6 +5868,12 @@
       <c r="X30" s="1">
         <v>300</v>
       </c>
+      <c r="AA30" t="s">
+        <v>1014</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>113</v>
+      </c>
       <c r="AE30" t="s">
         <v>227</v>
       </c>
@@ -6274,7 +5930,7 @@
         <v>231</v>
       </c>
       <c r="AB31" t="s">
-        <v>232</v>
+        <v>113</v>
       </c>
       <c r="AE31" t="s">
         <v>233</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills2" sheetId="1" r:id="Rbbba6652508a47af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位定義" sheetId="2" r:id="R759a0af19da44da0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills2" sheetId="1" r:id="R6b8fe0930e344e32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位定義" sheetId="2" r:id="R9838742100ee48ae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6321,7 +6321,7 @@
       </x:c>
       <x:c r="N39"/>
       <x:c r="O39" t="n">
-        <x:v>30</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="P39"/>
       <x:c r="Q39" t="n">
@@ -6344,7 +6344,7 @@
         <x:v>附加效果</x:v>
       </x:c>
       <x:c r="AF39" t="str">
-        <x:v>{"pct":200,"pctPer":20,"back":6,"rise":0.08}</x:v>
+        <x:v>{"pct":200,"pctPer":20,"count":3,"rise":0.08}</x:v>
       </x:c>
       <x:c r="AG39">
         <x:v>10000000</x:v>
@@ -6353,10 +6353,10 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="AI39" s="5" t="str">
-        <x:v>疾風破最後一擊觸發 1＋連擊數道貫穿雷電，每道造成 {pct}% 雷電傷害；每隔 {gap} 秒重新選擇自身周圍 {m} 米內敵人，無敵人即停止；從自身後方 {back} 米處伸出長 {len} 米、寬 {wid} 米的雷電</x:v>
+        <x:v>疾風破最後一擊觸發 {count}＋角色連擊數道貫穿雷電，每道造成 {pct}% 雷電傷害；每隔 {gap} 秒重新選擇自身周圍 {m} 米內敵人，無敵人即停止；沿自身與目標連線，以自身為中心貫穿長 {len} 米、寬 {wid} 米的範圍</x:v>
       </x:c>
       <x:c r="AJ39" s="5" t="str">
-        <x:v>選敵半徑20米，無敵人即停止；傷害矩形長30米寬10米，從玩家後方6米開始，0.08秒伸滿；連擊數3時發射4道，每道間隔0.2秒。每級+20%雷電傷害。</x:v>
+        <x:v>選敵半徑20米，無敵人即停止；以玩家為中心，沿玩家與目標連線貫穿長100米寬10米（前後各50米），0.08秒伸滿；0連擊發射3道、3連擊發射6道，每道間隔0.2秒。每級+20%雷電傷害。</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -18107,8 +18107,8 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac9083c8037e4e04"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf330e825f173463d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8713701cc8244235"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e2f3a60fd5e4cb1"/>
 </x:worksheet>
 </file>
 

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -3666,8 +3666,8 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <xdr:twoCellAnchor editAs="oneCell">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
@@ -3680,35 +3680,43 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Text Box 2"/>
-        <xdr:cNvSpPr>
-          <a:spLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noGrp="1"/>
+        <xdr:cNvPr id="1026" name="Text Box 2" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93CE4C46-79BE-EFA0-5BDE-C8E09C3DDA60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noSelect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
       </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="7620000" cy="7620000"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+        <a:ln w="9525">
           <a:solidFill>
             <a:srgbClr val="000000"/>
           </a:solidFill>
-          <a:miter/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
         </a:ln>
       </xdr:spPr>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
@@ -3721,24 +3729,43 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 2"/>
+        <xdr:cNvPr id="12" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B3C2D5D-F93A-0EAA-77D9-13B0298AF0CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
-          <a:spLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noGrp="1"/>
+          <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
       </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="7620000" cy="7620000"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:custGeom>
           <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
       </xdr:spPr>
     </xdr:sp>
     <xdr:clientData/>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -6478,8 +6478,10 @@
       <x:c r="X41" s="1">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="AF41" t="s">
-        <x:v>204</x:v>
+      <x:c r="AF41" t="inlineStr">
+        <x:is>
+          <x:t>{"pct":50,"pctPer":5,"scatterPct":50,"scatterPctPer":5}</x:t>
+        </x:is>
       </x:c>
       <x:c r="AG41">
         <x:v>10000000</x:v>
@@ -6487,11 +6489,15 @@
       <x:c r="AH41">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="AI41" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="AJ41" t="s">
-        <x:v>205</x:v>
+      <x:c r="AI41" t="inlineStr">
+        <x:is>
+          <x:t>疾風月牙閃不再由範圍內的敵人均分傷害，改為每個敵人都受到完整傷害；爆散效果提高 {scatterPct}%（技能傷害係數與隨機目標數同時提高），且本體與爆散傷害再額外 +{pct}%</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AJ41" t="inlineStr">
+        <x:is>
+          <x:t>爆散傷害係數與隨機目標數各乘上1＋爆散效果加成；目標數乘算後的小數部分以機率追加。千鳥額外傷害加成套用於月牙閃與爆散，各只套用一次。升級：每級+5%爆散效果及傷害額外+5%。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="42">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB20A03-688D-4982-89D3-800E1406201C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A2F787-5FA0-4477-8F44-753A61A429EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
     <sheet name="欄位定義" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Skills2!$A$1:$AQ$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Skills2!$A$1:$AS$231</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10016" uniqueCount="1084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10109" uniqueCount="1187">
   <si>
     <t>群組ID</t>
   </si>
@@ -3327,6 +3327,315 @@
   <si>
     <t>附加效果</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我方狀態</t>
+  </si>
+  <si>
+    <t>敵方狀態</t>
+  </si>
+  <si>
+    <t>sgPhantomDodge</t>
+  </si>
+  <si>
+    <t>sgSoulRend</t>
+  </si>
+  <si>
+    <t>stun</t>
+  </si>
+  <si>
+    <t>sgDeathReaper</t>
+  </si>
+  <si>
+    <t>sgGale</t>
+  </si>
+  <si>
+    <t>sgBleed</t>
+  </si>
+  <si>
+    <t>sgPoison</t>
+  </si>
+  <si>
+    <t>sgSlayerMark</t>
+  </si>
+  <si>
+    <t>sgVenomField</t>
+  </si>
+  <si>
+    <t>sgFrenzyCr</t>
+  </si>
+  <si>
+    <t>sgIronBleed</t>
+  </si>
+  <si>
+    <t>sgStorm</t>
+  </si>
+  <si>
+    <t>sgKagura</t>
+  </si>
+  <si>
+    <t>sgArmorBrk</t>
+  </si>
+  <si>
+    <t>invuln</t>
+  </si>
+  <si>
+    <t>sgBloodrage</t>
+  </si>
+  <si>
+    <t>sgWarGodKill</t>
+  </si>
+  <si>
+    <t>sgAsuraFist</t>
+  </si>
+  <si>
+    <t>sgBurn</t>
+  </si>
+  <si>
+    <t>sgFireAmp</t>
+  </si>
+  <si>
+    <t>sgStarfall</t>
+  </si>
+  <si>
+    <t>sgFirehunt</t>
+  </si>
+  <si>
+    <t>shield; sgRockArmor</t>
+  </si>
+  <si>
+    <t>sgRockAmp</t>
+  </si>
+  <si>
+    <t>stun; sgPetrify</t>
+  </si>
+  <si>
+    <t>sgStiffen</t>
+  </si>
+  <si>
+    <t>sgMire</t>
+  </si>
+  <si>
+    <t>sgMirePoison</t>
+  </si>
+  <si>
+    <t>sgMireLava</t>
+  </si>
+  <si>
+    <t>sgPlague</t>
+  </si>
+  <si>
+    <t>sgInferno</t>
+  </si>
+  <si>
+    <t>sgSuperconduct</t>
+  </si>
+  <si>
+    <t>sgThunderOrb</t>
+  </si>
+  <si>
+    <t>sgFrost; sgFrostBite; sgFrozen; stun</t>
+  </si>
+  <si>
+    <t>sgIceRevert</t>
+  </si>
+  <si>
+    <t>atkDown; sgWaterPrison</t>
+  </si>
+  <si>
+    <t>sgFrostbody</t>
+  </si>
+  <si>
+    <t>sgWindSlow</t>
+  </si>
+  <si>
+    <t>sgWindRend; sgWindCut</t>
+  </si>
+  <si>
+    <t>sgVoidBlade</t>
+  </si>
+  <si>
+    <t>sgStormBarrier</t>
+  </si>
+  <si>
+    <t>sgStormGod</t>
+  </si>
+  <si>
+    <t>我方狀態 / 敵方狀態（2026-09-18 狀態表格化）</t>
+  </si>
+  <si>
+    <t>我方狀態＝施放時套在自己身上（被動技能以觸發當作施放）；敵方狀態＝這個技能命中敵人時附加。每列只在該階有等級（超神＝選中）時生效。</t>
+  </si>
+  <si>
+    <t>格式：狀態ID，多個以「;」分隔；可帶參數：狀態ID(參數=值, …)，例：atkDown(val=10, dur=3); stun(chance=25, dur=sec)</t>
+  </si>
+  <si>
+    <t>參數：val 效果數值／dmg 狀態傷害／dur 持續秒數／gap 作用間隔／max 層數上限／chance 機率%／stacks 一次疊幾層；沒填的吃狀態表。</t>
+  </si>
+  <si>
+    <t>參數值填數字＝固定值；填本列「效果參數」的鍵名（例 sec、pct）＝隨該階等級成長。</t>
+  </si>
+  <si>
+    <t>狀態長什麼樣子（上身特效、身上的持續特效、每跳特效）一律填在 Status 表，不填在這裡。</t>
+  </si>
+  <si>
+    <t>下列是技能原有的施加點：前幾格的觸發時機與數值由技能公式決定，格子只決定施加哪一個狀態；</t>
+  </si>
+  <si>
+    <t>　換成別的狀態，技能後續各階（例：燃燒結束的爆燃、流血中的虛弱增傷）會跟著作用在新狀態上；</t>
+  </si>
+  <si>
+    <t>　格子留空＝不施加；超出下列格數的條目，依上面的通用規則附加。</t>
+  </si>
+  <si>
+    <t>　thrust 超神 phantomOcta（我方）：第 1 格 施放突刺後的絕對閃避</t>
+  </si>
+  <si>
+    <t>　thrust 超神 shadowExecutioner（敵方）：第 1 格 突刺命中疊層</t>
+  </si>
+  <si>
+    <t>　cleave 第 5 階（敵方）：第 1 格 斬擊機率擊暈</t>
+  </si>
+  <si>
+    <t>　knife 超神 deathReaper（我方）：第 1 格 飛刀擊殺時疊層</t>
+  </si>
+  <si>
+    <t>　gale 第 5 階（我方）：第 1 格 施放時的攻速提升</t>
+  </si>
+  <si>
+    <t>　bloodblade 第 1 階（敵方）：第 1 格 流血〔限持續傷害〕</t>
+  </si>
+  <si>
+    <t>　bloodblade 第 4 階（敵方）：第 1 格 中毒〔限持續傷害〕</t>
+  </si>
+  <si>
+    <t>　bloodblade 超神 slayerDomain（我方）：第 1 格 領域內敵人死亡時疊層</t>
+  </si>
+  <si>
+    <t>　bloodblade 超神 venomDomain（敵方）：第 1 格 領域內每拍疊層</t>
+  </si>
+  <si>
+    <t>　dualdance 第 4 階（我方）：第 1 格 爆擊率提升</t>
+  </si>
+  <si>
+    <t>　dualdance 第 5 階（我方）：第 1 格 自身流血</t>
+  </si>
+  <si>
+    <t>　dualdance 第 5 階（敵方）：第 1 格 周圍敵人流血</t>
+  </si>
+  <si>
+    <t>　dualdance 第 7 階（我方）：第 1 格 暴風化身期間（化身本身由技能邏輯計時）</t>
+  </si>
+  <si>
+    <t>　dualdance 超神 flameKagura（敵方）：第 1 格 命中疊層灼燒</t>
+  </si>
+  <si>
+    <t>　counter 第 5 階（敵方）：第 1 格 格擋時機率破甲</t>
+  </si>
+  <si>
+    <t>　counter 超神 indomitable（我方）：第 1 格 倒地等待復活期間（拿掉無敵的話，倒地期間會被打死）</t>
+  </si>
+  <si>
+    <t>　bloodrage 第 1 階（我方）：第 1 格 狂怒</t>
+  </si>
+  <si>
+    <t>　bloodrage 超神 warGodRoll（我方）：第 1 格 狂怒期間擊殺疊層</t>
+  </si>
+  <si>
+    <t>　bloodrage 超神 asuraFist（我方）：第 1 格 定時爆發</t>
+  </si>
+  <si>
+    <t>　fireball 第 2 階（敵方）：第 1 格 燃燒〔限持續傷害〕</t>
+  </si>
+  <si>
+    <t>　fireball 超神 starfallCataclysm（我方）：第 1 格 距離下一顆超巨型殞石落下的倒數</t>
+  </si>
+  <si>
+    <t>　fireball 第 6 階（我方）：第 1 格 燃燒作用時累加的火焰增幅〔限屬性增減〕</t>
+  </si>
+  <si>
+    <t>　firepillar 第 4 階（敵方）：第 1 格 機率燃燒〔限持續傷害〕</t>
+  </si>
+  <si>
+    <t>　rockarmor 第 1 階（我方）：第 1 格 岩甲護盾；第 2 格 岩甲護盾存在期間的計時</t>
+  </si>
+  <si>
+    <t>　rockarmor 第 6 階（我方）：第 1 格 損失護盾累加的傷害增幅〔限屬性增減〕</t>
+  </si>
+  <si>
+    <t>　rockarmor 超神 superRockArt（敵方）：第 1 格 石化的行動限制；第 2 格 石化</t>
+  </si>
+  <si>
+    <t>　rockarmor 超神 gravityField（敵方）：第 1 格 僵化</t>
+  </si>
+  <si>
+    <t>　firehunt 第 1 階（我方）：第 1 格 火狩環繞期間（火狩本身由技能邏輯計時）</t>
+  </si>
+  <si>
+    <t>　mire 第 1 階（敵方）：第 1 格 沼澤中持續重塗的緩速〔限屬性增減〕</t>
+  </si>
+  <si>
+    <t>　mire 第 3 階（敵方）：第 1 格 沼澤毒性〔限持續傷害〕</t>
+  </si>
+  <si>
+    <t>　mire 第 7 階（敵方）：第 1 格 岩漿灼燒〔限持續傷害〕</t>
+  </si>
+  <si>
+    <t>　mire 超神 plagueMire（敵方）：第 1 格 瘟疫〔限持續傷害〕</t>
+  </si>
+  <si>
+    <t>　mire 超神 abyssInferno（敵方）：第 1 格 改為火屬性的烙印</t>
+  </si>
+  <si>
+    <t>　earthguard 第 7 階（我方）：第 1 格 復活後無敵</t>
+  </si>
+  <si>
+    <t>　chainlightning 超神 eternalSuperconductor（我方）：第 1 格 閃電鏈經過自身時疊層</t>
+  </si>
+  <si>
+    <t>　thunderstrike 第 5 階（敵方）：第 1 格 衝擊波暈眩</t>
+  </si>
+  <si>
+    <t>　thunderorb 第 4 階（我方）：第 1 格 環體電球環繞期間（電球本身由技能邏輯計時）</t>
+  </si>
+  <si>
+    <t>　thunderorb 第 7 階（敵方）：第 1 格 雷殞衝擊波暈眩</t>
+  </si>
+  <si>
+    <t>　icearrow 第 2 階（敵方）：第 1 格 寒霜層數與緩速〔限屬性增減〕；第 2 格 寒霜凍傷〔限持續傷害〕；第 3 格 疊滿時的凍結標記〔限屬性增減〕；第 4 格 凍結的行動限制〔限行動限制〕</t>
+  </si>
+  <si>
+    <t>　waterball 第 2 階（敵方）：第 1 格 改為寒冰屬性並提高寒冰受傷</t>
+  </si>
+  <si>
+    <t>　waterball 第 3 階（敵方）：第 1 格 寒霜層數與緩速〔限屬性增減〕；第 2 格 寒霜凍傷〔限持續傷害〕；第 3 格 疊滿時的凍結標記〔限屬性增減〕；第 4 格 凍結的行動限制〔限行動限制〕</t>
+  </si>
+  <si>
+    <t>　waterball 超神 waterPrisonFall（敵方）：第 1 格 水牢內攻擊力下降；第 2 格 水牢內受到的傷害提高</t>
+  </si>
+  <si>
+    <t>　frostnova 第 1 階（敵方）：第 1 格 寒霜層數與緩速〔限屬性增減〕；第 2 格 寒霜凍傷〔限持續傷害〕；第 3 格 疊滿時的凍結標記〔限屬性增減〕；第 4 格 凍結的行動限制〔限行動限制〕</t>
+  </si>
+  <si>
+    <t>　frostnova 第 3 階（我方）：第 1 格 寒冰體（攻擊者機率被附加寒霜）</t>
+  </si>
+  <si>
+    <t>　windblade 第 6 階（敵方）：第 1 格 風刃命中緩速</t>
+  </si>
+  <si>
+    <t>　vacuumslash 第 3 階（敵方）：第 1 格 風切層數與緩速〔限屬性增減〕；第 2 格 風切割裂〔限持續傷害〕</t>
+  </si>
+  <si>
+    <t>　vacuumslash 第 7 階（我方）：第 1 格 虛空斬繞行期間（斬擊本身由技能邏輯計時）</t>
+  </si>
+  <si>
+    <t>　stormbarrier 第 1 階（我方）：第 1 格 暴風屏障</t>
+  </si>
+  <si>
+    <t>　stormbarrier 第 3 階（敵方）：第 1 格 風切層數與緩速〔限屬性增減〕；第 2 格 風切割裂〔限持續傷害〕</t>
+  </si>
+  <si>
+    <t>　stormbarrier 第 7 階（我方）：第 1 格 暴風神體</t>
   </si>
 </sst>
 </file>
@@ -3782,7 +4091,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACC8F76D-B553-4CF8-BE7D-F03409684AEE}">
-  <dimension ref="A1:AQ231"/>
+  <dimension ref="A1:AS231"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -3794,12 +4103,13 @@
     <col min="7" max="7" width="20.125" bestFit="1" customWidth="1"/>
     <col min="8" max="31" width="8.5" customWidth="1"/>
     <col min="32" max="38" width="12.125" customWidth="1"/>
-    <col min="39" max="39" width="48.625" customWidth="1"/>
-    <col min="40" max="41" width="18.625" customWidth="1"/>
-    <col min="42" max="43" width="48.625" customWidth="1"/>
+    <col min="39" max="40" width="34.625" style="1" customWidth="1"/>
+    <col min="41" max="41" width="48.625" customWidth="1"/>
+    <col min="42" max="43" width="18.625" customWidth="1"/>
+    <col min="44" max="45" width="48.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="9" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" s="9" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3915,22 +4225,28 @@
         <v>18</v>
       </c>
       <c r="AM1" s="8" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AN1" s="8" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AO1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="AN1" s="8" t="s">
+      <c r="AP1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="AO1" s="8" t="s">
+      <c r="AQ1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="AP1" s="8" t="s">
+      <c r="AR1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="AQ1" s="8" t="s">
+      <c r="AS1" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
@@ -4045,23 +4361,23 @@
       <c r="AL2" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
@@ -4176,23 +4492,23 @@
       <c r="AL3" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM3" s="1" t="s">
+      <c r="AO3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AN3" s="1" t="s">
+      <c r="AP3" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO3" s="1" t="s">
+      <c r="AQ3" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP3" s="1" t="s">
+      <c r="AR3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AQ3" s="1" t="s">
+      <c r="AS3" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
@@ -4307,23 +4623,23 @@
       <c r="AL4" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM4" s="1" t="s">
+      <c r="AO4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AN4" s="1" t="s">
+      <c r="AP4" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO4" s="1" t="s">
+      <c r="AQ4" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP4" s="1" t="s">
+      <c r="AR4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ4" s="1" t="s">
+      <c r="AS4" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
@@ -4438,23 +4754,23 @@
       <c r="AL5" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM5" s="1" t="s">
+      <c r="AO5" s="1" t="s">
         <v>992</v>
       </c>
-      <c r="AN5" s="1" t="s">
+      <c r="AP5" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO5" s="1" t="s">
+      <c r="AQ5" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP5" s="1" t="s">
+      <c r="AR5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AQ5" s="1" t="s">
+      <c r="AS5" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -4569,23 +4885,23 @@
       <c r="AL6" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM6" s="1" t="s">
+      <c r="AO6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AN6" s="1" t="s">
+      <c r="AP6" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO6" s="1" t="s">
+      <c r="AQ6" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP6" s="1" t="s">
+      <c r="AR6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AQ6" s="1" t="s">
+      <c r="AS6" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
@@ -4700,23 +5016,23 @@
       <c r="AL7" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM7" s="1" t="s">
+      <c r="AO7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AN7" s="1" t="s">
+      <c r="AP7" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO7" s="1" t="s">
+      <c r="AQ7" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP7" s="1" t="s">
+      <c r="AR7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ7" s="1" t="s">
+      <c r="AS7" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -4831,23 +5147,23 @@
       <c r="AL8" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM8" s="1" t="s">
+      <c r="AO8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AN8" s="1" t="s">
+      <c r="AP8" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO8" s="1" t="s">
+      <c r="AQ8" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP8" s="1" t="s">
+      <c r="AR8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AQ8" s="1" t="s">
+      <c r="AS8" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
@@ -4963,22 +5279,25 @@
         <v>977</v>
       </c>
       <c r="AM9" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AO9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="1" t="s">
+      <c r="AP9" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO9" s="1" t="s">
+      <c r="AQ9" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP9" s="1" t="s">
+      <c r="AR9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AQ9" s="1" t="s">
+      <c r="AS9" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
@@ -5093,23 +5412,26 @@
       <c r="AL10" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM10" s="1" t="s">
+      <c r="AN10" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="AO10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AN10" s="1" t="s">
+      <c r="AP10" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO10" s="1" t="s">
+      <c r="AQ10" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP10" s="1" t="s">
+      <c r="AR10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AQ10" s="1" t="s">
+      <c r="AS10" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
@@ -5224,23 +5546,23 @@
       <c r="AL11" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM11" s="1" t="s">
+      <c r="AO11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AN11" s="1" t="s">
+      <c r="AP11" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO11" s="1" t="s">
+      <c r="AQ11" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP11" s="1" t="s">
+      <c r="AR11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="AQ11" s="1" t="s">
+      <c r="AS11" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>73</v>
       </c>
@@ -5355,23 +5677,23 @@
       <c r="AL12" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM12" s="1" t="s">
+      <c r="AO12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AN12" s="1" t="s">
+      <c r="AP12" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO12" s="1" t="s">
+      <c r="AQ12" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP12" s="1" t="s">
+      <c r="AR12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AQ12" s="1" t="s">
+      <c r="AS12" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>73</v>
       </c>
@@ -5486,23 +5808,23 @@
       <c r="AL13" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM13" s="1" t="s">
+      <c r="AO13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AN13" s="1" t="s">
+      <c r="AP13" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO13" s="1" t="s">
+      <c r="AQ13" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP13" s="1" t="s">
+      <c r="AR13" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AQ13" s="1" t="s">
+      <c r="AS13" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>73</v>
       </c>
@@ -5617,23 +5939,23 @@
       <c r="AL14" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM14" s="1" t="s">
+      <c r="AO14" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="AN14" s="1" t="s">
+      <c r="AP14" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO14" s="1" t="s">
+      <c r="AQ14" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP14" s="1" t="s">
+      <c r="AR14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AQ14" s="1" t="s">
+      <c r="AS14" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>73</v>
       </c>
@@ -5748,23 +6070,23 @@
       <c r="AL15" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM15" s="1" t="s">
+      <c r="AO15" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AN15" s="1" t="s">
+      <c r="AP15" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO15" s="1" t="s">
+      <c r="AQ15" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP15" s="1" t="s">
+      <c r="AR15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AQ15" s="1" t="s">
+      <c r="AS15" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>73</v>
       </c>
@@ -5879,23 +6201,26 @@
       <c r="AL16" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM16" s="1" t="s">
+      <c r="AN16" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="AO16" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="AN16" s="1" t="s">
+      <c r="AP16" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO16" s="1" t="s">
+      <c r="AQ16" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP16" s="1" t="s">
+      <c r="AR16" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AQ16" s="1" t="s">
+      <c r="AS16" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>73</v>
       </c>
@@ -6010,23 +6335,23 @@
       <c r="AL17" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM17" s="1" t="s">
+      <c r="AO17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AN17" s="1" t="s">
+      <c r="AP17" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO17" s="1" t="s">
+      <c r="AQ17" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP17" s="1" t="s">
+      <c r="AR17" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="AQ17" s="1" t="s">
+      <c r="AS17" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>73</v>
       </c>
@@ -6141,23 +6466,23 @@
       <c r="AL18" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM18" s="1" t="s">
+      <c r="AO18" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="AN18" s="1" t="s">
+      <c r="AP18" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO18" s="1" t="s">
+      <c r="AQ18" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP18" s="1" t="s">
+      <c r="AR18" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AQ18" s="1" t="s">
+      <c r="AS18" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>73</v>
       </c>
@@ -6272,23 +6597,23 @@
       <c r="AL19" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM19" s="1" t="s">
+      <c r="AO19" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AN19" s="1" t="s">
+      <c r="AP19" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO19" s="1" t="s">
+      <c r="AQ19" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP19" s="1" t="s">
+      <c r="AR19" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AQ19" s="1" t="s">
+      <c r="AS19" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>73</v>
       </c>
@@ -6403,23 +6728,23 @@
       <c r="AL20" s="1" t="s">
         <v>1083</v>
       </c>
-      <c r="AM20" s="1" t="s">
+      <c r="AO20" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AN20" s="1" t="s">
+      <c r="AP20" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO20" s="1" t="s">
+      <c r="AQ20" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP20" s="1" t="s">
+      <c r="AR20" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="AQ20" s="1" t="s">
+      <c r="AS20" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>73</v>
       </c>
@@ -6534,23 +6859,23 @@
       <c r="AL21" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM21" s="1" t="s">
+      <c r="AO21" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="AN21" s="1" t="s">
+      <c r="AP21" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO21" s="1" t="s">
+      <c r="AQ21" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP21" s="1" t="s">
+      <c r="AR21" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="AQ21" s="1" t="s">
+      <c r="AS21" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>110</v>
       </c>
@@ -6665,23 +6990,23 @@
       <c r="AL22" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM22" s="1" t="s">
+      <c r="AO22" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AN22" s="1" t="s">
+      <c r="AP22" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO22" s="1" t="s">
+      <c r="AQ22" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP22" s="1" t="s">
+      <c r="AR22" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AQ22" s="1" t="s">
+      <c r="AS22" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>110</v>
       </c>
@@ -6796,23 +7121,23 @@
       <c r="AL23" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM23" s="1" t="s">
+      <c r="AO23" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="AN23" s="1" t="s">
+      <c r="AP23" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO23" s="1" t="s">
+      <c r="AQ23" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP23" s="1" t="s">
+      <c r="AR23" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AQ23" s="1" t="s">
+      <c r="AS23" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>110</v>
       </c>
@@ -6927,23 +7252,23 @@
       <c r="AL24" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM24" s="1" t="s">
+      <c r="AO24" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="AN24" s="1" t="s">
+      <c r="AP24" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO24" s="1" t="s">
+      <c r="AQ24" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP24" s="1" t="s">
+      <c r="AR24" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="AQ24" s="1" t="s">
+      <c r="AS24" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>110</v>
       </c>
@@ -7058,23 +7383,23 @@
       <c r="AL25" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM25" s="1" t="s">
+      <c r="AO25" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="AN25" s="1" t="s">
+      <c r="AP25" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO25" s="1" t="s">
+      <c r="AQ25" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP25" s="1" t="s">
+      <c r="AR25" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="AQ25" s="1" t="s">
+      <c r="AS25" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>110</v>
       </c>
@@ -7189,23 +7514,23 @@
       <c r="AL26" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM26" s="1" t="s">
+      <c r="AO26" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="AN26" s="1" t="s">
+      <c r="AP26" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO26" s="1" t="s">
+      <c r="AQ26" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP26" s="1" t="s">
+      <c r="AR26" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="AQ26" s="1" t="s">
+      <c r="AS26" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>110</v>
       </c>
@@ -7320,23 +7645,23 @@
       <c r="AL27" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM27" s="1" t="s">
+      <c r="AO27" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="AN27" s="1" t="s">
+      <c r="AP27" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO27" s="1" t="s">
+      <c r="AQ27" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP27" s="1" t="s">
+      <c r="AR27" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="AQ27" s="1" t="s">
+      <c r="AS27" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>110</v>
       </c>
@@ -7451,23 +7776,23 @@
       <c r="AL28" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM28" s="1" t="s">
+      <c r="AO28" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AN28" s="1" t="s">
+      <c r="AP28" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO28" s="1" t="s">
+      <c r="AQ28" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP28" s="1" t="s">
+      <c r="AR28" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="AQ28" s="1" t="s">
+      <c r="AS28" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>110</v>
       </c>
@@ -7582,23 +7907,23 @@
       <c r="AL29" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM29" s="1" t="s">
+      <c r="AO29" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AN29" s="1" t="s">
+      <c r="AP29" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO29" s="1" t="s">
+      <c r="AQ29" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP29" s="1" t="s">
+      <c r="AR29" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="AQ29" s="1" t="s">
+      <c r="AS29" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>110</v>
       </c>
@@ -7714,22 +8039,25 @@
         <v>977</v>
       </c>
       <c r="AM30" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AO30" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="AN30" s="1" t="s">
+      <c r="AP30" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO30" s="1" t="s">
+      <c r="AQ30" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP30" s="1" t="s">
+      <c r="AR30" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="AQ30" s="1" t="s">
+      <c r="AS30" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>110</v>
       </c>
@@ -7844,23 +8172,23 @@
       <c r="AL31" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM31" s="1" t="s">
+      <c r="AO31" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AN31" s="1" t="s">
+      <c r="AP31" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO31" s="1" t="s">
+      <c r="AQ31" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP31" s="1" t="s">
+      <c r="AR31" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="AQ31" s="1" t="s">
+      <c r="AS31" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>151</v>
       </c>
@@ -7975,23 +8303,23 @@
       <c r="AL32" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM32" s="1" t="s">
+      <c r="AO32" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="AN32" s="1" t="s">
+      <c r="AP32" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO32" s="1" t="s">
+      <c r="AQ32" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP32" s="1" t="s">
+      <c r="AR32" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="AQ32" s="1" t="s">
+      <c r="AS32" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>151</v>
       </c>
@@ -8106,23 +8434,23 @@
       <c r="AL33" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM33" s="1" t="s">
+      <c r="AO33" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="AN33" s="1" t="s">
+      <c r="AP33" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO33" s="1" t="s">
+      <c r="AQ33" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP33" s="1" t="s">
+      <c r="AR33" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="AQ33" s="1" t="s">
+      <c r="AS33" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>151</v>
       </c>
@@ -8237,23 +8565,23 @@
       <c r="AL34" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM34" s="1" t="s">
+      <c r="AO34" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="AN34" s="1" t="s">
+      <c r="AP34" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO34" s="1" t="s">
+      <c r="AQ34" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP34" s="1" t="s">
+      <c r="AR34" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="AQ34" s="1" t="s">
+      <c r="AS34" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>151</v>
       </c>
@@ -8368,23 +8696,23 @@
       <c r="AL35" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM35" s="1" t="s">
+      <c r="AO35" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="AN35" s="1" t="s">
+      <c r="AP35" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO35" s="1" t="s">
+      <c r="AQ35" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP35" s="1" t="s">
+      <c r="AR35" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="AQ35" s="1" t="s">
+      <c r="AS35" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>151</v>
       </c>
@@ -8500,22 +8828,25 @@
         <v>977</v>
       </c>
       <c r="AM36" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="AO36" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="AN36" s="1" t="s">
+      <c r="AP36" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO36" s="1" t="s">
+      <c r="AQ36" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP36" s="1" t="s">
+      <c r="AR36" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="AQ36" s="1" t="s">
+      <c r="AS36" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>151</v>
       </c>
@@ -8630,23 +8961,23 @@
       <c r="AL37" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM37" s="1" t="s">
+      <c r="AO37" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="AN37" s="1" t="s">
+      <c r="AP37" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO37" s="1" t="s">
+      <c r="AQ37" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP37" s="1" t="s">
+      <c r="AR37" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="AQ37" s="1" t="s">
+      <c r="AS37" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>151</v>
       </c>
@@ -8761,23 +9092,23 @@
       <c r="AL38" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM38" s="1" t="s">
+      <c r="AO38" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="AN38" s="1" t="s">
+      <c r="AP38" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO38" s="1" t="s">
+      <c r="AQ38" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP38" s="1" t="s">
+      <c r="AR38" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="AQ38" s="1" t="s">
+      <c r="AS38" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>151</v>
       </c>
@@ -8892,23 +9223,23 @@
       <c r="AL39" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AM39" s="1" t="s">
+      <c r="AO39" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="AN39" s="1" t="s">
+      <c r="AP39" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO39" s="1" t="s">
+      <c r="AQ39" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP39" s="1" t="s">
+      <c r="AR39" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="AQ39" s="1" t="s">
+      <c r="AS39" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>151</v>
       </c>
@@ -9023,23 +9354,23 @@
       <c r="AL40" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AM40" s="1" t="s">
+      <c r="AO40" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="AN40" s="1" t="s">
+      <c r="AP40" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO40" s="1" t="s">
+      <c r="AQ40" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP40" s="1" t="s">
+      <c r="AR40" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="AQ40" s="1" t="s">
+      <c r="AS40" s="1" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>151</v>
       </c>
@@ -9154,23 +9485,23 @@
       <c r="AL41" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM41" s="1" t="s">
+      <c r="AO41" s="1" t="s">
         <v>1025</v>
       </c>
-      <c r="AN41" s="1" t="s">
+      <c r="AP41" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO41" s="1" t="s">
+      <c r="AQ41" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP41" s="1" t="s">
+      <c r="AR41" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="AQ41" s="1" t="s">
+      <c r="AS41" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>191</v>
       </c>
@@ -9283,23 +9614,26 @@
       <c r="AL42" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM42" s="1" t="s">
+      <c r="AN42" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AO42" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="AN42" s="1" t="s">
+      <c r="AP42" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO42" s="1" t="s">
+      <c r="AQ42" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP42" s="1" t="s">
+      <c r="AR42" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="AQ42" s="1" t="s">
+      <c r="AS42" s="1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>191</v>
       </c>
@@ -9410,23 +9744,23 @@
       <c r="AL43" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM43" s="1" t="s">
+      <c r="AO43" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="AN43" s="1" t="s">
+      <c r="AP43" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO43" s="1" t="s">
+      <c r="AQ43" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP43" s="1" t="s">
+      <c r="AR43" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AQ43" s="1" t="s">
+      <c r="AS43" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>191</v>
       </c>
@@ -9541,23 +9875,23 @@
       <c r="AL44" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM44" s="1" t="s">
+      <c r="AO44" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AN44" s="1" t="s">
+      <c r="AP44" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO44" s="1" t="s">
+      <c r="AQ44" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP44" s="1" t="s">
+      <c r="AR44" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="AQ44" s="1" t="s">
+      <c r="AS44" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>191</v>
       </c>
@@ -9670,23 +10004,26 @@
       <c r="AL45" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM45" s="1" t="s">
+      <c r="AN45" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AO45" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="AN45" s="1" t="s">
+      <c r="AP45" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO45" s="1" t="s">
+      <c r="AQ45" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP45" s="1" t="s">
+      <c r="AR45" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="AQ45" s="1" t="s">
+      <c r="AS45" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>1076</v>
       </c>
@@ -9801,23 +10138,23 @@
       <c r="AL46" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM46" s="1" t="s">
+      <c r="AO46" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="AN46" s="1" t="s">
+      <c r="AP46" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO46" s="1" t="s">
+      <c r="AQ46" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP46" s="1" t="s">
+      <c r="AR46" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="AQ46" s="1" t="s">
+      <c r="AS46" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>191</v>
       </c>
@@ -9928,23 +10265,23 @@
       <c r="AL47" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM47" s="1" t="s">
+      <c r="AO47" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="AN47" s="1" t="s">
+      <c r="AP47" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO47" s="1" t="s">
+      <c r="AQ47" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP47" s="1" t="s">
+      <c r="AR47" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="AQ47" s="1" t="s">
+      <c r="AS47" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>191</v>
       </c>
@@ -10052,23 +10389,23 @@
         <v>977</v>
       </c>
       <c r="AL48" s="1"/>
-      <c r="AM48" s="1" t="s">
+      <c r="AO48" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="AN48" s="1" t="s">
+      <c r="AP48" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO48" s="1" t="s">
+      <c r="AQ48" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP48" s="1" t="s">
+      <c r="AR48" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="AQ48" s="1" t="s">
+      <c r="AS48" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>191</v>
       </c>
@@ -10182,22 +10519,25 @@
         <v>104</v>
       </c>
       <c r="AM49" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AO49" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="AN49" s="1" t="s">
+      <c r="AP49" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO49" s="1" t="s">
+      <c r="AQ49" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP49" s="1" t="s">
+      <c r="AR49" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="AQ49" s="1" t="s">
+      <c r="AS49" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>191</v>
       </c>
@@ -10308,23 +10648,26 @@
       <c r="AL50" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AM50" s="1" t="s">
+      <c r="AN50" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AO50" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="AN50" s="1" t="s">
+      <c r="AP50" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO50" s="1" t="s">
+      <c r="AQ50" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP50" s="1" t="s">
+      <c r="AR50" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="AQ50" s="1" t="s">
+      <c r="AS50" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>191</v>
       </c>
@@ -10435,23 +10778,23 @@
         <v>977</v>
       </c>
       <c r="AL51" s="1"/>
-      <c r="AM51" s="1" t="s">
+      <c r="AO51" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="AN51" s="1" t="s">
+      <c r="AP51" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO51" s="1" t="s">
+      <c r="AQ51" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP51" s="1" t="s">
+      <c r="AR51" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="AQ51" s="1" t="s">
+      <c r="AS51" s="1" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>230</v>
       </c>
@@ -10562,23 +10905,23 @@
       <c r="AL52" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM52" s="1" t="s">
+      <c r="AO52" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="AN52" s="1" t="s">
+      <c r="AP52" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO52" s="1" t="s">
+      <c r="AQ52" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP52" s="1" t="s">
+      <c r="AR52" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="AQ52" s="1" t="s">
+      <c r="AS52" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>230</v>
       </c>
@@ -10691,23 +11034,23 @@
       <c r="AL53" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM53" s="1" t="s">
+      <c r="AO53" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="AN53" s="1" t="s">
+      <c r="AP53" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO53" s="1" t="s">
+      <c r="AQ53" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP53" s="1" t="s">
+      <c r="AR53" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="AQ53" s="1" t="s">
+      <c r="AS53" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>230</v>
       </c>
@@ -10820,23 +11163,23 @@
       <c r="AL54" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM54" s="1" t="s">
+      <c r="AO54" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="AN54" s="1" t="s">
+      <c r="AP54" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO54" s="1" t="s">
+      <c r="AQ54" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP54" s="1" t="s">
+      <c r="AR54" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="AQ54" s="1" t="s">
+      <c r="AS54" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>230</v>
       </c>
@@ -10952,22 +11295,25 @@
         <v>977</v>
       </c>
       <c r="AM55" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AO55" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="AN55" s="1" t="s">
+      <c r="AP55" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO55" s="1" t="s">
+      <c r="AQ55" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP55" s="1" t="s">
+      <c r="AR55" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="AQ55" s="1" t="s">
+      <c r="AS55" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>230</v>
       </c>
@@ -11083,22 +11429,28 @@
         <v>977</v>
       </c>
       <c r="AM56" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AN56" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AO56" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="AN56" s="1" t="s">
+      <c r="AP56" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO56" s="1" t="s">
+      <c r="AQ56" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP56" s="1" t="s">
+      <c r="AR56" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="AQ56" s="1" t="s">
+      <c r="AS56" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>230</v>
       </c>
@@ -11213,23 +11565,23 @@
       <c r="AL57" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM57" s="1" t="s">
+      <c r="AO57" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="AN57" s="1" t="s">
+      <c r="AP57" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO57" s="1" t="s">
+      <c r="AQ57" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP57" s="1" t="s">
+      <c r="AR57" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="AQ57" s="1" t="s">
+      <c r="AS57" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>230</v>
       </c>
@@ -11343,22 +11695,25 @@
         <v>977</v>
       </c>
       <c r="AM58" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AO58" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="AN58" s="1" t="s">
+      <c r="AP58" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO58" s="1" t="s">
+      <c r="AQ58" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP58" s="1" t="s">
+      <c r="AR58" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="AQ58" s="1" t="s">
+      <c r="AS58" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>230</v>
       </c>
@@ -11473,23 +11828,23 @@
       <c r="AL59" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM59" s="1" t="s">
+      <c r="AO59" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="AN59" s="1" t="s">
+      <c r="AP59" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO59" s="1" t="s">
+      <c r="AQ59" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP59" s="1" t="s">
+      <c r="AR59" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AQ59" s="1" t="s">
+      <c r="AS59" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>230</v>
       </c>
@@ -11604,23 +11959,26 @@
       <c r="AL60" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM60" s="1" t="s">
+      <c r="AN60" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AO60" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="AN60" s="1" t="s">
+      <c r="AP60" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO60" s="1" t="s">
+      <c r="AQ60" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP60" s="1" t="s">
+      <c r="AR60" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="AQ60" s="1" t="s">
+      <c r="AS60" s="1" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>230</v>
       </c>
@@ -11735,23 +12093,23 @@
       <c r="AL61" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM61" s="1" t="s">
+      <c r="AO61" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AN61" s="1" t="s">
+      <c r="AP61" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO61" s="1" t="s">
+      <c r="AQ61" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP61" s="1" t="s">
+      <c r="AR61" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="AQ61" s="1" t="s">
+      <c r="AS61" s="1" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>266</v>
       </c>
@@ -11866,23 +12224,23 @@
       <c r="AL62" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM62" s="1" t="s">
+      <c r="AO62" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="AN62" s="1" t="s">
+      <c r="AP62" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO62" s="1" t="s">
+      <c r="AQ62" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP62" s="1" t="s">
+      <c r="AR62" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="AQ62" s="1" t="s">
+      <c r="AS62" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>266</v>
       </c>
@@ -11997,23 +12355,23 @@
       <c r="AL63" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM63" s="1" t="s">
+      <c r="AO63" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="AN63" s="1" t="s">
+      <c r="AP63" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO63" s="1" t="s">
+      <c r="AQ63" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP63" s="1" t="s">
+      <c r="AR63" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="AQ63" s="1" t="s">
+      <c r="AS63" s="1" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>266</v>
       </c>
@@ -12128,23 +12486,23 @@
       <c r="AL64" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM64" s="1" t="s">
+      <c r="AO64" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="AN64" s="1" t="s">
+      <c r="AP64" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO64" s="1" t="s">
+      <c r="AQ64" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP64" s="1" t="s">
+      <c r="AR64" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="AQ64" s="1" t="s">
+      <c r="AS64" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>266</v>
       </c>
@@ -12259,23 +12617,23 @@
       <c r="AL65" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM65" s="1" t="s">
+      <c r="AO65" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="AN65" s="1" t="s">
+      <c r="AP65" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO65" s="1" t="s">
+      <c r="AQ65" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP65" s="1" t="s">
+      <c r="AR65" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="AQ65" s="1" t="s">
+      <c r="AS65" s="1" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>266</v>
       </c>
@@ -12390,23 +12748,26 @@
       <c r="AL66" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM66" s="1" t="s">
+      <c r="AN66" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AO66" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="AN66" s="1" t="s">
+      <c r="AP66" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO66" s="1" t="s">
+      <c r="AQ66" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP66" s="1" t="s">
+      <c r="AR66" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="AQ66" s="1" t="s">
+      <c r="AS66" s="1" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>266</v>
       </c>
@@ -12521,23 +12882,23 @@
       <c r="AL67" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM67" s="1" t="s">
+      <c r="AO67" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="AN67" s="1" t="s">
+      <c r="AP67" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO67" s="1" t="s">
+      <c r="AQ67" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP67" s="1" t="s">
+      <c r="AR67" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="AQ67" s="1" t="s">
+      <c r="AS67" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>266</v>
       </c>
@@ -12652,23 +13013,23 @@
       <c r="AL68" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM68" s="1" t="s">
+      <c r="AO68" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="AN68" s="1" t="s">
+      <c r="AP68" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO68" s="1" t="s">
+      <c r="AQ68" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP68" s="1" t="s">
+      <c r="AR68" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="AQ68" s="1" t="s">
+      <c r="AS68" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>266</v>
       </c>
@@ -12783,23 +13144,23 @@
       <c r="AL69" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM69" s="1" t="s">
+      <c r="AO69" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="AN69" s="1" t="s">
+      <c r="AP69" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO69" s="1" t="s">
+      <c r="AQ69" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP69" s="1" t="s">
+      <c r="AR69" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="AQ69" s="1" t="s">
+      <c r="AS69" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>266</v>
       </c>
@@ -12915,22 +13276,25 @@
         <v>977</v>
       </c>
       <c r="AM70" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AO70" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="AN70" s="1" t="s">
+      <c r="AP70" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO70" s="1" t="s">
+      <c r="AQ70" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP70" s="1" t="s">
+      <c r="AR70" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="AQ70" s="1" t="s">
+      <c r="AS70" s="1" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>266</v>
       </c>
@@ -13045,23 +13409,23 @@
       <c r="AL71" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM71" s="1" t="s">
+      <c r="AO71" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="AN71" s="1" t="s">
+      <c r="AP71" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO71" s="1" t="s">
+      <c r="AQ71" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP71" s="1" t="s">
+      <c r="AR71" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="AQ71" s="1" t="s">
+      <c r="AS71" s="1" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="72" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>307</v>
       </c>
@@ -13177,22 +13541,25 @@
         <v>977</v>
       </c>
       <c r="AM72" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AO72" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="AN72" s="1" t="s">
+      <c r="AP72" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO72" s="1" t="s">
+      <c r="AQ72" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP72" s="1" t="s">
+      <c r="AR72" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="AQ72" s="1" t="s">
+      <c r="AS72" s="1" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>307</v>
       </c>
@@ -13307,23 +13674,23 @@
       <c r="AL73" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM73" s="1" t="s">
+      <c r="AO73" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AN73" s="1" t="s">
+      <c r="AP73" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO73" s="1" t="s">
+      <c r="AQ73" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP73" s="1" t="s">
+      <c r="AR73" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="AQ73" s="1" t="s">
+      <c r="AS73" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>307</v>
       </c>
@@ -13438,23 +13805,23 @@
       <c r="AL74" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM74" s="1" t="s">
+      <c r="AO74" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AN74" s="1" t="s">
+      <c r="AP74" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO74" s="1" t="s">
+      <c r="AQ74" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP74" s="1" t="s">
+      <c r="AR74" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="AQ74" s="1" t="s">
+      <c r="AS74" s="1" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>307</v>
       </c>
@@ -13569,23 +13936,23 @@
       <c r="AL75" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM75" s="1" t="s">
+      <c r="AO75" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="AN75" s="1" t="s">
+      <c r="AP75" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO75" s="1" t="s">
+      <c r="AQ75" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP75" s="1" t="s">
+      <c r="AR75" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="AQ75" s="1" t="s">
+      <c r="AS75" s="1" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>307</v>
       </c>
@@ -13700,23 +14067,23 @@
       <c r="AL76" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM76" s="1" t="s">
+      <c r="AO76" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AN76" s="1" t="s">
+      <c r="AP76" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO76" s="1" t="s">
+      <c r="AQ76" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP76" s="1" t="s">
+      <c r="AR76" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="AQ76" s="1" t="s">
+      <c r="AS76" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>307</v>
       </c>
@@ -13831,23 +14198,23 @@
       <c r="AL77" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM77" s="1" t="s">
+      <c r="AO77" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="AN77" s="1" t="s">
+      <c r="AP77" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO77" s="1" t="s">
+      <c r="AQ77" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP77" s="1" t="s">
+      <c r="AR77" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="AQ77" s="1" t="s">
+      <c r="AS77" s="1" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>307</v>
       </c>
@@ -13962,23 +14329,23 @@
       <c r="AL78" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM78" s="1" t="s">
+      <c r="AO78" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="AN78" s="1" t="s">
+      <c r="AP78" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO78" s="1" t="s">
+      <c r="AQ78" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP78" s="1" t="s">
+      <c r="AR78" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="AQ78" s="1" t="s">
+      <c r="AS78" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>307</v>
       </c>
@@ -14093,23 +14460,23 @@
       <c r="AL79" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM79" s="1" t="s">
+      <c r="AO79" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="AN79" s="1" t="s">
+      <c r="AP79" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO79" s="1" t="s">
+      <c r="AQ79" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP79" s="1" t="s">
+      <c r="AR79" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="AQ79" s="1" t="s">
+      <c r="AS79" s="1" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>307</v>
       </c>
@@ -14225,22 +14592,25 @@
         <v>977</v>
       </c>
       <c r="AM80" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AO80" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="AN80" s="1" t="s">
+      <c r="AP80" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO80" s="1" t="s">
+      <c r="AQ80" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP80" s="1" t="s">
+      <c r="AR80" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="AQ80" s="1" t="s">
+      <c r="AS80" s="1" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>307</v>
       </c>
@@ -14356,22 +14726,25 @@
         <v>977</v>
       </c>
       <c r="AM81" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AO81" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="AN81" s="1" t="s">
+      <c r="AP81" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO81" s="1" t="s">
+      <c r="AQ81" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP81" s="1" t="s">
+      <c r="AR81" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="AQ81" s="1" t="s">
+      <c r="AS81" s="1" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>342</v>
       </c>
@@ -14486,23 +14859,23 @@
       <c r="AL82" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM82" s="1" t="s">
+      <c r="AO82" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="AN82" s="1" t="s">
+      <c r="AP82" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO82" s="1" t="s">
+      <c r="AQ82" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP82" s="1" t="s">
+      <c r="AR82" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="AQ82" s="1" t="s">
+      <c r="AS82" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>342</v>
       </c>
@@ -14617,23 +14990,26 @@
       <c r="AL83" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM83" s="1" t="s">
+      <c r="AN83" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AO83" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="AN83" s="1" t="s">
+      <c r="AP83" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO83" s="1" t="s">
+      <c r="AQ83" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP83" s="1" t="s">
+      <c r="AR83" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="AQ83" s="1" t="s">
+      <c r="AS83" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>342</v>
       </c>
@@ -14748,23 +15124,23 @@
       <c r="AL84" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM84" s="1" t="s">
+      <c r="AO84" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="AN84" s="1" t="s">
+      <c r="AP84" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO84" s="1" t="s">
+      <c r="AQ84" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP84" s="1" t="s">
+      <c r="AR84" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="AQ84" s="1" t="s">
+      <c r="AS84" s="1" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>342</v>
       </c>
@@ -14879,23 +15255,23 @@
       <c r="AL85" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM85" s="1" t="s">
+      <c r="AO85" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AN85" s="1" t="s">
+      <c r="AP85" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO85" s="1" t="s">
+      <c r="AQ85" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP85" s="1" t="s">
+      <c r="AR85" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="AQ85" s="1" t="s">
+      <c r="AS85" s="1" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>342</v>
       </c>
@@ -15010,23 +15386,23 @@
       <c r="AL86" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM86" s="1" t="s">
+      <c r="AO86" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="AN86" s="1" t="s">
+      <c r="AP86" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO86" s="1" t="s">
+      <c r="AQ86" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP86" s="1" t="s">
+      <c r="AR86" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="AQ86" s="1" t="s">
+      <c r="AS86" s="1" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="87" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>342</v>
       </c>
@@ -15142,22 +15518,25 @@
         <v>977</v>
       </c>
       <c r="AM87" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AO87" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="AN87" s="1" t="s">
+      <c r="AP87" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO87" s="1" t="s">
+      <c r="AQ87" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP87" s="1" t="s">
+      <c r="AR87" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="AQ87" s="1" t="s">
+      <c r="AS87" s="1" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>342</v>
       </c>
@@ -15272,23 +15651,23 @@
       <c r="AL88" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM88" s="1" t="s">
+      <c r="AO88" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="AN88" s="1" t="s">
+      <c r="AP88" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO88" s="1" t="s">
+      <c r="AQ88" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP88" s="1" t="s">
+      <c r="AR88" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="AQ88" s="1" t="s">
+      <c r="AS88" s="1" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>342</v>
       </c>
@@ -15403,23 +15782,23 @@
       <c r="AL89" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM89" s="1" t="s">
+      <c r="AO89" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="AN89" s="1" t="s">
+      <c r="AP89" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO89" s="1" t="s">
+      <c r="AQ89" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP89" s="1" t="s">
+      <c r="AR89" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="AQ89" s="1" t="s">
+      <c r="AS89" s="1" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>342</v>
       </c>
@@ -15535,22 +15914,25 @@
         <v>977</v>
       </c>
       <c r="AM90" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AO90" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="AN90" s="1" t="s">
+      <c r="AP90" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO90" s="1" t="s">
+      <c r="AQ90" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP90" s="1" t="s">
+      <c r="AR90" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="AQ90" s="1" t="s">
+      <c r="AS90" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>342</v>
       </c>
@@ -15665,23 +16047,23 @@
       <c r="AL91" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM91" s="1" t="s">
+      <c r="AO91" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="AN91" s="1" t="s">
+      <c r="AP91" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO91" s="1" t="s">
+      <c r="AQ91" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP91" s="1" t="s">
+      <c r="AR91" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="AQ91" s="1" t="s">
+      <c r="AS91" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>391</v>
       </c>
@@ -15796,23 +16178,23 @@
       <c r="AL92" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM92" s="1" t="s">
+      <c r="AO92" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="AN92" s="1" t="s">
+      <c r="AP92" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO92" s="1" t="s">
+      <c r="AQ92" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP92" s="1" t="s">
+      <c r="AR92" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="AQ92" s="1" t="s">
+      <c r="AS92" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>391</v>
       </c>
@@ -15927,23 +16309,23 @@
       <c r="AL93" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM93" s="1" t="s">
+      <c r="AO93" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AN93" s="1" t="s">
+      <c r="AP93" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO93" s="1" t="s">
+      <c r="AQ93" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP93" s="1" t="s">
+      <c r="AR93" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="AQ93" s="1" t="s">
+      <c r="AS93" s="1" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>391</v>
       </c>
@@ -16058,23 +16440,23 @@
       <c r="AL94" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM94" s="1" t="s">
+      <c r="AO94" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="AN94" s="1" t="s">
+      <c r="AP94" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO94" s="1" t="s">
+      <c r="AQ94" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP94" s="1" t="s">
+      <c r="AR94" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="AQ94" s="1" t="s">
+      <c r="AS94" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>391</v>
       </c>
@@ -16189,23 +16571,26 @@
       <c r="AL95" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM95" s="1" t="s">
+      <c r="AN95" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AO95" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="AN95" s="1" t="s">
+      <c r="AP95" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO95" s="1" t="s">
+      <c r="AQ95" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP95" s="1" t="s">
+      <c r="AR95" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="AQ95" s="1" t="s">
+      <c r="AS95" s="1" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>391</v>
       </c>
@@ -16320,23 +16705,23 @@
       <c r="AL96" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM96" s="1" t="s">
+      <c r="AO96" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="AN96" s="1" t="s">
+      <c r="AP96" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO96" s="1" t="s">
+      <c r="AQ96" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP96" s="1" t="s">
+      <c r="AR96" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="AQ96" s="1" t="s">
+      <c r="AS96" s="1" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="97" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>391</v>
       </c>
@@ -16451,23 +16836,23 @@
       <c r="AL97" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM97" s="1" t="s">
+      <c r="AO97" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="AN97" s="1" t="s">
+      <c r="AP97" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO97" s="1" t="s">
+      <c r="AQ97" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP97" s="1" t="s">
+      <c r="AR97" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="AQ97" s="1" t="s">
+      <c r="AS97" s="1" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="98" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>391</v>
       </c>
@@ -16582,23 +16967,23 @@
       <c r="AL98" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM98" s="1" t="s">
+      <c r="AO98" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="AN98" s="1" t="s">
+      <c r="AP98" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO98" s="1" t="s">
+      <c r="AQ98" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP98" s="1" t="s">
+      <c r="AR98" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="AQ98" s="1" t="s">
+      <c r="AS98" s="1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="99" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>391</v>
       </c>
@@ -16713,23 +17098,23 @@
       <c r="AL99" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM99" s="1" t="s">
+      <c r="AO99" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="AN99" s="1" t="s">
+      <c r="AP99" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO99" s="1" t="s">
+      <c r="AQ99" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP99" s="1" t="s">
+      <c r="AR99" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="AQ99" s="1" t="s">
+      <c r="AS99" s="1" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="100" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>391</v>
       </c>
@@ -16844,23 +17229,23 @@
       <c r="AL100" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM100" s="1" t="s">
+      <c r="AO100" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="AN100" s="1" t="s">
+      <c r="AP100" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO100" s="1" t="s">
+      <c r="AQ100" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP100" s="1" t="s">
+      <c r="AR100" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="AQ100" s="1" t="s">
+      <c r="AS100" s="1" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="101" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>391</v>
       </c>
@@ -16975,23 +17360,23 @@
       <c r="AL101" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM101" s="1" t="s">
+      <c r="AO101" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="AN101" s="1" t="s">
+      <c r="AP101" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO101" s="1" t="s">
+      <c r="AQ101" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP101" s="1" t="s">
+      <c r="AR101" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="AQ101" s="1" t="s">
+      <c r="AS101" s="1" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="102" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>426</v>
       </c>
@@ -17107,22 +17492,25 @@
         <v>977</v>
       </c>
       <c r="AM102" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AO102" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="AN102" s="1" t="s">
+      <c r="AP102" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO102" s="1" t="s">
+      <c r="AQ102" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP102" s="1" t="s">
+      <c r="AR102" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="AQ102" s="1" t="s">
+      <c r="AS102" s="1" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="103" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>426</v>
       </c>
@@ -17237,23 +17625,23 @@
       <c r="AL103" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM103" s="1" t="s">
+      <c r="AO103" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="AN103" s="1" t="s">
+      <c r="AP103" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO103" s="1" t="s">
+      <c r="AQ103" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP103" s="1" t="s">
+      <c r="AR103" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="AQ103" s="1" t="s">
+      <c r="AS103" s="1" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="104" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>426</v>
       </c>
@@ -17368,23 +17756,23 @@
       <c r="AL104" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM104" s="1" t="s">
+      <c r="AO104" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="AN104" s="1" t="s">
+      <c r="AP104" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO104" s="1" t="s">
+      <c r="AQ104" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP104" s="1" t="s">
+      <c r="AR104" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="AQ104" s="1" t="s">
+      <c r="AS104" s="1" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="105" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>426</v>
       </c>
@@ -17499,23 +17887,23 @@
       <c r="AL105" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM105" s="1" t="s">
+      <c r="AO105" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="AN105" s="1" t="s">
+      <c r="AP105" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO105" s="1" t="s">
+      <c r="AQ105" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP105" s="1" t="s">
+      <c r="AR105" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="AQ105" s="1" t="s">
+      <c r="AS105" s="1" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="106" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>426</v>
       </c>
@@ -17630,23 +18018,23 @@
       <c r="AL106" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM106" s="1" t="s">
+      <c r="AO106" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="AN106" s="1" t="s">
+      <c r="AP106" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO106" s="1" t="s">
+      <c r="AQ106" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP106" s="1" t="s">
+      <c r="AR106" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="AQ106" s="1" t="s">
+      <c r="AS106" s="1" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="107" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>426</v>
       </c>
@@ -17761,23 +18149,23 @@
       <c r="AL107" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM107" s="1" t="s">
+      <c r="AO107" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="AN107" s="1" t="s">
+      <c r="AP107" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO107" s="1" t="s">
+      <c r="AQ107" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP107" s="1" t="s">
+      <c r="AR107" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="AQ107" s="1" t="s">
+      <c r="AS107" s="1" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="108" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>426</v>
       </c>
@@ -17892,23 +18280,23 @@
       <c r="AL108" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM108" s="1" t="s">
+      <c r="AO108" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="AN108" s="1" t="s">
+      <c r="AP108" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO108" s="1" t="s">
+      <c r="AQ108" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP108" s="1" t="s">
+      <c r="AR108" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="AQ108" s="1" t="s">
+      <c r="AS108" s="1" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="109" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>426</v>
       </c>
@@ -18023,23 +18411,23 @@
       <c r="AL109" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM109" s="1" t="s">
+      <c r="AO109" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="AN109" s="1" t="s">
+      <c r="AP109" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO109" s="1" t="s">
+      <c r="AQ109" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP109" s="1" t="s">
+      <c r="AR109" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="AQ109" s="1" t="s">
+      <c r="AS109" s="1" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="110" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>426</v>
       </c>
@@ -18154,23 +18542,23 @@
       <c r="AL110" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM110" s="1" t="s">
+      <c r="AO110" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="AN110" s="1" t="s">
+      <c r="AP110" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO110" s="1" t="s">
+      <c r="AQ110" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP110" s="1" t="s">
+      <c r="AR110" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="AQ110" s="1" t="s">
+      <c r="AS110" s="1" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="111" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>426</v>
       </c>
@@ -18285,23 +18673,23 @@
       <c r="AL111" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM111" s="1" t="s">
+      <c r="AO111" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="AN111" s="1" t="s">
+      <c r="AP111" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO111" s="1" t="s">
+      <c r="AQ111" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP111" s="1" t="s">
+      <c r="AR111" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="AQ111" s="1" t="s">
+      <c r="AS111" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="112" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>466</v>
       </c>
@@ -18417,22 +18805,25 @@
         <v>977</v>
       </c>
       <c r="AM112" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AO112" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="AN112" s="1" t="s">
+      <c r="AP112" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO112" s="1" t="s">
+      <c r="AQ112" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP112" s="1" t="s">
+      <c r="AR112" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="AQ112" s="1" t="s">
+      <c r="AS112" s="1" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="113" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>466</v>
       </c>
@@ -18547,23 +18938,23 @@
       <c r="AL113" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM113" s="1" t="s">
+      <c r="AO113" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AN113" s="1" t="s">
+      <c r="AP113" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO113" s="1" t="s">
+      <c r="AQ113" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP113" s="1" t="s">
+      <c r="AR113" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="AQ113" s="1" t="s">
+      <c r="AS113" s="1" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="114" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>466</v>
       </c>
@@ -18678,23 +19069,23 @@
       <c r="AL114" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM114" s="1" t="s">
+      <c r="AO114" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="AN114" s="1" t="s">
+      <c r="AP114" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO114" s="1" t="s">
+      <c r="AQ114" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP114" s="1" t="s">
+      <c r="AR114" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="AQ114" s="1" t="s">
+      <c r="AS114" s="1" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="115" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>466</v>
       </c>
@@ -18809,23 +19200,23 @@
       <c r="AL115" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM115" s="1" t="s">
+      <c r="AO115" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="AN115" s="1" t="s">
+      <c r="AP115" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO115" s="1" t="s">
+      <c r="AQ115" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP115" s="1" t="s">
+      <c r="AR115" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="AQ115" s="1" t="s">
+      <c r="AS115" s="1" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="116" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>466</v>
       </c>
@@ -18940,23 +19331,23 @@
       <c r="AL116" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM116" s="1" t="s">
+      <c r="AO116" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="AN116" s="1" t="s">
+      <c r="AP116" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO116" s="1" t="s">
+      <c r="AQ116" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP116" s="1" t="s">
+      <c r="AR116" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="AQ116" s="1" t="s">
+      <c r="AS116" s="1" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="117" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>466</v>
       </c>
@@ -19072,22 +19463,25 @@
         <v>977</v>
       </c>
       <c r="AM117" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AO117" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="AN117" s="1" t="s">
+      <c r="AP117" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO117" s="1" t="s">
+      <c r="AQ117" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP117" s="1" t="s">
+      <c r="AR117" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="AQ117" s="1" t="s">
+      <c r="AS117" s="1" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="118" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>466</v>
       </c>
@@ -19202,23 +19596,23 @@
       <c r="AL118" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM118" s="1" t="s">
+      <c r="AO118" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="AN118" s="1" t="s">
+      <c r="AP118" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO118" s="1" t="s">
+      <c r="AQ118" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP118" s="1" t="s">
+      <c r="AR118" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="AQ118" s="1" t="s">
+      <c r="AS118" s="1" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="119" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>466</v>
       </c>
@@ -19333,23 +19727,26 @@
       <c r="AL119" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM119" s="1" t="s">
+      <c r="AN119" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AO119" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="AN119" s="1" t="s">
+      <c r="AP119" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO119" s="1" t="s">
+      <c r="AQ119" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP119" s="1" t="s">
+      <c r="AR119" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="AQ119" s="1" t="s">
+      <c r="AS119" s="1" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="120" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>466</v>
       </c>
@@ -19464,23 +19861,23 @@
       <c r="AL120" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM120" s="1" t="s">
+      <c r="AO120" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="AN120" s="1" t="s">
+      <c r="AP120" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO120" s="1" t="s">
+      <c r="AQ120" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP120" s="1" t="s">
+      <c r="AR120" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="AQ120" s="1" t="s">
+      <c r="AS120" s="1" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="121" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>466</v>
       </c>
@@ -19595,23 +19992,26 @@
       <c r="AL121" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM121" s="1" t="s">
+      <c r="AN121" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AO121" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="AN121" s="1" t="s">
+      <c r="AP121" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO121" s="1" t="s">
+      <c r="AQ121" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP121" s="1" t="s">
+      <c r="AR121" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="AQ121" s="1" t="s">
+      <c r="AS121" s="1" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="122" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>504</v>
       </c>
@@ -19726,23 +20126,26 @@
       <c r="AL122" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM122" s="1" t="s">
+      <c r="AN122" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AO122" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="AN122" s="1" t="s">
+      <c r="AP122" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO122" s="1" t="s">
+      <c r="AQ122" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP122" s="1" t="s">
+      <c r="AR122" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="AQ122" s="1" t="s">
+      <c r="AS122" s="1" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="123" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>504</v>
       </c>
@@ -19857,23 +20260,23 @@
       <c r="AL123" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM123" s="1" t="s">
+      <c r="AO123" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="AN123" s="1" t="s">
+      <c r="AP123" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO123" s="1" t="s">
+      <c r="AQ123" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP123" s="1" t="s">
+      <c r="AR123" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="AQ123" s="1" t="s">
+      <c r="AS123" s="1" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="124" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>504</v>
       </c>
@@ -19988,23 +20391,26 @@
       <c r="AL124" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM124" s="1" t="s">
+      <c r="AN124" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AO124" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="AN124" s="1" t="s">
+      <c r="AP124" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO124" s="1" t="s">
+      <c r="AQ124" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP124" s="1" t="s">
+      <c r="AR124" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="AQ124" s="1" t="s">
+      <c r="AS124" s="1" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="125" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>504</v>
       </c>
@@ -20119,23 +20525,23 @@
       <c r="AL125" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM125" s="1" t="s">
+      <c r="AO125" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="AN125" s="1" t="s">
+      <c r="AP125" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO125" s="1" t="s">
+      <c r="AQ125" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP125" s="1" t="s">
+      <c r="AR125" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="AQ125" s="1" t="s">
+      <c r="AS125" s="1" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="126" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>504</v>
       </c>
@@ -20250,23 +20656,23 @@
       <c r="AL126" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM126" s="1" t="s">
+      <c r="AO126" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="AN126" s="1" t="s">
+      <c r="AP126" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO126" s="1" t="s">
+      <c r="AQ126" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP126" s="1" t="s">
+      <c r="AR126" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="AQ126" s="1" t="s">
+      <c r="AS126" s="1" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="127" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>504</v>
       </c>
@@ -20381,23 +20787,23 @@
       <c r="AL127" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM127" s="1" t="s">
+      <c r="AO127" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="AN127" s="1" t="s">
+      <c r="AP127" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO127" s="1" t="s">
+      <c r="AQ127" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP127" s="1" t="s">
+      <c r="AR127" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="AQ127" s="1" t="s">
+      <c r="AS127" s="1" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="128" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>504</v>
       </c>
@@ -20512,23 +20918,26 @@
       <c r="AL128" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM128" s="1" t="s">
+      <c r="AN128" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AO128" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="AN128" s="1" t="s">
+      <c r="AP128" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO128" s="1" t="s">
+      <c r="AQ128" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP128" s="1" t="s">
+      <c r="AR128" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="AQ128" s="1" t="s">
+      <c r="AS128" s="1" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="129" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>504</v>
       </c>
@@ -20643,23 +21052,26 @@
       <c r="AL129" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM129" s="1" t="s">
+      <c r="AN129" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AO129" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="AN129" s="1" t="s">
+      <c r="AP129" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO129" s="1" t="s">
+      <c r="AQ129" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP129" s="1" t="s">
+      <c r="AR129" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="AQ129" s="1" t="s">
+      <c r="AS129" s="1" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="130" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>504</v>
       </c>
@@ -20774,23 +21186,26 @@
       <c r="AL130" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM130" s="1" t="s">
+      <c r="AN130" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AO130" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="AN130" s="1" t="s">
+      <c r="AP130" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO130" s="1" t="s">
+      <c r="AQ130" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP130" s="1" t="s">
+      <c r="AR130" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="AQ130" s="1" t="s">
+      <c r="AS130" s="1" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="131" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>504</v>
       </c>
@@ -20905,23 +21320,23 @@
       <c r="AL131" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM131" s="1" t="s">
+      <c r="AO131" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="AN131" s="1" t="s">
+      <c r="AP131" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO131" s="1" t="s">
+      <c r="AQ131" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP131" s="1" t="s">
+      <c r="AR131" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="AQ131" s="1" t="s">
+      <c r="AS131" s="1" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="132" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>542</v>
       </c>
@@ -21036,23 +21451,23 @@
       <c r="AL132" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM132" s="1" t="s">
+      <c r="AO132" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="AN132" s="1" t="s">
+      <c r="AP132" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO132" s="1" t="s">
+      <c r="AQ132" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP132" s="1" t="s">
+      <c r="AR132" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="AQ132" s="1" t="s">
+      <c r="AS132" s="1" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="133" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>542</v>
       </c>
@@ -21167,23 +21582,23 @@
       <c r="AL133" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM133" s="1" t="s">
+      <c r="AO133" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="AN133" s="1" t="s">
+      <c r="AP133" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO133" s="1" t="s">
+      <c r="AQ133" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP133" s="1" t="s">
+      <c r="AR133" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="AQ133" s="1" t="s">
+      <c r="AS133" s="1" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="134" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>542</v>
       </c>
@@ -21298,23 +21713,23 @@
       <c r="AL134" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM134" s="1" t="s">
+      <c r="AO134" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="AN134" s="1" t="s">
+      <c r="AP134" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO134" s="1" t="s">
+      <c r="AQ134" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP134" s="1" t="s">
+      <c r="AR134" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="AQ134" s="1" t="s">
+      <c r="AS134" s="1" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="135" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>542</v>
       </c>
@@ -21429,23 +21844,23 @@
       <c r="AL135" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM135" s="1" t="s">
+      <c r="AO135" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="AN135" s="1" t="s">
+      <c r="AP135" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO135" s="1" t="s">
+      <c r="AQ135" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP135" s="1" t="s">
+      <c r="AR135" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="AQ135" s="1" t="s">
+      <c r="AS135" s="1" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="136" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>542</v>
       </c>
@@ -21560,23 +21975,23 @@
       <c r="AL136" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM136" s="1" t="s">
+      <c r="AO136" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="AN136" s="1" t="s">
+      <c r="AP136" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO136" s="1" t="s">
+      <c r="AQ136" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP136" s="1" t="s">
+      <c r="AR136" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="AQ136" s="1" t="s">
+      <c r="AS136" s="1" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="137" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>542</v>
       </c>
@@ -21691,23 +22106,23 @@
       <c r="AL137" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM137" s="1" t="s">
+      <c r="AO137" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="AN137" s="1" t="s">
+      <c r="AP137" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO137" s="1" t="s">
+      <c r="AQ137" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP137" s="1" t="s">
+      <c r="AR137" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="AQ137" s="1" t="s">
+      <c r="AS137" s="1" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="138" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>542</v>
       </c>
@@ -21823,22 +22238,25 @@
         <v>977</v>
       </c>
       <c r="AM138" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AO138" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="AN138" s="1" t="s">
+      <c r="AP138" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO138" s="1" t="s">
+      <c r="AQ138" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP138" s="1" t="s">
+      <c r="AR138" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="AQ138" s="1" t="s">
+      <c r="AS138" s="1" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="139" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>542</v>
       </c>
@@ -21953,23 +22371,23 @@
       <c r="AL139" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM139" s="1" t="s">
+      <c r="AO139" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="AN139" s="1" t="s">
+      <c r="AP139" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO139" s="1" t="s">
+      <c r="AQ139" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP139" s="1" t="s">
+      <c r="AR139" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="AQ139" s="1" t="s">
+      <c r="AS139" s="1" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="140" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>542</v>
       </c>
@@ -22084,23 +22502,23 @@
       <c r="AL140" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM140" s="1" t="s">
+      <c r="AO140" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="AN140" s="1" t="s">
+      <c r="AP140" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO140" s="1" t="s">
+      <c r="AQ140" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP140" s="1" t="s">
+      <c r="AR140" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="AQ140" s="1" t="s">
+      <c r="AS140" s="1" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="141" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>542</v>
       </c>
@@ -22215,23 +22633,23 @@
       <c r="AL141" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM141" s="1" t="s">
+      <c r="AO141" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="AN141" s="1" t="s">
+      <c r="AP141" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO141" s="1" t="s">
+      <c r="AQ141" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP141" s="1" t="s">
+      <c r="AR141" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="AQ141" s="1" t="s">
+      <c r="AS141" s="1" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="142" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>578</v>
       </c>
@@ -22346,23 +22764,23 @@
       <c r="AL142" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM142" s="1" t="s">
+      <c r="AO142" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="AN142" s="1" t="s">
+      <c r="AP142" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO142" s="1" t="s">
+      <c r="AQ142" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP142" s="1" t="s">
+      <c r="AR142" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="AQ142" s="1" t="s">
+      <c r="AS142" s="1" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="143" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>578</v>
       </c>
@@ -22477,23 +22895,23 @@
       <c r="AL143" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM143" s="1" t="s">
+      <c r="AO143" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="AN143" s="1" t="s">
+      <c r="AP143" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO143" s="1" t="s">
+      <c r="AQ143" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP143" s="1" t="s">
+      <c r="AR143" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="AQ143" s="1" t="s">
+      <c r="AS143" s="1" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="144" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>578</v>
       </c>
@@ -22608,23 +23026,23 @@
       <c r="AL144" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM144" s="1" t="s">
+      <c r="AO144" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="AN144" s="1" t="s">
+      <c r="AP144" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO144" s="1" t="s">
+      <c r="AQ144" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP144" s="1" t="s">
+      <c r="AR144" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="AQ144" s="1" t="s">
+      <c r="AS144" s="1" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="145" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>578</v>
       </c>
@@ -22739,23 +23157,23 @@
       <c r="AL145" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM145" s="1" t="s">
+      <c r="AO145" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="AN145" s="1" t="s">
+      <c r="AP145" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO145" s="1" t="s">
+      <c r="AQ145" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP145" s="1" t="s">
+      <c r="AR145" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="AQ145" s="1" t="s">
+      <c r="AS145" s="1" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="146" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>578</v>
       </c>
@@ -22870,23 +23288,23 @@
       <c r="AL146" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM146" s="1" t="s">
+      <c r="AO146" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="AN146" s="1" t="s">
+      <c r="AP146" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO146" s="1" t="s">
+      <c r="AQ146" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP146" s="1" t="s">
+      <c r="AR146" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="AQ146" s="1" t="s">
+      <c r="AS146" s="1" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="147" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>578</v>
       </c>
@@ -23001,23 +23419,23 @@
       <c r="AL147" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM147" s="1" t="s">
+      <c r="AO147" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="AN147" s="1" t="s">
+      <c r="AP147" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO147" s="1" t="s">
+      <c r="AQ147" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP147" s="1" t="s">
+      <c r="AR147" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="AQ147" s="1" t="s">
+      <c r="AS147" s="1" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="148" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>578</v>
       </c>
@@ -23132,23 +23550,23 @@
       <c r="AL148" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM148" s="1" t="s">
+      <c r="AO148" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="AN148" s="1" t="s">
+      <c r="AP148" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO148" s="1" t="s">
+      <c r="AQ148" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP148" s="1" t="s">
+      <c r="AR148" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="AQ148" s="1" t="s">
+      <c r="AS148" s="1" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="149" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>578</v>
       </c>
@@ -23263,23 +23681,23 @@
       <c r="AL149" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM149" s="1" t="s">
+      <c r="AO149" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="AN149" s="1" t="s">
+      <c r="AP149" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO149" s="1" t="s">
+      <c r="AQ149" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP149" s="1" t="s">
+      <c r="AR149" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="AQ149" s="1" t="s">
+      <c r="AS149" s="1" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="150" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>578</v>
       </c>
@@ -23395,22 +23813,25 @@
         <v>977</v>
       </c>
       <c r="AM150" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AO150" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="AN150" s="1" t="s">
+      <c r="AP150" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO150" s="1" t="s">
+      <c r="AQ150" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP150" s="1" t="s">
+      <c r="AR150" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="AQ150" s="1" t="s">
+      <c r="AS150" s="1" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="151" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>578</v>
       </c>
@@ -23525,23 +23946,23 @@
       <c r="AL151" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM151" s="1" t="s">
+      <c r="AO151" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="AN151" s="1" t="s">
+      <c r="AP151" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO151" s="1" t="s">
+      <c r="AQ151" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP151" s="1" t="s">
+      <c r="AR151" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="AQ151" s="1" t="s">
+      <c r="AS151" s="1" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="152" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>611</v>
       </c>
@@ -23656,23 +24077,23 @@
       <c r="AL152" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM152" s="1" t="s">
+      <c r="AO152" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="AN152" s="1" t="s">
+      <c r="AP152" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO152" s="1" t="s">
+      <c r="AQ152" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP152" s="1" t="s">
+      <c r="AR152" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="AQ152" s="1" t="s">
+      <c r="AS152" s="1" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="153" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>611</v>
       </c>
@@ -23787,23 +24208,23 @@
       <c r="AL153" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM153" s="1" t="s">
+      <c r="AO153" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="AN153" s="1" t="s">
+      <c r="AP153" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO153" s="1" t="s">
+      <c r="AQ153" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP153" s="1" t="s">
+      <c r="AR153" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="AQ153" s="1" t="s">
+      <c r="AS153" s="1" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="154" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>611</v>
       </c>
@@ -23918,23 +24339,23 @@
       <c r="AL154" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM154" s="1" t="s">
+      <c r="AO154" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="AN154" s="1" t="s">
+      <c r="AP154" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO154" s="1" t="s">
+      <c r="AQ154" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP154" s="1" t="s">
+      <c r="AR154" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="AQ154" s="1" t="s">
+      <c r="AS154" s="1" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="155" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>611</v>
       </c>
@@ -24049,23 +24470,23 @@
       <c r="AL155" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM155" s="1" t="s">
+      <c r="AO155" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="AN155" s="1" t="s">
+      <c r="AP155" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO155" s="1" t="s">
+      <c r="AQ155" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP155" s="1" t="s">
+      <c r="AR155" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="AQ155" s="1" t="s">
+      <c r="AS155" s="1" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="156" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>611</v>
       </c>
@@ -24180,23 +24601,26 @@
       <c r="AL156" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM156" s="1" t="s">
+      <c r="AN156" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="AO156" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="AN156" s="1" t="s">
+      <c r="AP156" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO156" s="1" t="s">
+      <c r="AQ156" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP156" s="1" t="s">
+      <c r="AR156" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="AQ156" s="1" t="s">
+      <c r="AS156" s="1" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="157" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>611</v>
       </c>
@@ -24311,23 +24735,23 @@
       <c r="AL157" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM157" s="1" t="s">
+      <c r="AO157" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="AN157" s="1" t="s">
+      <c r="AP157" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO157" s="1" t="s">
+      <c r="AQ157" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP157" s="1" t="s">
+      <c r="AR157" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="AQ157" s="1" t="s">
+      <c r="AS157" s="1" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="158" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>611</v>
       </c>
@@ -24442,23 +24866,23 @@
       <c r="AL158" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM158" s="1" t="s">
+      <c r="AO158" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="AN158" s="1" t="s">
+      <c r="AP158" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO158" s="1" t="s">
+      <c r="AQ158" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP158" s="1" t="s">
+      <c r="AR158" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="AQ158" s="1" t="s">
+      <c r="AS158" s="1" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="159" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>611</v>
       </c>
@@ -24573,23 +24997,23 @@
       <c r="AL159" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM159" s="1" t="s">
+      <c r="AO159" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="AN159" s="1" t="s">
+      <c r="AP159" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO159" s="1" t="s">
+      <c r="AQ159" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP159" s="1" t="s">
+      <c r="AR159" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="AQ159" s="1" t="s">
+      <c r="AS159" s="1" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="160" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>611</v>
       </c>
@@ -24704,23 +25128,23 @@
       <c r="AL160" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM160" s="1" t="s">
+      <c r="AO160" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="AN160" s="1" t="s">
+      <c r="AP160" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO160" s="1" t="s">
+      <c r="AQ160" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP160" s="1" t="s">
+      <c r="AR160" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="AQ160" s="1" t="s">
+      <c r="AS160" s="1" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="161" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>611</v>
       </c>
@@ -24835,23 +25259,23 @@
       <c r="AL161" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM161" s="1" t="s">
+      <c r="AO161" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="AN161" s="1" t="s">
+      <c r="AP161" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO161" s="1" t="s">
+      <c r="AQ161" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP161" s="1" t="s">
+      <c r="AR161" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="AQ161" s="1" t="s">
+      <c r="AS161" s="1" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="162" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>646</v>
       </c>
@@ -24966,23 +25390,23 @@
       <c r="AL162" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM162" s="1" t="s">
+      <c r="AO162" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="AN162" s="1" t="s">
+      <c r="AP162" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO162" s="1" t="s">
+      <c r="AQ162" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP162" s="1" t="s">
+      <c r="AR162" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="AQ162" s="1" t="s">
+      <c r="AS162" s="1" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="163" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>646</v>
       </c>
@@ -25097,23 +25521,23 @@
       <c r="AL163" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM163" s="1" t="s">
+      <c r="AO163" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="AN163" s="1" t="s">
+      <c r="AP163" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO163" s="1" t="s">
+      <c r="AQ163" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP163" s="1" t="s">
+      <c r="AR163" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="AQ163" s="1" t="s">
+      <c r="AS163" s="1" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="164" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>646</v>
       </c>
@@ -25228,23 +25652,23 @@
       <c r="AL164" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM164" s="1" t="s">
+      <c r="AO164" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="AN164" s="1" t="s">
+      <c r="AP164" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO164" s="1" t="s">
+      <c r="AQ164" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP164" s="1" t="s">
+      <c r="AR164" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="AQ164" s="1" t="s">
+      <c r="AS164" s="1" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="165" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>646</v>
       </c>
@@ -25360,22 +25784,25 @@
         <v>977</v>
       </c>
       <c r="AM165" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AO165" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="AN165" s="1" t="s">
+      <c r="AP165" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO165" s="1" t="s">
+      <c r="AQ165" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP165" s="1" t="s">
+      <c r="AR165" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="AQ165" s="1" t="s">
+      <c r="AS165" s="1" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="166" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>646</v>
       </c>
@@ -25490,23 +25917,23 @@
       <c r="AL166" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM166" s="1" t="s">
+      <c r="AO166" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="AN166" s="1" t="s">
+      <c r="AP166" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO166" s="1" t="s">
+      <c r="AQ166" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP166" s="1" t="s">
+      <c r="AR166" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="AQ166" s="1" t="s">
+      <c r="AS166" s="1" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="167" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>646</v>
       </c>
@@ -25621,23 +26048,23 @@
       <c r="AL167" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM167" s="1" t="s">
+      <c r="AO167" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="AN167" s="1" t="s">
+      <c r="AP167" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO167" s="1" t="s">
+      <c r="AQ167" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP167" s="1" t="s">
+      <c r="AR167" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="AQ167" s="1" t="s">
+      <c r="AS167" s="1" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="168" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>646</v>
       </c>
@@ -25752,23 +26179,26 @@
       <c r="AL168" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM168" s="1" t="s">
+      <c r="AN168" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="AO168" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="AN168" s="1" t="s">
+      <c r="AP168" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO168" s="1" t="s">
+      <c r="AQ168" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP168" s="1" t="s">
+      <c r="AR168" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="AQ168" s="1" t="s">
+      <c r="AS168" s="1" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="169" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>646</v>
       </c>
@@ -25883,23 +26313,23 @@
       <c r="AL169" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM169" s="1" t="s">
+      <c r="AO169" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="AN169" s="1" t="s">
+      <c r="AP169" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO169" s="1" t="s">
+      <c r="AQ169" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP169" s="1" t="s">
+      <c r="AR169" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="AQ169" s="1" t="s">
+      <c r="AS169" s="1" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="170" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>646</v>
       </c>
@@ -26014,23 +26444,23 @@
       <c r="AL170" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM170" s="1" t="s">
+      <c r="AO170" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="AN170" s="1" t="s">
+      <c r="AP170" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO170" s="1" t="s">
+      <c r="AQ170" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP170" s="1" t="s">
+      <c r="AR170" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="AQ170" s="1" t="s">
+      <c r="AS170" s="1" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="171" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>646</v>
       </c>
@@ -26145,23 +26575,23 @@
       <c r="AL171" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM171" s="1" t="s">
+      <c r="AO171" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="AN171" s="1" t="s">
+      <c r="AP171" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO171" s="1" t="s">
+      <c r="AQ171" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP171" s="1" t="s">
+      <c r="AR171" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="AQ171" s="1" t="s">
+      <c r="AS171" s="1" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="172" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>685</v>
       </c>
@@ -26276,23 +26706,23 @@
       <c r="AL172" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM172" s="1" t="s">
+      <c r="AO172" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="AN172" s="1" t="s">
+      <c r="AP172" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO172" s="1" t="s">
+      <c r="AQ172" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP172" s="1" t="s">
+      <c r="AR172" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="AQ172" s="1" t="s">
+      <c r="AS172" s="1" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="173" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>685</v>
       </c>
@@ -26407,23 +26837,26 @@
       <c r="AL173" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM173" s="1" t="s">
+      <c r="AN173" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AO173" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="AN173" s="1" t="s">
+      <c r="AP173" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO173" s="1" t="s">
+      <c r="AQ173" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP173" s="1" t="s">
+      <c r="AR173" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="AQ173" s="1" t="s">
+      <c r="AS173" s="1" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="174" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>685</v>
       </c>
@@ -26538,23 +26971,23 @@
       <c r="AL174" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM174" s="1" t="s">
+      <c r="AO174" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="AN174" s="1" t="s">
+      <c r="AP174" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO174" s="1" t="s">
+      <c r="AQ174" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP174" s="1" t="s">
+      <c r="AR174" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="AQ174" s="1" t="s">
+      <c r="AS174" s="1" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="175" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>685</v>
       </c>
@@ -26669,23 +27102,23 @@
       <c r="AL175" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM175" s="1" t="s">
+      <c r="AO175" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AN175" s="1" t="s">
+      <c r="AP175" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO175" s="1" t="s">
+      <c r="AQ175" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP175" s="1" t="s">
+      <c r="AR175" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="AQ175" s="1" t="s">
+      <c r="AS175" s="1" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="176" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>685</v>
       </c>
@@ -26800,23 +27233,23 @@
       <c r="AL176" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM176" s="1" t="s">
+      <c r="AO176" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="AN176" s="1" t="s">
+      <c r="AP176" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO176" s="1" t="s">
+      <c r="AQ176" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP176" s="1" t="s">
+      <c r="AR176" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="AQ176" s="1" t="s">
+      <c r="AS176" s="1" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="177" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>685</v>
       </c>
@@ -26931,23 +27364,23 @@
       <c r="AL177" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM177" s="1" t="s">
+      <c r="AO177" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="AN177" s="1" t="s">
+      <c r="AP177" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO177" s="1" t="s">
+      <c r="AQ177" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP177" s="1" t="s">
+      <c r="AR177" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="AQ177" s="1" t="s">
+      <c r="AS177" s="1" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="178" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>685</v>
       </c>
@@ -27062,23 +27495,23 @@
       <c r="AL178" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM178" s="1" t="s">
+      <c r="AO178" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="AN178" s="1" t="s">
+      <c r="AP178" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO178" s="1" t="s">
+      <c r="AQ178" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP178" s="1" t="s">
+      <c r="AR178" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="AQ178" s="1" t="s">
+      <c r="AS178" s="1" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="179" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>685</v>
       </c>
@@ -27193,23 +27626,23 @@
       <c r="AL179" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM179" s="1" t="s">
+      <c r="AO179" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="AN179" s="1" t="s">
+      <c r="AP179" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO179" s="1" t="s">
+      <c r="AQ179" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP179" s="1" t="s">
+      <c r="AR179" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="AQ179" s="1" t="s">
+      <c r="AS179" s="1" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="180" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>685</v>
       </c>
@@ -27324,23 +27757,23 @@
       <c r="AL180" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM180" s="1" t="s">
+      <c r="AO180" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="AN180" s="1" t="s">
+      <c r="AP180" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO180" s="1" t="s">
+      <c r="AQ180" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP180" s="1" t="s">
+      <c r="AR180" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="AQ180" s="1" t="s">
+      <c r="AS180" s="1" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="181" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>685</v>
       </c>
@@ -27455,23 +27888,23 @@
       <c r="AL181" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM181" s="1" t="s">
+      <c r="AO181" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="AN181" s="1" t="s">
+      <c r="AP181" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO181" s="1" t="s">
+      <c r="AQ181" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP181" s="1" t="s">
+      <c r="AR181" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="AQ181" s="1" t="s">
+      <c r="AS181" s="1" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="182" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>724</v>
       </c>
@@ -27586,23 +28019,23 @@
       <c r="AL182" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM182" s="1" t="s">
+      <c r="AO182" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="AN182" s="1" t="s">
+      <c r="AP182" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO182" s="1" t="s">
+      <c r="AQ182" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP182" s="1" t="s">
+      <c r="AR182" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="AQ182" s="1" t="s">
+      <c r="AS182" s="1" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="183" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>724</v>
       </c>
@@ -27717,23 +28150,26 @@
       <c r="AL183" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM183" s="1" t="s">
+      <c r="AN183" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="AO183" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="AN183" s="1" t="s">
+      <c r="AP183" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO183" s="1" t="s">
+      <c r="AQ183" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP183" s="1" t="s">
+      <c r="AR183" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="AQ183" s="1" t="s">
+      <c r="AS183" s="1" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="184" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>724</v>
       </c>
@@ -27848,23 +28284,26 @@
       <c r="AL184" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM184" s="1" t="s">
+      <c r="AN184" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AO184" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="AN184" s="1" t="s">
+      <c r="AP184" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO184" s="1" t="s">
+      <c r="AQ184" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP184" s="1" t="s">
+      <c r="AR184" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="AQ184" s="1" t="s">
+      <c r="AS184" s="1" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="185" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>724</v>
       </c>
@@ -27979,23 +28418,23 @@
       <c r="AL185" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM185" s="1" t="s">
+      <c r="AO185" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="AN185" s="1" t="s">
+      <c r="AP185" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO185" s="1" t="s">
+      <c r="AQ185" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP185" s="1" t="s">
+      <c r="AR185" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="AQ185" s="1" t="s">
+      <c r="AS185" s="1" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="186" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>724</v>
       </c>
@@ -28110,23 +28549,23 @@
       <c r="AL186" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM186" s="1" t="s">
+      <c r="AO186" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="AN186" s="1" t="s">
+      <c r="AP186" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO186" s="1" t="s">
+      <c r="AQ186" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP186" s="1" t="s">
+      <c r="AR186" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="AQ186" s="1" t="s">
+      <c r="AS186" s="1" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="187" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>724</v>
       </c>
@@ -28241,23 +28680,23 @@
       <c r="AL187" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM187" s="1" t="s">
+      <c r="AO187" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="AN187" s="1" t="s">
+      <c r="AP187" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO187" s="1" t="s">
+      <c r="AQ187" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP187" s="1" t="s">
+      <c r="AR187" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="AQ187" s="1" t="s">
+      <c r="AS187" s="1" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="188" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>724</v>
       </c>
@@ -28372,23 +28811,23 @@
       <c r="AL188" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM188" s="1" t="s">
+      <c r="AO188" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="AN188" s="1" t="s">
+      <c r="AP188" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO188" s="1" t="s">
+      <c r="AQ188" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP188" s="1" t="s">
+      <c r="AR188" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="AQ188" s="1" t="s">
+      <c r="AS188" s="1" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="189" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>724</v>
       </c>
@@ -28503,23 +28942,26 @@
       <c r="AL189" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM189" s="1" t="s">
+      <c r="AN189" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AO189" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="AN189" s="1" t="s">
+      <c r="AP189" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO189" s="1" t="s">
+      <c r="AQ189" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP189" s="1" t="s">
+      <c r="AR189" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="AQ189" s="1" t="s">
+      <c r="AS189" s="1" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="190" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>724</v>
       </c>
@@ -28634,23 +29076,23 @@
       <c r="AL190" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM190" s="1" t="s">
+      <c r="AO190" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="AN190" s="1" t="s">
+      <c r="AP190" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO190" s="1" t="s">
+      <c r="AQ190" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP190" s="1" t="s">
+      <c r="AR190" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="AQ190" s="1" t="s">
+      <c r="AS190" s="1" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="191" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>724</v>
       </c>
@@ -28765,23 +29207,23 @@
       <c r="AL191" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM191" s="1" t="s">
+      <c r="AO191" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="AN191" s="1" t="s">
+      <c r="AP191" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO191" s="1" t="s">
+      <c r="AQ191" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP191" s="1" t="s">
+      <c r="AR191" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="AQ191" s="1" t="s">
+      <c r="AS191" s="1" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="192" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>764</v>
       </c>
@@ -28896,23 +29338,26 @@
       <c r="AL192" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM192" s="1" t="s">
+      <c r="AN192" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AO192" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="AN192" s="1" t="s">
+      <c r="AP192" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO192" s="1" t="s">
+      <c r="AQ192" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP192" s="1" t="s">
+      <c r="AR192" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="AQ192" s="1" t="s">
+      <c r="AS192" s="1" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="193" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>764</v>
       </c>
@@ -29027,23 +29472,23 @@
       <c r="AL193" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM193" s="1" t="s">
+      <c r="AO193" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="AN193" s="1" t="s">
+      <c r="AP193" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO193" s="1" t="s">
+      <c r="AQ193" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP193" s="1" t="s">
+      <c r="AR193" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="AQ193" s="1" t="s">
+      <c r="AS193" s="1" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="194" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>764</v>
       </c>
@@ -29159,22 +29604,25 @@
         <v>977</v>
       </c>
       <c r="AM194" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AO194" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="AN194" s="1" t="s">
+      <c r="AP194" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO194" s="1" t="s">
+      <c r="AQ194" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP194" s="1" t="s">
+      <c r="AR194" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="AQ194" s="1" t="s">
+      <c r="AS194" s="1" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="195" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>764</v>
       </c>
@@ -29289,23 +29737,23 @@
       <c r="AL195" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM195" s="1" t="s">
+      <c r="AO195" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="AN195" s="1" t="s">
+      <c r="AP195" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO195" s="1" t="s">
+      <c r="AQ195" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP195" s="1" t="s">
+      <c r="AR195" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="AQ195" s="1" t="s">
+      <c r="AS195" s="1" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="196" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>764</v>
       </c>
@@ -29420,23 +29868,23 @@
       <c r="AL196" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM196" s="1" t="s">
+      <c r="AO196" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="AN196" s="1" t="s">
+      <c r="AP196" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO196" s="1" t="s">
+      <c r="AQ196" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP196" s="1" t="s">
+      <c r="AR196" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="AQ196" s="1" t="s">
+      <c r="AS196" s="1" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="197" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>764</v>
       </c>
@@ -29551,23 +29999,23 @@
       <c r="AL197" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM197" s="1" t="s">
+      <c r="AO197" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="AN197" s="1" t="s">
+      <c r="AP197" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO197" s="1" t="s">
+      <c r="AQ197" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP197" s="1" t="s">
+      <c r="AR197" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="AQ197" s="1" t="s">
+      <c r="AS197" s="1" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="198" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>764</v>
       </c>
@@ -29682,23 +30130,23 @@
       <c r="AL198" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM198" s="1" t="s">
+      <c r="AO198" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="AN198" s="1" t="s">
+      <c r="AP198" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO198" s="1" t="s">
+      <c r="AQ198" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP198" s="1" t="s">
+      <c r="AR198" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="AQ198" s="1" t="s">
+      <c r="AS198" s="1" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="199" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>764</v>
       </c>
@@ -29813,23 +30261,23 @@
       <c r="AL199" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM199" s="1" t="s">
+      <c r="AO199" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="AN199" s="1" t="s">
+      <c r="AP199" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO199" s="1" t="s">
+      <c r="AQ199" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP199" s="1" t="s">
+      <c r="AR199" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="AQ199" s="1" t="s">
+      <c r="AS199" s="1" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="200" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>764</v>
       </c>
@@ -29944,23 +30392,23 @@
       <c r="AL200" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM200" s="1" t="s">
+      <c r="AO200" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="AN200" s="1" t="s">
+      <c r="AP200" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO200" s="1" t="s">
+      <c r="AQ200" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP200" s="1" t="s">
+      <c r="AR200" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="AQ200" s="1" t="s">
+      <c r="AS200" s="1" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="201" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>764</v>
       </c>
@@ -30075,23 +30523,23 @@
       <c r="AL201" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM201" s="1" t="s">
+      <c r="AO201" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="AN201" s="1" t="s">
+      <c r="AP201" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO201" s="1" t="s">
+      <c r="AQ201" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP201" s="1" t="s">
+      <c r="AR201" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="AQ201" s="1" t="s">
+      <c r="AS201" s="1" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="202" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>798</v>
       </c>
@@ -30206,23 +30654,23 @@
       <c r="AL202" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM202" s="1" t="s">
+      <c r="AO202" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="AN202" s="1" t="s">
+      <c r="AP202" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO202" s="1" t="s">
+      <c r="AQ202" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP202" s="1" t="s">
+      <c r="AR202" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="AQ202" s="1" t="s">
+      <c r="AS202" s="1" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="203" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>798</v>
       </c>
@@ -30337,23 +30785,23 @@
       <c r="AL203" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM203" s="1" t="s">
+      <c r="AO203" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="AN203" s="1" t="s">
+      <c r="AP203" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO203" s="1" t="s">
+      <c r="AQ203" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP203" s="1" t="s">
+      <c r="AR203" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="AQ203" s="1" t="s">
+      <c r="AS203" s="1" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="204" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>798</v>
       </c>
@@ -30468,23 +30916,23 @@
       <c r="AL204" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM204" s="1" t="s">
+      <c r="AO204" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="AN204" s="1" t="s">
+      <c r="AP204" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO204" s="1" t="s">
+      <c r="AQ204" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP204" s="1" t="s">
+      <c r="AR204" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="AQ204" s="1" t="s">
+      <c r="AS204" s="1" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="205" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>798</v>
       </c>
@@ -30599,23 +31047,23 @@
       <c r="AL205" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM205" s="1" t="s">
+      <c r="AO205" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="AN205" s="1" t="s">
+      <c r="AP205" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO205" s="1" t="s">
+      <c r="AQ205" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP205" s="1" t="s">
+      <c r="AR205" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="AQ205" s="1" t="s">
+      <c r="AS205" s="1" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="206" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>798</v>
       </c>
@@ -30730,23 +31178,23 @@
       <c r="AL206" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM206" s="1" t="s">
+      <c r="AO206" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="AN206" s="1" t="s">
+      <c r="AP206" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO206" s="1" t="s">
+      <c r="AQ206" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP206" s="1" t="s">
+      <c r="AR206" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="AQ206" s="1" t="s">
+      <c r="AS206" s="1" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="207" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>798</v>
       </c>
@@ -30861,23 +31309,26 @@
       <c r="AL207" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM207" s="1" t="s">
+      <c r="AN207" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AO207" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="AN207" s="1" t="s">
+      <c r="AP207" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO207" s="1" t="s">
+      <c r="AQ207" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP207" s="1" t="s">
+      <c r="AR207" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="AQ207" s="1" t="s">
+      <c r="AS207" s="1" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="208" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>798</v>
       </c>
@@ -30992,23 +31443,23 @@
       <c r="AL208" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM208" s="1" t="s">
+      <c r="AO208" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="AN208" s="1" t="s">
+      <c r="AP208" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO208" s="1" t="s">
+      <c r="AQ208" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP208" s="1" t="s">
+      <c r="AR208" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="AQ208" s="1" t="s">
+      <c r="AS208" s="1" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="209" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>798</v>
       </c>
@@ -31123,23 +31574,23 @@
       <c r="AL209" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM209" s="1" t="s">
+      <c r="AO209" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="AN209" s="1" t="s">
+      <c r="AP209" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO209" s="1" t="s">
+      <c r="AQ209" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP209" s="1" t="s">
+      <c r="AR209" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="AQ209" s="1" t="s">
+      <c r="AS209" s="1" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="210" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>798</v>
       </c>
@@ -31254,23 +31705,23 @@
       <c r="AL210" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM210" s="1" t="s">
+      <c r="AO210" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="AN210" s="1" t="s">
+      <c r="AP210" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO210" s="1" t="s">
+      <c r="AQ210" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP210" s="1" t="s">
+      <c r="AR210" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="AQ210" s="1" t="s">
+      <c r="AS210" s="1" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="211" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>798</v>
       </c>
@@ -31385,23 +31836,23 @@
       <c r="AL211" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM211" s="1" t="s">
+      <c r="AO211" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="AN211" s="1" t="s">
+      <c r="AP211" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO211" s="1" t="s">
+      <c r="AQ211" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP211" s="1" t="s">
+      <c r="AR211" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="AQ211" s="1" t="s">
+      <c r="AS211" s="1" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="212" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>836</v>
       </c>
@@ -31516,23 +31967,23 @@
       <c r="AL212" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM212" s="1" t="s">
+      <c r="AO212" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="AN212" s="1" t="s">
+      <c r="AP212" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO212" s="1" t="s">
+      <c r="AQ212" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP212" s="1" t="s">
+      <c r="AR212" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="AQ212" s="1" t="s">
+      <c r="AS212" s="1" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="213" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>836</v>
       </c>
@@ -31647,23 +32098,23 @@
       <c r="AL213" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM213" s="1" t="s">
+      <c r="AO213" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="AN213" s="1" t="s">
+      <c r="AP213" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO213" s="1" t="s">
+      <c r="AQ213" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP213" s="1" t="s">
+      <c r="AR213" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="AQ213" s="1" t="s">
+      <c r="AS213" s="1" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="214" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>836</v>
       </c>
@@ -31778,23 +32229,26 @@
       <c r="AL214" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM214" s="1" t="s">
+      <c r="AN214" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AO214" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="AN214" s="1" t="s">
+      <c r="AP214" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO214" s="1" t="s">
+      <c r="AQ214" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP214" s="1" t="s">
+      <c r="AR214" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="AQ214" s="1" t="s">
+      <c r="AS214" s="1" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="215" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>836</v>
       </c>
@@ -31909,23 +32363,23 @@
       <c r="AL215" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM215" s="1" t="s">
+      <c r="AO215" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="AN215" s="1" t="s">
+      <c r="AP215" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO215" s="1" t="s">
+      <c r="AQ215" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP215" s="1" t="s">
+      <c r="AR215" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="AQ215" s="1" t="s">
+      <c r="AS215" s="1" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="216" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>836</v>
       </c>
@@ -32040,23 +32494,23 @@
       <c r="AL216" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM216" s="1" t="s">
+      <c r="AO216" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="AN216" s="1" t="s">
+      <c r="AP216" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO216" s="1" t="s">
+      <c r="AQ216" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP216" s="1" t="s">
+      <c r="AR216" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="AQ216" s="1" t="s">
+      <c r="AS216" s="1" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="217" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>836</v>
       </c>
@@ -32171,23 +32625,23 @@
       <c r="AL217" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM217" s="1" t="s">
+      <c r="AO217" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="AN217" s="1" t="s">
+      <c r="AP217" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO217" s="1" t="s">
+      <c r="AQ217" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP217" s="1" t="s">
+      <c r="AR217" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="AQ217" s="1" t="s">
+      <c r="AS217" s="1" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="218" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>836</v>
       </c>
@@ -32303,22 +32757,25 @@
         <v>977</v>
       </c>
       <c r="AM218" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="AO218" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="AN218" s="1" t="s">
+      <c r="AP218" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO218" s="1" t="s">
+      <c r="AQ218" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP218" s="1" t="s">
+      <c r="AR218" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="AQ218" s="1" t="s">
+      <c r="AS218" s="1" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="219" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>836</v>
       </c>
@@ -32433,23 +32890,23 @@
       <c r="AL219" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM219" s="1" t="s">
+      <c r="AO219" s="1" t="s">
         <v>863</v>
       </c>
-      <c r="AN219" s="1" t="s">
+      <c r="AP219" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO219" s="1" t="s">
+      <c r="AQ219" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP219" s="1" t="s">
+      <c r="AR219" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="AQ219" s="1" t="s">
+      <c r="AS219" s="1" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="220" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>836</v>
       </c>
@@ -32564,23 +33021,23 @@
       <c r="AL220" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM220" s="1" t="s">
+      <c r="AO220" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="AN220" s="1" t="s">
+      <c r="AP220" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO220" s="1" t="s">
+      <c r="AQ220" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP220" s="1" t="s">
+      <c r="AR220" s="1" t="s">
         <v>867</v>
       </c>
-      <c r="AQ220" s="1" t="s">
+      <c r="AS220" s="1" t="s">
         <v>867</v>
       </c>
     </row>
-    <row r="221" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>836</v>
       </c>
@@ -32695,23 +33152,23 @@
       <c r="AL221" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM221" s="1" t="s">
+      <c r="AO221" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="AN221" s="1" t="s">
+      <c r="AP221" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO221" s="1" t="s">
+      <c r="AQ221" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP221" s="1" t="s">
+      <c r="AR221" s="1" t="s">
         <v>870</v>
       </c>
-      <c r="AQ221" s="1" t="s">
+      <c r="AS221" s="1" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="222" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>871</v>
       </c>
@@ -32827,22 +33284,25 @@
         <v>977</v>
       </c>
       <c r="AM222" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AO222" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="AN222" s="1" t="s">
+      <c r="AP222" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="AO222" s="1" t="s">
+      <c r="AQ222" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP222" s="1" t="s">
+      <c r="AR222" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="AQ222" s="1" t="s">
+      <c r="AS222" s="1" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="223" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>871</v>
       </c>
@@ -32957,23 +33417,23 @@
       <c r="AL223" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM223" s="1" t="s">
+      <c r="AO223" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="AN223" s="1" t="s">
+      <c r="AP223" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="AO223" s="1" t="s">
+      <c r="AQ223" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP223" s="1" t="s">
+      <c r="AR223" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="AQ223" s="1" t="s">
+      <c r="AS223" s="1" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="224" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>871</v>
       </c>
@@ -33088,23 +33548,26 @@
       <c r="AL224" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM224" s="1" t="s">
+      <c r="AN224" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AO224" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="AN224" s="1" t="s">
+      <c r="AP224" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="AO224" s="1" t="s">
+      <c r="AQ224" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP224" s="1" t="s">
+      <c r="AR224" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="AQ224" s="1" t="s">
+      <c r="AS224" s="1" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="225" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>871</v>
       </c>
@@ -33219,23 +33682,23 @@
       <c r="AL225" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM225" s="1" t="s">
+      <c r="AO225" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="AN225" s="1" t="s">
+      <c r="AP225" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="AO225" s="1" t="s">
+      <c r="AQ225" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP225" s="1" t="s">
+      <c r="AR225" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="AQ225" s="1" t="s">
+      <c r="AS225" s="1" t="s">
         <v>885</v>
       </c>
     </row>
-    <row r="226" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>871</v>
       </c>
@@ -33350,23 +33813,23 @@
       <c r="AL226" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM226" s="1" t="s">
+      <c r="AO226" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="AN226" s="1" t="s">
+      <c r="AP226" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="AO226" s="1" t="s">
+      <c r="AQ226" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP226" s="1" t="s">
+      <c r="AR226" s="1" t="s">
         <v>887</v>
       </c>
-      <c r="AQ226" s="1" t="s">
+      <c r="AS226" s="1" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="227" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>871</v>
       </c>
@@ -33481,23 +33944,23 @@
       <c r="AL227" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM227" s="1" t="s">
+      <c r="AO227" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="AN227" s="1" t="s">
+      <c r="AP227" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="AO227" s="1" t="s">
+      <c r="AQ227" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP227" s="1" t="s">
+      <c r="AR227" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="AQ227" s="1" t="s">
+      <c r="AS227" s="1" t="s">
         <v>890</v>
       </c>
     </row>
-    <row r="228" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>871</v>
       </c>
@@ -33613,22 +34076,25 @@
         <v>977</v>
       </c>
       <c r="AM228" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AO228" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="AN228" s="1" t="s">
+      <c r="AP228" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="AO228" s="1" t="s">
+      <c r="AQ228" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP228" s="1" t="s">
+      <c r="AR228" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="AQ228" s="1" t="s">
+      <c r="AS228" s="1" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="229" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>871</v>
       </c>
@@ -33743,23 +34209,23 @@
       <c r="AL229" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM229" s="1" t="s">
+      <c r="AO229" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="AN229" s="1" t="s">
+      <c r="AP229" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO229" s="1" t="s">
+      <c r="AQ229" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP229" s="1" t="s">
+      <c r="AR229" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="AQ229" s="1" t="s">
+      <c r="AS229" s="1" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="230" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>871</v>
       </c>
@@ -33874,23 +34340,23 @@
       <c r="AL230" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM230" s="1" t="s">
+      <c r="AO230" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="AN230" s="1" t="s">
+      <c r="AP230" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO230" s="1" t="s">
+      <c r="AQ230" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP230" s="1" t="s">
+      <c r="AR230" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="AQ230" s="1" t="s">
+      <c r="AS230" s="1" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="231" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>871</v>
       </c>
@@ -34005,24 +34471,24 @@
       <c r="AL231" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="AM231" s="1" t="s">
+      <c r="AO231" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="AN231" s="1" t="s">
+      <c r="AP231" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="AO231" s="1" t="s">
+      <c r="AQ231" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="AP231" s="1" t="s">
+      <c r="AR231" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="AQ231" s="1" t="s">
+      <c r="AS231" s="1" t="s">
         <v>906</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ231" xr:uid="{ACC8F76D-B553-4CF8-BE7D-F03409684AEE}"/>
+  <autoFilter ref="A1:AS231" xr:uid="{ACC8F76D-B553-4CF8-BE7D-F03409684AEE}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="特效用途特效" error="請選擇技能本體、附加效果，或留白。" sqref="AE2:AE231" xr:uid="{5E1344D4-93BC-4296-948D-83F81E070204}">
@@ -34036,7 +34502,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A83FB8B-F526-4731-A8B0-CF3B6BDD1233}">
-  <dimension ref="A1:A83"/>
+  <dimension ref="A1:A143"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="125.625" customWidth="1"/>
@@ -34084,376 +34550,676 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>1057</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>1058</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>1059</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>1060</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1062</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>1063</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>1064</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>1065</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>1066</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>1067</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>0</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>913</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>914</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>977</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>4</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>915</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>916</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>917</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>918</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>919</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>977</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>6</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>920</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>921</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>922</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>977</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>923</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>924</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>925</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>977</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>926</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>927</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>928</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>929</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>977</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>930</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>931</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>932</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>933</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>934</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>977</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>935</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>936</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>938</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>940</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>942</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>943</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>944</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>945</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>977</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>5</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>946</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>947</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>948</v>
+        <v>977</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>977</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>949</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>950</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>977</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>22</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>977</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>952</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>953</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>954</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>955</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>1069</v>
+        <v>913</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="5" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="5" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="5" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="5" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="5" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="5" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="5" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="5" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="5" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="5" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="5" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="5" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="5" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="5" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="5" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="5" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="5" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="5" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A113" s="5" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="5" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="5" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="5" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="5" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="5" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="5" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="5" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="5" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="5" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="5" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="5" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="5" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="5" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="5" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="5" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="5" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="5" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="5" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="5" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="5" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="5" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="5" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="5" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="5" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="5" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="5" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A142" s="5" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="5" t="s">
         <v>957</v>
       </c>
     </row>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFE91ED-C7CE-459B-9C34-E5B50E5DC58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39851C2-7261-4A12-829D-AEFF0B0A4BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10145" uniqueCount="1199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10140" uniqueCount="1200">
   <si>
     <t>群組ID</t>
   </si>
@@ -3676,6 +3676,10 @@
   </si>
   <si>
     <t>proj-cleave-ring-tricolor-08</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>proj-cleave-ring-tricolor-09</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3759,7 +3763,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3792,6 +3796,9 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6264,12 +6271,8 @@
       <c r="AK16" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="AL16" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="AM16" s="1" t="s">
-        <v>959</v>
-      </c>
+      <c r="AL16" s="1"/>
+      <c r="AM16" s="1"/>
       <c r="AT16" s="1" t="s">
         <v>1063</v>
       </c>
@@ -6398,12 +6401,8 @@
       <c r="AK17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AL17" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="AM17" s="1" t="s">
-        <v>959</v>
-      </c>
+      <c r="AL17" s="1"/>
+      <c r="AM17" s="1"/>
       <c r="AU17" s="1" t="s">
         <v>51</v>
       </c>
@@ -6529,12 +6528,8 @@
       <c r="AK18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AL18" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="AM18" s="1" t="s">
-        <v>959</v>
-      </c>
+      <c r="AL18" s="1"/>
+      <c r="AM18" s="1"/>
       <c r="AU18" s="1" t="s">
         <v>94</v>
       </c>
@@ -6654,18 +6649,12 @@
       <c r="AI19" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="AJ19" s="1" t="s">
+      <c r="AJ19" s="11" t="s">
         <v>1198</v>
       </c>
-      <c r="AK19" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="AL19" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="AM19" s="1" t="s">
-        <v>959</v>
-      </c>
+      <c r="AK19" s="1"/>
+      <c r="AL19" s="1"/>
+      <c r="AM19" s="1"/>
       <c r="AU19" s="1" t="s">
         <v>98</v>
       </c>
@@ -6785,18 +6774,12 @@
       <c r="AI20" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="AJ20" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="AK20" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="AL20" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="AM20" s="1" t="s">
-        <v>959</v>
-      </c>
+      <c r="AJ20" s="11" t="s">
+        <v>1199</v>
+      </c>
+      <c r="AK20" s="1"/>
+      <c r="AL20" s="1"/>
+      <c r="AM20" s="1"/>
       <c r="AQ20" s="1" t="s">
         <v>102</v>
       </c>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\codex-dualdance-20260921\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\codex-holy-20260921\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F131C6-BBEC-49CA-87E2-FBD66B6D1038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C31B4C-4FFD-49A8-A996-A98E84293EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10125" uniqueCount="1200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10127" uniqueCount="1202">
   <si>
     <t>群組ID</t>
   </si>
@@ -3685,6 +3685,13 @@
   </si>
   <si>
     <t>每施放 1 次雙刀亂舞就失去當下 {hpPct}% 生命值（不會致死），但雙刀亂舞的傷害提高 {pct}%，且額外 +{add} 個攻擊目標（每刀在當前攻擊範圍內隨機選敵，可重複命中同一目標）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>proj-light-orb</t>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：反擊滿計數後發射一顆光彈；觸發子彈飛到本次鎖定的目標位置，抵達時結算範圍傷害並在落點播放一次觸發特效。爆炸匹配傷害半徑，不在每個受害者身上重播。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發子彈。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -13227,25 +13234,31 @@
         <v>954</v>
       </c>
       <c r="AI69" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="AJ69" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="AK69" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="AL69" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="AM69" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="AN69" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="AJ69" s="1" t="s">
-        <v>954</v>
-      </c>
-      <c r="AK69" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="AL69" s="1" t="s">
-        <v>954</v>
-      </c>
-      <c r="AM69" s="1" t="s">
-        <v>954</v>
+      <c r="AO69" s="1" t="s">
+        <v>1200</v>
       </c>
       <c r="AU69" s="1" t="s">
         <v>285</v>
       </c>
       <c r="AV69" s="1" t="s">
-        <v>1161</v>
+        <v>1201</v>
       </c>
       <c r="AW69" s="1" t="s">
         <v>286</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -34643,8 +34643,8 @@
   <autoFilter ref="A1:AX231" xr:uid="{ACC8F76D-B553-4CF8-BE7D-F03409684AEE}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="特效用途特效" error="請選擇技能本體、附加效果，或留白。" sqref="AG2:AG231" xr:uid="{5E1344D4-93BC-4296-948D-83F81E070204}">
-      <formula1>"技能本體,附加效果"</formula1>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="施法消耗" error="請輸入大於或等於 0 的數字，或留白。" sqref="AG2:AG231">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -927,7 +927,7 @@
     <t>{"pct":2000,"pctPer":200,"sec":5,"cd":60}</t>
   </si>
   <si>
-    <t>死亡時對 {m} 米內的所有敵人造成 {pct}% 地系傷害，並在 {sec} 秒後原地復活繼續戰鬥（不算戰鬥失敗）；冷卻 {cd} 秒</t>
+    <t>反擊系列所有傷害轉為地屬性；死亡時對 {m} 米內的所有敵人造成 {pct}% 地系傷害，並在 {sec} 秒後原地復活繼續戰鬥（不算戰鬥失敗）；冷卻 {cd} 秒</t>
   </si>
   <si>
     <t>戰神體</t>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -14478,11 +14478,23 @@
       <c r="AM78" s="1" t="s">
         <v>946</v>
       </c>
+      <c r="AN78" t="inlineStr">
+        <is>
+          <t>burst-detonate-phys</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>hit-bleed</t>
+        </is>
+      </c>
       <c r="AU78" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="AV78" s="1" t="s">
-        <v>1153</v>
+      <c r="AV78" s="1" t="inlineStr">
+        <is>
+          <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：狂怒期間每次普攻在主目標位置播放一次範圍爆炸，匹配多目標普攻半徑；實際命中的敵人各播放原尺寸小型命中特效，追加目標同時結算與播放。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+        </is>
       </c>
       <c r="AW78" s="1" t="s">
         <v>311</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -14898,17 +14898,23 @@
       <c r="AS81" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="AU81" s="1" t="s">
-        <v>321</v>
+      <c r="AU81" s="1" t="inlineStr">
+        <is>
+          <t>{"pct":500,"pctPer":50,"sec":1.5,"secPer":0.15,"killSec":0.2}</t>
+        </is>
       </c>
       <c r="AV81" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="AW81" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="AX81" s="1" t="s">
-        <v>322</v>
+      <c r="AW81" s="1" t="inlineStr">
+        <is>
+          <t>每 {gap} 秒，你造成的所有傷害 +{pct}%，持續 {sec} 秒；效果期間每擊殺 1 個敵人，持續時間延長 {killSec} 秒</t>
+        </is>
+      </c>
+      <c r="AX81" s="1" t="inlineStr">
+        <is>
+          <t>每 {gap} 秒，你造成的所有傷害 +{pct}%，持續 {sec} 秒；效果期間每擊殺 1 個敵人，持續時間延長 {killSec} 秒</t>
+        </is>
       </c>
     </row>
     <row r="82" spans="1:50" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD6F0EE-0B14-48D0-BB73-777C579F597E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D809152-3FC8-48AE-A597-990DB933F660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10132" uniqueCount="1215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10156" uniqueCount="1216">
   <si>
     <t>群組ID</t>
   </si>
@@ -3052,9 +3052,6 @@
   </si>
   <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>60,-3</t>
   </si>
   <si>
     <t>{"pct":300,"pctPer":30,"orbs":3,"orbsPer":0.3}</t>
@@ -3718,9 +3715,6 @@
     <t>burst-detonate-phys</t>
   </si>
   <si>
-    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：狂怒期間每次普攻在主目標位置播放一次範圍爆炸，匹配多目標普攻半徑；實際命中的敵人各播放原尺寸小型命中特效，追加目標同時結算與播放。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
-  </si>
-  <si>
     <t>{"pct":2,"pctPer":0.2,"maxStacks":200,"drain":100,"drainPer":10}</t>
   </si>
   <si>
@@ -3745,6 +3739,17 @@
   </si>
   <si>
     <t>burst-detonate-dark-09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄與觸發欄獨立。觸發欄：狂怒系列普攻事件：攻擊特效於主目標播放一次，命中特效於每個實際受傷敵人播放；第七階前單體維持原尺寸，多目標普攻依實際半徑縮放。阿修羅效果生效期間亦可播放。 觸發攻擊／命中特效逐階同角色繼承，超神非空欄覆寫；其他觸發角色未接線。狀態光殼仍由 Status 表決定。</t>
+  </si>
+  <si>
+    <t>50,-3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>burst-fire-shockwave</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4350,31 +4355,31 @@
         <v>17</v>
       </c>
       <c r="AN1" s="8" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AO1" s="8" t="s">
         <v>1142</v>
       </c>
-      <c r="AO1" s="8" t="s">
+      <c r="AP1" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="AP1" s="8" t="s">
+      <c r="AQ1" s="8" t="s">
         <v>1144</v>
       </c>
-      <c r="AQ1" s="8" t="s">
+      <c r="AR1" s="8" t="s">
         <v>1145</v>
       </c>
-      <c r="AR1" s="8" t="s">
-        <v>1146</v>
-      </c>
       <c r="AS1" s="10" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AT1" s="10" t="s">
         <v>1041</v>
-      </c>
-      <c r="AT1" s="10" t="s">
-        <v>1042</v>
       </c>
       <c r="AU1" s="8" t="s">
         <v>18</v>
       </c>
       <c r="AV1" s="8" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="AW1" s="8" t="s">
         <v>21</v>
@@ -4505,7 +4510,7 @@
         <v>31</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW2" s="1" t="s">
         <v>32</v>
@@ -4636,7 +4641,7 @@
         <v>34</v>
       </c>
       <c r="AV3" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW3" s="1" t="s">
         <v>35</v>
@@ -4767,7 +4772,7 @@
         <v>39</v>
       </c>
       <c r="AV4" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW4" s="1" t="s">
         <v>40</v>
@@ -4898,7 +4903,7 @@
         <v>956</v>
       </c>
       <c r="AV5" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW5" s="1" t="s">
         <v>43</v>
@@ -5029,7 +5034,7 @@
         <v>47</v>
       </c>
       <c r="AV6" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW6" s="1" t="s">
         <v>48</v>
@@ -5160,7 +5165,7 @@
         <v>51</v>
       </c>
       <c r="AV7" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW7" s="1" t="s">
         <v>52</v>
@@ -5291,7 +5296,7 @@
         <v>55</v>
       </c>
       <c r="AV8" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW8" s="1" t="s">
         <v>56</v>
@@ -5419,13 +5424,13 @@
         <v>941</v>
       </c>
       <c r="AS9" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="AU9" s="1" t="s">
         <v>60</v>
       </c>
       <c r="AV9" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW9" s="1" t="s">
         <v>61</v>
@@ -5553,13 +5558,13 @@
         <v>941</v>
       </c>
       <c r="AT10" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="AU10" s="1" t="s">
         <v>65</v>
       </c>
       <c r="AV10" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW10" s="1" t="s">
         <v>66</v>
@@ -5690,7 +5695,7 @@
         <v>70</v>
       </c>
       <c r="AV11" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW11" s="1" t="s">
         <v>71</v>
@@ -5821,7 +5826,7 @@
         <v>76</v>
       </c>
       <c r="AV12" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW12" s="1" t="s">
         <v>77</v>
@@ -5952,7 +5957,7 @@
         <v>51</v>
       </c>
       <c r="AV13" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW13" s="1" t="s">
         <v>79</v>
@@ -6083,7 +6088,7 @@
         <v>81</v>
       </c>
       <c r="AV14" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW14" s="1" t="s">
         <v>82</v>
@@ -6214,7 +6219,7 @@
         <v>84</v>
       </c>
       <c r="AV15" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW15" s="1" t="s">
         <v>85</v>
@@ -6338,13 +6343,13 @@
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
       <c r="AT16" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="AU16" s="1" t="s">
         <v>87</v>
       </c>
       <c r="AV16" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW16" s="1" t="s">
         <v>88</v>
@@ -6471,7 +6476,7 @@
         <v>51</v>
       </c>
       <c r="AV17" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW17" s="1" t="s">
         <v>91</v>
@@ -6598,7 +6603,7 @@
         <v>94</v>
       </c>
       <c r="AV18" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW18" s="1" t="s">
         <v>95</v>
@@ -6714,7 +6719,7 @@
         <v>941</v>
       </c>
       <c r="AJ19" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
@@ -6723,7 +6728,7 @@
         <v>98</v>
       </c>
       <c r="AV19" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW19" s="1" t="s">
         <v>99</v>
@@ -6839,7 +6844,7 @@
         <v>941</v>
       </c>
       <c r="AJ20" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AK20" s="1"/>
       <c r="AL20" s="1"/>
@@ -6851,7 +6856,7 @@
         <v>103</v>
       </c>
       <c r="AV20" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="AW20" s="1" t="s">
         <v>104</v>
@@ -6982,7 +6987,7 @@
         <v>980</v>
       </c>
       <c r="AV21" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW21" s="1" t="s">
         <v>107</v>
@@ -7113,7 +7118,7 @@
         <v>112</v>
       </c>
       <c r="AV22" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW22" s="1" t="s">
         <v>113</v>
@@ -7244,7 +7249,7 @@
         <v>115</v>
       </c>
       <c r="AV23" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW23" s="1" t="s">
         <v>116</v>
@@ -7375,7 +7380,7 @@
         <v>118</v>
       </c>
       <c r="AV24" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW24" s="1" t="s">
         <v>119</v>
@@ -7506,7 +7511,7 @@
         <v>121</v>
       </c>
       <c r="AV25" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW25" s="1" t="s">
         <v>122</v>
@@ -7637,7 +7642,7 @@
         <v>124</v>
       </c>
       <c r="AV26" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW26" s="1" t="s">
         <v>125</v>
@@ -7768,7 +7773,7 @@
         <v>128</v>
       </c>
       <c r="AV27" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW27" s="1" t="s">
         <v>129</v>
@@ -7899,7 +7904,7 @@
         <v>132</v>
       </c>
       <c r="AV28" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW28" s="1" t="s">
         <v>133</v>
@@ -8030,7 +8035,7 @@
         <v>137</v>
       </c>
       <c r="AV29" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW29" s="1" t="s">
         <v>138</v>
@@ -8158,13 +8163,13 @@
         <v>941</v>
       </c>
       <c r="AS30" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="AU30" s="1" t="s">
         <v>142</v>
       </c>
       <c r="AV30" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW30" s="1" t="s">
         <v>143</v>
@@ -8295,7 +8300,7 @@
         <v>147</v>
       </c>
       <c r="AV31" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW31" s="1" t="s">
         <v>148</v>
@@ -8426,7 +8431,7 @@
         <v>153</v>
       </c>
       <c r="AV32" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW32" s="1" t="s">
         <v>154</v>
@@ -8557,7 +8562,7 @@
         <v>156</v>
       </c>
       <c r="AV33" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW33" s="1" t="s">
         <v>157</v>
@@ -8688,7 +8693,7 @@
         <v>160</v>
       </c>
       <c r="AV34" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW34" s="1" t="s">
         <v>161</v>
@@ -8819,7 +8824,7 @@
         <v>164</v>
       </c>
       <c r="AV35" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW35" s="1" t="s">
         <v>165</v>
@@ -8947,13 +8952,13 @@
         <v>941</v>
       </c>
       <c r="AS36" s="1" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="AU36" s="1" t="s">
         <v>167</v>
       </c>
       <c r="AV36" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW36" s="1" t="s">
         <v>168</v>
@@ -9084,7 +9089,7 @@
         <v>170</v>
       </c>
       <c r="AV37" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW37" s="1" t="s">
         <v>171</v>
@@ -9215,7 +9220,7 @@
         <v>175</v>
       </c>
       <c r="AV38" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW38" s="1" t="s">
         <v>176</v>
@@ -9349,7 +9354,7 @@
         <v>986</v>
       </c>
       <c r="AV39" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="AW39" s="1" t="s">
         <v>180</v>
@@ -9483,7 +9488,7 @@
         <v>313</v>
       </c>
       <c r="AV40" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AW40" s="1" t="s">
         <v>988</v>
@@ -9614,7 +9619,7 @@
         <v>989</v>
       </c>
       <c r="AV41" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW41" s="1" t="s">
         <v>187</v>
@@ -9740,13 +9745,13 @@
         <v>941</v>
       </c>
       <c r="AT42" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="AU42" s="1" t="s">
         <v>193</v>
       </c>
       <c r="AV42" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW42" s="1" t="s">
         <v>194</v>
@@ -9873,7 +9878,7 @@
         <v>196</v>
       </c>
       <c r="AV43" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW43" s="1" t="s">
         <v>197</v>
@@ -10004,7 +10009,7 @@
         <v>199</v>
       </c>
       <c r="AV44" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW44" s="1" t="s">
         <v>200</v>
@@ -10130,13 +10135,13 @@
         <v>941</v>
       </c>
       <c r="AT45" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="AU45" s="1" t="s">
         <v>203</v>
       </c>
       <c r="AV45" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW45" s="1" t="s">
         <v>204</v>
@@ -10147,7 +10152,7 @@
     </row>
     <row r="46" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>190</v>
@@ -10228,7 +10233,7 @@
         <v>941</v>
       </c>
       <c r="AB46" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="AC46" s="1" t="s">
         <v>941</v>
@@ -10264,7 +10269,7 @@
         <v>941</v>
       </c>
       <c r="AO46" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="AP46" s="1" t="s">
         <v>202</v>
@@ -10273,7 +10278,7 @@
         <v>206</v>
       </c>
       <c r="AV46" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="AW46" s="1" t="s">
         <v>207</v>
@@ -10403,7 +10408,7 @@
         <v>211</v>
       </c>
       <c r="AV47" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="AW47" s="1" t="s">
         <v>212</v>
@@ -10420,7 +10425,7 @@
         <v>190</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>191</v>
@@ -10526,13 +10531,13 @@
         <v>941</v>
       </c>
       <c r="AN48" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="AU48" s="1" t="s">
         <v>214</v>
       </c>
       <c r="AV48" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="AW48" s="1" t="s">
         <v>215</v>
@@ -10661,13 +10666,13 @@
         <v>941</v>
       </c>
       <c r="AS49" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="AU49" s="1" t="s">
         <v>218</v>
       </c>
       <c r="AV49" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW49" s="1" t="s">
         <v>219</v>
@@ -10797,16 +10802,16 @@
         <v>941</v>
       </c>
       <c r="AS50" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="AT50" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="AU50" s="1" t="s">
         <v>222</v>
       </c>
       <c r="AV50" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="AW50" s="1" t="s">
         <v>223</v>
@@ -10823,7 +10828,7 @@
         <v>941</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>941</v>
@@ -10898,7 +10903,7 @@
         <v>941</v>
       </c>
       <c r="AB51" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="AC51" s="1" t="s">
         <v>941</v>
@@ -10935,19 +10940,19 @@
         <v>210</v>
       </c>
       <c r="AO51" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AU51" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="AV51" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="AU51" s="1" t="s">
+      <c r="AW51" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="AV51" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="AW51" s="1" t="s">
-        <v>1035</v>
-      </c>
       <c r="AX51" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="52" spans="1:50" x14ac:dyDescent="0.25">
@@ -11068,13 +11073,13 @@
         <v>230</v>
       </c>
       <c r="AV52" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW52" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="AX52" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="53" spans="1:50" x14ac:dyDescent="0.25">
@@ -11197,13 +11202,13 @@
         <v>232</v>
       </c>
       <c r="AV53" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW53" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="AX53" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="54" spans="1:50" x14ac:dyDescent="0.25">
@@ -11326,7 +11331,7 @@
         <v>234</v>
       </c>
       <c r="AV54" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW54" s="1" t="s">
         <v>235</v>
@@ -11454,13 +11459,13 @@
         <v>941</v>
       </c>
       <c r="AS55" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="AU55" s="1" t="s">
         <v>237</v>
       </c>
       <c r="AV55" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW55" s="1" t="s">
         <v>238</v>
@@ -11573,7 +11578,7 @@
         <v>941</v>
       </c>
       <c r="AI56" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AJ56" s="1" t="s">
         <v>941</v>
@@ -11588,16 +11593,16 @@
         <v>941</v>
       </c>
       <c r="AS56" s="1" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AT56" s="1" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AU56" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="AV56" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW56" s="1" t="s">
         <v>240</v>
@@ -11728,10 +11733,10 @@
         <v>242</v>
       </c>
       <c r="AV57" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW57" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="AX57" s="1" t="s">
         <v>243</v>
@@ -11854,19 +11859,19 @@
         <v>941</v>
       </c>
       <c r="AS58" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="AU58" s="1" t="s">
         <v>246</v>
       </c>
       <c r="AV58" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW58" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="AX58" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="59" spans="1:50" x14ac:dyDescent="0.25">
@@ -11877,7 +11882,7 @@
         <v>941</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>941</v>
@@ -11973,7 +11978,7 @@
         <v>941</v>
       </c>
       <c r="AI59" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="AJ59" s="1" t="s">
         <v>941</v>
@@ -11988,16 +11993,16 @@
         <v>941</v>
       </c>
       <c r="AU59" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="AV59" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW59" s="1" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="AX59" s="1" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="60" spans="1:50" x14ac:dyDescent="0.25">
@@ -12104,7 +12109,7 @@
         <v>941</v>
       </c>
       <c r="AI60" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="AJ60" s="1" t="s">
         <v>941</v>
@@ -12119,13 +12124,13 @@
         <v>941</v>
       </c>
       <c r="AT60" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="AU60" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="AV60" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW60" s="1" t="s">
         <v>250</v>
@@ -12238,7 +12243,7 @@
         <v>941</v>
       </c>
       <c r="AI61" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="AJ61" s="1" t="s">
         <v>941</v>
@@ -12256,7 +12261,7 @@
         <v>137</v>
       </c>
       <c r="AV61" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW61" s="1" t="s">
         <v>253</v>
@@ -12387,7 +12392,7 @@
         <v>258</v>
       </c>
       <c r="AV62" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW62" s="1" t="s">
         <v>259</v>
@@ -12518,7 +12523,7 @@
         <v>261</v>
       </c>
       <c r="AV63" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW63" s="1" t="s">
         <v>262</v>
@@ -12649,7 +12654,7 @@
         <v>264</v>
       </c>
       <c r="AV64" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW64" s="1" t="s">
         <v>265</v>
@@ -12780,7 +12785,7 @@
         <v>267</v>
       </c>
       <c r="AV65" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW65" s="1" t="s">
         <v>268</v>
@@ -12908,13 +12913,13 @@
         <v>941</v>
       </c>
       <c r="AT66" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="AU66" s="1" t="s">
         <v>271</v>
       </c>
       <c r="AV66" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW66" s="1" t="s">
         <v>272</v>
@@ -13042,10 +13047,10 @@
         <v>941</v>
       </c>
       <c r="AU67" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="AV67" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW67" s="1" t="s">
         <v>274</v>
@@ -13173,10 +13178,10 @@
         <v>941</v>
       </c>
       <c r="AU68" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AV68" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW68" s="1" t="s">
         <v>277</v>
@@ -13307,13 +13312,13 @@
         <v>280</v>
       </c>
       <c r="AO69" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="AU69" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="AV69" s="1" t="s">
         <v>1192</v>
-      </c>
-      <c r="AU69" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="AV69" s="1" t="s">
-        <v>1193</v>
       </c>
       <c r="AW69" s="1" t="s">
         <v>282</v>
@@ -13439,22 +13444,22 @@
         <v>941</v>
       </c>
       <c r="AQ70" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="AS70" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="AU70" s="1" t="s">
         <v>286</v>
       </c>
       <c r="AV70" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="AW70" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="AW70" s="1" t="s">
-        <v>1204</v>
-      </c>
       <c r="AX70" s="1" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="71" spans="1:50" x14ac:dyDescent="0.25">
@@ -13534,7 +13539,7 @@
         <v>941</v>
       </c>
       <c r="Z71" s="3" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="AA71" s="1" t="s">
         <v>941</v>
@@ -13576,16 +13581,16 @@
         <v>941</v>
       </c>
       <c r="AU71" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="AV71" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="AW71" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="AV71" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AW71" s="1" t="s">
+      <c r="AX71" s="1" t="s">
         <v>1199</v>
-      </c>
-      <c r="AX71" s="1" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="72" spans="1:50" x14ac:dyDescent="0.25">
@@ -13707,18 +13712,16 @@
         <v>941</v>
       </c>
       <c r="AN72" s="1" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="AS72" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="AU72" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="AV72" s="1" t="inlineStr">
-        <is>
-          <t>本體欄與觸發欄獨立。觸發欄：狂怒系列普攻事件：攻擊特效於主目標播放一次，命中特效於每個實際受傷敵人播放；第七階前單體維持原尺寸，多目標普攻依實際半徑縮放。阿修羅效果生效期間亦可播放。 觸發攻擊／命中特效逐階同角色繼承，超神非空欄覆寫；其他觸發角色未接線。狀態光殼仍由 Status 表決定。</t>
-        </is>
+      <c r="AV72" s="1" t="s">
+        <v>1213</v>
       </c>
       <c r="AW72" s="1" t="s">
         <v>293</v>
@@ -13848,10 +13851,8 @@
       <c r="AU73" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="AV73" s="1" t="inlineStr">
-        <is>
-          <t>本體欄與觸發欄獨立。觸發欄：狂怒系列普攻事件：攻擊特效於主目標播放一次，命中特效於每個實際受傷敵人播放；第七階前單體維持原尺寸，多目標普攻依實際半徑縮放。阿修羅效果生效期間亦可播放。 觸發攻擊／命中特效逐階同角色繼承，超神非空欄覆寫；其他觸發角色未接線。狀態光殼仍由 Status 表決定。</t>
-        </is>
+      <c r="AV73" s="1" t="s">
+        <v>1213</v>
       </c>
       <c r="AW73" s="1" t="s">
         <v>295</v>
@@ -13981,10 +13982,8 @@
       <c r="AU74" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="AV74" s="1" t="inlineStr">
-        <is>
-          <t>本體欄與觸發欄獨立。觸發欄：狂怒系列普攻事件：攻擊特效於主目標播放一次，命中特效於每個實際受傷敵人播放；第七階前單體維持原尺寸，多目標普攻依實際半徑縮放。阿修羅效果生效期間亦可播放。 觸發攻擊／命中特效逐階同角色繼承，超神非空欄覆寫；其他觸發角色未接線。狀態光殼仍由 Status 表決定。</t>
-        </is>
+      <c r="AV74" s="1" t="s">
+        <v>1213</v>
       </c>
       <c r="AW74" s="1" t="s">
         <v>297</v>
@@ -14114,10 +14113,8 @@
       <c r="AU75" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="AV75" s="1" t="inlineStr">
-        <is>
-          <t>本體欄與觸發欄獨立。觸發欄：狂怒系列普攻事件：攻擊特效於主目標播放一次，命中特效於每個實際受傷敵人播放；第七階前單體維持原尺寸，多目標普攻依實際半徑縮放。阿修羅效果生效期間亦可播放。 觸發攻擊／命中特效逐階同角色繼承，超神非空欄覆寫；其他觸發角色未接線。狀態光殼仍由 Status 表決定。</t>
-        </is>
+      <c r="AV75" s="1" t="s">
+        <v>1213</v>
       </c>
       <c r="AW75" s="1" t="s">
         <v>300</v>
@@ -14247,10 +14244,8 @@
       <c r="AU76" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="AV76" s="1" t="inlineStr">
-        <is>
-          <t>本體欄與觸發欄獨立。觸發欄：狂怒系列普攻事件：攻擊特效於主目標播放一次，命中特效於每個實際受傷敵人播放；第七階前單體維持原尺寸，多目標普攻依實際半徑縮放。阿修羅效果生效期間亦可播放。 觸發攻擊／命中特效逐階同角色繼承，超神非空欄覆寫；其他觸發角色未接線。狀態光殼仍由 Status 表決定。</t>
-        </is>
+      <c r="AV76" s="1" t="s">
+        <v>1213</v>
       </c>
       <c r="AW76" s="1" t="s">
         <v>302</v>
@@ -14380,10 +14375,8 @@
       <c r="AU77" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="AV77" s="1" t="inlineStr">
-        <is>
-          <t>本體欄與觸發欄獨立。觸發欄：狂怒系列普攻事件：攻擊特效於主目標播放一次，命中特效於每個實際受傷敵人播放；第七階前單體維持原尺寸，多目標普攻依實際半徑縮放。阿修羅效果生效期間亦可播放。 觸發攻擊／命中特效逐階同角色繼承，超神非空欄覆寫；其他觸發角色未接線。狀態光殼仍由 Status 表決定。</t>
-        </is>
+      <c r="AV77" s="1" t="s">
+        <v>1213</v>
       </c>
       <c r="AW77" s="1" t="s">
         <v>306</v>
@@ -14511,16 +14504,14 @@
         <v>941</v>
       </c>
       <c r="AN78" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="AP78"/>
       <c r="AU78" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="AV78" s="1" t="inlineStr">
-        <is>
-          <t>本體欄與觸發欄獨立。觸發欄：狂怒系列普攻事件：攻擊特效於主目標播放一次，命中特效於每個實際受傷敵人播放；第七階前單體維持原尺寸，多目標普攻依實際半徑縮放。阿修羅效果生效期間亦可播放。 觸發攻擊／命中特效逐階同角色繼承，超神非空欄覆寫；其他觸發角色未接線。狀態光殼仍由 Status 表決定。</t>
-        </is>
+      <c r="AV78" s="1" t="s">
+        <v>1213</v>
       </c>
       <c r="AW78" s="1" t="s">
         <v>310</v>
@@ -14648,15 +14639,13 @@
         <v>941</v>
       </c>
       <c r="AN79" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="AU79" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="AV79" s="1" t="inlineStr">
-        <is>
-          <t>本體欄與觸發欄獨立。觸發欄：狂怒系列普攻事件：攻擊特效於主目標播放一次，命中特效於每個實際受傷敵人播放；第七階前單體維持原尺寸，多目標普攻依實際半徑縮放。阿修羅效果生效期間亦可播放。 觸發攻擊／命中特效逐階同角色繼承，超神非空欄覆寫；其他觸發角色未接線。狀態光殼仍由 Status 表決定。</t>
-        </is>
+      <c r="AV79" s="1" t="s">
+        <v>1213</v>
       </c>
       <c r="AW79" s="1" t="s">
         <v>314</v>
@@ -14784,24 +14773,22 @@
         <v>941</v>
       </c>
       <c r="AN80" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="AS80" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="AU80" s="1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="AV80" s="1" t="inlineStr">
-        <is>
-          <t>本體欄與觸發欄獨立。觸發欄：狂怒系列普攻事件：攻擊特效於主目標播放一次，命中特效於每個實際受傷敵人播放；第七階前單體維持原尺寸，多目標普攻依實際半徑縮放。阿修羅效果生效期間亦可播放。 觸發攻擊／命中特效逐階同角色繼承，超神非空欄覆寫；其他觸發角色未接線。狀態光殼仍由 Status 表決定。</t>
-        </is>
+        <v>1205</v>
+      </c>
+      <c r="AV80" s="1" t="s">
+        <v>1213</v>
       </c>
       <c r="AW80" s="1" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="AX80" s="1" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="81" spans="1:50" x14ac:dyDescent="0.25">
@@ -14923,24 +14910,22 @@
         <v>941</v>
       </c>
       <c r="AN81" s="1" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="AS81" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AU81" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="AV81" s="1" t="inlineStr">
-        <is>
-          <t>本體欄與觸發欄獨立。觸發欄：狂怒系列普攻事件：攻擊特效於主目標播放一次，命中特效於每個實際受傷敵人播放；第七階前單體維持原尺寸，多目標普攻依實際半徑縮放。阿修羅效果生效期間亦可播放。 觸發攻擊／命中特效逐階同角色繼承，超神非空欄覆寫；其他觸發角色未接線。狀態光殼仍由 Status 表決定。</t>
-        </is>
+        <v>1207</v>
+      </c>
+      <c r="AV81" s="1" t="s">
+        <v>1213</v>
       </c>
       <c r="AW81" s="1" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="AX81" s="1" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="82" spans="1:50" x14ac:dyDescent="0.25">
@@ -15065,7 +15050,7 @@
         <v>327</v>
       </c>
       <c r="AV82" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW82" s="1" t="s">
         <v>328</v>
@@ -15193,13 +15178,13 @@
         <v>941</v>
       </c>
       <c r="AT83" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="AU83" s="1" t="s">
         <v>330</v>
       </c>
       <c r="AV83" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW83" s="1" t="s">
         <v>331</v>
@@ -15330,7 +15315,7 @@
         <v>333</v>
       </c>
       <c r="AV84" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW84" s="1" t="s">
         <v>334</v>
@@ -15461,7 +15446,7 @@
         <v>51</v>
       </c>
       <c r="AV85" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW85" s="1" t="s">
         <v>336</v>
@@ -15592,7 +15577,7 @@
         <v>211</v>
       </c>
       <c r="AV86" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW86" s="1" t="s">
         <v>340</v>
@@ -15720,13 +15705,13 @@
         <v>941</v>
       </c>
       <c r="AS87" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="AU87" s="1" t="s">
         <v>342</v>
       </c>
       <c r="AV87" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW87" s="1" t="s">
         <v>343</v>
@@ -15839,7 +15824,7 @@
         <v>941</v>
       </c>
       <c r="AI88" s="1" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="AJ88" s="1" t="s">
         <v>346</v>
@@ -15857,7 +15842,7 @@
         <v>348</v>
       </c>
       <c r="AV88" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW88" s="1" t="s">
         <v>349</v>
@@ -15988,7 +15973,7 @@
         <v>352</v>
       </c>
       <c r="AV89" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW89" s="1" t="s">
         <v>353</v>
@@ -16074,7 +16059,7 @@
         <v>941</v>
       </c>
       <c r="Z90" s="3" t="s">
-        <v>997</v>
+        <v>1214</v>
       </c>
       <c r="AA90" s="1" t="s">
         <v>941</v>
@@ -16100,14 +16085,18 @@
       <c r="AH90" s="1" t="s">
         <v>941</v>
       </c>
-      <c r="AI90" s="1" t="s">
-        <v>356</v>
+      <c r="AI90" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AJ90" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="AK90" s="1" t="s">
-        <v>339</v>
+      <c r="AK90" s="1" t="inlineStr">
+        <is>
+          <t>burst-fire</t>
+        </is>
       </c>
       <c r="AL90" s="1" t="s">
         <v>358</v>
@@ -16115,14 +16104,21 @@
       <c r="AM90" s="1" t="s">
         <v>941</v>
       </c>
+      <c r="AN90" t="inlineStr">
+        <is>
+          <t>burst-fire-shockwave</t>
+        </is>
+      </c>
       <c r="AS90" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="AU90" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="AV90" s="1" t="s">
-        <v>1148</v>
+      <c r="AV90" s="1" t="inlineStr">
+        <is>
+          <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：超巨型殞石落地時，在角色當下中心播放一次全場爆炸；小型受擊另讀本列本體命中特效，各自依 Preset 持續時間播放。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+        </is>
       </c>
       <c r="AW90" s="1" t="s">
         <v>360</v>
@@ -16253,7 +16249,7 @@
         <v>365</v>
       </c>
       <c r="AV91" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW91" s="1" t="s">
         <v>366</v>
@@ -16384,7 +16380,7 @@
         <v>371</v>
       </c>
       <c r="AV92" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW92" s="1" t="s">
         <v>372</v>
@@ -16515,7 +16511,7 @@
         <v>199</v>
       </c>
       <c r="AV93" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW93" s="1" t="s">
         <v>374</v>
@@ -16646,7 +16642,7 @@
         <v>376</v>
       </c>
       <c r="AV94" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW94" s="1" t="s">
         <v>377</v>
@@ -16774,13 +16770,13 @@
         <v>941</v>
       </c>
       <c r="AT95" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="AU95" s="1" t="s">
         <v>378</v>
       </c>
       <c r="AV95" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW95" s="1" t="s">
         <v>379</v>
@@ -16911,7 +16907,7 @@
         <v>313</v>
       </c>
       <c r="AV96" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW96" s="1" t="s">
         <v>381</v>
@@ -17042,7 +17038,7 @@
         <v>383</v>
       </c>
       <c r="AV97" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW97" s="1" t="s">
         <v>384</v>
@@ -17173,7 +17169,7 @@
         <v>387</v>
       </c>
       <c r="AV98" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW98" s="1" t="s">
         <v>388</v>
@@ -17304,7 +17300,7 @@
         <v>391</v>
       </c>
       <c r="AV99" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW99" s="1" t="s">
         <v>392</v>
@@ -17435,7 +17431,7 @@
         <v>396</v>
       </c>
       <c r="AV100" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW100" s="1" t="s">
         <v>397</v>
@@ -17566,7 +17562,7 @@
         <v>400</v>
       </c>
       <c r="AV101" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW101" s="1" t="s">
         <v>401</v>
@@ -17694,13 +17690,13 @@
         <v>941</v>
       </c>
       <c r="AS102" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AU102" s="1" t="s">
         <v>408</v>
       </c>
       <c r="AV102" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW102" s="1" t="s">
         <v>409</v>
@@ -17831,7 +17827,7 @@
         <v>411</v>
       </c>
       <c r="AV103" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW103" s="1" t="s">
         <v>412</v>
@@ -17962,7 +17958,7 @@
         <v>415</v>
       </c>
       <c r="AV104" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW104" s="1" t="s">
         <v>416</v>
@@ -18093,7 +18089,7 @@
         <v>418</v>
       </c>
       <c r="AV105" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW105" s="1" t="s">
         <v>419</v>
@@ -18224,7 +18220,7 @@
         <v>421</v>
       </c>
       <c r="AV106" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW106" s="1" t="s">
         <v>422</v>
@@ -18355,7 +18351,7 @@
         <v>424</v>
       </c>
       <c r="AV107" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW107" s="1" t="s">
         <v>425</v>
@@ -18486,7 +18482,7 @@
         <v>427</v>
       </c>
       <c r="AV108" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW108" s="1" t="s">
         <v>428</v>
@@ -18617,7 +18613,7 @@
         <v>431</v>
       </c>
       <c r="AV109" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW109" s="1" t="s">
         <v>432</v>
@@ -18748,7 +18744,7 @@
         <v>435</v>
       </c>
       <c r="AV110" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW110" s="1" t="s">
         <v>436</v>
@@ -18876,13 +18872,13 @@
         <v>941</v>
       </c>
       <c r="AS111" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="AU111" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AV111" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW111" s="1" t="s">
         <v>440</v>
@@ -19010,13 +19006,13 @@
         <v>941</v>
       </c>
       <c r="AS112" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="AU112" s="1" t="s">
         <v>446</v>
       </c>
       <c r="AV112" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW112" s="1" t="s">
         <v>447</v>
@@ -19147,7 +19143,7 @@
         <v>137</v>
       </c>
       <c r="AV113" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW113" s="1" t="s">
         <v>449</v>
@@ -19278,7 +19274,7 @@
         <v>451</v>
       </c>
       <c r="AV114" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW114" s="1" t="s">
         <v>452</v>
@@ -19409,7 +19405,7 @@
         <v>411</v>
       </c>
       <c r="AV115" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW115" s="1" t="s">
         <v>454</v>
@@ -19540,7 +19536,7 @@
         <v>267</v>
       </c>
       <c r="AV116" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW116" s="1" t="s">
         <v>456</v>
@@ -19668,13 +19664,13 @@
         <v>941</v>
       </c>
       <c r="AS117" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="AU117" s="1" t="s">
         <v>458</v>
       </c>
       <c r="AV117" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW117" s="1" t="s">
         <v>459</v>
@@ -19805,7 +19801,7 @@
         <v>462</v>
       </c>
       <c r="AV118" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW118" s="1" t="s">
         <v>463</v>
@@ -19933,16 +19929,16 @@
         <v>941</v>
       </c>
       <c r="AS119" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="AT119" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="AU119" s="1" t="s">
         <v>467</v>
       </c>
       <c r="AV119" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW119" s="1" t="s">
         <v>468</v>
@@ -20070,10 +20066,10 @@
         <v>941</v>
       </c>
       <c r="AU120" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="AV120" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW120" s="1" t="s">
         <v>471</v>
@@ -20201,16 +20197,16 @@
         <v>941</v>
       </c>
       <c r="AS121" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="AT121" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="AU121" s="1" t="s">
         <v>475</v>
       </c>
       <c r="AV121" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW121" s="1" t="s">
         <v>476</v>
@@ -20338,13 +20334,13 @@
         <v>941</v>
       </c>
       <c r="AT122" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="AU122" s="1" t="s">
         <v>482</v>
       </c>
       <c r="AV122" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW122" s="1" t="s">
         <v>483</v>
@@ -20475,7 +20471,7 @@
         <v>411</v>
       </c>
       <c r="AV123" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW123" s="1" t="s">
         <v>484</v>
@@ -20603,13 +20599,13 @@
         <v>941</v>
       </c>
       <c r="AT124" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="AU124" s="1" t="s">
         <v>487</v>
       </c>
       <c r="AV124" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW124" s="1" t="s">
         <v>488</v>
@@ -20740,7 +20736,7 @@
         <v>490</v>
       </c>
       <c r="AV125" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW125" s="1" t="s">
         <v>491</v>
@@ -20871,7 +20867,7 @@
         <v>493</v>
       </c>
       <c r="AV126" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW126" s="1" t="s">
         <v>494</v>
@@ -21002,7 +20998,7 @@
         <v>496</v>
       </c>
       <c r="AV127" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW127" s="1" t="s">
         <v>497</v>
@@ -21130,13 +21126,13 @@
         <v>941</v>
       </c>
       <c r="AT128" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="AU128" s="1" t="s">
         <v>500</v>
       </c>
       <c r="AV128" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW128" s="1" t="s">
         <v>501</v>
@@ -21264,13 +21260,13 @@
         <v>941</v>
       </c>
       <c r="AT129" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="AU129" s="1" t="s">
         <v>504</v>
       </c>
       <c r="AV129" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW129" s="1" t="s">
         <v>505</v>
@@ -21398,13 +21394,13 @@
         <v>941</v>
       </c>
       <c r="AT130" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="AU130" s="1" t="s">
         <v>509</v>
       </c>
       <c r="AV130" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW130" s="1" t="s">
         <v>510</v>
@@ -21535,7 +21531,7 @@
         <v>513</v>
       </c>
       <c r="AV131" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW131" s="1" t="s">
         <v>514</v>
@@ -21666,7 +21662,7 @@
         <v>518</v>
       </c>
       <c r="AV132" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW132" s="1" t="s">
         <v>519</v>
@@ -21797,7 +21793,7 @@
         <v>421</v>
       </c>
       <c r="AV133" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW133" s="1" t="s">
         <v>521</v>
@@ -21928,7 +21924,7 @@
         <v>523</v>
       </c>
       <c r="AV134" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW134" s="1" t="s">
         <v>524</v>
@@ -22059,7 +22055,7 @@
         <v>523</v>
       </c>
       <c r="AV135" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW135" s="1" t="s">
         <v>526</v>
@@ -22190,7 +22186,7 @@
         <v>528</v>
       </c>
       <c r="AV136" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW136" s="1" t="s">
         <v>529</v>
@@ -22321,7 +22317,7 @@
         <v>532</v>
       </c>
       <c r="AV137" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW137" s="1" t="s">
         <v>533</v>
@@ -22449,13 +22445,13 @@
         <v>941</v>
       </c>
       <c r="AS138" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="AU138" s="1" t="s">
         <v>536</v>
       </c>
       <c r="AV138" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW138" s="1" t="s">
         <v>537</v>
@@ -22586,7 +22582,7 @@
         <v>540</v>
       </c>
       <c r="AV139" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW139" s="1" t="s">
         <v>541</v>
@@ -22717,7 +22713,7 @@
         <v>545</v>
       </c>
       <c r="AV140" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW140" s="1" t="s">
         <v>546</v>
@@ -22848,7 +22844,7 @@
         <v>549</v>
       </c>
       <c r="AV141" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW141" s="1" t="s">
         <v>550</v>
@@ -22979,7 +22975,7 @@
         <v>556</v>
       </c>
       <c r="AV142" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW142" s="1" t="s">
         <v>557</v>
@@ -23110,7 +23106,7 @@
         <v>225</v>
       </c>
       <c r="AV143" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW143" s="1" t="s">
         <v>559</v>
@@ -23241,7 +23237,7 @@
         <v>490</v>
       </c>
       <c r="AV144" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW144" s="1" t="s">
         <v>561</v>
@@ -23372,7 +23368,7 @@
         <v>232</v>
       </c>
       <c r="AV145" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW145" s="1" t="s">
         <v>563</v>
@@ -23503,7 +23499,7 @@
         <v>565</v>
       </c>
       <c r="AV146" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW146" s="1" t="s">
         <v>566</v>
@@ -23634,7 +23630,7 @@
         <v>225</v>
       </c>
       <c r="AV147" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW147" s="1" t="s">
         <v>569</v>
@@ -23765,7 +23761,7 @@
         <v>571</v>
       </c>
       <c r="AV148" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW148" s="1" t="s">
         <v>572</v>
@@ -23851,7 +23847,7 @@
         <v>941</v>
       </c>
       <c r="Z149" s="3" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="AA149" s="1" t="s">
         <v>941</v>
@@ -23896,7 +23892,7 @@
         <v>246</v>
       </c>
       <c r="AV149" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW149" s="1" t="s">
         <v>575</v>
@@ -24024,13 +24020,13 @@
         <v>941</v>
       </c>
       <c r="AS150" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="AU150" s="1" t="s">
         <v>579</v>
       </c>
       <c r="AV150" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW150" s="1" t="s">
         <v>580</v>
@@ -24158,10 +24154,10 @@
         <v>941</v>
       </c>
       <c r="AU151" s="1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="AV151" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW151" s="1" t="s">
         <v>583</v>
@@ -24292,7 +24288,7 @@
         <v>588</v>
       </c>
       <c r="AV152" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW152" s="1" t="s">
         <v>589</v>
@@ -24423,7 +24419,7 @@
         <v>490</v>
       </c>
       <c r="AV153" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW153" s="1" t="s">
         <v>591</v>
@@ -24554,7 +24550,7 @@
         <v>490</v>
       </c>
       <c r="AV154" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW154" s="1" t="s">
         <v>593</v>
@@ -24685,7 +24681,7 @@
         <v>313</v>
       </c>
       <c r="AV155" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW155" s="1" t="s">
         <v>595</v>
@@ -24813,13 +24809,13 @@
         <v>941</v>
       </c>
       <c r="AT156" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="AU156" s="1" t="s">
         <v>597</v>
       </c>
       <c r="AV156" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW156" s="1" t="s">
         <v>598</v>
@@ -24950,7 +24946,7 @@
         <v>600</v>
       </c>
       <c r="AV157" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW157" s="1" t="s">
         <v>601</v>
@@ -25081,7 +25077,7 @@
         <v>603</v>
       </c>
       <c r="AV158" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW158" s="1" t="s">
         <v>604</v>
@@ -25212,7 +25208,7 @@
         <v>609</v>
       </c>
       <c r="AV159" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW159" s="1" t="s">
         <v>610</v>
@@ -25343,7 +25339,7 @@
         <v>614</v>
       </c>
       <c r="AV160" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW160" s="1" t="s">
         <v>615</v>
@@ -25429,7 +25425,7 @@
         <v>941</v>
       </c>
       <c r="Z161" s="3" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="AA161" s="1" t="s">
         <v>941</v>
@@ -25474,7 +25470,7 @@
         <v>246</v>
       </c>
       <c r="AV161" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW161" s="1" t="s">
         <v>618</v>
@@ -25605,7 +25601,7 @@
         <v>624</v>
       </c>
       <c r="AV162" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW162" s="1" t="s">
         <v>625</v>
@@ -25736,7 +25732,7 @@
         <v>411</v>
       </c>
       <c r="AV163" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW163" s="1" t="s">
         <v>627</v>
@@ -25867,7 +25863,7 @@
         <v>490</v>
       </c>
       <c r="AV164" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW164" s="1" t="s">
         <v>629</v>
@@ -25995,13 +25991,13 @@
         <v>941</v>
       </c>
       <c r="AS165" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="AU165" s="1" t="s">
         <v>633</v>
       </c>
       <c r="AV165" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW165" s="1" t="s">
         <v>634</v>
@@ -26132,7 +26128,7 @@
         <v>462</v>
       </c>
       <c r="AV166" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW166" s="1" t="s">
         <v>636</v>
@@ -26263,7 +26259,7 @@
         <v>638</v>
       </c>
       <c r="AV167" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW167" s="1" t="s">
         <v>639</v>
@@ -26391,13 +26387,13 @@
         <v>941</v>
       </c>
       <c r="AT168" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="AU168" s="1" t="s">
         <v>644</v>
       </c>
       <c r="AV168" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW168" s="1" t="s">
         <v>645</v>
@@ -26528,7 +26524,7 @@
         <v>648</v>
       </c>
       <c r="AV169" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW169" s="1" t="s">
         <v>649</v>
@@ -26659,7 +26655,7 @@
         <v>652</v>
       </c>
       <c r="AV170" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW170" s="1" t="s">
         <v>653</v>
@@ -26790,7 +26786,7 @@
         <v>656</v>
       </c>
       <c r="AV171" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW171" s="1" t="s">
         <v>657</v>
@@ -26882,7 +26878,7 @@
         <v>943</v>
       </c>
       <c r="AB172" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="AC172" s="1" t="s">
         <v>941</v>
@@ -26921,7 +26917,7 @@
         <v>664</v>
       </c>
       <c r="AV172" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW172" s="1" t="s">
         <v>665</v>
@@ -27049,13 +27045,13 @@
         <v>941</v>
       </c>
       <c r="AT173" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="AU173" s="1" t="s">
         <v>668</v>
       </c>
       <c r="AV173" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW173" s="1" t="s">
         <v>669</v>
@@ -27186,7 +27182,7 @@
         <v>313</v>
       </c>
       <c r="AV174" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW174" s="1" t="s">
         <v>671</v>
@@ -27245,7 +27241,7 @@
         <v>941</v>
       </c>
       <c r="Q175" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="R175" s="1" t="s">
         <v>941</v>
@@ -27317,7 +27313,7 @@
         <v>51</v>
       </c>
       <c r="AV175" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW175" s="1" t="s">
         <v>673</v>
@@ -27448,7 +27444,7 @@
         <v>490</v>
       </c>
       <c r="AV176" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW176" s="1" t="s">
         <v>675</v>
@@ -27579,7 +27575,7 @@
         <v>677</v>
       </c>
       <c r="AV177" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW177" s="1" t="s">
         <v>678</v>
@@ -27632,40 +27628,40 @@
         <v>941</v>
       </c>
       <c r="O178" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="P178" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="Q178" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="R178" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="S178" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="T178" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="U178" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="V178" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="W178" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="X178" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="Y178" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="Z178" s="3" t="s">
         <v>1003</v>
-      </c>
-      <c r="P178" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="Q178" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="R178" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="S178" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="T178" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="U178" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="V178" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="W178" s="3" t="s">
-        <v>941</v>
-      </c>
-      <c r="X178" s="3" t="s">
-        <v>941</v>
-      </c>
-      <c r="Y178" s="3" t="s">
-        <v>941</v>
-      </c>
-      <c r="Z178" s="3" t="s">
-        <v>1004</v>
       </c>
       <c r="AA178" s="1" t="s">
         <v>941</v>
@@ -27707,10 +27703,10 @@
         <v>941</v>
       </c>
       <c r="AU178" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AV178" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW178" s="1" t="s">
         <v>684</v>
@@ -27841,7 +27837,7 @@
         <v>687</v>
       </c>
       <c r="AV179" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW179" s="1" t="s">
         <v>688</v>
@@ -27972,7 +27968,7 @@
         <v>691</v>
       </c>
       <c r="AV180" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW180" s="1" t="s">
         <v>692</v>
@@ -28103,7 +28099,7 @@
         <v>695</v>
       </c>
       <c r="AV181" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW181" s="1" t="s">
         <v>696</v>
@@ -28195,7 +28191,7 @@
         <v>941</v>
       </c>
       <c r="AB182" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AC182" s="1" t="s">
         <v>941</v>
@@ -28234,7 +28230,7 @@
         <v>764</v>
       </c>
       <c r="AV182" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW182" s="1" t="s">
         <v>702</v>
@@ -28362,13 +28358,13 @@
         <v>941</v>
       </c>
       <c r="AT183" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="AU183" s="1" t="s">
         <v>704</v>
       </c>
       <c r="AV183" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW183" s="1" t="s">
         <v>705</v>
@@ -28496,13 +28492,13 @@
         <v>941</v>
       </c>
       <c r="AT184" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="AU184" s="1" t="s">
         <v>707</v>
       </c>
       <c r="AV184" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW184" s="1" t="s">
         <v>708</v>
@@ -28633,7 +28629,7 @@
         <v>711</v>
       </c>
       <c r="AV185" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW185" s="1" t="s">
         <v>712</v>
@@ -28764,7 +28760,7 @@
         <v>715</v>
       </c>
       <c r="AV186" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW186" s="1" t="s">
         <v>716</v>
@@ -28895,7 +28891,7 @@
         <v>232</v>
       </c>
       <c r="AV187" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW187" s="1" t="s">
         <v>718</v>
@@ -28969,7 +28965,7 @@
         <v>941</v>
       </c>
       <c r="V188" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="W188" s="3" t="s">
         <v>941</v>
@@ -29023,10 +29019,10 @@
         <v>721</v>
       </c>
       <c r="AU188" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AV188" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW188" s="1" t="s">
         <v>722</v>
@@ -29154,16 +29150,16 @@
         <v>941</v>
       </c>
       <c r="AS189" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="AT189" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AU189" s="1" t="s">
         <v>725</v>
       </c>
       <c r="AV189" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW189" s="1" t="s">
         <v>726</v>
@@ -29294,7 +29290,7 @@
         <v>730</v>
       </c>
       <c r="AV190" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW190" s="1" t="s">
         <v>731</v>
@@ -29422,13 +29418,13 @@
         <v>941</v>
       </c>
       <c r="AS191" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="AU191" s="1" t="s">
         <v>734</v>
       </c>
       <c r="AV191" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW191" s="1" t="s">
         <v>735</v>
@@ -29556,13 +29552,13 @@
         <v>941</v>
       </c>
       <c r="AT192" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="AU192" s="1" t="s">
         <v>739</v>
       </c>
       <c r="AV192" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW192" s="1" t="s">
         <v>740</v>
@@ -29600,13 +29596,13 @@
         <v>941</v>
       </c>
       <c r="J193" s="3" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="K193" s="3" t="s">
         <v>941</v>
       </c>
       <c r="L193" s="3" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="M193" s="3" t="s">
         <v>941</v>
@@ -29693,7 +29689,7 @@
         <v>225</v>
       </c>
       <c r="AV193" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW193" s="1" t="s">
         <v>742</v>
@@ -29821,13 +29817,13 @@
         <v>941</v>
       </c>
       <c r="AS194" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AU194" s="1" t="s">
         <v>744</v>
       </c>
       <c r="AV194" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW194" s="1" t="s">
         <v>745</v>
@@ -29958,7 +29954,7 @@
         <v>748</v>
       </c>
       <c r="AV195" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW195" s="1" t="s">
         <v>749</v>
@@ -30089,7 +30085,7 @@
         <v>490</v>
       </c>
       <c r="AV196" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW196" s="1" t="s">
         <v>751</v>
@@ -30220,7 +30216,7 @@
         <v>753</v>
       </c>
       <c r="AV197" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW197" s="1" t="s">
         <v>754</v>
@@ -30264,7 +30260,7 @@
         <v>941</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="M198" s="1" t="s">
         <v>941</v>
@@ -30348,10 +30344,10 @@
         <v>941</v>
       </c>
       <c r="AU198" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="AV198" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW198" s="1" t="s">
         <v>758</v>
@@ -30482,7 +30478,7 @@
         <v>225</v>
       </c>
       <c r="AV199" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW199" s="1" t="s">
         <v>761</v>
@@ -30613,7 +30609,7 @@
         <v>764</v>
       </c>
       <c r="AV200" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW200" s="1" t="s">
         <v>765</v>
@@ -30744,7 +30740,7 @@
         <v>768</v>
       </c>
       <c r="AV201" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW201" s="1" t="s">
         <v>769</v>
@@ -30836,7 +30832,7 @@
         <v>941</v>
       </c>
       <c r="AB202" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="AC202" s="1" t="s">
         <v>941</v>
@@ -30875,7 +30871,7 @@
         <v>764</v>
       </c>
       <c r="AV202" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW202" s="1" t="s">
         <v>777</v>
@@ -31006,7 +31002,7 @@
         <v>779</v>
       </c>
       <c r="AV203" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW203" s="1" t="s">
         <v>780</v>
@@ -31137,7 +31133,7 @@
         <v>782</v>
       </c>
       <c r="AV204" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW204" s="1" t="s">
         <v>783</v>
@@ -31190,7 +31186,7 @@
         <v>941</v>
       </c>
       <c r="O205" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="P205" s="1" t="s">
         <v>941</v>
@@ -31268,7 +31264,7 @@
         <v>462</v>
       </c>
       <c r="AV205" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW205" s="1" t="s">
         <v>785</v>
@@ -31354,7 +31350,7 @@
         <v>941</v>
       </c>
       <c r="Z206" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="AA206" s="1" t="s">
         <v>941</v>
@@ -31396,10 +31392,10 @@
         <v>941</v>
       </c>
       <c r="AU206" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="AV206" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW206" s="1" t="s">
         <v>788</v>
@@ -31485,7 +31481,7 @@
         <v>941</v>
       </c>
       <c r="Z207" s="3" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="AA207" s="1" t="s">
         <v>941</v>
@@ -31527,13 +31523,13 @@
         <v>941</v>
       </c>
       <c r="AT207" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AU207" s="1" t="s">
         <v>791</v>
       </c>
       <c r="AV207" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW207" s="1" t="s">
         <v>792</v>
@@ -31664,7 +31660,7 @@
         <v>795</v>
       </c>
       <c r="AV208" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW208" s="1" t="s">
         <v>796</v>
@@ -31792,10 +31788,10 @@
         <v>941</v>
       </c>
       <c r="AU209" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="AV209" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW209" s="1" t="s">
         <v>799</v>
@@ -31926,7 +31922,7 @@
         <v>802</v>
       </c>
       <c r="AV210" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW210" s="1" t="s">
         <v>803</v>
@@ -32057,7 +32053,7 @@
         <v>806</v>
       </c>
       <c r="AV211" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW211" s="1" t="s">
         <v>807</v>
@@ -32188,7 +32184,7 @@
         <v>348</v>
       </c>
       <c r="AV212" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW212" s="1" t="s">
         <v>812</v>
@@ -32319,7 +32315,7 @@
         <v>815</v>
       </c>
       <c r="AV213" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW213" s="1" t="s">
         <v>816</v>
@@ -32447,13 +32443,13 @@
         <v>941</v>
       </c>
       <c r="AT214" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="AU214" s="1" t="s">
         <v>818</v>
       </c>
       <c r="AV214" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW214" s="1" t="s">
         <v>819</v>
@@ -32584,7 +32580,7 @@
         <v>462</v>
       </c>
       <c r="AV215" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW215" s="1" t="s">
         <v>822</v>
@@ -32715,7 +32711,7 @@
         <v>156</v>
       </c>
       <c r="AV216" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW216" s="1" t="s">
         <v>824</v>
@@ -32846,7 +32842,7 @@
         <v>826</v>
       </c>
       <c r="AV217" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW217" s="1" t="s">
         <v>827</v>
@@ -32974,13 +32970,13 @@
         <v>941</v>
       </c>
       <c r="AS218" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="AU218" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="AV218" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW218" s="1" t="s">
         <v>832</v>
@@ -33066,7 +33062,7 @@
         <v>941</v>
       </c>
       <c r="Z219" s="3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="AA219" s="1" t="s">
         <v>941</v>
@@ -33111,7 +33107,7 @@
         <v>835</v>
       </c>
       <c r="AV219" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW219" s="1" t="s">
         <v>836</v>
@@ -33242,7 +33238,7 @@
         <v>313</v>
       </c>
       <c r="AV220" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW220" s="1" t="s">
         <v>839</v>
@@ -33373,7 +33369,7 @@
         <v>225</v>
       </c>
       <c r="AV221" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW221" s="1" t="s">
         <v>842</v>
@@ -33501,13 +33497,13 @@
         <v>941</v>
       </c>
       <c r="AS222" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="AU222" s="1" t="s">
         <v>846</v>
       </c>
       <c r="AV222" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW222" s="1" t="s">
         <v>847</v>
@@ -33638,7 +33634,7 @@
         <v>225</v>
       </c>
       <c r="AV223" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW223" s="1" t="s">
         <v>850</v>
@@ -33766,13 +33762,13 @@
         <v>941</v>
       </c>
       <c r="AT224" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="AU224" s="1" t="s">
         <v>852</v>
       </c>
       <c r="AV224" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW224" s="1" t="s">
         <v>853</v>
@@ -33903,7 +33899,7 @@
         <v>855</v>
       </c>
       <c r="AV225" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW225" s="1" t="s">
         <v>856</v>
@@ -34034,7 +34030,7 @@
         <v>852</v>
       </c>
       <c r="AV226" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW226" s="1" t="s">
         <v>858</v>
@@ -34165,7 +34161,7 @@
         <v>860</v>
       </c>
       <c r="AV227" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW227" s="1" t="s">
         <v>861</v>
@@ -34293,13 +34289,13 @@
         <v>941</v>
       </c>
       <c r="AS228" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AU228" s="1" t="s">
         <v>864</v>
       </c>
       <c r="AV228" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW228" s="1" t="s">
         <v>865</v>
@@ -34430,7 +34426,7 @@
         <v>868</v>
       </c>
       <c r="AV229" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW229" s="1" t="s">
         <v>869</v>
@@ -34561,7 +34557,7 @@
         <v>872</v>
       </c>
       <c r="AV230" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW230" s="1" t="s">
         <v>873</v>
@@ -34692,7 +34688,7 @@
         <v>225</v>
       </c>
       <c r="AV231" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AW231" s="1" t="s">
         <v>876</v>
@@ -34724,352 +34720,352 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
@@ -35079,62 +35075,62 @@
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
@@ -35434,7 +35430,7 @@
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
@@ -35444,7 +35440,7 @@
     </row>
     <row r="145" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -17430,17 +17430,26 @@
       <c r="AK100" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="AL100" s="1" t="s">
-        <v>391</v>
+      <c r="AL100" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AM100" s="1" t="s">
         <v>937</v>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>ground-mire-lava</t>
+        </is>
       </c>
       <c r="AU100" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="AV100" s="1" t="s">
-        <v>1143</v>
+      <c r="AV100" s="1" t="inlineStr">
+        <is>
+          <t>沿龍捲移動軌跡產生的火池只播放本列觸發地板特效，範圍與存續時間依火池判定，不繼承龍捲本體。</t>
+        </is>
       </c>
       <c r="AW100" s="1" t="s">
         <v>393</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -17254,11 +17254,15 @@
       <c r="J99" s="3" t="s">
         <v>934</v>
       </c>
-      <c r="K99" s="1" t="s">
-        <v>934</v>
-      </c>
-      <c r="L99" s="1" t="s">
-        <v>934</v>
+      <c r="K99" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L99" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="M99" s="1" t="s">
         <v>934</v>
@@ -17299,14 +17303,18 @@
       <c r="Y99" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="Z99" s="3" t="s">
-        <v>934</v>
+      <c r="Z99" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="AA99" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="AB99" s="1" t="s">
-        <v>934</v>
+      <c r="AB99" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="AC99" s="1" t="s">
         <v>934</v>
@@ -17341,17 +17349,35 @@
       <c r="AM99" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="AU99" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="AV99" s="1" t="s">
-        <v>1140</v>
-      </c>
-      <c r="AW99" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="AX99" s="1" t="s">
-        <v>388</v>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>burst-fire</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>proj-fireball</t>
+        </is>
+      </c>
+      <c r="AU99" s="1" t="inlineStr">
+        <is>
+          <t>{"pct":200,"pctPer":20,"count":3}</t>
+        </is>
+      </c>
+      <c r="AV99" s="1" t="inlineStr">
+        <is>
+          <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：每道火龍捲每秒向搜敵範圍內最多3名敵人平射火球；觸發子彈表示直線飛行，抵達後觸發特效匹配爆炸傷害半徑。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發子彈。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+        </is>
+      </c>
+      <c r="AW99" s="1" t="inlineStr">
+        <is>
+          <t>火龍捲每 {gap} 秒向 {searchM} 米內最多 {count} 名敵人平射火球，命中後爆炸，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+        </is>
+      </c>
+      <c r="AX99" s="1" t="inlineStr">
+        <is>
+          <t>火龍捲每 {gap} 秒向 {searchM} 米內最多 {count} 名敵人平射火球，命中後爆炸，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+        </is>
       </c>
     </row>
     <row r="100" spans="1:50" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -1041,7 +1041,7 @@
     <t>hit-fireball-rupture</t>
   </si>
   <si>
-    <t>proj-fireball-ember</t>
+    <t>proj-dragon-devour</t>
   </si>
   <si>
     <t>{"pct":150,"pctPer":15}</t>
@@ -17303,9 +17303,9 @@
       <c r="Y99" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="Z99" s="3" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AA99" s="1" t="s">
@@ -17356,27 +17356,27 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>proj-fireball</t>
+          <t>proj-dragon-devour</t>
         </is>
       </c>
-      <c r="AU99" s="1" t="inlineStr">
+      <c r="AU99" t="inlineStr">
         <is>
-          <t>{"pct":200,"pctPer":20,"count":3}</t>
+          <t>{"pct":200,"pctPer":20,"count":1}</t>
         </is>
       </c>
       <c r="AV99" s="1" t="inlineStr">
         <is>
-          <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：每道火龍捲每秒向搜敵範圍內最多3名敵人平射火球；觸發子彈表示直線飛行，抵達後觸發特效匹配爆炸傷害半徑。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發子彈。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+          <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：每道火龍捲每0.33秒向搜敵範圍內每次重新隨機選取1名敵人平射1顆火球；觸發子彈表示直線飛行，抵達後觸發特效匹配爆炸傷害半徑。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發子彈。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
         </is>
       </c>
       <c r="AW99" s="1" t="inlineStr">
         <is>
-          <t>火龍捲每 {gap} 秒向 {searchM} 米內最多 {count} 名敵人平射火球，命中後爆炸，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+          <t>火龍捲每 {gap} 秒向 {searchM} 米內每次重新隨機選取最多 {count} 名敵人平射火球，命中後爆炸，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
         </is>
       </c>
       <c r="AX99" s="1" t="inlineStr">
         <is>
-          <t>火龍捲每 {gap} 秒向 {searchM} 米內最多 {count} 名敵人平射火球，命中後爆炸，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+          <t>火龍捲每 {gap} 秒向 {searchM} 米內每次重新隨機選取最多 {count} 名敵人平射火球，命中後爆炸，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
         </is>
       </c>
     </row>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -17311,9 +17311,9 @@
       <c r="AA99" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="AB99" s="1" t="inlineStr">
+      <c r="AB99" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AC99" s="1" t="s">
@@ -17366,17 +17366,17 @@
       </c>
       <c r="AV99" s="1" t="inlineStr">
         <is>
-          <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：每道火龍捲每0.33秒向搜敵範圍內每次重新隨機選取1名敵人平射1顆火球；觸發子彈表示直線飛行，抵達後觸發特效匹配爆炸傷害半徑。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發子彈。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+          <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：每道火龍捲每0.33秒向搜敵範圍內每次重新隨機選取1名敵人平射1顆火球；觸發子彈以36米／秒追蹤敵人，主目標必中，抵達後觸發特效匹配爆炸傷害半徑。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發子彈。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
         </is>
       </c>
       <c r="AW99" s="1" t="inlineStr">
         <is>
-          <t>火龍捲每 {gap} 秒向 {searchM} 米內每次重新隨機選取最多 {count} 名敵人平射火球，命中後爆炸，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+          <t>火龍捲每 {gap} 秒向 {searchM} 米內每次重新隨機選取最多 {count} 名敵人發射追蹤必中火球，命中後爆炸，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
         </is>
       </c>
       <c r="AX99" s="1" t="inlineStr">
         <is>
-          <t>火龍捲每 {gap} 秒向 {searchM} 米內每次重新隨機選取最多 {count} 名敵人平射火球，命中後爆炸，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+          <t>火龍捲每 {gap} 秒向 {searchM} 米內每次重新隨機選取最多 {count} 名敵人發射追蹤必中火球，命中後爆炸，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
         </is>
       </c>
     </row>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -17254,9 +17254,9 @@
       <c r="J99" s="3" t="s">
         <v>934</v>
       </c>
-      <c r="K99" s="1" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L99" s="1" t="inlineStr">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -18876,8 +18876,10 @@
       <c r="O111" s="3" t="s">
         <v>934</v>
       </c>
-      <c r="P111" s="1" t="s">
-        <v>934</v>
+      <c r="P111" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="Q111" s="1" t="s">
         <v>941</v>
@@ -18912,8 +18914,10 @@
       <c r="AA111" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="AB111" s="1" t="s">
-        <v>967</v>
+      <c r="AB111" s="1" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="AC111" s="1" t="s">
         <v>934</v>
@@ -18951,17 +18955,23 @@
       <c r="AS111" s="1" t="s">
         <v>1159</v>
       </c>
-      <c r="AU111" s="1" t="s">
-        <v>990</v>
+      <c r="AU111" s="1" t="inlineStr">
+        <is>
+          <t>{"pct":300,"pctPer":30,"orbs":3,"orbsPer":0.3,"rps":1.5}</t>
+        </is>
       </c>
       <c r="AV111" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="AW111" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="AX111" s="1" t="s">
-        <v>433</v>
+      <c r="AW111" s="1" t="inlineStr">
+        <is>
+          <t>你的身體被火焰包裹：每 {gap} 秒對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害；普攻同時朝目標射出 {orbs} 顆火狩星環，以半徑 {orbitM} 米組成圓環，每秒順時針旋轉 {rps} 圈，整組以 {speed} 米／秒貫穿飛行 {flyM} 米</t>
+        </is>
+      </c>
+      <c r="AX111" s="1" t="inlineStr">
+        <is>
+          <t>你的身體被火焰包裹：每 {gap} 秒對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害；普攻同時朝目標射出 {orbs} 顆火狩星環，以半徑 {orbitM} 米組成圓環，每秒順時針旋轉 {rps} 圈，整組以 {speed} 米／秒貫穿飛行 {flyM} 米</t>
+        </is>
       </c>
     </row>
     <row r="112" spans="1:50" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D41B9A6-51A3-4445-893D-8A241457D963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84AF4CD-894E-4C35-B48F-CD3A74964F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10148" uniqueCount="1231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10143" uniqueCount="1237">
   <si>
     <t>群組ID</t>
   </si>
@@ -3811,6 +3811,28 @@
   </si>
   <si>
     <t>24</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：伴生火狩（含第七階狩神之舞出生即帶的伴生）：觸發子彈沿母體的軌道跟在母體後方繞行，依火狩體積縮放。沒選超神時用本列；選了超神改用該超神列的觸發子彈。母體是本體欄的飛行子彈。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>orb-firehunt-solar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>orb-firehunt-solar-companion</t>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：選擇本超神時伴生火狩的外觀：觸發子彈跟在母體後方繞行，依火狩體積縮放。母體讀本列本體欄的飛行子彈（留白沿前階繼承）。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>orb-firehunt-firegod-companion</t>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：選擇本超神時伴生火狩的外觀：觸發子彈跟在母體後方繞行，依火狩體積縮放。本列本體欄的飛行子彈是普攻射出的火狩星環，環繞的母體因此維持第一階的外觀。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -18014,22 +18036,25 @@
         <v>932</v>
       </c>
       <c r="AJ104" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="AK104" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="AL104" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="AM104" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="AO104" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="AK104" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="AL104" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="AM104" s="1" t="s">
-        <v>932</v>
       </c>
       <c r="AU104" s="1" t="s">
         <v>407</v>
       </c>
       <c r="AV104" s="1" t="s">
-        <v>1137</v>
+        <v>1231</v>
       </c>
       <c r="AW104" s="1" t="s">
         <v>408</v>
@@ -18669,7 +18694,7 @@
         <v>932</v>
       </c>
       <c r="AJ109" s="1" t="s">
-        <v>932</v>
+        <v>1232</v>
       </c>
       <c r="AK109" s="1" t="s">
         <v>932</v>
@@ -18679,12 +18704,15 @@
       </c>
       <c r="AM109" s="1" t="s">
         <v>932</v>
+      </c>
+      <c r="AO109" s="1" t="s">
+        <v>1233</v>
       </c>
       <c r="AU109" s="1" t="s">
         <v>423</v>
       </c>
       <c r="AV109" s="1" t="s">
-        <v>1137</v>
+        <v>1234</v>
       </c>
       <c r="AW109" s="1" t="s">
         <v>424</v>
@@ -18811,11 +18839,14 @@
       <c r="AM110" s="1" t="s">
         <v>932</v>
       </c>
+      <c r="AO110" s="1" t="s">
+        <v>406</v>
+      </c>
       <c r="AU110" s="1" t="s">
         <v>427</v>
       </c>
       <c r="AV110" s="1" t="s">
-        <v>1137</v>
+        <v>1234</v>
       </c>
       <c r="AW110" s="1" t="s">
         <v>428</v>
@@ -18942,6 +18973,9 @@
       <c r="AM111" s="1" t="s">
         <v>932</v>
       </c>
+      <c r="AO111" s="1" t="s">
+        <v>1235</v>
+      </c>
       <c r="AS111" s="1" t="s">
         <v>1156</v>
       </c>
@@ -18949,7 +18983,7 @@
         <v>1229</v>
       </c>
       <c r="AV111" s="1" t="s">
-        <v>1137</v>
+        <v>1236</v>
       </c>
       <c r="AW111" s="1" t="s">
         <v>1227</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84AF4CD-894E-4C35-B48F-CD3A74964F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB79C75-2B99-4D55-AADA-32D13BA6D3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -3669,10 +3669,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"red":45,"redPer":0.5,"hp":50,"hpPer":5,"spike":100}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>pillar-indomitable</t>
   </si>
   <si>
@@ -3833,6 +3829,10 @@
   </si>
   <si>
     <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：選擇本超神時伴生火狩的外觀：觸發子彈跟在母體後方繞行，依火狩體積縮放。本列本體欄的飛行子彈是普攻射出的火狩星環，環繞的母體因此維持第一階的外觀。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"red":40,"redPer":5,"hp":50,"hpPer":5,"spike":100}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -13527,7 +13527,7 @@
         <v>932</v>
       </c>
       <c r="AQ70" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="AS70" s="1" t="s">
         <v>1045</v>
@@ -13536,13 +13536,13 @@
         <v>286</v>
       </c>
       <c r="AV70" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="AW70" s="1" t="s">
         <v>1192</v>
       </c>
-      <c r="AW70" s="1" t="s">
-        <v>1193</v>
-      </c>
       <c r="AX70" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="71" spans="1:50" x14ac:dyDescent="0.25">
@@ -13795,7 +13795,7 @@
         <v>932</v>
       </c>
       <c r="AN72" s="1" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="AS72" s="1" t="s">
         <v>1046</v>
@@ -13804,7 +13804,7 @@
         <v>292</v>
       </c>
       <c r="AV72" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="AW72" s="1" t="s">
         <v>293</v>
@@ -13935,7 +13935,7 @@
         <v>137</v>
       </c>
       <c r="AV73" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="AW73" s="1" t="s">
         <v>295</v>
@@ -14066,7 +14066,7 @@
         <v>137</v>
       </c>
       <c r="AV74" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="AW74" s="1" t="s">
         <v>297</v>
@@ -14197,7 +14197,7 @@
         <v>299</v>
       </c>
       <c r="AV75" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="AW75" s="1" t="s">
         <v>300</v>
@@ -14328,7 +14328,7 @@
         <v>137</v>
       </c>
       <c r="AV76" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="AW76" s="1" t="s">
         <v>302</v>
@@ -14459,7 +14459,7 @@
         <v>305</v>
       </c>
       <c r="AV77" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="AW77" s="1" t="s">
         <v>306</v>
@@ -14587,14 +14587,14 @@
         <v>932</v>
       </c>
       <c r="AN78" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="AP78"/>
       <c r="AU78" s="1" t="s">
         <v>309</v>
       </c>
       <c r="AV78" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="AW78" s="1" t="s">
         <v>310</v>
@@ -14722,13 +14722,13 @@
         <v>932</v>
       </c>
       <c r="AN79" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="AU79" s="1" t="s">
         <v>313</v>
       </c>
       <c r="AV79" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="AW79" s="1" t="s">
         <v>314</v>
@@ -14856,22 +14856,22 @@
         <v>932</v>
       </c>
       <c r="AN80" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="AS80" s="1" t="s">
         <v>1047</v>
       </c>
       <c r="AU80" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="AV80" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="AW80" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="AV80" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="AW80" s="1" t="s">
-        <v>1196</v>
-      </c>
       <c r="AX80" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="81" spans="1:50" x14ac:dyDescent="0.25">
@@ -14993,22 +14993,22 @@
         <v>932</v>
       </c>
       <c r="AN81" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="AS81" s="1" t="s">
         <v>1048</v>
       </c>
       <c r="AU81" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="AV81" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="AW81" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="AV81" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="AW81" s="1" t="s">
-        <v>1198</v>
-      </c>
       <c r="AX81" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="82" spans="1:50" x14ac:dyDescent="0.25">
@@ -16142,7 +16142,7 @@
         <v>932</v>
       </c>
       <c r="Z90" s="3" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="AA90" s="1" t="s">
         <v>932</v>
@@ -16193,7 +16193,7 @@
         <v>359</v>
       </c>
       <c r="AV90" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="AW90" s="1" t="s">
         <v>360</v>
@@ -16868,7 +16868,7 @@
         <v>367</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>368</v>
@@ -16895,7 +16895,7 @@
         <v>932</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>932</v>
@@ -16988,7 +16988,7 @@
         <v>313</v>
       </c>
       <c r="AV96" s="1" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AW96" s="1" t="s">
         <v>379</v>
@@ -17267,7 +17267,7 @@
         <v>932</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>932</v>
@@ -17336,7 +17336,7 @@
         <v>932</v>
       </c>
       <c r="Z99" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="AA99" s="1" t="s">
         <v>932</v>
@@ -17384,16 +17384,16 @@
         <v>326</v>
       </c>
       <c r="AU99" t="s">
+        <v>1223</v>
+      </c>
+      <c r="AV99" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="AV99" s="1" t="s">
+      <c r="AW99" s="1" t="s">
         <v>1225</v>
       </c>
-      <c r="AW99" s="1" t="s">
-        <v>1226</v>
-      </c>
       <c r="AX99" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="100" spans="1:50" x14ac:dyDescent="0.25">
@@ -17521,7 +17521,7 @@
         <v>391</v>
       </c>
       <c r="AV100" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="AW100" s="1" t="s">
         <v>392</v>
@@ -17538,7 +17538,7 @@
         <v>932</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>932</v>
@@ -17565,49 +17565,49 @@
         <v>932</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="M101" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="P101" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="Q101" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="R101" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="S101" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="T101" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="U101" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="V101" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="W101" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="X101" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="Y101" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="Z101" s="3" t="s">
         <v>1211</v>
-      </c>
-      <c r="N101" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>932</v>
-      </c>
-      <c r="P101" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="Q101" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="R101" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="S101" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="T101" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="U101" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="V101" s="1" t="s">
-        <v>1219</v>
-      </c>
-      <c r="W101" s="1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="X101" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="Y101" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>1212</v>
       </c>
       <c r="AA101" s="1" t="s">
         <v>932</v>
@@ -17637,31 +17637,31 @@
         <v>932</v>
       </c>
       <c r="AJ101" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="AK101" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="AL101" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="AM101" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="AN101" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="AU101" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="AV101" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="AW101" s="1" t="s">
         <v>1217</v>
       </c>
-      <c r="AK101" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="AL101" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="AM101" s="1" t="s">
-        <v>1214</v>
-      </c>
-      <c r="AN101" s="1" t="s">
-        <v>1216</v>
-      </c>
-      <c r="AU101" s="1" t="s">
-        <v>1221</v>
-      </c>
-      <c r="AV101" s="1" t="s">
-        <v>1215</v>
-      </c>
-      <c r="AW101" s="1" t="s">
-        <v>1218</v>
-      </c>
       <c r="AX101" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="102" spans="1:50" x14ac:dyDescent="0.25">
@@ -18054,7 +18054,7 @@
         <v>407</v>
       </c>
       <c r="AV104" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="AW104" s="1" t="s">
         <v>408</v>
@@ -18694,25 +18694,25 @@
         <v>932</v>
       </c>
       <c r="AJ109" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="AK109" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="AL109" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="AM109" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="AO109" s="1" t="s">
         <v>1232</v>
-      </c>
-      <c r="AK109" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="AL109" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="AM109" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="AO109" s="1" t="s">
-        <v>1233</v>
       </c>
       <c r="AU109" s="1" t="s">
         <v>423</v>
       </c>
       <c r="AV109" s="1" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="AW109" s="1" t="s">
         <v>424</v>
@@ -18846,7 +18846,7 @@
         <v>427</v>
       </c>
       <c r="AV110" s="1" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="AW110" s="1" t="s">
         <v>428</v>
@@ -18905,7 +18905,7 @@
         <v>959</v>
       </c>
       <c r="Q111" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="R111" s="1" t="s">
         <v>932</v>
@@ -18938,7 +18938,7 @@
         <v>932</v>
       </c>
       <c r="AB111" s="1" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="AC111" s="1" t="s">
         <v>932</v>
@@ -18974,22 +18974,22 @@
         <v>932</v>
       </c>
       <c r="AO111" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="AS111" s="1" t="s">
         <v>1156</v>
       </c>
       <c r="AU111" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="AV111" s="1" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="AW111" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="AX111" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="112" spans="1:50" x14ac:dyDescent="0.25">
@@ -20171,7 +20171,7 @@
         <v>932</v>
       </c>
       <c r="AU120" s="1" t="s">
-        <v>1190</v>
+        <v>1236</v>
       </c>
       <c r="AV120" s="1" t="s">
         <v>1137</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BEF9F4-BD85-4E80-9E88-6902D51B2877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8140DB1-E50A-4E73-8450-3AC463D9D770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10142" uniqueCount="1240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10164" uniqueCount="1243">
   <si>
     <t>群組ID</t>
   </si>
@@ -3847,6 +3847,18 @@
   </si>
   <si>
     <t>fire-tornado-inferno</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ground-mire-magma-10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ground-mire-venom-08</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ground-mire-magma-09</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -21372,7 +21384,7 @@
         <v>929</v>
       </c>
       <c r="AL129" s="1" t="s">
-        <v>929</v>
+        <v>1241</v>
       </c>
       <c r="AM129" s="1" t="s">
         <v>929</v>
@@ -21506,7 +21518,7 @@
         <v>339</v>
       </c>
       <c r="AL130" s="1" t="s">
-        <v>929</v>
+        <v>1242</v>
       </c>
       <c r="AM130" s="1" t="s">
         <v>1239</v>
@@ -21640,7 +21652,7 @@
         <v>929</v>
       </c>
       <c r="AL131" s="1" t="s">
-        <v>929</v>
+        <v>1240</v>
       </c>
       <c r="AM131" s="1" t="s">
         <v>929</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3C449A-AC8C-44BF-BC83-D1817E231956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0E531A-BEE7-41CC-89E9-0C9FA2128A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10143" uniqueCount="1246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10143" uniqueCount="1247">
   <si>
     <t>群組ID</t>
   </si>
@@ -3877,6 +3877,10 @@
   </si>
   <si>
     <t>{"chance":15,"chancePer":15,"hp":80,"hpPer":-3}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bolt-chain-travel-bluewhite</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -23108,7 +23112,7 @@
         <v>324</v>
       </c>
       <c r="AI142" s="1" t="s">
-        <v>923</v>
+        <v>1246</v>
       </c>
       <c r="AJ142" s="1" t="s">
         <v>923</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0E531A-BEE7-41CC-89E9-0C9FA2128A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B59DAF-918B-4E44-824B-4BBCC8F28BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10143" uniqueCount="1247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10143" uniqueCount="1248">
   <si>
     <t>群組ID</t>
   </si>
@@ -3881,6 +3881,10 @@
   </si>
   <si>
     <t>bolt-chain-travel-bluewhite</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -23103,7 +23107,7 @@
         <v>536</v>
       </c>
       <c r="AF142" s="1" t="s">
-        <v>925</v>
+        <v>1247</v>
       </c>
       <c r="AG142" s="1" t="s">
         <v>930</v>
@@ -23234,7 +23238,7 @@
         <v>536</v>
       </c>
       <c r="AF143" s="1" t="s">
-        <v>925</v>
+        <v>1247</v>
       </c>
       <c r="AG143" s="1" t="s">
         <v>930</v>
@@ -23365,7 +23369,7 @@
         <v>536</v>
       </c>
       <c r="AF144" s="1" t="s">
-        <v>925</v>
+        <v>1247</v>
       </c>
       <c r="AG144" s="1" t="s">
         <v>930</v>
@@ -23496,7 +23500,7 @@
         <v>536</v>
       </c>
       <c r="AF145" s="1" t="s">
-        <v>925</v>
+        <v>1247</v>
       </c>
       <c r="AG145" s="1" t="s">
         <v>930</v>
@@ -23627,7 +23631,7 @@
         <v>536</v>
       </c>
       <c r="AF146" s="1" t="s">
-        <v>925</v>
+        <v>1247</v>
       </c>
       <c r="AG146" s="1" t="s">
         <v>930</v>
@@ -23758,7 +23762,7 @@
         <v>536</v>
       </c>
       <c r="AF147" s="1" t="s">
-        <v>925</v>
+        <v>1247</v>
       </c>
       <c r="AG147" s="1" t="s">
         <v>930</v>
@@ -23889,7 +23893,7 @@
         <v>536</v>
       </c>
       <c r="AF148" s="1" t="s">
-        <v>925</v>
+        <v>1247</v>
       </c>
       <c r="AG148" s="1" t="s">
         <v>930</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B59DAF-918B-4E44-824B-4BBCC8F28BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E28741C-9985-469E-8BA3-C607941D1B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10143" uniqueCount="1248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10092" uniqueCount="1248">
   <si>
     <t>群組ID</t>
   </si>
@@ -23112,9 +23112,7 @@
       <c r="AG142" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH142" s="1" t="s">
-        <v>324</v>
-      </c>
+      <c r="AH142" s="1"/>
       <c r="AI142" s="1" t="s">
         <v>1246</v>
       </c>
@@ -24425,9 +24423,7 @@
       <c r="AG152" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH152" s="1" t="s">
-        <v>324</v>
-      </c>
+      <c r="AH152" s="1"/>
       <c r="AI152" s="1" t="s">
         <v>569</v>
       </c>
@@ -25738,9 +25734,7 @@
       <c r="AG162" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH162" s="1" t="s">
-        <v>324</v>
-      </c>
+      <c r="AH162" s="1"/>
       <c r="AI162" s="1" t="s">
         <v>923</v>
       </c>
@@ -27054,9 +27048,7 @@
       <c r="AG172" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH172" s="1" t="s">
-        <v>324</v>
-      </c>
+      <c r="AH172" s="1"/>
       <c r="AI172" s="1" t="s">
         <v>923</v>
       </c>
@@ -28367,9 +28359,7 @@
       <c r="AG182" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH182" s="1" t="s">
-        <v>324</v>
-      </c>
+      <c r="AH182" s="1"/>
       <c r="AI182" s="1" t="s">
         <v>923</v>
       </c>
@@ -28498,9 +28488,7 @@
       <c r="AG183" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH183" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH183" s="1"/>
       <c r="AI183" s="1" t="s">
         <v>923</v>
       </c>
@@ -28632,9 +28620,7 @@
       <c r="AG184" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH184" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH184" s="1"/>
       <c r="AI184" s="1" t="s">
         <v>923</v>
       </c>
@@ -28766,9 +28752,7 @@
       <c r="AG185" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH185" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH185" s="1"/>
       <c r="AI185" s="1" t="s">
         <v>692</v>
       </c>
@@ -28897,9 +28881,7 @@
       <c r="AG186" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH186" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH186" s="1"/>
       <c r="AI186" s="1" t="s">
         <v>923</v>
       </c>
@@ -29028,9 +29010,7 @@
       <c r="AG187" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH187" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH187" s="1"/>
       <c r="AI187" s="1" t="s">
         <v>923</v>
       </c>
@@ -29159,9 +29139,7 @@
       <c r="AG188" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH188" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH188" s="1"/>
       <c r="AI188" s="1" t="s">
         <v>923</v>
       </c>
@@ -29290,9 +29268,7 @@
       <c r="AG189" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="AH189" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH189" s="1"/>
       <c r="AI189" s="1" t="s">
         <v>923</v>
       </c>
@@ -29427,9 +29403,7 @@
       <c r="AG190" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="AH190" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH190" s="1"/>
       <c r="AI190" s="1" t="s">
         <v>923</v>
       </c>
@@ -29558,9 +29532,7 @@
       <c r="AG191" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="AH191" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH191" s="1"/>
       <c r="AI191" s="1" t="s">
         <v>923</v>
       </c>
@@ -29692,9 +29664,7 @@
       <c r="AG192" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH192" s="1" t="s">
-        <v>324</v>
-      </c>
+      <c r="AH192" s="1"/>
       <c r="AI192" s="1" t="s">
         <v>692</v>
       </c>
@@ -29826,9 +29796,7 @@
       <c r="AG193" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH193" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH193" s="1"/>
       <c r="AI193" s="1" t="s">
         <v>923</v>
       </c>
@@ -29957,9 +29925,7 @@
       <c r="AG194" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH194" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH194" s="1"/>
       <c r="AI194" s="1" t="s">
         <v>923</v>
       </c>
@@ -30091,9 +30057,7 @@
       <c r="AG195" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH195" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH195" s="1"/>
       <c r="AI195" s="1" t="s">
         <v>729</v>
       </c>
@@ -30222,9 +30186,7 @@
       <c r="AG196" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH196" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH196" s="1"/>
       <c r="AI196" s="1" t="s">
         <v>923</v>
       </c>
@@ -30353,9 +30315,7 @@
       <c r="AG197" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH197" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH197" s="1"/>
       <c r="AI197" s="1" t="s">
         <v>923</v>
       </c>
@@ -30484,9 +30444,7 @@
       <c r="AG198" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH198" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH198" s="1"/>
       <c r="AI198" s="1" t="s">
         <v>923</v>
       </c>
@@ -30615,9 +30573,7 @@
       <c r="AG199" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="AH199" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH199" s="1"/>
       <c r="AI199" s="1" t="s">
         <v>923</v>
       </c>
@@ -30746,9 +30702,7 @@
       <c r="AG200" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="AH200" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH200" s="1"/>
       <c r="AI200" s="1" t="s">
         <v>923</v>
       </c>
@@ -30877,9 +30831,7 @@
       <c r="AG201" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="AH201" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH201" s="1"/>
       <c r="AI201" s="1" t="s">
         <v>923</v>
       </c>
@@ -31008,9 +30960,7 @@
       <c r="AG202" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH202" s="1" t="s">
-        <v>324</v>
-      </c>
+      <c r="AH202" s="1"/>
       <c r="AI202" s="1" t="s">
         <v>923</v>
       </c>
@@ -31139,9 +31089,7 @@
       <c r="AG203" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH203" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH203" s="1"/>
       <c r="AI203" s="1" t="s">
         <v>923</v>
       </c>
@@ -31270,9 +31218,7 @@
       <c r="AG204" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH204" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH204" s="1"/>
       <c r="AI204" s="1" t="s">
         <v>923</v>
       </c>
@@ -31401,9 +31347,7 @@
       <c r="AG205" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH205" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH205" s="1"/>
       <c r="AI205" s="1" t="s">
         <v>923</v>
       </c>
@@ -31532,9 +31476,7 @@
       <c r="AG206" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH206" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH206" s="1"/>
       <c r="AI206" s="1" t="s">
         <v>923</v>
       </c>
@@ -31663,9 +31605,7 @@
       <c r="AG207" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH207" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH207" s="1"/>
       <c r="AI207" s="1" t="s">
         <v>772</v>
       </c>
@@ -31797,9 +31737,7 @@
       <c r="AG208" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH208" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH208" s="1"/>
       <c r="AI208" s="1" t="s">
         <v>923</v>
       </c>
@@ -31928,9 +31866,7 @@
       <c r="AG209" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="AH209" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH209" s="1"/>
       <c r="AI209" s="1" t="s">
         <v>923</v>
       </c>
@@ -32059,9 +31995,7 @@
       <c r="AG210" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="AH210" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH210" s="1"/>
       <c r="AI210" s="1" t="s">
         <v>923</v>
       </c>
@@ -32190,9 +32124,7 @@
       <c r="AG211" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="AH211" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH211" s="1"/>
       <c r="AI211" s="1" t="s">
         <v>923</v>
       </c>
@@ -32321,9 +32253,7 @@
       <c r="AG212" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH212" s="1" t="s">
-        <v>324</v>
-      </c>
+      <c r="AH212" s="1"/>
       <c r="AI212" s="1" t="s">
         <v>793</v>
       </c>
@@ -32452,9 +32382,7 @@
       <c r="AG213" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH213" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH213" s="1"/>
       <c r="AI213" s="1" t="s">
         <v>796</v>
       </c>
@@ -32583,9 +32511,7 @@
       <c r="AG214" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH214" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH214" s="1"/>
       <c r="AI214" s="1" t="s">
         <v>923</v>
       </c>
@@ -32717,9 +32643,7 @@
       <c r="AG215" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH215" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH215" s="1"/>
       <c r="AI215" s="1" t="s">
         <v>803</v>
       </c>
@@ -32848,9 +32772,7 @@
       <c r="AG216" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH216" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH216" s="1"/>
       <c r="AI216" s="1" t="s">
         <v>923</v>
       </c>
@@ -32979,9 +32901,7 @@
       <c r="AG217" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH217" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH217" s="1"/>
       <c r="AI217" s="1" t="s">
         <v>923</v>
       </c>
@@ -33110,9 +33030,7 @@
       <c r="AG218" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH218" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH218" s="1"/>
       <c r="AI218" s="1" t="s">
         <v>772</v>
       </c>
@@ -33244,9 +33162,7 @@
       <c r="AG219" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="AH219" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH219" s="1"/>
       <c r="AI219" s="1" t="s">
         <v>923</v>
       </c>
@@ -33375,9 +33291,7 @@
       <c r="AG220" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="AH220" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH220" s="1"/>
       <c r="AI220" s="1" t="s">
         <v>923</v>
       </c>
@@ -33506,9 +33420,7 @@
       <c r="AG221" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="AH221" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH221" s="1"/>
       <c r="AI221" s="1" t="s">
         <v>923</v>
       </c>
@@ -33637,9 +33549,7 @@
       <c r="AG222" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH222" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH222" s="1"/>
       <c r="AI222" s="1" t="s">
         <v>923</v>
       </c>
@@ -33771,9 +33681,7 @@
       <c r="AG223" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH223" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH223" s="1"/>
       <c r="AI223" s="1" t="s">
         <v>923</v>
       </c>
@@ -33902,9 +33810,7 @@
       <c r="AG224" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH224" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH224" s="1"/>
       <c r="AI224" s="1" t="s">
         <v>923</v>
       </c>
@@ -34036,9 +33942,7 @@
       <c r="AG225" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH225" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH225" s="1"/>
       <c r="AI225" s="1" t="s">
         <v>923</v>
       </c>
@@ -34167,9 +34071,7 @@
       <c r="AG226" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH226" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH226" s="1"/>
       <c r="AI226" s="1" t="s">
         <v>923</v>
       </c>
@@ -34298,9 +34200,7 @@
       <c r="AG227" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH227" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH227" s="1"/>
       <c r="AI227" s="1" t="s">
         <v>923</v>
       </c>
@@ -34429,9 +34329,7 @@
       <c r="AG228" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="AH228" s="1" t="s">
-        <v>923</v>
-      </c>
+      <c r="AH228" s="1"/>
       <c r="AI228" s="1" t="s">
         <v>923</v>
       </c>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\codex-chain-table-20260929\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E28741C-9985-469E-8BA3-C607941D1B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFB259C-1F25-4A05-93D4-139170A874CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10092" uniqueCount="1248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10090" uniqueCount="1248">
   <si>
     <t>群組ID</t>
   </si>
@@ -3880,11 +3880,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>bolt-chain-travel-bluewhite</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -23094,8 +23094,8 @@
       <c r="AA142" s="1" t="s">
         <v>923</v>
       </c>
-      <c r="AB142" s="1" t="s">
-        <v>923</v>
+      <c r="AB142" s="1">
+        <v>73.770491803278688</v>
       </c>
       <c r="AC142" s="1" t="s">
         <v>923</v>
@@ -23107,17 +23107,15 @@
         <v>536</v>
       </c>
       <c r="AF142" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="AG142" s="1" t="s">
         <v>930</v>
       </c>
       <c r="AH142" s="1"/>
-      <c r="AI142" s="1" t="s">
-        <v>1246</v>
-      </c>
+      <c r="AI142" s="1"/>
       <c r="AJ142" s="1" t="s">
-        <v>923</v>
+        <v>1247</v>
       </c>
       <c r="AK142" s="1" t="s">
         <v>537</v>
@@ -23236,7 +23234,7 @@
         <v>536</v>
       </c>
       <c r="AF143" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="AG143" s="1" t="s">
         <v>930</v>
@@ -23367,7 +23365,7 @@
         <v>536</v>
       </c>
       <c r="AF144" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="AG144" s="1" t="s">
         <v>930</v>
@@ -23498,7 +23496,7 @@
         <v>536</v>
       </c>
       <c r="AF145" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="AG145" s="1" t="s">
         <v>930</v>
@@ -23629,7 +23627,7 @@
         <v>536</v>
       </c>
       <c r="AF146" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="AG146" s="1" t="s">
         <v>930</v>
@@ -23760,7 +23758,7 @@
         <v>536</v>
       </c>
       <c r="AF147" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="AG147" s="1" t="s">
         <v>930</v>
@@ -23891,7 +23889,7 @@
         <v>536</v>
       </c>
       <c r="AF148" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="AG148" s="1" t="s">
         <v>930</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\codex-chain-table-20260929\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFB259C-1F25-4A05-93D4-139170A874CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E2731B-11E6-4C23-A08A-8B28907DFE65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10090" uniqueCount="1248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10135" uniqueCount="1249">
   <si>
     <t>群組ID</t>
   </si>
@@ -3885,6 +3885,10 @@
   </si>
   <si>
     <t>bolt-chain-travel-bluewhite</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>120</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -23094,8 +23098,8 @@
       <c r="AA142" s="1" t="s">
         <v>923</v>
       </c>
-      <c r="AB142" s="1">
-        <v>73.770491803278688</v>
+      <c r="AB142" s="1" t="s">
+        <v>1248</v>
       </c>
       <c r="AC142" s="1" t="s">
         <v>923</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E2731B-11E6-4C23-A08A-8B28907DFE65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE4C12F-B95E-4E0A-9EE3-3027E77E542B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10135" uniqueCount="1249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10107" uniqueCount="1250">
   <si>
     <t>群組ID</t>
   </si>
@@ -3888,7 +3888,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>120</t>
+    <t>bolt-chain-travel-bluewhite-08</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -23099,7 +23103,7 @@
         <v>923</v>
       </c>
       <c r="AB142" s="1" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="AC142" s="1" t="s">
         <v>923</v>
@@ -24032,14 +24036,11 @@
       <c r="AH149" s="1" t="s">
         <v>923</v>
       </c>
-      <c r="AI149" s="1" t="s">
-        <v>923</v>
-      </c>
       <c r="AJ149" s="1" t="s">
-        <v>923</v>
+        <v>1248</v>
       </c>
       <c r="AK149" s="1" t="s">
-        <v>923</v>
+        <v>537</v>
       </c>
       <c r="AL149" s="1" t="s">
         <v>923</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -24167,17 +24167,33 @@
       <c r="AI150" s="1" t="s">
         <v>923</v>
       </c>
-      <c r="AJ150" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="AK150" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="AL150" s="1" t="s">
-        <v>550</v>
+      <c r="AJ150" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK150" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL150" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AM150" s="1" t="s">
         <v>923</v>
+      </c>
+      <c r="AO150" s="1" t="inlineStr">
+        <is>
+          <t>bolt-chain-lightning</t>
+        </is>
+      </c>
+      <c r="AP150" s="1" t="inlineStr">
+        <is>
+          <t>hit-lightning</t>
+        </is>
       </c>
       <c r="AS150" s="1" t="s">
         <v>1052</v>
@@ -24185,8 +24201,10 @@
       <c r="AU150" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="AV150" s="1" t="s">
-        <v>1127</v>
+      <c r="AV150" s="1" t="inlineStr">
+        <is>
+          <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：額外維持一道自身與範圍內敵人往返的雷鏈；觸發子彈不覆蓋普通雷鏈，追蹤抵達敵人時播放觸發命中特效，回到自身才疊層；無目標立即終止。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈、觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+        </is>
       </c>
       <c r="AW150" s="1" t="s">
         <v>562</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE4C12F-B95E-4E0A-9EE3-3027E77E542B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F104E4-240D-43C3-A0A7-D8D993985AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10107" uniqueCount="1250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10129" uniqueCount="1251">
   <si>
     <t>群組ID</t>
   </si>
@@ -3892,8 +3892,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>30</t>
+    <t>120</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hit-lightning-08</t>
   </si>
 </sst>
 </file>
@@ -24040,7 +24043,7 @@
         <v>1248</v>
       </c>
       <c r="AK149" s="1" t="s">
-        <v>537</v>
+        <v>1250</v>
       </c>
       <c r="AL149" s="1" t="s">
         <v>923</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5079C30-9E07-45C7-9F1D-CAC6F138AB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD24CEB-3A9D-4BAE-9D96-8FC39A983B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -3896,10 +3896,6 @@
     <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：額外維持一道自身與範圍內敵人往返的雷鏈；觸發子彈不覆蓋普通雷鏈，追蹤抵達敵人時播放觸發命中特效，回到自身才疊層；無目標立即終止。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈、觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
   </si>
   <si>
-    <t>200*6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>0.25</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3911,15 +3907,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：每波逐道生成全場貫穿雷電；每道出生時依自身與隨機敵人決定固定方向，寬度、長度及持續時間由權威事件傳入。觸發持續場域不覆蓋普通雷鏈。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發持續場域特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <t>200*30</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>每 {interval} 秒額外產生 {count}～{countMax} 道巨大閃電，每道間隔 {gap} 秒；出生時隨機選擇場上敵人，沿自身與敵人連線貫穿全場，寬 {wid} 米，持續 {sec} 秒，每 {tick} 秒對路徑上的敵人造成 {pct}% 雷電傷害</t>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：每波逐道生成全場貫穿雷電；每道出生時以隨機兩名不同敵人連線決定固定方向，不足兩名或位置重疊則略過，寬度、長度及持續時間由權威事件傳入。觸發持續場域不覆蓋普通雷鏈。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發持續場域特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>傷害範圍為最低全場長度*雷電寬度；出生時依全場敵人延伸長度並固定位置與方向。間隔為同波逐道生成間隔；效果 JSON 的 interval 為每波間隔、tick 為每道傷害間隔、sec 為每道壽命。</t>
+    <t>每 {interval} 秒額外產生 {count}～{countMax} 道巨大閃電，每道間隔 {gap} 秒；出生時隨機選擇兩名不同敵人，沿兩敵連線貫穿全場，寬 {wid} 米，保持形態逐漸淡出，持續 {sec} 秒，每 {tick} 秒對路徑上的敵人造成 {pct}% 雷電傷害；不足兩名可連線敵人時不生成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>傷害範圍為最低全場長度*雷電寬度；出生時以兩名不同敵人的中點與連線固定位置方向，並依全場敵人延伸長度。不足兩名或兩敵位置重疊時略過。間隔為同波逐道生成間隔；JSON interval為每波間隔、tick為傷害間隔、sec為壽命。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -24263,49 +24263,49 @@
         <v>922</v>
       </c>
       <c r="L151" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="M151" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="N151" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="O151" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="P151" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q151" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="R151" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="S151" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="T151" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="U151" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="V151" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="W151" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="X151" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="Y151" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="Z151" s="3" t="s">
         <v>1250</v>
-      </c>
-      <c r="M151" s="3" t="s">
-        <v>922</v>
-      </c>
-      <c r="N151" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="O151" s="3" t="s">
-        <v>922</v>
-      </c>
-      <c r="P151" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="Q151" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="R151" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="S151" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="T151" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="U151" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="V151" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="W151" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="X151" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="Y151" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="Z151" s="3" t="s">
-        <v>1251</v>
       </c>
       <c r="AA151" s="1" t="s">
         <v>922</v>
@@ -24347,10 +24347,10 @@
         <v>922</v>
       </c>
       <c r="AR151" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="AU151" s="1" t="s">
         <v>1252</v>
-      </c>
-      <c r="AU151" s="1" t="s">
-        <v>1253</v>
       </c>
       <c r="AV151" s="1" t="s">
         <v>1254</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\magic-shield-20260929\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\codex-thunder-single\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0012CE7A-DA69-454C-9C84-0A9807CF31FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3FE7FE-EBFA-4460-B1BC-B33F117B1E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -3905,23 +3905,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：每波逐道生成全場貫穿雷電；每道出生時以隨機兩名不同敵人連線決定固定方向，不足兩名或位置重疊則略過，寬度、長度及持續時間由權威事件傳入。觸發持續場域不覆蓋普通雷鏈。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發持續場域特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>每 {interval} 秒額外產生 {count}～{countMax} 道巨大閃電，每道間隔 {gap} 秒；出生時隨機選擇兩名不同敵人，沿兩敵連線貫穿全場，寬 {wid} 米，保持形態逐漸淡出，持續 {sec} 秒，每 {tick} 秒對路徑上的敵人造成 {pct}% 雷電傷害；不足兩名可連線敵人時不生成</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>傷害範圍為最低全場長度*雷電寬度；出生時以兩名不同敵人的中點與連線固定位置方向，並依全場敵人延伸長度。不足兩名或兩敵位置重疊時略過。間隔為同波逐道生成間隔；JSON interval為每波間隔、tick為傷害間隔、sec為壽命。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>{"manaRed":0,"manaRedPer":5}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>生命損耗改由法力按上限百分比承擔：每減少 1% 最大生命，改為消耗 1% 最大法力，再乘以法力消耗降低 {manaRed}% 的效果（每級降低 5%；法力不足的部分仍扣生命）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：每波逐道生成全場貫穿雷電；每道出生時以隨機兩名不同敵人連線決定固定方向；只有一名敵人時改用玩家與該敵人連線，零敵人時才略過，寬度、長度及持續時間由權威事件傳入。觸發持續場域不覆蓋普通雷鏈。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發持續場域特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每 {interval} 秒額外產生 {count}～{countMax} 道巨大閃電，每道間隔 {gap} 秒；出生時隨機選擇兩名不同敵人，沿兩敵連線貫穿全場，寬 {wid} 米，保持形態逐漸淡出，持續 {sec} 秒，每 {tick} 秒對路徑上的敵人造成 {pct}% 雷電傷害；只有一名敵人時改用玩家與該敵人連線，零敵人時才不生成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>傷害範圍為最低全場長度*雷電寬度；出生時以兩名不同敵人的中點與連線固定位置方向，並依全場敵人延伸長度。只有一名敵人時改用玩家與該敵人連線，零敵人時才略過；位置重疊仍生成。間隔為同波逐道生成間隔；JSON interval為每波間隔、tick為傷害間隔、sec為壽命。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -22379,16 +22379,16 @@
         <v>920</v>
       </c>
       <c r="AU136" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="AV136" s="1" t="s">
         <v>1123</v>
       </c>
       <c r="AW136" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="AX136" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="137" spans="1:50" x14ac:dyDescent="0.25">
@@ -24355,13 +24355,13 @@
         <v>1250</v>
       </c>
       <c r="AV151" s="1" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="AW151" s="1" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="AX151" s="1" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="152" spans="1:50" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\codex-thunder-single\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3FE7FE-EBFA-4460-B1BC-B33F117B1E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A38184C-11F0-4D36-8CB1-BA2C73AA1150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10093" uniqueCount="1257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10093" uniqueCount="1258">
   <si>
     <t>群組ID</t>
   </si>
@@ -3897,12 +3897,15 @@
     <t>beam-flying-thunder-god</t>
   </si>
   <si>
-    <t>{"count":3,"countMax":6,"interval":3,"tick":0.5,"pct":200,"pctPer":20,"sec":3}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>200*30</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"count":3,"countMax":6,"interval":3,"tick":0.5,"pct":300,"pctPer":30,"sec":3}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hit-lightning-blue</t>
   </si>
   <si>
     <t>{"manaRed":0,"manaRedPer":5}</t>
@@ -22379,16 +22382,16 @@
         <v>920</v>
       </c>
       <c r="AU136" s="1" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="AV136" s="1" t="s">
         <v>1123</v>
       </c>
       <c r="AW136" s="1" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="AX136" s="1" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="137" spans="1:50" x14ac:dyDescent="0.25">
@@ -23155,7 +23158,7 @@
         <v>1243</v>
       </c>
       <c r="AK142" s="1" t="s">
-        <v>535</v>
+        <v>1252</v>
       </c>
       <c r="AL142" s="1" t="s">
         <v>920</v>
@@ -23679,7 +23682,7 @@
         <v>920</v>
       </c>
       <c r="AK146" s="1" t="s">
-        <v>535</v>
+        <v>1252</v>
       </c>
       <c r="AL146" s="1" t="s">
         <v>920</v>
@@ -24265,7 +24268,7 @@
         <v>920</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="M151" s="3" t="s">
         <v>920</v>
@@ -24352,16 +24355,16 @@
         <v>1249</v>
       </c>
       <c r="AU151" s="1" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="AV151" s="1" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="AW151" s="1" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="AX151" s="1" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="152" spans="1:50" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A38184C-11F0-4D36-8CB1-BA2C73AA1150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2818EFE0-9884-4CCA-959A-A9EA8B71C91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10093" uniqueCount="1258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10093" uniqueCount="1260">
   <si>
     <t>群組ID</t>
   </si>
@@ -3925,6 +3925,13 @@
   </si>
   <si>
     <t>傷害範圍為最低全場長度*雷電寬度；出生時以兩名不同敵人的中點與連線固定位置方向，並依全場敵人延伸長度。只有一名敵人時改用玩家與該敵人連線，零敵人時才略過；位置重疊仍生成。間隔為同波逐道生成間隔；JSON interval為每波間隔、tick為傷害間隔、sec為壽命。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hit-thunder-blue</t>
+  </si>
+  <si>
+    <t>6</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -25264,7 +25271,7 @@
         <v>920</v>
       </c>
       <c r="AK158" s="1" t="s">
-        <v>920</v>
+        <v>1258</v>
       </c>
       <c r="AL158" s="1" t="s">
         <v>920</v>
@@ -25359,7 +25366,7 @@
         <v>920</v>
       </c>
       <c r="Y159" s="1" t="s">
-        <v>929</v>
+        <v>1259</v>
       </c>
       <c r="Z159" s="3" t="s">
         <v>920</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2818EFE0-9884-4CCA-959A-A9EA8B71C91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A0AD21-F0F5-49AF-9577-203D52CB1320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10093" uniqueCount="1260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10093" uniqueCount="1262">
   <si>
     <t>群組ID</t>
   </si>
@@ -3932,6 +3932,14 @@
   </si>
   <si>
     <t>6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.25</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：額外天劫雷電每次追擊時，在目標位置播放觸發特效與觸發命中特效；不覆蓋普通落雷的本體外觀，單體維持原尺寸。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -25500,7 +25508,7 @@
         <v>920</v>
       </c>
       <c r="Z160" s="3" t="s">
-        <v>961</v>
+        <v>1260</v>
       </c>
       <c r="AA160" s="1" t="s">
         <v>920</v>
@@ -25526,26 +25534,29 @@
       <c r="AH160" s="1" t="s">
         <v>920</v>
       </c>
-      <c r="AI160" s="1" t="s">
+      <c r="AI160" s="1"/>
+      <c r="AJ160" s="1"/>
+      <c r="AK160" s="1"/>
+      <c r="AL160" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="AM160" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="AN160" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="AJ160" s="1" t="s">
-        <v>920</v>
-      </c>
-      <c r="AK160" s="1" t="s">
+      <c r="AO160" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="AP160" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="AL160" s="1" t="s">
-        <v>920</v>
-      </c>
-      <c r="AM160" s="1" t="s">
-        <v>920</v>
       </c>
       <c r="AU160" s="1" t="s">
         <v>593</v>
       </c>
       <c r="AV160" s="1" t="s">
-        <v>1123</v>
+        <v>1261</v>
       </c>
       <c r="AW160" s="1" t="s">
         <v>594</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C3B99F-5FD2-4BF7-AEF5-AF533EBBBB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF6C7DA-9D0B-4DD2-8B32-C0A027D85ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10091" uniqueCount="1261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10087" uniqueCount="1261">
   <si>
     <t>群組ID</t>
   </si>
@@ -4022,7 +4022,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4055,6 +4055,9 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -25802,13 +25805,11 @@
       <c r="AJ162" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="AK162" s="1" t="s">
-        <v>535</v>
-      </c>
+      <c r="AK162" s="1"/>
       <c r="AL162" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="AM162" s="3" t="s">
+      <c r="AM162" s="11" t="s">
         <v>600</v>
       </c>
       <c r="AU162" s="1" t="s">
@@ -26195,9 +26196,7 @@
       <c r="AJ165" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="AK165" s="1" t="s">
-        <v>535</v>
-      </c>
+      <c r="AK165" s="1"/>
       <c r="AL165" s="1"/>
       <c r="AM165" s="1" t="s">
         <v>917</v>
@@ -26458,9 +26457,7 @@
       <c r="AJ167" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="AK167" s="1" t="s">
-        <v>535</v>
-      </c>
+      <c r="AK167" s="1"/>
       <c r="AL167" s="1" t="s">
         <v>917</v>
       </c>
@@ -26583,20 +26580,28 @@
       <c r="AH168" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="AI168" s="1" t="s">
+      <c r="AI168" s="1"/>
+      <c r="AJ168" s="1"/>
+      <c r="AK168" s="1"/>
+      <c r="AL168" s="1"/>
+      <c r="AM168" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="AN168" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AO168" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-thunderfall-sky</t>
+        </is>
+      </c>
+      <c r="AP168" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="AJ168" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="AK168" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="AL168" s="1" t="s">
+      <c r="AQ168" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="AM168" s="1" t="s">
-        <v>917</v>
       </c>
       <c r="AT168" s="1" t="s">
         <v>1018</v>
@@ -26604,8 +26609,10 @@
       <c r="AU168" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="AV168" s="1" t="s">
-        <v>1120</v>
+      <c r="AV168" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：額外雷殞天落的觸發子彈從天而降，觸發地板特效標示落點，落地時播放觸發命中特效並按實際傷害半徑縮放；雷殞天地碎的永久追加落雷共用本列。這些觸發欄不覆蓋普通雷球、伴生雷球或環體電球的本體外觀。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈、觸發命中特效、觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+        </is>
       </c>
       <c r="AW168" s="1" t="s">
         <v>621</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -26783,8 +26783,10 @@
       <c r="J170" s="3" t="s">
         <v>917</v>
       </c>
-      <c r="K170" s="1" t="s">
-        <v>959</v>
+      <c r="K170" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
       </c>
       <c r="L170" s="1" t="s">
         <v>917</v>
@@ -26861,8 +26863,10 @@
       <c r="AJ170" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="AK170" s="1" t="s">
-        <v>535</v>
+      <c r="AK170" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="AL170" s="1" t="s">
         <v>917</v>
@@ -26870,17 +26874,35 @@
       <c r="AM170" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="AU170" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="AV170" s="1" t="s">
-        <v>1120</v>
-      </c>
-      <c r="AW170" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="AX170" s="1" t="s">
-        <v>629</v>
+      <c r="AO170" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bolt-chain-travel-bluewhite</t>
+        </is>
+      </c>
+      <c r="AP170" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-lightning-blue</t>
+        </is>
+      </c>
+      <c r="AU170" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chance":15,"chancePer":0.15,"bounces":4,"pct":100,"pctPer":10,"speedMult":4}</t>
+        </is>
+      </c>
+      <c r="AV170" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：雷球每次命中各自判定；觸發後從命中位置發出連鎖閃電，使用普通連鎖閃電的素材與尺寸，按一般雷球速度的表定倍率逐段追蹤、抵達才傷害。彈射次數含原目標，30米搜尋範圍不放大特效；觸發角色不覆蓋普通雷球或環體電球。原目標被擊殺仍從原位置彈向其他敵人，結束或玩家死亡立即回收鏈段。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈、觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+        </is>
+      </c>
+      <c r="AW170" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每次被雷球命中的敵人有 {chance}% 機率觸發 1 道連鎖閃電，以一般雷球 {speedMult} 倍速度在附近 {m} 米範圍內逐段追蹤彈射，抵達目標才造成 {pct}% 雷電傷害，最多命中 {bounces} 次（含原目標）；使用一般連鎖閃電特效與尺寸</t>
+        </is>
+      </c>
+      <c r="AX170" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每次被雷球命中的敵人有 {chance}% 機率觸發 1 道連鎖閃電，以一般雷球 {speedMult} 倍速度在附近 {m} 米範圍內逐段追蹤彈射，抵達目標才造成 {pct}% 雷電傷害，最多命中 {bounces} 次（含原目標）；使用一般連鎖閃電特效與尺寸</t>
+        </is>
       </c>
     </row>
     <row r="171" spans="1:50" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2B0DD6-3A8C-440D-92C2-BEEE04DDCD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1D614B-D7D3-4AB7-8118-A65953E19859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10089" uniqueCount="1264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10089" uniqueCount="1265">
   <si>
     <t>群組ID</t>
   </si>
@@ -3956,6 +3956,9 @@
   <si>
     <t>{"sec":10,"chance":5,"chancePer":0.5,"pct":50,"pctPer":5}</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lightning-orb-field-purple</t>
   </si>
 </sst>
 </file>
@@ -26747,7 +26750,7 @@
         <v>910</v>
       </c>
       <c r="AM169" s="1" t="s">
-        <v>910</v>
+        <v>1264</v>
       </c>
       <c r="AU169" s="1" t="s">
         <v>1263</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087EC6A4-BAEC-49AB-A1EB-DC9398B93D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E1D998-A492-47F6-A6C5-31AECCA04ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10088" uniqueCount="1265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10100" uniqueCount="1275">
   <si>
     <t>群組ID</t>
   </si>
@@ -3960,6 +3960,46 @@
   </si>
   <si>
     <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：追蹤冰箭本體沿用飛行子彈欄並沿權威移動航向連續播放；敵人凍結結束時，在該敵人的當下位置播放一次觸發特效，匹配冰爆傷害半徑。觸發特效不在冰箭發射、追蹤或普通命中時播放。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：額外箭雨每波只讀本列觸發子彈與命中特效，從每個受害者上方落下；普通發射及追蹤冰箭不繼承箭雨角色。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈、觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：水流彈每次落地在權威落點播放一次觸發爆散，匹配本次傷害半徑；起飛及寒霜擴散不播放爆散。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：寒霜成功擴散時，由原敵人向每個實際受感染者分別播放觸發子彈與命中特效；普通水彈不繼承此冰晶外觀，搜敵距離不放大特效。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈、觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：額外水龍捲只播放本列觸發持續場域，每道沿權威位置與半徑續播；普通水彈起飛及落地不播放龍捲。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發持續場域特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：達到水龍捲數量門檻後，巨大水龍捲只播放本列觸發地板特效；不混入普通水彈或第七階龍捲。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：永久領域每拍施加寒霜時只播放本列觸發命中特效；領域外殼仍讀Status表，普通水彈命中不繼承領域每拍特效。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：額外暴風雪只播放本列觸發地板特效，矩形範圍及跟隨中心取權威場域；新星爆發、凍結、死亡新星及共鳴不播放暴風雪。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：冰晶共鳴每條實際傷害連線各自讀本列觸發子彈及命中特效，從來源敵人到受害者；普通新星及暴風雪不繼承共鳴冰晶。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈、觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：每根額外冰錐只讀本列觸發地板特效，固定在生成位置並匹配傷害半徑；暴風雪仍用第七階觸發地板，不變為冰錐或水龍捲。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ground-icearrow-frost</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -28321,22 +28361,28 @@
         <v>908</v>
       </c>
       <c r="AJ181" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AK181" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL181" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM181" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AO181" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="AK181" s="1" t="s">
+      <c r="AP181" s="1" t="s">
         <v>632</v>
-      </c>
-      <c r="AL181" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="AM181" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU181" s="1" t="s">
         <v>662</v>
       </c>
       <c r="AV181" s="1" t="s">
-        <v>1111</v>
+        <v>1265</v>
       </c>
       <c r="AW181" s="1" t="s">
         <v>663</v>
@@ -28840,7 +28886,7 @@
       </c>
       <c r="AH185" s="1"/>
       <c r="AI185" s="1" t="s">
-        <v>677</v>
+        <v>908</v>
       </c>
       <c r="AJ185" s="1" t="s">
         <v>667</v>
@@ -28854,11 +28900,14 @@
       <c r="AM185" s="1" t="s">
         <v>908</v>
       </c>
+      <c r="AN185" s="1" t="s">
+        <v>677</v>
+      </c>
       <c r="AU185" s="1" t="s">
         <v>678</v>
       </c>
       <c r="AV185" s="1" t="s">
-        <v>1111</v>
+        <v>1266</v>
       </c>
       <c r="AW185" s="1" t="s">
         <v>679</v>
@@ -28972,22 +29021,28 @@
         <v>908</v>
       </c>
       <c r="AJ186" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AK186" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL186" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM186" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AO186" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="AK186" s="1" t="s">
+      <c r="AP186" s="1" t="s">
         <v>650</v>
-      </c>
-      <c r="AL186" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="AM186" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU186" s="1" t="s">
         <v>682</v>
       </c>
       <c r="AV186" s="1" t="s">
-        <v>1111</v>
+        <v>1267</v>
       </c>
       <c r="AW186" s="1" t="s">
         <v>683</v>
@@ -29239,13 +29294,16 @@
         <v>908</v>
       </c>
       <c r="AM188" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AR188" s="1" t="s">
         <v>688</v>
       </c>
       <c r="AU188" s="1" t="s">
         <v>972</v>
       </c>
       <c r="AV188" s="1" t="s">
-        <v>1111</v>
+        <v>1268</v>
       </c>
       <c r="AW188" s="1" t="s">
         <v>689</v>
@@ -29500,16 +29558,19 @@
         <v>908</v>
       </c>
       <c r="AL190" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM190" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AQ190" s="1" t="s">
         <v>696</v>
-      </c>
-      <c r="AM190" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU190" s="1" t="s">
         <v>697</v>
       </c>
       <c r="AV190" s="1" t="s">
-        <v>1111</v>
+        <v>1269</v>
       </c>
       <c r="AW190" s="1" t="s">
         <v>698</v>
@@ -29626,13 +29687,16 @@
         <v>908</v>
       </c>
       <c r="AK191" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL191" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM191" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AP191" s="1" t="s">
         <v>636</v>
-      </c>
-      <c r="AL191" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="AM191" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AS191" s="1" t="s">
         <v>1134</v>
@@ -29641,7 +29705,7 @@
         <v>701</v>
       </c>
       <c r="AV191" s="1" t="s">
-        <v>1111</v>
+        <v>1270</v>
       </c>
       <c r="AW191" s="1" t="s">
         <v>702</v>
@@ -30541,16 +30605,19 @@
         <v>908</v>
       </c>
       <c r="AL198" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM198" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AQ198" s="1" t="s">
         <v>724</v>
-      </c>
-      <c r="AM198" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU198" s="1" t="s">
         <v>975</v>
       </c>
       <c r="AV198" s="1" t="s">
-        <v>1111</v>
+        <v>1271</v>
       </c>
       <c r="AW198" s="1" t="s">
         <v>725</v>
@@ -30793,22 +30860,28 @@
         <v>908</v>
       </c>
       <c r="AJ200" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AK200" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL200" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM200" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AO200" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="AK200" s="1" t="s">
+      <c r="AP200" s="1" t="s">
         <v>650</v>
-      </c>
-      <c r="AL200" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="AM200" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU200" s="1" t="s">
         <v>731</v>
       </c>
       <c r="AV200" s="1" t="s">
-        <v>1111</v>
+        <v>1272</v>
       </c>
       <c r="AW200" s="1" t="s">
         <v>732</v>
@@ -30928,16 +31001,19 @@
         <v>908</v>
       </c>
       <c r="AL201" s="1" t="s">
-        <v>696</v>
+        <v>908</v>
       </c>
       <c r="AM201" s="1" t="s">
         <v>908</v>
+      </c>
+      <c r="AQ201" s="1" t="s">
+        <v>1274</v>
       </c>
       <c r="AU201" s="1" t="s">
         <v>735</v>
       </c>
       <c r="AV201" s="1" t="s">
-        <v>1111</v>
+        <v>1273</v>
       </c>
       <c r="AW201" s="1" t="s">
         <v>736</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E1D998-A492-47F6-A6C5-31AECCA04ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315B7043-26C3-46A9-9550-683797E73DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -3936,10 +3936,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>環體電球觸發的靜止雷球持續時間改為 {sec} 秒，並以生成時角色為中心向外緩慢移動（每秒 {speed} 米）；靜止雷球每次命中有 {chance}% 機率在自身位置再形成 1 個靜止雷球，持續 {sec} 秒且不移動；所有雷球與電球傷害額外 +{pct}%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>{"pct":50,"pctPer":5,"conv":25,"convPer":2.5}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3948,10 +3944,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"sec":10,"chance":5,"chancePer":0.5,"pct":50,"pctPer":5}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>lightning-orb-field-purple</t>
   </si>
   <si>
@@ -4000,6 +3992,14 @@
   </si>
   <si>
     <t>ground-icearrow-frost</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"sec":10,"chance":5,"chancePer":0.5,"pct":50,"pctPer":5,"childSec":3}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>環體電球觸發的電球持續 {sec} 秒，並以生成時角色為中心向外緩慢移動（每秒 {speed} 米）；每次命中有 {chance}% 機率在自身位置形成 1 個靜止電球，持續 {childSec} 秒且不移動、不再生成電球；同一緩速電球成功生成後冷卻 0.75 秒；所有雷球與電球傷害額外 +{pct}%</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -22198,7 +22198,7 @@
         <v>908</v>
       </c>
       <c r="AU134" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="AV134" s="1" t="s">
         <v>1111</v>
@@ -22329,7 +22329,7 @@
         <v>908</v>
       </c>
       <c r="AU135" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="AV135" s="1" t="s">
         <v>1111</v>
@@ -22856,7 +22856,7 @@
         <v>908</v>
       </c>
       <c r="AU139" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="AV139" s="1" t="s">
         <v>1111</v>
@@ -26792,19 +26792,19 @@
         <v>908</v>
       </c>
       <c r="AM169" s="1" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="AU169" s="1" t="s">
-        <v>1261</v>
+        <v>1273</v>
       </c>
       <c r="AV169" s="1" t="s">
         <v>1111</v>
       </c>
       <c r="AW169" s="1" t="s">
-        <v>1258</v>
+        <v>1274</v>
       </c>
       <c r="AX169" s="1" t="s">
-        <v>1258</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="170" spans="1:50" x14ac:dyDescent="0.25">
@@ -27977,13 +27977,13 @@
         <v>908</v>
       </c>
       <c r="AN178" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="AU178" s="1" t="s">
         <v>969</v>
       </c>
       <c r="AV178" s="1" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="AW178" s="1" t="s">
         <v>651</v>
@@ -28382,7 +28382,7 @@
         <v>662</v>
       </c>
       <c r="AV181" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="AW181" s="1" t="s">
         <v>663</v>
@@ -28907,7 +28907,7 @@
         <v>678</v>
       </c>
       <c r="AV185" s="1" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="AW185" s="1" t="s">
         <v>679</v>
@@ -29042,7 +29042,7 @@
         <v>682</v>
       </c>
       <c r="AV186" s="1" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="AW186" s="1" t="s">
         <v>683</v>
@@ -29303,7 +29303,7 @@
         <v>972</v>
       </c>
       <c r="AV188" s="1" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="AW188" s="1" t="s">
         <v>689</v>
@@ -29570,7 +29570,7 @@
         <v>697</v>
       </c>
       <c r="AV190" s="1" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="AW190" s="1" t="s">
         <v>698</v>
@@ -29705,7 +29705,7 @@
         <v>701</v>
       </c>
       <c r="AV191" s="1" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="AW191" s="1" t="s">
         <v>702</v>
@@ -30617,7 +30617,7 @@
         <v>975</v>
       </c>
       <c r="AV198" s="1" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="AW198" s="1" t="s">
         <v>725</v>
@@ -30881,7 +30881,7 @@
         <v>731</v>
       </c>
       <c r="AV200" s="1" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="AW200" s="1" t="s">
         <v>732</v>
@@ -31007,13 +31007,13 @@
         <v>908</v>
       </c>
       <c r="AQ201" s="1" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="AU201" s="1" t="s">
         <v>735</v>
       </c>
       <c r="AV201" s="1" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="AW201" s="1" t="s">
         <v>736</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315B7043-26C3-46A9-9550-683797E73DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F06974F-30B5-470F-9F5A-E731306BFA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10100" uniqueCount="1275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10130" uniqueCount="1288">
   <si>
     <t>群組ID</t>
   </si>
@@ -4000,6 +4000,58 @@
   </si>
   <si>
     <t>環體電球觸發的電球持續 {sec} 秒，並以生成時角色為中心向外緩慢移動（每秒 {speed} 米）；每次命中有 {chance}% 機率在自身位置形成 1 個靜止電球，持續 {childSec} 秒且不移動、不再生成電球；同一緩速電球成功生成後冷卻 0.75 秒；所有雷球與電球傷害額外 +{pct}%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：額外直射小型風刃只讀本階觸發子彈及命中特效；保留主風刃的外觀、航向及各波發射時間。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈、觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：追跡小風刃只讀本階觸發地板與命中特效；沿權威位置及轉速持續播放，不另發射直線大風刃。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發命中特效、觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：大型風刃沿途脈衝只讀本階觸發與命中特效，匹配脈衝半徑；主刃及小風刃不繼承爆點。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：追蹤大型風刃只讀本超神觸發地板與命中特效；小型追跡風刃仍讀第五階，不混入直射或沿途脈衝。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發命中特效、觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：前方真空斬的追加震波只讀本階觸發特效，沿施放方向；普通斬擊及迴旋斬外觀分開。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：額外虛空斬只讀本階觸發角色；環繞體與軌道依實際半徑及成長播放，接觸只播命中特效，不重新發射。虛空滅界與時空崩解共用本列。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發子彈、觸發命中特效、觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：命中觸發的靜止真空斬只讀本超神地板與命中特效，保持出生位置且按權威半徑成長；普通斬擊不繼承靜止場域。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發命中特效、觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：屏障每拍撕裂只播本階觸發地板，跟隨玩家且匹配傷害半徑；命中特效另播在實際受害者，不播在玩家身上。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發命中特效、觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：每拍成功附加亂風切時，只對實際目標播放本階觸發命中特效；風切本身畫面由Status表提供。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：屏障受擊觸發的貫穿風刃只讀本階觸發子彈與命中特效，沿攻擊者方向；不套用其他技能或超神外觀。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈、觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：風切結束時，向每個實際受感染者各播一條來源到目標的觸發子彈與命中特效；不借播屏障反擊或虛空斬。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈、觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：追加天降星體與屏障分離。火殞石讀本列觸發角色；雷殞石借雷球第七階觸發外觀；巨大風刃借風刃第一階子彈／命中與第六階爆點。三者都在固定落點落地後結算八米範圍，星體屬性各自為火／雷／風。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發子彈、觸發命中特效、觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：追加虛空斬讀本列觸發角色；追加四方向風刃借風刃第一階本體子彈／命中，不讀玩家在風刃樹的超神。屏障撕裂／反擊／擴散仍各讀自身階段。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發子彈、觸發命中特效、觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -31514,22 +31566,28 @@
         <v>908</v>
       </c>
       <c r="AJ205" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AK205" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL205" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM205" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AO205" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="AK205" s="1" t="s">
+      <c r="AP205" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="AL205" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="AM205" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU205" s="1" t="s">
         <v>452</v>
       </c>
       <c r="AV205" s="1" t="s">
-        <v>1111</v>
+        <v>1275</v>
       </c>
       <c r="AW205" s="1" t="s">
         <v>752</v>
@@ -31646,19 +31704,25 @@
         <v>908</v>
       </c>
       <c r="AK206" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL206" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM206" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AP206" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="AL206" s="1" t="s">
+      <c r="AQ206" s="1" t="s">
         <v>754</v>
-      </c>
-      <c r="AM206" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU206" s="1" t="s">
         <v>978</v>
       </c>
       <c r="AV206" s="1" t="s">
-        <v>1111</v>
+        <v>1276</v>
       </c>
       <c r="AW206" s="1" t="s">
         <v>755</v>
@@ -31769,19 +31833,25 @@
       </c>
       <c r="AH207" s="1"/>
       <c r="AI207" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AJ207" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AK207" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL207" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM207" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AN207" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="AJ207" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="AK207" s="1" t="s">
+      <c r="AP207" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="AL207" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="AM207" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AT207" s="1" t="s">
         <v>1042</v>
@@ -31790,7 +31860,7 @@
         <v>758</v>
       </c>
       <c r="AV207" s="1" t="s">
-        <v>1111</v>
+        <v>1277</v>
       </c>
       <c r="AW207" s="1" t="s">
         <v>759</v>
@@ -32036,19 +32106,25 @@
         <v>908</v>
       </c>
       <c r="AK209" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL209" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM209" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AP209" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="AL209" s="1" t="s">
+      <c r="AQ209" s="1" t="s">
         <v>754</v>
-      </c>
-      <c r="AM209" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU209" s="1" t="s">
         <v>980</v>
       </c>
       <c r="AV209" s="1" t="s">
-        <v>1111</v>
+        <v>1278</v>
       </c>
       <c r="AW209" s="1" t="s">
         <v>766</v>
@@ -32546,25 +32622,28 @@
       </c>
       <c r="AH213" s="1"/>
       <c r="AI213" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AJ213" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AK213" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL213" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM213" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AN213" s="1" t="s">
         <v>781</v>
-      </c>
-      <c r="AJ213" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="AK213" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="AL213" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="AM213" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU213" s="1" t="s">
         <v>782</v>
       </c>
       <c r="AV213" s="1" t="s">
-        <v>1111</v>
+        <v>1279</v>
       </c>
       <c r="AW213" s="1" t="s">
         <v>783</v>
@@ -33194,19 +33273,31 @@
       </c>
       <c r="AH218" s="1"/>
       <c r="AI218" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AJ218" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AK218" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL218" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM218" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AN218" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="AJ218" s="1" t="s">
+      <c r="AO218" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="AK218" s="1" t="s">
+      <c r="AP218" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="AL218" s="1" t="s">
+      <c r="AQ218" s="1" t="s">
         <v>798</v>
-      </c>
-      <c r="AM218" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AS218" s="1" t="s">
         <v>1044</v>
@@ -33215,7 +33306,7 @@
         <v>981</v>
       </c>
       <c r="AV218" s="1" t="s">
-        <v>1111</v>
+        <v>1280</v>
       </c>
       <c r="AW218" s="1" t="s">
         <v>799</v>
@@ -33332,19 +33423,25 @@
         <v>908</v>
       </c>
       <c r="AK219" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL219" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM219" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AP219" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="AL219" s="1" t="s">
+      <c r="AQ219" s="1" t="s">
         <v>754</v>
-      </c>
-      <c r="AM219" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU219" s="1" t="s">
         <v>802</v>
       </c>
       <c r="AV219" s="1" t="s">
-        <v>1111</v>
+        <v>1281</v>
       </c>
       <c r="AW219" s="1" t="s">
         <v>803</v>
@@ -33851,19 +33948,25 @@
         <v>908</v>
       </c>
       <c r="AK223" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL223" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM223" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AP223" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="AL223" s="1" t="s">
+      <c r="AQ223" s="1" t="s">
         <v>816</v>
-      </c>
-      <c r="AM223" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU223" s="1" t="s">
         <v>225</v>
       </c>
       <c r="AV223" s="1" t="s">
-        <v>1111</v>
+        <v>1282</v>
       </c>
       <c r="AW223" s="1" t="s">
         <v>817</v>
@@ -33980,13 +34083,16 @@
         <v>908</v>
       </c>
       <c r="AK224" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL224" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM224" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AP224" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="AL224" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="AM224" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AT224" s="1" t="s">
         <v>1043</v>
@@ -33995,7 +34101,7 @@
         <v>819</v>
       </c>
       <c r="AV224" s="1" t="s">
-        <v>1111</v>
+        <v>1283</v>
       </c>
       <c r="AW224" s="1" t="s">
         <v>820</v>
@@ -34109,22 +34215,28 @@
         <v>908</v>
       </c>
       <c r="AJ225" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AK225" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL225" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM225" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AO225" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="AK225" s="1" t="s">
+      <c r="AP225" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="AL225" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="AM225" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU225" s="1" t="s">
         <v>822</v>
       </c>
       <c r="AV225" s="1" t="s">
-        <v>1111</v>
+        <v>1284</v>
       </c>
       <c r="AW225" s="1" t="s">
         <v>823</v>
@@ -34238,22 +34350,28 @@
         <v>908</v>
       </c>
       <c r="AJ226" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AK226" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL226" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM226" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AO226" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="AK226" s="1" t="s">
+      <c r="AP226" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="AL226" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="AM226" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU226" s="1" t="s">
         <v>819</v>
       </c>
       <c r="AV226" s="1" t="s">
-        <v>1111</v>
+        <v>1285</v>
       </c>
       <c r="AW226" s="1" t="s">
         <v>825</v>
@@ -34758,25 +34876,37 @@
         <v>908</v>
       </c>
       <c r="AI230" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AJ230" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AK230" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL230" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM230" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AN230" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="AJ230" s="1" t="s">
+      <c r="AO230" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="AK230" s="1" t="s">
+      <c r="AP230" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="AL230" s="1" t="s">
+      <c r="AQ230" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="AM230" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU230" s="1" t="s">
         <v>839</v>
       </c>
       <c r="AV230" s="1" t="s">
-        <v>1111</v>
+        <v>1286</v>
       </c>
       <c r="AW230" s="1" t="s">
         <v>840</v>
@@ -34889,25 +35019,37 @@
         <v>908</v>
       </c>
       <c r="AI231" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AJ231" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AK231" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AL231" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AM231" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="AN231" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="AJ231" s="1" t="s">
+      <c r="AO231" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="AK231" s="1" t="s">
+      <c r="AP231" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="AL231" s="1" t="s">
+      <c r="AQ231" s="1" t="s">
         <v>798</v>
-      </c>
-      <c r="AM231" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="AU231" s="1" t="s">
         <v>225</v>
       </c>
       <c r="AV231" s="1" t="s">
-        <v>1111</v>
+        <v>1287</v>
       </c>
       <c r="AW231" s="1" t="s">
         <v>843</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F06974F-30B5-470F-9F5A-E731306BFA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1D3CA6-A197-4935-80F1-9A4D04C041D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -3928,10 +3928,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"chance":18,"chancePer":0.18,"bounces":6,"pct":200,"pctPer":20,"speedMult":20}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>臨界雷劫</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4052,6 +4048,10 @@
   </si>
   <si>
     <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：追加虛空斬讀本列觸發角色；追加四方向風刃借風刃第一階本體子彈／命中，不讀玩家在風刃樹的超神。屏障撕裂／反擊／擴散仍各讀自身階段。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發子彈、觸發命中特效、觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"chance":10,"chancePer":1,"bounces":6,"pct":200,"pctPer":20,"speedMult":20}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -22250,7 +22250,7 @@
         <v>908</v>
       </c>
       <c r="AU134" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="AV134" s="1" t="s">
         <v>1111</v>
@@ -22381,7 +22381,7 @@
         <v>908</v>
       </c>
       <c r="AU135" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="AV135" s="1" t="s">
         <v>1111</v>
@@ -22908,7 +22908,7 @@
         <v>908</v>
       </c>
       <c r="AU139" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="AV139" s="1" t="s">
         <v>1111</v>
@@ -26736,7 +26736,7 @@
         <v>908</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>908</v>
@@ -26844,19 +26844,19 @@
         <v>908</v>
       </c>
       <c r="AM169" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="AU169" s="1" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="AV169" s="1" t="s">
         <v>1111</v>
       </c>
       <c r="AW169" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="AX169" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="170" spans="1:50" x14ac:dyDescent="0.25">
@@ -26984,7 +26984,7 @@
         <v>1233</v>
       </c>
       <c r="AU170" s="1" t="s">
-        <v>1256</v>
+        <v>1287</v>
       </c>
       <c r="AV170" s="1" t="s">
         <v>1252</v>
@@ -28029,13 +28029,13 @@
         <v>908</v>
       </c>
       <c r="AN178" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="AU178" s="1" t="s">
         <v>969</v>
       </c>
       <c r="AV178" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="AW178" s="1" t="s">
         <v>651</v>
@@ -28434,7 +28434,7 @@
         <v>662</v>
       </c>
       <c r="AV181" s="1" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="AW181" s="1" t="s">
         <v>663</v>
@@ -28959,7 +28959,7 @@
         <v>678</v>
       </c>
       <c r="AV185" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="AW185" s="1" t="s">
         <v>679</v>
@@ -29094,7 +29094,7 @@
         <v>682</v>
       </c>
       <c r="AV186" s="1" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="AW186" s="1" t="s">
         <v>683</v>
@@ -29355,7 +29355,7 @@
         <v>972</v>
       </c>
       <c r="AV188" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="AW188" s="1" t="s">
         <v>689</v>
@@ -29622,7 +29622,7 @@
         <v>697</v>
       </c>
       <c r="AV190" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="AW190" s="1" t="s">
         <v>698</v>
@@ -29757,7 +29757,7 @@
         <v>701</v>
       </c>
       <c r="AV191" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="AW191" s="1" t="s">
         <v>702</v>
@@ -30669,7 +30669,7 @@
         <v>975</v>
       </c>
       <c r="AV198" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="AW198" s="1" t="s">
         <v>725</v>
@@ -30933,7 +30933,7 @@
         <v>731</v>
       </c>
       <c r="AV200" s="1" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="AW200" s="1" t="s">
         <v>732</v>
@@ -31059,13 +31059,13 @@
         <v>908</v>
       </c>
       <c r="AQ201" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="AU201" s="1" t="s">
         <v>735</v>
       </c>
       <c r="AV201" s="1" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="AW201" s="1" t="s">
         <v>736</v>
@@ -31587,7 +31587,7 @@
         <v>452</v>
       </c>
       <c r="AV205" s="1" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="AW205" s="1" t="s">
         <v>752</v>
@@ -31722,7 +31722,7 @@
         <v>978</v>
       </c>
       <c r="AV206" s="1" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="AW206" s="1" t="s">
         <v>755</v>
@@ -31860,7 +31860,7 @@
         <v>758</v>
       </c>
       <c r="AV207" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="AW207" s="1" t="s">
         <v>759</v>
@@ -32124,7 +32124,7 @@
         <v>980</v>
       </c>
       <c r="AV209" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="AW209" s="1" t="s">
         <v>766</v>
@@ -32643,7 +32643,7 @@
         <v>782</v>
       </c>
       <c r="AV213" s="1" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="AW213" s="1" t="s">
         <v>783</v>
@@ -33306,7 +33306,7 @@
         <v>981</v>
       </c>
       <c r="AV218" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="AW218" s="1" t="s">
         <v>799</v>
@@ -33441,7 +33441,7 @@
         <v>802</v>
       </c>
       <c r="AV219" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="AW219" s="1" t="s">
         <v>803</v>
@@ -33966,7 +33966,7 @@
         <v>225</v>
       </c>
       <c r="AV223" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="AW223" s="1" t="s">
         <v>817</v>
@@ -34101,7 +34101,7 @@
         <v>819</v>
       </c>
       <c r="AV224" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="AW224" s="1" t="s">
         <v>820</v>
@@ -34236,7 +34236,7 @@
         <v>822</v>
       </c>
       <c r="AV225" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="AW225" s="1" t="s">
         <v>823</v>
@@ -34371,7 +34371,7 @@
         <v>819</v>
       </c>
       <c r="AV226" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="AW226" s="1" t="s">
         <v>825</v>
@@ -34906,7 +34906,7 @@
         <v>839</v>
       </c>
       <c r="AV230" s="1" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="AW230" s="1" t="s">
         <v>840</v>
@@ -35049,7 +35049,7 @@
         <v>225</v>
       </c>
       <c r="AV231" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="AW231" s="1" t="s">
         <v>843</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909D27DC-7B33-49B2-BF92-BC167CEDE4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54AEA335-7EB3-4672-9648-613376E806A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -4049,11 +4049,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：額外箭雨每波固定讀 count 支觸發子彈，於波次間隔內錯落落下；每支落地都對我方傷害範圍內所有敵人結算一次完整配置傷害。觸發命中特效僅在成功命中時播放；無鎖定目標的箭仍在範圍內落下並結算。普通發射及追蹤冰箭不繼承箭雨角色。本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈、觸發命中特效。單箭維持原尺寸，不以整片箭雨範圍縮放。</t>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：額外箭雨每波固定讀 count 支觸發子彈，於波次間隔內錯落落下；從我方範圍內選擇各箭目標，敵人不足 count 名時重複分配。每支只在抵達自己的目標時結算一次完整配置傷害並播放成功受擊；無敵時空箭落下、不造成傷害，離場或移出範圍的目標不轉打其他敵人。普通發射及追蹤冰箭不繼承箭雨角色。本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈、觸發命中特效。單箭維持原尺寸，不以整片箭雨範圍縮放。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>施放寒冰箭時同時召喚 {waves} 波寒冰箭雨從天射下（每波間隔 {gap} 秒，每波 {count} 支冰箭錯落落下），每支冰箭落地時對我方 {m} 米內的所有敵人各造成 {pct}% 寒冰傷害</t>
+    <t>施放寒冰箭時同時召喚 {waves} 波寒冰箭雨從天射下（每波間隔 {gap} 秒，每波 {count} 支冰箭錯落落下），各箭選擇我方 {m} 米內的1名敵人，抵達自己的目標時造成 {pct}% 寒冰傷害（敵人不足時可重複選中）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54AEA335-7EB3-4672-9648-613376E806A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51E027F-311A-43FE-AB7D-7E869ADE67C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10130" uniqueCount="1288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10129" uniqueCount="1288">
   <si>
     <t>群組ID</t>
   </si>
@@ -3945,10 +3945,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：水流彈每次落地在權威落點播放一次觸發爆散，匹配本次傷害半徑；起飛及寒霜擴散不播放爆散。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：寒霜成功擴散時，由原敵人向每個實際受感染者分別播放觸發子彈與命中特效；普通水彈不繼承此冰晶外觀，搜敵距離不放大特效。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發子彈、觸發命中特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4054,6 +4050,10 @@
   </si>
   <si>
     <t>施放寒冰箭時同時召喚 {waves} 波寒冰箭雨從天射下（每波間隔 {gap} 秒，每波 {count} 支冰箭錯落落下），各箭選擇我方 {m} 米內的1名敵人，抵達自己的目標時造成 {pct}% 寒冰傷害（敵人不足時可重複選中）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：普通水流彈爆散沿用本體水花受擊，匹配本次傷害半徑；本列觸發特效留白不額外播放、不繼承其他來源。如指定觸發特效，僅在水彈落地時播放，起飛及寒霜擴散不播放爆散。傳奇冰霜擴散生效時改借冰霜新星第1階本體特效，保留水流彈傷害並放大本次爆散範圍30%，不繼承新星高階或超神；不讀本列普通爆散。可填：觸發特效。普通水彈起飛與水龍捲各讀自身配置，傷害範圍與落點取權威模擬。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -26849,16 +26849,16 @@
         <v>1257</v>
       </c>
       <c r="AU169" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="AV169" s="1" t="s">
         <v>1109</v>
       </c>
       <c r="AW169" s="1" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="AX169" s="1" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="170" spans="1:50" x14ac:dyDescent="0.25">
@@ -26986,7 +26986,7 @@
         <v>1231</v>
       </c>
       <c r="AU170" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="AV170" s="1" t="s">
         <v>1250</v>
@@ -28433,16 +28433,16 @@
         <v>632</v>
       </c>
       <c r="AU181" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="AV181" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="AV181" s="1" t="s">
+      <c r="AW181" s="1" t="s">
         <v>1286</v>
       </c>
-      <c r="AW181" s="1" t="s">
-        <v>1287</v>
-      </c>
       <c r="AX181" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="182" spans="1:50" x14ac:dyDescent="0.25">
@@ -28954,14 +28954,11 @@
       <c r="AM185" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="AN185" s="1" t="s">
-        <v>675</v>
-      </c>
       <c r="AU185" s="1" t="s">
         <v>676</v>
       </c>
       <c r="AV185" s="1" t="s">
-        <v>1260</v>
+        <v>1287</v>
       </c>
       <c r="AW185" s="1" t="s">
         <v>677</v>
@@ -29096,7 +29093,7 @@
         <v>680</v>
       </c>
       <c r="AV186" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="AW186" s="1" t="s">
         <v>681</v>
@@ -29357,7 +29354,7 @@
         <v>970</v>
       </c>
       <c r="AV188" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="AW188" s="1" t="s">
         <v>687</v>
@@ -29624,7 +29621,7 @@
         <v>695</v>
       </c>
       <c r="AV190" s="1" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="AW190" s="1" t="s">
         <v>696</v>
@@ -29759,7 +29756,7 @@
         <v>699</v>
       </c>
       <c r="AV191" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="AW191" s="1" t="s">
         <v>700</v>
@@ -30671,7 +30668,7 @@
         <v>973</v>
       </c>
       <c r="AV198" s="1" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="AW198" s="1" t="s">
         <v>723</v>
@@ -30935,7 +30932,7 @@
         <v>729</v>
       </c>
       <c r="AV200" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="AW200" s="1" t="s">
         <v>730</v>
@@ -31061,13 +31058,13 @@
         <v>906</v>
       </c>
       <c r="AQ201" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="AU201" s="1" t="s">
         <v>733</v>
       </c>
       <c r="AV201" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="AW201" s="1" t="s">
         <v>734</v>
@@ -31589,7 +31586,7 @@
         <v>452</v>
       </c>
       <c r="AV205" s="1" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="AW205" s="1" t="s">
         <v>750</v>
@@ -31724,7 +31721,7 @@
         <v>976</v>
       </c>
       <c r="AV206" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="AW206" s="1" t="s">
         <v>753</v>
@@ -31862,7 +31859,7 @@
         <v>756</v>
       </c>
       <c r="AV207" s="1" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="AW207" s="1" t="s">
         <v>757</v>
@@ -32126,7 +32123,7 @@
         <v>978</v>
       </c>
       <c r="AV209" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="AW209" s="1" t="s">
         <v>764</v>
@@ -32645,7 +32642,7 @@
         <v>780</v>
       </c>
       <c r="AV213" s="1" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="AW213" s="1" t="s">
         <v>781</v>
@@ -33308,7 +33305,7 @@
         <v>979</v>
       </c>
       <c r="AV218" s="1" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="AW218" s="1" t="s">
         <v>797</v>
@@ -33443,7 +33440,7 @@
         <v>800</v>
       </c>
       <c r="AV219" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="AW219" s="1" t="s">
         <v>801</v>
@@ -33968,7 +33965,7 @@
         <v>225</v>
       </c>
       <c r="AV223" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="AW223" s="1" t="s">
         <v>815</v>
@@ -34103,7 +34100,7 @@
         <v>817</v>
       </c>
       <c r="AV224" s="1" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="AW224" s="1" t="s">
         <v>818</v>
@@ -34238,7 +34235,7 @@
         <v>820</v>
       </c>
       <c r="AV225" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="AW225" s="1" t="s">
         <v>821</v>
@@ -34373,7 +34370,7 @@
         <v>817</v>
       </c>
       <c r="AV226" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="AW226" s="1" t="s">
         <v>823</v>
@@ -34908,7 +34905,7 @@
         <v>837</v>
       </c>
       <c r="AV230" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="AW230" s="1" t="s">
         <v>838</v>
@@ -35051,7 +35048,7 @@
         <v>225</v>
       </c>
       <c r="AV231" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="AW231" s="1" t="s">
         <v>841</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161F7BF4-DAEC-4988-9788-CBEFCCB21940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8010C781-75B9-4482-B9EA-21FDDB61B494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -4057,15 +4057,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>朝敵人起飛時的座標拋出水彈（射程 {castM} 米、每段弧高為該段飛行距離的一半），途中不追蹤；落地時對落點半徑 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>{"rangedRed":30,"rangedRedPer":3,"atkRed":30,"vuln":50,"vulnPer":5,"sec":6}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>施放水流彈時在周圍 {m} 米展開水牢天瀑：受到的遠程傷害 -{rangedRed}%，範圍內敵人攻擊力 -{atkRed}%且受到的傷害 +{vuln}%，持續 {sec} 秒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>朝敵人起飛時的座標拋出水彈（射程 {castM} 米、每段弧高為該段飛行距離的四分之一），途中不追蹤；落地時對落點半徑 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -28578,10 +28578,10 @@
         <v>1101</v>
       </c>
       <c r="AW182" s="1" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="AX182" s="1" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="183" spans="1:50" x14ac:dyDescent="0.25">
@@ -29496,16 +29496,16 @@
         <v>1030</v>
       </c>
       <c r="AU189" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="AV189" s="1" t="s">
         <v>1101</v>
       </c>
       <c r="AW189" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="AX189" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="190" spans="1:50" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\codex-mana-shield-20261002\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8010C781-75B9-4482-B9EA-21FDDB61B494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1334211-97C3-4B4B-B28C-9CF02D1AA36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -3838,14 +3838,6 @@
     <t>hit-lightning-blue</t>
   </si>
   <si>
-    <t>{"manaRed":0,"manaRedPer":5}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命損耗改由法力按上限百分比承擔：每減少 1% 最大生命，改為消耗 1% 最大法力，再乘以法力消耗降低 {manaRed}% 的效果（每級降低 5%；法力不足的部分仍扣生命）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：每波逐道生成全場貫穿雷電；每道出生時以隨機兩名不同敵人連線決定固定方向；只有一名敵人時改用玩家與該敵人連線，零敵人時才略過，寬度、長度及持續時間由權威事件傳入。觸發持續場域不覆蓋普通雷鏈。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發持續場域特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4066,6 +4058,14 @@
   </si>
   <si>
     <t>朝敵人起飛時的座標拋出水彈（射程 {castM} 米、每段弧高為該段飛行距離的四分之一），途中不追蹤；落地時對落點半徑 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"pct":25,"pctPer":2.5,"manaRed":25,"manaRedPer":2.5}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的傷害有 {pct}% 可轉由法力承擔，且承擔的法力消耗降低 {manaRed}%（法力消耗以本次傷害占最大生命的比例換算為最大法力百分比；法力不足的部分仍扣生命）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -22264,7 +22264,7 @@
         <v>899</v>
       </c>
       <c r="AU134" s="1" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="AV134" s="1" t="s">
         <v>1101</v>
@@ -22395,7 +22395,7 @@
         <v>899</v>
       </c>
       <c r="AU135" s="1" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="AV135" s="1" t="s">
         <v>1101</v>
@@ -22526,16 +22526,16 @@
         <v>899</v>
       </c>
       <c r="AU136" s="1" t="s">
-        <v>1230</v>
+        <v>1287</v>
       </c>
       <c r="AV136" s="1" t="s">
         <v>1101</v>
       </c>
       <c r="AW136" s="1" t="s">
-        <v>1231</v>
+        <v>1288</v>
       </c>
       <c r="AX136" s="1" t="s">
-        <v>1231</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="137" spans="1:50" x14ac:dyDescent="0.25">
@@ -22922,7 +22922,7 @@
         <v>899</v>
       </c>
       <c r="AU139" s="1" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="AV139" s="1" t="s">
         <v>1101</v>
@@ -24502,13 +24502,13 @@
         <v>1228</v>
       </c>
       <c r="AV151" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="AW151" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="AX151" s="1" t="s">
         <v>1232</v>
-      </c>
-      <c r="AW151" s="1" t="s">
-        <v>1233</v>
-      </c>
-      <c r="AX151" s="1" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="152" spans="1:50" x14ac:dyDescent="0.25">
@@ -25408,7 +25408,7 @@
         <v>899</v>
       </c>
       <c r="AK158" s="1" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="AL158" s="1" t="s">
         <v>899</v>
@@ -25515,7 +25515,7 @@
         <v>899</v>
       </c>
       <c r="AC159" s="1" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="AD159" s="3" t="s">
         <v>899</v>
@@ -25649,7 +25649,7 @@
         <v>899</v>
       </c>
       <c r="AD160" s="3" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="AE160" s="1" t="s">
         <v>899</v>
@@ -25682,16 +25682,16 @@
         <v>591</v>
       </c>
       <c r="AU160" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="AV160" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="AW160" s="1" t="s">
         <v>1238</v>
       </c>
-      <c r="AV160" s="1" t="s">
-        <v>1239</v>
-      </c>
-      <c r="AW160" s="1" t="s">
-        <v>1240</v>
-      </c>
       <c r="AX160" s="1" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="161" spans="1:50" x14ac:dyDescent="0.25">
@@ -26733,7 +26733,7 @@
         <v>619</v>
       </c>
       <c r="AV168" s="1" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="AW168" s="1" t="s">
         <v>620</v>
@@ -26750,7 +26750,7 @@
         <v>899</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>899</v>
@@ -26858,19 +26858,19 @@
         <v>899</v>
       </c>
       <c r="AM169" s="1" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="AU169" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="AV169" s="1" t="s">
         <v>1101</v>
       </c>
       <c r="AW169" s="1" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="AX169" s="1" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="170" spans="1:50" x14ac:dyDescent="0.25">
@@ -26881,7 +26881,7 @@
         <v>899</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>899</v>
@@ -26992,22 +26992,22 @@
         <v>899</v>
       </c>
       <c r="AO170" s="1" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="AP170" s="1" t="s">
         <v>1223</v>
       </c>
       <c r="AU170" s="1" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="AV170" s="1" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="AW170" s="1" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="AX170" s="1" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="171" spans="1:50" x14ac:dyDescent="0.25">
@@ -27176,7 +27176,7 @@
         <v>630</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="M172" s="1" t="s">
         <v>906</v>
@@ -27305,7 +27305,7 @@
         <v>630</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="M173" s="1" t="s">
         <v>906</v>
@@ -27439,7 +27439,7 @@
         <v>630</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="M174" s="1" t="s">
         <v>906</v>
@@ -27570,7 +27570,7 @@
         <v>630</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="M175" s="1" t="s">
         <v>906</v>
@@ -27701,7 +27701,7 @@
         <v>630</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="M176" s="1" t="s">
         <v>906</v>
@@ -27832,7 +27832,7 @@
         <v>630</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="M177" s="1" t="s">
         <v>906</v>
@@ -27963,7 +27963,7 @@
         <v>630</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="M178" s="1" t="s">
         <v>906</v>
@@ -28043,13 +28043,13 @@
         <v>899</v>
       </c>
       <c r="AN178" s="1" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="AU178" s="1" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="AV178" s="1" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="AW178" s="1" t="s">
         <v>651</v>
@@ -28177,16 +28177,16 @@
         <v>899</v>
       </c>
       <c r="AU179" s="1" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="AV179" s="1" t="s">
         <v>1101</v>
       </c>
       <c r="AW179" s="1" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="AX179" s="1" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="180" spans="1:50" x14ac:dyDescent="0.25">
@@ -28308,16 +28308,16 @@
         <v>899</v>
       </c>
       <c r="AU180" s="1" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="AV180" s="1" t="s">
         <v>1101</v>
       </c>
       <c r="AW180" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="AX180" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="181" spans="1:50" x14ac:dyDescent="0.25">
@@ -28445,16 +28445,16 @@
         <v>632</v>
       </c>
       <c r="AU181" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="AV181" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="AW181" s="1" t="s">
         <v>1276</v>
       </c>
-      <c r="AV181" s="1" t="s">
-        <v>1277</v>
-      </c>
-      <c r="AW181" s="1" t="s">
-        <v>1278</v>
-      </c>
       <c r="AX181" s="1" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="182" spans="1:50" x14ac:dyDescent="0.25">
@@ -28578,10 +28578,10 @@
         <v>1101</v>
       </c>
       <c r="AW182" s="1" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="AX182" s="1" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="183" spans="1:50" x14ac:dyDescent="0.25">
@@ -28968,7 +28968,7 @@
         <v>671</v>
       </c>
       <c r="AV185" s="1" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="AW185" s="1" t="s">
         <v>672</v>
@@ -29103,7 +29103,7 @@
         <v>675</v>
       </c>
       <c r="AV186" s="1" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="AW186" s="1" t="s">
         <v>676</v>
@@ -29364,7 +29364,7 @@
         <v>962</v>
       </c>
       <c r="AV188" s="1" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="AW188" s="1" t="s">
         <v>682</v>
@@ -29496,16 +29496,16 @@
         <v>1030</v>
       </c>
       <c r="AU189" s="1" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="AV189" s="1" t="s">
         <v>1101</v>
       </c>
       <c r="AW189" s="1" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="AX189" s="1" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="190" spans="1:50" x14ac:dyDescent="0.25">
@@ -29631,7 +29631,7 @@
         <v>688</v>
       </c>
       <c r="AV190" s="1" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="AW190" s="1" t="s">
         <v>689</v>
@@ -29766,7 +29766,7 @@
         <v>692</v>
       </c>
       <c r="AV191" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="AW191" s="1" t="s">
         <v>693</v>
@@ -30678,7 +30678,7 @@
         <v>965</v>
       </c>
       <c r="AV198" s="1" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="AW198" s="1" t="s">
         <v>716</v>
@@ -30942,7 +30942,7 @@
         <v>722</v>
       </c>
       <c r="AV200" s="1" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="AW200" s="1" t="s">
         <v>723</v>
@@ -31068,13 +31068,13 @@
         <v>899</v>
       </c>
       <c r="AQ201" s="1" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="AU201" s="1" t="s">
         <v>726</v>
       </c>
       <c r="AV201" s="1" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="AW201" s="1" t="s">
         <v>727</v>
@@ -31596,7 +31596,7 @@
         <v>452</v>
       </c>
       <c r="AV205" s="1" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="AW205" s="1" t="s">
         <v>743</v>
@@ -31731,7 +31731,7 @@
         <v>968</v>
       </c>
       <c r="AV206" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="AW206" s="1" t="s">
         <v>746</v>
@@ -31869,7 +31869,7 @@
         <v>749</v>
       </c>
       <c r="AV207" s="1" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="AW207" s="1" t="s">
         <v>750</v>
@@ -32133,7 +32133,7 @@
         <v>970</v>
       </c>
       <c r="AV209" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="AW209" s="1" t="s">
         <v>757</v>
@@ -32652,7 +32652,7 @@
         <v>773</v>
       </c>
       <c r="AV213" s="1" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="AW213" s="1" t="s">
         <v>774</v>
@@ -33315,7 +33315,7 @@
         <v>971</v>
       </c>
       <c r="AV218" s="1" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="AW218" s="1" t="s">
         <v>790</v>
@@ -33450,7 +33450,7 @@
         <v>793</v>
       </c>
       <c r="AV219" s="1" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="AW219" s="1" t="s">
         <v>794</v>
@@ -33975,7 +33975,7 @@
         <v>225</v>
       </c>
       <c r="AV223" s="1" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="AW223" s="1" t="s">
         <v>808</v>
@@ -34110,7 +34110,7 @@
         <v>810</v>
       </c>
       <c r="AV224" s="1" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="AW224" s="1" t="s">
         <v>811</v>
@@ -34245,7 +34245,7 @@
         <v>813</v>
       </c>
       <c r="AV225" s="1" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="AW225" s="1" t="s">
         <v>814</v>
@@ -34380,7 +34380,7 @@
         <v>810</v>
       </c>
       <c r="AV226" s="1" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="AW226" s="1" t="s">
         <v>816</v>
@@ -34915,7 +34915,7 @@
         <v>830</v>
       </c>
       <c r="AV230" s="1" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="AW230" s="1" t="s">
         <v>831</v>
@@ -35058,7 +35058,7 @@
         <v>225</v>
       </c>
       <c r="AV231" s="1" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="AW231" s="1" t="s">
         <v>834</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9938919-F6F5-4E18-BB21-98B0F88A5246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299DB7EC-50D5-4BB2-BAA4-1880D122F8C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -3888,10 +3888,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ground-icearrow-frost</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>{"sec":10,"chance":5,"chancePer":0.5,"pct":50,"pctPer":5,"childSec":3}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4084,6 +4080,10 @@
   </si>
   <si>
     <t>怒海狂濤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ground-ice-spike</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -19894,7 +19894,7 @@
         <v>892</v>
       </c>
       <c r="AU116" s="1" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="AV116" s="1" t="s">
         <v>1086</v>
@@ -22547,16 +22547,16 @@
         <v>892</v>
       </c>
       <c r="AU136" s="1" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="AV136" s="1" t="s">
         <v>1086</v>
       </c>
       <c r="AW136" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="AX136" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="137" spans="1:50" x14ac:dyDescent="0.25">
@@ -26882,16 +26882,16 @@
         <v>1232</v>
       </c>
       <c r="AU169" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="AV169" s="1" t="s">
         <v>1086</v>
       </c>
       <c r="AW169" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="AX169" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="170" spans="1:50" x14ac:dyDescent="0.25">
@@ -27019,7 +27019,7 @@
         <v>1208</v>
       </c>
       <c r="AU170" s="1" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="AV170" s="1" t="s">
         <v>1225</v>
@@ -27197,7 +27197,7 @@
         <v>630</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="M172">
         <v>25</v>
@@ -27326,7 +27326,7 @@
         <v>630</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="M173">
         <v>50</v>
@@ -27460,7 +27460,7 @@
         <v>630</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="M174">
         <v>100</v>
@@ -27591,7 +27591,7 @@
         <v>630</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="M175">
         <v>200</v>
@@ -27722,7 +27722,7 @@
         <v>630</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="M176">
         <v>300</v>
@@ -27853,7 +27853,7 @@
         <v>630</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="M177">
         <v>500</v>
@@ -27984,7 +27984,7 @@
         <v>630</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="M178">
         <v>1000</v>
@@ -28067,7 +28067,7 @@
         <v>1233</v>
       </c>
       <c r="AU178" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="AV178" s="1" t="s">
         <v>1234</v>
@@ -28198,16 +28198,16 @@
         <v>892</v>
       </c>
       <c r="AU179" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="AV179" s="1" t="s">
         <v>1086</v>
       </c>
       <c r="AW179" s="1" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="AX179" s="1" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="180" spans="1:50" x14ac:dyDescent="0.25">
@@ -28329,16 +28329,16 @@
         <v>892</v>
       </c>
       <c r="AU180" s="1" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="AV180" s="1" t="s">
         <v>1086</v>
       </c>
       <c r="AW180" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="AX180" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="181" spans="1:50" x14ac:dyDescent="0.25">
@@ -28466,16 +28466,16 @@
         <v>632</v>
       </c>
       <c r="AU181" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="AV181" s="1" t="s">
         <v>1257</v>
       </c>
-      <c r="AV181" s="1" t="s">
+      <c r="AW181" s="1" t="s">
         <v>1258</v>
       </c>
-      <c r="AW181" s="1" t="s">
-        <v>1259</v>
-      </c>
       <c r="AX181" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="182" spans="1:50" x14ac:dyDescent="0.25">
@@ -28599,10 +28599,10 @@
         <v>1086</v>
       </c>
       <c r="AW182" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="AX182" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="183" spans="1:50" x14ac:dyDescent="0.25">
@@ -28989,7 +28989,7 @@
         <v>671</v>
       </c>
       <c r="AV185" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="AW185" s="1" t="s">
         <v>672</v>
@@ -29382,7 +29382,7 @@
         <v>681</v>
       </c>
       <c r="AU188" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="AV188" s="1" t="s">
         <v>1236</v>
@@ -29517,16 +29517,16 @@
         <v>1015</v>
       </c>
       <c r="AU189" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="AV189" s="1" t="s">
         <v>1086</v>
       </c>
       <c r="AW189" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="AX189" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="190" spans="1:50" x14ac:dyDescent="0.25">
@@ -29537,7 +29537,7 @@
         <v>892</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>892</v>
@@ -29646,22 +29646,22 @@
         <v>892</v>
       </c>
       <c r="AQ190" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="AR190" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="AR190" s="1" t="s">
+      <c r="AU190" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="AV190" s="1" t="s">
         <v>1279</v>
       </c>
-      <c r="AU190" s="1" t="s">
-        <v>1287</v>
-      </c>
-      <c r="AV190" s="1" t="s">
-        <v>1280</v>
-      </c>
       <c r="AW190" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="AX190" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="191" spans="1:50" x14ac:dyDescent="0.25">
@@ -29714,7 +29714,7 @@
         <v>892</v>
       </c>
       <c r="Q191" s="3" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="R191" s="1" t="s">
         <v>892</v>
@@ -29787,16 +29787,16 @@
         <v>1109</v>
       </c>
       <c r="AU191" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="AV191" s="1" t="s">
         <v>1237</v>
       </c>
       <c r="AW191" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="AX191" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="AX191" s="1" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="192" spans="1:50" x14ac:dyDescent="0.25">
@@ -30885,49 +30885,49 @@
       </c>
       <c r="O200" s="1"/>
       <c r="P200" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="Q200" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="R200" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="S200" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="T200" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="U200" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="V200" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="W200" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="X200" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="Y200" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="Z200" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="AA200" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="AB200" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="AC200" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="AD200" s="3" t="s">
         <v>1281</v>
-      </c>
-      <c r="Q200" s="3" t="s">
-        <v>892</v>
-      </c>
-      <c r="R200" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="S200" s="3" t="s">
-        <v>892</v>
-      </c>
-      <c r="T200" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="U200" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="V200" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="W200" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="X200" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="Y200" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="Z200" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="AA200" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="AB200" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="AC200" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="AD200" s="3" t="s">
-        <v>1282</v>
       </c>
       <c r="AE200" s="1" t="s">
         <v>892</v>
@@ -30955,19 +30955,19 @@
         <v>892</v>
       </c>
       <c r="AN200" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="AU200" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="AU200" s="1" t="s">
+      <c r="AV200" s="1" t="s">
         <v>1284</v>
       </c>
-      <c r="AV200" s="1" t="s">
+      <c r="AW200" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="AW200" s="1" t="s">
-        <v>1286</v>
-      </c>
       <c r="AX200" s="1" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="201" spans="1:50" x14ac:dyDescent="0.25">
@@ -31087,7 +31087,7 @@
         <v>892</v>
       </c>
       <c r="AQ201" s="1" t="s">
-        <v>1240</v>
+        <v>1289</v>
       </c>
       <c r="AU201" s="1" t="s">
         <v>719</v>
@@ -31615,7 +31615,7 @@
         <v>452</v>
       </c>
       <c r="AV205" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="AW205" s="1" t="s">
         <v>736</v>
@@ -31750,7 +31750,7 @@
         <v>953</v>
       </c>
       <c r="AV206" s="1" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="AW206" s="1" t="s">
         <v>739</v>
@@ -31888,7 +31888,7 @@
         <v>742</v>
       </c>
       <c r="AV207" s="1" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="AW207" s="1" t="s">
         <v>743</v>
@@ -32152,7 +32152,7 @@
         <v>955</v>
       </c>
       <c r="AV209" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="AW209" s="1" t="s">
         <v>750</v>
@@ -32671,7 +32671,7 @@
         <v>766</v>
       </c>
       <c r="AV213" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="AW213" s="1" t="s">
         <v>767</v>
@@ -33334,7 +33334,7 @@
         <v>956</v>
       </c>
       <c r="AV218" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="AW218" s="1" t="s">
         <v>783</v>
@@ -33469,7 +33469,7 @@
         <v>786</v>
       </c>
       <c r="AV219" s="1" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="AW219" s="1" t="s">
         <v>787</v>
@@ -33994,7 +33994,7 @@
         <v>225</v>
       </c>
       <c r="AV223" s="1" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="AW223" s="1" t="s">
         <v>801</v>
@@ -34129,7 +34129,7 @@
         <v>803</v>
       </c>
       <c r="AV224" s="1" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="AW224" s="1" t="s">
         <v>804</v>
@@ -34264,7 +34264,7 @@
         <v>806</v>
       </c>
       <c r="AV225" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="AW225" s="1" t="s">
         <v>807</v>
@@ -34399,7 +34399,7 @@
         <v>803</v>
       </c>
       <c r="AV226" s="1" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="AW226" s="1" t="s">
         <v>809</v>
@@ -34934,7 +34934,7 @@
         <v>823</v>
       </c>
       <c r="AV230" s="1" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="AW230" s="1" t="s">
         <v>824</v>
@@ -35077,7 +35077,7 @@
         <v>225</v>
       </c>
       <c r="AV231" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="AW231" s="1" t="s">
         <v>827</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299DB7EC-50D5-4BB2-BAA4-1880D122F8C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C15E414-6571-4AA6-8993-A768FE0DD3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9895" uniqueCount="1290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9897" uniqueCount="1294">
   <si>
     <t>群組ID</t>
   </si>
@@ -4084,6 +4084,22 @@
   </si>
   <si>
     <t>ground-ice-spike</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>風刃改為被動技能：受到攻擊時有 {chance}% 機率朝攻擊者射出 1 道小型追蹤風刃，傷害沿用【亂披風】，追蹤範圍與持續時間沿用【追跡風刃】，且其傷害額外 +{pct}%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hit-wind</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ground-homing-wind-crescent</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：受擊觸發時只生成一道小型追蹤風刃，讀本超神觸發地板與命中特效；沿權威位置持續播放，不產生大型風刃、連射、鏡射或沿途脈衝。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發命中特效、觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -32406,14 +32422,20 @@
       <c r="AM211" s="1" t="s">
         <v>892</v>
       </c>
+      <c r="AP211" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="AQ211" s="1" t="s">
+        <v>1292</v>
+      </c>
       <c r="AU211" s="1" t="s">
         <v>757</v>
       </c>
       <c r="AV211" s="1" t="s">
-        <v>1086</v>
+        <v>1293</v>
       </c>
       <c r="AW211" s="1" t="s">
-        <v>758</v>
+        <v>1290</v>
       </c>
       <c r="AX211" s="1" t="s">
         <v>758</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9807CBE8-77C0-494F-A3E4-C8D7B8BAA7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D64E3FD-8052-400F-A295-71873C9D300A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9897" uniqueCount="1294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9899" uniqueCount="1296">
   <si>
     <t>群組ID</t>
   </si>
@@ -4104,6 +4104,13 @@
   </si>
   <si>
     <t>風刃具備風系與地系雙屬性；屬性傷害加成為角色風系傷害提升 ×{windPct}%＋地系傷害提升 ×{earthPct}%；風刃擊殺敵人時回復最大生命 {shieldPct}% 的護盾</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ground-homing-wind-crescent-09</t>
+  </si>
+  <si>
+    <t>hit-wind-09</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -32297,6 +32304,12 @@
       <c r="AM210" s="1" t="s">
         <v>889</v>
       </c>
+      <c r="AP210" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AQ210" s="1" t="s">
+        <v>1294</v>
+      </c>
       <c r="AU210" s="1" t="s">
         <v>1292</v>
       </c>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D64E3FD-8052-400F-A295-71873C9D300A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9C0413-F9B6-4C86-A5B5-FD87F8573526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9899" uniqueCount="1296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9897" uniqueCount="1295">
   <si>
     <t>群組ID</t>
   </si>
@@ -4107,10 +4107,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ground-homing-wind-crescent-09</t>
-  </si>
-  <si>
-    <t>hit-wind-09</t>
+    <t>proj-wind-crescent-09</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -32293,7 +32290,7 @@
         <v>889</v>
       </c>
       <c r="AJ210" s="1" t="s">
-        <v>726</v>
+        <v>1294</v>
       </c>
       <c r="AK210" s="1" t="s">
         <v>727</v>
@@ -32303,12 +32300,6 @@
       </c>
       <c r="AM210" s="1" t="s">
         <v>889</v>
-      </c>
-      <c r="AP210" s="1" t="s">
-        <v>1295</v>
-      </c>
-      <c r="AQ210" s="1" t="s">
-        <v>1294</v>
       </c>
       <c r="AU210" s="1" t="s">
         <v>1292</v>
@@ -35128,7 +35119,7 @@
   </sheetData>
   <autoFilter ref="A1:AX231" xr:uid="{ACC8F76D-B553-4CF8-BE7D-F03409684AEE}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="施法消耗" error="請輸入大於或等於 0 的數字，或留白。" sqref="M2:M231" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0</formula1>
     </dataValidation>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9C0413-F9B6-4C86-A5B5-FD87F8573526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8F1975-D9F8-48EC-8CD8-3C2D4AF440A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9897" uniqueCount="1295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9901" uniqueCount="1298">
   <si>
     <t>群組ID</t>
   </si>
@@ -4108,6 +4108,18 @@
   </si>
   <si>
     <t>proj-wind-crescent-09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ground-homing-wind-crescent-09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>burst-wind-09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：嵐之山的觸發特效控制大型主刃沿途風爆（須學第六階），風爆命中仍讀第六階命中欄。小型風刃直射時播放觸發子彈，追蹤時觸發子彈與地板沿同一權威位置及航向持續播放，接觸命中才播放觸發命中特效；四欄獨立，留白不播放。大型主刃仍讀本體欄。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發特效、觸發子彈、觸發命中特效、觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -32301,11 +32313,23 @@
       <c r="AM210" s="1" t="s">
         <v>889</v>
       </c>
+      <c r="AN210" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="AO210" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AP210" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="AQ210" s="1" t="s">
+        <v>1295</v>
+      </c>
       <c r="AU210" s="1" t="s">
         <v>1292</v>
       </c>
       <c r="AV210" s="1" t="s">
-        <v>1082</v>
+        <v>1297</v>
       </c>
       <c r="AW210" s="1" t="s">
         <v>1293</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGames\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029676D4-4D04-4B85-853D-CAEA901E8066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD18795E-EA5E-465C-8A9F-68F4A57258B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -4138,7 +4138,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>真空斬命中時有 {chance}% 機率在該處留下一道靜止的真空斬：持續 {sec} 秒、半徑隨時間擴大為 {grow} 倍，對碰到的敵人造成 {pct}% 風系傷害。系統限制：每個敵人在存活期間最多成功觸發 1 次，全場最多同時存在 10 個靜止真空斬。</t>
+    <t>真空斬命中時有 {chance}% 機率在該處留下一道靜止的真空斬：持續 {sec} 秒、半徑隨時間擴大為 {grow} 倍，對碰到的敵人造成 {pct}% 風系傷害。系統限制：同一個敵人生成的靜止真空斬結束後可再次觸發，全場最多同時存在 15 個靜止真空斬（不包含原本圍繞自身的虛空斬）。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4611,29 +4611,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACC8F76D-B553-4CF8-BE7D-F03409684AEE}">
   <dimension ref="A1:AX231"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="9.25" customWidth="1"/>
-    <col min="9" max="9" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="33" width="8.5" customWidth="1"/>
-    <col min="34" max="34" width="7.625" customWidth="1"/>
-    <col min="35" max="35" width="14.25" customWidth="1"/>
-    <col min="36" max="37" width="7.625" customWidth="1"/>
-    <col min="38" max="38" width="20.5" customWidth="1"/>
-    <col min="39" max="39" width="7.625" customWidth="1"/>
-    <col min="40" max="44" width="7.625" style="1" customWidth="1"/>
-    <col min="45" max="46" width="12.375" style="1" customWidth="1"/>
-    <col min="47" max="47" width="48.625" customWidth="1"/>
-    <col min="48" max="48" width="12.125" customWidth="1"/>
-    <col min="49" max="50" width="48.625" customWidth="1"/>
+    <col min="6" max="8" width="9.21875" customWidth="1"/>
+    <col min="9" max="9" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="33" width="8.44140625" customWidth="1"/>
+    <col min="34" max="34" width="7.6640625" customWidth="1"/>
+    <col min="35" max="35" width="14.21875" customWidth="1"/>
+    <col min="36" max="37" width="7.6640625" customWidth="1"/>
+    <col min="38" max="38" width="20.44140625" customWidth="1"/>
+    <col min="39" max="39" width="7.6640625" customWidth="1"/>
+    <col min="40" max="44" width="7.6640625" style="1" customWidth="1"/>
+    <col min="45" max="46" width="12.33203125" style="1" customWidth="1"/>
+    <col min="47" max="47" width="48.6640625" customWidth="1"/>
+    <col min="48" max="48" width="12.109375" customWidth="1"/>
+    <col min="49" max="50" width="48.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" s="9" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" s="9" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -5309,7 +5309,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -5571,7 +5571,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
@@ -5702,7 +5702,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -5836,7 +5836,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -5970,7 +5970,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -6101,7 +6101,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>72</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>72</v>
       </c>
@@ -6363,7 +6363,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>72</v>
       </c>
@@ -6494,7 +6494,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>72</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>72</v>
       </c>
@@ -6755,7 +6755,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>72</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>72</v>
       </c>
@@ -7009,7 +7009,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>72</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>72</v>
       </c>
@@ -7262,7 +7262,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>72</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>108</v>
       </c>
@@ -7524,7 +7524,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>108</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>108</v>
       </c>
@@ -7786,7 +7786,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>108</v>
       </c>
@@ -7917,7 +7917,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>108</v>
       </c>
@@ -8048,7 +8048,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>108</v>
       </c>
@@ -8179,7 +8179,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>108</v>
       </c>
@@ -8310,7 +8310,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>108</v>
       </c>
@@ -8441,7 +8441,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>108</v>
       </c>
@@ -8575,7 +8575,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>108</v>
       </c>
@@ -8706,7 +8706,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>149</v>
       </c>
@@ -8837,7 +8837,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>149</v>
       </c>
@@ -8968,7 +8968,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="34" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>149</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>149</v>
       </c>
@@ -9230,7 +9230,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>149</v>
       </c>
@@ -9364,7 +9364,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>149</v>
       </c>
@@ -9495,7 +9495,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>149</v>
       </c>
@@ -9626,7 +9626,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>149</v>
       </c>
@@ -9760,7 +9760,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="40" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>149</v>
       </c>
@@ -9894,7 +9894,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="41" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>149</v>
       </c>
@@ -10025,7 +10025,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="42" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>189</v>
       </c>
@@ -10157,7 +10157,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="43" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>189</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="44" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>189</v>
       </c>
@@ -10415,7 +10415,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>189</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="46" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>968</v>
       </c>
@@ -10684,7 +10684,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="47" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>189</v>
       </c>
@@ -10814,7 +10814,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="48" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>189</v>
       </c>
@@ -10943,7 +10943,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="49" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>189</v>
       </c>
@@ -11078,7 +11078,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="50" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>189</v>
       </c>
@@ -11217,7 +11217,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="51" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>189</v>
       </c>
@@ -11352,7 +11352,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="52" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>226</v>
       </c>
@@ -11479,7 +11479,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="53" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>226</v>
       </c>
@@ -11608,7 +11608,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="54" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>226</v>
       </c>
@@ -11737,7 +11737,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="55" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>226</v>
       </c>
@@ -11871,7 +11871,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="56" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>226</v>
       </c>
@@ -12008,7 +12008,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="57" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>226</v>
       </c>
@@ -12139,7 +12139,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="58" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>226</v>
       </c>
@@ -12271,7 +12271,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="59" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>226</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="60" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>226</v>
       </c>
@@ -12536,7 +12536,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="61" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>226</v>
       </c>
@@ -12667,7 +12667,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="62" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>254</v>
       </c>
@@ -12798,7 +12798,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="63" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>254</v>
       </c>
@@ -12929,7 +12929,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="64" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>254</v>
       </c>
@@ -13060,7 +13060,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="65" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>254</v>
       </c>
@@ -13191,7 +13191,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="66" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>254</v>
       </c>
@@ -13325,7 +13325,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="67" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>254</v>
       </c>
@@ -13456,7 +13456,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="68" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>254</v>
       </c>
@@ -13587,7 +13587,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="69" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>254</v>
       </c>
@@ -13724,7 +13724,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="70" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>254</v>
       </c>
@@ -13859,7 +13859,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="71" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>254</v>
       </c>
@@ -13990,7 +13990,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="72" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>289</v>
       </c>
@@ -14127,7 +14127,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="73" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>289</v>
       </c>
@@ -14258,7 +14258,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="74" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>289</v>
       </c>
@@ -14389,7 +14389,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="75" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>289</v>
       </c>
@@ -14520,7 +14520,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="76" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>289</v>
       </c>
@@ -14651,7 +14651,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="77" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>289</v>
       </c>
@@ -14782,7 +14782,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="78" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>289</v>
       </c>
@@ -14917,7 +14917,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="79" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>289</v>
       </c>
@@ -15051,7 +15051,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="80" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>289</v>
       </c>
@@ -15188,7 +15188,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="81" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>289</v>
       </c>
@@ -15325,7 +15325,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="82" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>319</v>
       </c>
@@ -15456,7 +15456,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="83" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>319</v>
       </c>
@@ -15590,7 +15590,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="84" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>319</v>
       </c>
@@ -15721,7 +15721,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="85" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>319</v>
       </c>
@@ -15852,7 +15852,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="86" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>319</v>
       </c>
@@ -15983,7 +15983,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="87" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>319</v>
       </c>
@@ -16117,7 +16117,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="88" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>319</v>
       </c>
@@ -16248,7 +16248,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="89" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>319</v>
       </c>
@@ -16379,7 +16379,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="90" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>319</v>
       </c>
@@ -16516,7 +16516,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="91" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>319</v>
       </c>
@@ -16647,7 +16647,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="92" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>366</v>
       </c>
@@ -16778,7 +16778,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="93" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>366</v>
       </c>
@@ -16909,7 +16909,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="94" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>366</v>
       </c>
@@ -17040,7 +17040,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="95" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>366</v>
       </c>
@@ -17174,7 +17174,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="96" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>366</v>
       </c>
@@ -17311,7 +17311,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="97" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>366</v>
       </c>
@@ -17442,7 +17442,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="98" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>366</v>
       </c>
@@ -17573,7 +17573,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="99" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>366</v>
       </c>
@@ -17710,7 +17710,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="100" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>366</v>
       </c>
@@ -17844,7 +17844,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="101" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>366</v>
       </c>
@@ -17978,7 +17978,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="102" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>394</v>
       </c>
@@ -18112,7 +18112,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="103" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>394</v>
       </c>
@@ -18243,7 +18243,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="104" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>394</v>
       </c>
@@ -18377,7 +18377,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="105" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>394</v>
       </c>
@@ -18508,7 +18508,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="106" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>394</v>
       </c>
@@ -18639,7 +18639,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="107" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>394</v>
       </c>
@@ -18770,7 +18770,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="108" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>394</v>
       </c>
@@ -18901,7 +18901,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="109" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>394</v>
       </c>
@@ -19035,7 +19035,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="110" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>394</v>
       </c>
@@ -19169,7 +19169,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="111" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>394</v>
       </c>
@@ -19306,7 +19306,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="112" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>432</v>
       </c>
@@ -19437,7 +19437,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="113" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>432</v>
       </c>
@@ -19568,7 +19568,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="114" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>432</v>
       </c>
@@ -19699,7 +19699,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="115" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>432</v>
       </c>
@@ -19830,7 +19830,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="116" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>432</v>
       </c>
@@ -19961,7 +19961,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="117" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>432</v>
       </c>
@@ -20095,7 +20095,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="118" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>432</v>
       </c>
@@ -20226,7 +20226,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="119" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>432</v>
       </c>
@@ -20363,7 +20363,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="120" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>432</v>
       </c>
@@ -20494,7 +20494,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="121" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>432</v>
       </c>
@@ -20631,7 +20631,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="122" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>466</v>
       </c>
@@ -20765,7 +20765,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="123" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>466</v>
       </c>
@@ -20896,7 +20896,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="124" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>466</v>
       </c>
@@ -21030,7 +21030,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="125" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>466</v>
       </c>
@@ -21161,7 +21161,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="126" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>466</v>
       </c>
@@ -21292,7 +21292,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="127" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>466</v>
       </c>
@@ -21423,7 +21423,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="128" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>466</v>
       </c>
@@ -21557,7 +21557,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="129" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>466</v>
       </c>
@@ -21691,7 +21691,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="130" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>466</v>
       </c>
@@ -21828,7 +21828,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="131" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>466</v>
       </c>
@@ -21959,7 +21959,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="132" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>501</v>
       </c>
@@ -22090,7 +22090,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="133" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>501</v>
       </c>
@@ -22221,7 +22221,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="134" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>501</v>
       </c>
@@ -22352,7 +22352,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="135" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>501</v>
       </c>
@@ -22483,7 +22483,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="136" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>501</v>
       </c>
@@ -22614,7 +22614,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="137" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>501</v>
       </c>
@@ -22745,7 +22745,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="138" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>501</v>
       </c>
@@ -22879,7 +22879,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="139" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>501</v>
       </c>
@@ -23010,7 +23010,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="140" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>501</v>
       </c>
@@ -23141,7 +23141,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="141" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>501</v>
       </c>
@@ -23272,7 +23272,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="142" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>530</v>
       </c>
@@ -23399,7 +23399,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="143" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>530</v>
       </c>
@@ -23530,7 +23530,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="144" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>530</v>
       </c>
@@ -23661,7 +23661,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="145" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>530</v>
       </c>
@@ -23792,7 +23792,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="146" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>530</v>
       </c>
@@ -23923,7 +23923,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="147" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>530</v>
       </c>
@@ -24054,7 +24054,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="148" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>530</v>
       </c>
@@ -24185,7 +24185,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="149" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>530</v>
       </c>
@@ -24313,7 +24313,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="150" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>530</v>
       </c>
@@ -24453,7 +24453,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="151" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>530</v>
       </c>
@@ -24587,7 +24587,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="152" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>562</v>
       </c>
@@ -24716,7 +24716,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="153" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>562</v>
       </c>
@@ -24847,7 +24847,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="154" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>562</v>
       </c>
@@ -24978,7 +24978,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="155" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>562</v>
       </c>
@@ -25109,7 +25109,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="156" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>562</v>
       </c>
@@ -25243,7 +25243,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="157" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>562</v>
       </c>
@@ -25374,7 +25374,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="158" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>562</v>
       </c>
@@ -25505,7 +25505,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="159" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>562</v>
       </c>
@@ -25636,7 +25636,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="160" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>562</v>
       </c>
@@ -25770,7 +25770,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="161" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>562</v>
       </c>
@@ -25901,7 +25901,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="162" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>595</v>
       </c>
@@ -26028,7 +26028,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="163" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>595</v>
       </c>
@@ -26159,7 +26159,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="164" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>595</v>
       </c>
@@ -26290,7 +26290,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="165" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>595</v>
       </c>
@@ -26420,7 +26420,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="166" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>595</v>
       </c>
@@ -26551,7 +26551,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="167" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>595</v>
       </c>
@@ -26680,7 +26680,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="168" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>595</v>
       </c>
@@ -26818,7 +26818,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="169" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>595</v>
       </c>
@@ -26949,7 +26949,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="170" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>595</v>
       </c>
@@ -27086,7 +27086,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="171" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>595</v>
       </c>
@@ -27217,7 +27217,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="172" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>627</v>
       </c>
@@ -27346,7 +27346,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="173" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>627</v>
       </c>
@@ -27480,7 +27480,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="174" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>627</v>
       </c>
@@ -27611,7 +27611,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="175" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>627</v>
       </c>
@@ -27742,7 +27742,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="176" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>627</v>
       </c>
@@ -27873,7 +27873,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="177" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>627</v>
       </c>
@@ -28004,7 +28004,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="178" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>627</v>
       </c>
@@ -28134,7 +28134,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="179" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>627</v>
       </c>
@@ -28265,7 +28265,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="180" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>627</v>
       </c>
@@ -28396,7 +28396,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="181" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>627</v>
       </c>
@@ -28533,7 +28533,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="182" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>658</v>
       </c>
@@ -28660,7 +28660,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="183" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>658</v>
       </c>
@@ -28792,7 +28792,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="184" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>658</v>
       </c>
@@ -28924,7 +28924,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="185" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>658</v>
       </c>
@@ -29053,7 +29053,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="186" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>658</v>
       </c>
@@ -29188,7 +29188,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="187" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>658</v>
       </c>
@@ -29317,7 +29317,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="188" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>658</v>
       </c>
@@ -29449,7 +29449,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="189" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>658</v>
       </c>
@@ -29584,7 +29584,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="190" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>658</v>
       </c>
@@ -29719,7 +29719,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="191" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>658</v>
       </c>
@@ -29854,7 +29854,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="192" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>688</v>
       </c>
@@ -29986,7 +29986,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="193" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>688</v>
       </c>
@@ -30115,7 +30115,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="194" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>688</v>
       </c>
@@ -30247,7 +30247,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="195" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>688</v>
       </c>
@@ -30376,7 +30376,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="196" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>688</v>
       </c>
@@ -30505,7 +30505,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="197" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>688</v>
       </c>
@@ -30634,7 +30634,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="198" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>688</v>
       </c>
@@ -30766,7 +30766,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="199" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>688</v>
       </c>
@@ -30895,7 +30895,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="200" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>688</v>
       </c>
@@ -31025,7 +31025,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="201" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>688</v>
       </c>
@@ -31157,7 +31157,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="202" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>721</v>
       </c>
@@ -31286,7 +31286,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="203" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>721</v>
       </c>
@@ -31415,7 +31415,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="204" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>721</v>
       </c>
@@ -31544,7 +31544,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="205" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>721</v>
       </c>
@@ -31679,7 +31679,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="206" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>721</v>
       </c>
@@ -31814,7 +31814,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="207" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>721</v>
       </c>
@@ -31952,7 +31952,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="208" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>721</v>
       </c>
@@ -32081,7 +32081,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="209" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>721</v>
       </c>
@@ -32216,7 +32216,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="210" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>721</v>
       </c>
@@ -32357,7 +32357,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="211" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>721</v>
       </c>
@@ -32492,7 +32492,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="212" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>756</v>
       </c>
@@ -32621,7 +32621,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="213" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>756</v>
       </c>
@@ -32753,7 +32753,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="214" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>756</v>
       </c>
@@ -32885,7 +32885,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="215" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>756</v>
       </c>
@@ -33014,7 +33014,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="216" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>756</v>
       </c>
@@ -33143,7 +33143,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="217" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>756</v>
       </c>
@@ -33272,7 +33272,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="218" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>756</v>
       </c>
@@ -33416,7 +33416,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="219" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>756</v>
       </c>
@@ -33551,7 +33551,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="220" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>756</v>
       </c>
@@ -33680,7 +33680,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="221" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>756</v>
       </c>
@@ -33809,7 +33809,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="222" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>788</v>
       </c>
@@ -33941,7 +33941,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="223" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>788</v>
       </c>
@@ -34076,7 +34076,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="224" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>788</v>
       </c>
@@ -34211,7 +34211,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="225" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>788</v>
       </c>
@@ -34346,7 +34346,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="226" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>788</v>
       </c>
@@ -34481,7 +34481,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="227" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>788</v>
       </c>
@@ -34610,7 +34610,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="228" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>788</v>
       </c>
@@ -34742,7 +34742,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="229" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>788</v>
       </c>
@@ -34873,7 +34873,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="230" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>788</v>
       </c>
@@ -35016,7 +35016,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="231" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>788</v>
       </c>
@@ -35176,737 +35176,737 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A83FB8B-F526-4731-A8B0-CF3B6BDD1233}">
   <dimension ref="A1:A146"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="125.625" customWidth="1"/>
+    <col min="1" max="1" width="125.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>1090</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>1091</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>1092</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>1093</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>1094</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>1015</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>1017</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>1018</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>1019</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>1023</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>1103</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>1104</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>1036</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>1037</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>1038</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>1039</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>1040</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>1041</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>1042</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>1043</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>1047</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>1105</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>1106</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>1048</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>1049</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>1050</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>1107</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>1051</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>1052</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>1053</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>1054</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>1055</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>1056</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>1057</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>1058</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>1059</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>1060</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>1061</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>1062</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>1063</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>1109</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>1064</v>
       </c>
     </row>
-    <row r="63" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>1065</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>1066</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>1067</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>1068</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>1069</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>1070</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>1071</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>1072</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>954</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>956</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>958</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>960</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>961</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="145" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
         <v>963</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
         <v>866</v>
       </c>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGames\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD18795E-EA5E-465C-8A9F-68F4A57258B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03425AC8-459A-4262-A2FF-6A45B1D5A2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
+      <xlwcv:version warnBelowVersion="2" setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9901" uniqueCount="1302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9916" uniqueCount="1303">
   <si>
     <t>群組ID</t>
   </si>
@@ -4114,10 +4114,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>真空三重奏</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4130,15 +4126,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"chance":15,"chancePer":1.5,"pct":100,"sec":3,"grow":2}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。觸發欄：命中觸發的靜止真空斬只讀本超神地板與命中特效，保持出生位置且按權威半徑成長；普通斬擊不繼承靜止場域。 本列觸發欄留白不播放、不繼承本體或其他事件。可填：觸發命中特效、觸發地板特效。 有傷害範圍時匹配傷害範圍；單體維持原尺寸，不以搜敵距離縮放。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>真空斬命中時有 {chance}% 機率在該處留下一道靜止的真空斬：持續 {sec} 秒、半徑隨時間擴大為 {grow} 倍，對碰到的敵人造成 {pct}% 風系傷害。系統限制：同一個敵人生成的靜止真空斬結束後可再次觸發，全場最多同時存在 15 個靜止真空斬（不包含原本圍繞自身的虛空斬）。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"chance":8,"chancePer":0.8,"pct":100,"sec":3,"grow":2}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>真空斬命中時有 {chance}% 機率在該處留下一道靜止的真空斬，持續 {sec} 秒，對敵人造成 {pct}% 風系傷害，最多同時存在 15 個靜止真空斬。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4610,30 +4614,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACC8F76D-B553-4CF8-BE7D-F03409684AEE}">
-  <dimension ref="A1:AX231"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AY231"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="9.21875" customWidth="1"/>
-    <col min="9" max="9" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="33" width="8.44140625" customWidth="1"/>
-    <col min="34" max="34" width="7.6640625" customWidth="1"/>
-    <col min="35" max="35" width="14.21875" customWidth="1"/>
-    <col min="36" max="37" width="7.6640625" customWidth="1"/>
-    <col min="38" max="38" width="20.44140625" customWidth="1"/>
-    <col min="39" max="39" width="7.6640625" customWidth="1"/>
-    <col min="40" max="44" width="7.6640625" style="1" customWidth="1"/>
-    <col min="45" max="46" width="12.33203125" style="1" customWidth="1"/>
-    <col min="47" max="47" width="48.6640625" customWidth="1"/>
-    <col min="48" max="48" width="12.109375" customWidth="1"/>
-    <col min="49" max="50" width="48.6640625" customWidth="1"/>
+    <col min="6" max="8" width="9.25" customWidth="1"/>
+    <col min="9" max="9" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="33" width="8.5" customWidth="1"/>
+    <col min="34" max="34" width="7.625" customWidth="1"/>
+    <col min="35" max="35" width="14.25" customWidth="1"/>
+    <col min="36" max="37" width="7.625" customWidth="1"/>
+    <col min="38" max="38" width="20.5" customWidth="1"/>
+    <col min="39" max="39" width="7.625" customWidth="1"/>
+    <col min="40" max="44" width="7.625" style="1" customWidth="1"/>
+    <col min="45" max="46" width="12.375" style="1" customWidth="1"/>
+    <col min="47" max="47" width="48.625" customWidth="1"/>
+    <col min="48" max="48" width="12.125" customWidth="1"/>
+    <col min="49" max="50" width="48.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" s="9" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:51" s="9" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -4785,7 +4789,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
@@ -4915,8 +4919,12 @@
       <c r="AX2" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY2">
+        <f>LEN(AW2)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
@@ -5046,8 +5054,12 @@
       <c r="AX3" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY3">
+        <f t="shared" ref="AY3:AY66" si="0">LEN(AW3)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -5177,8 +5189,12 @@
       <c r="AX4" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -5308,8 +5324,12 @@
       <c r="AX5" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -5439,8 +5459,12 @@
       <c r="AX6" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -5570,8 +5594,12 @@
       <c r="AX7" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
@@ -5701,8 +5729,12 @@
       <c r="AX8" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -5835,8 +5867,12 @@
       <c r="AX9" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY9">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -5969,8 +6005,12 @@
       <c r="AX10" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY10">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -6100,8 +6140,12 @@
       <c r="AX11" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY11">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>72</v>
       </c>
@@ -6231,8 +6275,12 @@
       <c r="AX12" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY12">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>72</v>
       </c>
@@ -6362,8 +6410,12 @@
       <c r="AX13" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>72</v>
       </c>
@@ -6493,8 +6545,12 @@
       <c r="AX14" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY14">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>72</v>
       </c>
@@ -6624,8 +6680,12 @@
       <c r="AX15" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY15">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>72</v>
       </c>
@@ -6754,8 +6814,12 @@
       <c r="AX16" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY16">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>72</v>
       </c>
@@ -6881,8 +6945,12 @@
       <c r="AX17" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY17">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>72</v>
       </c>
@@ -7008,8 +7076,12 @@
       <c r="AX18" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY18">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>72</v>
       </c>
@@ -7133,8 +7205,12 @@
       <c r="AX19" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="20" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY19">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>72</v>
       </c>
@@ -7261,8 +7337,12 @@
       <c r="AX20" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="21" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY20">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>72</v>
       </c>
@@ -7392,8 +7472,12 @@
       <c r="AX21" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY21">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>108</v>
       </c>
@@ -7523,8 +7607,12 @@
       <c r="AX22" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY22">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>108</v>
       </c>
@@ -7654,8 +7742,12 @@
       <c r="AX23" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY23">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>108</v>
       </c>
@@ -7785,8 +7877,12 @@
       <c r="AX24" s="1" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY24">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>108</v>
       </c>
@@ -7916,8 +8012,12 @@
       <c r="AX25" s="1" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY25">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>108</v>
       </c>
@@ -8047,8 +8147,12 @@
       <c r="AX26" s="1" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY26">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>108</v>
       </c>
@@ -8178,8 +8282,12 @@
       <c r="AX27" s="1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY27">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>108</v>
       </c>
@@ -8309,8 +8417,12 @@
       <c r="AX28" s="1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY28">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>108</v>
       </c>
@@ -8440,8 +8552,12 @@
       <c r="AX29" s="1" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY29">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>108</v>
       </c>
@@ -8574,8 +8690,12 @@
       <c r="AX30" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY30">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>108</v>
       </c>
@@ -8705,8 +8825,12 @@
       <c r="AX31" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY31">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>149</v>
       </c>
@@ -8836,8 +8960,12 @@
       <c r="AX32" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY32">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>149</v>
       </c>
@@ -8967,8 +9095,12 @@
       <c r="AX33" s="1" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="34" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY33">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>149</v>
       </c>
@@ -9098,8 +9230,12 @@
       <c r="AX34" s="1" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY34">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>149</v>
       </c>
@@ -9229,8 +9365,12 @@
       <c r="AX35" s="1" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY35">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>149</v>
       </c>
@@ -9363,8 +9503,12 @@
       <c r="AX36" s="1" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY36">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>149</v>
       </c>
@@ -9494,8 +9638,12 @@
       <c r="AX37" s="1" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY37">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>149</v>
       </c>
@@ -9625,8 +9773,12 @@
       <c r="AX38" s="1" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY38">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>149</v>
       </c>
@@ -9759,8 +9911,12 @@
       <c r="AX39" s="1" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="40" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY39">
+        <f t="shared" si="0"/>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>149</v>
       </c>
@@ -9893,8 +10049,12 @@
       <c r="AX40" s="1" t="s">
         <v>928</v>
       </c>
-    </row>
-    <row r="41" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY40">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>149</v>
       </c>
@@ -10024,8 +10184,12 @@
       <c r="AX41" s="1" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="42" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY41">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>189</v>
       </c>
@@ -10156,8 +10320,12 @@
       <c r="AX42" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="43" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY42">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>189</v>
       </c>
@@ -10283,8 +10451,12 @@
       <c r="AX43" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="44" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY43">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>189</v>
       </c>
@@ -10414,8 +10586,12 @@
       <c r="AX44" s="1" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="45" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY44">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>189</v>
       </c>
@@ -10546,8 +10722,12 @@
       <c r="AX45" s="1" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="46" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY45">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>968</v>
       </c>
@@ -10683,8 +10863,12 @@
       <c r="AX46" s="1" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="47" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY46">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>189</v>
       </c>
@@ -10813,8 +10997,12 @@
       <c r="AX47" s="1" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="48" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY47">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>189</v>
       </c>
@@ -10942,8 +11130,12 @@
       <c r="AX48" s="1" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="49" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY48">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>189</v>
       </c>
@@ -11077,8 +11269,12 @@
       <c r="AX49" s="1" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="50" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY49">
+        <f t="shared" si="0"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>189</v>
       </c>
@@ -11216,8 +11412,12 @@
       <c r="AX50" s="1" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="51" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY50">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>189</v>
       </c>
@@ -11351,8 +11551,12 @@
       <c r="AX51" s="1" t="s">
         <v>967</v>
       </c>
-    </row>
-    <row r="52" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY51">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>226</v>
       </c>
@@ -11478,8 +11682,12 @@
       <c r="AX52" s="1" t="s">
         <v>1120</v>
       </c>
-    </row>
-    <row r="53" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY52">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>226</v>
       </c>
@@ -11607,8 +11815,12 @@
       <c r="AX53" s="1" t="s">
         <v>1121</v>
       </c>
-    </row>
-    <row r="54" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY53">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>226</v>
       </c>
@@ -11736,8 +11948,12 @@
       <c r="AX54" s="1" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="55" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY54">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>226</v>
       </c>
@@ -11870,8 +12086,12 @@
       <c r="AX55" s="1" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="56" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY55">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>226</v>
       </c>
@@ -12007,8 +12227,12 @@
       <c r="AX56" s="1" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="57" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY56">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>226</v>
       </c>
@@ -12138,8 +12362,12 @@
       <c r="AX57" s="1" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="58" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY57">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>226</v>
       </c>
@@ -12270,8 +12498,12 @@
       <c r="AX58" s="1" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="59" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY58">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>226</v>
       </c>
@@ -12401,8 +12633,12 @@
       <c r="AX59" s="1" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="60" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY59">
+        <f t="shared" si="0"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="60" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>226</v>
       </c>
@@ -12535,8 +12771,12 @@
       <c r="AX60" s="1" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="61" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY60">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>226</v>
       </c>
@@ -12666,8 +12906,12 @@
       <c r="AX61" s="1" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="62" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY61">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>254</v>
       </c>
@@ -12797,8 +13041,12 @@
       <c r="AX62" s="1" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="63" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY62">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>254</v>
       </c>
@@ -12928,8 +13176,12 @@
       <c r="AX63" s="1" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="64" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY63">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>254</v>
       </c>
@@ -13059,8 +13311,12 @@
       <c r="AX64" s="1" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="65" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY64">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>254</v>
       </c>
@@ -13190,8 +13446,12 @@
       <c r="AX65" s="1" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="66" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY65">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>254</v>
       </c>
@@ -13324,8 +13584,12 @@
       <c r="AX66" s="1" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="67" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY66">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>254</v>
       </c>
@@ -13455,8 +13719,12 @@
       <c r="AX67" s="1" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="68" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY67">
+        <f t="shared" ref="AY67:AY130" si="1">LEN(AW67)</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>254</v>
       </c>
@@ -13586,8 +13854,12 @@
       <c r="AX68" s="1" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="69" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY68">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="69" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>254</v>
       </c>
@@ -13723,8 +13995,12 @@
       <c r="AX69" s="1" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="70" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY69">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="70" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>254</v>
       </c>
@@ -13858,8 +14134,12 @@
       <c r="AX70" s="1" t="s">
         <v>1134</v>
       </c>
-    </row>
-    <row r="71" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY70">
+        <f t="shared" si="1"/>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>254</v>
       </c>
@@ -13989,8 +14269,12 @@
       <c r="AX71" s="1" t="s">
         <v>1131</v>
       </c>
-    </row>
-    <row r="72" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY71">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="72" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>289</v>
       </c>
@@ -14126,8 +14410,12 @@
       <c r="AX72" s="1" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="73" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY72">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>289</v>
       </c>
@@ -14257,8 +14545,12 @@
       <c r="AX73" s="1" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="74" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY73">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>289</v>
       </c>
@@ -14388,8 +14680,12 @@
       <c r="AX74" s="1" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="75" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY74">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>289</v>
       </c>
@@ -14519,8 +14815,12 @@
       <c r="AX75" s="1" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="76" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY75">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="76" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>289</v>
       </c>
@@ -14650,8 +14950,12 @@
       <c r="AX76" s="1" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="77" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY76">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>289</v>
       </c>
@@ -14781,8 +15085,12 @@
       <c r="AX77" s="1" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="78" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY77">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="78" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>289</v>
       </c>
@@ -14916,8 +15224,12 @@
       <c r="AX78" s="1" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="79" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY78">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="79" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>289</v>
       </c>
@@ -15050,8 +15362,12 @@
       <c r="AX79" s="1" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="80" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY79">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="80" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>289</v>
       </c>
@@ -15187,8 +15503,12 @@
       <c r="AX80" s="1" t="s">
         <v>1137</v>
       </c>
-    </row>
-    <row r="81" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY80">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="81" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>289</v>
       </c>
@@ -15324,8 +15644,12 @@
       <c r="AX81" s="1" t="s">
         <v>1139</v>
       </c>
-    </row>
-    <row r="82" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY81">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="82" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>319</v>
       </c>
@@ -15455,8 +15779,12 @@
       <c r="AX82" s="1" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="83" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY82">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="83" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>319</v>
       </c>
@@ -15589,8 +15917,12 @@
       <c r="AX83" s="1" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="84" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY83">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>319</v>
       </c>
@@ -15720,8 +16052,12 @@
       <c r="AX84" s="1" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="85" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY84">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="85" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>319</v>
       </c>
@@ -15851,8 +16187,12 @@
       <c r="AX85" s="1" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="86" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY85">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>319</v>
       </c>
@@ -15982,8 +16322,12 @@
       <c r="AX86" s="1" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="87" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY86">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="87" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>319</v>
       </c>
@@ -16116,8 +16460,12 @@
       <c r="AX87" s="1" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="88" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY87">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>319</v>
       </c>
@@ -16247,8 +16595,12 @@
       <c r="AX88" s="1" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="89" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY88">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="89" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>319</v>
       </c>
@@ -16378,8 +16730,12 @@
       <c r="AX89" s="1" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="90" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY89">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="90" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>319</v>
       </c>
@@ -16515,8 +16871,12 @@
       <c r="AX90" s="1" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="91" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY90">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="91" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>319</v>
       </c>
@@ -16646,8 +17006,12 @@
       <c r="AX91" s="1" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="92" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY91">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>366</v>
       </c>
@@ -16777,8 +17141,12 @@
       <c r="AX92" s="1" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="93" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY92">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="93" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>366</v>
       </c>
@@ -16908,8 +17276,12 @@
       <c r="AX93" s="1" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="94" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY93">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>366</v>
       </c>
@@ -17039,8 +17411,12 @@
       <c r="AX94" s="1" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="95" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY94">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="95" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>366</v>
       </c>
@@ -17173,8 +17549,12 @@
       <c r="AX95" s="1" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="96" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY95">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="96" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>366</v>
       </c>
@@ -17310,8 +17690,12 @@
       <c r="AX96" s="1" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="97" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY96">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="97" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>366</v>
       </c>
@@ -17441,8 +17825,12 @@
       <c r="AX97" s="1" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="98" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY97">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="98" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>366</v>
       </c>
@@ -17572,8 +17960,12 @@
       <c r="AX98" s="1" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="99" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY98">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="99" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>366</v>
       </c>
@@ -17709,8 +18101,12 @@
       <c r="AX99" s="1" t="s">
         <v>1167</v>
       </c>
-    </row>
-    <row r="100" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY99">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="100" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>366</v>
       </c>
@@ -17843,8 +18239,12 @@
       <c r="AX100" s="1" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="101" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY100">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="101" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>366</v>
       </c>
@@ -17977,8 +18377,12 @@
       <c r="AX101" s="1" t="s">
         <v>1161</v>
       </c>
-    </row>
-    <row r="102" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY101">
+        <f t="shared" si="1"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="102" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>394</v>
       </c>
@@ -18111,8 +18515,12 @@
       <c r="AX102" s="1" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="103" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY102">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="103" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>394</v>
       </c>
@@ -18242,8 +18650,12 @@
       <c r="AX103" s="1" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="104" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY103">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="104" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>394</v>
       </c>
@@ -18376,8 +18788,12 @@
       <c r="AX104" s="1" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="105" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY104">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="105" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>394</v>
       </c>
@@ -18507,8 +18923,12 @@
       <c r="AX105" s="1" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="106" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY105">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="106" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>394</v>
       </c>
@@ -18638,8 +19058,12 @@
       <c r="AX106" s="1" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="107" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY106">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>394</v>
       </c>
@@ -18769,8 +19193,12 @@
       <c r="AX107" s="1" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="108" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY107">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="108" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>394</v>
       </c>
@@ -18900,8 +19328,12 @@
       <c r="AX108" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="109" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY108">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="109" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>394</v>
       </c>
@@ -19034,8 +19466,12 @@
       <c r="AX109" s="1" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="110" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY109">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="110" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>394</v>
       </c>
@@ -19168,8 +19604,12 @@
       <c r="AX110" s="1" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="111" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY110">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="111" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>394</v>
       </c>
@@ -19305,8 +19745,12 @@
       <c r="AX111" s="1" t="s">
         <v>1168</v>
       </c>
-    </row>
-    <row r="112" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY111">
+        <f t="shared" si="1"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="112" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>432</v>
       </c>
@@ -19436,8 +19880,12 @@
       <c r="AX112" s="1" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="113" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY112">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="113" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>432</v>
       </c>
@@ -19567,8 +20015,12 @@
       <c r="AX113" s="1" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="114" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY113">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="114" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>432</v>
       </c>
@@ -19698,8 +20150,12 @@
       <c r="AX114" s="1" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="115" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY114">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="115" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>432</v>
       </c>
@@ -19829,8 +20285,12 @@
       <c r="AX115" s="1" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="116" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY115">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="116" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>432</v>
       </c>
@@ -19960,8 +20420,12 @@
       <c r="AX116" s="1" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="117" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY116">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="117" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>432</v>
       </c>
@@ -20094,8 +20558,12 @@
       <c r="AX117" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="118" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY117">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="118" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>432</v>
       </c>
@@ -20225,8 +20693,12 @@
       <c r="AX118" s="1" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="119" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY118">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="119" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>432</v>
       </c>
@@ -20362,8 +20834,12 @@
       <c r="AX119" s="1" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="120" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY119">
+        <f t="shared" si="1"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="120" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>432</v>
       </c>
@@ -20493,8 +20969,12 @@
       <c r="AX120" s="1" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="121" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY120">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="121" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>432</v>
       </c>
@@ -20630,8 +21110,12 @@
       <c r="AX121" s="1" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="122" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY121">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="122" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>466</v>
       </c>
@@ -20764,8 +21248,12 @@
       <c r="AX122" s="1" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="123" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY122">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="123" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>466</v>
       </c>
@@ -20895,8 +21383,12 @@
       <c r="AX123" s="1" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="124" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY123">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="124" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>466</v>
       </c>
@@ -21029,8 +21521,12 @@
       <c r="AX124" s="1" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="125" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY124">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="125" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>466</v>
       </c>
@@ -21160,8 +21656,12 @@
       <c r="AX125" s="1" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="126" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY125">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="126" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>466</v>
       </c>
@@ -21291,8 +21791,12 @@
       <c r="AX126" s="1" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="127" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY126">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="127" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>466</v>
       </c>
@@ -21422,8 +21926,12 @@
       <c r="AX127" s="1" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="128" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY127">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="128" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>466</v>
       </c>
@@ -21556,8 +22064,12 @@
       <c r="AX128" s="1" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="129" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY128">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="129" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>466</v>
       </c>
@@ -21690,8 +22202,12 @@
       <c r="AX129" s="1" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="130" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY129">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="130" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>466</v>
       </c>
@@ -21827,8 +22343,12 @@
       <c r="AX130" s="1" t="s">
         <v>1187</v>
       </c>
-    </row>
-    <row r="131" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY130">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="131" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>466</v>
       </c>
@@ -21958,8 +22478,12 @@
       <c r="AX131" s="1" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="132" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY131">
+        <f t="shared" ref="AY131:AY194" si="2">LEN(AW131)</f>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="132" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>501</v>
       </c>
@@ -22089,8 +22613,12 @@
       <c r="AX132" s="1" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="133" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY132">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="133" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>501</v>
       </c>
@@ -22220,8 +22748,12 @@
       <c r="AX133" s="1" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="134" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY133">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="134" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>501</v>
       </c>
@@ -22351,8 +22883,12 @@
       <c r="AX134" s="1" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="135" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY134">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="135" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>501</v>
       </c>
@@ -22482,8 +23018,12 @@
       <c r="AX135" s="1" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="136" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY135">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="136" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>501</v>
       </c>
@@ -22613,8 +23153,12 @@
       <c r="AX136" s="1" t="s">
         <v>1263</v>
       </c>
-    </row>
-    <row r="137" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY136">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="137" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>501</v>
       </c>
@@ -22744,8 +23288,12 @@
       <c r="AX137" s="1" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="138" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY137">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="138" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>501</v>
       </c>
@@ -22878,8 +23426,12 @@
       <c r="AX138" s="1" t="s">
         <v>1195</v>
       </c>
-    </row>
-    <row r="139" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY138">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="139" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>501</v>
       </c>
@@ -23009,8 +23561,12 @@
       <c r="AX139" s="1" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="140" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY139">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="140" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>501</v>
       </c>
@@ -23140,8 +23696,12 @@
       <c r="AX140" s="1" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="141" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY140">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="141" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>501</v>
       </c>
@@ -23271,8 +23831,12 @@
       <c r="AX141" s="1" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="142" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY141">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="142" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>530</v>
       </c>
@@ -23398,8 +23962,12 @@
       <c r="AX142" s="1" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="143" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY142">
+        <f t="shared" si="2"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="143" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>530</v>
       </c>
@@ -23529,8 +24097,12 @@
       <c r="AX143" s="1" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="144" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY143">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="144" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>530</v>
       </c>
@@ -23660,8 +24232,12 @@
       <c r="AX144" s="1" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="145" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY144">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="145" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>530</v>
       </c>
@@ -23791,8 +24367,12 @@
       <c r="AX145" s="1" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="146" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY145">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="146" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>530</v>
       </c>
@@ -23922,8 +24502,12 @@
       <c r="AX146" s="1" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="147" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY146">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="147" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>530</v>
       </c>
@@ -24053,8 +24637,12 @@
       <c r="AX147" s="1" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="148" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY147">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="148" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>530</v>
       </c>
@@ -24184,8 +24772,12 @@
       <c r="AX148" s="1" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="149" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY148">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="149" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>530</v>
       </c>
@@ -24312,8 +24904,12 @@
       <c r="AX149" s="1" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="150" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY149">
+        <f t="shared" si="2"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="150" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>530</v>
       </c>
@@ -24452,8 +25048,12 @@
       <c r="AX150" s="1" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="151" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY150">
+        <f t="shared" si="2"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="151" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>530</v>
       </c>
@@ -24586,8 +25186,12 @@
       <c r="AX151" s="1" t="s">
         <v>1210</v>
       </c>
-    </row>
-    <row r="152" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY151">
+        <f t="shared" si="2"/>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="152" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>562</v>
       </c>
@@ -24715,8 +25319,12 @@
       <c r="AX152" s="1" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="153" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY152">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="153" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>562</v>
       </c>
@@ -24846,8 +25454,12 @@
       <c r="AX153" s="1" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="154" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY153">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="154" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>562</v>
       </c>
@@ -24977,8 +25589,12 @@
       <c r="AX154" s="1" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="155" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY154">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="155" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>562</v>
       </c>
@@ -25108,8 +25724,12 @@
       <c r="AX155" s="1" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="156" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY155">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="156" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>562</v>
       </c>
@@ -25242,8 +25862,12 @@
       <c r="AX156" s="1" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="157" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY156">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="157" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>562</v>
       </c>
@@ -25373,8 +25997,12 @@
       <c r="AX157" s="1" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="158" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY157">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="158" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>562</v>
       </c>
@@ -25504,8 +26132,12 @@
       <c r="AX158" s="1" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="159" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY158">
+        <f t="shared" si="2"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="159" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>562</v>
       </c>
@@ -25635,8 +26267,12 @@
       <c r="AX159" s="1" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="160" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY159">
+        <f t="shared" si="2"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="160" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>562</v>
       </c>
@@ -25769,8 +26405,12 @@
       <c r="AX160" s="1" t="s">
         <v>1216</v>
       </c>
-    </row>
-    <row r="161" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY160">
+        <f t="shared" si="2"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="161" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>562</v>
       </c>
@@ -25900,8 +26540,12 @@
       <c r="AX161" s="1" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="162" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY161">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="162" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>595</v>
       </c>
@@ -26027,8 +26671,12 @@
       <c r="AX162" s="1" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="163" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY162">
+        <f t="shared" si="2"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="163" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>595</v>
       </c>
@@ -26158,8 +26806,12 @@
       <c r="AX163" s="1" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="164" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY163">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="164" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>595</v>
       </c>
@@ -26289,8 +26941,12 @@
       <c r="AX164" s="1" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="165" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY164">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="165" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>595</v>
       </c>
@@ -26419,8 +27075,12 @@
       <c r="AX165" s="1" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="166" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY165">
+        <f t="shared" si="2"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="166" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>595</v>
       </c>
@@ -26550,8 +27210,12 @@
       <c r="AX166" s="1" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="167" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY166">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="167" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>595</v>
       </c>
@@ -26679,8 +27343,12 @@
       <c r="AX167" s="1" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="168" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY167">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="168" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>595</v>
       </c>
@@ -26817,8 +27485,12 @@
       <c r="AX168" s="1" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="169" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY168">
+        <f t="shared" si="2"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="169" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>595</v>
       </c>
@@ -26948,8 +27620,12 @@
       <c r="AX169" s="1" t="s">
         <v>1234</v>
       </c>
-    </row>
-    <row r="170" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY169">
+        <f t="shared" si="2"/>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="170" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>595</v>
       </c>
@@ -27085,8 +27761,12 @@
       <c r="AX170" s="1" t="s">
         <v>1219</v>
       </c>
-    </row>
-    <row r="171" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY170">
+        <f t="shared" si="2"/>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="171" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>595</v>
       </c>
@@ -27216,8 +27896,12 @@
       <c r="AX171" s="1" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="172" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY171">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="172" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>627</v>
       </c>
@@ -27345,8 +28029,12 @@
       <c r="AX172" s="1" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="173" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY172">
+        <f t="shared" si="2"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="173" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>627</v>
       </c>
@@ -27479,8 +28167,12 @@
       <c r="AX173" s="1" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="174" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY173">
+        <f t="shared" si="2"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="174" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>627</v>
       </c>
@@ -27610,8 +28302,12 @@
       <c r="AX174" s="1" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="175" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY174">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="175" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>627</v>
       </c>
@@ -27741,8 +28437,12 @@
       <c r="AX175" s="1" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="176" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY175">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="176" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>627</v>
       </c>
@@ -27872,8 +28572,12 @@
       <c r="AX176" s="1" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="177" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY176">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="177" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>627</v>
       </c>
@@ -28003,8 +28707,12 @@
       <c r="AX177" s="1" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="178" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY177">
+        <f t="shared" si="2"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="178" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>627</v>
       </c>
@@ -28133,8 +28841,12 @@
       <c r="AX178" s="1" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="179" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY178">
+        <f t="shared" si="2"/>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="179" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>627</v>
       </c>
@@ -28264,8 +28976,12 @@
       <c r="AX179" s="1" t="s">
         <v>1256</v>
       </c>
-    </row>
-    <row r="180" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY179">
+        <f t="shared" si="2"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="180" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>627</v>
       </c>
@@ -28395,8 +29111,12 @@
       <c r="AX180" s="1" t="s">
         <v>1255</v>
       </c>
-    </row>
-    <row r="181" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY180">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="181" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>627</v>
       </c>
@@ -28532,8 +29252,12 @@
       <c r="AX181" s="1" t="s">
         <v>1250</v>
       </c>
-    </row>
-    <row r="182" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY181">
+        <f t="shared" si="2"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="182" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>658</v>
       </c>
@@ -28659,8 +29383,12 @@
       <c r="AX182" s="1" t="s">
         <v>1260</v>
       </c>
-    </row>
-    <row r="183" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY182">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="183" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>658</v>
       </c>
@@ -28791,8 +29519,12 @@
       <c r="AX183" s="1" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="184" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY183">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="184" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>658</v>
       </c>
@@ -28923,8 +29655,12 @@
       <c r="AX184" s="1" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="185" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY184">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="185" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>658</v>
       </c>
@@ -29052,8 +29788,12 @@
       <c r="AX185" s="1" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="186" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY185">
+        <f t="shared" si="2"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="186" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>658</v>
       </c>
@@ -29187,8 +29927,12 @@
       <c r="AX186" s="1" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="187" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY186">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="187" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>658</v>
       </c>
@@ -29316,8 +30060,12 @@
       <c r="AX187" s="1" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="188" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY187">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="188" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>658</v>
       </c>
@@ -29448,8 +30196,12 @@
       <c r="AX188" s="1" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="189" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY188">
+        <f t="shared" si="2"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="189" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>658</v>
       </c>
@@ -29583,8 +30335,12 @@
       <c r="AX189" s="1" t="s">
         <v>1259</v>
       </c>
-    </row>
-    <row r="190" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY189">
+        <f t="shared" si="2"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="190" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>658</v>
       </c>
@@ -29718,8 +30474,12 @@
       <c r="AX190" s="1" t="s">
         <v>1268</v>
       </c>
-    </row>
-    <row r="191" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY190">
+        <f t="shared" si="2"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="191" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>658</v>
       </c>
@@ -29853,8 +30613,12 @@
       <c r="AX191" s="1" t="s">
         <v>1267</v>
       </c>
-    </row>
-    <row r="192" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY191">
+        <f t="shared" si="2"/>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="192" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>688</v>
       </c>
@@ -29985,8 +30749,12 @@
       <c r="AX192" s="1" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="193" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY192">
+        <f t="shared" si="2"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="193" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>688</v>
       </c>
@@ -30114,8 +30882,12 @@
       <c r="AX193" s="1" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="194" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY193">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="194" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>688</v>
       </c>
@@ -30246,8 +31018,12 @@
       <c r="AX194" s="1" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="195" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY194">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="195" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>688</v>
       </c>
@@ -30375,8 +31151,12 @@
       <c r="AX195" s="1" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="196" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY195">
+        <f t="shared" ref="AY195:AY231" si="3">LEN(AW195)</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="196" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>688</v>
       </c>
@@ -30504,8 +31284,12 @@
       <c r="AX196" s="1" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="197" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY196">
+        <f t="shared" si="3"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="197" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>688</v>
       </c>
@@ -30633,8 +31417,12 @@
       <c r="AX197" s="1" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="198" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY197">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="198" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>688</v>
       </c>
@@ -30765,8 +31553,12 @@
       <c r="AX198" s="1" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="199" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY198">
+        <f t="shared" si="3"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="199" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>688</v>
       </c>
@@ -30894,8 +31686,12 @@
       <c r="AX199" s="1" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="200" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY199">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="200" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>688</v>
       </c>
@@ -31024,8 +31820,12 @@
       <c r="AX200" s="1" t="s">
         <v>1277</v>
       </c>
-    </row>
-    <row r="201" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY200">
+        <f t="shared" si="3"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="201" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>688</v>
       </c>
@@ -31156,8 +31956,12 @@
       <c r="AX201" s="1" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="202" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY201">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="202" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>721</v>
       </c>
@@ -31285,8 +32089,12 @@
       <c r="AX202" s="1" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="203" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY202">
+        <f t="shared" si="3"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="203" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>721</v>
       </c>
@@ -31414,8 +32222,12 @@
       <c r="AX203" s="1" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="204" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY203">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="204" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>721</v>
       </c>
@@ -31543,8 +32355,12 @@
       <c r="AX204" s="1" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="205" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY204">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="205" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>721</v>
       </c>
@@ -31678,8 +32494,12 @@
       <c r="AX205" s="1" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="206" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY205">
+        <f t="shared" si="3"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="206" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>721</v>
       </c>
@@ -31813,8 +32633,12 @@
       <c r="AX206" s="1" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="207" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY206">
+        <f t="shared" si="3"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="207" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>721</v>
       </c>
@@ -31951,8 +32775,12 @@
       <c r="AX207" s="1" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="208" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY207">
+        <f t="shared" si="3"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="208" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>721</v>
       </c>
@@ -32080,8 +32908,12 @@
       <c r="AX208" s="1" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="209" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY208">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="209" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>721</v>
       </c>
@@ -32215,8 +33047,12 @@
       <c r="AX209" s="1" t="s">
         <v>1287</v>
       </c>
-    </row>
-    <row r="210" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY209">
+        <f t="shared" si="3"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="210" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>721</v>
       </c>
@@ -32356,8 +33192,12 @@
       <c r="AX210" s="1" t="s">
         <v>1289</v>
       </c>
-    </row>
-    <row r="211" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY210">
+        <f t="shared" si="3"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="211" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>721</v>
       </c>
@@ -32491,8 +33331,12 @@
       <c r="AX211" s="1" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="212" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY211">
+        <f t="shared" si="3"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="212" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>756</v>
       </c>
@@ -32620,8 +33464,12 @@
       <c r="AX212" s="1" t="s">
         <v>760</v>
       </c>
-    </row>
-    <row r="213" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY212">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="213" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>756</v>
       </c>
@@ -32752,8 +33600,12 @@
       <c r="AX213" s="1" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="214" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY213">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="214" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>756</v>
       </c>
@@ -32884,8 +33736,12 @@
       <c r="AX214" s="1" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="215" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY214">
+        <f t="shared" si="3"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="215" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>756</v>
       </c>
@@ -33013,8 +33869,12 @@
       <c r="AX215" s="1" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="216" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY215">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="216" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>756</v>
       </c>
@@ -33022,7 +33882,7 @@
         <v>757</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>758</v>
@@ -33085,7 +33945,7 @@
         <v>886</v>
       </c>
       <c r="X216" s="1" t="s">
-        <v>1295</v>
+        <v>1302</v>
       </c>
       <c r="Y216" s="1" t="s">
         <v>886</v>
@@ -33142,8 +34002,12 @@
       <c r="AX216" s="1" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="217" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY216">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="217" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>756</v>
       </c>
@@ -33271,8 +34135,12 @@
       <c r="AX217" s="1" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="218" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY217">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="218" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>756</v>
       </c>
@@ -33328,7 +34196,7 @@
         <v>886</v>
       </c>
       <c r="S218" s="3" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="T218" s="1" t="s">
         <v>904</v>
@@ -33415,8 +34283,12 @@
       <c r="AX218" s="1" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="219" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY218">
+        <f t="shared" si="3"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="219" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>756</v>
       </c>
@@ -33536,22 +34408,26 @@
         <v>727</v>
       </c>
       <c r="AQ219" s="1" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="AU219" s="1" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="AV219" s="1" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="AW219" s="1" t="s">
         <v>1301</v>
       </c>
       <c r="AX219" s="1" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="220" spans="1:50" x14ac:dyDescent="0.3">
+        <v>1299</v>
+      </c>
+      <c r="AY219">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="220" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>756</v>
       </c>
@@ -33679,8 +34555,12 @@
       <c r="AX220" s="1" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="221" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY220">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="221" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>756</v>
       </c>
@@ -33808,8 +34688,12 @@
       <c r="AX221" s="1" t="s">
         <v>787</v>
       </c>
-    </row>
-    <row r="222" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY221">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="222" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>788</v>
       </c>
@@ -33940,8 +34824,12 @@
       <c r="AX222" s="1" t="s">
         <v>792</v>
       </c>
-    </row>
-    <row r="223" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY222">
+        <f t="shared" si="3"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="223" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>788</v>
       </c>
@@ -34075,8 +34963,12 @@
       <c r="AX223" s="1" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="224" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY223">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="224" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>788</v>
       </c>
@@ -34210,8 +35102,12 @@
       <c r="AX224" s="1" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="225" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY224">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="225" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>788</v>
       </c>
@@ -34345,8 +35241,12 @@
       <c r="AX225" s="1" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="226" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY225">
+        <f t="shared" si="3"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="226" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>788</v>
       </c>
@@ -34480,8 +35380,12 @@
       <c r="AX226" s="1" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="227" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY226">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="227" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>788</v>
       </c>
@@ -34609,8 +35513,12 @@
       <c r="AX227" s="1" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="228" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY227">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="228" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>788</v>
       </c>
@@ -34741,8 +35649,12 @@
       <c r="AX228" s="1" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="229" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY228">
+        <f t="shared" si="3"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="229" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>788</v>
       </c>
@@ -34872,8 +35784,12 @@
       <c r="AX229" s="1" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="230" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY229">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="230" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>788</v>
       </c>
@@ -35015,8 +35931,12 @@
       <c r="AX230" s="1" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="231" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="AY230">
+        <f t="shared" si="3"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="231" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>788</v>
       </c>
@@ -35157,12 +36077,16 @@
       </c>
       <c r="AX231" s="1" t="s">
         <v>821</v>
+      </c>
+      <c r="AY231">
+        <f t="shared" si="3"/>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AX231" xr:uid="{ACC8F76D-B553-4CF8-BE7D-F03409684AEE}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="施法消耗" error="請輸入大於或等於 0 的數字，或留白。" sqref="M2:M231" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0</formula1>
     </dataValidation>
@@ -35176,737 +36100,737 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A83FB8B-F526-4731-A8B0-CF3B6BDD1233}">
   <dimension ref="A1:A146"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="125.6640625" customWidth="1"/>
+    <col min="1" max="1" width="125.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>1090</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>1091</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>1092</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>1093</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>1094</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>1015</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>1017</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>1018</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>1019</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>1023</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>1103</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>1104</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>1036</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>1037</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>1038</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>1039</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>1040</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>1041</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>1042</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>1043</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>1047</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>1105</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>1106</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>1048</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>1049</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>1050</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>1107</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>1051</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>1052</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>1053</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>1054</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>1055</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>1056</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>1057</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>1058</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>1059</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>1060</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>1061</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>1062</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>1063</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>1109</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>1064</v>
       </c>
     </row>
-    <row r="63" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>1065</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>1066</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>1067</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>1068</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>1069</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>1070</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>1071</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
         <v>1072</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
         <v>954</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="77" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
         <v>956</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>958</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>960</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>961</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="145" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
         <v>963</v>
       </c>
     </row>
-    <row r="146" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
         <v>866</v>
       </c>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03425AC8-459A-4262-A2FF-6A45B1D5A2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBDEFA5-3344-4CD1-8BF4-A70EF63187DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9916" uniqueCount="1303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9746" uniqueCount="1300">
   <si>
     <t>群組ID</t>
   </si>
@@ -2854,9 +2854,6 @@
   </si>
   <si>
     <t>0.5</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>65.52</t>
@@ -3732,10 +3729,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>bolt-chain-travel-bluewhite</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3944,10 +3937,6 @@
   </si>
   <si>
     <t>{"pct":300,"pctPer":30,"sec":3,"waves":3,"waveGap":0.3}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>18</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -4226,7 +4215,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4265,6 +4254,9 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4756,31 +4748,31 @@
         <v>17</v>
       </c>
       <c r="AN1" s="8" t="s">
+        <v>1072</v>
+      </c>
+      <c r="AO1" s="8" t="s">
         <v>1073</v>
       </c>
-      <c r="AO1" s="8" t="s">
+      <c r="AP1" s="8" t="s">
         <v>1074</v>
       </c>
-      <c r="AP1" s="8" t="s">
+      <c r="AQ1" s="8" t="s">
         <v>1075</v>
       </c>
-      <c r="AQ1" s="8" t="s">
+      <c r="AR1" s="8" t="s">
         <v>1076</v>
       </c>
-      <c r="AR1" s="8" t="s">
-        <v>1077</v>
-      </c>
       <c r="AS1" s="10" t="s">
+        <v>972</v>
+      </c>
+      <c r="AT1" s="10" t="s">
         <v>973</v>
-      </c>
-      <c r="AT1" s="10" t="s">
-        <v>974</v>
       </c>
       <c r="AU1" s="8" t="s">
         <v>18</v>
       </c>
       <c r="AV1" s="8" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AW1" s="8" t="s">
         <v>21</v>
@@ -4823,8 +4815,8 @@
       <c r="K2" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>888</v>
+      <c r="L2" s="13">
+        <v>8</v>
       </c>
       <c r="M2">
         <v>25</v>
@@ -4911,7 +4903,7 @@
         <v>31</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW2" s="1" t="s">
         <v>32</v>
@@ -4958,8 +4950,8 @@
       <c r="K3" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>888</v>
+      <c r="L3" s="13">
+        <v>8</v>
       </c>
       <c r="M3">
         <v>50</v>
@@ -5046,7 +5038,7 @@
         <v>34</v>
       </c>
       <c r="AV3" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW3" s="1" t="s">
         <v>35</v>
@@ -5093,8 +5085,8 @@
       <c r="K4" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>888</v>
+      <c r="L4" s="13">
+        <v>8</v>
       </c>
       <c r="M4">
         <v>100</v>
@@ -5181,7 +5173,7 @@
         <v>39</v>
       </c>
       <c r="AV4" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW4" s="1" t="s">
         <v>40</v>
@@ -5228,8 +5220,8 @@
       <c r="K5" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>888</v>
+      <c r="L5" s="13">
+        <v>8</v>
       </c>
       <c r="M5">
         <v>200</v>
@@ -5316,7 +5308,7 @@
         <v>900</v>
       </c>
       <c r="AV5" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW5" s="1" t="s">
         <v>43</v>
@@ -5363,8 +5355,8 @@
       <c r="K6" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>888</v>
+      <c r="L6" s="13">
+        <v>8</v>
       </c>
       <c r="M6">
         <v>300</v>
@@ -5451,7 +5443,7 @@
         <v>47</v>
       </c>
       <c r="AV6" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW6" s="1" t="s">
         <v>48</v>
@@ -5498,8 +5490,8 @@
       <c r="K7" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>888</v>
+      <c r="L7" s="13">
+        <v>8</v>
       </c>
       <c r="M7">
         <v>500</v>
@@ -5586,7 +5578,7 @@
         <v>51</v>
       </c>
       <c r="AV7" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW7" s="1" t="s">
         <v>52</v>
@@ -5633,8 +5625,8 @@
       <c r="K8" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>888</v>
+      <c r="L8" s="13">
+        <v>8</v>
       </c>
       <c r="M8">
         <v>1000</v>
@@ -5721,7 +5713,7 @@
         <v>55</v>
       </c>
       <c r="AV8" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW8" s="1" t="s">
         <v>56</v>
@@ -5853,13 +5845,13 @@
         <v>886</v>
       </c>
       <c r="AS9" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="AU9" s="1" t="s">
         <v>60</v>
       </c>
       <c r="AV9" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW9" s="1" t="s">
         <v>61</v>
@@ -5991,13 +5983,13 @@
         <v>886</v>
       </c>
       <c r="AT10" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="AU10" s="1" t="s">
         <v>65</v>
       </c>
       <c r="AV10" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW10" s="1" t="s">
         <v>66</v>
@@ -6132,7 +6124,7 @@
         <v>70</v>
       </c>
       <c r="AV11" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW11" s="1" t="s">
         <v>71</v>
@@ -6179,8 +6171,8 @@
       <c r="K12" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>915</v>
+      <c r="L12" s="13">
+        <v>12</v>
       </c>
       <c r="M12">
         <v>25</v>
@@ -6267,7 +6259,7 @@
         <v>76</v>
       </c>
       <c r="AV12" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW12" s="1" t="s">
         <v>77</v>
@@ -6314,8 +6306,8 @@
       <c r="K13" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>915</v>
+      <c r="L13" s="13">
+        <v>12</v>
       </c>
       <c r="M13">
         <v>50</v>
@@ -6402,7 +6394,7 @@
         <v>51</v>
       </c>
       <c r="AV13" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW13" s="1" t="s">
         <v>79</v>
@@ -6449,8 +6441,8 @@
       <c r="K14" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>915</v>
+      <c r="L14" s="13">
+        <v>12</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -6537,7 +6529,7 @@
         <v>81</v>
       </c>
       <c r="AV14" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW14" s="1" t="s">
         <v>82</v>
@@ -6584,8 +6576,8 @@
       <c r="K15" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>915</v>
+      <c r="L15" s="13">
+        <v>12</v>
       </c>
       <c r="M15">
         <v>200</v>
@@ -6672,7 +6664,7 @@
         <v>84</v>
       </c>
       <c r="AV15" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW15" s="1" t="s">
         <v>85</v>
@@ -6719,8 +6711,8 @@
       <c r="K16" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>915</v>
+      <c r="L16" s="13">
+        <v>12</v>
       </c>
       <c r="M16">
         <v>300</v>
@@ -6800,13 +6792,13 @@
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
       <c r="AT16" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="AU16" s="1" t="s">
         <v>87</v>
       </c>
       <c r="AV16" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW16" s="1" t="s">
         <v>88</v>
@@ -6853,8 +6845,8 @@
       <c r="K17" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>915</v>
+      <c r="L17" s="13">
+        <v>12</v>
       </c>
       <c r="M17">
         <v>500</v>
@@ -6937,7 +6929,7 @@
         <v>51</v>
       </c>
       <c r="AV17" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW17" s="1" t="s">
         <v>91</v>
@@ -6984,8 +6976,8 @@
       <c r="K18" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>915</v>
+      <c r="L18" s="13">
+        <v>12</v>
       </c>
       <c r="M18">
         <v>1000</v>
@@ -7068,7 +7060,7 @@
         <v>94</v>
       </c>
       <c r="AV18" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW18" s="1" t="s">
         <v>95</v>
@@ -7188,7 +7180,7 @@
         <v>886</v>
       </c>
       <c r="AJ19" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
@@ -7197,7 +7189,7 @@
         <v>98</v>
       </c>
       <c r="AV19" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW19" s="1" t="s">
         <v>99</v>
@@ -7317,7 +7309,7 @@
         <v>886</v>
       </c>
       <c r="AJ20" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="AK20" s="1"/>
       <c r="AL20" s="1"/>
@@ -7329,7 +7321,7 @@
         <v>103</v>
       </c>
       <c r="AV20" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="AW20" s="1" t="s">
         <v>104</v>
@@ -7464,7 +7456,7 @@
         <v>920</v>
       </c>
       <c r="AV21" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW21" s="1" t="s">
         <v>107</v>
@@ -7511,8 +7503,8 @@
       <c r="K22" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>888</v>
+      <c r="L22" s="13">
+        <v>8</v>
       </c>
       <c r="M22">
         <v>25</v>
@@ -7599,7 +7591,7 @@
         <v>112</v>
       </c>
       <c r="AV22" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW22" s="1" t="s">
         <v>113</v>
@@ -7646,8 +7638,8 @@
       <c r="K23" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>888</v>
+      <c r="L23" s="13">
+        <v>8</v>
       </c>
       <c r="M23">
         <v>50</v>
@@ -7734,7 +7726,7 @@
         <v>115</v>
       </c>
       <c r="AV23" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW23" s="1" t="s">
         <v>116</v>
@@ -7781,8 +7773,8 @@
       <c r="K24" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>888</v>
+      <c r="L24" s="13">
+        <v>8</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -7869,7 +7861,7 @@
         <v>118</v>
       </c>
       <c r="AV24" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW24" s="1" t="s">
         <v>119</v>
@@ -7916,8 +7908,8 @@
       <c r="K25" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>888</v>
+      <c r="L25" s="13">
+        <v>8</v>
       </c>
       <c r="M25">
         <v>200</v>
@@ -8004,7 +7996,7 @@
         <v>121</v>
       </c>
       <c r="AV25" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW25" s="1" t="s">
         <v>122</v>
@@ -8051,8 +8043,8 @@
       <c r="K26" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>888</v>
+      <c r="L26" s="13">
+        <v>8</v>
       </c>
       <c r="M26">
         <v>300</v>
@@ -8139,7 +8131,7 @@
         <v>124</v>
       </c>
       <c r="AV26" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW26" s="1" t="s">
         <v>125</v>
@@ -8186,8 +8178,8 @@
       <c r="K27" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>888</v>
+      <c r="L27" s="13">
+        <v>8</v>
       </c>
       <c r="M27">
         <v>500</v>
@@ -8274,7 +8266,7 @@
         <v>128</v>
       </c>
       <c r="AV27" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW27" s="1" t="s">
         <v>129</v>
@@ -8321,8 +8313,8 @@
       <c r="K28" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>888</v>
+      <c r="L28" s="13">
+        <v>8</v>
       </c>
       <c r="M28">
         <v>1000</v>
@@ -8409,7 +8401,7 @@
         <v>132</v>
       </c>
       <c r="AV28" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW28" s="1" t="s">
         <v>133</v>
@@ -8544,7 +8536,7 @@
         <v>137</v>
       </c>
       <c r="AV29" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW29" s="1" t="s">
         <v>138</v>
@@ -8676,13 +8668,13 @@
         <v>886</v>
       </c>
       <c r="AS30" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="AU30" s="1" t="s">
         <v>142</v>
       </c>
       <c r="AV30" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW30" s="1" t="s">
         <v>143</v>
@@ -8817,7 +8809,7 @@
         <v>147</v>
       </c>
       <c r="AV31" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW31" s="1" t="s">
         <v>148</v>
@@ -8864,8 +8856,8 @@
       <c r="K32" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>888</v>
+      <c r="L32" s="13">
+        <v>8</v>
       </c>
       <c r="M32">
         <v>25</v>
@@ -8952,7 +8944,7 @@
         <v>153</v>
       </c>
       <c r="AV32" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW32" s="1" t="s">
         <v>154</v>
@@ -8999,8 +8991,8 @@
       <c r="K33" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>888</v>
+      <c r="L33" s="13">
+        <v>8</v>
       </c>
       <c r="M33">
         <v>50</v>
@@ -9087,7 +9079,7 @@
         <v>156</v>
       </c>
       <c r="AV33" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW33" s="1" t="s">
         <v>157</v>
@@ -9134,8 +9126,8 @@
       <c r="K34" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>888</v>
+      <c r="L34" s="13">
+        <v>8</v>
       </c>
       <c r="M34">
         <v>100</v>
@@ -9222,7 +9214,7 @@
         <v>160</v>
       </c>
       <c r="AV34" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW34" s="1" t="s">
         <v>161</v>
@@ -9269,8 +9261,8 @@
       <c r="K35" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L35" s="1" t="s">
-        <v>888</v>
+      <c r="L35" s="13">
+        <v>8</v>
       </c>
       <c r="M35">
         <v>200</v>
@@ -9357,7 +9349,7 @@
         <v>164</v>
       </c>
       <c r="AV35" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW35" s="1" t="s">
         <v>165</v>
@@ -9404,8 +9396,8 @@
       <c r="K36" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L36" s="1" t="s">
-        <v>888</v>
+      <c r="L36" s="13">
+        <v>8</v>
       </c>
       <c r="M36">
         <v>300</v>
@@ -9489,13 +9481,13 @@
         <v>886</v>
       </c>
       <c r="AS36" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AU36" s="1" t="s">
         <v>167</v>
       </c>
       <c r="AV36" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW36" s="1" t="s">
         <v>168</v>
@@ -9542,8 +9534,8 @@
       <c r="K37" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>888</v>
+      <c r="L37" s="13">
+        <v>8</v>
       </c>
       <c r="M37">
         <v>500</v>
@@ -9630,7 +9622,7 @@
         <v>170</v>
       </c>
       <c r="AV37" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW37" s="1" t="s">
         <v>171</v>
@@ -9677,8 +9669,8 @@
       <c r="K38" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>888</v>
+      <c r="L38" s="13">
+        <v>8</v>
       </c>
       <c r="M38">
         <v>1000</v>
@@ -9765,7 +9757,7 @@
         <v>175</v>
       </c>
       <c r="AV38" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW38" s="1" t="s">
         <v>176</v>
@@ -9903,7 +9895,7 @@
         <v>926</v>
       </c>
       <c r="AV39" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="AW39" s="1" t="s">
         <v>180</v>
@@ -10041,7 +10033,7 @@
         <v>313</v>
       </c>
       <c r="AV40" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="AW40" s="1" t="s">
         <v>928</v>
@@ -10176,7 +10168,7 @@
         <v>929</v>
       </c>
       <c r="AV41" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW41" s="1" t="s">
         <v>187</v>
@@ -10223,8 +10215,8 @@
       <c r="K42" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>888</v>
+      <c r="L42" s="13">
+        <v>8</v>
       </c>
       <c r="M42">
         <v>25</v>
@@ -10306,13 +10298,13 @@
         <v>886</v>
       </c>
       <c r="AT42" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="AU42" s="1" t="s">
         <v>193</v>
       </c>
       <c r="AV42" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW42" s="1" t="s">
         <v>194</v>
@@ -10359,8 +10351,8 @@
       <c r="K43" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L43" s="1" t="s">
-        <v>888</v>
+      <c r="L43" s="13">
+        <v>8</v>
       </c>
       <c r="M43">
         <v>50</v>
@@ -10443,7 +10435,7 @@
         <v>196</v>
       </c>
       <c r="AV43" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW43" s="1" t="s">
         <v>197</v>
@@ -10490,8 +10482,8 @@
       <c r="K44" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>888</v>
+      <c r="L44" s="13">
+        <v>8</v>
       </c>
       <c r="M44">
         <v>100</v>
@@ -10578,7 +10570,7 @@
         <v>199</v>
       </c>
       <c r="AV44" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW44" s="1" t="s">
         <v>200</v>
@@ -10625,8 +10617,8 @@
       <c r="K45" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L45" s="1" t="s">
-        <v>888</v>
+      <c r="L45" s="13">
+        <v>8</v>
       </c>
       <c r="M45">
         <v>200</v>
@@ -10708,13 +10700,13 @@
         <v>886</v>
       </c>
       <c r="AT45" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="AU45" s="1" t="s">
         <v>203</v>
       </c>
       <c r="AV45" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW45" s="1" t="s">
         <v>204</v>
@@ -10729,7 +10721,7 @@
     </row>
     <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>190</v>
@@ -10761,8 +10753,8 @@
       <c r="K46" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L46" s="1" t="s">
-        <v>888</v>
+      <c r="L46" s="13">
+        <v>8</v>
       </c>
       <c r="M46">
         <v>300</v>
@@ -10822,7 +10814,7 @@
         <v>886</v>
       </c>
       <c r="AF46" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="AG46" s="1" t="s">
         <v>886</v>
@@ -10846,7 +10838,7 @@
         <v>886</v>
       </c>
       <c r="AO46" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AP46" s="1" t="s">
         <v>202</v>
@@ -10855,7 +10847,7 @@
         <v>206</v>
       </c>
       <c r="AV46" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="AW46" s="1" t="s">
         <v>207</v>
@@ -10902,8 +10894,8 @@
       <c r="K47" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>888</v>
+      <c r="L47" s="13">
+        <v>8</v>
       </c>
       <c r="M47">
         <v>500</v>
@@ -10989,7 +10981,7 @@
         <v>211</v>
       </c>
       <c r="AV47" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="AW47" s="1" t="s">
         <v>212</v>
@@ -11010,7 +11002,7 @@
         <v>190</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>191</v>
@@ -11036,8 +11028,8 @@
       <c r="K48" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L48" s="1" t="s">
-        <v>888</v>
+      <c r="L48" s="13">
+        <v>8</v>
       </c>
       <c r="M48">
         <v>1000</v>
@@ -11116,13 +11108,13 @@
         <v>886</v>
       </c>
       <c r="AN48" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="AU48" s="1" t="s">
         <v>214</v>
       </c>
       <c r="AV48" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="AW48" s="1" t="s">
         <v>215</v>
@@ -11255,13 +11247,13 @@
         <v>886</v>
       </c>
       <c r="AS49" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="AU49" s="1" t="s">
         <v>218</v>
       </c>
       <c r="AV49" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW49" s="1" t="s">
         <v>219</v>
@@ -11395,16 +11387,16 @@
         <v>886</v>
       </c>
       <c r="AS50" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="AT50" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="AU50" s="1" t="s">
         <v>222</v>
       </c>
       <c r="AV50" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AW50" s="1" t="s">
         <v>223</v>
@@ -11425,7 +11417,7 @@
         <v>886</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>886</v>
@@ -11512,7 +11504,7 @@
         <v>886</v>
       </c>
       <c r="AF51" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="AG51" s="1" t="s">
         <v>886</v>
@@ -11537,19 +11529,19 @@
         <v>210</v>
       </c>
       <c r="AO51" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="AU51" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="AV51" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="AU51" s="1" t="s">
+      <c r="AW51" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="AV51" s="1" t="s">
-        <v>1089</v>
-      </c>
-      <c r="AW51" s="1" t="s">
-        <v>967</v>
-      </c>
       <c r="AX51" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="AY51">
         <f t="shared" si="0"/>
@@ -11590,8 +11582,8 @@
       <c r="K52" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L52" s="1" t="s">
-        <v>888</v>
+      <c r="L52" s="13">
+        <v>8</v>
       </c>
       <c r="M52">
         <v>25</v>
@@ -11674,13 +11666,13 @@
         <v>230</v>
       </c>
       <c r="AV52" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW52" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="AX52" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="AY52">
         <f t="shared" si="0"/>
@@ -11721,8 +11713,8 @@
       <c r="K53" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L53" s="1" t="s">
-        <v>888</v>
+      <c r="L53" s="13">
+        <v>8</v>
       </c>
       <c r="M53">
         <v>50</v>
@@ -11807,13 +11799,13 @@
         <v>232</v>
       </c>
       <c r="AV53" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW53" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="AX53" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="AY53">
         <f t="shared" si="0"/>
@@ -11854,8 +11846,8 @@
       <c r="K54" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L54" s="1" t="s">
-        <v>888</v>
+      <c r="L54" s="13">
+        <v>8</v>
       </c>
       <c r="M54">
         <v>100</v>
@@ -11940,7 +11932,7 @@
         <v>234</v>
       </c>
       <c r="AV54" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW54" s="1" t="s">
         <v>235</v>
@@ -11987,8 +11979,8 @@
       <c r="K55" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L55" s="1" t="s">
-        <v>888</v>
+      <c r="L55" s="13">
+        <v>8</v>
       </c>
       <c r="M55">
         <v>200</v>
@@ -12072,13 +12064,13 @@
         <v>886</v>
       </c>
       <c r="AS55" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="AU55" s="1" t="s">
         <v>237</v>
       </c>
       <c r="AV55" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW55" s="1" t="s">
         <v>238</v>
@@ -12125,8 +12117,8 @@
       <c r="K56" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L56" s="1" t="s">
-        <v>888</v>
+      <c r="L56" s="13">
+        <v>8</v>
       </c>
       <c r="M56">
         <v>300</v>
@@ -12195,7 +12187,7 @@
         <v>886</v>
       </c>
       <c r="AI56" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="AJ56" s="1" t="s">
         <v>886</v>
@@ -12210,16 +12202,16 @@
         <v>886</v>
       </c>
       <c r="AS56" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="AT56" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="AU56" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="AV56" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW56" s="1" t="s">
         <v>240</v>
@@ -12266,8 +12258,8 @@
       <c r="K57" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L57" s="1" t="s">
-        <v>888</v>
+      <c r="L57" s="13">
+        <v>8</v>
       </c>
       <c r="M57">
         <v>500</v>
@@ -12354,10 +12346,10 @@
         <v>242</v>
       </c>
       <c r="AV57" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW57" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="AX57" s="1" t="s">
         <v>243</v>
@@ -12401,8 +12393,8 @@
       <c r="K58" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L58" s="1" t="s">
-        <v>888</v>
+      <c r="L58" s="13">
+        <v>8</v>
       </c>
       <c r="M58">
         <v>1000</v>
@@ -12484,19 +12476,19 @@
         <v>886</v>
       </c>
       <c r="AS58" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="AU58" s="1" t="s">
         <v>246</v>
       </c>
       <c r="AV58" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW58" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="AX58" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="AY58">
         <f t="shared" si="0"/>
@@ -12511,7 +12503,7 @@
         <v>886</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>886</v>
@@ -12607,7 +12599,7 @@
         <v>886</v>
       </c>
       <c r="AI59" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AJ59" s="1" t="s">
         <v>886</v>
@@ -12622,16 +12614,16 @@
         <v>886</v>
       </c>
       <c r="AU59" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AV59" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW59" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="AX59" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="AY59">
         <f t="shared" si="0"/>
@@ -12742,7 +12734,7 @@
         <v>886</v>
       </c>
       <c r="AI60" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="AJ60" s="1" t="s">
         <v>886</v>
@@ -12757,13 +12749,13 @@
         <v>886</v>
       </c>
       <c r="AT60" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="AU60" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="AV60" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW60" s="1" t="s">
         <v>250</v>
@@ -12880,7 +12872,7 @@
         <v>886</v>
       </c>
       <c r="AI61" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AJ61" s="1" t="s">
         <v>886</v>
@@ -12898,7 +12890,7 @@
         <v>137</v>
       </c>
       <c r="AV61" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW61" s="1" t="s">
         <v>253</v>
@@ -12945,8 +12937,8 @@
       <c r="K62" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L62" s="1" t="s">
-        <v>931</v>
+      <c r="L62" s="13">
+        <v>0</v>
       </c>
       <c r="M62">
         <v>25</v>
@@ -13033,7 +13025,7 @@
         <v>258</v>
       </c>
       <c r="AV62" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW62" s="1" t="s">
         <v>259</v>
@@ -13080,8 +13072,8 @@
       <c r="K63" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L63" s="1" t="s">
-        <v>931</v>
+      <c r="L63" s="13">
+        <v>0</v>
       </c>
       <c r="M63">
         <v>50</v>
@@ -13168,7 +13160,7 @@
         <v>261</v>
       </c>
       <c r="AV63" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW63" s="1" t="s">
         <v>262</v>
@@ -13215,8 +13207,8 @@
       <c r="K64" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L64" s="1" t="s">
-        <v>931</v>
+      <c r="L64" s="13">
+        <v>0</v>
       </c>
       <c r="M64">
         <v>100</v>
@@ -13303,7 +13295,7 @@
         <v>264</v>
       </c>
       <c r="AV64" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW64" s="1" t="s">
         <v>265</v>
@@ -13350,8 +13342,8 @@
       <c r="K65" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L65" s="1" t="s">
-        <v>931</v>
+      <c r="L65" s="13">
+        <v>0</v>
       </c>
       <c r="M65">
         <v>200</v>
@@ -13438,7 +13430,7 @@
         <v>267</v>
       </c>
       <c r="AV65" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW65" s="1" t="s">
         <v>268</v>
@@ -13485,8 +13477,8 @@
       <c r="K66" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L66" s="1" t="s">
-        <v>931</v>
+      <c r="L66" s="13">
+        <v>0</v>
       </c>
       <c r="M66">
         <v>300</v>
@@ -13570,13 +13562,13 @@
         <v>886</v>
       </c>
       <c r="AT66" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="AU66" s="1" t="s">
         <v>271</v>
       </c>
       <c r="AV66" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW66" s="1" t="s">
         <v>272</v>
@@ -13623,8 +13615,8 @@
       <c r="K67" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L67" s="1" t="s">
-        <v>931</v>
+      <c r="L67" s="13">
+        <v>0</v>
       </c>
       <c r="M67">
         <v>500</v>
@@ -13708,10 +13700,10 @@
         <v>886</v>
       </c>
       <c r="AU67" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="AV67" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW67" s="1" t="s">
         <v>274</v>
@@ -13758,8 +13750,8 @@
       <c r="K68" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L68" s="1" t="s">
-        <v>931</v>
+      <c r="L68" s="13">
+        <v>0</v>
       </c>
       <c r="M68">
         <v>1000</v>
@@ -13843,10 +13835,10 @@
         <v>886</v>
       </c>
       <c r="AU68" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="AV68" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW68" s="1" t="s">
         <v>277</v>
@@ -13981,13 +13973,13 @@
         <v>280</v>
       </c>
       <c r="AO69" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AU69" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AV69" s="1" t="s">
         <v>1123</v>
-      </c>
-      <c r="AU69" s="1" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AV69" s="1" t="s">
-        <v>1124</v>
       </c>
       <c r="AW69" s="1" t="s">
         <v>282</v>
@@ -14117,22 +14109,22 @@
         <v>886</v>
       </c>
       <c r="AQ70" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="AS70" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="AU70" s="1" t="s">
         <v>286</v>
       </c>
       <c r="AV70" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="AW70" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="AW70" s="1" t="s">
-        <v>1134</v>
-      </c>
       <c r="AX70" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="AY70">
         <f t="shared" si="1"/>
@@ -14228,46 +14220,46 @@
         <v>886</v>
       </c>
       <c r="AD71" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AE71" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AF71" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AG71" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AH71" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AI71" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AJ71" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AK71" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AL71" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AM71" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AU71" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="AE71" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AF71" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AG71" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AH71" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AI71" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AJ71" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AK71" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AL71" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AM71" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AU71" s="1" t="s">
+      <c r="AV71" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="AW71" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="AV71" s="1" t="s">
-        <v>1079</v>
-      </c>
-      <c r="AW71" s="1" t="s">
+      <c r="AX71" s="1" t="s">
         <v>1130</v>
-      </c>
-      <c r="AX71" s="1" t="s">
-        <v>1131</v>
       </c>
       <c r="AY71">
         <f t="shared" si="1"/>
@@ -14308,8 +14300,8 @@
       <c r="K72" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L72" s="1" t="s">
-        <v>895</v>
+      <c r="L72" s="13">
+        <v>40</v>
       </c>
       <c r="M72">
         <v>25</v>
@@ -14393,16 +14385,16 @@
         <v>886</v>
       </c>
       <c r="AN72" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="AS72" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="AU72" s="1" t="s">
         <v>292</v>
       </c>
       <c r="AV72" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="AW72" s="1" t="s">
         <v>293</v>
@@ -14449,8 +14441,8 @@
       <c r="K73" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L73" s="1" t="s">
-        <v>895</v>
+      <c r="L73" s="13">
+        <v>40</v>
       </c>
       <c r="M73">
         <v>50</v>
@@ -14537,7 +14529,7 @@
         <v>137</v>
       </c>
       <c r="AV73" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="AW73" s="1" t="s">
         <v>295</v>
@@ -14584,8 +14576,8 @@
       <c r="K74" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L74" s="1" t="s">
-        <v>895</v>
+      <c r="L74" s="13">
+        <v>40</v>
       </c>
       <c r="M74">
         <v>100</v>
@@ -14672,7 +14664,7 @@
         <v>137</v>
       </c>
       <c r="AV74" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="AW74" s="1" t="s">
         <v>297</v>
@@ -14719,8 +14711,8 @@
       <c r="K75" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L75" s="1" t="s">
-        <v>895</v>
+      <c r="L75" s="13">
+        <v>40</v>
       </c>
       <c r="M75">
         <v>200</v>
@@ -14807,7 +14799,7 @@
         <v>299</v>
       </c>
       <c r="AV75" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="AW75" s="1" t="s">
         <v>300</v>
@@ -14854,8 +14846,8 @@
       <c r="K76" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L76" s="1" t="s">
-        <v>895</v>
+      <c r="L76" s="13">
+        <v>40</v>
       </c>
       <c r="M76">
         <v>300</v>
@@ -14942,7 +14934,7 @@
         <v>137</v>
       </c>
       <c r="AV76" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="AW76" s="1" t="s">
         <v>302</v>
@@ -14989,8 +14981,8 @@
       <c r="K77" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L77" s="1" t="s">
-        <v>895</v>
+      <c r="L77" s="13">
+        <v>40</v>
       </c>
       <c r="M77">
         <v>500</v>
@@ -15077,7 +15069,7 @@
         <v>305</v>
       </c>
       <c r="AV77" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="AW77" s="1" t="s">
         <v>306</v>
@@ -15124,8 +15116,8 @@
       <c r="K78" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="L78" s="1" t="s">
-        <v>895</v>
+      <c r="L78" s="13">
+        <v>40</v>
       </c>
       <c r="M78">
         <v>1000</v>
@@ -15209,14 +15201,14 @@
         <v>886</v>
       </c>
       <c r="AN78" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="AP78"/>
       <c r="AU78" s="1" t="s">
         <v>309</v>
       </c>
       <c r="AV78" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="AW78" s="1" t="s">
         <v>310</v>
@@ -15348,13 +15340,13 @@
         <v>886</v>
       </c>
       <c r="AN79" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="AU79" s="1" t="s">
         <v>313</v>
       </c>
       <c r="AV79" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="AW79" s="1" t="s">
         <v>314</v>
@@ -15486,22 +15478,22 @@
         <v>886</v>
       </c>
       <c r="AN80" t="s">
+        <v>1142</v>
+      </c>
+      <c r="AS80" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="AU80" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AV80" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="AS80" s="1" t="s">
-        <v>990</v>
-      </c>
-      <c r="AU80" s="1" t="s">
+      <c r="AW80" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="AV80" s="1" t="s">
-        <v>1144</v>
-      </c>
-      <c r="AW80" s="1" t="s">
-        <v>1137</v>
-      </c>
       <c r="AX80" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AY80">
         <f t="shared" si="1"/>
@@ -15627,22 +15619,22 @@
         <v>886</v>
       </c>
       <c r="AN81" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="AS81" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="AU81" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AV81" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AW81" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="AV81" s="1" t="s">
-        <v>1144</v>
-      </c>
-      <c r="AW81" s="1" t="s">
-        <v>1139</v>
-      </c>
       <c r="AX81" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="AY81">
         <f t="shared" si="1"/>
@@ -15683,8 +15675,8 @@
       <c r="K82" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L82" s="1" t="s">
-        <v>888</v>
+      <c r="L82" s="13">
+        <v>8</v>
       </c>
       <c r="M82">
         <v>25</v>
@@ -15744,7 +15736,7 @@
         <v>886</v>
       </c>
       <c r="AF82" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="AG82" s="1" t="s">
         <v>886</v>
@@ -15771,7 +15763,7 @@
         <v>327</v>
       </c>
       <c r="AV82" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW82" s="1" t="s">
         <v>328</v>
@@ -15818,8 +15810,8 @@
       <c r="K83" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L83" s="1" t="s">
-        <v>888</v>
+      <c r="L83" s="13">
+        <v>8</v>
       </c>
       <c r="M83">
         <v>50</v>
@@ -15903,13 +15895,13 @@
         <v>886</v>
       </c>
       <c r="AT83" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AU83" s="1" t="s">
         <v>330</v>
       </c>
       <c r="AV83" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW83" s="1" t="s">
         <v>331</v>
@@ -15956,8 +15948,8 @@
       <c r="K84" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L84" s="1" t="s">
-        <v>888</v>
+      <c r="L84" s="13">
+        <v>8</v>
       </c>
       <c r="M84">
         <v>100</v>
@@ -16044,7 +16036,7 @@
         <v>333</v>
       </c>
       <c r="AV84" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW84" s="1" t="s">
         <v>334</v>
@@ -16091,8 +16083,8 @@
       <c r="K85" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L85" s="1" t="s">
-        <v>888</v>
+      <c r="L85" s="13">
+        <v>8</v>
       </c>
       <c r="M85">
         <v>200</v>
@@ -16146,7 +16138,7 @@
         <v>886</v>
       </c>
       <c r="AD85" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="AE85" s="1" t="s">
         <v>886</v>
@@ -16179,7 +16171,7 @@
         <v>51</v>
       </c>
       <c r="AV85" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW85" s="1" t="s">
         <v>336</v>
@@ -16226,8 +16218,8 @@
       <c r="K86" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L86" s="1" t="s">
-        <v>888</v>
+      <c r="L86" s="13">
+        <v>8</v>
       </c>
       <c r="M86">
         <v>300</v>
@@ -16314,7 +16306,7 @@
         <v>211</v>
       </c>
       <c r="AV86" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW86" s="1" t="s">
         <v>340</v>
@@ -16361,8 +16353,8 @@
       <c r="K87" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L87" s="1" t="s">
-        <v>888</v>
+      <c r="L87" s="13">
+        <v>8</v>
       </c>
       <c r="M87">
         <v>500</v>
@@ -16446,13 +16438,13 @@
         <v>886</v>
       </c>
       <c r="AS87" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="AU87" s="1" t="s">
         <v>342</v>
       </c>
       <c r="AV87" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW87" s="1" t="s">
         <v>343</v>
@@ -16499,8 +16491,8 @@
       <c r="K88" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L88" s="1" t="s">
-        <v>888</v>
+      <c r="L88" s="13">
+        <v>8</v>
       </c>
       <c r="M88">
         <v>1000</v>
@@ -16560,7 +16552,7 @@
         <v>886</v>
       </c>
       <c r="AF88" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AG88" s="1" t="s">
         <v>886</v>
@@ -16587,7 +16579,7 @@
         <v>348</v>
       </c>
       <c r="AV88" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW88" s="1" t="s">
         <v>349</v>
@@ -16722,7 +16714,7 @@
         <v>352</v>
       </c>
       <c r="AV89" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW89" s="1" t="s">
         <v>353</v>
@@ -16824,7 +16816,7 @@
         <v>886</v>
       </c>
       <c r="AD90" s="3" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="AE90" s="1" t="s">
         <v>886</v>
@@ -16857,13 +16849,13 @@
         <v>356</v>
       </c>
       <c r="AS90" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AU90" s="1" t="s">
         <v>359</v>
       </c>
       <c r="AV90" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="AW90" s="1" t="s">
         <v>360</v>
@@ -16998,7 +16990,7 @@
         <v>364</v>
       </c>
       <c r="AV91" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW91" s="1" t="s">
         <v>365</v>
@@ -17045,8 +17037,8 @@
       <c r="K92" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L92" s="1" t="s">
-        <v>888</v>
+      <c r="L92" s="13">
+        <v>8</v>
       </c>
       <c r="M92">
         <v>25</v>
@@ -17133,7 +17125,7 @@
         <v>370</v>
       </c>
       <c r="AV92" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW92" s="1" t="s">
         <v>371</v>
@@ -17180,8 +17172,8 @@
       <c r="K93" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L93" s="1" t="s">
-        <v>888</v>
+      <c r="L93" s="13">
+        <v>8</v>
       </c>
       <c r="M93">
         <v>50</v>
@@ -17268,7 +17260,7 @@
         <v>199</v>
       </c>
       <c r="AV93" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW93" s="1" t="s">
         <v>373</v>
@@ -17315,8 +17307,8 @@
       <c r="K94" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L94" s="1" t="s">
-        <v>888</v>
+      <c r="L94" s="13">
+        <v>8</v>
       </c>
       <c r="M94">
         <v>100</v>
@@ -17403,7 +17395,7 @@
         <v>375</v>
       </c>
       <c r="AV94" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW94" s="1" t="s">
         <v>376</v>
@@ -17450,8 +17442,8 @@
       <c r="K95" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L95" s="1" t="s">
-        <v>888</v>
+      <c r="L95" s="13">
+        <v>8</v>
       </c>
       <c r="M95">
         <v>200</v>
@@ -17535,13 +17527,13 @@
         <v>886</v>
       </c>
       <c r="AT95" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AU95" s="1" t="s">
         <v>377</v>
       </c>
       <c r="AV95" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW95" s="1" t="s">
         <v>378</v>
@@ -17562,7 +17554,7 @@
         <v>367</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>368</v>
@@ -17588,8 +17580,8 @@
       <c r="K96" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L96" s="1" t="s">
-        <v>888</v>
+      <c r="L96" s="13">
+        <v>8</v>
       </c>
       <c r="M96">
         <v>300</v>
@@ -17601,7 +17593,7 @@
         <v>886</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>886</v>
@@ -17682,7 +17674,7 @@
         <v>313</v>
       </c>
       <c r="AV96" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="AW96" s="1" t="s">
         <v>379</v>
@@ -17729,8 +17721,8 @@
       <c r="K97" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L97" s="1" t="s">
-        <v>888</v>
+      <c r="L97" s="13">
+        <v>8</v>
       </c>
       <c r="M97">
         <v>500</v>
@@ -17817,7 +17809,7 @@
         <v>381</v>
       </c>
       <c r="AV97" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW97" s="1" t="s">
         <v>382</v>
@@ -17864,8 +17856,8 @@
       <c r="K98" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L98" s="1" t="s">
-        <v>888</v>
+      <c r="L98" s="13">
+        <v>8</v>
       </c>
       <c r="M98">
         <v>1000</v>
@@ -17952,7 +17944,7 @@
         <v>385</v>
       </c>
       <c r="AV98" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW98" s="1" t="s">
         <v>386</v>
@@ -17973,7 +17965,7 @@
         <v>886</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>886</v>
@@ -18009,7 +18001,7 @@
         <v>886</v>
       </c>
       <c r="O99" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="P99" s="1" t="s">
         <v>904</v>
@@ -18054,13 +18046,13 @@
         <v>886</v>
       </c>
       <c r="AD99" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="AE99" s="1" t="s">
         <v>886</v>
       </c>
       <c r="AF99" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AG99" s="1" t="s">
         <v>886</v>
@@ -18090,16 +18082,16 @@
         <v>326</v>
       </c>
       <c r="AU99" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AV99" s="1" t="s">
         <v>1165</v>
       </c>
-      <c r="AV99" s="1" t="s">
+      <c r="AW99" s="1" t="s">
         <v>1166</v>
       </c>
-      <c r="AW99" s="1" t="s">
-        <v>1167</v>
-      </c>
       <c r="AX99" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="AY99">
         <f t="shared" si="1"/>
@@ -18231,7 +18223,7 @@
         <v>391</v>
       </c>
       <c r="AV100" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AW100" s="1" t="s">
         <v>392</v>
@@ -18252,7 +18244,7 @@
         <v>886</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>886</v>
@@ -18291,91 +18283,91 @@
         <v>886</v>
       </c>
       <c r="P101" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="R101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="T101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="U101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="V101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="W101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="X101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="Y101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="Z101" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AA101" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="AB101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AC101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AD101" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="AE101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AF101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AG101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AH101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AI101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AJ101" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AK101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AL101" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AM101" s="1" t="s">
         <v>1154</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="R101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="T101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="U101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="V101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="W101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="X101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="Y101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="Z101" s="1" t="s">
+      <c r="AN101" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AU101" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AV101" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="AW101" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="AX101" s="1" t="s">
         <v>1160</v>
-      </c>
-      <c r="AA101" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="AB101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AC101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AD101" s="3" t="s">
-        <v>1153</v>
-      </c>
-      <c r="AE101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AF101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AG101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AH101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AI101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AJ101" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="AK101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AL101" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AM101" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="AN101" s="1" t="s">
-        <v>1157</v>
-      </c>
-      <c r="AU101" s="1" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AV101" s="1" t="s">
-        <v>1156</v>
-      </c>
-      <c r="AW101" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="AX101" s="1" t="s">
-        <v>1161</v>
       </c>
       <c r="AY101">
         <f t="shared" si="1"/>
@@ -18416,8 +18408,8 @@
       <c r="K102" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L102" s="1" t="s">
-        <v>888</v>
+      <c r="L102" s="13">
+        <v>8</v>
       </c>
       <c r="M102">
         <v>25</v>
@@ -18501,13 +18493,13 @@
         <v>886</v>
       </c>
       <c r="AS102" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="AU102" s="1" t="s">
         <v>400</v>
       </c>
       <c r="AV102" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW102" s="1" t="s">
         <v>401</v>
@@ -18554,8 +18546,8 @@
       <c r="K103" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L103" s="1" t="s">
-        <v>888</v>
+      <c r="L103" s="13">
+        <v>8</v>
       </c>
       <c r="M103">
         <v>50</v>
@@ -18642,7 +18634,7 @@
         <v>403</v>
       </c>
       <c r="AV103" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW103" s="1" t="s">
         <v>404</v>
@@ -18689,8 +18681,8 @@
       <c r="K104" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L104" s="1" t="s">
-        <v>888</v>
+      <c r="L104" s="13">
+        <v>8</v>
       </c>
       <c r="M104">
         <v>100</v>
@@ -18780,7 +18772,7 @@
         <v>407</v>
       </c>
       <c r="AV104" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="AW104" s="1" t="s">
         <v>408</v>
@@ -18827,8 +18819,8 @@
       <c r="K105" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L105" s="1" t="s">
-        <v>888</v>
+      <c r="L105" s="13">
+        <v>8</v>
       </c>
       <c r="M105">
         <v>200</v>
@@ -18915,7 +18907,7 @@
         <v>410</v>
       </c>
       <c r="AV105" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW105" s="1" t="s">
         <v>411</v>
@@ -18962,8 +18954,8 @@
       <c r="K106" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L106" s="1" t="s">
-        <v>888</v>
+      <c r="L106" s="13">
+        <v>8</v>
       </c>
       <c r="M106">
         <v>300</v>
@@ -19050,7 +19042,7 @@
         <v>413</v>
       </c>
       <c r="AV106" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW106" s="1" t="s">
         <v>414</v>
@@ -19097,8 +19089,8 @@
       <c r="K107" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L107" s="1" t="s">
-        <v>888</v>
+      <c r="L107" s="13">
+        <v>8</v>
       </c>
       <c r="M107">
         <v>500</v>
@@ -19185,7 +19177,7 @@
         <v>416</v>
       </c>
       <c r="AV107" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW107" s="1" t="s">
         <v>417</v>
@@ -19232,8 +19224,8 @@
       <c r="K108" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="L108" s="1" t="s">
-        <v>888</v>
+      <c r="L108" s="13">
+        <v>8</v>
       </c>
       <c r="M108">
         <v>1000</v>
@@ -19320,7 +19312,7 @@
         <v>419</v>
       </c>
       <c r="AV108" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW108" s="1" t="s">
         <v>420</v>
@@ -19440,25 +19432,25 @@
         <v>886</v>
       </c>
       <c r="AJ109" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="AK109" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AL109" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AM109" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AO109" s="1" t="s">
         <v>1173</v>
-      </c>
-      <c r="AK109" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AL109" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AM109" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AO109" s="1" t="s">
-        <v>1174</v>
       </c>
       <c r="AU109" s="1" t="s">
         <v>423</v>
       </c>
       <c r="AV109" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="AW109" s="1" t="s">
         <v>424</v>
@@ -19596,7 +19588,7 @@
         <v>427</v>
       </c>
       <c r="AV110" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="AW110" s="1" t="s">
         <v>428</v>
@@ -19671,7 +19663,7 @@
         <v>909</v>
       </c>
       <c r="U111" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="V111" s="1" t="s">
         <v>886</v>
@@ -19704,7 +19696,7 @@
         <v>886</v>
       </c>
       <c r="AF111" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="AG111" s="1" t="s">
         <v>886</v>
@@ -19728,22 +19720,22 @@
         <v>886</v>
       </c>
       <c r="AO111" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="AS111" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AU111" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AV111" s="1" t="s">
         <v>1176</v>
       </c>
-      <c r="AS111" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="AU111" s="1" t="s">
-        <v>1170</v>
-      </c>
-      <c r="AV111" s="1" t="s">
-        <v>1177</v>
-      </c>
       <c r="AW111" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="AX111" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="AY111">
         <f t="shared" si="1"/>
@@ -19784,8 +19776,8 @@
       <c r="K112" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L112" s="1" t="s">
-        <v>888</v>
+      <c r="L112" s="13">
+        <v>8</v>
       </c>
       <c r="M112">
         <v>25</v>
@@ -19866,13 +19858,13 @@
         <v>451</v>
       </c>
       <c r="AS112" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="AU112" s="1" t="s">
         <v>437</v>
       </c>
       <c r="AV112" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW112" s="1" t="s">
         <v>438</v>
@@ -19919,8 +19911,8 @@
       <c r="K113" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L113" s="1" t="s">
-        <v>888</v>
+      <c r="L113" s="13">
+        <v>8</v>
       </c>
       <c r="M113">
         <v>50</v>
@@ -20007,7 +19999,7 @@
         <v>137</v>
       </c>
       <c r="AV113" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW113" s="1" t="s">
         <v>440</v>
@@ -20054,8 +20046,8 @@
       <c r="K114" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L114" s="1" t="s">
-        <v>888</v>
+      <c r="L114" s="13">
+        <v>8</v>
       </c>
       <c r="M114">
         <v>100</v>
@@ -20142,7 +20134,7 @@
         <v>442</v>
       </c>
       <c r="AV114" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW114" s="1" t="s">
         <v>443</v>
@@ -20189,8 +20181,8 @@
       <c r="K115" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L115" s="1" t="s">
-        <v>888</v>
+      <c r="L115" s="13">
+        <v>8</v>
       </c>
       <c r="M115">
         <v>200</v>
@@ -20277,7 +20269,7 @@
         <v>403</v>
       </c>
       <c r="AV115" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW115" s="1" t="s">
         <v>445</v>
@@ -20324,8 +20316,8 @@
       <c r="K116" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L116" s="1" t="s">
-        <v>888</v>
+      <c r="L116" s="13">
+        <v>8</v>
       </c>
       <c r="M116">
         <v>300</v>
@@ -20409,10 +20401,10 @@
         <v>886</v>
       </c>
       <c r="AU116" s="1" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="AV116" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW116" s="1" t="s">
         <v>447</v>
@@ -20459,8 +20451,8 @@
       <c r="K117" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L117" s="1" t="s">
-        <v>888</v>
+      <c r="L117" s="13">
+        <v>8</v>
       </c>
       <c r="M117">
         <v>500</v>
@@ -20544,13 +20536,13 @@
         <v>886</v>
       </c>
       <c r="AS117" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="AU117" s="1" t="s">
         <v>449</v>
       </c>
       <c r="AV117" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW117" s="1" t="s">
         <v>450</v>
@@ -20571,7 +20563,7 @@
         <v>433</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>434</v>
@@ -20597,8 +20589,8 @@
       <c r="K118" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L118" s="1" t="s">
-        <v>888</v>
+      <c r="L118" s="13">
+        <v>8</v>
       </c>
       <c r="M118">
         <v>1000</v>
@@ -20685,7 +20677,7 @@
         <v>452</v>
       </c>
       <c r="AV118" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW118" s="1" t="s">
         <v>453</v>
@@ -20706,7 +20698,7 @@
         <v>886</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>886</v>
@@ -20748,7 +20740,7 @@
         <v>886</v>
       </c>
       <c r="Q119" s="3" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="R119" s="1" t="s">
         <v>886</v>
@@ -20811,22 +20803,22 @@
         <v>270</v>
       </c>
       <c r="AL119" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="AM119" s="1" t="s">
         <v>886</v>
       </c>
       <c r="AS119" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="AT119" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AU119" s="1" t="s">
         <v>456</v>
       </c>
       <c r="AV119" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW119" s="1" t="s">
         <v>457</v>
@@ -20952,16 +20944,16 @@
         <v>886</v>
       </c>
       <c r="AL120" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="AM120" s="1" t="s">
         <v>886</v>
       </c>
       <c r="AU120" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="AV120" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW120" s="1" t="s">
         <v>460</v>
@@ -21024,7 +21016,7 @@
         <v>886</v>
       </c>
       <c r="Q121" s="3" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="R121" s="1" t="s">
         <v>886</v>
@@ -21087,22 +21079,22 @@
         <v>270</v>
       </c>
       <c r="AL121" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="AM121" s="1" t="s">
         <v>886</v>
       </c>
       <c r="AS121" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="AT121" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="AU121" s="1" t="s">
         <v>464</v>
       </c>
       <c r="AV121" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW121" s="1" t="s">
         <v>465</v>
@@ -21149,8 +21141,8 @@
       <c r="K122" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L122" s="1" t="s">
-        <v>888</v>
+      <c r="L122" s="13">
+        <v>8</v>
       </c>
       <c r="M122">
         <v>25</v>
@@ -21234,13 +21226,13 @@
         <v>886</v>
       </c>
       <c r="AT122" s="1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="AU122" s="1" t="s">
         <v>471</v>
       </c>
       <c r="AV122" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW122" s="1" t="s">
         <v>472</v>
@@ -21287,8 +21279,8 @@
       <c r="K123" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L123" s="1" t="s">
-        <v>888</v>
+      <c r="L123" s="13">
+        <v>8</v>
       </c>
       <c r="M123">
         <v>50</v>
@@ -21375,7 +21367,7 @@
         <v>403</v>
       </c>
       <c r="AV123" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW123" s="1" t="s">
         <v>473</v>
@@ -21422,8 +21414,8 @@
       <c r="K124" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L124" s="1" t="s">
-        <v>888</v>
+      <c r="L124" s="13">
+        <v>8</v>
       </c>
       <c r="M124">
         <v>100</v>
@@ -21507,13 +21499,13 @@
         <v>886</v>
       </c>
       <c r="AT124" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="AU124" s="1" t="s">
         <v>476</v>
       </c>
       <c r="AV124" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW124" s="1" t="s">
         <v>477</v>
@@ -21560,8 +21552,8 @@
       <c r="K125" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L125" s="1" t="s">
-        <v>888</v>
+      <c r="L125" s="13">
+        <v>8</v>
       </c>
       <c r="M125">
         <v>200</v>
@@ -21648,7 +21640,7 @@
         <v>479</v>
       </c>
       <c r="AV125" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW125" s="1" t="s">
         <v>480</v>
@@ -21695,8 +21687,8 @@
       <c r="K126" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L126" s="1" t="s">
-        <v>888</v>
+      <c r="L126" s="13">
+        <v>8</v>
       </c>
       <c r="M126">
         <v>300</v>
@@ -21783,7 +21775,7 @@
         <v>482</v>
       </c>
       <c r="AV126" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW126" s="1" t="s">
         <v>483</v>
@@ -21830,8 +21822,8 @@
       <c r="K127" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L127" s="1" t="s">
-        <v>888</v>
+      <c r="L127" s="13">
+        <v>8</v>
       </c>
       <c r="M127">
         <v>500</v>
@@ -21918,7 +21910,7 @@
         <v>485</v>
       </c>
       <c r="AV127" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW127" s="1" t="s">
         <v>486</v>
@@ -21965,8 +21957,8 @@
       <c r="K128" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L128" s="1" t="s">
-        <v>888</v>
+      <c r="L128" s="13">
+        <v>8</v>
       </c>
       <c r="M128">
         <v>1000</v>
@@ -22050,13 +22042,13 @@
         <v>886</v>
       </c>
       <c r="AT128" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="AU128" s="1" t="s">
         <v>489</v>
       </c>
       <c r="AV128" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW128" s="1" t="s">
         <v>490</v>
@@ -22182,19 +22174,19 @@
         <v>886</v>
       </c>
       <c r="AL129" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="AM129" s="1" t="s">
         <v>886</v>
       </c>
       <c r="AT129" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="AU129" s="1" t="s">
         <v>493</v>
       </c>
       <c r="AV129" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW129" s="1" t="s">
         <v>494</v>
@@ -22287,61 +22279,61 @@
         <v>886</v>
       </c>
       <c r="AA130" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="AB130" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AC130" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AD130" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="AE130" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AF130" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AG130" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AH130" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AI130" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AJ130" s="1" t="s">
         <v>1191</v>
       </c>
-      <c r="AB130" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AC130" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AD130" s="3" t="s">
-        <v>1190</v>
-      </c>
-      <c r="AE130" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AF130" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AG130" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AH130" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AI130" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AJ130" s="1" t="s">
+      <c r="AK130" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AL130" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AM130" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AN130" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="AT130" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AU130" s="1" t="s">
         <v>1192</v>
       </c>
-      <c r="AK130" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AL130" s="1" t="s">
+      <c r="AV130" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="AW130" s="1" t="s">
         <v>1186</v>
       </c>
-      <c r="AM130" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AN130" s="1" t="s">
-        <v>1188</v>
-      </c>
-      <c r="AT130" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AU130" s="1" t="s">
-        <v>1193</v>
-      </c>
-      <c r="AV130" s="1" t="s">
-        <v>1189</v>
-      </c>
-      <c r="AW130" s="1" t="s">
-        <v>1187</v>
-      </c>
       <c r="AX130" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="AY130">
         <f t="shared" si="1"/>
@@ -22461,7 +22453,7 @@
         <v>886</v>
       </c>
       <c r="AL131" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="AM131" s="1" t="s">
         <v>886</v>
@@ -22470,7 +22462,7 @@
         <v>499</v>
       </c>
       <c r="AV131" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW131" s="1" t="s">
         <v>500</v>
@@ -22517,8 +22509,8 @@
       <c r="K132" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L132" s="1" t="s">
-        <v>931</v>
+      <c r="L132" s="13">
+        <v>0</v>
       </c>
       <c r="M132">
         <v>25</v>
@@ -22605,7 +22597,7 @@
         <v>504</v>
       </c>
       <c r="AV132" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW132" s="1" t="s">
         <v>505</v>
@@ -22652,8 +22644,8 @@
       <c r="K133" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L133" s="1" t="s">
-        <v>931</v>
+      <c r="L133" s="13">
+        <v>0</v>
       </c>
       <c r="M133">
         <v>50</v>
@@ -22740,7 +22732,7 @@
         <v>413</v>
       </c>
       <c r="AV133" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW133" s="1" t="s">
         <v>507</v>
@@ -22787,8 +22779,8 @@
       <c r="K134" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L134" s="1" t="s">
-        <v>931</v>
+      <c r="L134" s="13">
+        <v>0</v>
       </c>
       <c r="M134">
         <v>100</v>
@@ -22872,10 +22864,10 @@
         <v>886</v>
       </c>
       <c r="AU134" s="1" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="AV134" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW134" s="1" t="s">
         <v>509</v>
@@ -22922,8 +22914,8 @@
       <c r="K135" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L135" s="1" t="s">
-        <v>931</v>
+      <c r="L135" s="13">
+        <v>0</v>
       </c>
       <c r="M135">
         <v>200</v>
@@ -23007,10 +22999,10 @@
         <v>886</v>
       </c>
       <c r="AU135" s="1" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="AV135" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW135" s="1" t="s">
         <v>511</v>
@@ -23057,8 +23049,8 @@
       <c r="K136" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L136" s="1" t="s">
-        <v>931</v>
+      <c r="L136" s="13">
+        <v>0</v>
       </c>
       <c r="M136">
         <v>300</v>
@@ -23142,16 +23134,16 @@
         <v>886</v>
       </c>
       <c r="AU136" s="1" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="AV136" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW136" s="1" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="AX136" s="1" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="AY136">
         <f t="shared" si="2"/>
@@ -23192,8 +23184,8 @@
       <c r="K137" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L137" s="1" t="s">
-        <v>931</v>
+      <c r="L137" s="13">
+        <v>0</v>
       </c>
       <c r="M137">
         <v>500</v>
@@ -23280,7 +23272,7 @@
         <v>515</v>
       </c>
       <c r="AV137" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW137" s="1" t="s">
         <v>516</v>
@@ -23327,8 +23319,8 @@
       <c r="K138" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="L138" s="1" t="s">
-        <v>931</v>
+      <c r="L138" s="13">
+        <v>0</v>
       </c>
       <c r="M138">
         <v>1000</v>
@@ -23412,19 +23404,19 @@
         <v>886</v>
       </c>
       <c r="AS138" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="AU138" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="AV138" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="AW138" s="1" t="s">
         <v>1194</v>
       </c>
-      <c r="AV138" s="1" t="s">
-        <v>1079</v>
-      </c>
-      <c r="AW138" s="1" t="s">
-        <v>1195</v>
-      </c>
       <c r="AX138" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AY138">
         <f t="shared" si="2"/>
@@ -23550,10 +23542,10 @@
         <v>886</v>
       </c>
       <c r="AU139" s="1" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="AV139" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW139" s="1" t="s">
         <v>521</v>
@@ -23685,10 +23677,10 @@
         <v>886</v>
       </c>
       <c r="AU140" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="AV140" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW140" s="1" t="s">
         <v>525</v>
@@ -23823,7 +23815,7 @@
         <v>528</v>
       </c>
       <c r="AV141" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW141" s="1" t="s">
         <v>529</v>
@@ -23870,8 +23862,8 @@
       <c r="K142" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L142" s="1" t="s">
-        <v>1197</v>
+      <c r="L142" s="13">
+        <v>6</v>
       </c>
       <c r="M142">
         <v>25</v>
@@ -23931,7 +23923,7 @@
         <v>886</v>
       </c>
       <c r="AF142" s="1" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="AG142" s="1" t="s">
         <v>886</v>
@@ -23939,10 +23931,10 @@
       <c r="AH142" s="1"/>
       <c r="AI142" s="1"/>
       <c r="AJ142" s="1" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="AK142" s="1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="AL142" s="1" t="s">
         <v>886</v>
@@ -23954,7 +23946,7 @@
         <v>535</v>
       </c>
       <c r="AV142" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW142" s="1" t="s">
         <v>536</v>
@@ -24001,8 +23993,8 @@
       <c r="K143" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L143" s="1" t="s">
-        <v>1197</v>
+      <c r="L143" s="13">
+        <v>6</v>
       </c>
       <c r="M143">
         <v>50</v>
@@ -24089,7 +24081,7 @@
         <v>225</v>
       </c>
       <c r="AV143" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW143" s="1" t="s">
         <v>538</v>
@@ -24136,8 +24128,8 @@
       <c r="K144" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L144" s="1" t="s">
-        <v>1197</v>
+      <c r="L144" s="13">
+        <v>6</v>
       </c>
       <c r="M144">
         <v>100</v>
@@ -24224,7 +24216,7 @@
         <v>479</v>
       </c>
       <c r="AV144" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW144" s="1" t="s">
         <v>540</v>
@@ -24271,8 +24263,8 @@
       <c r="K145" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L145" s="1" t="s">
-        <v>1197</v>
+      <c r="L145" s="13">
+        <v>6</v>
       </c>
       <c r="M145">
         <v>200</v>
@@ -24359,7 +24351,7 @@
         <v>232</v>
       </c>
       <c r="AV145" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW145" s="1" t="s">
         <v>542</v>
@@ -24406,8 +24398,8 @@
       <c r="K146" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L146" s="1" t="s">
-        <v>1197</v>
+      <c r="L146" s="13">
+        <v>6</v>
       </c>
       <c r="M146">
         <v>300</v>
@@ -24482,7 +24474,7 @@
         <v>886</v>
       </c>
       <c r="AK146" s="1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="AL146" s="1" t="s">
         <v>886</v>
@@ -24494,7 +24486,7 @@
         <v>544</v>
       </c>
       <c r="AV146" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW146" s="1" t="s">
         <v>545</v>
@@ -24541,8 +24533,8 @@
       <c r="K147" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L147" s="1" t="s">
-        <v>1197</v>
+      <c r="L147" s="13">
+        <v>6</v>
       </c>
       <c r="M147">
         <v>500</v>
@@ -24629,7 +24621,7 @@
         <v>225</v>
       </c>
       <c r="AV147" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW147" s="1" t="s">
         <v>548</v>
@@ -24676,8 +24668,8 @@
       <c r="K148" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L148" s="1" t="s">
-        <v>1197</v>
+      <c r="L148" s="13">
+        <v>6</v>
       </c>
       <c r="M148">
         <v>1000</v>
@@ -24764,7 +24756,7 @@
         <v>550</v>
       </c>
       <c r="AV148" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW148" s="1" t="s">
         <v>551</v>
@@ -24866,7 +24858,7 @@
         <v>886</v>
       </c>
       <c r="AD149" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="AE149" s="1" t="s">
         <v>886</v>
@@ -24881,10 +24873,10 @@
         <v>886</v>
       </c>
       <c r="AJ149" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="AK149" s="1" t="s">
         <v>1199</v>
-      </c>
-      <c r="AK149" s="1" t="s">
-        <v>1201</v>
       </c>
       <c r="AL149" s="1" t="s">
         <v>886</v>
@@ -24896,7 +24888,7 @@
         <v>246</v>
       </c>
       <c r="AV149" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW149" s="1" t="s">
         <v>554</v>
@@ -25034,13 +25026,13 @@
         <v>534</v>
       </c>
       <c r="AS150" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="AU150" s="1" t="s">
         <v>558</v>
       </c>
       <c r="AV150" s="1" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="AW150" s="1" t="s">
         <v>559</v>
@@ -25100,7 +25092,7 @@
         <v>886</v>
       </c>
       <c r="P151" s="1" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="Q151" s="3" t="s">
         <v>886</v>
@@ -25142,7 +25134,7 @@
         <v>886</v>
       </c>
       <c r="AD151" s="3" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="AE151" s="1" t="s">
         <v>886</v>
@@ -25172,19 +25164,19 @@
         <v>886</v>
       </c>
       <c r="AR151" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="AU151" s="1" t="s">
         <v>1204</v>
       </c>
-      <c r="AU151" s="1" t="s">
+      <c r="AV151" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="AV151" s="1" t="s">
+      <c r="AW151" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="AX151" s="1" t="s">
         <v>1208</v>
-      </c>
-      <c r="AW151" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="AX151" s="1" t="s">
-        <v>1210</v>
       </c>
       <c r="AY151">
         <f t="shared" si="2"/>
@@ -25225,8 +25217,8 @@
       <c r="K152" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L152" s="1" t="s">
-        <v>888</v>
+      <c r="L152" s="13">
+        <v>8</v>
       </c>
       <c r="M152">
         <v>25</v>
@@ -25311,7 +25303,7 @@
         <v>566</v>
       </c>
       <c r="AV152" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW152" s="1" t="s">
         <v>567</v>
@@ -25358,8 +25350,8 @@
       <c r="K153" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L153" s="1" t="s">
-        <v>888</v>
+      <c r="L153" s="13">
+        <v>8</v>
       </c>
       <c r="M153">
         <v>50</v>
@@ -25446,7 +25438,7 @@
         <v>479</v>
       </c>
       <c r="AV153" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW153" s="1" t="s">
         <v>569</v>
@@ -25493,8 +25485,8 @@
       <c r="K154" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L154" s="1" t="s">
-        <v>888</v>
+      <c r="L154" s="13">
+        <v>8</v>
       </c>
       <c r="M154">
         <v>100</v>
@@ -25581,7 +25573,7 @@
         <v>479</v>
       </c>
       <c r="AV154" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW154" s="1" t="s">
         <v>571</v>
@@ -25628,8 +25620,8 @@
       <c r="K155" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L155" s="1" t="s">
-        <v>888</v>
+      <c r="L155" s="13">
+        <v>8</v>
       </c>
       <c r="M155">
         <v>200</v>
@@ -25716,7 +25708,7 @@
         <v>313</v>
       </c>
       <c r="AV155" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW155" s="1" t="s">
         <v>573</v>
@@ -25763,8 +25755,8 @@
       <c r="K156" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L156" s="1" t="s">
-        <v>888</v>
+      <c r="L156" s="13">
+        <v>8</v>
       </c>
       <c r="M156">
         <v>300</v>
@@ -25848,13 +25840,13 @@
         <v>886</v>
       </c>
       <c r="AT156" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="AU156" s="1" t="s">
         <v>575</v>
       </c>
       <c r="AV156" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW156" s="1" t="s">
         <v>576</v>
@@ -25901,8 +25893,8 @@
       <c r="K157" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L157" s="1" t="s">
-        <v>888</v>
+      <c r="L157" s="13">
+        <v>8</v>
       </c>
       <c r="M157">
         <v>500</v>
@@ -25989,7 +25981,7 @@
         <v>578</v>
       </c>
       <c r="AV157" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW157" s="1" t="s">
         <v>579</v>
@@ -26036,8 +26028,8 @@
       <c r="K158" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L158" s="1" t="s">
-        <v>888</v>
+      <c r="L158" s="13">
+        <v>8</v>
       </c>
       <c r="M158">
         <v>1000</v>
@@ -26112,7 +26104,7 @@
         <v>886</v>
       </c>
       <c r="AK158" s="1" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="AL158" s="1" t="s">
         <v>886</v>
@@ -26124,7 +26116,7 @@
         <v>581</v>
       </c>
       <c r="AV158" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW158" s="1" t="s">
         <v>582</v>
@@ -26223,7 +26215,7 @@
         <v>886</v>
       </c>
       <c r="AC159" s="1" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="AD159" s="3" t="s">
         <v>886</v>
@@ -26259,7 +26251,7 @@
         <v>587</v>
       </c>
       <c r="AV159" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW159" s="1" t="s">
         <v>588</v>
@@ -26361,7 +26353,7 @@
         <v>886</v>
       </c>
       <c r="AD160" s="3" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="AE160" s="1" t="s">
         <v>886</v>
@@ -26394,16 +26386,16 @@
         <v>591</v>
       </c>
       <c r="AU160" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="AV160" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="AW160" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="AV160" s="1" t="s">
-        <v>1215</v>
-      </c>
-      <c r="AW160" s="1" t="s">
-        <v>1216</v>
-      </c>
       <c r="AX160" s="1" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="AY160">
         <f t="shared" si="2"/>
@@ -26499,7 +26491,7 @@
         <v>886</v>
       </c>
       <c r="AD161" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="AE161" s="1" t="s">
         <v>886</v>
@@ -26532,7 +26524,7 @@
         <v>246</v>
       </c>
       <c r="AV161" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW161" s="1" t="s">
         <v>594</v>
@@ -26579,8 +26571,8 @@
       <c r="K162" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L162" s="1" t="s">
-        <v>888</v>
+      <c r="L162" s="13">
+        <v>8</v>
       </c>
       <c r="M162">
         <v>25</v>
@@ -26663,7 +26655,7 @@
         <v>600</v>
       </c>
       <c r="AV162" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW162" s="1" t="s">
         <v>601</v>
@@ -26710,8 +26702,8 @@
       <c r="K163" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L163" s="1" t="s">
-        <v>888</v>
+      <c r="L163" s="13">
+        <v>8</v>
       </c>
       <c r="M163">
         <v>50</v>
@@ -26798,7 +26790,7 @@
         <v>403</v>
       </c>
       <c r="AV163" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW163" s="1" t="s">
         <v>603</v>
@@ -26845,8 +26837,8 @@
       <c r="K164" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L164" s="1" t="s">
-        <v>888</v>
+      <c r="L164" s="13">
+        <v>8</v>
       </c>
       <c r="M164">
         <v>100</v>
@@ -26933,7 +26925,7 @@
         <v>479</v>
       </c>
       <c r="AV164" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW164" s="1" t="s">
         <v>605</v>
@@ -26980,8 +26972,8 @@
       <c r="K165" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L165" s="1" t="s">
-        <v>888</v>
+      <c r="L165" s="13">
+        <v>8</v>
       </c>
       <c r="M165">
         <v>200</v>
@@ -27061,13 +27053,13 @@
         <v>886</v>
       </c>
       <c r="AS165" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AU165" s="1" t="s">
         <v>608</v>
       </c>
       <c r="AV165" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW165" s="1" t="s">
         <v>609</v>
@@ -27114,8 +27106,8 @@
       <c r="K166" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L166" s="1" t="s">
-        <v>888</v>
+      <c r="L166" s="13">
+        <v>8</v>
       </c>
       <c r="M166">
         <v>300</v>
@@ -27202,7 +27194,7 @@
         <v>452</v>
       </c>
       <c r="AV166" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW166" s="1" t="s">
         <v>611</v>
@@ -27249,8 +27241,8 @@
       <c r="K167" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L167" s="1" t="s">
-        <v>888</v>
+      <c r="L167" s="13">
+        <v>8</v>
       </c>
       <c r="M167">
         <v>500</v>
@@ -27335,7 +27327,7 @@
         <v>613</v>
       </c>
       <c r="AV167" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW167" s="1" t="s">
         <v>614</v>
@@ -27382,8 +27374,8 @@
       <c r="K168" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="L168" s="1" t="s">
-        <v>888</v>
+      <c r="L168" s="13">
+        <v>8</v>
       </c>
       <c r="M168">
         <v>1000</v>
@@ -27471,13 +27463,13 @@
         <v>618</v>
       </c>
       <c r="AT168" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="AU168" s="1" t="s">
         <v>619</v>
       </c>
       <c r="AV168" s="1" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="AW168" s="1" t="s">
         <v>620</v>
@@ -27498,7 +27490,7 @@
         <v>886</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>886</v>
@@ -27606,19 +27598,19 @@
         <v>886</v>
       </c>
       <c r="AM169" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="AU169" s="1" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="AV169" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW169" s="1" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="AX169" s="1" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="AY169">
         <f t="shared" si="2"/>
@@ -27633,7 +27625,7 @@
         <v>886</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>886</v>
@@ -27744,22 +27736,22 @@
         <v>886</v>
       </c>
       <c r="AO170" s="1" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="AP170" s="1" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="AU170" s="1" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="AV170" s="1" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="AW170" s="1" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="AX170" s="1" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="AY170">
         <f t="shared" si="2"/>
@@ -27888,7 +27880,7 @@
         <v>625</v>
       </c>
       <c r="AV171" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW171" s="1" t="s">
         <v>626</v>
@@ -27935,8 +27927,8 @@
       <c r="K172" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L172" s="1" t="s">
-        <v>1253</v>
+      <c r="L172" s="13">
+        <v>10</v>
       </c>
       <c r="M172">
         <v>25</v>
@@ -27996,7 +27988,7 @@
         <v>888</v>
       </c>
       <c r="AF172" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="AG172" s="1" t="s">
         <v>886</v>
@@ -28021,7 +28013,7 @@
         <v>633</v>
       </c>
       <c r="AV172" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW172" s="1" t="s">
         <v>634</v>
@@ -28068,8 +28060,8 @@
       <c r="K173" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L173" s="1" t="s">
-        <v>1253</v>
+      <c r="L173" s="13">
+        <v>10</v>
       </c>
       <c r="M173">
         <v>50</v>
@@ -28153,13 +28145,13 @@
         <v>886</v>
       </c>
       <c r="AT173" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AU173" s="1" t="s">
         <v>637</v>
       </c>
       <c r="AV173" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW173" s="1" t="s">
         <v>638</v>
@@ -28206,8 +28198,8 @@
       <c r="K174" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L174" s="1" t="s">
-        <v>1253</v>
+      <c r="L174" s="13">
+        <v>10</v>
       </c>
       <c r="M174">
         <v>100</v>
@@ -28294,7 +28286,7 @@
         <v>313</v>
       </c>
       <c r="AV174" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW174" s="1" t="s">
         <v>640</v>
@@ -28341,8 +28333,8 @@
       <c r="K175" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L175" s="1" t="s">
-        <v>1253</v>
+      <c r="L175" s="13">
+        <v>10</v>
       </c>
       <c r="M175">
         <v>200</v>
@@ -28369,7 +28361,7 @@
         <v>886</v>
       </c>
       <c r="U175" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="V175" s="1" t="s">
         <v>886</v>
@@ -28429,7 +28421,7 @@
         <v>51</v>
       </c>
       <c r="AV175" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW175" s="1" t="s">
         <v>642</v>
@@ -28476,8 +28468,8 @@
       <c r="K176" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L176" s="1" t="s">
-        <v>1253</v>
+      <c r="L176" s="13">
+        <v>10</v>
       </c>
       <c r="M176">
         <v>300</v>
@@ -28564,7 +28556,7 @@
         <v>479</v>
       </c>
       <c r="AV176" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW176" s="1" t="s">
         <v>644</v>
@@ -28611,8 +28603,8 @@
       <c r="K177" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L177" s="1" t="s">
-        <v>1253</v>
+      <c r="L177" s="13">
+        <v>10</v>
       </c>
       <c r="M177">
         <v>500</v>
@@ -28699,7 +28691,7 @@
         <v>646</v>
       </c>
       <c r="AV177" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW177" s="1" t="s">
         <v>647</v>
@@ -28746,8 +28738,8 @@
       <c r="K178" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L178" s="1" t="s">
-        <v>1253</v>
+      <c r="L178" s="13">
+        <v>10</v>
       </c>
       <c r="M178">
         <v>1000</v>
@@ -28768,40 +28760,40 @@
         <v>886</v>
       </c>
       <c r="S178" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="T178" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="U178" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="V178" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="W178" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="X178" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="Y178" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="Z178" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="AA178" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="AB178" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="AC178" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="AD178" s="3" t="s">
         <v>938</v>
-      </c>
-      <c r="T178" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="U178" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="V178" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="W178" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="X178" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="Y178" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="Z178" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AA178" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="AB178" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="AC178" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="AD178" s="3" t="s">
-        <v>939</v>
       </c>
       <c r="AE178" s="1" t="s">
         <v>886</v>
@@ -28827,13 +28819,13 @@
         <v>886</v>
       </c>
       <c r="AN178" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="AU178" s="1" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="AV178" s="1" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="AW178" s="1" t="s">
         <v>651</v>
@@ -28965,16 +28957,16 @@
         <v>886</v>
       </c>
       <c r="AU179" s="1" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="AV179" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW179" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="AX179" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="AY179">
         <f t="shared" si="2"/>
@@ -29100,16 +29092,16 @@
         <v>886</v>
       </c>
       <c r="AU180" s="1" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="AV180" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW180" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="AX180" s="1" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="AY180">
         <f t="shared" si="2"/>
@@ -29241,16 +29233,16 @@
         <v>632</v>
       </c>
       <c r="AU181" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="AV181" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="AW181" s="1" t="s">
         <v>1248</v>
       </c>
-      <c r="AV181" s="1" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AW181" s="1" t="s">
-        <v>1250</v>
-      </c>
       <c r="AX181" s="1" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="AY181">
         <f t="shared" si="2"/>
@@ -29291,8 +29283,8 @@
       <c r="K182" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L182" s="1" t="s">
-        <v>888</v>
+      <c r="L182" s="13">
+        <v>8</v>
       </c>
       <c r="M182">
         <v>25</v>
@@ -29350,7 +29342,7 @@
         <v>886</v>
       </c>
       <c r="AF182" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="AG182" s="1" t="s">
         <v>886</v>
@@ -29375,13 +29367,13 @@
         <v>716</v>
       </c>
       <c r="AV182" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW182" s="1" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="AX182" s="1" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="AY182">
         <f t="shared" si="2"/>
@@ -29422,8 +29414,8 @@
       <c r="K183" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L183" s="1" t="s">
-        <v>888</v>
+      <c r="L183" s="13">
+        <v>8</v>
       </c>
       <c r="M183">
         <v>50</v>
@@ -29505,13 +29497,13 @@
         <v>886</v>
       </c>
       <c r="AT183" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="AU183" s="1" t="s">
         <v>664</v>
       </c>
       <c r="AV183" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW183" s="1" t="s">
         <v>665</v>
@@ -29558,8 +29550,8 @@
       <c r="K184" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L184" s="1" t="s">
-        <v>888</v>
+      <c r="L184" s="13">
+        <v>8</v>
       </c>
       <c r="M184">
         <v>100</v>
@@ -29641,13 +29633,13 @@
         <v>886</v>
       </c>
       <c r="AT184" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AU184" s="1" t="s">
         <v>667</v>
       </c>
       <c r="AV184" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW184" s="1" t="s">
         <v>668</v>
@@ -29694,8 +29686,8 @@
       <c r="K185" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L185" s="1" t="s">
-        <v>888</v>
+      <c r="L185" s="13">
+        <v>8</v>
       </c>
       <c r="M185">
         <v>200</v>
@@ -29780,7 +29772,7 @@
         <v>671</v>
       </c>
       <c r="AV185" s="1" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="AW185" s="1" t="s">
         <v>672</v>
@@ -29827,8 +29819,8 @@
       <c r="K186" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L186" s="1" t="s">
-        <v>888</v>
+      <c r="L186" s="13">
+        <v>8</v>
       </c>
       <c r="M186">
         <v>300</v>
@@ -29919,7 +29911,7 @@
         <v>675</v>
       </c>
       <c r="AV186" s="1" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="AW186" s="1" t="s">
         <v>676</v>
@@ -29966,8 +29958,8 @@
       <c r="K187" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L187" s="1" t="s">
-        <v>888</v>
+      <c r="L187" s="13">
+        <v>8</v>
       </c>
       <c r="M187">
         <v>500</v>
@@ -30052,7 +30044,7 @@
         <v>232</v>
       </c>
       <c r="AV187" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW187" s="1" t="s">
         <v>678</v>
@@ -30099,8 +30091,8 @@
       <c r="K188" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L188" s="1" t="s">
-        <v>888</v>
+      <c r="L188" s="13">
+        <v>8</v>
       </c>
       <c r="M188">
         <v>1000</v>
@@ -30142,7 +30134,7 @@
         <v>886</v>
       </c>
       <c r="Z188" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="AA188" s="3" t="s">
         <v>886</v>
@@ -30185,10 +30177,10 @@
         <v>681</v>
       </c>
       <c r="AU188" s="1" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="AV188" s="1" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="AW188" s="1" t="s">
         <v>682</v>
@@ -30318,22 +30310,22 @@
         <v>886</v>
       </c>
       <c r="AS189" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="AT189" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AU189" s="1" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="AV189" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW189" s="1" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="AX189" s="1" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="AY189">
         <f t="shared" si="2"/>
@@ -30348,7 +30340,7 @@
         <v>886</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>886</v>
@@ -30457,22 +30449,22 @@
         <v>886</v>
       </c>
       <c r="AQ190" s="1" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="AR190" s="1" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="AU190" s="1" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="AV190" s="1" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="AW190" s="1" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="AX190" s="1" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="AY190">
         <f t="shared" si="2"/>
@@ -30529,7 +30521,7 @@
         <v>886</v>
       </c>
       <c r="Q191" s="3" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="R191" s="1" t="s">
         <v>886</v>
@@ -30599,19 +30591,19 @@
         <v>636</v>
       </c>
       <c r="AS191" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="AU191" s="1" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="AV191" s="1" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="AW191" s="1" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="AX191" s="1" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="AY191">
         <f t="shared" si="2"/>
@@ -30652,8 +30644,8 @@
       <c r="K192" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L192" s="1" t="s">
-        <v>888</v>
+      <c r="L192" s="13">
+        <v>8</v>
       </c>
       <c r="M192">
         <v>25</v>
@@ -30735,13 +30727,13 @@
         <v>886</v>
       </c>
       <c r="AT192" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AU192" s="1" t="s">
         <v>691</v>
       </c>
       <c r="AV192" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW192" s="1" t="s">
         <v>692</v>
@@ -30788,20 +30780,20 @@
       <c r="K193" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L193" s="1" t="s">
-        <v>888</v>
+      <c r="L193" s="13">
+        <v>8</v>
       </c>
       <c r="M193">
         <v>50</v>
       </c>
       <c r="N193" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="O193" s="3" t="s">
         <v>886</v>
       </c>
       <c r="P193" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="Q193" s="3" t="s">
         <v>886</v>
@@ -30874,7 +30866,7 @@
         <v>225</v>
       </c>
       <c r="AV193" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW193" s="1" t="s">
         <v>694</v>
@@ -30921,8 +30913,8 @@
       <c r="K194" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L194" s="1" t="s">
-        <v>888</v>
+      <c r="L194" s="13">
+        <v>8</v>
       </c>
       <c r="M194">
         <v>100</v>
@@ -31004,13 +30996,13 @@
         <v>886</v>
       </c>
       <c r="AS194" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="AU194" s="1" t="s">
         <v>696</v>
       </c>
       <c r="AV194" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW194" s="1" t="s">
         <v>697</v>
@@ -31057,8 +31049,8 @@
       <c r="K195" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L195" s="1" t="s">
-        <v>888</v>
+      <c r="L195" s="13">
+        <v>8</v>
       </c>
       <c r="M195">
         <v>200</v>
@@ -31143,7 +31135,7 @@
         <v>700</v>
       </c>
       <c r="AV195" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW195" s="1" t="s">
         <v>701</v>
@@ -31190,8 +31182,8 @@
       <c r="K196" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L196" s="1" t="s">
-        <v>888</v>
+      <c r="L196" s="13">
+        <v>8</v>
       </c>
       <c r="M196">
         <v>300</v>
@@ -31276,7 +31268,7 @@
         <v>479</v>
       </c>
       <c r="AV196" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW196" s="1" t="s">
         <v>703</v>
@@ -31323,8 +31315,8 @@
       <c r="K197" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L197" s="1" t="s">
-        <v>888</v>
+      <c r="L197" s="13">
+        <v>8</v>
       </c>
       <c r="M197">
         <v>500</v>
@@ -31409,7 +31401,7 @@
         <v>705</v>
       </c>
       <c r="AV197" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW197" s="1" t="s">
         <v>706</v>
@@ -31456,8 +31448,8 @@
       <c r="K198" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="L198" s="1" t="s">
-        <v>888</v>
+      <c r="L198" s="13">
+        <v>8</v>
       </c>
       <c r="M198">
         <v>1000</v>
@@ -31469,7 +31461,7 @@
         <v>886</v>
       </c>
       <c r="P198" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="Q198" s="1" t="s">
         <v>886</v>
@@ -31542,10 +31534,10 @@
         <v>709</v>
       </c>
       <c r="AU198" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="AV198" s="1" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="AW198" s="1" t="s">
         <v>710</v>
@@ -31678,7 +31670,7 @@
         <v>225</v>
       </c>
       <c r="AV199" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW199" s="1" t="s">
         <v>713</v>
@@ -31736,7 +31728,7 @@
       </c>
       <c r="O200" s="1"/>
       <c r="P200" s="1" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="Q200" s="3" t="s">
         <v>886</v>
@@ -31778,7 +31770,7 @@
         <v>886</v>
       </c>
       <c r="AD200" s="3" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="AE200" s="1" t="s">
         <v>886</v>
@@ -31806,19 +31798,19 @@
         <v>886</v>
       </c>
       <c r="AN200" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="AU200" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="AV200" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="AW200" s="1" t="s">
         <v>1274</v>
       </c>
-      <c r="AU200" s="1" t="s">
-        <v>1275</v>
-      </c>
-      <c r="AV200" s="1" t="s">
-        <v>1276</v>
-      </c>
-      <c r="AW200" s="1" t="s">
-        <v>1277</v>
-      </c>
       <c r="AX200" s="1" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="AY200">
         <f t="shared" si="3"/>
@@ -31942,13 +31934,13 @@
         <v>886</v>
       </c>
       <c r="AQ201" s="1" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="AU201" s="1" t="s">
         <v>719</v>
       </c>
       <c r="AV201" s="1" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="AW201" s="1" t="s">
         <v>720</v>
@@ -31995,8 +31987,8 @@
       <c r="K202" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L202" s="1" t="s">
-        <v>888</v>
+      <c r="L202" s="13">
+        <v>8</v>
       </c>
       <c r="M202">
         <v>25</v>
@@ -32056,7 +32048,7 @@
         <v>886</v>
       </c>
       <c r="AF202" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="AG202" s="1" t="s">
         <v>886</v>
@@ -32081,7 +32073,7 @@
         <v>716</v>
       </c>
       <c r="AV202" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW202" s="1" t="s">
         <v>728</v>
@@ -32128,8 +32120,8 @@
       <c r="K203" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L203" s="1" t="s">
-        <v>888</v>
+      <c r="L203" s="13">
+        <v>8</v>
       </c>
       <c r="M203">
         <v>50</v>
@@ -32214,7 +32206,7 @@
         <v>730</v>
       </c>
       <c r="AV203" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW203" s="1" t="s">
         <v>731</v>
@@ -32261,8 +32253,8 @@
       <c r="K204" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L204" s="1" t="s">
-        <v>888</v>
+      <c r="L204" s="13">
+        <v>8</v>
       </c>
       <c r="M204">
         <v>100</v>
@@ -32347,7 +32339,7 @@
         <v>733</v>
       </c>
       <c r="AV204" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW204" s="1" t="s">
         <v>734</v>
@@ -32394,8 +32386,8 @@
       <c r="K205" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L205" s="1" t="s">
-        <v>888</v>
+      <c r="L205" s="13">
+        <v>8</v>
       </c>
       <c r="M205">
         <v>200</v>
@@ -32416,7 +32408,7 @@
         <v>886</v>
       </c>
       <c r="S205" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="T205" s="1" t="s">
         <v>886</v>
@@ -32486,7 +32478,7 @@
         <v>452</v>
       </c>
       <c r="AV205" s="1" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="AW205" s="1" t="s">
         <v>736</v>
@@ -32533,8 +32525,8 @@
       <c r="K206" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L206" s="1" t="s">
-        <v>888</v>
+      <c r="L206" s="13">
+        <v>8</v>
       </c>
       <c r="M206">
         <v>300</v>
@@ -32588,7 +32580,7 @@
         <v>886</v>
       </c>
       <c r="AD206" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="AE206" s="1" t="s">
         <v>886</v>
@@ -32622,10 +32614,10 @@
         <v>738</v>
       </c>
       <c r="AU206" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="AV206" s="1" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="AW206" s="1" t="s">
         <v>739</v>
@@ -32672,8 +32664,8 @@
       <c r="K207" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L207" s="1" t="s">
-        <v>888</v>
+      <c r="L207" s="13">
+        <v>8</v>
       </c>
       <c r="M207">
         <v>500</v>
@@ -32727,7 +32719,7 @@
         <v>886</v>
       </c>
       <c r="AD207" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="AE207" s="1" t="s">
         <v>886</v>
@@ -32761,13 +32753,13 @@
         <v>727</v>
       </c>
       <c r="AT207" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="AU207" s="1" t="s">
         <v>742</v>
       </c>
       <c r="AV207" s="1" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="AW207" s="1" t="s">
         <v>743</v>
@@ -32814,8 +32806,8 @@
       <c r="K208" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L208" s="1" t="s">
-        <v>888</v>
+      <c r="L208" s="13">
+        <v>8</v>
       </c>
       <c r="M208">
         <v>1000</v>
@@ -32900,7 +32892,7 @@
         <v>746</v>
       </c>
       <c r="AV208" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW208" s="1" t="s">
         <v>747</v>
@@ -33036,16 +33028,16 @@
         <v>738</v>
       </c>
       <c r="AU209" s="1" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="AV209" s="1" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="AW209" s="1" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="AX209" s="1" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="AY209">
         <f t="shared" si="3"/>
@@ -33157,7 +33149,7 @@
         <v>886</v>
       </c>
       <c r="AJ210" s="1" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="AK210" s="1" t="s">
         <v>727</v>
@@ -33169,28 +33161,28 @@
         <v>886</v>
       </c>
       <c r="AN210" s="1" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="AO210" s="1" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="AP210" s="1" t="s">
         <v>727</v>
       </c>
       <c r="AQ210" s="1" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="AU210" s="1" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="AV210" s="1" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="AW210" s="1" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="AX210" s="1" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="AY210">
         <f t="shared" si="3"/>
@@ -33314,19 +33306,19 @@
         <v>886</v>
       </c>
       <c r="AP211" s="1" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="AQ211" s="1" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="AU211" s="1" t="s">
         <v>754</v>
       </c>
       <c r="AV211" s="1" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="AW211" s="1" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="AX211" s="1" t="s">
         <v>755</v>
@@ -33370,8 +33362,8 @@
       <c r="K212" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L212" s="1" t="s">
-        <v>888</v>
+      <c r="L212" s="13">
+        <v>8</v>
       </c>
       <c r="M212">
         <v>25</v>
@@ -33456,7 +33448,7 @@
         <v>348</v>
       </c>
       <c r="AV212" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW212" s="1" t="s">
         <v>760</v>
@@ -33503,8 +33495,8 @@
       <c r="K213" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L213" s="1" t="s">
-        <v>888</v>
+      <c r="L213" s="13">
+        <v>8</v>
       </c>
       <c r="M213">
         <v>50</v>
@@ -33592,7 +33584,7 @@
         <v>763</v>
       </c>
       <c r="AV213" s="1" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="AW213" s="1" t="s">
         <v>764</v>
@@ -33639,8 +33631,8 @@
       <c r="K214" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L214" s="1" t="s">
-        <v>888</v>
+      <c r="L214" s="13">
+        <v>8</v>
       </c>
       <c r="M214">
         <v>100</v>
@@ -33722,13 +33714,13 @@
         <v>886</v>
       </c>
       <c r="AT214" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="AU214" s="1" t="s">
         <v>766</v>
       </c>
       <c r="AV214" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW214" s="1" t="s">
         <v>767</v>
@@ -33775,8 +33767,8 @@
       <c r="K215" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L215" s="1" t="s">
-        <v>888</v>
+      <c r="L215" s="13">
+        <v>8</v>
       </c>
       <c r="M215">
         <v>200</v>
@@ -33788,7 +33780,7 @@
         <v>886</v>
       </c>
       <c r="P215" s="1" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="Q215" s="3" t="s">
         <v>886</v>
@@ -33861,7 +33853,7 @@
         <v>452</v>
       </c>
       <c r="AV215" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW215" s="1" t="s">
         <v>770</v>
@@ -33882,7 +33874,7 @@
         <v>757</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>758</v>
@@ -33908,8 +33900,8 @@
       <c r="K216" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L216" s="1" t="s">
-        <v>888</v>
+      <c r="L216" s="13">
+        <v>8</v>
       </c>
       <c r="M216">
         <v>300</v>
@@ -33945,7 +33937,7 @@
         <v>886</v>
       </c>
       <c r="X216" s="1" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="Y216" s="1" t="s">
         <v>886</v>
@@ -33994,7 +33986,7 @@
         <v>156</v>
       </c>
       <c r="AV216" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW216" s="1" t="s">
         <v>771</v>
@@ -34041,8 +34033,8 @@
       <c r="K217" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L217" s="1" t="s">
-        <v>888</v>
+      <c r="L217" s="13">
+        <v>8</v>
       </c>
       <c r="M217">
         <v>500</v>
@@ -34127,7 +34119,7 @@
         <v>773</v>
       </c>
       <c r="AV217" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW217" s="1" t="s">
         <v>774</v>
@@ -34174,8 +34166,8 @@
       <c r="K218" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L218" s="1" t="s">
-        <v>888</v>
+      <c r="L218" s="13">
+        <v>8</v>
       </c>
       <c r="M218">
         <v>1000</v>
@@ -34196,7 +34188,7 @@
         <v>886</v>
       </c>
       <c r="S218" s="3" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="T218" s="1" t="s">
         <v>904</v>
@@ -34269,13 +34261,13 @@
         <v>778</v>
       </c>
       <c r="AS218" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="AU218" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AV218" s="1" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="AW218" s="1" t="s">
         <v>779</v>
@@ -34377,7 +34369,7 @@
         <v>886</v>
       </c>
       <c r="AD219" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="AE219" s="1" t="s">
         <v>886</v>
@@ -34408,19 +34400,19 @@
         <v>727</v>
       </c>
       <c r="AQ219" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AU219" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AV219" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AW219" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AX219" s="1" t="s">
         <v>1296</v>
-      </c>
-      <c r="AU219" s="1" t="s">
-        <v>1300</v>
-      </c>
-      <c r="AV219" s="1" t="s">
-        <v>1298</v>
-      </c>
-      <c r="AW219" s="1" t="s">
-        <v>1301</v>
-      </c>
-      <c r="AX219" s="1" t="s">
-        <v>1299</v>
       </c>
       <c r="AY219">
         <f t="shared" si="3"/>
@@ -34547,7 +34539,7 @@
         <v>313</v>
       </c>
       <c r="AV220" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW220" s="1" t="s">
         <v>784</v>
@@ -34680,7 +34672,7 @@
         <v>225</v>
       </c>
       <c r="AV221" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW221" s="1" t="s">
         <v>787</v>
@@ -34727,8 +34719,8 @@
       <c r="K222" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L222" s="1" t="s">
-        <v>888</v>
+      <c r="L222" s="13">
+        <v>10</v>
       </c>
       <c r="M222">
         <v>25</v>
@@ -34810,13 +34802,13 @@
         <v>886</v>
       </c>
       <c r="AS222" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="AU222" s="1" t="s">
         <v>791</v>
       </c>
       <c r="AV222" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW222" s="1" t="s">
         <v>792</v>
@@ -34863,8 +34855,8 @@
       <c r="K223" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L223" s="1" t="s">
-        <v>888</v>
+      <c r="L223" s="13">
+        <v>10</v>
       </c>
       <c r="M223">
         <v>50</v>
@@ -34955,7 +34947,7 @@
         <v>225</v>
       </c>
       <c r="AV223" s="1" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="AW223" s="1" t="s">
         <v>795</v>
@@ -35002,8 +34994,8 @@
       <c r="K224" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L224" s="1" t="s">
-        <v>888</v>
+      <c r="L224" s="13">
+        <v>10</v>
       </c>
       <c r="M224">
         <v>100</v>
@@ -35088,13 +35080,13 @@
         <v>727</v>
       </c>
       <c r="AT224" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="AU224" s="1" t="s">
         <v>797</v>
       </c>
       <c r="AV224" s="1" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="AW224" s="1" t="s">
         <v>798</v>
@@ -35141,8 +35133,8 @@
       <c r="K225" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L225" s="1" t="s">
-        <v>888</v>
+      <c r="L225" s="13">
+        <v>10</v>
       </c>
       <c r="M225">
         <v>200</v>
@@ -35233,7 +35225,7 @@
         <v>800</v>
       </c>
       <c r="AV225" s="1" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="AW225" s="1" t="s">
         <v>801</v>
@@ -35280,8 +35272,8 @@
       <c r="K226" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L226" s="1" t="s">
-        <v>888</v>
+      <c r="L226" s="13">
+        <v>10</v>
       </c>
       <c r="M226">
         <v>300</v>
@@ -35372,7 +35364,7 @@
         <v>797</v>
       </c>
       <c r="AV226" s="1" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="AW226" s="1" t="s">
         <v>803</v>
@@ -35419,8 +35411,8 @@
       <c r="K227" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L227" s="1" t="s">
-        <v>888</v>
+      <c r="L227" s="13">
+        <v>10</v>
       </c>
       <c r="M227">
         <v>500</v>
@@ -35505,7 +35497,7 @@
         <v>805</v>
       </c>
       <c r="AV227" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW227" s="1" t="s">
         <v>806</v>
@@ -35552,8 +35544,8 @@
       <c r="K228" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="L228" s="1" t="s">
-        <v>888</v>
+      <c r="L228" s="13">
+        <v>10</v>
       </c>
       <c r="M228">
         <v>1000</v>
@@ -35635,13 +35627,13 @@
         <v>886</v>
       </c>
       <c r="AS228" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="AU228" s="1" t="s">
         <v>809</v>
       </c>
       <c r="AV228" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW228" s="1" t="s">
         <v>810</v>
@@ -35776,7 +35768,7 @@
         <v>813</v>
       </c>
       <c r="AV229" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AW229" s="1" t="s">
         <v>814</v>
@@ -35923,7 +35915,7 @@
         <v>817</v>
       </c>
       <c r="AV230" s="1" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="AW230" s="1" t="s">
         <v>818</v>
@@ -36070,7 +36062,7 @@
         <v>225</v>
       </c>
       <c r="AV231" s="1" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="AW231" s="1" t="s">
         <v>821</v>
@@ -36107,352 +36099,352 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
@@ -36462,62 +36454,62 @@
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
@@ -36817,7 +36809,7 @@
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
@@ -36827,7 +36819,7 @@
     </row>
     <row r="145" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\idle-rpg-wind-chaser-20261006\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D218EB1-D107-4888-86BB-3B66C6082E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FC168D-6EC8-440B-8A1E-C3CD01472260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9742" uniqueCount="1305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9742" uniqueCount="1307">
   <si>
     <t>群組ID</t>
   </si>
@@ -2764,9 +2764,6 @@
   </si>
   <si>
     <t>30</t>
-  </si>
-  <si>
-    <t>{"sec":8,"secPer":-0.5}</t>
   </si>
   <si>
     <t>50.4</t>
@@ -4110,10 +4107,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"times":1,"timesPer":0.1,"pct":50,"pctPer":5}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>{"pct":150,"pctPer":15,"count":2}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4171,6 +4164,22 @@
   </si>
   <si>
     <t>命中時有 {chance}% 機率觸發真空迴旋，對該敵人造成 {hits} 段傷害，每段造成 {pct}% 風系傷害，且迴旋斬傷害 +{cleavePct}%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"times":1.5,"timesPer":0.15,"pct":150,"pctPer":15}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>迴旋斬範圍擴大 {range}%，並改為被動技能：不再主動施放，改為每 {sec} 秒自動施放 1 次</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"sec":8,"secPer":-0.4}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>12</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4785,31 +4794,31 @@
         <v>17</v>
       </c>
       <c r="AN1" s="8" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AO1" s="8" t="s">
         <v>1053</v>
       </c>
-      <c r="AO1" s="8" t="s">
+      <c r="AP1" s="8" t="s">
         <v>1054</v>
       </c>
-      <c r="AP1" s="8" t="s">
+      <c r="AQ1" s="8" t="s">
         <v>1055</v>
       </c>
-      <c r="AQ1" s="8" t="s">
+      <c r="AR1" s="8" t="s">
         <v>1056</v>
       </c>
-      <c r="AR1" s="8" t="s">
-        <v>1057</v>
-      </c>
       <c r="AS1" s="10" t="s">
+        <v>952</v>
+      </c>
+      <c r="AT1" s="10" t="s">
         <v>953</v>
-      </c>
-      <c r="AT1" s="10" t="s">
-        <v>954</v>
       </c>
       <c r="AU1" s="8" t="s">
         <v>18</v>
       </c>
       <c r="AV1" s="8" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="AW1" s="8" t="s">
         <v>21</v>
@@ -4940,7 +4949,7 @@
         <v>31</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW2" s="1" t="s">
         <v>32</v>
@@ -4991,7 +5000,7 @@
         <v>8</v>
       </c>
       <c r="M3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>867</v>
@@ -5075,7 +5084,7 @@
         <v>34</v>
       </c>
       <c r="AV3" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW3" s="1" t="s">
         <v>35</v>
@@ -5126,7 +5135,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>867</v>
@@ -5210,10 +5219,10 @@
         <v>39</v>
       </c>
       <c r="AV4" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW4" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="AX4" s="1" t="s">
         <v>40</v>
@@ -5261,7 +5270,7 @@
         <v>8</v>
       </c>
       <c r="M5">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>867</v>
@@ -5345,7 +5354,7 @@
         <v>881</v>
       </c>
       <c r="AV5" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW5" s="1" t="s">
         <v>43</v>
@@ -5396,7 +5405,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>867</v>
@@ -5480,7 +5489,7 @@
         <v>47</v>
       </c>
       <c r="AV6" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW6" s="1" t="s">
         <v>48</v>
@@ -5531,7 +5540,7 @@
         <v>8</v>
       </c>
       <c r="M7">
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>867</v>
@@ -5615,7 +5624,7 @@
         <v>51</v>
       </c>
       <c r="AV7" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW7" s="1" t="s">
         <v>52</v>
@@ -5636,7 +5645,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>26</v>
@@ -5666,7 +5675,7 @@
         <v>8</v>
       </c>
       <c r="M8">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>867</v>
@@ -5747,16 +5756,16 @@
         <v>867</v>
       </c>
       <c r="AU8" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="AV8" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW8" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="AX8" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="AY8">
         <f t="shared" si="0"/>
@@ -5801,7 +5810,7 @@
         <v>867</v>
       </c>
       <c r="M9">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>867</v>
@@ -5882,19 +5891,19 @@
         <v>867</v>
       </c>
       <c r="AS9" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AU9" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="AV9" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW9" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="AX9" s="1" t="s">
         <v>1285</v>
-      </c>
-      <c r="AX9" s="1" t="s">
-        <v>1286</v>
       </c>
       <c r="AY9">
         <f t="shared" si="0"/>
@@ -5939,7 +5948,7 @@
         <v>867</v>
       </c>
       <c r="M10">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>867</v>
@@ -6020,13 +6029,13 @@
         <v>867</v>
       </c>
       <c r="AT10" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="AU10" s="1" t="s">
         <v>60</v>
       </c>
       <c r="AV10" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW10" s="1" t="s">
         <v>61</v>
@@ -6077,7 +6086,7 @@
         <v>867</v>
       </c>
       <c r="M11">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>867</v>
@@ -6161,13 +6170,13 @@
         <v>65</v>
       </c>
       <c r="AV11" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW11" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="AX11" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="AY11">
         <f t="shared" si="0"/>
@@ -6221,7 +6230,7 @@
         <v>867</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>890</v>
+        <v>1306</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>867</v>
@@ -6296,7 +6305,7 @@
         <v>70</v>
       </c>
       <c r="AV12" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW12" s="1" t="s">
         <v>71</v>
@@ -6431,7 +6440,7 @@
         <v>51</v>
       </c>
       <c r="AV13" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW13" s="1" t="s">
         <v>73</v>
@@ -6566,7 +6575,7 @@
         <v>75</v>
       </c>
       <c r="AV14" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW14" s="1" t="s">
         <v>76</v>
@@ -6701,7 +6710,7 @@
         <v>78</v>
       </c>
       <c r="AV15" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW15" s="1" t="s">
         <v>79</v>
@@ -6829,13 +6838,13 @@
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
       <c r="AT16" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AU16" s="1" t="s">
         <v>81</v>
       </c>
       <c r="AV16" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW16" s="1" t="s">
         <v>82</v>
@@ -6966,7 +6975,7 @@
         <v>51</v>
       </c>
       <c r="AV17" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW17" s="1" t="s">
         <v>85</v>
@@ -7094,10 +7103,10 @@
       <c r="AL18" s="1"/>
       <c r="AM18" s="1"/>
       <c r="AU18" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="AV18" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW18" s="1" t="s">
         <v>88</v>
@@ -7217,16 +7226,16 @@
         <v>867</v>
       </c>
       <c r="AJ19" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
       <c r="AU19" s="1" t="s">
-        <v>1289</v>
+        <v>1303</v>
       </c>
       <c r="AV19" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW19" s="1" t="s">
         <v>91</v>
@@ -7328,7 +7337,7 @@
         <v>867</v>
       </c>
       <c r="AD20" s="3" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="AE20" s="1" t="s">
         <v>867</v>
@@ -7346,13 +7355,13 @@
         <v>867</v>
       </c>
       <c r="AJ20" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="AK20" s="1"/>
       <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
       <c r="AN20" s="1" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="AP20" s="1" t="s">
         <v>709</v>
@@ -7361,16 +7370,16 @@
         <v>94</v>
       </c>
       <c r="AU20" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="AV20" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="AW20" s="1" t="s">
         <v>1302</v>
       </c>
-      <c r="AV20" s="1" t="s">
-        <v>1303</v>
-      </c>
-      <c r="AW20" s="1" t="s">
-        <v>1304</v>
-      </c>
       <c r="AX20" s="1" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="AY20">
         <f t="shared" si="0"/>
@@ -7496,20 +7505,20 @@
         <v>867</v>
       </c>
       <c r="AU21" s="1" t="s">
-        <v>901</v>
+        <v>1305</v>
       </c>
       <c r="AV21" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW21" s="1" t="s">
-        <v>97</v>
+        <v>1304</v>
       </c>
       <c r="AX21" s="1" t="s">
         <v>97</v>
       </c>
       <c r="AY21">
         <f t="shared" si="0"/>
-        <v>78</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:51" x14ac:dyDescent="0.25">
@@ -7607,7 +7616,7 @@
         <v>876</v>
       </c>
       <c r="AF22" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="AG22" s="1" t="s">
         <v>867</v>
@@ -7631,10 +7640,10 @@
         <v>867</v>
       </c>
       <c r="AU22" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="AV22" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW22" s="1" t="s">
         <v>102</v>
@@ -7769,7 +7778,7 @@
         <v>104</v>
       </c>
       <c r="AV23" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW23" s="1" t="s">
         <v>105</v>
@@ -7904,7 +7913,7 @@
         <v>107</v>
       </c>
       <c r="AV24" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW24" s="1" t="s">
         <v>108</v>
@@ -8036,10 +8045,10 @@
         <v>867</v>
       </c>
       <c r="AU25" s="1" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="AV25" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW25" s="1" t="s">
         <v>110</v>
@@ -8171,10 +8180,10 @@
         <v>867</v>
       </c>
       <c r="AU26" s="1" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="AV26" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW26" s="1" t="s">
         <v>112</v>
@@ -8306,10 +8315,10 @@
         <v>867</v>
       </c>
       <c r="AU27" s="1" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AV27" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW27" s="1" t="s">
         <v>115</v>
@@ -8444,7 +8453,7 @@
         <v>118</v>
       </c>
       <c r="AV28" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW28" s="1" t="s">
         <v>119</v>
@@ -8579,7 +8588,7 @@
         <v>123</v>
       </c>
       <c r="AV29" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW29" s="1" t="s">
         <v>124</v>
@@ -8711,13 +8720,13 @@
         <v>867</v>
       </c>
       <c r="AS30" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="AU30" s="1" t="s">
         <v>128</v>
       </c>
       <c r="AV30" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW30" s="1" t="s">
         <v>129</v>
@@ -8849,10 +8858,10 @@
         <v>867</v>
       </c>
       <c r="AU31" s="1" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="AV31" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW31" s="1" t="s">
         <v>133</v>
@@ -8954,7 +8963,7 @@
         <v>867</v>
       </c>
       <c r="AD32" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="AE32" s="1" t="s">
         <v>867</v>
@@ -8987,10 +8996,10 @@
         <v>138</v>
       </c>
       <c r="AV32" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW32" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="AX32" s="1" t="s">
         <v>139</v>
@@ -9119,10 +9128,10 @@
         <v>867</v>
       </c>
       <c r="AU33" s="1" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="AV33" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW33" s="1" t="s">
         <v>142</v>
@@ -9254,10 +9263,10 @@
         <v>867</v>
       </c>
       <c r="AU34" s="1" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="AV34" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW34" s="1" t="s">
         <v>145</v>
@@ -9314,7 +9323,7 @@
         <v>867</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>867</v>
@@ -9389,10 +9398,10 @@
         <v>867</v>
       </c>
       <c r="AU35" s="1" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="AV35" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW35" s="1" t="s">
         <v>148</v>
@@ -9524,13 +9533,13 @@
         <v>867</v>
       </c>
       <c r="AS36" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="AU36" s="1" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="AV36" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW36" s="1" t="s">
         <v>150</v>
@@ -9665,7 +9674,7 @@
         <v>152</v>
       </c>
       <c r="AV37" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW37" s="1" t="s">
         <v>153</v>
@@ -9800,7 +9809,7 @@
         <v>157</v>
       </c>
       <c r="AV38" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW38" s="1" t="s">
         <v>158</v>
@@ -9857,52 +9866,52 @@
         <v>867</v>
       </c>
       <c r="O39" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="P39" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="P39" s="1" t="s">
+      <c r="Q39" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="S39" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="V39" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="X39" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="Y39" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="Z39" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AA39" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AB39" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AC39" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AD39" s="3" t="s">
         <v>905</v>
-      </c>
-      <c r="Q39" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="R39" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="S39" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="U39" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="V39" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="W39" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="X39" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="Y39" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="Z39" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AA39" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AB39" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AC39" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AD39" s="3" t="s">
-        <v>906</v>
       </c>
       <c r="AE39" s="1" t="s">
         <v>867</v>
@@ -9935,10 +9944,10 @@
         <v>161</v>
       </c>
       <c r="AU39" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="AV39" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="AW39" s="1" t="s">
         <v>162</v>
@@ -9959,7 +9968,7 @@
         <v>867</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>867</v>
@@ -10076,13 +10085,13 @@
         <v>295</v>
       </c>
       <c r="AV40" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="AW40" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AX40" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AY40">
         <f t="shared" si="0"/>
@@ -10208,10 +10217,10 @@
         <v>867</v>
       </c>
       <c r="AU41" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="AV41" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW41" s="1" t="s">
         <v>169</v>
@@ -10341,13 +10350,13 @@
         <v>867</v>
       </c>
       <c r="AT42" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AU42" s="1" t="s">
         <v>175</v>
       </c>
       <c r="AV42" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW42" s="1" t="s">
         <v>176</v>
@@ -10478,7 +10487,7 @@
         <v>178</v>
       </c>
       <c r="AV43" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW43" s="1" t="s">
         <v>179</v>
@@ -10613,7 +10622,7 @@
         <v>181</v>
       </c>
       <c r="AV44" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW44" s="1" t="s">
         <v>182</v>
@@ -10743,13 +10752,13 @@
         <v>867</v>
       </c>
       <c r="AT45" s="1" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="AU45" s="1" t="s">
         <v>185</v>
       </c>
       <c r="AV45" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW45" s="1" t="s">
         <v>186</v>
@@ -10764,7 +10773,7 @@
     </row>
     <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>172</v>
@@ -10857,7 +10866,7 @@
         <v>867</v>
       </c>
       <c r="AF46" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AG46" s="1" t="s">
         <v>867</v>
@@ -10881,7 +10890,7 @@
         <v>867</v>
       </c>
       <c r="AO46" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="AP46" s="1" t="s">
         <v>184</v>
@@ -10890,7 +10899,7 @@
         <v>188</v>
       </c>
       <c r="AV46" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AW46" s="1" t="s">
         <v>189</v>
@@ -11024,7 +11033,7 @@
         <v>193</v>
       </c>
       <c r="AV47" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="AW47" s="1" t="s">
         <v>194</v>
@@ -11045,7 +11054,7 @@
         <v>172</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>173</v>
@@ -11151,13 +11160,13 @@
         <v>867</v>
       </c>
       <c r="AN48" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="AU48" s="1" t="s">
         <v>196</v>
       </c>
       <c r="AV48" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="AW48" s="1" t="s">
         <v>197</v>
@@ -11290,13 +11299,13 @@
         <v>867</v>
       </c>
       <c r="AS49" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="AU49" s="1" t="s">
         <v>200</v>
       </c>
       <c r="AV49" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW49" s="1" t="s">
         <v>201</v>
@@ -11398,7 +11407,7 @@
         <v>867</v>
       </c>
       <c r="AD50" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="AE50" s="1" t="s">
         <v>867</v>
@@ -11430,16 +11439,16 @@
         <v>867</v>
       </c>
       <c r="AS50" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="AT50" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="AU50" s="1" t="s">
         <v>204</v>
       </c>
       <c r="AV50" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="AW50" s="1" t="s">
         <v>205</v>
@@ -11460,7 +11469,7 @@
         <v>867</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>867</v>
@@ -11547,7 +11556,7 @@
         <v>867</v>
       </c>
       <c r="AF51" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AG51" s="1" t="s">
         <v>867</v>
@@ -11572,19 +11581,19 @@
         <v>192</v>
       </c>
       <c r="AO51" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="AU51" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="AV51" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="AU51" s="1" t="s">
+      <c r="AW51" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="AV51" s="1" t="s">
-        <v>1068</v>
-      </c>
-      <c r="AW51" s="1" t="s">
-        <v>947</v>
-      </c>
       <c r="AX51" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="AY51">
         <f t="shared" si="0"/>
@@ -11709,13 +11718,13 @@
         <v>212</v>
       </c>
       <c r="AV52" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW52" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="AX52" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="AY52">
         <f t="shared" si="0"/>
@@ -11842,13 +11851,13 @@
         <v>214</v>
       </c>
       <c r="AV53" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW53" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="AX53" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="AY53">
         <f t="shared" si="0"/>
@@ -11975,7 +11984,7 @@
         <v>216</v>
       </c>
       <c r="AV54" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW54" s="1" t="s">
         <v>217</v>
@@ -12107,13 +12116,13 @@
         <v>867</v>
       </c>
       <c r="AS55" s="1" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="AU55" s="1" t="s">
         <v>219</v>
       </c>
       <c r="AV55" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW55" s="1" t="s">
         <v>220</v>
@@ -12215,7 +12224,7 @@
         <v>867</v>
       </c>
       <c r="AD56" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="AE56" s="1" t="s">
         <v>867</v>
@@ -12230,7 +12239,7 @@
         <v>867</v>
       </c>
       <c r="AI56" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="AJ56" s="1" t="s">
         <v>867</v>
@@ -12245,16 +12254,16 @@
         <v>867</v>
       </c>
       <c r="AS56" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="AT56" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="AU56" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="AV56" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW56" s="1" t="s">
         <v>222</v>
@@ -12389,10 +12398,10 @@
         <v>224</v>
       </c>
       <c r="AV57" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW57" s="1" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="AX57" s="1" t="s">
         <v>225</v>
@@ -12491,7 +12500,7 @@
         <v>867</v>
       </c>
       <c r="AD58" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="AE58" s="1" t="s">
         <v>867</v>
@@ -12519,19 +12528,19 @@
         <v>867</v>
       </c>
       <c r="AS58" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="AU58" s="1" t="s">
         <v>228</v>
       </c>
       <c r="AV58" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW58" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="AX58" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="AY58">
         <f t="shared" si="0"/>
@@ -12546,7 +12555,7 @@
         <v>867</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>867</v>
@@ -12642,7 +12651,7 @@
         <v>867</v>
       </c>
       <c r="AI59" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="AJ59" s="1" t="s">
         <v>867</v>
@@ -12657,16 +12666,16 @@
         <v>867</v>
       </c>
       <c r="AU59" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="AV59" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW59" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="AX59" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="AY59">
         <f t="shared" si="0"/>
@@ -12762,7 +12771,7 @@
         <v>867</v>
       </c>
       <c r="AD60" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="AE60" s="1" t="s">
         <v>867</v>
@@ -12777,7 +12786,7 @@
         <v>867</v>
       </c>
       <c r="AI60" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="AJ60" s="1" t="s">
         <v>867</v>
@@ -12792,13 +12801,13 @@
         <v>867</v>
       </c>
       <c r="AT60" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AU60" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AV60" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW60" s="1" t="s">
         <v>232</v>
@@ -12915,7 +12924,7 @@
         <v>867</v>
       </c>
       <c r="AI61" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="AJ61" s="1" t="s">
         <v>867</v>
@@ -12933,7 +12942,7 @@
         <v>123</v>
       </c>
       <c r="AV61" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW61" s="1" t="s">
         <v>235</v>
@@ -13068,7 +13077,7 @@
         <v>240</v>
       </c>
       <c r="AV62" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW62" s="1" t="s">
         <v>241</v>
@@ -13203,7 +13212,7 @@
         <v>243</v>
       </c>
       <c r="AV63" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW63" s="1" t="s">
         <v>244</v>
@@ -13338,7 +13347,7 @@
         <v>246</v>
       </c>
       <c r="AV64" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW64" s="1" t="s">
         <v>247</v>
@@ -13473,7 +13482,7 @@
         <v>249</v>
       </c>
       <c r="AV65" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW65" s="1" t="s">
         <v>250</v>
@@ -13605,13 +13614,13 @@
         <v>867</v>
       </c>
       <c r="AT66" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="AU66" s="1" t="s">
         <v>253</v>
       </c>
       <c r="AV66" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW66" s="1" t="s">
         <v>254</v>
@@ -13743,10 +13752,10 @@
         <v>867</v>
       </c>
       <c r="AU67" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="AV67" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW67" s="1" t="s">
         <v>256</v>
@@ -13878,10 +13887,10 @@
         <v>867</v>
       </c>
       <c r="AU68" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="AV68" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW68" s="1" t="s">
         <v>259</v>
@@ -14016,13 +14025,13 @@
         <v>262</v>
       </c>
       <c r="AO69" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AU69" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AV69" s="1" t="s">
         <v>1102</v>
-      </c>
-      <c r="AU69" s="1" t="s">
-        <v>1106</v>
-      </c>
-      <c r="AV69" s="1" t="s">
-        <v>1103</v>
       </c>
       <c r="AW69" s="1" t="s">
         <v>264</v>
@@ -14124,7 +14133,7 @@
         <v>867</v>
       </c>
       <c r="AD70" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="AE70" s="1" t="s">
         <v>867</v>
@@ -14152,22 +14161,22 @@
         <v>867</v>
       </c>
       <c r="AQ70" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AS70" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="AU70" s="1" t="s">
         <v>268</v>
       </c>
       <c r="AV70" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AW70" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="AW70" s="1" t="s">
-        <v>1113</v>
-      </c>
       <c r="AX70" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="AY70">
         <f t="shared" si="1"/>
@@ -14263,46 +14272,46 @@
         <v>867</v>
       </c>
       <c r="AD71" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AE71" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AF71" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AG71" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AH71" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AI71" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AJ71" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AK71" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AL71" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AM71" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AU71" s="1" t="s">
         <v>1107</v>
       </c>
-      <c r="AE71" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AF71" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AG71" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AH71" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AI71" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AJ71" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AK71" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AL71" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AM71" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AU71" s="1" t="s">
+      <c r="AV71" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="AW71" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="AV71" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="AW71" s="1" t="s">
+      <c r="AX71" s="1" t="s">
         <v>1109</v>
-      </c>
-      <c r="AX71" s="1" t="s">
-        <v>1110</v>
       </c>
       <c r="AY71">
         <f t="shared" si="1"/>
@@ -14428,16 +14437,16 @@
         <v>867</v>
       </c>
       <c r="AN72" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="AS72" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="AU72" s="1" t="s">
         <v>274</v>
       </c>
       <c r="AV72" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="AW72" s="1" t="s">
         <v>275</v>
@@ -14572,7 +14581,7 @@
         <v>123</v>
       </c>
       <c r="AV73" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="AW73" s="1" t="s">
         <v>277</v>
@@ -14707,7 +14716,7 @@
         <v>123</v>
       </c>
       <c r="AV74" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="AW74" s="1" t="s">
         <v>279</v>
@@ -14842,7 +14851,7 @@
         <v>281</v>
       </c>
       <c r="AV75" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="AW75" s="1" t="s">
         <v>282</v>
@@ -14977,7 +14986,7 @@
         <v>123</v>
       </c>
       <c r="AV76" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="AW76" s="1" t="s">
         <v>284</v>
@@ -15112,7 +15121,7 @@
         <v>287</v>
       </c>
       <c r="AV77" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="AW77" s="1" t="s">
         <v>288</v>
@@ -15244,14 +15253,14 @@
         <v>867</v>
       </c>
       <c r="AN78" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="AP78"/>
       <c r="AU78" s="1" t="s">
         <v>291</v>
       </c>
       <c r="AV78" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="AW78" s="1" t="s">
         <v>292</v>
@@ -15383,13 +15392,13 @@
         <v>867</v>
       </c>
       <c r="AN79" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="AU79" s="1" t="s">
         <v>295</v>
       </c>
       <c r="AV79" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="AW79" s="1" t="s">
         <v>296</v>
@@ -15521,22 +15530,22 @@
         <v>867</v>
       </c>
       <c r="AN80" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AS80" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="AU80" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AV80" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="AS80" s="1" t="s">
-        <v>970</v>
-      </c>
-      <c r="AU80" s="1" t="s">
+      <c r="AW80" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="AV80" s="1" t="s">
-        <v>1123</v>
-      </c>
-      <c r="AW80" s="1" t="s">
-        <v>1116</v>
-      </c>
       <c r="AX80" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AY80">
         <f t="shared" si="1"/>
@@ -15662,22 +15671,22 @@
         <v>867</v>
       </c>
       <c r="AN81" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="AS81" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="AU81" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AV81" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AW81" s="1" t="s">
         <v>1117</v>
       </c>
-      <c r="AV81" s="1" t="s">
-        <v>1123</v>
-      </c>
-      <c r="AW81" s="1" t="s">
-        <v>1118</v>
-      </c>
       <c r="AX81" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AY81">
         <f t="shared" si="1"/>
@@ -15779,7 +15788,7 @@
         <v>867</v>
       </c>
       <c r="AF82" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="AG82" s="1" t="s">
         <v>867</v>
@@ -15806,7 +15815,7 @@
         <v>309</v>
       </c>
       <c r="AV82" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW82" s="1" t="s">
         <v>310</v>
@@ -15938,13 +15947,13 @@
         <v>867</v>
       </c>
       <c r="AT83" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="AU83" s="1" t="s">
         <v>312</v>
       </c>
       <c r="AV83" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW83" s="1" t="s">
         <v>313</v>
@@ -16079,7 +16088,7 @@
         <v>315</v>
       </c>
       <c r="AV84" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW84" s="1" t="s">
         <v>316</v>
@@ -16181,7 +16190,7 @@
         <v>867</v>
       </c>
       <c r="AD85" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="AE85" s="1" t="s">
         <v>867</v>
@@ -16214,7 +16223,7 @@
         <v>51</v>
       </c>
       <c r="AV85" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW85" s="1" t="s">
         <v>318</v>
@@ -16271,7 +16280,7 @@
         <v>867</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="P86" s="1" t="s">
         <v>867</v>
@@ -16349,7 +16358,7 @@
         <v>193</v>
       </c>
       <c r="AV86" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW86" s="1" t="s">
         <v>322</v>
@@ -16481,13 +16490,13 @@
         <v>867</v>
       </c>
       <c r="AS87" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="AU87" s="1" t="s">
         <v>324</v>
       </c>
       <c r="AV87" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW87" s="1" t="s">
         <v>325</v>
@@ -16595,7 +16604,7 @@
         <v>867</v>
       </c>
       <c r="AF88" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="AG88" s="1" t="s">
         <v>867</v>
@@ -16622,7 +16631,7 @@
         <v>330</v>
       </c>
       <c r="AV88" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW88" s="1" t="s">
         <v>331</v>
@@ -16757,7 +16766,7 @@
         <v>334</v>
       </c>
       <c r="AV89" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW89" s="1" t="s">
         <v>335</v>
@@ -16859,7 +16868,7 @@
         <v>867</v>
       </c>
       <c r="AD90" s="3" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="AE90" s="1" t="s">
         <v>867</v>
@@ -16892,13 +16901,13 @@
         <v>338</v>
       </c>
       <c r="AS90" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="AU90" s="1" t="s">
         <v>341</v>
       </c>
       <c r="AV90" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="AW90" s="1" t="s">
         <v>342</v>
@@ -17033,7 +17042,7 @@
         <v>346</v>
       </c>
       <c r="AV91" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW91" s="1" t="s">
         <v>347</v>
@@ -17168,7 +17177,7 @@
         <v>352</v>
       </c>
       <c r="AV92" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW92" s="1" t="s">
         <v>353</v>
@@ -17303,7 +17312,7 @@
         <v>181</v>
       </c>
       <c r="AV93" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW93" s="1" t="s">
         <v>355</v>
@@ -17438,7 +17447,7 @@
         <v>357</v>
       </c>
       <c r="AV94" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW94" s="1" t="s">
         <v>358</v>
@@ -17570,13 +17579,13 @@
         <v>867</v>
       </c>
       <c r="AT95" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="AU95" s="1" t="s">
         <v>359</v>
       </c>
       <c r="AV95" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW95" s="1" t="s">
         <v>360</v>
@@ -17597,7 +17606,7 @@
         <v>349</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>350</v>
@@ -17636,7 +17645,7 @@
         <v>867</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>867</v>
@@ -17717,7 +17726,7 @@
         <v>295</v>
       </c>
       <c r="AV96" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="AW96" s="1" t="s">
         <v>361</v>
@@ -17852,7 +17861,7 @@
         <v>363</v>
       </c>
       <c r="AV97" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW97" s="1" t="s">
         <v>364</v>
@@ -17987,7 +17996,7 @@
         <v>367</v>
       </c>
       <c r="AV98" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW98" s="1" t="s">
         <v>368</v>
@@ -18008,7 +18017,7 @@
         <v>867</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>867</v>
@@ -18044,7 +18053,7 @@
         <v>867</v>
       </c>
       <c r="O99" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="P99" s="1" t="s">
         <v>885</v>
@@ -18089,13 +18098,13 @@
         <v>867</v>
       </c>
       <c r="AD99" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="AE99" s="1" t="s">
         <v>867</v>
       </c>
       <c r="AF99" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="AG99" s="1" t="s">
         <v>867</v>
@@ -18125,16 +18134,16 @@
         <v>308</v>
       </c>
       <c r="AU99" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AV99" s="1" t="s">
         <v>1144</v>
       </c>
-      <c r="AV99" s="1" t="s">
+      <c r="AW99" s="1" t="s">
         <v>1145</v>
       </c>
-      <c r="AW99" s="1" t="s">
-        <v>1146</v>
-      </c>
       <c r="AX99" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="AY99">
         <f t="shared" si="1"/>
@@ -18230,7 +18239,7 @@
         <v>867</v>
       </c>
       <c r="AD100" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="AE100" s="1" t="s">
         <v>867</v>
@@ -18266,7 +18275,7 @@
         <v>373</v>
       </c>
       <c r="AV100" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="AW100" s="1" t="s">
         <v>374</v>
@@ -18287,7 +18296,7 @@
         <v>867</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>867</v>
@@ -18326,91 +18335,91 @@
         <v>867</v>
       </c>
       <c r="P101" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="R101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="T101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="U101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="V101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="W101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="X101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="Y101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="Z101" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="AA101" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AB101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AC101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AD101" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="AE101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AF101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AG101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AH101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AI101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AJ101" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AK101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AL101" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AM101" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>1131</v>
-      </c>
-      <c r="R101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="T101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="U101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="V101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="W101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="X101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="Y101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="Z101" s="1" t="s">
+      <c r="AN101" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AU101" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AV101" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AW101" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AX101" s="1" t="s">
         <v>1139</v>
-      </c>
-      <c r="AA101" s="1" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AB101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AC101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AD101" s="3" t="s">
-        <v>1132</v>
-      </c>
-      <c r="AE101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AF101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AG101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AH101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AI101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AJ101" s="1" t="s">
-        <v>1137</v>
-      </c>
-      <c r="AK101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AL101" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AM101" s="1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AN101" s="1" t="s">
-        <v>1136</v>
-      </c>
-      <c r="AU101" s="1" t="s">
-        <v>1141</v>
-      </c>
-      <c r="AV101" s="1" t="s">
-        <v>1135</v>
-      </c>
-      <c r="AW101" s="1" t="s">
-        <v>1138</v>
-      </c>
-      <c r="AX101" s="1" t="s">
-        <v>1140</v>
       </c>
       <c r="AY101">
         <f t="shared" si="1"/>
@@ -18536,13 +18545,13 @@
         <v>867</v>
       </c>
       <c r="AS102" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="AU102" s="1" t="s">
         <v>382</v>
       </c>
       <c r="AV102" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW102" s="1" t="s">
         <v>383</v>
@@ -18677,7 +18686,7 @@
         <v>385</v>
       </c>
       <c r="AV103" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW103" s="1" t="s">
         <v>386</v>
@@ -18815,7 +18824,7 @@
         <v>389</v>
       </c>
       <c r="AV104" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AW104" s="1" t="s">
         <v>390</v>
@@ -18950,7 +18959,7 @@
         <v>392</v>
       </c>
       <c r="AV105" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW105" s="1" t="s">
         <v>393</v>
@@ -19085,7 +19094,7 @@
         <v>395</v>
       </c>
       <c r="AV106" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW106" s="1" t="s">
         <v>396</v>
@@ -19220,7 +19229,7 @@
         <v>398</v>
       </c>
       <c r="AV107" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW107" s="1" t="s">
         <v>399</v>
@@ -19355,7 +19364,7 @@
         <v>401</v>
       </c>
       <c r="AV108" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW108" s="1" t="s">
         <v>402</v>
@@ -19475,25 +19484,25 @@
         <v>867</v>
       </c>
       <c r="AJ109" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AK109" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AL109" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AM109" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AO109" s="1" t="s">
         <v>1152</v>
-      </c>
-      <c r="AK109" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AL109" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AM109" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AO109" s="1" t="s">
-        <v>1153</v>
       </c>
       <c r="AU109" s="1" t="s">
         <v>405</v>
       </c>
       <c r="AV109" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="AW109" s="1" t="s">
         <v>406</v>
@@ -19631,7 +19640,7 @@
         <v>409</v>
       </c>
       <c r="AV110" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="AW110" s="1" t="s">
         <v>410</v>
@@ -19706,7 +19715,7 @@
         <v>890</v>
       </c>
       <c r="U111" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="V111" s="1" t="s">
         <v>867</v>
@@ -19733,13 +19742,13 @@
         <v>867</v>
       </c>
       <c r="AD111" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="AE111" s="1" t="s">
         <v>867</v>
       </c>
       <c r="AF111" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="AG111" s="1" t="s">
         <v>867</v>
@@ -19763,22 +19772,22 @@
         <v>867</v>
       </c>
       <c r="AO111" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AS111" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AU111" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AV111" s="1" t="s">
         <v>1155</v>
       </c>
-      <c r="AS111" s="1" t="s">
-        <v>1077</v>
-      </c>
-      <c r="AU111" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="AV111" s="1" t="s">
-        <v>1156</v>
-      </c>
       <c r="AW111" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="AX111" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="AY111">
         <f t="shared" si="1"/>
@@ -19901,13 +19910,13 @@
         <v>433</v>
       </c>
       <c r="AS112" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="AU112" s="1" t="s">
         <v>419</v>
       </c>
       <c r="AV112" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW112" s="1" t="s">
         <v>420</v>
@@ -20042,7 +20051,7 @@
         <v>123</v>
       </c>
       <c r="AV113" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW113" s="1" t="s">
         <v>422</v>
@@ -20177,7 +20186,7 @@
         <v>424</v>
       </c>
       <c r="AV114" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW114" s="1" t="s">
         <v>425</v>
@@ -20312,7 +20321,7 @@
         <v>385</v>
       </c>
       <c r="AV115" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW115" s="1" t="s">
         <v>427</v>
@@ -20444,10 +20453,10 @@
         <v>867</v>
       </c>
       <c r="AU116" s="1" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="AV116" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW116" s="1" t="s">
         <v>429</v>
@@ -20579,13 +20588,13 @@
         <v>867</v>
       </c>
       <c r="AS117" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="AU117" s="1" t="s">
         <v>431</v>
       </c>
       <c r="AV117" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW117" s="1" t="s">
         <v>432</v>
@@ -20606,7 +20615,7 @@
         <v>415</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>416</v>
@@ -20720,7 +20729,7 @@
         <v>434</v>
       </c>
       <c r="AV118" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW118" s="1" t="s">
         <v>435</v>
@@ -20741,7 +20750,7 @@
         <v>867</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>867</v>
@@ -20783,7 +20792,7 @@
         <v>867</v>
       </c>
       <c r="Q119" s="3" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="R119" s="1" t="s">
         <v>867</v>
@@ -20846,22 +20855,22 @@
         <v>252</v>
       </c>
       <c r="AL119" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="AM119" s="1" t="s">
         <v>867</v>
       </c>
       <c r="AS119" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AT119" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="AU119" s="1" t="s">
         <v>438</v>
       </c>
       <c r="AV119" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW119" s="1" t="s">
         <v>439</v>
@@ -20987,16 +20996,16 @@
         <v>867</v>
       </c>
       <c r="AL120" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="AM120" s="1" t="s">
         <v>867</v>
       </c>
       <c r="AU120" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="AV120" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW120" s="1" t="s">
         <v>442</v>
@@ -21059,7 +21068,7 @@
         <v>867</v>
       </c>
       <c r="Q121" s="3" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="R121" s="1" t="s">
         <v>867</v>
@@ -21122,22 +21131,22 @@
         <v>252</v>
       </c>
       <c r="AL121" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="AM121" s="1" t="s">
         <v>867</v>
       </c>
       <c r="AS121" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AT121" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AU121" s="1" t="s">
         <v>446</v>
       </c>
       <c r="AV121" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW121" s="1" t="s">
         <v>447</v>
@@ -21269,13 +21278,13 @@
         <v>867</v>
       </c>
       <c r="AT122" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="AU122" s="1" t="s">
         <v>453</v>
       </c>
       <c r="AV122" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW122" s="1" t="s">
         <v>454</v>
@@ -21410,7 +21419,7 @@
         <v>385</v>
       </c>
       <c r="AV123" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW123" s="1" t="s">
         <v>455</v>
@@ -21542,13 +21551,13 @@
         <v>867</v>
       </c>
       <c r="AT124" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="AU124" s="1" t="s">
         <v>458</v>
       </c>
       <c r="AV124" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW124" s="1" t="s">
         <v>459</v>
@@ -21683,7 +21692,7 @@
         <v>461</v>
       </c>
       <c r="AV125" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW125" s="1" t="s">
         <v>462</v>
@@ -21818,7 +21827,7 @@
         <v>464</v>
       </c>
       <c r="AV126" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW126" s="1" t="s">
         <v>465</v>
@@ -21953,7 +21962,7 @@
         <v>467</v>
       </c>
       <c r="AV127" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW127" s="1" t="s">
         <v>468</v>
@@ -22085,13 +22094,13 @@
         <v>867</v>
       </c>
       <c r="AT128" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="AU128" s="1" t="s">
         <v>471</v>
       </c>
       <c r="AV128" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW128" s="1" t="s">
         <v>472</v>
@@ -22193,7 +22202,7 @@
         <v>867</v>
       </c>
       <c r="AD129" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="AE129" s="1" t="s">
         <v>867</v>
@@ -22217,19 +22226,19 @@
         <v>867</v>
       </c>
       <c r="AL129" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="AM129" s="1" t="s">
         <v>867</v>
       </c>
       <c r="AT129" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="AU129" s="1" t="s">
         <v>475</v>
       </c>
       <c r="AV129" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW129" s="1" t="s">
         <v>476</v>
@@ -22322,61 +22331,61 @@
         <v>867</v>
       </c>
       <c r="AA130" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AB130" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AC130" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AD130" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AE130" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AF130" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AG130" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AH130" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AI130" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AJ130" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="AB130" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AC130" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AD130" s="3" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AE130" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AF130" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AG130" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AH130" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AI130" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AJ130" s="1" t="s">
+      <c r="AK130" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AL130" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AM130" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AN130" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="AT130" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AU130" s="1" t="s">
         <v>1171</v>
       </c>
-      <c r="AK130" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AL130" s="1" t="s">
+      <c r="AV130" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AW130" s="1" t="s">
         <v>1165</v>
       </c>
-      <c r="AM130" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AN130" s="1" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AT130" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AU130" s="1" t="s">
-        <v>1172</v>
-      </c>
-      <c r="AV130" s="1" t="s">
-        <v>1168</v>
-      </c>
-      <c r="AW130" s="1" t="s">
-        <v>1166</v>
-      </c>
       <c r="AX130" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="AY130">
         <f t="shared" si="1"/>
@@ -22496,7 +22505,7 @@
         <v>867</v>
       </c>
       <c r="AL131" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="AM131" s="1" t="s">
         <v>867</v>
@@ -22505,7 +22514,7 @@
         <v>481</v>
       </c>
       <c r="AV131" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW131" s="1" t="s">
         <v>482</v>
@@ -22640,7 +22649,7 @@
         <v>486</v>
       </c>
       <c r="AV132" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW132" s="1" t="s">
         <v>487</v>
@@ -22775,7 +22784,7 @@
         <v>395</v>
       </c>
       <c r="AV133" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW133" s="1" t="s">
         <v>489</v>
@@ -22907,10 +22916,10 @@
         <v>867</v>
       </c>
       <c r="AU134" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="AV134" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW134" s="1" t="s">
         <v>491</v>
@@ -23042,10 +23051,10 @@
         <v>867</v>
       </c>
       <c r="AU135" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="AV135" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW135" s="1" t="s">
         <v>493</v>
@@ -23177,16 +23186,16 @@
         <v>867</v>
       </c>
       <c r="AU136" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="AV136" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="AW136" s="1" t="s">
         <v>1239</v>
       </c>
-      <c r="AV136" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="AW136" s="1" t="s">
-        <v>1240</v>
-      </c>
       <c r="AX136" s="1" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="AY136">
         <f t="shared" si="2"/>
@@ -23315,7 +23324,7 @@
         <v>497</v>
       </c>
       <c r="AV137" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW137" s="1" t="s">
         <v>498</v>
@@ -23447,19 +23456,19 @@
         <v>867</v>
       </c>
       <c r="AS138" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="AU138" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="AV138" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="AW138" s="1" t="s">
         <v>1173</v>
       </c>
-      <c r="AV138" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="AW138" s="1" t="s">
-        <v>1174</v>
-      </c>
       <c r="AX138" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="AY138">
         <f t="shared" si="2"/>
@@ -23585,10 +23594,10 @@
         <v>867</v>
       </c>
       <c r="AU139" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="AV139" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW139" s="1" t="s">
         <v>503</v>
@@ -23720,10 +23729,10 @@
         <v>867</v>
       </c>
       <c r="AU140" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="AV140" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW140" s="1" t="s">
         <v>507</v>
@@ -23858,7 +23867,7 @@
         <v>510</v>
       </c>
       <c r="AV141" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW141" s="1" t="s">
         <v>511</v>
@@ -23966,7 +23975,7 @@
         <v>867</v>
       </c>
       <c r="AF142" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="AG142" s="1" t="s">
         <v>867</v>
@@ -23974,10 +23983,10 @@
       <c r="AH142" s="1"/>
       <c r="AI142" s="1"/>
       <c r="AJ142" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="AK142" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="AL142" s="1" t="s">
         <v>867</v>
@@ -23989,7 +23998,7 @@
         <v>517</v>
       </c>
       <c r="AV142" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW142" s="1" t="s">
         <v>518</v>
@@ -24124,7 +24133,7 @@
         <v>207</v>
       </c>
       <c r="AV143" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW143" s="1" t="s">
         <v>520</v>
@@ -24259,7 +24268,7 @@
         <v>461</v>
       </c>
       <c r="AV144" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW144" s="1" t="s">
         <v>522</v>
@@ -24394,7 +24403,7 @@
         <v>214</v>
       </c>
       <c r="AV145" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW145" s="1" t="s">
         <v>524</v>
@@ -24517,7 +24526,7 @@
         <v>867</v>
       </c>
       <c r="AK146" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="AL146" s="1" t="s">
         <v>867</v>
@@ -24529,7 +24538,7 @@
         <v>526</v>
       </c>
       <c r="AV146" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW146" s="1" t="s">
         <v>527</v>
@@ -24664,7 +24673,7 @@
         <v>207</v>
       </c>
       <c r="AV147" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW147" s="1" t="s">
         <v>530</v>
@@ -24799,7 +24808,7 @@
         <v>532</v>
       </c>
       <c r="AV148" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW148" s="1" t="s">
         <v>533</v>
@@ -24901,7 +24910,7 @@
         <v>867</v>
       </c>
       <c r="AD149" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="AE149" s="1" t="s">
         <v>867</v>
@@ -24916,10 +24925,10 @@
         <v>867</v>
       </c>
       <c r="AJ149" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="AK149" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="AL149" s="1" t="s">
         <v>867</v>
@@ -24931,7 +24940,7 @@
         <v>228</v>
       </c>
       <c r="AV149" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW149" s="1" t="s">
         <v>536</v>
@@ -25069,13 +25078,13 @@
         <v>516</v>
       </c>
       <c r="AS150" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="AU150" s="1" t="s">
         <v>540</v>
       </c>
       <c r="AV150" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AW150" s="1" t="s">
         <v>541</v>
@@ -25135,91 +25144,91 @@
         <v>867</v>
       </c>
       <c r="P151" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Q151" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="R151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="S151" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="T151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="U151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="V151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="W151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="X151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="Y151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="Z151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AA151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AB151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AC151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AD151" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="AE151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AF151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AG151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AH151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AI151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AJ151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AK151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AL151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AM151" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AR151" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="AU151" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="Q151" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="R151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="S151" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="T151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="U151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="V151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="W151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="X151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="Y151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="Z151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AA151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AB151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AC151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AD151" s="3" t="s">
-        <v>1181</v>
-      </c>
-      <c r="AE151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AF151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AG151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AH151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AI151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AJ151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AK151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AL151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AM151" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AR151" s="1" t="s">
-        <v>1182</v>
-      </c>
-      <c r="AU151" s="1" t="s">
-        <v>1184</v>
-      </c>
       <c r="AV151" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AW151" s="1" t="s">
         <v>1186</v>
       </c>
-      <c r="AW151" s="1" t="s">
+      <c r="AX151" s="1" t="s">
         <v>1187</v>
-      </c>
-      <c r="AX151" s="1" t="s">
-        <v>1188</v>
       </c>
       <c r="AY151">
         <f t="shared" si="2"/>
@@ -25315,7 +25324,7 @@
         <v>867</v>
       </c>
       <c r="AD152" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="AE152" s="1" t="s">
         <v>867</v>
@@ -25346,7 +25355,7 @@
         <v>548</v>
       </c>
       <c r="AV152" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW152" s="1" t="s">
         <v>549</v>
@@ -25481,7 +25490,7 @@
         <v>461</v>
       </c>
       <c r="AV153" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW153" s="1" t="s">
         <v>551</v>
@@ -25616,7 +25625,7 @@
         <v>461</v>
       </c>
       <c r="AV154" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW154" s="1" t="s">
         <v>553</v>
@@ -25751,7 +25760,7 @@
         <v>295</v>
       </c>
       <c r="AV155" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW155" s="1" t="s">
         <v>555</v>
@@ -25883,13 +25892,13 @@
         <v>867</v>
       </c>
       <c r="AT156" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AU156" s="1" t="s">
         <v>557</v>
       </c>
       <c r="AV156" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW156" s="1" t="s">
         <v>558</v>
@@ -26024,7 +26033,7 @@
         <v>560</v>
       </c>
       <c r="AV157" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW157" s="1" t="s">
         <v>561</v>
@@ -26147,7 +26156,7 @@
         <v>867</v>
       </c>
       <c r="AK158" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="AL158" s="1" t="s">
         <v>867</v>
@@ -26159,7 +26168,7 @@
         <v>563</v>
       </c>
       <c r="AV158" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW158" s="1" t="s">
         <v>564</v>
@@ -26258,7 +26267,7 @@
         <v>867</v>
       </c>
       <c r="AC159" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="AD159" s="3" t="s">
         <v>867</v>
@@ -26294,7 +26303,7 @@
         <v>569</v>
       </c>
       <c r="AV159" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW159" s="1" t="s">
         <v>570</v>
@@ -26396,7 +26405,7 @@
         <v>867</v>
       </c>
       <c r="AD160" s="3" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="AE160" s="1" t="s">
         <v>867</v>
@@ -26429,16 +26438,16 @@
         <v>573</v>
       </c>
       <c r="AU160" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="AV160" s="1" t="s">
         <v>1192</v>
       </c>
-      <c r="AV160" s="1" t="s">
+      <c r="AW160" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="AW160" s="1" t="s">
-        <v>1194</v>
-      </c>
       <c r="AX160" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="AY160">
         <f t="shared" si="2"/>
@@ -26534,7 +26543,7 @@
         <v>867</v>
       </c>
       <c r="AD161" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="AE161" s="1" t="s">
         <v>867</v>
@@ -26567,7 +26576,7 @@
         <v>228</v>
       </c>
       <c r="AV161" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW161" s="1" t="s">
         <v>576</v>
@@ -26669,7 +26678,7 @@
         <v>867</v>
       </c>
       <c r="AD162" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="AE162" s="1" t="s">
         <v>867</v>
@@ -26698,7 +26707,7 @@
         <v>582</v>
       </c>
       <c r="AV162" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW162" s="1" t="s">
         <v>583</v>
@@ -26833,7 +26842,7 @@
         <v>385</v>
       </c>
       <c r="AV163" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW163" s="1" t="s">
         <v>585</v>
@@ -26968,7 +26977,7 @@
         <v>461</v>
       </c>
       <c r="AV164" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW164" s="1" t="s">
         <v>587</v>
@@ -27096,13 +27105,13 @@
         <v>867</v>
       </c>
       <c r="AS165" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="AU165" s="1" t="s">
         <v>590</v>
       </c>
       <c r="AV165" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW165" s="1" t="s">
         <v>591</v>
@@ -27237,7 +27246,7 @@
         <v>434</v>
       </c>
       <c r="AV166" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW166" s="1" t="s">
         <v>593</v>
@@ -27370,7 +27379,7 @@
         <v>595</v>
       </c>
       <c r="AV167" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW167" s="1" t="s">
         <v>596</v>
@@ -27506,13 +27515,13 @@
         <v>600</v>
       </c>
       <c r="AT168" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AU168" s="1" t="s">
         <v>601</v>
       </c>
       <c r="AV168" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="AW168" s="1" t="s">
         <v>602</v>
@@ -27533,7 +27542,7 @@
         <v>867</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>867</v>
@@ -27641,19 +27650,19 @@
         <v>867</v>
       </c>
       <c r="AM169" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="AU169" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="AV169" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="AW169" s="1" t="s">
         <v>1211</v>
       </c>
-      <c r="AV169" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="AW169" s="1" t="s">
-        <v>1212</v>
-      </c>
       <c r="AX169" s="1" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="AY169">
         <f t="shared" si="2"/>
@@ -27668,7 +27677,7 @@
         <v>867</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>867</v>
@@ -27779,22 +27788,22 @@
         <v>867</v>
       </c>
       <c r="AO170" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="AP170" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="AU170" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="AV170" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="AW170" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="AW170" s="1" t="s">
-        <v>1197</v>
-      </c>
       <c r="AX170" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="AY170">
         <f t="shared" si="2"/>
@@ -27923,7 +27932,7 @@
         <v>607</v>
       </c>
       <c r="AV171" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW171" s="1" t="s">
         <v>608</v>
@@ -28031,7 +28040,7 @@
         <v>869</v>
       </c>
       <c r="AF172" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="AG172" s="1" t="s">
         <v>867</v>
@@ -28056,7 +28065,7 @@
         <v>615</v>
       </c>
       <c r="AV172" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW172" s="1" t="s">
         <v>616</v>
@@ -28188,13 +28197,13 @@
         <v>867</v>
       </c>
       <c r="AT173" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="AU173" s="1" t="s">
         <v>619</v>
       </c>
       <c r="AV173" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW173" s="1" t="s">
         <v>620</v>
@@ -28329,7 +28338,7 @@
         <v>295</v>
       </c>
       <c r="AV174" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW174" s="1" t="s">
         <v>622</v>
@@ -28404,7 +28413,7 @@
         <v>867</v>
       </c>
       <c r="U175" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="V175" s="1" t="s">
         <v>867</v>
@@ -28464,7 +28473,7 @@
         <v>51</v>
       </c>
       <c r="AV175" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW175" s="1" t="s">
         <v>624</v>
@@ -28599,7 +28608,7 @@
         <v>461</v>
       </c>
       <c r="AV176" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW176" s="1" t="s">
         <v>626</v>
@@ -28734,7 +28743,7 @@
         <v>628</v>
       </c>
       <c r="AV177" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW177" s="1" t="s">
         <v>629</v>
@@ -28803,40 +28812,40 @@
         <v>867</v>
       </c>
       <c r="S178" s="3" t="s">
+        <v>917</v>
+      </c>
+      <c r="T178" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="U178" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="V178" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="W178" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="X178" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="Y178" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="Z178" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AA178" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="AB178" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="AC178" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="AD178" s="3" t="s">
         <v>918</v>
-      </c>
-      <c r="T178" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="U178" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="V178" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="W178" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="X178" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="Y178" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="Z178" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AA178" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="AB178" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="AC178" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="AD178" s="3" t="s">
-        <v>919</v>
       </c>
       <c r="AE178" s="1" t="s">
         <v>867</v>
@@ -28862,13 +28871,13 @@
         <v>867</v>
       </c>
       <c r="AN178" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="AU178" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="AV178" s="1" t="s">
         <v>1204</v>
-      </c>
-      <c r="AU178" s="1" t="s">
-        <v>1230</v>
-      </c>
-      <c r="AV178" s="1" t="s">
-        <v>1205</v>
       </c>
       <c r="AW178" s="1" t="s">
         <v>633</v>
@@ -29000,16 +29009,16 @@
         <v>867</v>
       </c>
       <c r="AU179" s="1" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="AV179" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW179" s="1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="AX179" s="1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="AY179">
         <f t="shared" si="2"/>
@@ -29135,16 +29144,16 @@
         <v>867</v>
       </c>
       <c r="AU180" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="AV180" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="AW180" s="1" t="s">
         <v>1231</v>
       </c>
-      <c r="AV180" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="AW180" s="1" t="s">
-        <v>1232</v>
-      </c>
       <c r="AX180" s="1" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="AY180">
         <f t="shared" si="2"/>
@@ -29240,7 +29249,7 @@
         <v>867</v>
       </c>
       <c r="AD181" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="AE181" s="1" t="s">
         <v>867</v>
@@ -29276,16 +29285,16 @@
         <v>614</v>
       </c>
       <c r="AU181" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="AV181" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="AV181" s="1" t="s">
+      <c r="AW181" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="AW181" s="1" t="s">
-        <v>1228</v>
-      </c>
       <c r="AX181" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="AY181">
         <f t="shared" si="2"/>
@@ -29385,7 +29394,7 @@
         <v>867</v>
       </c>
       <c r="AF182" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AG182" s="1" t="s">
         <v>867</v>
@@ -29410,13 +29419,13 @@
         <v>698</v>
       </c>
       <c r="AV182" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW182" s="1" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="AX182" s="1" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="AY182">
         <f t="shared" si="2"/>
@@ -29540,13 +29549,13 @@
         <v>867</v>
       </c>
       <c r="AT183" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="AU183" s="1" t="s">
         <v>646</v>
       </c>
       <c r="AV183" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW183" s="1" t="s">
         <v>647</v>
@@ -29676,13 +29685,13 @@
         <v>867</v>
       </c>
       <c r="AT184" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="AU184" s="1" t="s">
         <v>649</v>
       </c>
       <c r="AV184" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW184" s="1" t="s">
         <v>650</v>
@@ -29815,7 +29824,7 @@
         <v>653</v>
       </c>
       <c r="AV185" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="AW185" s="1" t="s">
         <v>654</v>
@@ -29954,7 +29963,7 @@
         <v>657</v>
       </c>
       <c r="AV186" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="AW186" s="1" t="s">
         <v>658</v>
@@ -30087,7 +30096,7 @@
         <v>214</v>
       </c>
       <c r="AV187" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW187" s="1" t="s">
         <v>660</v>
@@ -30177,7 +30186,7 @@
         <v>867</v>
       </c>
       <c r="Z188" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA188" s="3" t="s">
         <v>867</v>
@@ -30189,7 +30198,7 @@
         <v>867</v>
       </c>
       <c r="AD188" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="AE188" s="1" t="s">
         <v>867</v>
@@ -30220,10 +30229,10 @@
         <v>663</v>
       </c>
       <c r="AU188" s="1" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="AV188" s="1" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="AW188" s="1" t="s">
         <v>664</v>
@@ -30353,22 +30362,22 @@
         <v>867</v>
       </c>
       <c r="AS189" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="AT189" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="AU189" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="AV189" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="AW189" s="1" t="s">
         <v>1235</v>
       </c>
-      <c r="AV189" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="AW189" s="1" t="s">
-        <v>1236</v>
-      </c>
       <c r="AX189" s="1" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="AY189">
         <f t="shared" si="2"/>
@@ -30383,7 +30392,7 @@
         <v>867</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>867</v>
@@ -30492,22 +30501,22 @@
         <v>867</v>
       </c>
       <c r="AQ190" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="AR190" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="AR190" s="1" t="s">
+      <c r="AU190" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="AV190" s="1" t="s">
         <v>1247</v>
       </c>
-      <c r="AU190" s="1" t="s">
-        <v>1255</v>
-      </c>
-      <c r="AV190" s="1" t="s">
-        <v>1248</v>
-      </c>
       <c r="AW190" s="1" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="AX190" s="1" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="AY190">
         <f t="shared" si="2"/>
@@ -30564,7 +30573,7 @@
         <v>867</v>
       </c>
       <c r="Q191" s="3" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="R191" s="1" t="s">
         <v>867</v>
@@ -30603,7 +30612,7 @@
         <v>867</v>
       </c>
       <c r="AD191" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="AE191" s="1" t="s">
         <v>867</v>
@@ -30634,19 +30643,19 @@
         <v>618</v>
       </c>
       <c r="AS191" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="AU191" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="AV191" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="AW191" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="AV191" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="AW191" s="1" t="s">
+      <c r="AX191" s="1" t="s">
         <v>1243</v>
-      </c>
-      <c r="AX191" s="1" t="s">
-        <v>1244</v>
       </c>
       <c r="AY191">
         <f t="shared" si="2"/>
@@ -30694,13 +30703,13 @@
         <v>25</v>
       </c>
       <c r="N192" s="3" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="O192" s="3" t="s">
         <v>867</v>
       </c>
       <c r="P192" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="Q192" s="3" t="s">
         <v>867</v>
@@ -30770,13 +30779,13 @@
         <v>867</v>
       </c>
       <c r="AT192" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="AU192" s="1" t="s">
         <v>673</v>
       </c>
       <c r="AV192" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW192" s="1" t="s">
         <v>674</v>
@@ -30830,13 +30839,13 @@
         <v>50</v>
       </c>
       <c r="N193" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="O193" s="3" t="s">
         <v>867</v>
       </c>
       <c r="P193" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="Q193" s="3" t="s">
         <v>867</v>
@@ -30909,7 +30918,7 @@
         <v>207</v>
       </c>
       <c r="AV193" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW193" s="1" t="s">
         <v>676</v>
@@ -31039,13 +31048,13 @@
         <v>867</v>
       </c>
       <c r="AS194" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="AU194" s="1" t="s">
         <v>678</v>
       </c>
       <c r="AV194" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW194" s="1" t="s">
         <v>679</v>
@@ -31178,7 +31187,7 @@
         <v>682</v>
       </c>
       <c r="AV195" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW195" s="1" t="s">
         <v>683</v>
@@ -31311,7 +31320,7 @@
         <v>461</v>
       </c>
       <c r="AV196" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW196" s="1" t="s">
         <v>685</v>
@@ -31444,7 +31453,7 @@
         <v>687</v>
       </c>
       <c r="AV197" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW197" s="1" t="s">
         <v>688</v>
@@ -31504,7 +31513,7 @@
         <v>867</v>
       </c>
       <c r="P198" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="Q198" s="1" t="s">
         <v>867</v>
@@ -31577,10 +31586,10 @@
         <v>691</v>
       </c>
       <c r="AU198" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="AV198" s="1" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="AW198" s="1" t="s">
         <v>692</v>
@@ -31713,7 +31722,7 @@
         <v>207</v>
       </c>
       <c r="AV199" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW199" s="1" t="s">
         <v>695</v>
@@ -31771,49 +31780,49 @@
       </c>
       <c r="O200" s="1"/>
       <c r="P200" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="Q200" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="R200" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="S200" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="T200" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="U200" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="V200" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="W200" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="X200" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="Y200" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="Z200" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AA200" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AB200" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AC200" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="AD200" s="3" t="s">
         <v>1249</v>
-      </c>
-      <c r="Q200" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="R200" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="S200" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="T200" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="U200" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="V200" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="W200" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="X200" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="Y200" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="Z200" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AA200" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AB200" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AC200" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="AD200" s="3" t="s">
-        <v>1250</v>
       </c>
       <c r="AE200" s="1" t="s">
         <v>867</v>
@@ -31841,19 +31850,19 @@
         <v>867</v>
       </c>
       <c r="AN200" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="AU200" s="1" t="s">
         <v>1251</v>
       </c>
-      <c r="AU200" s="1" t="s">
+      <c r="AV200" s="1" t="s">
         <v>1252</v>
       </c>
-      <c r="AV200" s="1" t="s">
+      <c r="AW200" s="1" t="s">
         <v>1253</v>
       </c>
-      <c r="AW200" s="1" t="s">
-        <v>1254</v>
-      </c>
       <c r="AX200" s="1" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="AY200">
         <f t="shared" si="3"/>
@@ -31977,13 +31986,13 @@
         <v>867</v>
       </c>
       <c r="AQ201" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="AU201" s="1" t="s">
         <v>701</v>
       </c>
       <c r="AV201" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="AW201" s="1" t="s">
         <v>702</v>
@@ -32091,7 +32100,7 @@
         <v>867</v>
       </c>
       <c r="AF202" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="AG202" s="1" t="s">
         <v>867</v>
@@ -32116,7 +32125,7 @@
         <v>698</v>
       </c>
       <c r="AV202" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW202" s="1" t="s">
         <v>710</v>
@@ -32249,7 +32258,7 @@
         <v>712</v>
       </c>
       <c r="AV203" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW203" s="1" t="s">
         <v>713</v>
@@ -32382,7 +32391,7 @@
         <v>715</v>
       </c>
       <c r="AV204" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW204" s="1" t="s">
         <v>716</v>
@@ -32451,7 +32460,7 @@
         <v>867</v>
       </c>
       <c r="S205" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="T205" s="1" t="s">
         <v>867</v>
@@ -32521,7 +32530,7 @@
         <v>434</v>
       </c>
       <c r="AV205" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="AW205" s="1" t="s">
         <v>718</v>
@@ -32623,7 +32632,7 @@
         <v>867</v>
       </c>
       <c r="AD206" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="AE206" s="1" t="s">
         <v>867</v>
@@ -32657,10 +32666,10 @@
         <v>720</v>
       </c>
       <c r="AU206" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="AV206" s="1" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="AW206" s="1" t="s">
         <v>721</v>
@@ -32762,7 +32771,7 @@
         <v>867</v>
       </c>
       <c r="AD207" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="AE207" s="1" t="s">
         <v>867</v>
@@ -32796,13 +32805,13 @@
         <v>709</v>
       </c>
       <c r="AT207" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="AU207" s="1" t="s">
         <v>724</v>
       </c>
       <c r="AV207" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="AW207" s="1" t="s">
         <v>725</v>
@@ -32904,7 +32913,7 @@
         <v>867</v>
       </c>
       <c r="AD208" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="AE208" s="1" t="s">
         <v>867</v>
@@ -32935,7 +32944,7 @@
         <v>728</v>
       </c>
       <c r="AV208" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW208" s="1" t="s">
         <v>729</v>
@@ -33071,16 +33080,16 @@
         <v>720</v>
       </c>
       <c r="AU209" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="AV209" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="AW209" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="AV209" s="1" t="s">
-        <v>1216</v>
-      </c>
-      <c r="AW209" s="1" t="s">
-        <v>1264</v>
-      </c>
       <c r="AX209" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="AY209">
         <f t="shared" si="3"/>
@@ -33192,7 +33201,7 @@
         <v>867</v>
       </c>
       <c r="AJ210" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="AK210" s="1" t="s">
         <v>709</v>
@@ -33204,28 +33213,28 @@
         <v>867</v>
       </c>
       <c r="AN210" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="AO210" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="AP210" s="1" t="s">
         <v>709</v>
       </c>
       <c r="AQ210" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="AU210" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="AV210" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="AW210" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="AV210" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="AW210" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="AX210" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="AY210">
         <f t="shared" si="3"/>
@@ -33349,19 +33358,19 @@
         <v>867</v>
       </c>
       <c r="AP211" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="AQ211" s="1" t="s">
         <v>1260</v>
-      </c>
-      <c r="AQ211" s="1" t="s">
-        <v>1261</v>
       </c>
       <c r="AU211" s="1" t="s">
         <v>736</v>
       </c>
       <c r="AV211" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="AW211" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="AX211" s="1" t="s">
         <v>737</v>
@@ -33491,7 +33500,7 @@
         <v>330</v>
       </c>
       <c r="AV212" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW212" s="1" t="s">
         <v>742</v>
@@ -33627,7 +33636,7 @@
         <v>745</v>
       </c>
       <c r="AV213" s="1" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="AW213" s="1" t="s">
         <v>746</v>
@@ -33729,7 +33738,7 @@
         <v>867</v>
       </c>
       <c r="AD214" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="AE214" s="1" t="s">
         <v>867</v>
@@ -33757,13 +33766,13 @@
         <v>867</v>
       </c>
       <c r="AT214" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="AU214" s="1" t="s">
         <v>748</v>
       </c>
       <c r="AV214" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW214" s="1" t="s">
         <v>749</v>
@@ -33784,7 +33793,7 @@
         <v>739</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>740</v>
@@ -33823,7 +33832,7 @@
         <v>867</v>
       </c>
       <c r="P215" s="1" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="Q215" s="3" t="s">
         <v>867</v>
@@ -33896,7 +33905,7 @@
         <v>434</v>
       </c>
       <c r="AV215" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW215" s="1" t="s">
         <v>751</v>
@@ -33917,7 +33926,7 @@
         <v>739</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>740</v>
@@ -33980,7 +33989,7 @@
         <v>867</v>
       </c>
       <c r="X216" s="1" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="Y216" s="1" t="s">
         <v>867</v>
@@ -34029,7 +34038,7 @@
         <v>141</v>
       </c>
       <c r="AV216" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW216" s="1" t="s">
         <v>752</v>
@@ -34162,7 +34171,7 @@
         <v>754</v>
       </c>
       <c r="AV217" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW217" s="1" t="s">
         <v>755</v>
@@ -34231,7 +34240,7 @@
         <v>867</v>
       </c>
       <c r="S218" s="3" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="T218" s="1" t="s">
         <v>885</v>
@@ -34304,13 +34313,13 @@
         <v>759</v>
       </c>
       <c r="AS218" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AU218" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="AV218" s="1" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="AW218" s="1" t="s">
         <v>760</v>
@@ -34412,7 +34421,7 @@
         <v>867</v>
       </c>
       <c r="AD219" s="3" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="AE219" s="1" t="s">
         <v>867</v>
@@ -34443,19 +34452,19 @@
         <v>709</v>
       </c>
       <c r="AQ219" s="1" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="AU219" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="AV219" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="AW219" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="AV219" s="1" t="s">
+      <c r="AX219" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="AW219" s="1" t="s">
-        <v>1278</v>
-      </c>
-      <c r="AX219" s="1" t="s">
-        <v>1276</v>
       </c>
       <c r="AY219">
         <f t="shared" si="3"/>
@@ -34582,7 +34591,7 @@
         <v>295</v>
       </c>
       <c r="AV220" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW220" s="1" t="s">
         <v>765</v>
@@ -34654,7 +34663,7 @@
         <v>867</v>
       </c>
       <c r="T221" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="U221" s="1" t="s">
         <v>867</v>
@@ -34715,7 +34724,7 @@
         <v>207</v>
       </c>
       <c r="AV221" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW221" s="1" t="s">
         <v>768</v>
@@ -34817,7 +34826,7 @@
         <v>867</v>
       </c>
       <c r="AD222" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="AE222" s="1" t="s">
         <v>867</v>
@@ -34845,13 +34854,13 @@
         <v>867</v>
       </c>
       <c r="AS222" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="AU222" s="1" t="s">
         <v>772</v>
       </c>
       <c r="AV222" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW222" s="1" t="s">
         <v>773</v>
@@ -34990,7 +34999,7 @@
         <v>207</v>
       </c>
       <c r="AV223" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="AW223" s="1" t="s">
         <v>776</v>
@@ -35123,13 +35132,13 @@
         <v>709</v>
       </c>
       <c r="AT224" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="AU224" s="1" t="s">
         <v>778</v>
       </c>
       <c r="AV224" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="AW224" s="1" t="s">
         <v>779</v>
@@ -35268,7 +35277,7 @@
         <v>781</v>
       </c>
       <c r="AV225" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="AW225" s="1" t="s">
         <v>782</v>
@@ -35407,7 +35416,7 @@
         <v>778</v>
       </c>
       <c r="AV226" s="1" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="AW226" s="1" t="s">
         <v>784</v>
@@ -35540,7 +35549,7 @@
         <v>786</v>
       </c>
       <c r="AV227" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW227" s="1" t="s">
         <v>787</v>
@@ -35670,13 +35679,13 @@
         <v>867</v>
       </c>
       <c r="AS228" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="AU228" s="1" t="s">
         <v>790</v>
       </c>
       <c r="AV228" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW228" s="1" t="s">
         <v>791</v>
@@ -35811,7 +35820,7 @@
         <v>794</v>
       </c>
       <c r="AV229" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AW229" s="1" t="s">
         <v>795</v>
@@ -35958,7 +35967,7 @@
         <v>798</v>
       </c>
       <c r="AV230" s="1" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="AW230" s="1" t="s">
         <v>799</v>
@@ -36105,7 +36114,7 @@
         <v>207</v>
       </c>
       <c r="AV231" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="AW231" s="1" t="s">
         <v>802</v>
@@ -36121,7 +36130,7 @@
   </sheetData>
   <autoFilter ref="A1:AX231" xr:uid="{ACC8F76D-B553-4CF8-BE7D-F03409684AEE}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="施法消耗" error="請輸入大於或等於 0 的數字，或留白。" sqref="M2:M231" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0</formula1>
     </dataValidation>
@@ -36142,352 +36151,352 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
@@ -36497,62 +36506,62 @@
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
@@ -36852,7 +36861,7 @@
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
@@ -36862,7 +36871,7 @@
     </row>
     <row r="145" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F517CEFC-A6DB-4AB8-AF78-D9CF4E1D77AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F0708D-6C9D-4D20-A699-B0932988F87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -3865,10 +3865,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"pct":25,"pctPer":2.5,"manaRed":25,"manaRedPer":2.5}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>受到的傷害有 {pct}% 可轉由法力承擔，且承擔的法力消耗降低 {manaRed}%（法力消耗以本次傷害占最大生命的比例換算為最大法力百分比；法力不足的部分仍扣生命）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4220,6 +4216,10 @@
   </si>
   <si>
     <t>使 {m} 米內的敵人石化 {sec} 秒，石化時無法行動且轉變為地屬性；在 {dur} 秒內每 {gap} 秒隨機升起 {count} 道岩柱刺穿範圍內敵人，每道造成 {pct}% 地屬性傷害（每波每名敵人最多一道，不足以隨機空地補足）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"pct":25,"pctPer":2.5,"manaRed":35,"manaRedPer":3.5}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5175,7 +5175,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>856</v>
@@ -5262,7 +5262,7 @@
         <v>1045</v>
       </c>
       <c r="AW4" s="1" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="AX4" s="1" t="s">
         <v>40</v>
@@ -5310,7 +5310,7 @@
         <v>8</v>
       </c>
       <c r="M5">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>856</v>
@@ -5445,7 +5445,7 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>856</v>
@@ -5580,7 +5580,7 @@
         <v>8</v>
       </c>
       <c r="M7">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>856</v>
@@ -5685,7 +5685,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>26</v>
@@ -5715,7 +5715,7 @@
         <v>8</v>
       </c>
       <c r="M8">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>856</v>
@@ -5796,16 +5796,16 @@
         <v>856</v>
       </c>
       <c r="AU8" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="AV8" s="1" t="s">
         <v>1045</v>
       </c>
       <c r="AW8" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="AX8" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="AY8">
         <f t="shared" si="0"/>
@@ -5850,7 +5850,7 @@
         <v>856</v>
       </c>
       <c r="M9">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>856</v>
@@ -5934,16 +5934,16 @@
         <v>941</v>
       </c>
       <c r="AU9" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="AV9" s="1" t="s">
         <v>1045</v>
       </c>
       <c r="AW9" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="AX9" s="1" t="s">
         <v>1270</v>
-      </c>
-      <c r="AX9" s="1" t="s">
-        <v>1271</v>
       </c>
       <c r="AY9">
         <f t="shared" si="0"/>
@@ -5988,7 +5988,7 @@
         <v>856</v>
       </c>
       <c r="M10">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>856</v>
@@ -6126,7 +6126,7 @@
         <v>856</v>
       </c>
       <c r="M11">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>856</v>
@@ -6213,10 +6213,10 @@
         <v>1045</v>
       </c>
       <c r="AW11" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="AX11" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="AY11">
         <f t="shared" si="0"/>
@@ -6270,7 +6270,7 @@
         <v>856</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>856</v>
@@ -6531,7 +6531,7 @@
         <v>12</v>
       </c>
       <c r="M14">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>856</v>
@@ -6666,7 +6666,7 @@
         <v>12</v>
       </c>
       <c r="M15">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>856</v>
@@ -6801,7 +6801,7 @@
         <v>12</v>
       </c>
       <c r="M16">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>856</v>
@@ -6935,7 +6935,7 @@
         <v>12</v>
       </c>
       <c r="M17">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>856</v>
@@ -7066,7 +7066,7 @@
         <v>12</v>
       </c>
       <c r="M18">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>856</v>
@@ -7143,7 +7143,7 @@
       <c r="AL18" s="1"/>
       <c r="AM18" s="1"/>
       <c r="AU18" s="1" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="AV18" s="1" t="s">
         <v>1045</v>
@@ -7197,7 +7197,7 @@
         <v>856</v>
       </c>
       <c r="M19">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>856</v>
@@ -7272,7 +7272,7 @@
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
       <c r="AU19" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="AV19" s="1" t="s">
         <v>1045</v>
@@ -7326,7 +7326,7 @@
         <v>856</v>
       </c>
       <c r="M20">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>856</v>
@@ -7377,7 +7377,7 @@
         <v>856</v>
       </c>
       <c r="AD20" s="3" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="AE20" s="1" t="s">
         <v>856</v>
@@ -7401,7 +7401,7 @@
       <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
       <c r="AN20" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="AP20" s="1" t="s">
         <v>698</v>
@@ -7410,16 +7410,16 @@
         <v>94</v>
       </c>
       <c r="AU20" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="AV20" s="1" t="s">
         <v>1286</v>
       </c>
-      <c r="AV20" s="1" t="s">
+      <c r="AW20" s="1" t="s">
         <v>1287</v>
       </c>
-      <c r="AW20" s="1" t="s">
-        <v>1288</v>
-      </c>
       <c r="AX20" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="AY20">
         <f t="shared" si="0"/>
@@ -7464,7 +7464,7 @@
         <v>856</v>
       </c>
       <c r="M21">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>856</v>
@@ -7545,13 +7545,13 @@
         <v>856</v>
       </c>
       <c r="AU21" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="AV21" s="1" t="s">
         <v>1045</v>
       </c>
       <c r="AW21" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="AX21" s="1" t="s">
         <v>97</v>
@@ -7680,7 +7680,7 @@
         <v>856</v>
       </c>
       <c r="AU22" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="AV22" s="1" t="s">
         <v>1045</v>
@@ -7869,7 +7869,7 @@
         <v>8</v>
       </c>
       <c r="M24">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>856</v>
@@ -8004,7 +8004,7 @@
         <v>8</v>
       </c>
       <c r="M25">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>856</v>
@@ -8085,7 +8085,7 @@
         <v>856</v>
       </c>
       <c r="AU25" s="1" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="AV25" s="1" t="s">
         <v>1045</v>
@@ -8139,7 +8139,7 @@
         <v>8</v>
       </c>
       <c r="M26">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>856</v>
@@ -8220,7 +8220,7 @@
         <v>856</v>
       </c>
       <c r="AU26" s="1" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="AV26" s="1" t="s">
         <v>1045</v>
@@ -8274,7 +8274,7 @@
         <v>8</v>
       </c>
       <c r="M27">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>856</v>
@@ -8355,7 +8355,7 @@
         <v>856</v>
       </c>
       <c r="AU27" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="AV27" s="1" t="s">
         <v>1045</v>
@@ -8409,7 +8409,7 @@
         <v>8</v>
       </c>
       <c r="M28">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>856</v>
@@ -8544,7 +8544,7 @@
         <v>856</v>
       </c>
       <c r="M29">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>856</v>
@@ -8679,7 +8679,7 @@
         <v>856</v>
       </c>
       <c r="M30">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N30" s="3" t="s">
         <v>856</v>
@@ -8817,7 +8817,7 @@
         <v>856</v>
       </c>
       <c r="M31">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N31" s="3" t="s">
         <v>856</v>
@@ -8898,7 +8898,7 @@
         <v>856</v>
       </c>
       <c r="AU31" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="AV31" s="1" t="s">
         <v>1045</v>
@@ -9039,7 +9039,7 @@
         <v>1045</v>
       </c>
       <c r="AW32" s="1" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="AX32" s="1" t="s">
         <v>139</v>
@@ -9168,7 +9168,7 @@
         <v>856</v>
       </c>
       <c r="AU33" s="1" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="AV33" s="1" t="s">
         <v>1045</v>
@@ -9222,7 +9222,7 @@
         <v>8</v>
       </c>
       <c r="M34">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>856</v>
@@ -9303,7 +9303,7 @@
         <v>856</v>
       </c>
       <c r="AU34" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="AV34" s="1" t="s">
         <v>1045</v>
@@ -9357,7 +9357,7 @@
         <v>8</v>
       </c>
       <c r="M35">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>856</v>
@@ -9438,7 +9438,7 @@
         <v>856</v>
       </c>
       <c r="AU35" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="AV35" s="1" t="s">
         <v>1045</v>
@@ -9492,7 +9492,7 @@
         <v>8</v>
       </c>
       <c r="M36">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N36" s="3" t="s">
         <v>856</v>
@@ -9576,7 +9576,7 @@
         <v>945</v>
       </c>
       <c r="AU36" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="AV36" s="1" t="s">
         <v>1045</v>
@@ -9630,7 +9630,7 @@
         <v>8</v>
       </c>
       <c r="M37">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N37" s="3" t="s">
         <v>856</v>
@@ -9765,7 +9765,7 @@
         <v>8</v>
       </c>
       <c r="M38">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N38" s="3" t="s">
         <v>883</v>
@@ -9900,7 +9900,7 @@
         <v>856</v>
       </c>
       <c r="M39">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N39" s="3" t="s">
         <v>856</v>
@@ -10038,7 +10038,7 @@
         <v>856</v>
       </c>
       <c r="M40">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>856</v>
@@ -10122,16 +10122,16 @@
         <v>165</v>
       </c>
       <c r="AU40" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="AV40" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AW40" s="1" t="s">
         <v>1299</v>
       </c>
-      <c r="AW40" s="1" t="s">
+      <c r="AX40" s="1" t="s">
         <v>1300</v>
-      </c>
-      <c r="AX40" s="1" t="s">
-        <v>1301</v>
       </c>
       <c r="AY40">
         <f>LEN(AW40)</f>
@@ -10176,13 +10176,13 @@
         <v>856</v>
       </c>
       <c r="M41">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>856</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>856</v>
@@ -10257,16 +10257,16 @@
         <v>856</v>
       </c>
       <c r="AU41" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="AV41" s="1" t="s">
         <v>1302</v>
       </c>
-      <c r="AV41" s="1" t="s">
+      <c r="AW41" s="1" t="s">
         <v>1303</v>
       </c>
-      <c r="AW41" s="1" t="s">
+      <c r="AX41" s="1" t="s">
         <v>1304</v>
-      </c>
-      <c r="AX41" s="1" t="s">
-        <v>1305</v>
       </c>
       <c r="AY41">
         <f>LEN(AW41)</f>
@@ -10578,7 +10578,7 @@
         <v>8</v>
       </c>
       <c r="M44">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>856</v>
@@ -10713,7 +10713,7 @@
         <v>8</v>
       </c>
       <c r="M45">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>856</v>
@@ -10849,7 +10849,7 @@
         <v>8</v>
       </c>
       <c r="M46">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>856</v>
@@ -10990,7 +10990,7 @@
         <v>8</v>
       </c>
       <c r="M47">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>856</v>
@@ -11124,7 +11124,7 @@
         <v>8</v>
       </c>
       <c r="M48">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>856</v>
@@ -11257,7 +11257,7 @@
         <v>856</v>
       </c>
       <c r="M49">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>856</v>
@@ -11348,7 +11348,7 @@
         <v>1045</v>
       </c>
       <c r="AW49" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="AX49" s="1" t="s">
         <v>199</v>
@@ -11396,7 +11396,7 @@
         <v>856</v>
       </c>
       <c r="M50">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N50" s="3" t="s">
         <v>856</v>
@@ -11405,7 +11405,7 @@
         <v>856</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>856</v>
@@ -11485,7 +11485,7 @@
         <v>948</v>
       </c>
       <c r="AU50" s="1" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="AV50" s="1" t="s">
         <v>1060</v>
@@ -11539,7 +11539,7 @@
         <v>856</v>
       </c>
       <c r="M51">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N51" s="3" t="s">
         <v>856</v>
@@ -11630,7 +11630,7 @@
         <v>1053</v>
       </c>
       <c r="AW51" s="1" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="AX51" s="1" t="s">
         <v>933</v>
@@ -11942,7 +11942,7 @@
         <v>8</v>
       </c>
       <c r="M54">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>856</v>
@@ -12075,7 +12075,7 @@
         <v>8</v>
       </c>
       <c r="M55">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N55" s="3" t="s">
         <v>856</v>
@@ -12213,7 +12213,7 @@
         <v>8</v>
       </c>
       <c r="M56">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N56" s="3" t="s">
         <v>856</v>
@@ -12354,7 +12354,7 @@
         <v>8</v>
       </c>
       <c r="M57">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>856</v>
@@ -12489,7 +12489,7 @@
         <v>8</v>
       </c>
       <c r="M58">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>856</v>
@@ -12625,7 +12625,7 @@
         <v>856</v>
       </c>
       <c r="M59">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>856</v>
@@ -12760,7 +12760,7 @@
         <v>856</v>
       </c>
       <c r="M60">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>856</v>
@@ -12898,7 +12898,7 @@
         <v>856</v>
       </c>
       <c r="M61">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N61" s="3" t="s">
         <v>856</v>
@@ -13303,7 +13303,7 @@
         <v>0</v>
       </c>
       <c r="M64">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N64" s="3" t="s">
         <v>856</v>
@@ -13438,7 +13438,7 @@
         <v>0</v>
       </c>
       <c r="M65">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N65" s="3" t="s">
         <v>856</v>
@@ -13573,7 +13573,7 @@
         <v>0</v>
       </c>
       <c r="M66">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>856</v>
@@ -13711,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="M67">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N67" s="3" t="s">
         <v>856</v>
@@ -13846,7 +13846,7 @@
         <v>0</v>
       </c>
       <c r="M68">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N68" s="3" t="s">
         <v>856</v>
@@ -13981,7 +13981,7 @@
         <v>856</v>
       </c>
       <c r="M69">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N69" s="3" t="s">
         <v>856</v>
@@ -14122,7 +14122,7 @@
         <v>856</v>
       </c>
       <c r="M70">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>856</v>
@@ -14261,7 +14261,7 @@
         <v>856</v>
       </c>
       <c r="M71">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N71" s="3" t="s">
         <v>856</v>
@@ -14672,7 +14672,7 @@
         <v>40</v>
       </c>
       <c r="M74">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N74" s="3" t="s">
         <v>856</v>
@@ -14805,7 +14805,7 @@
         <v>40</v>
       </c>
       <c r="M75">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N75" s="3" t="s">
         <v>856</v>
@@ -14938,7 +14938,7 @@
         <v>40</v>
       </c>
       <c r="M76">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>856</v>
@@ -15071,7 +15071,7 @@
         <v>40</v>
       </c>
       <c r="M77">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N77" s="3" t="s">
         <v>856</v>
@@ -15150,7 +15150,7 @@
         <v>856</v>
       </c>
       <c r="AU77" s="1" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="AV77" s="1" t="s">
         <v>1108</v>
@@ -15204,7 +15204,7 @@
         <v>40</v>
       </c>
       <c r="M78">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N78" s="3" t="s">
         <v>856</v>
@@ -15341,7 +15341,7 @@
         <v>856</v>
       </c>
       <c r="M79">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N79" s="3" t="s">
         <v>856</v>
@@ -15477,7 +15477,7 @@
         <v>856</v>
       </c>
       <c r="M80">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N80" s="3" t="s">
         <v>856</v>
@@ -15616,7 +15616,7 @@
         <v>856</v>
       </c>
       <c r="M81">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>856</v>
@@ -16024,7 +16024,7 @@
         <v>8</v>
       </c>
       <c r="M84">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N84" s="3" t="s">
         <v>856</v>
@@ -16157,7 +16157,7 @@
         <v>8</v>
       </c>
       <c r="M85">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N85" s="3" t="s">
         <v>856</v>
@@ -16290,7 +16290,7 @@
         <v>8</v>
       </c>
       <c r="M86">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N86" s="3" t="s">
         <v>856</v>
@@ -16423,7 +16423,7 @@
         <v>8</v>
       </c>
       <c r="M87">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N87" s="3" t="s">
         <v>856</v>
@@ -16559,7 +16559,7 @@
         <v>8</v>
       </c>
       <c r="M88">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N88" s="3" t="s">
         <v>885</v>
@@ -16692,7 +16692,7 @@
         <v>856</v>
       </c>
       <c r="M89">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>856</v>
@@ -16825,7 +16825,7 @@
         <v>856</v>
       </c>
       <c r="M90">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N90" s="3" t="s">
         <v>856</v>
@@ -16910,7 +16910,7 @@
         <v>960</v>
       </c>
       <c r="AU90" s="1" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="AV90" s="1" t="s">
         <v>1110</v>
@@ -16934,7 +16934,7 @@
         <v>856</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>856</v>
@@ -16964,7 +16964,7 @@
         <v>856</v>
       </c>
       <c r="M91">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>856</v>
@@ -17043,7 +17043,7 @@
         <v>856</v>
       </c>
       <c r="AU91" s="1" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="AV91" s="1" t="s">
         <v>1045</v>
@@ -17363,7 +17363,7 @@
         <v>8</v>
       </c>
       <c r="M94">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>856</v>
@@ -17496,7 +17496,7 @@
         <v>8</v>
       </c>
       <c r="M95">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N95" s="3" t="s">
         <v>856</v>
@@ -17632,7 +17632,7 @@
         <v>8</v>
       </c>
       <c r="M96">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>856</v>
@@ -17771,7 +17771,7 @@
         <v>8</v>
       </c>
       <c r="M97">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N97" s="3" t="s">
         <v>856</v>
@@ -17904,7 +17904,7 @@
         <v>8</v>
       </c>
       <c r="M98">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N98" s="3" t="s">
         <v>856</v>
@@ -18037,7 +18037,7 @@
         <v>856</v>
       </c>
       <c r="M99">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N99" s="3" t="s">
         <v>856</v>
@@ -18176,7 +18176,7 @@
         <v>856</v>
       </c>
       <c r="M100">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>856</v>
@@ -18312,7 +18312,7 @@
         <v>856</v>
       </c>
       <c r="M101">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>856</v>
@@ -18717,7 +18717,7 @@
         <v>8</v>
       </c>
       <c r="M104">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N104" s="3" t="s">
         <v>856</v>
@@ -18853,7 +18853,7 @@
         <v>8</v>
       </c>
       <c r="M105">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N105" s="3" t="s">
         <v>856</v>
@@ -18986,7 +18986,7 @@
         <v>8</v>
       </c>
       <c r="M106">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N106" s="3" t="s">
         <v>856</v>
@@ -19119,7 +19119,7 @@
         <v>8</v>
       </c>
       <c r="M107">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N107" s="3" t="s">
         <v>856</v>
@@ -19252,7 +19252,7 @@
         <v>8</v>
       </c>
       <c r="M108">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N108" s="3" t="s">
         <v>856</v>
@@ -19385,7 +19385,7 @@
         <v>856</v>
       </c>
       <c r="M109">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N109" s="3" t="s">
         <v>856</v>
@@ -19521,7 +19521,7 @@
         <v>856</v>
       </c>
       <c r="M110">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N110" s="3" t="s">
         <v>856</v>
@@ -19657,7 +19657,7 @@
         <v>856</v>
       </c>
       <c r="M111">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N111" s="3" t="s">
         <v>856</v>
@@ -20062,7 +20062,7 @@
         <v>8</v>
       </c>
       <c r="M114">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N114" s="3" t="s">
         <v>856</v>
@@ -20195,7 +20195,7 @@
         <v>8</v>
       </c>
       <c r="M115">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N115" s="3" t="s">
         <v>856</v>
@@ -20328,7 +20328,7 @@
         <v>8</v>
       </c>
       <c r="M116">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N116" s="3" t="s">
         <v>856</v>
@@ -20461,7 +20461,7 @@
         <v>8</v>
       </c>
       <c r="M117">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N117" s="3" t="s">
         <v>856</v>
@@ -20597,7 +20597,7 @@
         <v>8</v>
       </c>
       <c r="M118">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N118" s="3" t="s">
         <v>856</v>
@@ -20730,7 +20730,7 @@
         <v>856</v>
       </c>
       <c r="M119">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N119" s="3" t="s">
         <v>856</v>
@@ -20809,7 +20809,7 @@
         <v>856</v>
       </c>
       <c r="AN119" s="1" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="AP119" s="1" t="s">
         <v>249</v>
@@ -20821,16 +20821,16 @@
         <v>964</v>
       </c>
       <c r="AU119" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="AV119" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="AW119" s="1" t="s">
         <v>1312</v>
       </c>
-      <c r="AW119" s="1" t="s">
-        <v>1313</v>
-      </c>
       <c r="AX119" s="1" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="AY119">
         <f t="shared" si="1"/>
@@ -20875,7 +20875,7 @@
         <v>856</v>
       </c>
       <c r="M120">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N120" s="3" t="s">
         <v>856</v>
@@ -21008,7 +21008,7 @@
         <v>856</v>
       </c>
       <c r="M121">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N121" s="3" t="s">
         <v>856</v>
@@ -21150,13 +21150,13 @@
         <v>25</v>
       </c>
       <c r="N122" s="3" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="O122" s="3" t="s">
         <v>856</v>
       </c>
       <c r="P122" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q122" s="1" t="s">
         <v>856</v>
@@ -21416,7 +21416,7 @@
         <v>8</v>
       </c>
       <c r="M124">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N124" s="3" t="s">
         <v>856</v>
@@ -21552,7 +21552,7 @@
         <v>8</v>
       </c>
       <c r="M125">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N125" s="3" t="s">
         <v>856</v>
@@ -21685,7 +21685,7 @@
         <v>8</v>
       </c>
       <c r="M126">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N126" s="3" t="s">
         <v>856</v>
@@ -21818,7 +21818,7 @@
         <v>8</v>
       </c>
       <c r="M127">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N127" s="3" t="s">
         <v>856</v>
@@ -21951,7 +21951,7 @@
         <v>8</v>
       </c>
       <c r="M128">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N128" s="3" t="s">
         <v>856</v>
@@ -22087,7 +22087,7 @@
         <v>856</v>
       </c>
       <c r="M129">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N129" s="3" t="s">
         <v>856</v>
@@ -22223,7 +22223,7 @@
         <v>856</v>
       </c>
       <c r="M130">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N130" s="3" t="s">
         <v>856</v>
@@ -22362,7 +22362,7 @@
         <v>856</v>
       </c>
       <c r="M131">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N131" s="3" t="s">
         <v>856</v>
@@ -22761,7 +22761,7 @@
         <v>0</v>
       </c>
       <c r="M134">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N134" s="3" t="s">
         <v>856</v>
@@ -22894,7 +22894,7 @@
         <v>0</v>
       </c>
       <c r="M135">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N135" s="3" t="s">
         <v>856</v>
@@ -23027,7 +23027,7 @@
         <v>0</v>
       </c>
       <c r="M136">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N136" s="3" t="s">
         <v>856</v>
@@ -23106,16 +23106,16 @@
         <v>856</v>
       </c>
       <c r="AU136" s="1" t="s">
-        <v>1224</v>
+        <v>1313</v>
       </c>
       <c r="AV136" s="1" t="s">
         <v>1045</v>
       </c>
       <c r="AW136" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="AX136" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="AY136">
         <f t="shared" si="2"/>
@@ -23160,7 +23160,7 @@
         <v>0</v>
       </c>
       <c r="M137">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N137" s="3" t="s">
         <v>856</v>
@@ -23293,7 +23293,7 @@
         <v>0</v>
       </c>
       <c r="M138">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N138" s="3" t="s">
         <v>856</v>
@@ -23429,7 +23429,7 @@
         <v>856</v>
       </c>
       <c r="M139">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N139" s="3" t="s">
         <v>856</v>
@@ -23562,7 +23562,7 @@
         <v>856</v>
       </c>
       <c r="M140">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N140" s="3" t="s">
         <v>856</v>
@@ -23695,7 +23695,7 @@
         <v>856</v>
       </c>
       <c r="M141">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N141" s="3" t="s">
         <v>856</v>
@@ -24092,7 +24092,7 @@
         <v>6</v>
       </c>
       <c r="M144">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N144" s="3" t="s">
         <v>856</v>
@@ -24225,7 +24225,7 @@
         <v>6</v>
       </c>
       <c r="M145">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N145" s="3" t="s">
         <v>856</v>
@@ -24358,7 +24358,7 @@
         <v>6</v>
       </c>
       <c r="M146">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N146" s="3" t="s">
         <v>856</v>
@@ -24491,7 +24491,7 @@
         <v>6</v>
       </c>
       <c r="M147">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N147" s="3" t="s">
         <v>856</v>
@@ -24624,7 +24624,7 @@
         <v>6</v>
       </c>
       <c r="M148">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N148" s="3" t="s">
         <v>856</v>
@@ -24757,7 +24757,7 @@
         <v>856</v>
       </c>
       <c r="M149">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N149" s="3" t="s">
         <v>856</v>
@@ -24887,7 +24887,7 @@
         <v>856</v>
       </c>
       <c r="M150">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N150" s="3" t="s">
         <v>856</v>
@@ -25029,7 +25029,7 @@
         <v>856</v>
       </c>
       <c r="M151">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N151" s="3" t="s">
         <v>856</v>
@@ -25431,7 +25431,7 @@
         <v>8</v>
       </c>
       <c r="M154">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N154" s="3" t="s">
         <v>856</v>
@@ -25564,7 +25564,7 @@
         <v>8</v>
       </c>
       <c r="M155">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N155" s="3" t="s">
         <v>856</v>
@@ -25697,7 +25697,7 @@
         <v>8</v>
       </c>
       <c r="M156">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N156" s="3" t="s">
         <v>856</v>
@@ -25833,7 +25833,7 @@
         <v>8</v>
       </c>
       <c r="M157">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N157" s="3" t="s">
         <v>856</v>
@@ -25966,7 +25966,7 @@
         <v>8</v>
       </c>
       <c r="M158">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N158" s="3" t="s">
         <v>856</v>
@@ -26099,7 +26099,7 @@
         <v>856</v>
       </c>
       <c r="M159">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N159" s="3" t="s">
         <v>856</v>
@@ -26232,7 +26232,7 @@
         <v>856</v>
       </c>
       <c r="M160">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N160" s="3" t="s">
         <v>856</v>
@@ -26368,7 +26368,7 @@
         <v>856</v>
       </c>
       <c r="M161">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N161" s="3" t="s">
         <v>856</v>
@@ -26765,7 +26765,7 @@
         <v>8</v>
       </c>
       <c r="M164">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N164" s="3" t="s">
         <v>856</v>
@@ -26898,7 +26898,7 @@
         <v>8</v>
       </c>
       <c r="M165">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N165" s="3" t="s">
         <v>856</v>
@@ -27030,7 +27030,7 @@
         <v>8</v>
       </c>
       <c r="M166">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N166" s="3" t="s">
         <v>856</v>
@@ -27163,7 +27163,7 @@
         <v>8</v>
       </c>
       <c r="M167">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N167" s="3" t="s">
         <v>856</v>
@@ -27294,7 +27294,7 @@
         <v>8</v>
       </c>
       <c r="M168">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N168" s="3" t="s">
         <v>856</v>
@@ -27434,7 +27434,7 @@
         <v>856</v>
       </c>
       <c r="M169">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N169" s="3" t="s">
         <v>856</v>
@@ -27567,7 +27567,7 @@
         <v>856</v>
       </c>
       <c r="M170">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N170" s="3" t="s">
         <v>856</v>
@@ -27706,7 +27706,7 @@
         <v>856</v>
       </c>
       <c r="M171">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N171" s="3" t="s">
         <v>856</v>
@@ -28108,7 +28108,7 @@
         <v>10</v>
       </c>
       <c r="M174">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N174" s="3" t="s">
         <v>856</v>
@@ -28241,7 +28241,7 @@
         <v>10</v>
       </c>
       <c r="M175">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N175" s="3" t="s">
         <v>856</v>
@@ -28374,7 +28374,7 @@
         <v>10</v>
       </c>
       <c r="M176">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N176" s="3" t="s">
         <v>856</v>
@@ -28507,7 +28507,7 @@
         <v>10</v>
       </c>
       <c r="M177">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N177" s="3" t="s">
         <v>856</v>
@@ -28640,7 +28640,7 @@
         <v>10</v>
       </c>
       <c r="M178">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N178" s="3" t="s">
         <v>856</v>
@@ -28772,7 +28772,7 @@
         <v>856</v>
       </c>
       <c r="M179">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N179" s="3" t="s">
         <v>856</v>
@@ -28905,7 +28905,7 @@
         <v>856</v>
       </c>
       <c r="M180">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N180" s="3" t="s">
         <v>856</v>
@@ -29038,7 +29038,7 @@
         <v>856</v>
       </c>
       <c r="M181">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N181" s="3" t="s">
         <v>856</v>
@@ -29444,7 +29444,7 @@
         <v>8</v>
       </c>
       <c r="M184">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N184" s="3" t="s">
         <v>856</v>
@@ -29580,7 +29580,7 @@
         <v>8</v>
       </c>
       <c r="M185">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N185" s="3" t="s">
         <v>856</v>
@@ -29713,7 +29713,7 @@
         <v>8</v>
       </c>
       <c r="M186">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N186" s="3" t="s">
         <v>856</v>
@@ -29852,7 +29852,7 @@
         <v>8</v>
       </c>
       <c r="M187">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N187" s="3" t="s">
         <v>856</v>
@@ -29985,7 +29985,7 @@
         <v>8</v>
       </c>
       <c r="M188">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N188" s="3" t="s">
         <v>856</v>
@@ -30067,7 +30067,7 @@
         <v>652</v>
       </c>
       <c r="AU188" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="AV188" s="1" t="s">
         <v>1192</v>
@@ -30121,7 +30121,7 @@
         <v>856</v>
       </c>
       <c r="M189">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N189" s="3" t="s">
         <v>856</v>
@@ -30230,7 +30230,7 @@
         <v>856</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>856</v>
@@ -30260,7 +30260,7 @@
         <v>856</v>
       </c>
       <c r="M190">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N190" s="3" t="s">
         <v>856</v>
@@ -30339,22 +30339,22 @@
         <v>856</v>
       </c>
       <c r="AQ190" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="AR190" s="1" t="s">
         <v>1231</v>
       </c>
-      <c r="AR190" s="1" t="s">
+      <c r="AU190" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="AV190" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="AU190" s="1" t="s">
-        <v>1240</v>
-      </c>
-      <c r="AV190" s="1" t="s">
-        <v>1233</v>
-      </c>
       <c r="AW190" s="1" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="AX190" s="1" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="AY190">
         <f t="shared" si="2"/>
@@ -30399,7 +30399,7 @@
         <v>856</v>
       </c>
       <c r="M191">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N191" s="3" t="s">
         <v>856</v>
@@ -30411,7 +30411,7 @@
         <v>856</v>
       </c>
       <c r="Q191" s="3" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="R191" s="1" t="s">
         <v>856</v>
@@ -30484,16 +30484,16 @@
         <v>1066</v>
       </c>
       <c r="AU191" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="AV191" s="1" t="s">
         <v>1193</v>
       </c>
       <c r="AW191" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="AX191" s="1" t="s">
         <v>1228</v>
-      </c>
-      <c r="AX191" s="1" t="s">
-        <v>1229</v>
       </c>
       <c r="AY191">
         <f t="shared" si="2"/>
@@ -30807,7 +30807,7 @@
         <v>8</v>
       </c>
       <c r="M194">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N194" s="3" t="s">
         <v>856</v>
@@ -30943,7 +30943,7 @@
         <v>8</v>
       </c>
       <c r="M195">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N195" s="3" t="s">
         <v>856</v>
@@ -31076,7 +31076,7 @@
         <v>8</v>
       </c>
       <c r="M196">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N196" s="3" t="s">
         <v>856</v>
@@ -31209,7 +31209,7 @@
         <v>8</v>
       </c>
       <c r="M197">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N197" s="3" t="s">
         <v>856</v>
@@ -31342,7 +31342,7 @@
         <v>8</v>
       </c>
       <c r="M198">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N198" s="3" t="s">
         <v>856</v>
@@ -31478,7 +31478,7 @@
         <v>856</v>
       </c>
       <c r="M199">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N199" s="3" t="s">
         <v>856</v>
@@ -31611,56 +31611,56 @@
         <v>856</v>
       </c>
       <c r="M200">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N200" s="3" t="s">
         <v>856</v>
       </c>
       <c r="O200" s="1"/>
       <c r="P200" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="Q200" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="R200" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="S200" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="T200" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="U200" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="V200" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="W200" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="X200" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="Y200" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="Z200" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA200" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="AB200" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC200" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="AD200" s="3" t="s">
         <v>1234</v>
-      </c>
-      <c r="Q200" s="3" t="s">
-        <v>856</v>
-      </c>
-      <c r="R200" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="S200" s="3" t="s">
-        <v>856</v>
-      </c>
-      <c r="T200" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="U200" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="V200" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="W200" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="X200" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="Y200" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="Z200" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="AA200" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="AB200" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="AC200" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="AD200" s="3" t="s">
-        <v>1235</v>
       </c>
       <c r="AE200" s="1" t="s">
         <v>856</v>
@@ -31688,19 +31688,19 @@
         <v>856</v>
       </c>
       <c r="AN200" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="AU200" s="1" t="s">
         <v>1236</v>
       </c>
-      <c r="AU200" s="1" t="s">
+      <c r="AV200" s="1" t="s">
         <v>1237</v>
       </c>
-      <c r="AV200" s="1" t="s">
+      <c r="AW200" s="1" t="s">
         <v>1238</v>
       </c>
-      <c r="AW200" s="1" t="s">
-        <v>1239</v>
-      </c>
       <c r="AX200" s="1" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="AY200">
         <f t="shared" si="3"/>
@@ -31745,7 +31745,7 @@
         <v>856</v>
       </c>
       <c r="M201">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N201" s="3" t="s">
         <v>856</v>
@@ -31824,7 +31824,7 @@
         <v>856</v>
       </c>
       <c r="AQ201" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="AU201" s="1" t="s">
         <v>690</v>
@@ -32147,7 +32147,7 @@
         <v>8</v>
       </c>
       <c r="M204">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N204" s="3" t="s">
         <v>856</v>
@@ -32280,7 +32280,7 @@
         <v>8</v>
       </c>
       <c r="M205">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N205" s="3" t="s">
         <v>856</v>
@@ -32419,7 +32419,7 @@
         <v>8</v>
       </c>
       <c r="M206">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N206" s="3" t="s">
         <v>856</v>
@@ -32558,7 +32558,7 @@
         <v>8</v>
       </c>
       <c r="M207">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N207" s="3" t="s">
         <v>856</v>
@@ -32700,7 +32700,7 @@
         <v>8</v>
       </c>
       <c r="M208">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N208" s="3" t="s">
         <v>856</v>
@@ -32833,7 +32833,7 @@
         <v>856</v>
       </c>
       <c r="M209">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N209" s="3" t="s">
         <v>856</v>
@@ -32918,16 +32918,16 @@
         <v>709</v>
       </c>
       <c r="AU209" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="AV209" s="1" t="s">
         <v>1201</v>
       </c>
       <c r="AW209" s="1" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="AX209" s="1" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="AY209">
         <f t="shared" si="3"/>
@@ -32972,7 +32972,7 @@
         <v>856</v>
       </c>
       <c r="M210">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N210" s="3" t="s">
         <v>856</v>
@@ -33039,7 +33039,7 @@
         <v>856</v>
       </c>
       <c r="AJ210" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="AK210" s="1" t="s">
         <v>698</v>
@@ -33051,28 +33051,28 @@
         <v>856</v>
       </c>
       <c r="AN210" s="1" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="AO210" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="AP210" s="1" t="s">
         <v>698</v>
       </c>
       <c r="AQ210" s="1" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="AU210" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="AV210" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="AW210" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="AV210" s="1" t="s">
-        <v>1255</v>
-      </c>
-      <c r="AW210" s="1" t="s">
-        <v>1251</v>
-      </c>
       <c r="AX210" s="1" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="AY210">
         <f t="shared" si="3"/>
@@ -33117,7 +33117,7 @@
         <v>856</v>
       </c>
       <c r="M211">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N211" s="3" t="s">
         <v>856</v>
@@ -33196,19 +33196,19 @@
         <v>856</v>
       </c>
       <c r="AP211" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="AQ211" s="1" t="s">
         <v>1245</v>
-      </c>
-      <c r="AQ211" s="1" t="s">
-        <v>1246</v>
       </c>
       <c r="AU211" s="1" t="s">
         <v>725</v>
       </c>
       <c r="AV211" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="AW211" s="1" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="AX211" s="1" t="s">
         <v>726</v>
@@ -33525,7 +33525,7 @@
         <v>8</v>
       </c>
       <c r="M214">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N214" s="3" t="s">
         <v>856</v>
@@ -33631,7 +33631,7 @@
         <v>728</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>729</v>
@@ -33661,7 +33661,7 @@
         <v>8</v>
       </c>
       <c r="M215">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N215" s="3" t="s">
         <v>856</v>
@@ -33670,7 +33670,7 @@
         <v>856</v>
       </c>
       <c r="P215" s="1" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="Q215" s="3" t="s">
         <v>856</v>
@@ -33764,7 +33764,7 @@
         <v>728</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>729</v>
@@ -33794,7 +33794,7 @@
         <v>8</v>
       </c>
       <c r="M216">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N216" s="3" t="s">
         <v>856</v>
@@ -33827,7 +33827,7 @@
         <v>856</v>
       </c>
       <c r="X216" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="Y216" s="1" t="s">
         <v>856</v>
@@ -33927,7 +33927,7 @@
         <v>8</v>
       </c>
       <c r="M217">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N217" s="3" t="s">
         <v>856</v>
@@ -34060,7 +34060,7 @@
         <v>8</v>
       </c>
       <c r="M218">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N218" s="3" t="s">
         <v>856</v>
@@ -34078,7 +34078,7 @@
         <v>856</v>
       </c>
       <c r="S218" s="3" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="T218" s="1" t="s">
         <v>874</v>
@@ -34208,7 +34208,7 @@
         <v>856</v>
       </c>
       <c r="M219">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N219" s="3" t="s">
         <v>856</v>
@@ -34290,19 +34290,19 @@
         <v>698</v>
       </c>
       <c r="AQ219" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="AU219" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="AV219" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="AW219" s="1" t="s">
         <v>1262</v>
       </c>
-      <c r="AV219" s="1" t="s">
+      <c r="AX219" s="1" t="s">
         <v>1260</v>
-      </c>
-      <c r="AW219" s="1" t="s">
-        <v>1263</v>
-      </c>
-      <c r="AX219" s="1" t="s">
-        <v>1261</v>
       </c>
       <c r="AY219">
         <f t="shared" si="3"/>
@@ -34347,7 +34347,7 @@
         <v>856</v>
       </c>
       <c r="M220">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N220" s="3" t="s">
         <v>856</v>
@@ -34480,7 +34480,7 @@
         <v>856</v>
       </c>
       <c r="M221">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N221" s="3" t="s">
         <v>856</v>
@@ -34888,7 +34888,7 @@
         <v>10</v>
       </c>
       <c r="M224">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N224" s="3" t="s">
         <v>856</v>
@@ -35027,7 +35027,7 @@
         <v>10</v>
       </c>
       <c r="M225">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N225" s="3" t="s">
         <v>856</v>
@@ -35166,7 +35166,7 @@
         <v>10</v>
       </c>
       <c r="M226">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="N226" s="3" t="s">
         <v>856</v>
@@ -35305,7 +35305,7 @@
         <v>10</v>
       </c>
       <c r="M227">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="N227" s="3" t="s">
         <v>856</v>
@@ -35438,7 +35438,7 @@
         <v>10</v>
       </c>
       <c r="M228">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="N228" s="3" t="s">
         <v>856</v>
@@ -35574,7 +35574,7 @@
         <v>856</v>
       </c>
       <c r="M229">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N229" s="3" t="s">
         <v>856</v>
@@ -35707,7 +35707,7 @@
         <v>856</v>
       </c>
       <c r="M230">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N230" s="3" t="s">
         <v>856</v>
@@ -35852,7 +35852,7 @@
         <v>856</v>
       </c>
       <c r="M231">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="N231" s="3" t="s">
         <v>856</v>
@@ -35962,8 +35962,8 @@
   </sheetData>
   <autoFilter ref="A1:AX231" xr:uid="{ACC8F76D-B553-4CF8-BE7D-F03409684AEE}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="施法消耗" error="請輸入大於或等於 0 的數字，或留白。" sqref="M2:M231" xr:uid="{3187FD28-75E5-4917-822A-B64AB89D8C44}">
+  <dataValidations count="1">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="施法消耗" error="請輸入大於或等於 0 的數字，或留白。" sqref="M2:M231" xr:uid="{67E86C72-A2EA-443A-8CEE-9BB96F4F1AA5}">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4830565-0E38-4AA5-8B09-1FE0515217D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DEFD04C-B60B-4D57-8979-811C26AFC3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -3927,14 +3927,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"windPct":75,"windPctPer":7.5,"earthPct":50,"earthPctPer":5,"shieldPct":2,"shieldPctPer":0.2}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>風刃具備風系與地系雙屬性；屬性傷害加成為角色風系傷害提升 ×{windPct}%＋地系傷害提升 ×{earthPct}%；風刃擊殺敵人時回復最大生命 {shieldPct}% 的護盾</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>proj-wind-crescent-09</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4243,6 +4235,14 @@
   </si>
   <si>
     <t>{"sec":2.5,"secPer":0.25,"cd":60,"cdPer":-2,"stunSec":3,"pushM":5,"pushSec":0.25}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"windPct":75,"windPctPer":7.5,"earthPct":50,"earthPctPer":5,"healPct":2,"healPctPer":0.2}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>風刃具備風系與地系雙屬性；屬性傷害加成為角色風系傷害提升 ×{windPct}%＋地系傷害提升 ×{earthPct}%；風刃擊殺敵人時回復最大生命 {healPct}% 的生命值</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5285,7 +5285,7 @@
         <v>1037</v>
       </c>
       <c r="AW4" s="1" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="AX4" s="1" t="s">
         <v>40</v>
@@ -5708,7 +5708,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>26</v>
@@ -5819,16 +5819,16 @@
         <v>848</v>
       </c>
       <c r="AU8" s="1" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="AV8" s="1" t="s">
         <v>1037</v>
       </c>
       <c r="AW8" s="1" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="AX8" s="1" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="AY8">
         <f t="shared" si="0"/>
@@ -5957,16 +5957,16 @@
         <v>933</v>
       </c>
       <c r="AU9" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="AV9" s="1" t="s">
         <v>1037</v>
       </c>
       <c r="AW9" s="1" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="AX9" s="1" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="AY9">
         <f t="shared" si="0"/>
@@ -6236,10 +6236,10 @@
         <v>1037</v>
       </c>
       <c r="AW11" s="1" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="AX11" s="1" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="AY11">
         <f t="shared" si="0"/>
@@ -6293,7 +6293,7 @@
         <v>848</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>848</v>
@@ -7166,7 +7166,7 @@
       <c r="AL18" s="1"/>
       <c r="AM18" s="1"/>
       <c r="AU18" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="AV18" s="1" t="s">
         <v>1037</v>
@@ -7295,7 +7295,7 @@
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
       <c r="AU19" s="1" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="AV19" s="1" t="s">
         <v>1037</v>
@@ -7400,7 +7400,7 @@
         <v>848</v>
       </c>
       <c r="AD20" s="3" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="AE20" s="1" t="s">
         <v>848</v>
@@ -7424,7 +7424,7 @@
       <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
       <c r="AN20" s="1" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="AP20" s="1" t="s">
         <v>690</v>
@@ -7433,16 +7433,16 @@
         <v>94</v>
       </c>
       <c r="AU20" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="AV20" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="AW20" s="1" t="s">
         <v>1273</v>
       </c>
-      <c r="AV20" s="1" t="s">
-        <v>1274</v>
-      </c>
-      <c r="AW20" s="1" t="s">
-        <v>1275</v>
-      </c>
       <c r="AX20" s="1" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="AY20">
         <f t="shared" si="0"/>
@@ -7568,13 +7568,13 @@
         <v>848</v>
       </c>
       <c r="AU21" s="1" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="AV21" s="1" t="s">
         <v>1037</v>
       </c>
       <c r="AW21" s="1" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="AX21" s="1" t="s">
         <v>97</v>
@@ -7703,7 +7703,7 @@
         <v>848</v>
       </c>
       <c r="AU22" s="1" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="AV22" s="1" t="s">
         <v>1037</v>
@@ -8108,7 +8108,7 @@
         <v>848</v>
       </c>
       <c r="AU25" s="1" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="AV25" s="1" t="s">
         <v>1037</v>
@@ -8243,7 +8243,7 @@
         <v>848</v>
       </c>
       <c r="AU26" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="AV26" s="1" t="s">
         <v>1037</v>
@@ -8378,7 +8378,7 @@
         <v>848</v>
       </c>
       <c r="AU27" s="1" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="AV27" s="1" t="s">
         <v>1037</v>
@@ -8921,7 +8921,7 @@
         <v>848</v>
       </c>
       <c r="AU31" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="AV31" s="1" t="s">
         <v>1037</v>
@@ -9062,7 +9062,7 @@
         <v>1037</v>
       </c>
       <c r="AW32" s="1" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="AX32" s="1" t="s">
         <v>139</v>
@@ -9191,7 +9191,7 @@
         <v>848</v>
       </c>
       <c r="AU33" s="1" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="AV33" s="1" t="s">
         <v>1037</v>
@@ -9326,7 +9326,7 @@
         <v>848</v>
       </c>
       <c r="AU34" s="1" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="AV34" s="1" t="s">
         <v>1037</v>
@@ -9461,7 +9461,7 @@
         <v>848</v>
       </c>
       <c r="AU35" s="1" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="AV35" s="1" t="s">
         <v>1037</v>
@@ -9599,7 +9599,7 @@
         <v>937</v>
       </c>
       <c r="AU36" s="1" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="AV36" s="1" t="s">
         <v>1037</v>
@@ -10145,16 +10145,16 @@
         <v>165</v>
       </c>
       <c r="AU40" s="1" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="AV40" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="AW40" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="AX40" s="1" t="s">
         <v>1286</v>
-      </c>
-      <c r="AW40" s="1" t="s">
-        <v>1287</v>
-      </c>
-      <c r="AX40" s="1" t="s">
-        <v>1288</v>
       </c>
       <c r="AY40">
         <f>LEN(AW40)</f>
@@ -10280,16 +10280,16 @@
         <v>848</v>
       </c>
       <c r="AU41" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="AV41" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="AW41" s="1" t="s">
         <v>1289</v>
       </c>
-      <c r="AV41" s="1" t="s">
+      <c r="AX41" s="1" t="s">
         <v>1290</v>
-      </c>
-      <c r="AW41" s="1" t="s">
-        <v>1291</v>
-      </c>
-      <c r="AX41" s="1" t="s">
-        <v>1292</v>
       </c>
       <c r="AY41">
         <f>LEN(AW41)</f>
@@ -11371,7 +11371,7 @@
         <v>1037</v>
       </c>
       <c r="AW49" s="1" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="AX49" s="1" t="s">
         <v>199</v>
@@ -11508,7 +11508,7 @@
         <v>940</v>
       </c>
       <c r="AU50" s="1" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="AV50" s="1" t="s">
         <v>1052</v>
@@ -11653,7 +11653,7 @@
         <v>1045</v>
       </c>
       <c r="AW51" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="AX51" s="1" t="s">
         <v>925</v>
@@ -14227,7 +14227,7 @@
         <v>264</v>
       </c>
       <c r="AQ70" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="AS70" s="1" t="s">
         <v>946</v>
@@ -14236,16 +14236,16 @@
         <v>935</v>
       </c>
       <c r="AU70" s="1" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="AV70" s="1" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="AW70" s="1" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="AX70" s="1" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="AY70">
         <f t="shared" si="1"/>
@@ -15179,7 +15179,7 @@
         <v>848</v>
       </c>
       <c r="AU77" s="1" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="AV77" s="1" t="s">
         <v>1097</v>
@@ -16939,7 +16939,7 @@
         <v>952</v>
       </c>
       <c r="AU90" s="1" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="AV90" s="1" t="s">
         <v>1099</v>
@@ -16963,7 +16963,7 @@
         <v>848</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>848</v>
@@ -17072,7 +17072,7 @@
         <v>848</v>
       </c>
       <c r="AU91" s="1" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="AV91" s="1" t="s">
         <v>1037</v>
@@ -20838,7 +20838,7 @@
         <v>848</v>
       </c>
       <c r="AN119" s="1" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="AP119" s="1" t="s">
         <v>249</v>
@@ -20850,16 +20850,16 @@
         <v>956</v>
       </c>
       <c r="AU119" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AV119" s="1" t="s">
         <v>1297</v>
       </c>
-      <c r="AV119" s="1" t="s">
-        <v>1299</v>
-      </c>
       <c r="AW119" s="1" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="AX119" s="1" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="AY119">
         <f t="shared" si="1"/>
@@ -21179,13 +21179,13 @@
         <v>25</v>
       </c>
       <c r="N122" s="3" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="O122" s="3" t="s">
         <v>848</v>
       </c>
       <c r="P122" s="1" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="Q122" s="1" t="s">
         <v>848</v>
@@ -23135,7 +23135,7 @@
         <v>848</v>
       </c>
       <c r="AU136" s="1" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="AV136" s="1" t="s">
         <v>1037</v>
@@ -23537,16 +23537,16 @@
         <v>848</v>
       </c>
       <c r="AU139" s="1" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="AV139" s="1" t="s">
         <v>1037</v>
       </c>
       <c r="AW139" s="1" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="AX139" s="1" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="AY139">
         <f t="shared" si="2"/>
@@ -23934,7 +23934,7 @@
         <v>848</v>
       </c>
       <c r="AU142" s="1" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="AV142" s="1" t="s">
         <v>1037</v>
@@ -24224,7 +24224,7 @@
         <v>500</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>501</v>
@@ -24357,7 +24357,7 @@
         <v>500</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>501</v>
@@ -24472,7 +24472,7 @@
         <v>1037</v>
       </c>
       <c r="AW146" s="1" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="AX146" s="1" t="s">
         <v>511</v>
@@ -24490,7 +24490,7 @@
         <v>500</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>501</v>
@@ -24732,7 +24732,7 @@
         <v>848</v>
       </c>
       <c r="AU148" s="1" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="AV148" s="1" t="s">
         <v>1037</v>
@@ -24756,7 +24756,7 @@
         <v>848</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>848</v>
@@ -24862,13 +24862,13 @@
         <v>848</v>
       </c>
       <c r="AU149" s="1" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="AV149" s="1" t="s">
         <v>1037</v>
       </c>
       <c r="AW149" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="AX149" s="1" t="s">
         <v>517</v>
@@ -33068,7 +33068,7 @@
         <v>848</v>
       </c>
       <c r="AJ210" s="1" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="AK210" s="1" t="s">
         <v>690</v>
@@ -33080,32 +33080,32 @@
         <v>848</v>
       </c>
       <c r="AN210" s="1" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="AO210" s="1" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="AP210" s="1" t="s">
         <v>690</v>
       </c>
       <c r="AQ210" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="AU210" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="AV210" s="1" t="s">
         <v>1240</v>
       </c>
-      <c r="AU210" s="1" t="s">
-        <v>1237</v>
-      </c>
-      <c r="AV210" s="1" t="s">
-        <v>1242</v>
-      </c>
       <c r="AW210" s="1" t="s">
-        <v>1238</v>
+        <v>1316</v>
       </c>
       <c r="AX210" s="1" t="s">
-        <v>1238</v>
+        <v>1316</v>
       </c>
       <c r="AY210">
         <f t="shared" si="3"/>
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="211" spans="1:51" x14ac:dyDescent="0.25">
@@ -33660,7 +33660,7 @@
         <v>720</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>721</v>
@@ -33699,7 +33699,7 @@
         <v>848</v>
       </c>
       <c r="P215" s="1" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="Q215" s="3" t="s">
         <v>848</v>
@@ -33793,7 +33793,7 @@
         <v>720</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>721</v>
@@ -33856,7 +33856,7 @@
         <v>848</v>
       </c>
       <c r="X216" s="1" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="Y216" s="1" t="s">
         <v>848</v>
@@ -34107,7 +34107,7 @@
         <v>848</v>
       </c>
       <c r="S218" s="3" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="T218" s="1" t="s">
         <v>866</v>
@@ -34319,19 +34319,19 @@
         <v>690</v>
       </c>
       <c r="AQ219" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="AU219" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="AV219" s="1" t="s">
         <v>1245</v>
       </c>
-      <c r="AU219" s="1" t="s">
-        <v>1249</v>
-      </c>
-      <c r="AV219" s="1" t="s">
-        <v>1247</v>
-      </c>
       <c r="AW219" s="1" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="AX219" s="1" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="AY219">
         <f t="shared" si="3"/>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC07B7EC-5002-46C6-B785-73BB01E873FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26E3405-F138-4086-8B7C-A582FB76BC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9639" uniqueCount="1319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9640" uniqueCount="1320">
   <si>
     <t>群組ID</t>
   </si>
@@ -4232,27 +4232,30 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>面臨死亡時將範圍{m}米以內的敵人擊退並擊暈{stunSec}秒，同時獲得{sec}秒的無敵護盾，此招有{cd}秒冷卻時間；本招發動時不算死亡，戰鬥繼續</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>st-shield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>致命傷免死時於玩家位置播放控制範圍震波；護盾特效貼身持續至無敵結束，不播放復甦光束。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"sec":2.5,"secPer":0.25,"cd":60,"cdPer":-2,"stunSec":3,"pushM":5,"pushSec":0.25}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>{"windPct":75,"windPctPer":7.5,"earthPct":50,"earthPctPer":5,"healPct":2,"healPctPer":0.2}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>風刃具備風系與地系雙屬性；屬性傷害加成為角色風系傷害提升 ×{windPct}%＋地系傷害提升 ×{earthPct}%；風刃擊殺敵人時回復最大生命 {healPct}% 的生命值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pillar-indomitable-white</t>
+  </si>
+  <si>
+    <t>st-indomitable-gold</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"sec":2.5,"secPer":0.25,"cd":60,"cdPer":-2,"stunSec":3,"pushM":30,"pushSec":0.25,"lightSec":2}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命傷免死時播放控制範圍震波；觸發命中特效為自上而下的白光，持續時間讀lightSec；觸發地板特效為貼身金色護罩，持續至無敵結束。兩者保持作者尺寸並跟隨角色。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>面臨死亡時將範圍{m}米以內的敵人擊退{pushM}米並擊暈{stunSec}秒，同時獲得{sec}秒的無敵護盾，此招有{cd}秒冷卻時間；本招發動時不算死亡，戰鬥繼續</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -14236,8 +14239,11 @@
       <c r="AN70" s="1" t="s">
         <v>264</v>
       </c>
+      <c r="AP70" s="1" t="s">
+        <v>1315</v>
+      </c>
       <c r="AQ70" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="AS70" s="1" t="s">
         <v>945</v>
@@ -14246,20 +14252,20 @@
         <v>934</v>
       </c>
       <c r="AU70" s="1" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="AV70" s="1" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="AW70" s="1" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="AX70" s="1" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="AY70">
         <f t="shared" si="1"/>
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="1:51" x14ac:dyDescent="0.25">
@@ -33102,16 +33108,16 @@
         <v>1234</v>
       </c>
       <c r="AU210" s="1" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="AV210" s="1" t="s">
         <v>1236</v>
       </c>
       <c r="AW210" s="1" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="AX210" s="1" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="AY210">
         <f t="shared" si="3"/>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26E3405-F138-4086-8B7C-A582FB76BC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAF8132-9C10-48CD-A833-316A36C2698E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -36008,7 +36008,7 @@
   <autoFilter ref="A1:AX231" xr:uid="{ACC8F76D-B553-4CF8-BE7D-F03409684AEE}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="施法消耗" error="請輸入大於或等於 0 的數字，或留白。" sqref="M2:M231" xr:uid="{67E86C72-A2EA-443A-8CEE-9BB96F4F1AA5}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="施法消耗" error="請輸入大於或等於 0 的數字，或留白。" sqref="M2:M231" xr:uid="{159C0F28-1393-4930-8F0F-F949865663F7}">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD356F2-080F-419C-8644-D6ECC8A16E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5068C542-AD32-4508-A195-3526A54486A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -6650,11 +6650,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"pool":"random","arch":"sparks","kind":"passive","color":"#8ad8ff","n":[2,4],"speed":8,"life":3.5,"r":1.2,"dmg":0.45,"gap":0.35,"cap":36}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>每次被你擊中，就向四面八方隨機射出 2~4 顆緩慢飛行的橘黃色閃電絲（不規則的鋸齒電光、不停閃爍抖動，不是圓球）；貼臉近戰很容易吃到大量傷害。</t>
+    <t>{"pool":"random","arch":"sparks","kind":"passive","color":"#8ad8ff","n":[2,4],"speed":8,"life":5,"r":1.2,"dmg":0.45,"gap":0.35,"cap":36}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次被你擊中，就向四面八方隨機射出 2~4 條緩慢飛行的藍白色閃電絲（向外最遠 40 米）（不規則的鋸齒電光、不停閃爍抖動，不是圓球）；貼臉近戰很容易吃到大量傷害。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBBD1C6-B397-4A6E-9F6C-DCFC03F3B3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463D35D6-5524-4C94-9462-09B72775ED6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -6880,15 +6880,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"pool":"random","arch":"avenger","kind":"passive","color":"#ff2a2a","needs":"group","size":0.2,"atk":0.2,"aspd":0.2,"run":0.2,"maxStacks":5}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>每有一名同伴陣亡，存活的牠體積增大 20%，攻擊力、攻擊速度與跑速各 +20%（可疊加，最多疊 5 層），並散發血紅色狂暴氣息。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>用途：一般階與超神進化各選項的門檻；格式「轉生次數|等級」或「轉生次數|等級|封魔塔層級」，第三段留白／省略＝無塔層限制；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"pool":"random","arch":"avenger","kind":"passive","color":"#ff2a2a","needs":"group","size":0.2,"atk":0.2,"aspd":0.2,"run":0.2,"sizeMax":2,"bossSize":0.1,"bossSizeMax":1.5}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每有一名同伴陣亡，存活的牠體積增大 20%（最多長到 2 倍；BOSS 每次 10%、最多 1.5 倍），攻擊力、攻擊速度與跑速各 +20%（可疊加，體積長到上限就不再疊），並散發血紅色狂暴氣息。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -39466,10 +39466,10 @@
         <v>331</v>
       </c>
       <c r="AV245" s="1" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="AW245" s="1" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="AY245" s="1" t="s">
         <v>331</v>
@@ -42117,7 +42117,7 @@
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9621CF-BC0C-45DA-A7F9-089085D4B8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{956FD08C-E203-48C1-9EEE-9254697905DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -6888,11 +6888,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"pool":"random","arch":"cross","kind":"active","color":"#7ee02a","repo":1,"throwRange":12,"dur":6,"balls":7,"ballR":1.8,"dmg":0.4,"tick":0.25,"warn":0.9,"dot":{"id":"poison","name":"中毒","pct":25,"dur":3},"len":36,"speed":12,"hubR":2.8}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>地面先生出一個綠色毒圈（半徑 2.8 米），隨後從中心向上下左右四個方向「長出」一排排毒水球（每秒 12 米、最長 36 米），持續 6 秒；碰到毒球或站在毒圈裡會受到高額毒素傷害。</t>
+    <t>{"pool":"random","arch":"cross","kind":"active","color":"#7ee02a","repo":1,"throwRange":12,"dur":6,"balls":7,"ballR":1.8,"dmg":0.4,"tick":0.25,"warn":0.9,"dot":{"id":"poison","name":"中毒","pct":25,"dur":3},"len":36,"speed":12,"hubR":4}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地面先生出一個綠色毒圈（半徑 4 米），隨後從中心向上下左右四個方向「長出」一排排毒水球（每秒 12 米、最長 36 米），持續 6 秒；碰到毒球或站在毒圈裡會受到高額毒素傷害。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F38F0BD-F159-4389-B9F7-7276412472B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97A2271-A422-48AF-BA4E-7F8CE0CE27A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -6879,10 +6879,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>在你周圍從地面升起 2~3 面整塊岩壁（平行 2 面或 U 型 3 面，每面長 18 米、厚 6 米，由三塊約 6×6 米的岩塊組成），持續 7 秒：你和敵人都無法隔著牆壁近戰攻擊（遠程不受影響），常把你關在危險的地面技能裡。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>en-stone-wall-0</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -6898,6 +6894,10 @@
   </si>
   <si>
     <t>我方狀態／敵方狀態（敵人列也能填）：我方狀態＝施放者自己身上的狀態（例：護盾→eInvuln）；敵方狀態＝玩家身上的狀態（例：衰弱詛咒→eCurse）。格式同玩家技能（狀態ID，可帶 dur 等參數）。狀態上身、持續、作用的畫面一律填在 Status 表，不填在這裡。</t>
+  </si>
+  <si>
+    <t>在你周圍從地面升起 2~3 面整塊岩壁（平行 2 面或 U 型 3 面，每面長 18 米、厚 6 米，由四塊約 4.5×6 米的岩塊組成），持續 7 秒：你和敵人都無法隔著牆壁近戰攻擊（遠程不受影響），常把你關在危險的地面技能裡。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -7375,31 +7375,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACC8F76D-B553-4CF8-BE7D-F03409684AEE}">
   <dimension ref="A1:AZ283"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="9.25" customWidth="1"/>
-    <col min="9" max="9" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="33" width="8.5" customWidth="1"/>
-    <col min="34" max="34" width="7.625" customWidth="1"/>
-    <col min="35" max="35" width="14.25" customWidth="1"/>
-    <col min="36" max="37" width="7.625" customWidth="1"/>
-    <col min="38" max="38" width="20.5" customWidth="1"/>
-    <col min="39" max="39" width="7.625" customWidth="1"/>
-    <col min="40" max="44" width="7.625" style="1" customWidth="1"/>
-    <col min="45" max="46" width="12.375" style="1" customWidth="1"/>
-    <col min="47" max="47" width="48.625" customWidth="1"/>
-    <col min="48" max="48" width="12.125" customWidth="1"/>
-    <col min="49" max="49" width="48.625" customWidth="1"/>
-    <col min="50" max="50" width="39.625" customWidth="1"/>
-    <col min="51" max="51" width="14.625" customWidth="1"/>
+    <col min="6" max="8" width="9.21875" customWidth="1"/>
+    <col min="9" max="9" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="33" width="8.44140625" customWidth="1"/>
+    <col min="34" max="34" width="7.6640625" customWidth="1"/>
+    <col min="35" max="35" width="14.21875" customWidth="1"/>
+    <col min="36" max="37" width="7.6640625" customWidth="1"/>
+    <col min="38" max="38" width="20.44140625" customWidth="1"/>
+    <col min="39" max="39" width="7.6640625" customWidth="1"/>
+    <col min="40" max="44" width="7.6640625" style="1" customWidth="1"/>
+    <col min="45" max="46" width="12.33203125" style="1" customWidth="1"/>
+    <col min="47" max="47" width="48.6640625" customWidth="1"/>
+    <col min="48" max="48" width="12.109375" customWidth="1"/>
+    <col min="49" max="49" width="48.6640625" customWidth="1"/>
+    <col min="50" max="50" width="39.6640625" customWidth="1"/>
+    <col min="51" max="51" width="14.6640625" customWidth="1"/>
     <col min="52" max="52" width="9" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" s="9" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" s="9" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="AZ1" s="13"/>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
@@ -7689,7 +7689,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -7823,7 +7823,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -7957,7 +7957,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
@@ -8359,7 +8359,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -8627,7 +8627,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -8901,7 +8901,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
@@ -9035,7 +9035,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
@@ -9303,7 +9303,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
@@ -9437,7 +9437,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
@@ -9571,7 +9571,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
@@ -9705,7 +9705,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
@@ -9839,7 +9839,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -9979,7 +9979,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
@@ -10116,7 +10116,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
@@ -10250,7 +10250,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>16</v>
       </c>
@@ -10384,7 +10384,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
@@ -10518,7 +10518,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>16</v>
       </c>
@@ -10652,7 +10652,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>16</v>
       </c>
@@ -10786,7 +10786,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>16</v>
       </c>
@@ -10919,7 +10919,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>16</v>
       </c>
@@ -11051,7 +11051,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>16</v>
       </c>
@@ -11183,7 +11183,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="29" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>16</v>
       </c>
@@ -11313,7 +11313,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="30" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>16</v>
       </c>
@@ -11458,7 +11458,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="31" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>16</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="32" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>40</v>
       </c>
@@ -11726,7 +11726,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="33" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>40</v>
       </c>
@@ -11860,7 +11860,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="34" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>40</v>
       </c>
@@ -11994,7 +11994,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>40</v>
       </c>
@@ -12128,7 +12128,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="36" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>40</v>
       </c>
@@ -12268,7 +12268,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="37" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>40</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
@@ -12536,7 +12536,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="39" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>40</v>
       </c>
@@ -12676,7 +12676,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="40" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>40</v>
       </c>
@@ -12816,7 +12816,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="41" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>40</v>
       </c>
@@ -12950,7 +12950,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="42" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>52</v>
       </c>
@@ -13085,7 +13085,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="43" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>52</v>
       </c>
@@ -13215,7 +13215,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="44" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>52</v>
       </c>
@@ -13349,7 +13349,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="45" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>52</v>
       </c>
@@ -13484,7 +13484,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="46" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>361</v>
       </c>
@@ -13627,7 +13627,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="47" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>52</v>
       </c>
@@ -13763,7 +13763,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="48" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>52</v>
       </c>
@@ -13898,7 +13898,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="49" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>52</v>
       </c>
@@ -14039,7 +14039,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="50" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>52</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="51" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>52</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="52" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>65</v>
       </c>
@@ -14452,7 +14452,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="53" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>65</v>
       </c>
@@ -14584,7 +14584,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="54" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>65</v>
       </c>
@@ -14716,7 +14716,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="55" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>65</v>
       </c>
@@ -14856,7 +14856,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="56" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>65</v>
       </c>
@@ -14996,7 +14996,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="57" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>65</v>
       </c>
@@ -15130,7 +15130,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="58" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>65</v>
       </c>
@@ -15268,7 +15268,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="59" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>65</v>
       </c>
@@ -15402,7 +15402,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="60" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>65</v>
       </c>
@@ -15539,7 +15539,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="61" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>65</v>
       </c>
@@ -15673,7 +15673,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="62" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>73</v>
       </c>
@@ -15807,7 +15807,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="63" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>73</v>
       </c>
@@ -15941,7 +15941,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="64" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>73</v>
       </c>
@@ -16075,7 +16075,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="65" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>73</v>
       </c>
@@ -16209,7 +16209,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="66" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>73</v>
       </c>
@@ -16346,7 +16346,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="67" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>73</v>
       </c>
@@ -16480,7 +16480,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="68" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>73</v>
       </c>
@@ -16614,7 +16614,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="69" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>73</v>
       </c>
@@ -16757,7 +16757,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="70" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>73</v>
       </c>
@@ -16910,7 +16910,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="71" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>73</v>
       </c>
@@ -17044,7 +17044,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="72" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>85</v>
       </c>
@@ -17190,7 +17190,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="73" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>85</v>
       </c>
@@ -17324,7 +17324,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="74" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>85</v>
       </c>
@@ -17456,7 +17456,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="75" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>85</v>
       </c>
@@ -17588,7 +17588,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="76" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>85</v>
       </c>
@@ -17720,7 +17720,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="77" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>85</v>
       </c>
@@ -17852,7 +17852,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="78" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>85</v>
       </c>
@@ -17991,7 +17991,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="79" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>85</v>
       </c>
@@ -18129,7 +18129,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="80" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>85</v>
       </c>
@@ -18273,7 +18273,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="81" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>85</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="82" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>96</v>
       </c>
@@ -18549,7 +18549,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="83" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>96</v>
       </c>
@@ -18684,7 +18684,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="84" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>96</v>
       </c>
@@ -18816,7 +18816,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="85" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>96</v>
       </c>
@@ -18948,7 +18948,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="86" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>96</v>
       </c>
@@ -19080,7 +19080,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="87" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>96</v>
       </c>
@@ -19218,7 +19218,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="88" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>96</v>
       </c>
@@ -19350,7 +19350,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="89" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>96</v>
       </c>
@@ -19482,7 +19482,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="90" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>96</v>
       </c>
@@ -19626,7 +19626,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="91" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>96</v>
       </c>
@@ -19758,7 +19758,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="92" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>113</v>
       </c>
@@ -19893,7 +19893,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="93" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>113</v>
       </c>
@@ -20025,7 +20025,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="94" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>113</v>
       </c>
@@ -20157,7 +20157,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="95" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>113</v>
       </c>
@@ -20292,7 +20292,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="96" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>113</v>
       </c>
@@ -20436,7 +20436,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="97" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>113</v>
       </c>
@@ -20568,7 +20568,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="98" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>113</v>
       </c>
@@ -20703,7 +20703,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="99" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>113</v>
       </c>
@@ -20844,7 +20844,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="100" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>113</v>
       </c>
@@ -20982,7 +20982,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="101" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>113</v>
       </c>
@@ -21120,7 +21120,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="102" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>126</v>
       </c>
@@ -21258,7 +21258,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="103" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>126</v>
       </c>
@@ -21390,7 +21390,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="104" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>126</v>
       </c>
@@ -21528,7 +21528,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="105" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>126</v>
       </c>
@@ -21660,7 +21660,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="106" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>126</v>
       </c>
@@ -21792,7 +21792,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="107" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>126</v>
       </c>
@@ -21924,7 +21924,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="108" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>126</v>
       </c>
@@ -22056,7 +22056,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="109" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>126</v>
       </c>
@@ -22194,7 +22194,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="110" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>126</v>
       </c>
@@ -22332,7 +22332,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="111" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>126</v>
       </c>
@@ -22476,7 +22476,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="112" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>139</v>
       </c>
@@ -22614,7 +22614,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="113" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>139</v>
       </c>
@@ -22746,7 +22746,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="114" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>139</v>
       </c>
@@ -22878,7 +22878,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="115" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>139</v>
       </c>
@@ -23010,7 +23010,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="116" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>139</v>
       </c>
@@ -23142,7 +23142,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="117" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>139</v>
       </c>
@@ -23280,7 +23280,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="118" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>139</v>
       </c>
@@ -23412,7 +23412,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="119" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>139</v>
       </c>
@@ -23562,7 +23562,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="120" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>139</v>
       </c>
@@ -23694,7 +23694,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="121" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>139</v>
       </c>
@@ -23832,7 +23832,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="122" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>152</v>
       </c>
@@ -23967,7 +23967,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="123" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>152</v>
       </c>
@@ -24099,7 +24099,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="124" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>152</v>
       </c>
@@ -24234,7 +24234,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="125" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>152</v>
       </c>
@@ -24366,7 +24366,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="126" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>152</v>
       </c>
@@ -24498,7 +24498,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="127" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>152</v>
       </c>
@@ -24630,7 +24630,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="128" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>152</v>
       </c>
@@ -24765,7 +24765,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="129" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>152</v>
       </c>
@@ -24900,7 +24900,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="130" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>152</v>
       </c>
@@ -25041,7 +25041,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="131" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>152</v>
       </c>
@@ -25173,7 +25173,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="132" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>163</v>
       </c>
@@ -25305,7 +25305,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="133" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>163</v>
       </c>
@@ -25437,7 +25437,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="134" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>163</v>
       </c>
@@ -25569,7 +25569,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="135" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>163</v>
       </c>
@@ -25701,7 +25701,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="136" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>163</v>
       </c>
@@ -25833,7 +25833,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="137" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>163</v>
       </c>
@@ -25965,7 +25965,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="138" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>163</v>
       </c>
@@ -26103,7 +26103,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="139" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>163</v>
       </c>
@@ -26235,7 +26235,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="140" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>163</v>
       </c>
@@ -26367,7 +26367,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="141" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>163</v>
       </c>
@@ -26499,7 +26499,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="142" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>172</v>
       </c>
@@ -26629,7 +26629,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="143" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>172</v>
       </c>
@@ -26761,7 +26761,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="144" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>172</v>
       </c>
@@ -26893,7 +26893,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="145" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>172</v>
       </c>
@@ -27025,7 +27025,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="146" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>172</v>
       </c>
@@ -27157,7 +27157,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="147" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>172</v>
       </c>
@@ -27289,7 +27289,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="148" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>172</v>
       </c>
@@ -27421,7 +27421,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="149" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>172</v>
       </c>
@@ -27550,7 +27550,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="150" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>172</v>
       </c>
@@ -27697,7 +27697,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="151" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>172</v>
       </c>
@@ -27835,7 +27835,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="152" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>185</v>
       </c>
@@ -27967,7 +27967,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="153" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>185</v>
       </c>
@@ -28099,7 +28099,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="154" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>185</v>
       </c>
@@ -28231,7 +28231,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="155" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>185</v>
       </c>
@@ -28363,7 +28363,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="156" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>185</v>
       </c>
@@ -28498,7 +28498,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="157" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>185</v>
       </c>
@@ -28630,7 +28630,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="158" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>185</v>
       </c>
@@ -28762,7 +28762,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="159" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>185</v>
       </c>
@@ -28894,7 +28894,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="160" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>185</v>
       </c>
@@ -29032,7 +29032,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="161" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>185</v>
       </c>
@@ -29164,7 +29164,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="162" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>197</v>
       </c>
@@ -29297,7 +29297,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="163" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>197</v>
       </c>
@@ -29429,7 +29429,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="164" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>197</v>
       </c>
@@ -29561,7 +29561,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="165" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>197</v>
       </c>
@@ -29697,7 +29697,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="166" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>197</v>
       </c>
@@ -29829,7 +29829,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="167" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>197</v>
       </c>
@@ -29962,7 +29962,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="168" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>197</v>
       </c>
@@ -30104,7 +30104,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="169" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>197</v>
       </c>
@@ -30239,7 +30239,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="170" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>197</v>
       </c>
@@ -30380,7 +30380,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="171" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>197</v>
       </c>
@@ -30512,7 +30512,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="172" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>210</v>
       </c>
@@ -30644,7 +30644,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="173" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>210</v>
       </c>
@@ -30779,7 +30779,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="174" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>210</v>
       </c>
@@ -30911,7 +30911,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="175" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>210</v>
       </c>
@@ -31043,7 +31043,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="176" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>210</v>
       </c>
@@ -31175,7 +31175,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="177" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>210</v>
       </c>
@@ -31307,7 +31307,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="178" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>210</v>
       </c>
@@ -31443,7 +31443,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="179" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>210</v>
       </c>
@@ -31575,7 +31575,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="180" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>210</v>
       </c>
@@ -31707,7 +31707,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="181" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>210</v>
       </c>
@@ -31848,7 +31848,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="182" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>223</v>
       </c>
@@ -31978,7 +31978,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="183" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>223</v>
       </c>
@@ -32113,7 +32113,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="184" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>223</v>
       </c>
@@ -32248,7 +32248,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="185" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>223</v>
       </c>
@@ -32380,7 +32380,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="186" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>223</v>
       </c>
@@ -32521,7 +32521,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="187" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>223</v>
       </c>
@@ -32653,7 +32653,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="188" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>223</v>
       </c>
@@ -32791,7 +32791,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="189" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>223</v>
       </c>
@@ -32929,7 +32929,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="190" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>223</v>
       </c>
@@ -33070,7 +33070,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="191" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>223</v>
       </c>
@@ -33214,7 +33214,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="192" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>232</v>
       </c>
@@ -33349,7 +33349,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="193" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>232</v>
       </c>
@@ -33481,7 +33481,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="194" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>232</v>
       </c>
@@ -33619,7 +33619,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="195" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>232</v>
       </c>
@@ -33751,7 +33751,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="196" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>232</v>
       </c>
@@ -33883,7 +33883,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="197" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>232</v>
       </c>
@@ -34015,7 +34015,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="198" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>232</v>
       </c>
@@ -34153,7 +34153,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="199" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>232</v>
       </c>
@@ -34285,7 +34285,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="200" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>232</v>
       </c>
@@ -34421,7 +34421,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="201" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>232</v>
       </c>
@@ -34559,7 +34559,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="202" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>245</v>
       </c>
@@ -34691,7 +34691,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="203" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>245</v>
       </c>
@@ -34823,7 +34823,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="204" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>245</v>
       </c>
@@ -34955,7 +34955,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="205" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>245</v>
       </c>
@@ -35096,7 +35096,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="206" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>245</v>
       </c>
@@ -35237,7 +35237,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="207" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>245</v>
       </c>
@@ -35384,7 +35384,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="208" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>245</v>
       </c>
@@ -35516,7 +35516,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="209" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>245</v>
       </c>
@@ -35657,7 +35657,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="210" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>245</v>
       </c>
@@ -35804,7 +35804,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="211" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>245</v>
       </c>
@@ -35945,7 +35945,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="212" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>259</v>
       </c>
@@ -36077,7 +36077,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="213" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>259</v>
       </c>
@@ -36215,7 +36215,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="214" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>259</v>
       </c>
@@ -36350,7 +36350,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="215" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>259</v>
       </c>
@@ -36482,7 +36482,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="216" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>259</v>
       </c>
@@ -36614,7 +36614,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="217" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>259</v>
       </c>
@@ -36746,7 +36746,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="218" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>259</v>
       </c>
@@ -36899,7 +36899,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="219" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>259</v>
       </c>
@@ -37040,7 +37040,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="220" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>259</v>
       </c>
@@ -37172,7 +37172,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="221" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>259</v>
       </c>
@@ -37304,7 +37304,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="222" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>274</v>
       </c>
@@ -37442,7 +37442,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="223" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>274</v>
       </c>
@@ -37583,7 +37583,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="224" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>274</v>
       </c>
@@ -37724,7 +37724,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="225" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>274</v>
       </c>
@@ -37865,7 +37865,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="226" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>274</v>
       </c>
@@ -38006,7 +38006,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="227" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>274</v>
       </c>
@@ -38138,7 +38138,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="228" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>274</v>
       </c>
@@ -38276,7 +38276,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="229" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>274</v>
       </c>
@@ -38408,7 +38408,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="230" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>274</v>
       </c>
@@ -38555,7 +38555,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="231" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>274</v>
       </c>
@@ -38702,7 +38702,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="232" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>671</v>
       </c>
@@ -38764,7 +38764,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="233" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>676</v>
       </c>
@@ -38832,7 +38832,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="234" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>682</v>
       </c>
@@ -38891,7 +38891,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="235" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>687</v>
       </c>
@@ -38953,7 +38953,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="236" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>693</v>
       </c>
@@ -39003,7 +39003,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="237" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>696</v>
       </c>
@@ -39059,7 +39059,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="238" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>699</v>
       </c>
@@ -39118,7 +39118,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="239" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>705</v>
       </c>
@@ -39180,7 +39180,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="240" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>713</v>
       </c>
@@ -39239,7 +39239,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="241" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>718</v>
       </c>
@@ -39283,22 +39283,22 @@
         <v>1722</v>
       </c>
       <c r="AN241" s="1" t="s">
+        <v>1944</v>
+      </c>
+      <c r="AU241" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="AV241" s="1" t="s">
         <v>1945</v>
       </c>
-      <c r="AU241" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="AV241" s="1" t="s">
-        <v>1946</v>
-      </c>
       <c r="AW241" s="1" t="s">
-        <v>1944</v>
+        <v>1949</v>
       </c>
       <c r="AY241" s="1" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="242" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>723</v>
       </c>
@@ -39357,7 +39357,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="243" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>728</v>
       </c>
@@ -39410,7 +39410,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="244" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>734</v>
       </c>
@@ -39442,7 +39442,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="245" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>738</v>
       </c>
@@ -39483,7 +39483,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="246" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>740</v>
       </c>
@@ -39530,7 +39530,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="247" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>746</v>
       </c>
@@ -39586,7 +39586,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="248" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>751</v>
       </c>
@@ -39651,7 +39651,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="249" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>758</v>
       </c>
@@ -39710,7 +39710,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="250" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>765</v>
       </c>
@@ -39766,7 +39766,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="251" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>772</v>
       </c>
@@ -39822,7 +39822,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="252" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>778</v>
       </c>
@@ -39884,7 +39884,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="253" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>786</v>
       </c>
@@ -39940,7 +39940,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="254" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>792</v>
       </c>
@@ -39996,7 +39996,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="255" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>797</v>
       </c>
@@ -40049,7 +40049,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="256" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>802</v>
       </c>
@@ -40102,7 +40102,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="257" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>807</v>
       </c>
@@ -40152,7 +40152,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="258" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>813</v>
       </c>
@@ -40202,7 +40202,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="259" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>818</v>
       </c>
@@ -40255,7 +40255,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="260" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>823</v>
       </c>
@@ -40308,7 +40308,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="261" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>829</v>
       </c>
@@ -40361,7 +40361,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="262" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>834</v>
       </c>
@@ -40414,7 +40414,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="263" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>838</v>
       </c>
@@ -40467,7 +40467,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="264" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>842</v>
       </c>
@@ -40523,7 +40523,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="265" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>848</v>
       </c>
@@ -40576,7 +40576,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="266" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>853</v>
       </c>
@@ -40629,7 +40629,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="267" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>858</v>
       </c>
@@ -40682,7 +40682,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="268" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>862</v>
       </c>
@@ -40741,7 +40741,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="269" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>866</v>
       </c>
@@ -40797,7 +40797,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="270" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>871</v>
       </c>
@@ -40850,7 +40850,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="271" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>876</v>
       </c>
@@ -40900,7 +40900,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="272" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>881</v>
       </c>
@@ -40953,7 +40953,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="273" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>885</v>
       </c>
@@ -41003,7 +41003,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="274" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>889</v>
       </c>
@@ -41053,7 +41053,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="275" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>894</v>
       </c>
@@ -41100,7 +41100,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="276" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>896</v>
       </c>
@@ -41138,7 +41138,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="277" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>900</v>
       </c>
@@ -41185,7 +41185,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="278" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>903</v>
       </c>
@@ -41229,7 +41229,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="279" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>908</v>
       </c>
@@ -41273,7 +41273,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="280" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>913</v>
       </c>
@@ -41311,7 +41311,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="281" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>916</v>
       </c>
@@ -41364,7 +41364,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="282" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>919</v>
       </c>
@@ -41417,7 +41417,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="283" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>923</v>
       </c>
@@ -41478,797 +41478,797 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A83FB8B-F526-4731-A8B0-CF3B6BDD1233}">
   <dimension ref="A1:A158"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="125.625" customWidth="1"/>
+    <col min="1" max="1" width="125.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="63" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>931</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A129" s="5" t="s">
         <v>1947</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="5" t="s">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="145" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="149" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="150" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="151" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="152" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="153" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="154" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="155" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="156" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A156" s="5" t="s">
         <v>940</v>
       </c>
     </row>
-    <row r="157" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
         <v>1835</v>
       </c>
@@ -42282,13 +42282,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1222779-D1F7-486F-9B13-D492D72521FD}">
   <dimension ref="A1:N231"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="19.875" customWidth="1"/>
+    <col min="7" max="7" width="19.88671875" customWidth="1"/>
     <col min="14" max="14" width="9" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="25.2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -42320,7 +42320,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
@@ -42354,7 +42354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -42388,7 +42388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -42422,7 +42422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
@@ -42456,7 +42456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
@@ -42490,7 +42490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
@@ -42524,7 +42524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -42558,7 +42558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -42595,7 +42595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
@@ -42632,7 +42632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -42669,7 +42669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
@@ -42703,7 +42703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -42737,7 +42737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
@@ -42771,7 +42771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
@@ -42805,7 +42805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
@@ -42839,7 +42839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
@@ -42873,7 +42873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
@@ -42907,7 +42907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -42944,7 +42944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
@@ -42981,7 +42981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
@@ -43018,7 +43018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>16</v>
       </c>
@@ -43052,7 +43052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
@@ -43086,7 +43086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>16</v>
       </c>
@@ -43120,7 +43120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>16</v>
       </c>
@@ -43154,7 +43154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>16</v>
       </c>
@@ -43188,7 +43188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>16</v>
       </c>
@@ -43222,7 +43222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>16</v>
       </c>
@@ -43256,7 +43256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>16</v>
       </c>
@@ -43294,7 +43294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>16</v>
       </c>
@@ -43332,7 +43332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>16</v>
       </c>
@@ -43369,7 +43369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>40</v>
       </c>
@@ -43403,7 +43403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>40</v>
       </c>
@@ -43437,7 +43437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>40</v>
       </c>
@@ -43471,7 +43471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>40</v>
       </c>
@@ -43505,7 +43505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>40</v>
       </c>
@@ -43539,7 +43539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>40</v>
       </c>
@@ -43573,7 +43573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
@@ -43607,7 +43607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>40</v>
       </c>
@@ -43645,7 +43645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>40</v>
       </c>
@@ -43683,7 +43683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>40</v>
       </c>
@@ -43721,7 +43721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>52</v>
       </c>
@@ -43755,7 +43755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>52</v>
       </c>
@@ -43789,7 +43789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>52</v>
       </c>
@@ -43823,7 +43823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>52</v>
       </c>
@@ -43857,7 +43857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>361</v>
       </c>
@@ -43891,7 +43891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>52</v>
       </c>
@@ -43925,7 +43925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>52</v>
       </c>
@@ -43959,7 +43959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>52</v>
       </c>
@@ -43997,7 +43997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>52</v>
       </c>
@@ -44035,7 +44035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>52</v>
       </c>
@@ -44073,7 +44073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>65</v>
       </c>
@@ -44107,7 +44107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>65</v>
       </c>
@@ -44141,7 +44141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>65</v>
       </c>
@@ -44175,7 +44175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>65</v>
       </c>
@@ -44209,7 +44209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>65</v>
       </c>
@@ -44243,7 +44243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>65</v>
       </c>
@@ -44277,7 +44277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>65</v>
       </c>
@@ -44311,7 +44311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>65</v>
       </c>
@@ -44349,7 +44349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>65</v>
       </c>
@@ -44386,7 +44386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>65</v>
       </c>
@@ -44424,7 +44424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>73</v>
       </c>
@@ -44458,7 +44458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>73</v>
       </c>
@@ -44492,7 +44492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>73</v>
       </c>
@@ -44526,7 +44526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>73</v>
       </c>
@@ -44560,7 +44560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>73</v>
       </c>
@@ -44594,7 +44594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>73</v>
       </c>
@@ -44628,7 +44628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>73</v>
       </c>
@@ -44662,7 +44662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>73</v>
       </c>
@@ -44700,7 +44700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>73</v>
       </c>
@@ -44738,7 +44738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>73</v>
       </c>
@@ -44776,7 +44776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>85</v>
       </c>
@@ -44810,7 +44810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>85</v>
       </c>
@@ -44844,7 +44844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>85</v>
       </c>
@@ -44878,7 +44878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>85</v>
       </c>
@@ -44912,7 +44912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>85</v>
       </c>
@@ -44946,7 +44946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>85</v>
       </c>
@@ -44980,7 +44980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>85</v>
       </c>
@@ -45014,7 +45014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>85</v>
       </c>
@@ -45052,7 +45052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>85</v>
       </c>
@@ -45090,7 +45090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>85</v>
       </c>
@@ -45128,7 +45128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>96</v>
       </c>
@@ -45162,7 +45162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>96</v>
       </c>
@@ -45196,7 +45196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>96</v>
       </c>
@@ -45230,7 +45230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>96</v>
       </c>
@@ -45264,7 +45264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>96</v>
       </c>
@@ -45298,7 +45298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>96</v>
       </c>
@@ -45332,7 +45332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>96</v>
       </c>
@@ -45366,7 +45366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>96</v>
       </c>
@@ -45403,7 +45403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>96</v>
       </c>
@@ -45440,7 +45440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>96</v>
       </c>
@@ -45477,7 +45477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>113</v>
       </c>
@@ -45511,7 +45511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>113</v>
       </c>
@@ -45545,7 +45545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>113</v>
       </c>
@@ -45579,7 +45579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>113</v>
       </c>
@@ -45613,7 +45613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>113</v>
       </c>
@@ -45647,7 +45647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>113</v>
       </c>
@@ -45681,7 +45681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>113</v>
       </c>
@@ -45715,7 +45715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>113</v>
       </c>
@@ -45752,7 +45752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>113</v>
       </c>
@@ -45789,7 +45789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>113</v>
       </c>
@@ -45826,7 +45826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>126</v>
       </c>
@@ -45860,7 +45860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>126</v>
       </c>
@@ -45894,7 +45894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>126</v>
       </c>
@@ -45928,7 +45928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>126</v>
       </c>
@@ -45962,7 +45962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>126</v>
       </c>
@@ -45996,7 +45996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>126</v>
       </c>
@@ -46030,7 +46030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>126</v>
       </c>
@@ -46064,7 +46064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>126</v>
       </c>
@@ -46101,7 +46101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>126</v>
       </c>
@@ -46138,7 +46138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>126</v>
       </c>
@@ -46175,7 +46175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>139</v>
       </c>
@@ -46209,7 +46209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>139</v>
       </c>
@@ -46243,7 +46243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>139</v>
       </c>
@@ -46277,7 +46277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>139</v>
       </c>
@@ -46311,7 +46311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>139</v>
       </c>
@@ -46345,7 +46345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>139</v>
       </c>
@@ -46379,7 +46379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>139</v>
       </c>
@@ -46413,7 +46413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>139</v>
       </c>
@@ -46451,7 +46451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>139</v>
       </c>
@@ -46489,7 +46489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>139</v>
       </c>
@@ -46527,7 +46527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>152</v>
       </c>
@@ -46561,7 +46561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>152</v>
       </c>
@@ -46595,7 +46595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>152</v>
       </c>
@@ -46629,7 +46629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>152</v>
       </c>
@@ -46663,7 +46663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>152</v>
       </c>
@@ -46697,7 +46697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>152</v>
       </c>
@@ -46731,7 +46731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>152</v>
       </c>
@@ -46765,7 +46765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>152</v>
       </c>
@@ -46803,7 +46803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>152</v>
       </c>
@@ -46840,7 +46840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>152</v>
       </c>
@@ -46878,7 +46878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>163</v>
       </c>
@@ -46912,7 +46912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>163</v>
       </c>
@@ -46946,7 +46946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>163</v>
       </c>
@@ -46980,7 +46980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>163</v>
       </c>
@@ -47014,7 +47014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>163</v>
       </c>
@@ -47048,7 +47048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>163</v>
       </c>
@@ -47082,7 +47082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>163</v>
       </c>
@@ -47116,7 +47116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>163</v>
       </c>
@@ -47154,7 +47154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>163</v>
       </c>
@@ -47192,7 +47192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>163</v>
       </c>
@@ -47230,7 +47230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>172</v>
       </c>
@@ -47264,7 +47264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>172</v>
       </c>
@@ -47298,7 +47298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>172</v>
       </c>
@@ -47332,7 +47332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>172</v>
       </c>
@@ -47366,7 +47366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>172</v>
       </c>
@@ -47400,7 +47400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>172</v>
       </c>
@@ -47434,7 +47434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>172</v>
       </c>
@@ -47468,7 +47468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>172</v>
       </c>
@@ -47506,7 +47506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>172</v>
       </c>
@@ -47544,7 +47544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>172</v>
       </c>
@@ -47582,7 +47582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>185</v>
       </c>
@@ -47616,7 +47616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>185</v>
       </c>
@@ -47650,7 +47650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>185</v>
       </c>
@@ -47684,7 +47684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>185</v>
       </c>
@@ -47718,7 +47718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>185</v>
       </c>
@@ -47752,7 +47752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>185</v>
       </c>
@@ -47786,7 +47786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>185</v>
       </c>
@@ -47820,7 +47820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>185</v>
       </c>
@@ -47858,7 +47858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>185</v>
       </c>
@@ -47896,7 +47896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>185</v>
       </c>
@@ -47934,7 +47934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>197</v>
       </c>
@@ -47968,7 +47968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>197</v>
       </c>
@@ -48002,7 +48002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>197</v>
       </c>
@@ -48036,7 +48036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>197</v>
       </c>
@@ -48070,7 +48070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>197</v>
       </c>
@@ -48104,7 +48104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>197</v>
       </c>
@@ -48138,7 +48138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>197</v>
       </c>
@@ -48172,7 +48172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>197</v>
       </c>
@@ -48210,7 +48210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>197</v>
       </c>
@@ -48248,7 +48248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>197</v>
       </c>
@@ -48286,7 +48286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>210</v>
       </c>
@@ -48320,7 +48320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>210</v>
       </c>
@@ -48354,7 +48354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>210</v>
       </c>
@@ -48388,7 +48388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>210</v>
       </c>
@@ -48422,7 +48422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>210</v>
       </c>
@@ -48456,7 +48456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>210</v>
       </c>
@@ -48490,7 +48490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>210</v>
       </c>
@@ -48524,7 +48524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>210</v>
       </c>
@@ -48562,7 +48562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>210</v>
       </c>
@@ -48600,7 +48600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>210</v>
       </c>
@@ -48638,7 +48638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>223</v>
       </c>
@@ -48672,7 +48672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>223</v>
       </c>
@@ -48706,7 +48706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>223</v>
       </c>
@@ -48740,7 +48740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>223</v>
       </c>
@@ -48774,7 +48774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>223</v>
       </c>
@@ -48808,7 +48808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>223</v>
       </c>
@@ -48842,7 +48842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>223</v>
       </c>
@@ -48876,7 +48876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>223</v>
       </c>
@@ -48914,7 +48914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>223</v>
       </c>
@@ -48952,7 +48952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>223</v>
       </c>
@@ -48990,7 +48990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>232</v>
       </c>
@@ -49024,7 +49024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>232</v>
       </c>
@@ -49058,7 +49058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>232</v>
       </c>
@@ -49092,7 +49092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>232</v>
       </c>
@@ -49126,7 +49126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>232</v>
       </c>
@@ -49160,7 +49160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>232</v>
       </c>
@@ -49194,7 +49194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>232</v>
       </c>
@@ -49228,7 +49228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>232</v>
       </c>
@@ -49265,7 +49265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>232</v>
       </c>
@@ -49303,7 +49303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>232</v>
       </c>
@@ -49341,7 +49341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>245</v>
       </c>
@@ -49368,7 +49368,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>245</v>
       </c>
@@ -49395,7 +49395,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>245</v>
       </c>
@@ -49422,7 +49422,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>245</v>
       </c>
@@ -49449,7 +49449,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>245</v>
       </c>
@@ -49476,7 +49476,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>245</v>
       </c>
@@ -49503,7 +49503,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>245</v>
       </c>
@@ -49530,7 +49530,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>245</v>
       </c>
@@ -49561,7 +49561,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>245</v>
       </c>
@@ -49592,7 +49592,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>245</v>
       </c>
@@ -49623,7 +49623,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>259</v>
       </c>
@@ -49650,7 +49650,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>259</v>
       </c>
@@ -49677,7 +49677,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>259</v>
       </c>
@@ -49704,7 +49704,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>259</v>
       </c>
@@ -49731,7 +49731,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>259</v>
       </c>
@@ -49758,7 +49758,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>259</v>
       </c>
@@ -49785,7 +49785,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>259</v>
       </c>
@@ -49812,7 +49812,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>259</v>
       </c>
@@ -49843,7 +49843,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>259</v>
       </c>
@@ -49874,7 +49874,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>259</v>
       </c>
@@ -49904,7 +49904,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>274</v>
       </c>
@@ -49931,7 +49931,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>274</v>
       </c>
@@ -49958,7 +49958,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>274</v>
       </c>
@@ -49985,7 +49985,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>274</v>
       </c>
@@ -50012,7 +50012,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>274</v>
       </c>
@@ -50039,7 +50039,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>274</v>
       </c>
@@ -50066,7 +50066,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>274</v>
       </c>
@@ -50093,7 +50093,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>274</v>
       </c>
@@ -50124,7 +50124,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>274</v>
       </c>
@@ -50155,7 +50155,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>274</v>
       </c>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97A2271-A422-48AF-BA4E-7F8CE0CE27A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF659753-792A-4B68-BE85-DAA4DACB313E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -34242,7 +34242,7 @@
         <v>331</v>
       </c>
       <c r="AE199" s="1" t="s">
-        <v>516</v>
+        <v>1005</v>
       </c>
       <c r="AF199" s="1" t="s">
         <v>331</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF659753-792A-4B68-BE85-DAA4DACB313E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A6ADD4-4EB6-4A09-8BDB-0C97B5F637EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -6883,10 +6883,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"pool":"random","arch":"walls","kind":"active","color":"#a99ac0","life":7,"len":18,"thick":6,"dist":9,"warn":0.8,"n":[2,3],"presets":["en-stone-wall-15","en-stone-wall-30","en-stone-wall-45","en-stone-wall-60","en-stone-wall-75","en-stone-wall-90","en-stone-wall-105","en-stone-wall-120","en-stone-wall-135","en-stone-wall-150","en-stone-wall-165"]}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>解鎖轉生/等級/封魔塔層級</t>
   </si>
   <si>
@@ -6896,7 +6892,11 @@
     <t>我方狀態／敵方狀態（敵人列也能填）：我方狀態＝施放者自己身上的狀態（例：護盾→eInvuln）；敵方狀態＝玩家身上的狀態（例：衰弱詛咒→eCurse）。格式同玩家技能（狀態ID，可帶 dur 等參數）。狀態上身、持續、作用的畫面一律填在 Status 表，不填在這裡。</t>
   </si>
   <si>
-    <t>在你周圍從地面升起 2~3 面整塊岩壁（平行 2 面或 U 型 3 面，每面長 18 米、厚 6 米，由四塊約 4.5×6 米的岩塊組成），持續 7 秒：你和敵人都無法隔著牆壁近戰攻擊（遠程不受影響），常把你關在危險的地面技能裡。</t>
+    <t>{"pool":"random","arch":"walls","kind":"active","color":"#a99ac0","life":7,"len":18,"thick":3.9,"dist":9,"warn":0.8,"n":[2,3],"presets":["en-stone-wall-15","en-stone-wall-30","en-stone-wall-45","en-stone-wall-60","en-stone-wall-75","en-stone-wall-90","en-stone-wall-105","en-stone-wall-120","en-stone-wall-135","en-stone-wall-150","en-stone-wall-165"]}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在你周圍從地面升起 2~3 面整塊岩壁（平行 2 面或 U 型 3 面，每面長 18 米、厚 3.9 米，由四塊約 4.5×3.9 米的不規則岩塊組成），持續 7 秒：你和敵人都無法隔著牆壁近戰攻擊（遠程不受影響），常把你關在危險的地面技能裡。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -7375,31 +7375,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACC8F76D-B553-4CF8-BE7D-F03409684AEE}">
   <dimension ref="A1:AZ283"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="9.21875" customWidth="1"/>
-    <col min="9" max="9" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="33" width="8.44140625" customWidth="1"/>
-    <col min="34" max="34" width="7.6640625" customWidth="1"/>
-    <col min="35" max="35" width="14.21875" customWidth="1"/>
-    <col min="36" max="37" width="7.6640625" customWidth="1"/>
-    <col min="38" max="38" width="20.44140625" customWidth="1"/>
-    <col min="39" max="39" width="7.6640625" customWidth="1"/>
-    <col min="40" max="44" width="7.6640625" style="1" customWidth="1"/>
-    <col min="45" max="46" width="12.33203125" style="1" customWidth="1"/>
-    <col min="47" max="47" width="48.6640625" customWidth="1"/>
-    <col min="48" max="48" width="12.109375" customWidth="1"/>
-    <col min="49" max="49" width="48.6640625" customWidth="1"/>
-    <col min="50" max="50" width="39.6640625" customWidth="1"/>
-    <col min="51" max="51" width="14.6640625" customWidth="1"/>
+    <col min="6" max="8" width="9.25" customWidth="1"/>
+    <col min="9" max="9" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="33" width="8.5" customWidth="1"/>
+    <col min="34" max="34" width="7.625" customWidth="1"/>
+    <col min="35" max="35" width="14.25" customWidth="1"/>
+    <col min="36" max="37" width="7.625" customWidth="1"/>
+    <col min="38" max="38" width="20.5" customWidth="1"/>
+    <col min="39" max="39" width="7.625" customWidth="1"/>
+    <col min="40" max="44" width="7.625" style="1" customWidth="1"/>
+    <col min="45" max="46" width="12.375" style="1" customWidth="1"/>
+    <col min="47" max="47" width="48.625" customWidth="1"/>
+    <col min="48" max="48" width="12.125" customWidth="1"/>
+    <col min="49" max="49" width="48.625" customWidth="1"/>
+    <col min="50" max="50" width="39.625" customWidth="1"/>
+    <col min="51" max="51" width="14.625" customWidth="1"/>
     <col min="52" max="52" width="9" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" s="9" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" s="9" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="AZ1" s="13"/>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
@@ -7689,7 +7689,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -7823,7 +7823,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -7957,7 +7957,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
@@ -8091,7 +8091,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
@@ -8359,7 +8359,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -8627,7 +8627,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -8901,7 +8901,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
@@ -9035,7 +9035,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
@@ -9303,7 +9303,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
@@ -9437,7 +9437,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
@@ -9571,7 +9571,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
@@ -9705,7 +9705,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="18" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
@@ -9839,7 +9839,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="19" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -9979,7 +9979,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
@@ -10116,7 +10116,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
@@ -10250,7 +10250,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="22" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>16</v>
       </c>
@@ -10384,7 +10384,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
@@ -10518,7 +10518,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>16</v>
       </c>
@@ -10652,7 +10652,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>16</v>
       </c>
@@ -10786,7 +10786,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>16</v>
       </c>
@@ -10919,7 +10919,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>16</v>
       </c>
@@ -11051,7 +11051,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>16</v>
       </c>
@@ -11183,7 +11183,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="29" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>16</v>
       </c>
@@ -11313,7 +11313,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="30" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>16</v>
       </c>
@@ -11458,7 +11458,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="31" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>16</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="32" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>40</v>
       </c>
@@ -11726,7 +11726,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="33" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>40</v>
       </c>
@@ -11860,7 +11860,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="34" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>40</v>
       </c>
@@ -11994,7 +11994,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>40</v>
       </c>
@@ -12128,7 +12128,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="36" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>40</v>
       </c>
@@ -12268,7 +12268,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="37" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>40</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
@@ -12536,7 +12536,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="39" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>40</v>
       </c>
@@ -12676,7 +12676,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="40" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>40</v>
       </c>
@@ -12816,7 +12816,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="41" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>40</v>
       </c>
@@ -12950,7 +12950,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="42" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>52</v>
       </c>
@@ -13085,7 +13085,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="43" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>52</v>
       </c>
@@ -13215,7 +13215,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="44" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>52</v>
       </c>
@@ -13349,7 +13349,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="45" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>52</v>
       </c>
@@ -13484,7 +13484,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="46" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>361</v>
       </c>
@@ -13627,7 +13627,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="47" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>52</v>
       </c>
@@ -13763,7 +13763,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="48" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>52</v>
       </c>
@@ -13898,7 +13898,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="49" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>52</v>
       </c>
@@ -14039,7 +14039,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="50" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>52</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="51" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>52</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="52" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>65</v>
       </c>
@@ -14452,7 +14452,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="53" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>65</v>
       </c>
@@ -14584,7 +14584,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="54" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>65</v>
       </c>
@@ -14716,7 +14716,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="55" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>65</v>
       </c>
@@ -14856,7 +14856,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="56" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>65</v>
       </c>
@@ -14996,7 +14996,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="57" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>65</v>
       </c>
@@ -15130,7 +15130,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="58" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>65</v>
       </c>
@@ -15268,7 +15268,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="59" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>65</v>
       </c>
@@ -15402,7 +15402,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="60" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>65</v>
       </c>
@@ -15539,7 +15539,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="61" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>65</v>
       </c>
@@ -15673,7 +15673,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="62" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>73</v>
       </c>
@@ -15807,7 +15807,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="63" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>73</v>
       </c>
@@ -15941,7 +15941,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="64" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>73</v>
       </c>
@@ -16075,7 +16075,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="65" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>73</v>
       </c>
@@ -16209,7 +16209,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="66" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>73</v>
       </c>
@@ -16346,7 +16346,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="67" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>73</v>
       </c>
@@ -16480,7 +16480,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="68" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>73</v>
       </c>
@@ -16614,7 +16614,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="69" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>73</v>
       </c>
@@ -16757,7 +16757,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="70" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>73</v>
       </c>
@@ -16910,7 +16910,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="71" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>73</v>
       </c>
@@ -17044,7 +17044,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="72" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>85</v>
       </c>
@@ -17190,7 +17190,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="73" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>85</v>
       </c>
@@ -17324,7 +17324,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="74" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>85</v>
       </c>
@@ -17456,7 +17456,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="75" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>85</v>
       </c>
@@ -17588,7 +17588,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="76" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>85</v>
       </c>
@@ -17720,7 +17720,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="77" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>85</v>
       </c>
@@ -17852,7 +17852,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="78" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>85</v>
       </c>
@@ -17991,7 +17991,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="79" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>85</v>
       </c>
@@ -18129,7 +18129,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="80" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>85</v>
       </c>
@@ -18273,7 +18273,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="81" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>85</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="82" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>96</v>
       </c>
@@ -18549,7 +18549,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="83" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>96</v>
       </c>
@@ -18684,7 +18684,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="84" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>96</v>
       </c>
@@ -18816,7 +18816,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="85" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>96</v>
       </c>
@@ -18948,7 +18948,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="86" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>96</v>
       </c>
@@ -19080,7 +19080,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="87" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>96</v>
       </c>
@@ -19218,7 +19218,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="88" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>96</v>
       </c>
@@ -19350,7 +19350,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="89" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>96</v>
       </c>
@@ -19482,7 +19482,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="90" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>96</v>
       </c>
@@ -19626,7 +19626,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="91" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>96</v>
       </c>
@@ -19758,7 +19758,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="92" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>113</v>
       </c>
@@ -19893,7 +19893,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="93" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>113</v>
       </c>
@@ -20025,7 +20025,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="94" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>113</v>
       </c>
@@ -20157,7 +20157,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="95" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>113</v>
       </c>
@@ -20292,7 +20292,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="96" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>113</v>
       </c>
@@ -20436,7 +20436,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="97" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>113</v>
       </c>
@@ -20568,7 +20568,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="98" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>113</v>
       </c>
@@ -20703,7 +20703,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="99" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>113</v>
       </c>
@@ -20844,7 +20844,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="100" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>113</v>
       </c>
@@ -20982,7 +20982,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="101" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>113</v>
       </c>
@@ -21120,7 +21120,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="102" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>126</v>
       </c>
@@ -21258,7 +21258,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="103" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>126</v>
       </c>
@@ -21390,7 +21390,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="104" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>126</v>
       </c>
@@ -21528,7 +21528,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="105" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>126</v>
       </c>
@@ -21660,7 +21660,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="106" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>126</v>
       </c>
@@ -21792,7 +21792,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="107" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>126</v>
       </c>
@@ -21924,7 +21924,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="108" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>126</v>
       </c>
@@ -22056,7 +22056,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="109" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>126</v>
       </c>
@@ -22194,7 +22194,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="110" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>126</v>
       </c>
@@ -22332,7 +22332,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="111" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>126</v>
       </c>
@@ -22476,7 +22476,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="112" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>139</v>
       </c>
@@ -22614,7 +22614,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="113" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>139</v>
       </c>
@@ -22746,7 +22746,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="114" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>139</v>
       </c>
@@ -22878,7 +22878,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="115" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>139</v>
       </c>
@@ -23010,7 +23010,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="116" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>139</v>
       </c>
@@ -23142,7 +23142,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="117" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>139</v>
       </c>
@@ -23280,7 +23280,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="118" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>139</v>
       </c>
@@ -23412,7 +23412,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="119" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>139</v>
       </c>
@@ -23562,7 +23562,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="120" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>139</v>
       </c>
@@ -23694,7 +23694,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="121" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>139</v>
       </c>
@@ -23832,7 +23832,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="122" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>152</v>
       </c>
@@ -23967,7 +23967,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="123" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>152</v>
       </c>
@@ -24099,7 +24099,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="124" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>152</v>
       </c>
@@ -24234,7 +24234,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="125" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>152</v>
       </c>
@@ -24366,7 +24366,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="126" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>152</v>
       </c>
@@ -24498,7 +24498,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="127" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>152</v>
       </c>
@@ -24630,7 +24630,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="128" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>152</v>
       </c>
@@ -24765,7 +24765,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="129" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>152</v>
       </c>
@@ -24900,7 +24900,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="130" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>152</v>
       </c>
@@ -25041,7 +25041,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="131" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>152</v>
       </c>
@@ -25173,7 +25173,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="132" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>163</v>
       </c>
@@ -25305,7 +25305,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="133" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>163</v>
       </c>
@@ -25437,7 +25437,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="134" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>163</v>
       </c>
@@ -25569,7 +25569,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="135" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>163</v>
       </c>
@@ -25701,7 +25701,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="136" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>163</v>
       </c>
@@ -25833,7 +25833,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="137" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>163</v>
       </c>
@@ -25965,7 +25965,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="138" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>163</v>
       </c>
@@ -26103,7 +26103,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="139" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>163</v>
       </c>
@@ -26235,7 +26235,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="140" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>163</v>
       </c>
@@ -26367,7 +26367,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="141" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>163</v>
       </c>
@@ -26499,7 +26499,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="142" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>172</v>
       </c>
@@ -26629,7 +26629,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="143" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>172</v>
       </c>
@@ -26761,7 +26761,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="144" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>172</v>
       </c>
@@ -26893,7 +26893,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="145" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>172</v>
       </c>
@@ -27025,7 +27025,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="146" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>172</v>
       </c>
@@ -27157,7 +27157,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="147" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>172</v>
       </c>
@@ -27289,7 +27289,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="148" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>172</v>
       </c>
@@ -27421,7 +27421,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="149" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>172</v>
       </c>
@@ -27550,7 +27550,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="150" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>172</v>
       </c>
@@ -27697,7 +27697,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="151" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>172</v>
       </c>
@@ -27835,7 +27835,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="152" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>185</v>
       </c>
@@ -27967,7 +27967,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="153" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>185</v>
       </c>
@@ -28099,7 +28099,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="154" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>185</v>
       </c>
@@ -28231,7 +28231,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="155" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>185</v>
       </c>
@@ -28363,7 +28363,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="156" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>185</v>
       </c>
@@ -28498,7 +28498,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="157" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>185</v>
       </c>
@@ -28630,7 +28630,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="158" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>185</v>
       </c>
@@ -28762,7 +28762,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="159" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>185</v>
       </c>
@@ -28894,7 +28894,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="160" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>185</v>
       </c>
@@ -29032,7 +29032,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="161" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>185</v>
       </c>
@@ -29164,7 +29164,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="162" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>197</v>
       </c>
@@ -29297,7 +29297,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="163" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>197</v>
       </c>
@@ -29429,7 +29429,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="164" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>197</v>
       </c>
@@ -29561,7 +29561,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="165" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>197</v>
       </c>
@@ -29697,7 +29697,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="166" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>197</v>
       </c>
@@ -29829,7 +29829,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="167" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>197</v>
       </c>
@@ -29962,7 +29962,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="168" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>197</v>
       </c>
@@ -30104,7 +30104,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="169" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>197</v>
       </c>
@@ -30239,7 +30239,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="170" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>197</v>
       </c>
@@ -30380,7 +30380,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="171" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>197</v>
       </c>
@@ -30512,7 +30512,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="172" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>210</v>
       </c>
@@ -30644,7 +30644,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="173" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>210</v>
       </c>
@@ -30779,7 +30779,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="174" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>210</v>
       </c>
@@ -30911,7 +30911,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="175" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>210</v>
       </c>
@@ -31043,7 +31043,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="176" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>210</v>
       </c>
@@ -31175,7 +31175,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="177" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>210</v>
       </c>
@@ -31307,7 +31307,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="178" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>210</v>
       </c>
@@ -31443,7 +31443,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="179" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>210</v>
       </c>
@@ -31575,7 +31575,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="180" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>210</v>
       </c>
@@ -31707,7 +31707,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="181" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>210</v>
       </c>
@@ -31848,7 +31848,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="182" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>223</v>
       </c>
@@ -31978,7 +31978,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="183" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>223</v>
       </c>
@@ -32113,7 +32113,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="184" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>223</v>
       </c>
@@ -32248,7 +32248,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="185" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>223</v>
       </c>
@@ -32380,7 +32380,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="186" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>223</v>
       </c>
@@ -32521,7 +32521,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="187" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>223</v>
       </c>
@@ -32653,7 +32653,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="188" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>223</v>
       </c>
@@ -32791,7 +32791,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="189" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>223</v>
       </c>
@@ -32929,7 +32929,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="190" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>223</v>
       </c>
@@ -33070,7 +33070,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="191" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>223</v>
       </c>
@@ -33214,7 +33214,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="192" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>232</v>
       </c>
@@ -33349,7 +33349,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="193" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>232</v>
       </c>
@@ -33481,7 +33481,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="194" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>232</v>
       </c>
@@ -33619,7 +33619,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="195" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>232</v>
       </c>
@@ -33751,7 +33751,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="196" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>232</v>
       </c>
@@ -33883,7 +33883,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="197" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>232</v>
       </c>
@@ -34015,7 +34015,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="198" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>232</v>
       </c>
@@ -34153,7 +34153,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="199" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>232</v>
       </c>
@@ -34285,7 +34285,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="200" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>232</v>
       </c>
@@ -34421,7 +34421,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="201" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>232</v>
       </c>
@@ -34559,7 +34559,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="202" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>245</v>
       </c>
@@ -34691,7 +34691,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="203" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>245</v>
       </c>
@@ -34823,7 +34823,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="204" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>245</v>
       </c>
@@ -34955,7 +34955,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="205" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>245</v>
       </c>
@@ -35096,7 +35096,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="206" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>245</v>
       </c>
@@ -35237,7 +35237,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="207" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>245</v>
       </c>
@@ -35384,7 +35384,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="208" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>245</v>
       </c>
@@ -35516,7 +35516,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="209" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>245</v>
       </c>
@@ -35657,7 +35657,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="210" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>245</v>
       </c>
@@ -35804,7 +35804,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="211" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>245</v>
       </c>
@@ -35945,7 +35945,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="212" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>259</v>
       </c>
@@ -36077,7 +36077,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="213" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>259</v>
       </c>
@@ -36215,7 +36215,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="214" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>259</v>
       </c>
@@ -36350,7 +36350,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="215" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>259</v>
       </c>
@@ -36482,7 +36482,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="216" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>259</v>
       </c>
@@ -36614,7 +36614,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="217" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>259</v>
       </c>
@@ -36746,7 +36746,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="218" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>259</v>
       </c>
@@ -36899,7 +36899,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="219" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>259</v>
       </c>
@@ -37040,7 +37040,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="220" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>259</v>
       </c>
@@ -37172,7 +37172,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="221" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>259</v>
       </c>
@@ -37304,7 +37304,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="222" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>274</v>
       </c>
@@ -37442,7 +37442,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="223" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>274</v>
       </c>
@@ -37583,7 +37583,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="224" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>274</v>
       </c>
@@ -37724,7 +37724,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="225" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>274</v>
       </c>
@@ -37865,7 +37865,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="226" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>274</v>
       </c>
@@ -38006,7 +38006,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="227" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>274</v>
       </c>
@@ -38138,7 +38138,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="228" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>274</v>
       </c>
@@ -38276,7 +38276,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="229" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>274</v>
       </c>
@@ -38408,7 +38408,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="230" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>274</v>
       </c>
@@ -38555,7 +38555,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="231" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>274</v>
       </c>
@@ -38702,7 +38702,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="232" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>671</v>
       </c>
@@ -38764,7 +38764,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="233" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>676</v>
       </c>
@@ -38832,7 +38832,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="234" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>682</v>
       </c>
@@ -38891,7 +38891,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="235" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>687</v>
       </c>
@@ -38953,7 +38953,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="236" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>693</v>
       </c>
@@ -39003,7 +39003,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="237" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>696</v>
       </c>
@@ -39059,7 +39059,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="238" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>699</v>
       </c>
@@ -39118,7 +39118,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="239" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>705</v>
       </c>
@@ -39180,7 +39180,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="240" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>713</v>
       </c>
@@ -39239,7 +39239,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="241" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>718</v>
       </c>
@@ -39289,7 +39289,7 @@
         <v>331</v>
       </c>
       <c r="AV241" s="1" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="AW241" s="1" t="s">
         <v>1949</v>
@@ -39298,7 +39298,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="242" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>723</v>
       </c>
@@ -39357,7 +39357,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="243" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>728</v>
       </c>
@@ -39410,7 +39410,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="244" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>734</v>
       </c>
@@ -39442,7 +39442,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="245" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>738</v>
       </c>
@@ -39483,7 +39483,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="246" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>740</v>
       </c>
@@ -39530,7 +39530,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="247" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>746</v>
       </c>
@@ -39586,7 +39586,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="248" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>751</v>
       </c>
@@ -39651,7 +39651,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="249" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>758</v>
       </c>
@@ -39710,7 +39710,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="250" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>765</v>
       </c>
@@ -39766,7 +39766,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="251" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>772</v>
       </c>
@@ -39822,7 +39822,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="252" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>778</v>
       </c>
@@ -39884,7 +39884,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="253" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>786</v>
       </c>
@@ -39940,7 +39940,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="254" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>792</v>
       </c>
@@ -39996,7 +39996,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="255" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>797</v>
       </c>
@@ -40049,7 +40049,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="256" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>802</v>
       </c>
@@ -40102,7 +40102,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="257" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>807</v>
       </c>
@@ -40152,7 +40152,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="258" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>813</v>
       </c>
@@ -40202,7 +40202,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="259" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>818</v>
       </c>
@@ -40255,7 +40255,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="260" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>823</v>
       </c>
@@ -40308,7 +40308,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="261" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>829</v>
       </c>
@@ -40361,7 +40361,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="262" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>834</v>
       </c>
@@ -40414,7 +40414,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="263" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>838</v>
       </c>
@@ -40467,7 +40467,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="264" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>842</v>
       </c>
@@ -40523,7 +40523,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="265" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>848</v>
       </c>
@@ -40576,7 +40576,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="266" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>853</v>
       </c>
@@ -40629,7 +40629,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="267" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>858</v>
       </c>
@@ -40682,7 +40682,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="268" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>862</v>
       </c>
@@ -40741,7 +40741,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="269" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>866</v>
       </c>
@@ -40797,7 +40797,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="270" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>871</v>
       </c>
@@ -40850,7 +40850,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="271" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>876</v>
       </c>
@@ -40900,7 +40900,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="272" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>881</v>
       </c>
@@ -40953,7 +40953,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="273" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>885</v>
       </c>
@@ -41003,7 +41003,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="274" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>889</v>
       </c>
@@ -41053,7 +41053,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="275" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>894</v>
       </c>
@@ -41100,7 +41100,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="276" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>896</v>
       </c>
@@ -41138,7 +41138,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="277" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>900</v>
       </c>
@@ -41185,7 +41185,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="278" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>903</v>
       </c>
@@ -41229,7 +41229,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="279" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>908</v>
       </c>
@@ -41273,7 +41273,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="280" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>913</v>
       </c>
@@ -41311,7 +41311,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="281" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>916</v>
       </c>
@@ -41364,7 +41364,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="282" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>919</v>
       </c>
@@ -41417,7 +41417,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="283" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>923</v>
       </c>
@@ -41478,797 +41478,797 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A83FB8B-F526-4731-A8B0-CF3B6BDD1233}">
   <dimension ref="A1:A158"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="125.6640625" customWidth="1"/>
+    <col min="1" max="1" width="125.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="63" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="77" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
         <v>931</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="5" t="s">
         <v>1946</v>
       </c>
     </row>
-    <row r="129" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A129" s="5" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="145" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="146" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="149" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="150" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="151" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="152" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="153" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="154" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="155" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="156" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
         <v>940</v>
       </c>
     </row>
-    <row r="157" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
         <v>1835</v>
       </c>
@@ -42282,13 +42282,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1222779-D1F7-486F-9B13-D492D72521FD}">
   <dimension ref="A1:N231"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="19.88671875" customWidth="1"/>
+    <col min="7" max="7" width="19.875" customWidth="1"/>
     <col min="14" max="14" width="9" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="25.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -42320,7 +42320,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
@@ -42354,7 +42354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -42388,7 +42388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -42422,7 +42422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
@@ -42456,7 +42456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
@@ -42490,7 +42490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
@@ -42524,7 +42524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -42558,7 +42558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -42595,7 +42595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
@@ -42632,7 +42632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -42669,7 +42669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
@@ -42703,7 +42703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -42737,7 +42737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
@@ -42771,7 +42771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
@@ -42805,7 +42805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
@@ -42839,7 +42839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
@@ -42873,7 +42873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
@@ -42907,7 +42907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -42944,7 +42944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
@@ -42981,7 +42981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
@@ -43018,7 +43018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>16</v>
       </c>
@@ -43052,7 +43052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
@@ -43086,7 +43086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>16</v>
       </c>
@@ -43120,7 +43120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>16</v>
       </c>
@@ -43154,7 +43154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>16</v>
       </c>
@@ -43188,7 +43188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>16</v>
       </c>
@@ -43222,7 +43222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>16</v>
       </c>
@@ -43256,7 +43256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>16</v>
       </c>
@@ -43294,7 +43294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>16</v>
       </c>
@@ -43332,7 +43332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>16</v>
       </c>
@@ -43369,7 +43369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>40</v>
       </c>
@@ -43403,7 +43403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>40</v>
       </c>
@@ -43437,7 +43437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>40</v>
       </c>
@@ -43471,7 +43471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>40</v>
       </c>
@@ -43505,7 +43505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>40</v>
       </c>
@@ -43539,7 +43539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>40</v>
       </c>
@@ -43573,7 +43573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
@@ -43607,7 +43607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>40</v>
       </c>
@@ -43645,7 +43645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>40</v>
       </c>
@@ -43683,7 +43683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>40</v>
       </c>
@@ -43721,7 +43721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>52</v>
       </c>
@@ -43755,7 +43755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>52</v>
       </c>
@@ -43789,7 +43789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>52</v>
       </c>
@@ -43823,7 +43823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>52</v>
       </c>
@@ -43857,7 +43857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>361</v>
       </c>
@@ -43891,7 +43891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>52</v>
       </c>
@@ -43925,7 +43925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>52</v>
       </c>
@@ -43959,7 +43959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>52</v>
       </c>
@@ -43997,7 +43997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>52</v>
       </c>
@@ -44035,7 +44035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>52</v>
       </c>
@@ -44073,7 +44073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>65</v>
       </c>
@@ -44107,7 +44107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>65</v>
       </c>
@@ -44141,7 +44141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>65</v>
       </c>
@@ -44175,7 +44175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>65</v>
       </c>
@@ -44209,7 +44209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>65</v>
       </c>
@@ -44243,7 +44243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>65</v>
       </c>
@@ -44277,7 +44277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>65</v>
       </c>
@@ -44311,7 +44311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>65</v>
       </c>
@@ -44349,7 +44349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>65</v>
       </c>
@@ -44386,7 +44386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>65</v>
       </c>
@@ -44424,7 +44424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>73</v>
       </c>
@@ -44458,7 +44458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>73</v>
       </c>
@@ -44492,7 +44492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>73</v>
       </c>
@@ -44526,7 +44526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>73</v>
       </c>
@@ -44560,7 +44560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>73</v>
       </c>
@@ -44594,7 +44594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>73</v>
       </c>
@@ -44628,7 +44628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>73</v>
       </c>
@@ -44662,7 +44662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>73</v>
       </c>
@@ -44700,7 +44700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>73</v>
       </c>
@@ -44738,7 +44738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>73</v>
       </c>
@@ -44776,7 +44776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>85</v>
       </c>
@@ -44810,7 +44810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>85</v>
       </c>
@@ -44844,7 +44844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>85</v>
       </c>
@@ -44878,7 +44878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>85</v>
       </c>
@@ -44912,7 +44912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>85</v>
       </c>
@@ -44946,7 +44946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>85</v>
       </c>
@@ -44980,7 +44980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>85</v>
       </c>
@@ -45014,7 +45014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>85</v>
       </c>
@@ -45052,7 +45052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>85</v>
       </c>
@@ -45090,7 +45090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>85</v>
       </c>
@@ -45128,7 +45128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>96</v>
       </c>
@@ -45162,7 +45162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>96</v>
       </c>
@@ -45196,7 +45196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>96</v>
       </c>
@@ -45230,7 +45230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>96</v>
       </c>
@@ -45264,7 +45264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>96</v>
       </c>
@@ -45298,7 +45298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>96</v>
       </c>
@@ -45332,7 +45332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>96</v>
       </c>
@@ -45366,7 +45366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>96</v>
       </c>
@@ -45403,7 +45403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>96</v>
       </c>
@@ -45440,7 +45440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>96</v>
       </c>
@@ -45477,7 +45477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>113</v>
       </c>
@@ -45511,7 +45511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>113</v>
       </c>
@@ -45545,7 +45545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>113</v>
       </c>
@@ -45579,7 +45579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>113</v>
       </c>
@@ -45613,7 +45613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>113</v>
       </c>
@@ -45647,7 +45647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>113</v>
       </c>
@@ -45681,7 +45681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>113</v>
       </c>
@@ -45715,7 +45715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>113</v>
       </c>
@@ -45752,7 +45752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>113</v>
       </c>
@@ -45789,7 +45789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>113</v>
       </c>
@@ -45826,7 +45826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>126</v>
       </c>
@@ -45860,7 +45860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>126</v>
       </c>
@@ -45894,7 +45894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>126</v>
       </c>
@@ -45928,7 +45928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>126</v>
       </c>
@@ -45962,7 +45962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>126</v>
       </c>
@@ -45996,7 +45996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>126</v>
       </c>
@@ -46030,7 +46030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>126</v>
       </c>
@@ -46064,7 +46064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>126</v>
       </c>
@@ -46101,7 +46101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>126</v>
       </c>
@@ -46138,7 +46138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>126</v>
       </c>
@@ -46175,7 +46175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>139</v>
       </c>
@@ -46209,7 +46209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>139</v>
       </c>
@@ -46243,7 +46243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>139</v>
       </c>
@@ -46277,7 +46277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>139</v>
       </c>
@@ -46311,7 +46311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>139</v>
       </c>
@@ -46345,7 +46345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>139</v>
       </c>
@@ -46379,7 +46379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>139</v>
       </c>
@@ -46413,7 +46413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>139</v>
       </c>
@@ -46451,7 +46451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>139</v>
       </c>
@@ -46489,7 +46489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>139</v>
       </c>
@@ -46527,7 +46527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>152</v>
       </c>
@@ -46561,7 +46561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>152</v>
       </c>
@@ -46595,7 +46595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>152</v>
       </c>
@@ -46629,7 +46629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>152</v>
       </c>
@@ -46663,7 +46663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>152</v>
       </c>
@@ -46697,7 +46697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>152</v>
       </c>
@@ -46731,7 +46731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>152</v>
       </c>
@@ -46765,7 +46765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>152</v>
       </c>
@@ -46803,7 +46803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>152</v>
       </c>
@@ -46840,7 +46840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>152</v>
       </c>
@@ -46878,7 +46878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>163</v>
       </c>
@@ -46912,7 +46912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>163</v>
       </c>
@@ -46946,7 +46946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>163</v>
       </c>
@@ -46980,7 +46980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>163</v>
       </c>
@@ -47014,7 +47014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>163</v>
       </c>
@@ -47048,7 +47048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>163</v>
       </c>
@@ -47082,7 +47082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>163</v>
       </c>
@@ -47116,7 +47116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>163</v>
       </c>
@@ -47154,7 +47154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>163</v>
       </c>
@@ -47192,7 +47192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>163</v>
       </c>
@@ -47230,7 +47230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>172</v>
       </c>
@@ -47264,7 +47264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>172</v>
       </c>
@@ -47298,7 +47298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>172</v>
       </c>
@@ -47332,7 +47332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>172</v>
       </c>
@@ -47366,7 +47366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>172</v>
       </c>
@@ -47400,7 +47400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>172</v>
       </c>
@@ -47434,7 +47434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>172</v>
       </c>
@@ -47468,7 +47468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>172</v>
       </c>
@@ -47506,7 +47506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>172</v>
       </c>
@@ -47544,7 +47544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>172</v>
       </c>
@@ -47582,7 +47582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>185</v>
       </c>
@@ -47616,7 +47616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>185</v>
       </c>
@@ -47650,7 +47650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>185</v>
       </c>
@@ -47684,7 +47684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>185</v>
       </c>
@@ -47718,7 +47718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>185</v>
       </c>
@@ -47752,7 +47752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>185</v>
       </c>
@@ -47786,7 +47786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>185</v>
       </c>
@@ -47820,7 +47820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>185</v>
       </c>
@@ -47858,7 +47858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>185</v>
       </c>
@@ -47896,7 +47896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>185</v>
       </c>
@@ -47934,7 +47934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>197</v>
       </c>
@@ -47968,7 +47968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>197</v>
       </c>
@@ -48002,7 +48002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>197</v>
       </c>
@@ -48036,7 +48036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>197</v>
       </c>
@@ -48070,7 +48070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>197</v>
       </c>
@@ -48104,7 +48104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>197</v>
       </c>
@@ -48138,7 +48138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>197</v>
       </c>
@@ -48172,7 +48172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>197</v>
       </c>
@@ -48210,7 +48210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>197</v>
       </c>
@@ -48248,7 +48248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>197</v>
       </c>
@@ -48286,7 +48286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>210</v>
       </c>
@@ -48320,7 +48320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>210</v>
       </c>
@@ -48354,7 +48354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>210</v>
       </c>
@@ -48388,7 +48388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>210</v>
       </c>
@@ -48422,7 +48422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>210</v>
       </c>
@@ -48456,7 +48456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>210</v>
       </c>
@@ -48490,7 +48490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>210</v>
       </c>
@@ -48524,7 +48524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>210</v>
       </c>
@@ -48562,7 +48562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>210</v>
       </c>
@@ -48600,7 +48600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>210</v>
       </c>
@@ -48638,7 +48638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>223</v>
       </c>
@@ -48672,7 +48672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>223</v>
       </c>
@@ -48706,7 +48706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>223</v>
       </c>
@@ -48740,7 +48740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>223</v>
       </c>
@@ -48774,7 +48774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>223</v>
       </c>
@@ -48808,7 +48808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>223</v>
       </c>
@@ -48842,7 +48842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>223</v>
       </c>
@@ -48876,7 +48876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>223</v>
       </c>
@@ -48914,7 +48914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>223</v>
       </c>
@@ -48952,7 +48952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>223</v>
       </c>
@@ -48990,7 +48990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>232</v>
       </c>
@@ -49024,7 +49024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>232</v>
       </c>
@@ -49058,7 +49058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>232</v>
       </c>
@@ -49092,7 +49092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>232</v>
       </c>
@@ -49126,7 +49126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>232</v>
       </c>
@@ -49160,7 +49160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>232</v>
       </c>
@@ -49194,7 +49194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>232</v>
       </c>
@@ -49228,7 +49228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>232</v>
       </c>
@@ -49265,7 +49265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>232</v>
       </c>
@@ -49303,7 +49303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>232</v>
       </c>
@@ -49341,7 +49341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>245</v>
       </c>
@@ -49368,7 +49368,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>245</v>
       </c>
@@ -49395,7 +49395,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>245</v>
       </c>
@@ -49422,7 +49422,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>245</v>
       </c>
@@ -49449,7 +49449,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>245</v>
       </c>
@@ -49476,7 +49476,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>245</v>
       </c>
@@ -49503,7 +49503,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>245</v>
       </c>
@@ -49530,7 +49530,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>245</v>
       </c>
@@ -49561,7 +49561,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>245</v>
       </c>
@@ -49592,7 +49592,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>245</v>
       </c>
@@ -49623,7 +49623,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>259</v>
       </c>
@@ -49650,7 +49650,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>259</v>
       </c>
@@ -49677,7 +49677,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>259</v>
       </c>
@@ -49704,7 +49704,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>259</v>
       </c>
@@ -49731,7 +49731,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>259</v>
       </c>
@@ -49758,7 +49758,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>259</v>
       </c>
@@ -49785,7 +49785,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>259</v>
       </c>
@@ -49812,7 +49812,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>259</v>
       </c>
@@ -49843,7 +49843,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>259</v>
       </c>
@@ -49874,7 +49874,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>259</v>
       </c>
@@ -49904,7 +49904,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>274</v>
       </c>
@@ -49931,7 +49931,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>274</v>
       </c>
@@ -49958,7 +49958,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>274</v>
       </c>
@@ -49985,7 +49985,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>274</v>
       </c>
@@ -50012,7 +50012,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>274</v>
       </c>
@@ -50039,7 +50039,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>274</v>
       </c>
@@ -50066,7 +50066,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>274</v>
       </c>
@@ -50093,7 +50093,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>274</v>
       </c>
@@ -50124,7 +50124,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>274</v>
       </c>
@@ -50155,7 +50155,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>274</v>
       </c>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\codex-mire-inferno-20261019\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\codex-mire-inferno-flames-20261019\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F1C426-405F-491D-8732-F9EA493600EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE0E24CE-5C3B-422F-9770-08E3CFD21FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12416" uniqueCount="2026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12416" uniqueCount="2027">
   <si>
     <t>群組ID</t>
   </si>
@@ -7217,6 +7217,10 @@
   </si>
   <si>
     <t>本體欄：非空覆寫同角色，留白沿前階繼承；狀態畫面由 Status 表決定。本列觸發特效在火球落地時播放，匹配爆炸傷害半徑。飛行子彈使用融火之心同款拋物線火球；本體地板只由沼澤播放，觸發地板由每顆火球落地後的固定火池播放，匹配火池半徑及完整持續時間。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ground-mire-inferno-pool</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -25335,7 +25339,7 @@
         <v>490</v>
       </c>
       <c r="AR130" s="1" t="s">
-        <v>120</v>
+        <v>2026</v>
       </c>
       <c r="AT130" s="1" t="s">
         <v>320</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\codex-mire-inferno-flames-20261019\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE0E24CE-5C3B-422F-9770-08E3CFD21FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EF8C70-D0D6-4272-814C-9DD524F2151C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12416" uniqueCount="2027">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12416" uniqueCount="2033">
   <si>
     <t>群組ID</t>
   </si>
@@ -4746,10 +4746,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"hpPct":30,"chance":0.5,"chancePer":0.05,"add":0.5,"addPer":0.05}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>大地守護</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -7205,6 +7201,34 @@
   </si>
   <si>
     <t>緩速強化為移動速度 -{move}%、攻速 -{aspd}%，且受影響目標受到的傷害再提高 {pct}%（與第 1 階累加）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>緩速強化為移動速度 -{move}%、攻速 -{aspd}%，且受影響目標受到的傷害再提高 {pct}%。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>沼澤持續放出毒氣：沼澤中的敵人每 {dotGap} 秒受到魔法攻擊 {dotPct}% 的毒性傷害。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>沼澤持續時間提高至 {sec} 秒，且在 {growSec} 秒內逐步擴大，最大擴增 {pct}%。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>沼澤轉變為岩漿：持續時間提高至 {sec} 秒、範圍再擴增 {pct}%，其中的目標每 {dotGap} 秒額外受到 {dotPct}% 的火焰傷害。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>沼澤範圍內的敵人染上【瘟疫】：每 {gap} 秒受到魔法攻擊 {pct}% 的毒性傷害，且受到的毒性傷害額外 +{amp}%；離開沼澤後仍持續 {sec} 秒。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"hpPct":25,"chance":0.5,"chancePer":0.05,"add":0.5,"addPer":0.05}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>沼澤範圍內生命值 {hpPct}% 以下的敵人，每次受到傷害有 {chance}% 機率直接被斬殺，且該機率每次受傷再累加 {add}%</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -7734,7 +7758,7 @@
         <v>907</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>908</v>
@@ -7743,7 +7767,7 @@
         <v>909</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>910</v>
@@ -7896,7 +7920,7 @@
         <v>491</v>
       </c>
       <c r="G2" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>954</v>
@@ -8001,7 +8025,7 @@
         <v>582</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="AX2" s="1" t="s">
         <v>30</v>
@@ -8030,7 +8054,7 @@
         <v>964</v>
       </c>
       <c r="G3" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>965</v>
@@ -8135,7 +8159,7 @@
         <v>1056</v>
       </c>
       <c r="AW3" s="1" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="AX3" s="1" t="s">
         <v>31</v>
@@ -8164,7 +8188,7 @@
         <v>970</v>
       </c>
       <c r="G4" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>971</v>
@@ -8269,7 +8293,7 @@
         <v>1058</v>
       </c>
       <c r="AW4" s="1" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="AX4" s="1" t="s">
         <v>32</v>
@@ -8298,7 +8322,7 @@
         <v>577</v>
       </c>
       <c r="G5" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>976</v>
@@ -8403,7 +8427,7 @@
         <v>583</v>
       </c>
       <c r="AW5" s="1" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="AX5" s="1" t="s">
         <v>33</v>
@@ -8432,7 +8456,7 @@
         <v>982</v>
       </c>
       <c r="G6" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>983</v>
@@ -8537,7 +8561,7 @@
         <v>584</v>
       </c>
       <c r="AW6" s="1" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="AX6" s="1" t="s">
         <v>34</v>
@@ -8566,7 +8590,7 @@
         <v>504</v>
       </c>
       <c r="G7" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>989</v>
@@ -8671,7 +8695,7 @@
         <v>585</v>
       </c>
       <c r="AW7" s="1" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="AX7" s="1" t="s">
         <v>35</v>
@@ -8700,7 +8724,7 @@
         <v>994</v>
       </c>
       <c r="G8" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>995</v>
@@ -8802,10 +8826,10 @@
         <v>320</v>
       </c>
       <c r="AV8" s="1" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="AW8" s="1" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="AX8" s="1" t="s">
         <v>36</v>
@@ -8834,7 +8858,7 @@
         <v>554</v>
       </c>
       <c r="G9" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>999</v>
@@ -8939,7 +8963,7 @@
         <v>1069</v>
       </c>
       <c r="AW9" s="1" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="AX9" s="1" t="s">
         <v>37</v>
@@ -8968,7 +8992,7 @@
         <v>1007</v>
       </c>
       <c r="G10" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>999</v>
@@ -9079,7 +9103,7 @@
         <v>1073</v>
       </c>
       <c r="AW10" s="1" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="AX10" s="1" t="s">
         <v>38</v>
@@ -9108,7 +9132,7 @@
         <v>1014</v>
       </c>
       <c r="G11" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>999</v>
@@ -9213,7 +9237,7 @@
         <v>586</v>
       </c>
       <c r="AW11" s="1" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="AX11" s="1" t="s">
         <v>39</v>
@@ -9242,7 +9266,7 @@
         <v>491</v>
       </c>
       <c r="G12" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>954</v>
@@ -9347,7 +9371,7 @@
         <v>582</v>
       </c>
       <c r="AW12" s="1" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="AX12" s="1" t="s">
         <v>9</v>
@@ -9376,7 +9400,7 @@
         <v>964</v>
       </c>
       <c r="G13" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>965</v>
@@ -9481,7 +9505,7 @@
         <v>967</v>
       </c>
       <c r="AW13" s="1" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="AX13" s="1" t="s">
         <v>10</v>
@@ -9510,7 +9534,7 @@
         <v>970</v>
       </c>
       <c r="G14" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>971</v>
@@ -9615,7 +9639,7 @@
         <v>974</v>
       </c>
       <c r="AW14" s="1" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="AX14" s="1" t="s">
         <v>11</v>
@@ -9644,7 +9668,7 @@
         <v>577</v>
       </c>
       <c r="G15" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>976</v>
@@ -9749,7 +9773,7 @@
         <v>979</v>
       </c>
       <c r="AW15" s="1" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="AX15" s="1" t="s">
         <v>12</v>
@@ -9778,7 +9802,7 @@
         <v>982</v>
       </c>
       <c r="G16" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>983</v>
@@ -9883,7 +9907,7 @@
         <v>986</v>
       </c>
       <c r="AW16" s="1" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="AX16" s="1" t="s">
         <v>13</v>
@@ -9912,7 +9936,7 @@
         <v>504</v>
       </c>
       <c r="G17" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>989</v>
@@ -10017,7 +10041,7 @@
         <v>992</v>
       </c>
       <c r="AW17" s="1" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="AX17" s="1" t="s">
         <v>14</v>
@@ -10046,7 +10070,7 @@
         <v>994</v>
       </c>
       <c r="G18" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>995</v>
@@ -10151,7 +10175,7 @@
         <v>579</v>
       </c>
       <c r="AW18" s="1" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="AX18" s="1" t="s">
         <v>997</v>
@@ -10180,7 +10204,7 @@
         <v>554</v>
       </c>
       <c r="G19" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>999</v>
@@ -10291,7 +10315,7 @@
         <v>580</v>
       </c>
       <c r="AW19" s="1" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="AX19" s="1" t="s">
         <v>1004</v>
@@ -10320,7 +10344,7 @@
         <v>1007</v>
       </c>
       <c r="G20" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>999</v>
@@ -10428,7 +10452,7 @@
         <v>1011</v>
       </c>
       <c r="AW20" s="1" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="AX20" s="1" t="s">
         <v>15</v>
@@ -10457,7 +10481,7 @@
         <v>1014</v>
       </c>
       <c r="G21" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>999</v>
@@ -10562,7 +10586,7 @@
         <v>1017</v>
       </c>
       <c r="AW21" s="1" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="AX21" s="1" t="s">
         <v>1018</v>
@@ -10591,7 +10615,7 @@
         <v>491</v>
       </c>
       <c r="G22" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>954</v>
@@ -10696,7 +10720,7 @@
         <v>1023</v>
       </c>
       <c r="AW22" s="1" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="AX22" s="1" t="s">
         <v>18</v>
@@ -10725,7 +10749,7 @@
         <v>964</v>
       </c>
       <c r="G23" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>965</v>
@@ -10830,7 +10854,7 @@
         <v>992</v>
       </c>
       <c r="AW23" s="1" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="AX23" s="1" t="s">
         <v>19</v>
@@ -10859,7 +10883,7 @@
         <v>970</v>
       </c>
       <c r="G24" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>971</v>
@@ -10964,7 +10988,7 @@
         <v>1027</v>
       </c>
       <c r="AW24" s="1" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="AX24" s="1" t="s">
         <v>20</v>
@@ -10993,7 +11017,7 @@
         <v>577</v>
       </c>
       <c r="G25" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>976</v>
@@ -11098,7 +11122,7 @@
         <v>1029</v>
       </c>
       <c r="AW25" s="1" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="AX25" s="1" t="s">
         <v>21</v>
@@ -11127,7 +11151,7 @@
         <v>982</v>
       </c>
       <c r="G26" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>983</v>
@@ -11231,7 +11255,7 @@
         <v>1033</v>
       </c>
       <c r="AW26" s="1" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="AX26" s="1" t="s">
         <v>22</v>
@@ -11260,7 +11284,7 @@
         <v>504</v>
       </c>
       <c r="G27" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>989</v>
@@ -11363,7 +11387,7 @@
         <v>992</v>
       </c>
       <c r="AW27" s="1" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="AX27" s="1" t="s">
         <v>23</v>
@@ -11392,7 +11416,7 @@
         <v>994</v>
       </c>
       <c r="G28" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>995</v>
@@ -11524,7 +11548,7 @@
         <v>554</v>
       </c>
       <c r="G29" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>999</v>
@@ -11654,7 +11678,7 @@
         <v>1007</v>
       </c>
       <c r="G30" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>999</v>
@@ -11799,7 +11823,7 @@
         <v>1014</v>
       </c>
       <c r="G31" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>999</v>
@@ -11933,7 +11957,7 @@
         <v>491</v>
       </c>
       <c r="G32" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>954</v>
@@ -12067,7 +12091,7 @@
         <v>964</v>
       </c>
       <c r="G33" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>965</v>
@@ -12201,7 +12225,7 @@
         <v>970</v>
       </c>
       <c r="G34" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>971</v>
@@ -12335,7 +12359,7 @@
         <v>577</v>
       </c>
       <c r="G35" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>976</v>
@@ -12469,7 +12493,7 @@
         <v>982</v>
       </c>
       <c r="G36" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>983</v>
@@ -12609,7 +12633,7 @@
         <v>504</v>
       </c>
       <c r="G37" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>989</v>
@@ -12743,7 +12767,7 @@
         <v>994</v>
       </c>
       <c r="G38" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>995</v>
@@ -12877,7 +12901,7 @@
         <v>554</v>
       </c>
       <c r="G39" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>999</v>
@@ -13017,7 +13041,7 @@
         <v>1007</v>
       </c>
       <c r="G40" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>999</v>
@@ -13157,7 +13181,7 @@
         <v>1014</v>
       </c>
       <c r="G41" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>999</v>
@@ -13291,7 +13315,7 @@
         <v>491</v>
       </c>
       <c r="G42" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>954</v>
@@ -13394,7 +13418,7 @@
         <v>1115</v>
       </c>
       <c r="AV42" s="1" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="AW42" s="1" t="s">
         <v>54</v>
@@ -13426,7 +13450,7 @@
         <v>964</v>
       </c>
       <c r="G43" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>965</v>
@@ -13524,7 +13548,7 @@
         <v>320</v>
       </c>
       <c r="AV43" s="1" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="AW43" s="1" t="s">
         <v>55</v>
@@ -13556,7 +13580,7 @@
         <v>970</v>
       </c>
       <c r="G44" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>971</v>
@@ -13690,7 +13714,7 @@
         <v>577</v>
       </c>
       <c r="G45" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>976</v>
@@ -13825,7 +13849,7 @@
         <v>982</v>
       </c>
       <c r="G46" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>983</v>
@@ -13936,7 +13960,7 @@
         <v>320</v>
       </c>
       <c r="AV46" s="1" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="AW46" s="1" t="s">
         <v>59</v>
@@ -13968,7 +13992,7 @@
         <v>504</v>
       </c>
       <c r="G47" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>989</v>
@@ -14104,7 +14128,7 @@
         <v>994</v>
       </c>
       <c r="G48" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>995</v>
@@ -14207,7 +14231,7 @@
         <v>320</v>
       </c>
       <c r="AV48" s="1" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="AW48" s="1" t="s">
         <v>62</v>
@@ -14239,7 +14263,7 @@
         <v>554</v>
       </c>
       <c r="G49" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>999</v>
@@ -14380,7 +14404,7 @@
         <v>1007</v>
       </c>
       <c r="G50" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>999</v>
@@ -14522,7 +14546,7 @@
         <v>1014</v>
       </c>
       <c r="G51" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>999</v>
@@ -14626,16 +14650,16 @@
         <v>320</v>
       </c>
       <c r="AV51" s="1" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="AW51" s="1" t="s">
+        <v>1924</v>
+      </c>
+      <c r="AX51" s="1" t="s">
         <v>1925</v>
       </c>
-      <c r="AX51" s="1" t="s">
-        <v>1926</v>
-      </c>
       <c r="AY51" s="1" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="AZ51" s="3" t="s">
         <v>1143</v>
@@ -14658,7 +14682,7 @@
         <v>491</v>
       </c>
       <c r="G52" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>954</v>
@@ -14759,7 +14783,7 @@
         <v>1147</v>
       </c>
       <c r="AW52" s="1" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="AX52" s="1" t="s">
         <v>1148</v>
@@ -14788,7 +14812,7 @@
         <v>964</v>
       </c>
       <c r="G53" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>965</v>
@@ -14891,7 +14915,7 @@
         <v>1150</v>
       </c>
       <c r="AW53" s="1" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="AX53" s="1" t="s">
         <v>1151</v>
@@ -14920,7 +14944,7 @@
         <v>970</v>
       </c>
       <c r="G54" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>971</v>
@@ -15023,7 +15047,7 @@
         <v>1154</v>
       </c>
       <c r="AW54" s="1" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="AX54" s="1" t="s">
         <v>67</v>
@@ -15052,7 +15076,7 @@
         <v>577</v>
       </c>
       <c r="G55" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>976</v>
@@ -15163,7 +15187,7 @@
         <v>1156</v>
       </c>
       <c r="AW55" s="1" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="AX55" s="1" t="s">
         <v>68</v>
@@ -15192,7 +15216,7 @@
         <v>982</v>
       </c>
       <c r="G56" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>983</v>
@@ -15303,7 +15327,7 @@
         <v>351</v>
       </c>
       <c r="AW56" s="1" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="AX56" s="1" t="s">
         <v>69</v>
@@ -15332,7 +15356,7 @@
         <v>504</v>
       </c>
       <c r="G57" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>989</v>
@@ -15437,7 +15461,7 @@
         <v>1161</v>
       </c>
       <c r="AW57" s="1" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="AX57" s="1" t="s">
         <v>70</v>
@@ -15466,7 +15490,7 @@
         <v>994</v>
       </c>
       <c r="G58" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>995</v>
@@ -15575,7 +15599,7 @@
         <v>1163</v>
       </c>
       <c r="AW58" s="1" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="AX58" s="1" t="s">
         <v>1164</v>
@@ -15604,7 +15628,7 @@
         <v>554</v>
       </c>
       <c r="G59" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>999</v>
@@ -15709,7 +15733,7 @@
         <v>452</v>
       </c>
       <c r="AW59" s="1" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="AX59" s="1" t="s">
         <v>1168</v>
@@ -15738,7 +15762,7 @@
         <v>1007</v>
       </c>
       <c r="G60" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>999</v>
@@ -15846,10 +15870,10 @@
         <v>623</v>
       </c>
       <c r="AW60" s="1" t="s">
+        <v>1944</v>
+      </c>
+      <c r="AX60" s="1" t="s">
         <v>1945</v>
-      </c>
-      <c r="AX60" s="1" t="s">
-        <v>1946</v>
       </c>
       <c r="AY60" s="1" t="s">
         <v>431</v>
@@ -15875,7 +15899,7 @@
         <v>1014</v>
       </c>
       <c r="G61" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>999</v>
@@ -15980,7 +16004,7 @@
         <v>1069</v>
       </c>
       <c r="AW61" s="1" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="AX61" s="1" t="s">
         <v>71</v>
@@ -16009,7 +16033,7 @@
         <v>491</v>
       </c>
       <c r="G62" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>954</v>
@@ -16114,10 +16138,10 @@
         <v>1180</v>
       </c>
       <c r="AW62" s="1" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="AX62" s="1" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="AY62" s="1" t="s">
         <v>431</v>
@@ -16143,7 +16167,7 @@
         <v>964</v>
       </c>
       <c r="G63" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>965</v>
@@ -16248,7 +16272,7 @@
         <v>1182</v>
       </c>
       <c r="AW63" s="1" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="AX63" s="1" t="s">
         <v>74</v>
@@ -16277,7 +16301,7 @@
         <v>970</v>
       </c>
       <c r="G64" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>971</v>
@@ -16382,7 +16406,7 @@
         <v>1184</v>
       </c>
       <c r="AW64" s="1" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="AX64" s="1" t="s">
         <v>75</v>
@@ -16411,7 +16435,7 @@
         <v>577</v>
       </c>
       <c r="G65" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>976</v>
@@ -16516,7 +16540,7 @@
         <v>546</v>
       </c>
       <c r="AW65" s="1" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="AX65" s="1" t="s">
         <v>76</v>
@@ -16545,7 +16569,7 @@
         <v>982</v>
       </c>
       <c r="G66" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>983</v>
@@ -16566,7 +16590,7 @@
         <v>1178</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="O66" s="1" t="s">
         <v>320</v>
@@ -16653,7 +16677,7 @@
         <v>1190</v>
       </c>
       <c r="AW66" s="1" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="AX66" s="1" t="s">
         <v>78</v>
@@ -16682,7 +16706,7 @@
         <v>504</v>
       </c>
       <c r="G67" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>989</v>
@@ -16703,7 +16727,7 @@
         <v>1178</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="O67" s="1" t="s">
         <v>320</v>
@@ -16787,7 +16811,7 @@
         <v>455</v>
       </c>
       <c r="AW67" s="1" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="AX67" s="1" t="s">
         <v>79</v>
@@ -16816,7 +16840,7 @@
         <v>994</v>
       </c>
       <c r="G68" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>995</v>
@@ -16837,7 +16861,7 @@
         <v>1178</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="O68" s="1" t="s">
         <v>320</v>
@@ -16921,7 +16945,7 @@
         <v>456</v>
       </c>
       <c r="AW68" s="1" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="AX68" s="1" t="s">
         <v>80</v>
@@ -16950,7 +16974,7 @@
         <v>554</v>
       </c>
       <c r="G69" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>999</v>
@@ -16971,7 +16995,7 @@
         <v>320</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="O69" s="1" t="s">
         <v>320</v>
@@ -17061,10 +17085,10 @@
         <v>320</v>
       </c>
       <c r="AV69" s="1" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="AW69" s="1" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="AX69" s="1" t="s">
         <v>81</v>
@@ -17093,7 +17117,7 @@
         <v>1007</v>
       </c>
       <c r="G70" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>999</v>
@@ -17114,7 +17138,7 @@
         <v>320</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="O70" s="1" t="s">
         <v>320</v>
@@ -17246,7 +17270,7 @@
         <v>1014</v>
       </c>
       <c r="G71" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>999</v>
@@ -17267,7 +17291,7 @@
         <v>320</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="O71" s="1" t="s">
         <v>320</v>
@@ -17348,13 +17372,13 @@
         <v>320</v>
       </c>
       <c r="AV71" s="1" t="s">
+        <v>1946</v>
+      </c>
+      <c r="AW71" s="1" t="s">
+        <v>1949</v>
+      </c>
+      <c r="AX71" s="1" t="s">
         <v>1947</v>
-      </c>
-      <c r="AW71" s="1" t="s">
-        <v>1950</v>
-      </c>
-      <c r="AX71" s="1" t="s">
-        <v>1948</v>
       </c>
       <c r="AY71" s="1" t="s">
         <v>431</v>
@@ -17380,7 +17404,7 @@
         <v>491</v>
       </c>
       <c r="G72" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>954</v>
@@ -17497,7 +17521,7 @@
         <v>1209</v>
       </c>
       <c r="AW72" s="1" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="AX72" s="1" t="s">
         <v>85</v>
@@ -17526,7 +17550,7 @@
         <v>964</v>
       </c>
       <c r="G73" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>965</v>
@@ -17631,7 +17655,7 @@
         <v>1069</v>
       </c>
       <c r="AW73" s="1" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="AX73" s="1" t="s">
         <v>87</v>
@@ -17660,7 +17684,7 @@
         <v>970</v>
       </c>
       <c r="G74" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>971</v>
@@ -17763,7 +17787,7 @@
         <v>1069</v>
       </c>
       <c r="AW74" s="1" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="AX74" s="1" t="s">
         <v>88</v>
@@ -17792,7 +17816,7 @@
         <v>577</v>
       </c>
       <c r="G75" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>976</v>
@@ -17895,7 +17919,7 @@
         <v>1216</v>
       </c>
       <c r="AW75" s="1" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="AX75" s="1" t="s">
         <v>89</v>
@@ -17924,7 +17948,7 @@
         <v>982</v>
       </c>
       <c r="G76" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>983</v>
@@ -18027,7 +18051,7 @@
         <v>1069</v>
       </c>
       <c r="AW76" s="1" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="AX76" s="1" t="s">
         <v>90</v>
@@ -18056,7 +18080,7 @@
         <v>504</v>
       </c>
       <c r="G77" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>989</v>
@@ -18156,10 +18180,10 @@
         <v>320</v>
       </c>
       <c r="AV77" s="1" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="AW77" s="1" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="AX77" s="1" t="s">
         <v>91</v>
@@ -18188,7 +18212,7 @@
         <v>994</v>
       </c>
       <c r="G78" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>995</v>
@@ -18295,13 +18319,13 @@
         <v>320</v>
       </c>
       <c r="AV78" s="1" t="s">
+        <v>1958</v>
+      </c>
+      <c r="AW78" s="1" t="s">
+        <v>1963</v>
+      </c>
+      <c r="AX78" s="1" t="s">
         <v>1959</v>
-      </c>
-      <c r="AW78" s="1" t="s">
-        <v>1964</v>
-      </c>
-      <c r="AX78" s="1" t="s">
-        <v>1960</v>
       </c>
       <c r="AY78" s="1" t="s">
         <v>1210</v>
@@ -18327,7 +18351,7 @@
         <v>554</v>
       </c>
       <c r="G79" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>999</v>
@@ -18436,7 +18460,7 @@
         <v>1225</v>
       </c>
       <c r="AW79" s="1" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="AX79" s="1" t="s">
         <v>92</v>
@@ -18465,7 +18489,7 @@
         <v>1007</v>
       </c>
       <c r="G80" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>999</v>
@@ -18577,10 +18601,10 @@
         <v>320</v>
       </c>
       <c r="AV80" s="1" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="AW80" s="1" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="AX80" s="1" t="s">
         <v>459</v>
@@ -18609,7 +18633,7 @@
         <v>1014</v>
       </c>
       <c r="G81" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>999</v>
@@ -18721,13 +18745,13 @@
         <v>320</v>
       </c>
       <c r="AV81" s="1" t="s">
+        <v>1960</v>
+      </c>
+      <c r="AW81" s="1" t="s">
+        <v>1965</v>
+      </c>
+      <c r="AX81" s="1" t="s">
         <v>1961</v>
-      </c>
-      <c r="AW81" s="1" t="s">
-        <v>1966</v>
-      </c>
-      <c r="AX81" s="1" t="s">
-        <v>1962</v>
       </c>
       <c r="AY81" s="1" t="s">
         <v>1210</v>
@@ -18753,7 +18777,7 @@
         <v>491</v>
       </c>
       <c r="G82" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>954</v>
@@ -18856,7 +18880,7 @@
         <v>1238</v>
       </c>
       <c r="AW82" s="1" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="AX82" s="1" t="s">
         <v>97</v>
@@ -18885,7 +18909,7 @@
         <v>964</v>
       </c>
       <c r="G83" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>965</v>
@@ -18991,7 +19015,7 @@
         <v>1241</v>
       </c>
       <c r="AW83" s="1" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="AX83" s="1" t="s">
         <v>98</v>
@@ -19020,7 +19044,7 @@
         <v>970</v>
       </c>
       <c r="G84" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>971</v>
@@ -19123,7 +19147,7 @@
         <v>1243</v>
       </c>
       <c r="AW84" s="1" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AX84" s="1" t="s">
         <v>99</v>
@@ -19152,7 +19176,7 @@
         <v>577</v>
       </c>
       <c r="G85" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>976</v>
@@ -19255,7 +19279,7 @@
         <v>992</v>
       </c>
       <c r="AW85" s="1" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="AX85" s="1" t="s">
         <v>100</v>
@@ -19284,7 +19308,7 @@
         <v>982</v>
       </c>
       <c r="G86" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>983</v>
@@ -19387,7 +19411,7 @@
         <v>1129</v>
       </c>
       <c r="AW86" s="1" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="AX86" s="1" t="s">
         <v>102</v>
@@ -19416,7 +19440,7 @@
         <v>504</v>
       </c>
       <c r="G87" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>989</v>
@@ -19522,13 +19546,13 @@
         <v>320</v>
       </c>
       <c r="AV87" s="1" t="s">
+        <v>1972</v>
+      </c>
+      <c r="AW87" s="1" t="s">
+        <v>1974</v>
+      </c>
+      <c r="AX87" s="1" t="s">
         <v>1973</v>
-      </c>
-      <c r="AW87" s="1" t="s">
-        <v>1975</v>
-      </c>
-      <c r="AX87" s="1" t="s">
-        <v>1974</v>
       </c>
       <c r="AY87" s="1" t="s">
         <v>431</v>
@@ -19554,7 +19578,7 @@
         <v>994</v>
       </c>
       <c r="G88" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>995</v>
@@ -19657,7 +19681,7 @@
         <v>1253</v>
       </c>
       <c r="AW88" s="1" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="AX88" s="1" t="s">
         <v>104</v>
@@ -19686,7 +19710,7 @@
         <v>554</v>
       </c>
       <c r="G89" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>999</v>
@@ -19789,7 +19813,7 @@
         <v>1257</v>
       </c>
       <c r="AW89" s="1" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="AX89" s="1" t="s">
         <v>105</v>
@@ -19818,7 +19842,7 @@
         <v>1007</v>
       </c>
       <c r="G90" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>999</v>
@@ -19933,7 +19957,7 @@
         <v>603</v>
       </c>
       <c r="AW90" s="1" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="AX90" s="1" t="s">
         <v>107</v>
@@ -19962,7 +19986,7 @@
         <v>1014</v>
       </c>
       <c r="G91" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>999</v>
@@ -20065,7 +20089,7 @@
         <v>602</v>
       </c>
       <c r="AW91" s="1" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="AX91" s="1" t="s">
         <v>108</v>
@@ -20094,7 +20118,7 @@
         <v>491</v>
       </c>
       <c r="G92" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>954</v>
@@ -20200,7 +20224,7 @@
         <v>1268</v>
       </c>
       <c r="AW92" s="1" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="AX92" s="1" t="s">
         <v>112</v>
@@ -20229,7 +20253,7 @@
         <v>964</v>
       </c>
       <c r="G93" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>965</v>
@@ -20332,7 +20356,7 @@
         <v>1119</v>
       </c>
       <c r="AW93" s="1" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="AX93" s="1" t="s">
         <v>113</v>
@@ -20361,7 +20385,7 @@
         <v>970</v>
       </c>
       <c r="G94" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>971</v>
@@ -20461,10 +20485,10 @@
         <v>320</v>
       </c>
       <c r="AV94" s="1" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="AW94" s="1" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="AX94" s="1" t="s">
         <v>114</v>
@@ -20493,7 +20517,7 @@
         <v>577</v>
       </c>
       <c r="G95" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>976</v>
@@ -20599,7 +20623,7 @@
         <v>1273</v>
       </c>
       <c r="AW95" s="1" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="AX95" s="1" t="s">
         <v>115</v>
@@ -20628,7 +20652,7 @@
         <v>982</v>
       </c>
       <c r="G96" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>983</v>
@@ -20743,7 +20767,7 @@
         <v>1225</v>
       </c>
       <c r="AW96" s="1" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="AX96" s="1" t="s">
         <v>116</v>
@@ -20772,7 +20796,7 @@
         <v>504</v>
       </c>
       <c r="G97" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>989</v>
@@ -20875,7 +20899,7 @@
         <v>1277</v>
       </c>
       <c r="AW97" s="1" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="AX97" s="1" t="s">
         <v>117</v>
@@ -20904,7 +20928,7 @@
         <v>994</v>
       </c>
       <c r="G98" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>995</v>
@@ -21010,7 +21034,7 @@
         <v>1279</v>
       </c>
       <c r="AW98" s="1" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="AX98" s="1" t="s">
         <v>119</v>
@@ -21039,7 +21063,7 @@
         <v>554</v>
       </c>
       <c r="G99" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>999</v>
@@ -21151,7 +21175,7 @@
         <v>1283</v>
       </c>
       <c r="AW99" s="1" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="AX99" s="1" t="s">
         <v>473</v>
@@ -21180,7 +21204,7 @@
         <v>1007</v>
       </c>
       <c r="G100" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>999</v>
@@ -21286,10 +21310,10 @@
         <v>320</v>
       </c>
       <c r="AV100" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="AW100" s="1" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="AX100" s="1" t="s">
         <v>121</v>
@@ -21318,7 +21342,7 @@
         <v>1014</v>
       </c>
       <c r="G101" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>999</v>
@@ -21427,7 +21451,7 @@
         <v>472</v>
       </c>
       <c r="AW101" s="1" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="AX101" s="1" t="s">
         <v>1291</v>
@@ -21456,7 +21480,7 @@
         <v>491</v>
       </c>
       <c r="G102" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>954</v>
@@ -21565,7 +21589,7 @@
         <v>1298</v>
       </c>
       <c r="AW102" s="1" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="AX102" s="1" t="s">
         <v>124</v>
@@ -21594,7 +21618,7 @@
         <v>964</v>
       </c>
       <c r="G103" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>965</v>
@@ -21697,7 +21721,7 @@
         <v>1300</v>
       </c>
       <c r="AW103" s="1" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="AX103" s="1" t="s">
         <v>125</v>
@@ -21726,7 +21750,7 @@
         <v>970</v>
       </c>
       <c r="G104" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>971</v>
@@ -21835,7 +21859,7 @@
         <v>1302</v>
       </c>
       <c r="AW104" s="1" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="AX104" s="1" t="s">
         <v>127</v>
@@ -21864,7 +21888,7 @@
         <v>577</v>
       </c>
       <c r="G105" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>976</v>
@@ -21967,7 +21991,7 @@
         <v>1304</v>
       </c>
       <c r="AW105" s="1" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="AX105" s="1" t="s">
         <v>128</v>
@@ -21996,7 +22020,7 @@
         <v>982</v>
       </c>
       <c r="G106" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>983</v>
@@ -22099,7 +22123,7 @@
         <v>1069</v>
       </c>
       <c r="AW106" s="1" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="AX106" s="1" t="s">
         <v>129</v>
@@ -22128,7 +22152,7 @@
         <v>504</v>
       </c>
       <c r="G107" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>989</v>
@@ -22228,10 +22252,10 @@
         <v>320</v>
       </c>
       <c r="AV107" s="1" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="AW107" s="1" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="AX107" s="1" t="s">
         <v>131</v>
@@ -22260,7 +22284,7 @@
         <v>994</v>
       </c>
       <c r="G108" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>995</v>
@@ -22363,10 +22387,10 @@
         <v>1309</v>
       </c>
       <c r="AW108" s="1" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AX108" s="1" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="AY108" s="1" t="s">
         <v>431</v>
@@ -22392,7 +22416,7 @@
         <v>554</v>
       </c>
       <c r="G109" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>999</v>
@@ -22498,7 +22522,7 @@
         <v>320</v>
       </c>
       <c r="AV109" s="1" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="AW109" s="1" t="s">
         <v>132</v>
@@ -22530,7 +22554,7 @@
         <v>1007</v>
       </c>
       <c r="G110" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>999</v>
@@ -22636,13 +22660,13 @@
         <v>1240</v>
       </c>
       <c r="AV110" s="1" t="s">
+        <v>2000</v>
+      </c>
+      <c r="AW110" s="1" t="s">
         <v>2001</v>
       </c>
-      <c r="AW110" s="1" t="s">
+      <c r="AX110" s="1" t="s">
         <v>2002</v>
-      </c>
-      <c r="AX110" s="1" t="s">
-        <v>2003</v>
       </c>
       <c r="AY110" s="1" t="s">
         <v>480</v>
@@ -22668,7 +22692,7 @@
         <v>1014</v>
       </c>
       <c r="G111" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>999</v>
@@ -22783,7 +22807,7 @@
         <v>475</v>
       </c>
       <c r="AW111" s="1" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AX111" s="1" t="s">
         <v>474</v>
@@ -22812,7 +22836,7 @@
         <v>491</v>
       </c>
       <c r="G112" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>954</v>
@@ -22918,10 +22942,10 @@
         <v>320</v>
       </c>
       <c r="AV112" s="1" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="AW112" s="1" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="AX112" s="1" t="s">
         <v>136</v>
@@ -22950,7 +22974,7 @@
         <v>964</v>
       </c>
       <c r="G113" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>965</v>
@@ -23053,7 +23077,7 @@
         <v>1069</v>
       </c>
       <c r="AW113" s="1" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="AX113" s="1" t="s">
         <v>137</v>
@@ -23082,7 +23106,7 @@
         <v>970</v>
       </c>
       <c r="G114" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>971</v>
@@ -23185,7 +23209,7 @@
         <v>1323</v>
       </c>
       <c r="AW114" s="1" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="AX114" s="1" t="s">
         <v>138</v>
@@ -23214,7 +23238,7 @@
         <v>577</v>
       </c>
       <c r="G115" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>976</v>
@@ -23317,10 +23341,10 @@
         <v>1300</v>
       </c>
       <c r="AW115" s="1" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="AX115" s="1" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="AY115" s="1" t="s">
         <v>431</v>
@@ -23346,7 +23370,7 @@
         <v>982</v>
       </c>
       <c r="G116" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>983</v>
@@ -23449,7 +23473,7 @@
         <v>546</v>
       </c>
       <c r="AW116" s="1" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="AX116" s="1" t="s">
         <v>139</v>
@@ -23478,7 +23502,7 @@
         <v>504</v>
       </c>
       <c r="G117" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>989</v>
@@ -23584,10 +23608,10 @@
         <v>320</v>
       </c>
       <c r="AV117" s="1" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="AW117" s="1" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="AX117" s="1" t="s">
         <v>140</v>
@@ -23616,7 +23640,7 @@
         <v>994</v>
       </c>
       <c r="G118" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>995</v>
@@ -23719,7 +23743,7 @@
         <v>1328</v>
       </c>
       <c r="AW118" s="1" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="AX118" s="1" t="s">
         <v>142</v>
@@ -23748,7 +23772,7 @@
         <v>554</v>
       </c>
       <c r="G119" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>999</v>
@@ -23869,7 +23893,7 @@
         <v>612</v>
       </c>
       <c r="AW119" s="1" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="AX119" s="1" t="s">
         <v>1333</v>
@@ -23898,7 +23922,7 @@
         <v>1007</v>
       </c>
       <c r="G120" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>999</v>
@@ -23998,10 +24022,10 @@
         <v>320</v>
       </c>
       <c r="AV120" s="1" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="AW120" s="1" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="AX120" s="1" t="s">
         <v>143</v>
@@ -24030,7 +24054,7 @@
         <v>1014</v>
       </c>
       <c r="G121" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>999</v>
@@ -24136,13 +24160,13 @@
         <v>1342</v>
       </c>
       <c r="AV121" s="1" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="AW121" s="1" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="AX121" s="1" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="AY121" s="1" t="s">
         <v>431</v>
@@ -24168,7 +24192,7 @@
         <v>491</v>
       </c>
       <c r="G122" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>954</v>
@@ -24271,13 +24295,13 @@
         <v>1347</v>
       </c>
       <c r="AV122" s="1" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="AW122" s="1" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="AX122" s="1" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="AY122" s="1" t="s">
         <v>431</v>
@@ -24303,7 +24327,7 @@
         <v>964</v>
       </c>
       <c r="G123" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>965</v>
@@ -24406,10 +24430,10 @@
         <v>1300</v>
       </c>
       <c r="AW123" s="1" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="AX123" s="1" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="AY123" s="1" t="s">
         <v>431</v>
@@ -24435,7 +24459,7 @@
         <v>970</v>
       </c>
       <c r="G124" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>971</v>
@@ -24541,7 +24565,7 @@
         <v>1352</v>
       </c>
       <c r="AW124" s="1" t="s">
-        <v>146</v>
+        <v>2023</v>
       </c>
       <c r="AX124" s="1" t="s">
         <v>146</v>
@@ -24570,7 +24594,7 @@
         <v>577</v>
       </c>
       <c r="G125" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>976</v>
@@ -24702,7 +24726,7 @@
         <v>982</v>
       </c>
       <c r="G126" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>983</v>
@@ -24805,7 +24829,7 @@
         <v>1355</v>
       </c>
       <c r="AW126" s="1" t="s">
-        <v>148</v>
+        <v>2024</v>
       </c>
       <c r="AX126" s="1" t="s">
         <v>148</v>
@@ -24834,7 +24858,7 @@
         <v>504</v>
       </c>
       <c r="G127" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>989</v>
@@ -24940,7 +24964,7 @@
         <v>2022</v>
       </c>
       <c r="AX127" s="1" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="AY127" s="1" t="s">
         <v>431</v>
@@ -24966,7 +24990,7 @@
         <v>994</v>
       </c>
       <c r="G128" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>995</v>
@@ -25072,7 +25096,7 @@
         <v>1361</v>
       </c>
       <c r="AW128" s="1" t="s">
-        <v>149</v>
+        <v>2025</v>
       </c>
       <c r="AX128" s="1" t="s">
         <v>149</v>
@@ -25101,7 +25125,7 @@
         <v>554</v>
       </c>
       <c r="G129" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>999</v>
@@ -25207,7 +25231,7 @@
         <v>1365</v>
       </c>
       <c r="AW129" s="1" t="s">
-        <v>150</v>
+        <v>2026</v>
       </c>
       <c r="AX129" s="1" t="s">
         <v>150</v>
@@ -25236,7 +25260,7 @@
         <v>1007</v>
       </c>
       <c r="G130" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>999</v>
@@ -25339,7 +25363,7 @@
         <v>490</v>
       </c>
       <c r="AR130" s="1" t="s">
-        <v>2026</v>
+        <v>2032</v>
       </c>
       <c r="AT130" s="1" t="s">
         <v>320</v>
@@ -25348,16 +25372,16 @@
         <v>320</v>
       </c>
       <c r="AV130" s="1" t="s">
-        <v>2023</v>
+        <v>2029</v>
       </c>
       <c r="AW130" s="1" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="AX130" s="1" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="AY130" s="1" t="s">
-        <v>2025</v>
+        <v>2031</v>
       </c>
       <c r="AZ130" s="3" t="s">
         <v>1310</v>
@@ -25380,7 +25404,7 @@
         <v>1014</v>
       </c>
       <c r="G131" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>999</v>
@@ -25480,10 +25504,10 @@
         <v>320</v>
       </c>
       <c r="AV131" s="1" t="s">
-        <v>1370</v>
+        <v>2027</v>
       </c>
       <c r="AW131" s="1" t="s">
-        <v>151</v>
+        <v>2028</v>
       </c>
       <c r="AX131" s="1" t="s">
         <v>151</v>
@@ -25503,16 +25527,16 @@
         <v>153</v>
       </c>
       <c r="C132" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>491</v>
       </c>
       <c r="G132" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>954</v>
@@ -25612,7 +25636,7 @@
         <v>320</v>
       </c>
       <c r="AV132" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="AW132" s="1" t="s">
         <v>154</v>
@@ -25624,7 +25648,7 @@
         <v>431</v>
       </c>
       <c r="AZ132" s="3" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="133" spans="1:52" x14ac:dyDescent="0.3">
@@ -25632,19 +25656,19 @@
         <v>152</v>
       </c>
       <c r="B133" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>1375</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>964</v>
       </c>
       <c r="G133" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>965</v>
@@ -25764,19 +25788,19 @@
         <v>152</v>
       </c>
       <c r="B134" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>1376</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>970</v>
       </c>
       <c r="G134" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>971</v>
@@ -25896,19 +25920,19 @@
         <v>152</v>
       </c>
       <c r="B135" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>1377</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>577</v>
       </c>
       <c r="G135" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>976</v>
@@ -26028,19 +26052,19 @@
         <v>152</v>
       </c>
       <c r="B136" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>1378</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>982</v>
       </c>
       <c r="G136" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>983</v>
@@ -26146,7 +26170,7 @@
         <v>547</v>
       </c>
       <c r="AX136" s="1" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="AY136" s="1" t="s">
         <v>431</v>
@@ -26160,19 +26184,19 @@
         <v>152</v>
       </c>
       <c r="B137" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>1380</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>504</v>
       </c>
       <c r="G137" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>989</v>
@@ -26257,22 +26281,22 @@
         <v>320</v>
       </c>
       <c r="AJ137" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="AK137" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AL137" s="1" t="s">
         <v>1381</v>
       </c>
-      <c r="AK137" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AL137" s="1" t="s">
+      <c r="AM137" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AU137" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AV137" s="1" t="s">
         <v>1382</v>
-      </c>
-      <c r="AM137" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AU137" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AV137" s="1" t="s">
-        <v>1383</v>
       </c>
       <c r="AW137" s="1" t="s">
         <v>158</v>
@@ -26292,19 +26316,19 @@
         <v>152</v>
       </c>
       <c r="B138" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>1384</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>994</v>
       </c>
       <c r="G138" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H138" s="1" t="s">
         <v>995</v>
@@ -26389,13 +26413,13 @@
         <v>320</v>
       </c>
       <c r="AJ138" s="1" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="AK138" s="1" t="s">
         <v>320</v>
       </c>
       <c r="AL138" s="1" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="AM138" s="1" t="s">
         <v>320</v>
@@ -26416,13 +26440,13 @@
         <v>493</v>
       </c>
       <c r="AX138" s="1" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="AY138" s="1" t="s">
         <v>431</v>
       </c>
       <c r="AZ138" s="3" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="139" spans="1:52" x14ac:dyDescent="0.3">
@@ -26442,7 +26466,7 @@
         <v>554</v>
       </c>
       <c r="G139" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>999</v>
@@ -26451,7 +26475,7 @@
         <v>955</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="K139" s="1" t="s">
         <v>320</v>
@@ -26548,7 +26572,7 @@
         <v>625</v>
       </c>
       <c r="AX139" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="AY139" s="1" t="s">
         <v>431</v>
@@ -26565,7 +26589,7 @@
         <v>320</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>320</v>
@@ -26574,7 +26598,7 @@
         <v>1007</v>
       </c>
       <c r="G140" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>999</v>
@@ -26583,7 +26607,7 @@
         <v>955</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="K140" s="1" t="s">
         <v>320</v>
@@ -26659,7 +26683,7 @@
         <v>320</v>
       </c>
       <c r="AJ140" s="1" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="AK140" s="1" t="s">
         <v>320</v>
@@ -26697,7 +26721,7 @@
         <v>320</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>320</v>
@@ -26706,7 +26730,7 @@
         <v>1014</v>
       </c>
       <c r="G141" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>999</v>
@@ -26715,7 +26739,7 @@
         <v>955</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="K141" s="1" t="s">
         <v>320</v>
@@ -26806,7 +26830,7 @@
         <v>320</v>
       </c>
       <c r="AV141" s="1" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="AW141" s="1" t="s">
         <v>160</v>
@@ -26818,7 +26842,7 @@
         <v>431</v>
       </c>
       <c r="AZ141" s="3" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="142" spans="1:52" x14ac:dyDescent="0.3">
@@ -26829,16 +26853,16 @@
         <v>162</v>
       </c>
       <c r="C142" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>1397</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>491</v>
       </c>
       <c r="G142" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>954</v>
@@ -26927,7 +26951,7 @@
         <v>495</v>
       </c>
       <c r="AL142" s="1" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="AM142" s="1" t="s">
         <v>320</v>
@@ -26948,7 +26972,7 @@
         <v>431</v>
       </c>
       <c r="AZ142" s="3" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="143" spans="1:52" x14ac:dyDescent="0.3">
@@ -26956,19 +26980,19 @@
         <v>161</v>
       </c>
       <c r="B143" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>1400</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>1397</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>964</v>
       </c>
       <c r="G143" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>965</v>
@@ -27080,7 +27104,7 @@
         <v>431</v>
       </c>
       <c r="AZ143" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="144" spans="1:52" x14ac:dyDescent="0.3">
@@ -27088,19 +27112,19 @@
         <v>161</v>
       </c>
       <c r="B144" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E144" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>1402</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>1397</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>970</v>
       </c>
       <c r="G144" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H144" s="1" t="s">
         <v>971</v>
@@ -27212,7 +27236,7 @@
         <v>431</v>
       </c>
       <c r="AZ144" s="3" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="145" spans="1:52" x14ac:dyDescent="0.3">
@@ -27220,19 +27244,19 @@
         <v>161</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>618</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>577</v>
       </c>
       <c r="G145" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H145" s="1" t="s">
         <v>976</v>
@@ -27352,19 +27376,19 @@
         <v>161</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>619</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>982</v>
       </c>
       <c r="G146" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>983</v>
@@ -27455,7 +27479,7 @@
         <v>320</v>
       </c>
       <c r="AL146" s="1" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="AM146" s="1" t="s">
         <v>320</v>
@@ -27464,7 +27488,7 @@
         <v>320</v>
       </c>
       <c r="AV146" s="1" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="AW146" s="1" t="s">
         <v>169</v>
@@ -27484,19 +27508,19 @@
         <v>161</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>617</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>504</v>
       </c>
       <c r="G147" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H147" s="1" t="s">
         <v>989</v>
@@ -27590,7 +27614,7 @@
         <v>320</v>
       </c>
       <c r="AM147" s="1" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="AU147" s="1" t="s">
         <v>320</v>
@@ -27616,19 +27640,19 @@
         <v>161</v>
       </c>
       <c r="B148" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>1405</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>1397</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>994</v>
       </c>
       <c r="G148" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H148" s="1" t="s">
         <v>995</v>
@@ -27760,7 +27784,7 @@
         <v>554</v>
       </c>
       <c r="G149" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="H149" s="1" t="s">
         <v>999</v>
@@ -27769,7 +27793,7 @@
         <v>955</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="K149" s="1" t="s">
         <v>320</v>
@@ -27848,7 +27872,7 @@
         <v>496</v>
       </c>
       <c r="AL149" s="1" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="AM149" s="1" t="s">
         <v>320</v>
@@ -27880,7 +27904,7 @@
         <v>320</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>320</v>
@@ -27889,7 +27913,7 @@
         <v>1007</v>
       </c>
       <c r="G150" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="H150" s="1" t="s">
         <v>999</v>
@@ -27898,7 +27922,7 @@
         <v>955</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="K150" s="1" t="s">
         <v>320</v>
@@ -27989,7 +28013,7 @@
         <v>320</v>
       </c>
       <c r="AP150" s="1" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="AQ150" s="1" t="s">
         <v>164</v>
@@ -28004,7 +28028,7 @@
         <v>320</v>
       </c>
       <c r="AV150" s="1" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="AW150" s="1" t="s">
         <v>173</v>
@@ -28013,10 +28037,10 @@
         <v>173</v>
       </c>
       <c r="AY150" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="AZ150" s="3" t="s">
         <v>1412</v>
-      </c>
-      <c r="AZ150" s="3" t="s">
-        <v>1413</v>
       </c>
     </row>
     <row r="151" spans="1:52" x14ac:dyDescent="0.3">
@@ -28027,7 +28051,7 @@
         <v>320</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>320</v>
@@ -28036,7 +28060,7 @@
         <v>1014</v>
       </c>
       <c r="G151" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="H151" s="1" t="s">
         <v>999</v>
@@ -28045,7 +28069,7 @@
         <v>955</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="K151" s="1" t="s">
         <v>320</v>
@@ -28148,13 +28172,13 @@
         <v>503</v>
       </c>
       <c r="AX151" s="1" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="AY151" s="1" t="s">
         <v>502</v>
       </c>
       <c r="AZ151" s="3" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="152" spans="1:52" x14ac:dyDescent="0.3">
@@ -28165,16 +28189,16 @@
         <v>175</v>
       </c>
       <c r="C152" s="3" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>491</v>
       </c>
       <c r="G152" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>954</v>
@@ -28259,22 +28283,22 @@
         <v>320</v>
       </c>
       <c r="AJ152" s="1" t="s">
+        <v>1419</v>
+      </c>
+      <c r="AK152" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AL152" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AM152" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AU152" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AV152" s="1" t="s">
         <v>1420</v>
-      </c>
-      <c r="AK152" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AL152" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AM152" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AU152" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AV152" s="1" t="s">
-        <v>1421</v>
       </c>
       <c r="AW152" s="1" t="s">
         <v>176</v>
@@ -28294,19 +28318,19 @@
         <v>174</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>1422</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>964</v>
       </c>
       <c r="G153" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H153" s="1" t="s">
         <v>965</v>
@@ -28426,19 +28450,19 @@
         <v>174</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="C154" s="3" t="s">
-        <v>1423</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>970</v>
       </c>
       <c r="G154" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>971</v>
@@ -28550,7 +28574,7 @@
         <v>431</v>
       </c>
       <c r="AZ154" s="3" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="155" spans="1:52" x14ac:dyDescent="0.3">
@@ -28558,19 +28582,19 @@
         <v>174</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>1425</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>577</v>
       </c>
       <c r="G155" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H155" s="1" t="s">
         <v>976</v>
@@ -28690,19 +28714,19 @@
         <v>174</v>
       </c>
       <c r="B156" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E156" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>1426</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>982</v>
       </c>
       <c r="G156" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H156" s="1" t="s">
         <v>983</v>
@@ -28805,7 +28829,7 @@
         <v>1032</v>
       </c>
       <c r="AV156" s="1" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="AW156" s="1" t="s">
         <v>180</v>
@@ -28825,19 +28849,19 @@
         <v>174</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>1428</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>504</v>
       </c>
       <c r="G157" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H157" s="1" t="s">
         <v>989</v>
@@ -28937,7 +28961,7 @@
         <v>320</v>
       </c>
       <c r="AV157" s="1" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="AW157" s="1" t="s">
         <v>181</v>
@@ -28957,19 +28981,19 @@
         <v>174</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>1430</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>994</v>
       </c>
       <c r="G158" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H158" s="1" t="s">
         <v>995</v>
@@ -29060,16 +29084,16 @@
         <v>320</v>
       </c>
       <c r="AL158" s="1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="AM158" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AU158" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AV158" s="1" t="s">
         <v>1431</v>
-      </c>
-      <c r="AM158" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AU158" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AV158" s="1" t="s">
-        <v>1432</v>
       </c>
       <c r="AW158" s="1" t="s">
         <v>182</v>
@@ -29081,7 +29105,7 @@
         <v>431</v>
       </c>
       <c r="AZ158" s="3" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="159" spans="1:52" x14ac:dyDescent="0.3">
@@ -29092,7 +29116,7 @@
         <v>320</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>320</v>
@@ -29101,7 +29125,7 @@
         <v>554</v>
       </c>
       <c r="G159" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>999</v>
@@ -29110,7 +29134,7 @@
         <v>955</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="K159" s="1" t="s">
         <v>320</v>
@@ -29186,22 +29210,22 @@
         <v>320</v>
       </c>
       <c r="AJ159" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="AK159" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AL159" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AM159" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="AK159" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AL159" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AM159" s="1" t="s">
+      <c r="AU159" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AV159" s="1" t="s">
         <v>1437</v>
-      </c>
-      <c r="AU159" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AV159" s="1" t="s">
-        <v>1438</v>
       </c>
       <c r="AW159" s="1" t="s">
         <v>183</v>
@@ -29224,7 +29248,7 @@
         <v>320</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>320</v>
@@ -29233,7 +29257,7 @@
         <v>1007</v>
       </c>
       <c r="G160" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="H160" s="1" t="s">
         <v>999</v>
@@ -29242,7 +29266,7 @@
         <v>955</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="K160" s="1" t="s">
         <v>320</v>
@@ -29327,7 +29351,7 @@
         <v>320</v>
       </c>
       <c r="AO160" s="1" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="AP160" s="1" t="s">
         <v>320</v>
@@ -29345,13 +29369,13 @@
         <v>507</v>
       </c>
       <c r="AX160" s="1" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="AY160" s="1" t="s">
         <v>506</v>
       </c>
       <c r="AZ160" s="3" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="161" spans="1:52" x14ac:dyDescent="0.3">
@@ -29362,7 +29386,7 @@
         <v>320</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>320</v>
@@ -29371,7 +29395,7 @@
         <v>1014</v>
       </c>
       <c r="G161" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="H161" s="1" t="s">
         <v>999</v>
@@ -29380,7 +29404,7 @@
         <v>955</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="K161" s="1" t="s">
         <v>320</v>
@@ -29443,7 +29467,7 @@
         <v>320</v>
       </c>
       <c r="AE161" s="1" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="AF161" s="1" t="s">
         <v>320</v>
@@ -29494,16 +29518,16 @@
         <v>187</v>
       </c>
       <c r="C162" s="3" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>1447</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>1448</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>491</v>
       </c>
       <c r="G162" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H162" s="1" t="s">
         <v>954</v>
@@ -29542,7 +29566,7 @@
         <v>320</v>
       </c>
       <c r="T162" s="1" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="U162" s="1" t="s">
         <v>320</v>
@@ -29604,7 +29628,7 @@
         <v>320</v>
       </c>
       <c r="AV162" s="1" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="AW162" s="1" t="s">
         <v>189</v>
@@ -29616,7 +29640,7 @@
         <v>431</v>
       </c>
       <c r="AZ162" s="3" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="163" spans="1:52" x14ac:dyDescent="0.3">
@@ -29624,19 +29648,19 @@
         <v>186</v>
       </c>
       <c r="B163" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>1447</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>1452</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>1448</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>964</v>
       </c>
       <c r="G163" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H163" s="1" t="s">
         <v>965</v>
@@ -29748,7 +29772,7 @@
         <v>431</v>
       </c>
       <c r="AZ163" s="3" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="164" spans="1:52" x14ac:dyDescent="0.3">
@@ -29756,19 +29780,19 @@
         <v>186</v>
       </c>
       <c r="B164" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>1447</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>1454</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>1448</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>970</v>
       </c>
       <c r="G164" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>971</v>
@@ -29888,19 +29912,19 @@
         <v>186</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>1447</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>1455</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>1448</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>577</v>
       </c>
       <c r="G165" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>976</v>
@@ -30004,7 +30028,7 @@
         <v>320</v>
       </c>
       <c r="AV165" s="1" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="AW165" s="1" t="s">
         <v>193</v>
@@ -30016,7 +30040,7 @@
         <v>431</v>
       </c>
       <c r="AZ165" s="3" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="166" spans="1:52" x14ac:dyDescent="0.3">
@@ -30024,19 +30048,19 @@
         <v>186</v>
       </c>
       <c r="B166" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>1447</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>1458</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>1448</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>982</v>
       </c>
       <c r="G166" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>983</v>
@@ -30156,19 +30180,19 @@
         <v>186</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E167" s="1" t="s">
         <v>1447</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>1459</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>1448</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>504</v>
       </c>
       <c r="G167" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H167" s="1" t="s">
         <v>989</v>
@@ -30269,7 +30293,7 @@
         <v>320</v>
       </c>
       <c r="AV167" s="1" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="AW167" s="1" t="s">
         <v>195</v>
@@ -30289,19 +30313,19 @@
         <v>186</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E168" s="1" t="s">
         <v>1447</v>
-      </c>
-      <c r="C168" s="3" t="s">
-        <v>1461</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>1448</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>994</v>
       </c>
       <c r="G168" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H168" s="1" t="s">
         <v>995</v>
@@ -30396,10 +30420,10 @@
         <v>320</v>
       </c>
       <c r="AP168" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="AQ168" s="1" t="s">
         <v>1462</v>
-      </c>
-      <c r="AQ168" s="1" t="s">
-        <v>1463</v>
       </c>
       <c r="AR168" s="1" t="s">
         <v>196</v>
@@ -30411,7 +30435,7 @@
         <v>1032</v>
       </c>
       <c r="AV168" s="1" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="AW168" s="1" t="s">
         <v>197</v>
@@ -30420,7 +30444,7 @@
         <v>197</v>
       </c>
       <c r="AY168" s="1" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="AZ168" s="3" t="s">
         <v>1159</v>
@@ -30443,7 +30467,7 @@
         <v>554</v>
       </c>
       <c r="G169" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="H169" s="1" t="s">
         <v>999</v>
@@ -30452,7 +30476,7 @@
         <v>955</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="K169" s="1" t="s">
         <v>320</v>
@@ -30552,13 +30576,13 @@
         <v>520</v>
       </c>
       <c r="AX169" s="1" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="AY169" s="1" t="s">
         <v>431</v>
       </c>
       <c r="AZ169" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="170" spans="1:52" x14ac:dyDescent="0.3">
@@ -30578,7 +30602,7 @@
         <v>1007</v>
       </c>
       <c r="G170" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="H170" s="1" t="s">
         <v>999</v>
@@ -30587,7 +30611,7 @@
         <v>955</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="K170" s="1" t="s">
         <v>320</v>
@@ -30696,10 +30720,10 @@
         <v>508</v>
       </c>
       <c r="AY170" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="AZ170" s="3" t="s">
         <v>1470</v>
-      </c>
-      <c r="AZ170" s="3" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="171" spans="1:52" x14ac:dyDescent="0.3">
@@ -30710,7 +30734,7 @@
         <v>320</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>320</v>
@@ -30719,7 +30743,7 @@
         <v>1014</v>
       </c>
       <c r="G171" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>999</v>
@@ -30728,7 +30752,7 @@
         <v>955</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="K171" s="1" t="s">
         <v>320</v>
@@ -30819,7 +30843,7 @@
         <v>320</v>
       </c>
       <c r="AV171" s="1" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="AW171" s="1" t="s">
         <v>198</v>
@@ -30831,7 +30855,7 @@
         <v>431</v>
       </c>
       <c r="AZ171" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="172" spans="1:52" x14ac:dyDescent="0.3">
@@ -30842,16 +30866,16 @@
         <v>200</v>
       </c>
       <c r="C172" s="3" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E172" s="1" t="s">
         <v>1476</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>1477</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>491</v>
       </c>
       <c r="G172" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H172" s="1" t="s">
         <v>954</v>
@@ -30929,7 +30953,7 @@
         <v>467</v>
       </c>
       <c r="AG172" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="AH172" s="1"/>
       <c r="AI172" s="1" t="s">
@@ -30939,19 +30963,19 @@
         <v>320</v>
       </c>
       <c r="AK172" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="AL172" s="1" t="s">
         <v>1479</v>
       </c>
-      <c r="AL172" s="1" t="s">
+      <c r="AM172" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="AU172" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AV172" s="1" t="s">
         <v>1480</v>
-      </c>
-      <c r="AM172" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="AU172" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AV172" s="1" t="s">
-        <v>1481</v>
       </c>
       <c r="AW172" s="1" t="s">
         <v>203</v>
@@ -30963,7 +30987,7 @@
         <v>431</v>
       </c>
       <c r="AZ172" s="3" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="173" spans="1:52" x14ac:dyDescent="0.3">
@@ -30971,19 +30995,19 @@
         <v>199</v>
       </c>
       <c r="B173" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E173" s="1" t="s">
         <v>1476</v>
-      </c>
-      <c r="C173" s="3" t="s">
-        <v>1483</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>1477</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>964</v>
       </c>
       <c r="G173" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H173" s="1" t="s">
         <v>965</v>
@@ -31083,10 +31107,10 @@
         <v>320</v>
       </c>
       <c r="AU173" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="AV173" s="1" t="s">
         <v>1484</v>
-      </c>
-      <c r="AV173" s="1" t="s">
-        <v>1485</v>
       </c>
       <c r="AW173" s="1" t="s">
         <v>205</v>
@@ -31098,7 +31122,7 @@
         <v>431</v>
       </c>
       <c r="AZ173" s="3" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="174" spans="1:52" x14ac:dyDescent="0.3">
@@ -31106,19 +31130,19 @@
         <v>199</v>
       </c>
       <c r="B174" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E174" s="1" t="s">
         <v>1476</v>
-      </c>
-      <c r="C174" s="3" t="s">
-        <v>1486</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>1477</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>970</v>
       </c>
       <c r="G174" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H174" s="1" t="s">
         <v>971</v>
@@ -31238,19 +31262,19 @@
         <v>199</v>
       </c>
       <c r="B175" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E175" s="1" t="s">
         <v>1476</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>1487</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>1477</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>577</v>
       </c>
       <c r="G175" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H175" s="1" t="s">
         <v>976</v>
@@ -31295,7 +31319,7 @@
         <v>320</v>
       </c>
       <c r="V175" s="1" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="W175" s="1" t="s">
         <v>320</v>
@@ -31338,10 +31362,10 @@
         <v>320</v>
       </c>
       <c r="AK175" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="AL175" s="1" t="s">
         <v>1479</v>
-      </c>
-      <c r="AL175" s="1" t="s">
-        <v>1480</v>
       </c>
       <c r="AM175" s="1" t="s">
         <v>320</v>
@@ -31370,19 +31394,19 @@
         <v>199</v>
       </c>
       <c r="B176" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E176" s="1" t="s">
         <v>1476</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>1489</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>1477</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>982</v>
       </c>
       <c r="G176" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H176" s="1" t="s">
         <v>983</v>
@@ -31502,19 +31526,19 @@
         <v>199</v>
       </c>
       <c r="B177" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E177" s="1" t="s">
         <v>1476</v>
-      </c>
-      <c r="C177" s="3" t="s">
-        <v>1490</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>1477</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>504</v>
       </c>
       <c r="G177" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H177" s="1" t="s">
         <v>989</v>
@@ -31614,7 +31638,7 @@
         <v>320</v>
       </c>
       <c r="AV177" s="1" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="AW177" s="1" t="s">
         <v>209</v>
@@ -31634,19 +31658,19 @@
         <v>199</v>
       </c>
       <c r="B178" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>1476</v>
-      </c>
-      <c r="C178" s="3" t="s">
-        <v>1492</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>1477</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>994</v>
       </c>
       <c r="G178" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H178" s="1" t="s">
         <v>995</v>
@@ -31685,40 +31709,40 @@
         <v>320</v>
       </c>
       <c r="T178" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="U178" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="V178" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="W178" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="X178" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="Y178" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="Z178" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AA178" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="AB178" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="AC178" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="AD178" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="AE178" s="1" t="s">
         <v>1493</v>
-      </c>
-      <c r="U178" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="V178" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="W178" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="X178" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="Y178" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="Z178" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AA178" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="AB178" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="AC178" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="AD178" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="AE178" s="1" t="s">
-        <v>1494</v>
       </c>
       <c r="AF178" s="1" t="s">
         <v>320</v>
@@ -31762,7 +31786,7 @@
         <v>513</v>
       </c>
       <c r="AZ178" s="3" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="179" spans="1:52" x14ac:dyDescent="0.3">
@@ -31773,7 +31797,7 @@
         <v>320</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>320</v>
@@ -31782,7 +31806,7 @@
         <v>554</v>
       </c>
       <c r="G179" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="H179" s="1" t="s">
         <v>999</v>
@@ -31791,7 +31815,7 @@
         <v>955</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="K179" s="1" t="s">
         <v>320</v>
@@ -31888,7 +31912,7 @@
         <v>541</v>
       </c>
       <c r="AX179" s="1" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="AY179" s="1" t="s">
         <v>431</v>
@@ -31905,7 +31929,7 @@
         <v>320</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>320</v>
@@ -31914,7 +31938,7 @@
         <v>1007</v>
       </c>
       <c r="G180" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="H180" s="1" t="s">
         <v>999</v>
@@ -31923,7 +31947,7 @@
         <v>955</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="K180" s="1" t="s">
         <v>320</v>
@@ -32020,7 +32044,7 @@
         <v>540</v>
       </c>
       <c r="AX180" s="1" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="AY180" s="1" t="s">
         <v>431</v>
@@ -32037,7 +32061,7 @@
         <v>320</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>320</v>
@@ -32046,7 +32070,7 @@
         <v>1014</v>
       </c>
       <c r="G181" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="H181" s="1" t="s">
         <v>999</v>
@@ -32055,7 +32079,7 @@
         <v>955</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="K181" s="1" t="s">
         <v>320</v>
@@ -32146,7 +32170,7 @@
         <v>320</v>
       </c>
       <c r="AP181" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="AQ181" s="1" t="s">
         <v>202</v>
@@ -32161,13 +32185,13 @@
         <v>536</v>
       </c>
       <c r="AX181" s="1" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="AY181" s="1" t="s">
         <v>535</v>
       </c>
       <c r="AZ181" s="3" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="182" spans="1:52" x14ac:dyDescent="0.3">
@@ -32178,16 +32202,16 @@
         <v>213</v>
       </c>
       <c r="C182" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>491</v>
       </c>
       <c r="G182" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H182" s="1" t="s">
         <v>954</v>
@@ -32263,7 +32287,7 @@
         <v>320</v>
       </c>
       <c r="AG182" s="1" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="AH182" s="1"/>
       <c r="AI182" s="1" t="s">
@@ -32273,31 +32297,31 @@
         <v>320</v>
       </c>
       <c r="AK182" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="AL182" s="1" t="s">
         <v>1509</v>
       </c>
-      <c r="AL182" s="1" t="s">
+      <c r="AM182" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="AU182" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AV182" s="1" t="s">
         <v>1510</v>
-      </c>
-      <c r="AM182" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="AU182" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AV182" s="1" t="s">
-        <v>1511</v>
       </c>
       <c r="AW182" s="1" t="s">
         <v>545</v>
       </c>
       <c r="AX182" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="AY182" s="1" t="s">
         <v>431</v>
       </c>
       <c r="AZ182" s="3" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="183" spans="1:52" x14ac:dyDescent="0.3">
@@ -32305,19 +32329,19 @@
         <v>212</v>
       </c>
       <c r="B183" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="C183" s="3" t="s">
-        <v>1514</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>964</v>
       </c>
       <c r="G183" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H183" s="1" t="s">
         <v>965</v>
@@ -32417,10 +32441,10 @@
         <v>320</v>
       </c>
       <c r="AU183" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="AV183" s="1" t="s">
         <v>1515</v>
-      </c>
-      <c r="AV183" s="1" t="s">
-        <v>1516</v>
       </c>
       <c r="AW183" s="1" t="s">
         <v>214</v>
@@ -32440,19 +32464,19 @@
         <v>212</v>
       </c>
       <c r="B184" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E184" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="C184" s="3" t="s">
-        <v>1517</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>970</v>
       </c>
       <c r="G184" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H184" s="1" t="s">
         <v>971</v>
@@ -32552,10 +32576,10 @@
         <v>320</v>
       </c>
       <c r="AU184" s="1" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="AV184" s="1" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="AW184" s="1" t="s">
         <v>215</v>
@@ -32575,19 +32599,19 @@
         <v>212</v>
       </c>
       <c r="B185" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E185" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="C185" s="3" t="s">
-        <v>1519</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>577</v>
       </c>
       <c r="G185" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H185" s="1" t="s">
         <v>976</v>
@@ -32675,11 +32699,11 @@
         <v>320</v>
       </c>
       <c r="AK185" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="AL185" s="1" t="s">
         <v>1509</v>
       </c>
-      <c r="AL185" s="1" t="s">
-        <v>1510</v>
-      </c>
       <c r="AM185" s="1" t="s">
         <v>320</v>
       </c>
@@ -32687,7 +32711,7 @@
         <v>320</v>
       </c>
       <c r="AV185" s="1" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="AW185" s="1" t="s">
         <v>216</v>
@@ -32699,7 +32723,7 @@
         <v>537</v>
       </c>
       <c r="AZ185" s="3" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="186" spans="1:52" x14ac:dyDescent="0.3">
@@ -32707,19 +32731,19 @@
         <v>212</v>
       </c>
       <c r="B186" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>1520</v>
+      </c>
+      <c r="E186" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="C186" s="3" t="s">
-        <v>1521</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>982</v>
       </c>
       <c r="G186" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H186" s="1" t="s">
         <v>983</v>
@@ -32819,7 +32843,7 @@
         <v>320</v>
       </c>
       <c r="AP186" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="AQ186" s="1" t="s">
         <v>210</v>
@@ -32848,19 +32872,19 @@
         <v>212</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E187" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="C187" s="3" t="s">
-        <v>1523</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>504</v>
       </c>
       <c r="G187" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H187" s="1" t="s">
         <v>989</v>
@@ -32980,19 +33004,19 @@
         <v>212</v>
       </c>
       <c r="B188" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E188" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="C188" s="3" t="s">
-        <v>1524</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>994</v>
       </c>
       <c r="G188" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H188" s="1" t="s">
         <v>995</v>
@@ -33052,7 +33076,7 @@
         <v>320</v>
       </c>
       <c r="AA188" s="3" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="AB188" s="3" t="s">
         <v>320</v>
@@ -33110,7 +33134,7 @@
         <v>515</v>
       </c>
       <c r="AZ188" s="3" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="189" spans="1:52" x14ac:dyDescent="0.3">
@@ -33121,7 +33145,7 @@
         <v>320</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>320</v>
@@ -33130,7 +33154,7 @@
         <v>554</v>
       </c>
       <c r="G189" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H189" s="1" t="s">
         <v>999</v>
@@ -33139,7 +33163,7 @@
         <v>955</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="K189" s="1" t="s">
         <v>320</v>
@@ -33230,10 +33254,10 @@
         <v>320</v>
       </c>
       <c r="AT189" s="1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="AU189" s="1" t="s">
         <v>1529</v>
-      </c>
-      <c r="AU189" s="1" t="s">
-        <v>1530</v>
       </c>
       <c r="AV189" s="1" t="s">
         <v>543</v>
@@ -33242,7 +33266,7 @@
         <v>544</v>
       </c>
       <c r="AX189" s="1" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="AY189" s="1" t="s">
         <v>431</v>
@@ -33268,7 +33292,7 @@
         <v>1007</v>
       </c>
       <c r="G190" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="H190" s="1" t="s">
         <v>999</v>
@@ -33277,7 +33301,7 @@
         <v>955</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="K190" s="1" t="s">
         <v>320</v>
@@ -33371,7 +33395,7 @@
         <v>552</v>
       </c>
       <c r="AS190" s="1" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="AU190" s="1" t="s">
         <v>320</v>
@@ -33383,13 +33407,13 @@
         <v>551</v>
       </c>
       <c r="AX190" s="1" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="AY190" s="1" t="s">
         <v>553</v>
       </c>
       <c r="AZ190" s="3" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="191" spans="1:52" x14ac:dyDescent="0.3">
@@ -33400,7 +33424,7 @@
         <v>320</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>320</v>
@@ -33409,7 +33433,7 @@
         <v>1014</v>
       </c>
       <c r="G191" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="H191" s="1" t="s">
         <v>999</v>
@@ -33418,7 +33442,7 @@
         <v>955</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="K191" s="1" t="s">
         <v>320</v>
@@ -33527,13 +33551,13 @@
         <v>550</v>
       </c>
       <c r="AX191" s="1" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="AY191" s="1" t="s">
         <v>516</v>
       </c>
       <c r="AZ191" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="192" spans="1:52" x14ac:dyDescent="0.3">
@@ -33544,16 +33568,16 @@
         <v>222</v>
       </c>
       <c r="C192" s="3" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E192" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>491</v>
       </c>
       <c r="G192" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H192" s="1" t="s">
         <v>954</v>
@@ -33638,25 +33662,25 @@
         <v>320</v>
       </c>
       <c r="AJ192" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="AK192" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AL192" s="1" t="s">
         <v>1542</v>
       </c>
-      <c r="AK192" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AL192" s="1" t="s">
+      <c r="AM192" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AT192" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AU192" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="AV192" s="1" t="s">
         <v>1543</v>
-      </c>
-      <c r="AM192" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AT192" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AU192" s="1" t="s">
-        <v>1484</v>
-      </c>
-      <c r="AV192" s="1" t="s">
-        <v>1544</v>
       </c>
       <c r="AW192" s="1" t="s">
         <v>223</v>
@@ -33676,19 +33700,19 @@
         <v>221</v>
       </c>
       <c r="B193" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E193" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="C193" s="3" t="s">
-        <v>1545</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>964</v>
       </c>
       <c r="G193" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H193" s="1" t="s">
         <v>965</v>
@@ -33712,13 +33736,13 @@
         <v>966</v>
       </c>
       <c r="O193" s="3" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="P193" s="3" t="s">
         <v>320</v>
       </c>
       <c r="Q193" s="3" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="R193" s="3" t="s">
         <v>320</v>
@@ -33808,19 +33832,19 @@
         <v>221</v>
       </c>
       <c r="B194" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="E194" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="C194" s="3" t="s">
-        <v>1547</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>970</v>
       </c>
       <c r="G194" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H194" s="1" t="s">
         <v>971</v>
@@ -33911,7 +33935,7 @@
         <v>320</v>
       </c>
       <c r="AL194" s="1" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="AM194" s="1" t="s">
         <v>320</v>
@@ -33926,7 +33950,7 @@
         <v>320</v>
       </c>
       <c r="AV194" s="1" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="AW194" s="1" t="s">
         <v>225</v>
@@ -33946,19 +33970,19 @@
         <v>221</v>
       </c>
       <c r="B195" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E195" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="C195" s="3" t="s">
-        <v>1549</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>577</v>
       </c>
       <c r="G195" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H195" s="1" t="s">
         <v>976</v>
@@ -34043,22 +34067,22 @@
         <v>320</v>
       </c>
       <c r="AJ195" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="AK195" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AL195" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="AM195" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AU195" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AV195" s="1" t="s">
         <v>1550</v>
-      </c>
-      <c r="AK195" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AL195" s="1" t="s">
-        <v>1543</v>
-      </c>
-      <c r="AM195" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AU195" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AV195" s="1" t="s">
-        <v>1551</v>
       </c>
       <c r="AW195" s="1" t="s">
         <v>226</v>
@@ -34078,19 +34102,19 @@
         <v>221</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>1551</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="C196" s="3" t="s">
-        <v>1552</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>982</v>
       </c>
       <c r="G196" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H196" s="1" t="s">
         <v>983</v>
@@ -34202,7 +34226,7 @@
         <v>431</v>
       </c>
       <c r="AZ196" s="3" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="197" spans="1:52" x14ac:dyDescent="0.3">
@@ -34210,19 +34234,19 @@
         <v>221</v>
       </c>
       <c r="B197" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="C197" s="3" t="s">
-        <v>1554</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>504</v>
       </c>
       <c r="G197" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H197" s="1" t="s">
         <v>989</v>
@@ -34322,7 +34346,7 @@
         <v>320</v>
       </c>
       <c r="AV197" s="1" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="AW197" s="1" t="s">
         <v>228</v>
@@ -34342,19 +34366,19 @@
         <v>221</v>
       </c>
       <c r="B198" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="C198" s="3" t="s">
-        <v>1556</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>994</v>
       </c>
       <c r="G198" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H198" s="1" t="s">
         <v>995</v>
@@ -34384,49 +34408,49 @@
         <v>320</v>
       </c>
       <c r="Q198" s="1" t="s">
+        <v>1556</v>
+      </c>
+      <c r="R198" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="S198" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="T198" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="U198" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="V198" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="W198" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="X198" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="Y198" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="Z198" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AA198" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="AB198" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="AC198" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="AD198" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="AE198" s="1" t="s">
         <v>1557</v>
-      </c>
-      <c r="R198" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="S198" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="T198" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="U198" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="V198" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="W198" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="X198" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="Y198" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="Z198" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AA198" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="AB198" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="AC198" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="AD198" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="AE198" s="1" t="s">
-        <v>1558</v>
       </c>
       <c r="AF198" s="1" t="s">
         <v>320</v>
@@ -34460,7 +34484,7 @@
         <v>320</v>
       </c>
       <c r="AV198" s="1" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="AW198" s="1" t="s">
         <v>231</v>
@@ -34483,7 +34507,7 @@
         <v>320</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>320</v>
@@ -34492,7 +34516,7 @@
         <v>554</v>
       </c>
       <c r="G199" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H199" s="1" t="s">
         <v>999</v>
@@ -34501,7 +34525,7 @@
         <v>955</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="K199" s="1" t="s">
         <v>320</v>
@@ -34615,7 +34639,7 @@
         <v>320</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>320</v>
@@ -34624,7 +34648,7 @@
         <v>1007</v>
       </c>
       <c r="G200" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H200" s="1" t="s">
         <v>999</v>
@@ -34633,7 +34657,7 @@
         <v>955</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K200" s="1" t="s">
         <v>320</v>
@@ -34734,7 +34758,7 @@
         <v>558</v>
       </c>
       <c r="AX200" s="1" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="AY200" s="1" t="s">
         <v>557</v>
@@ -34751,7 +34775,7 @@
         <v>320</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>320</v>
@@ -34760,7 +34784,7 @@
         <v>1014</v>
       </c>
       <c r="G201" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="H201" s="1" t="s">
         <v>999</v>
@@ -34769,7 +34793,7 @@
         <v>955</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="K201" s="1" t="s">
         <v>320</v>
@@ -34860,13 +34884,13 @@
         <v>320</v>
       </c>
       <c r="AR201" s="1" t="s">
+        <v>1566</v>
+      </c>
+      <c r="AU201" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AV201" s="1" t="s">
         <v>1567</v>
-      </c>
-      <c r="AU201" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AV201" s="1" t="s">
-        <v>1568</v>
       </c>
       <c r="AW201" s="1" t="s">
         <v>233</v>
@@ -34878,7 +34902,7 @@
         <v>518</v>
       </c>
       <c r="AZ201" s="3" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="202" spans="1:52" x14ac:dyDescent="0.3">
@@ -34889,16 +34913,16 @@
         <v>235</v>
       </c>
       <c r="C202" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E202" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>491</v>
       </c>
       <c r="G202" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H202" s="1" t="s">
         <v>954</v>
@@ -34937,7 +34961,7 @@
         <v>320</v>
       </c>
       <c r="T202" s="1" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="U202" s="1" t="s">
         <v>320</v>
@@ -34986,7 +35010,7 @@
         <v>320</v>
       </c>
       <c r="AK202" s="1" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="AL202" s="1" t="s">
         <v>563</v>
@@ -34998,7 +35022,7 @@
         <v>320</v>
       </c>
       <c r="AV202" s="1" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="AW202" s="1" t="s">
         <v>238</v>
@@ -35010,7 +35034,7 @@
         <v>431</v>
       </c>
       <c r="AZ202" s="3" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="203" spans="1:52" x14ac:dyDescent="0.3">
@@ -35018,19 +35042,19 @@
         <v>234</v>
       </c>
       <c r="B203" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E203" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="C203" s="3" t="s">
-        <v>1575</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>964</v>
       </c>
       <c r="G203" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H203" s="1" t="s">
         <v>965</v>
@@ -35130,7 +35154,7 @@
         <v>320</v>
       </c>
       <c r="AV203" s="1" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="AW203" s="1" t="s">
         <v>239</v>
@@ -35150,19 +35174,19 @@
         <v>234</v>
       </c>
       <c r="B204" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E204" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="C204" s="3" t="s">
-        <v>1577</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>970</v>
       </c>
       <c r="G204" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H204" s="1" t="s">
         <v>971</v>
@@ -35262,7 +35286,7 @@
         <v>320</v>
       </c>
       <c r="AV204" s="1" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="AW204" s="1" t="s">
         <v>240</v>
@@ -35282,19 +35306,19 @@
         <v>234</v>
       </c>
       <c r="B205" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="C205" s="3" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>577</v>
       </c>
       <c r="G205" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H205" s="1" t="s">
         <v>976</v>
@@ -35333,7 +35357,7 @@
         <v>320</v>
       </c>
       <c r="T205" s="1" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="U205" s="1" t="s">
         <v>320</v>
@@ -35394,7 +35418,7 @@
         <v>320</v>
       </c>
       <c r="AP205" s="1" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="AQ205" s="1" t="s">
         <v>237</v>
@@ -35423,19 +35447,19 @@
         <v>234</v>
       </c>
       <c r="B206" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E206" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="C206" s="3" t="s">
-        <v>1581</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>982</v>
       </c>
       <c r="G206" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H206" s="1" t="s">
         <v>983</v>
@@ -35507,7 +35531,7 @@
         <v>320</v>
       </c>
       <c r="AE206" s="1" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="AF206" s="1" t="s">
         <v>320</v>
@@ -35544,7 +35568,7 @@
         <v>320</v>
       </c>
       <c r="AV206" s="1" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="AW206" s="1" t="s">
         <v>243</v>
@@ -35564,19 +35588,19 @@
         <v>234</v>
       </c>
       <c r="B207" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E207" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="C207" s="3" t="s">
-        <v>1583</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>504</v>
       </c>
       <c r="G207" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H207" s="1" t="s">
         <v>989</v>
@@ -35648,7 +35672,7 @@
         <v>320</v>
       </c>
       <c r="AE207" s="1" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="AF207" s="1" t="s">
         <v>320</v>
@@ -35688,10 +35712,10 @@
         <v>320</v>
       </c>
       <c r="AU207" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="AV207" s="1" t="s">
         <v>1585</v>
-      </c>
-      <c r="AV207" s="1" t="s">
-        <v>1586</v>
       </c>
       <c r="AW207" s="1" t="s">
         <v>245</v>
@@ -35711,19 +35735,19 @@
         <v>234</v>
       </c>
       <c r="B208" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="C208" s="3" t="s">
-        <v>1587</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>994</v>
       </c>
       <c r="G208" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="H208" s="1" t="s">
         <v>995</v>
@@ -35823,7 +35847,7 @@
         <v>320</v>
       </c>
       <c r="AV208" s="1" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="AW208" s="1" t="s">
         <v>246</v>
@@ -35846,7 +35870,7 @@
         <v>320</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>320</v>
@@ -35855,7 +35879,7 @@
         <v>554</v>
       </c>
       <c r="G209" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="H209" s="1" t="s">
         <v>999</v>
@@ -35864,7 +35888,7 @@
         <v>955</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="K209" s="1" t="s">
         <v>320</v>
@@ -35970,7 +35994,7 @@
         <v>566</v>
       </c>
       <c r="AX209" s="1" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="AY209" s="1" t="s">
         <v>524</v>
@@ -35987,7 +36011,7 @@
         <v>320</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>320</v>
@@ -35996,7 +36020,7 @@
         <v>1007</v>
       </c>
       <c r="G210" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H210" s="1" t="s">
         <v>999</v>
@@ -36005,7 +36029,7 @@
         <v>955</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="K210" s="1" t="s">
         <v>320</v>
@@ -36105,7 +36129,7 @@
         <v>563</v>
       </c>
       <c r="AR210" s="1" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="AU210" s="1" t="s">
         <v>320</v>
@@ -36117,7 +36141,7 @@
         <v>630</v>
       </c>
       <c r="AX210" s="1" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="AY210" s="1" t="s">
         <v>569</v>
@@ -36134,7 +36158,7 @@
         <v>320</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>320</v>
@@ -36143,7 +36167,7 @@
         <v>1014</v>
       </c>
       <c r="G211" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H211" s="1" t="s">
         <v>999</v>
@@ -36152,7 +36176,7 @@
         <v>955</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="K211" s="1" t="s">
         <v>320</v>
@@ -36252,7 +36276,7 @@
         <v>320</v>
       </c>
       <c r="AV211" s="1" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="AW211" s="1" t="s">
         <v>562</v>
@@ -36264,7 +36288,7 @@
         <v>564</v>
       </c>
       <c r="AZ211" s="3" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="212" spans="1:52" x14ac:dyDescent="0.3">
@@ -36275,16 +36299,16 @@
         <v>249</v>
       </c>
       <c r="C212" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>1599</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>1600</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>491</v>
       </c>
       <c r="G212" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H212" s="1" t="s">
         <v>954</v>
@@ -36369,7 +36393,7 @@
         <v>320</v>
       </c>
       <c r="AJ212" s="1" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="AK212" s="1" t="s">
         <v>320</v>
@@ -36404,19 +36428,19 @@
         <v>248</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="E213" s="1" t="s">
         <v>1599</v>
-      </c>
-      <c r="C213" s="3" t="s">
-        <v>1602</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>1600</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>964</v>
       </c>
       <c r="G213" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H213" s="1" t="s">
         <v>965</v>
@@ -36522,7 +36546,7 @@
         <v>320</v>
       </c>
       <c r="AV213" s="1" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="AW213" s="1" t="s">
         <v>252</v>
@@ -36542,19 +36566,19 @@
         <v>248</v>
       </c>
       <c r="B214" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E214" s="1" t="s">
         <v>1599</v>
-      </c>
-      <c r="C214" s="3" t="s">
-        <v>1604</v>
-      </c>
-      <c r="E214" s="1" t="s">
-        <v>1600</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>970</v>
       </c>
       <c r="G214" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H214" s="1" t="s">
         <v>971</v>
@@ -36654,10 +36678,10 @@
         <v>320</v>
       </c>
       <c r="AU214" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="AV214" s="1" t="s">
         <v>1605</v>
-      </c>
-      <c r="AV214" s="1" t="s">
-        <v>1606</v>
       </c>
       <c r="AW214" s="1" t="s">
         <v>253</v>
@@ -36669,7 +36693,7 @@
         <v>431</v>
       </c>
       <c r="AZ214" s="3" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="215" spans="1:52" x14ac:dyDescent="0.3">
@@ -36677,19 +36701,19 @@
         <v>248</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="C215" s="3" t="s">
         <v>591</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>577</v>
       </c>
       <c r="G215" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H215" s="1" t="s">
         <v>976</v>
@@ -36809,19 +36833,19 @@
         <v>248</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>571</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>982</v>
       </c>
       <c r="G216" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H216" s="1" t="s">
         <v>983</v>
@@ -36921,7 +36945,7 @@
         <v>320</v>
       </c>
       <c r="AV216" s="1" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="AW216" s="1" t="s">
         <v>256</v>
@@ -36941,19 +36965,19 @@
         <v>248</v>
       </c>
       <c r="B217" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E217" s="1" t="s">
         <v>1599</v>
-      </c>
-      <c r="C217" s="3" t="s">
-        <v>1609</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>1600</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>504</v>
       </c>
       <c r="G217" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="H217" s="1" t="s">
         <v>989</v>
@@ -37053,7 +37077,7 @@
         <v>320</v>
       </c>
       <c r="AV217" s="1" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AW217" s="1" t="s">
         <v>257</v>
@@ -37073,19 +37097,19 @@
         <v>248</v>
       </c>
       <c r="B218" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="E218" s="1" t="s">
         <v>1599</v>
-      </c>
-      <c r="C218" s="3" t="s">
-        <v>1611</v>
-      </c>
-      <c r="E218" s="1" t="s">
-        <v>1600</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>994</v>
       </c>
       <c r="G218" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H218" s="1" t="s">
         <v>995</v>
@@ -37185,7 +37209,7 @@
         <v>320</v>
       </c>
       <c r="AO218" s="1" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="AP218" s="1" t="s">
         <v>572</v>
@@ -37206,7 +37230,7 @@
         <v>320</v>
       </c>
       <c r="AV218" s="1" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="AW218" s="1" t="s">
         <v>260</v>
@@ -37229,7 +37253,7 @@
         <v>320</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>320</v>
@@ -37238,7 +37262,7 @@
         <v>554</v>
       </c>
       <c r="G219" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H219" s="1" t="s">
         <v>999</v>
@@ -37247,7 +37271,7 @@
         <v>955</v>
       </c>
       <c r="J219" s="1" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="K219" s="1" t="s">
         <v>320</v>
@@ -37353,7 +37377,7 @@
         <v>576</v>
       </c>
       <c r="AX219" s="1" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="AY219" s="1" t="s">
         <v>574</v>
@@ -37370,7 +37394,7 @@
         <v>320</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>320</v>
@@ -37379,7 +37403,7 @@
         <v>1007</v>
       </c>
       <c r="G220" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="H220" s="1" t="s">
         <v>999</v>
@@ -37388,7 +37412,7 @@
         <v>955</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="K220" s="1" t="s">
         <v>320</v>
@@ -37491,7 +37515,7 @@
         <v>431</v>
       </c>
       <c r="AZ220" s="3" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="221" spans="1:52" x14ac:dyDescent="0.3">
@@ -37502,7 +37526,7 @@
         <v>320</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>320</v>
@@ -37511,7 +37535,7 @@
         <v>1014</v>
       </c>
       <c r="G221" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H221" s="1" t="s">
         <v>999</v>
@@ -37520,7 +37544,7 @@
         <v>955</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="K221" s="1" t="s">
         <v>320</v>
@@ -37634,16 +37658,16 @@
         <v>264</v>
       </c>
       <c r="C222" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="E222" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>491</v>
       </c>
       <c r="G222" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H222" s="1" t="s">
         <v>954</v>
@@ -37749,7 +37773,7 @@
         <v>320</v>
       </c>
       <c r="AV222" s="1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="AW222" s="1" t="s">
         <v>265</v>
@@ -37761,7 +37785,7 @@
         <v>431</v>
       </c>
       <c r="AZ222" s="3" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="223" spans="1:52" x14ac:dyDescent="0.3">
@@ -37769,19 +37793,19 @@
         <v>263</v>
       </c>
       <c r="B223" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="E223" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C223" s="3" t="s">
-        <v>1625</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>964</v>
       </c>
       <c r="G223" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H223" s="1" t="s">
         <v>965</v>
@@ -37902,7 +37926,7 @@
         <v>527</v>
       </c>
       <c r="AZ223" s="3" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="224" spans="1:52" x14ac:dyDescent="0.3">
@@ -37910,19 +37934,19 @@
         <v>263</v>
       </c>
       <c r="B224" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="E224" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>1626</v>
-      </c>
-      <c r="E224" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>970</v>
       </c>
       <c r="G224" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H224" s="1" t="s">
         <v>971</v>
@@ -38028,10 +38052,10 @@
         <v>320</v>
       </c>
       <c r="AU224" s="1" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="AV224" s="1" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="AW224" s="1" t="s">
         <v>268</v>
@@ -38051,19 +38075,19 @@
         <v>263</v>
       </c>
       <c r="B225" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E225" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C225" s="3" t="s">
-        <v>1628</v>
-      </c>
-      <c r="E225" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>577</v>
       </c>
       <c r="G225" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H225" s="1" t="s">
         <v>976</v>
@@ -38163,7 +38187,7 @@
         <v>320</v>
       </c>
       <c r="AP225" s="1" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="AQ225" s="1" t="s">
         <v>237</v>
@@ -38172,7 +38196,7 @@
         <v>320</v>
       </c>
       <c r="AV225" s="1" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="AW225" s="1" t="s">
         <v>269</v>
@@ -38184,7 +38208,7 @@
         <v>529</v>
       </c>
       <c r="AZ225" s="3" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="226" spans="1:52" x14ac:dyDescent="0.3">
@@ -38192,19 +38216,19 @@
         <v>263</v>
       </c>
       <c r="B226" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E226" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>1631</v>
-      </c>
-      <c r="E226" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>982</v>
       </c>
       <c r="G226" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="H226" s="1" t="s">
         <v>983</v>
@@ -38304,7 +38328,7 @@
         <v>320</v>
       </c>
       <c r="AP226" s="1" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="AQ226" s="1" t="s">
         <v>237</v>
@@ -38313,7 +38337,7 @@
         <v>320</v>
       </c>
       <c r="AV226" s="1" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="AW226" s="1" t="s">
         <v>270</v>
@@ -38333,19 +38357,19 @@
         <v>263</v>
       </c>
       <c r="B227" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E227" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C227" s="3" t="s">
-        <v>1632</v>
-      </c>
-      <c r="E227" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>504</v>
       </c>
       <c r="G227" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H227" s="1" t="s">
         <v>989</v>
@@ -38445,7 +38469,7 @@
         <v>320</v>
       </c>
       <c r="AV227" s="1" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="AW227" s="1" t="s">
         <v>271</v>
@@ -38465,19 +38489,19 @@
         <v>263</v>
       </c>
       <c r="B228" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E228" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>1634</v>
-      </c>
-      <c r="E228" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>994</v>
       </c>
       <c r="G228" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="H228" s="1" t="s">
         <v>995</v>
@@ -38583,7 +38607,7 @@
         <v>320</v>
       </c>
       <c r="AV228" s="1" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="AW228" s="1" t="s">
         <v>272</v>
@@ -38606,7 +38630,7 @@
         <v>320</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>320</v>
@@ -38615,7 +38639,7 @@
         <v>554</v>
       </c>
       <c r="G229" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="H229" s="1" t="s">
         <v>999</v>
@@ -38624,7 +38648,7 @@
         <v>955</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="K229" s="1" t="s">
         <v>320</v>
@@ -38715,7 +38739,7 @@
         <v>320</v>
       </c>
       <c r="AV229" s="1" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="AW229" s="1" t="s">
         <v>273</v>
@@ -38738,7 +38762,7 @@
         <v>320</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>320</v>
@@ -38747,7 +38771,7 @@
         <v>1007</v>
       </c>
       <c r="G230" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H230" s="1" t="s">
         <v>999</v>
@@ -38756,7 +38780,7 @@
         <v>955</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="K230" s="1" t="s">
         <v>320</v>
@@ -38847,7 +38871,7 @@
         <v>320</v>
       </c>
       <c r="AO230" s="1" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="AP230" s="1" t="s">
         <v>634</v>
@@ -38862,7 +38886,7 @@
         <v>320</v>
       </c>
       <c r="AV230" s="1" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="AW230" s="1" t="s">
         <v>274</v>
@@ -38874,7 +38898,7 @@
         <v>531</v>
       </c>
       <c r="AZ230" s="3" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="231" spans="1:52" x14ac:dyDescent="0.3">
@@ -38885,7 +38909,7 @@
         <v>320</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>320</v>
@@ -38894,7 +38918,7 @@
         <v>1014</v>
       </c>
       <c r="G231" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="H231" s="1" t="s">
         <v>999</v>
@@ -38903,7 +38927,7 @@
         <v>955</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="K231" s="1" t="s">
         <v>320</v>
@@ -38994,7 +39018,7 @@
         <v>320</v>
       </c>
       <c r="AO231" s="1" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="AP231" s="1" t="s">
         <v>572</v>
@@ -39021,7 +39045,7 @@
         <v>532</v>
       </c>
       <c r="AZ231" s="3" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="232" spans="1:52" x14ac:dyDescent="0.3">
@@ -39032,13 +39056,13 @@
         <v>637</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>319</v>
@@ -39050,7 +39074,7 @@
         <v>1235</v>
       </c>
       <c r="L232" s="1" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="M232" s="1" t="s">
         <v>638</v>
@@ -39071,16 +39095,16 @@
         <v>320</v>
       </c>
       <c r="AN232" s="1" t="s">
+        <v>1879</v>
+      </c>
+      <c r="AU232" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AV232" s="1" t="s">
         <v>1880</v>
       </c>
-      <c r="AU232" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AV232" s="1" t="s">
+      <c r="AW232" s="1" t="s">
         <v>1881</v>
-      </c>
-      <c r="AW232" s="1" t="s">
-        <v>1882</v>
       </c>
       <c r="AY232" s="1" t="s">
         <v>320</v>
@@ -39094,13 +39118,13 @@
         <v>642</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>319</v>
@@ -39112,7 +39136,7 @@
         <v>1235</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="M233" s="1" t="s">
         <v>643</v>
@@ -39127,10 +39151,10 @@
         <v>320</v>
       </c>
       <c r="AL233" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="AM233" s="1" t="s">
         <v>1648</v>
-      </c>
-      <c r="AM233" s="1" t="s">
-        <v>1649</v>
       </c>
       <c r="AN233" s="1" t="s">
         <v>646</v>
@@ -39145,10 +39169,10 @@
         <v>320</v>
       </c>
       <c r="AV233" s="1" t="s">
+        <v>1763</v>
+      </c>
+      <c r="AW233" s="1" t="s">
         <v>1764</v>
-      </c>
-      <c r="AW233" s="1" t="s">
-        <v>1765</v>
       </c>
       <c r="AY233" s="1" t="s">
         <v>320</v>
@@ -39162,10 +39186,10 @@
         <v>648</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>1267</v>
@@ -39192,10 +39216,10 @@
         <v>320</v>
       </c>
       <c r="AL234" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="AM234" s="1" t="s">
         <v>1650</v>
-      </c>
-      <c r="AM234" s="1" t="s">
-        <v>1651</v>
       </c>
       <c r="AN234" s="1" t="s">
         <v>650</v>
@@ -39204,7 +39228,7 @@
         <v>320</v>
       </c>
       <c r="AV234" s="1" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="AW234" s="1" t="s">
         <v>651</v>
@@ -39221,13 +39245,13 @@
         <v>653</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>319</v>
@@ -39239,7 +39263,7 @@
         <v>1235</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="M235" s="1" t="s">
         <v>638</v>
@@ -39266,7 +39290,7 @@
         <v>320</v>
       </c>
       <c r="AV235" s="1" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="AW235" s="1" t="s">
         <v>657</v>
@@ -39283,13 +39307,13 @@
         <v>659</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>319</v>
@@ -39307,7 +39331,7 @@
         <v>320</v>
       </c>
       <c r="AK236" s="1" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="AL236" s="1" t="s">
         <v>660</v>
@@ -39316,10 +39340,10 @@
         <v>320</v>
       </c>
       <c r="AV236" s="1" t="s">
+        <v>1882</v>
+      </c>
+      <c r="AW236" s="1" t="s">
         <v>1883</v>
-      </c>
-      <c r="AW236" s="1" t="s">
-        <v>1884</v>
       </c>
       <c r="AY236" s="1" t="s">
         <v>320</v>
@@ -39333,13 +39357,13 @@
         <v>662</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>319</v>
@@ -39351,7 +39375,7 @@
         <v>1235</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="M237" s="1" t="s">
         <v>643</v>
@@ -39360,10 +39384,10 @@
         <v>320</v>
       </c>
       <c r="AL237" s="1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="AM237" s="1" t="s">
         <v>1657</v>
-      </c>
-      <c r="AM237" s="1" t="s">
-        <v>1658</v>
       </c>
       <c r="AN237" s="1" t="s">
         <v>663</v>
@@ -39372,10 +39396,10 @@
         <v>320</v>
       </c>
       <c r="AV237" s="1" t="s">
+        <v>1884</v>
+      </c>
+      <c r="AW237" s="1" t="s">
         <v>1885</v>
-      </c>
-      <c r="AW237" s="1" t="s">
-        <v>1886</v>
       </c>
       <c r="AY237" s="1" t="s">
         <v>320</v>
@@ -39389,13 +39413,13 @@
         <v>665</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>319</v>
@@ -39407,7 +39431,7 @@
         <v>1235</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="M238" s="1" t="s">
         <v>638</v>
@@ -39422,7 +39446,7 @@
         <v>320</v>
       </c>
       <c r="AL238" s="1" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="AM238" s="1" t="s">
         <v>667</v>
@@ -39448,13 +39472,13 @@
         <v>671</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>319</v>
@@ -39466,7 +39490,7 @@
         <v>1235</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="M239" s="1" t="s">
         <v>672</v>
@@ -39510,13 +39534,13 @@
         <v>679</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>319</v>
@@ -39528,7 +39552,7 @@
         <v>1235</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="M240" s="1" t="s">
         <v>680</v>
@@ -39537,13 +39561,13 @@
         <v>320</v>
       </c>
       <c r="AJ240" s="1" t="s">
+        <v>1661</v>
+      </c>
+      <c r="AK240" s="1" t="s">
         <v>1662</v>
       </c>
-      <c r="AK240" s="1" t="s">
-        <v>1663</v>
-      </c>
       <c r="AL240" s="1" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="AM240" s="1" t="s">
         <v>681</v>
@@ -39552,7 +39576,7 @@
         <v>320</v>
       </c>
       <c r="AV240" s="1" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="AW240" s="1" t="s">
         <v>682</v>
@@ -39569,13 +39593,13 @@
         <v>684</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>319</v>
@@ -39602,19 +39626,19 @@
         <v>320</v>
       </c>
       <c r="AM241" s="1" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="AN241" s="1" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="AU241" s="1" t="s">
         <v>320</v>
       </c>
       <c r="AV241" s="1" t="s">
+        <v>1890</v>
+      </c>
+      <c r="AW241" s="1" t="s">
         <v>1891</v>
-      </c>
-      <c r="AW241" s="1" t="s">
-        <v>1892</v>
       </c>
       <c r="AY241" s="1" t="s">
         <v>320</v>
@@ -39628,13 +39652,13 @@
         <v>689</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>319</v>
@@ -39646,7 +39670,7 @@
         <v>1235</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="M242" s="1" t="s">
         <v>690</v>
@@ -39670,10 +39694,10 @@
         <v>320</v>
       </c>
       <c r="AV242" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AW242" s="1" t="s">
         <v>1769</v>
-      </c>
-      <c r="AW242" s="1" t="s">
-        <v>1770</v>
       </c>
       <c r="AY242" s="1" t="s">
         <v>320</v>
@@ -39687,10 +39711,10 @@
         <v>694</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>1177</v>
@@ -39717,7 +39741,7 @@
         <v>320</v>
       </c>
       <c r="AT243" s="1" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="AU243" s="1" t="s">
         <v>320</v>
@@ -39740,13 +39764,13 @@
         <v>700</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>319</v>
@@ -39772,13 +39796,13 @@
         <v>704</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>319</v>
@@ -39790,16 +39814,16 @@
         <v>320</v>
       </c>
       <c r="AT245" s="1" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="AU245" s="1" t="s">
         <v>320</v>
       </c>
       <c r="AV245" s="1" t="s">
+        <v>1877</v>
+      </c>
+      <c r="AW245" s="1" t="s">
         <v>1878</v>
-      </c>
-      <c r="AW245" s="1" t="s">
-        <v>1879</v>
       </c>
       <c r="AY245" s="1" t="s">
         <v>320</v>
@@ -39813,13 +39837,13 @@
         <v>706</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>319</v>
@@ -39834,7 +39858,7 @@
         <v>320</v>
       </c>
       <c r="AI246" s="1" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="AJ246" s="1" t="s">
         <v>708</v>
@@ -39860,13 +39884,13 @@
         <v>712</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>319</v>
@@ -39878,7 +39902,7 @@
         <v>1235</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="M247" s="1" t="s">
         <v>713</v>
@@ -39899,7 +39923,7 @@
         <v>320</v>
       </c>
       <c r="AV247" s="1" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="AW247" s="1" t="s">
         <v>715</v>
@@ -39916,13 +39940,13 @@
         <v>717</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>319</v>
@@ -39934,7 +39958,7 @@
         <v>1235</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="M248" s="1" t="s">
         <v>686</v>
@@ -39949,7 +39973,7 @@
         <v>320</v>
       </c>
       <c r="AL248" s="1" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="AM248" s="1" t="s">
         <v>719</v>
@@ -39981,10 +40005,10 @@
         <v>724</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>1294</v>
@@ -39999,7 +40023,7 @@
         <v>1235</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="M249" s="1" t="s">
         <v>725</v>
@@ -40008,7 +40032,7 @@
         <v>320</v>
       </c>
       <c r="AJ249" s="1" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="AK249" s="1" t="s">
         <v>726</v>
@@ -40040,10 +40064,10 @@
         <v>731</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>1267</v>
@@ -40058,7 +40082,7 @@
         <v>1235</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="M250" s="1" t="s">
         <v>732</v>
@@ -40096,13 +40120,13 @@
         <v>222</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>319</v>
@@ -40114,7 +40138,7 @@
         <v>1235</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="M251" s="1" t="s">
         <v>738</v>
@@ -40152,13 +40176,13 @@
         <v>744</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>319</v>
@@ -40170,7 +40194,7 @@
         <v>1235</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="M252" s="1" t="s">
         <v>745</v>
@@ -40214,13 +40238,13 @@
         <v>752</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>319</v>
@@ -40232,7 +40256,7 @@
         <v>1235</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="M253" s="1" t="s">
         <v>753</v>
@@ -40270,13 +40294,13 @@
         <v>758</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>319</v>
@@ -40326,13 +40350,13 @@
         <v>229</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>319</v>
@@ -40344,7 +40368,7 @@
         <v>1235</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="M255" s="1" t="s">
         <v>763</v>
@@ -40353,7 +40377,7 @@
         <v>320</v>
       </c>
       <c r="AM255" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="AN255" s="1" t="s">
         <v>764</v>
@@ -40379,13 +40403,13 @@
         <v>768</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>319</v>
@@ -40397,7 +40421,7 @@
         <v>1235</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="M256" s="1" t="s">
         <v>745</v>
@@ -40406,7 +40430,7 @@
         <v>320</v>
       </c>
       <c r="AM256" s="1" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="AN256" s="1" t="s">
         <v>769</v>
@@ -40432,13 +40456,13 @@
         <v>773</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>319</v>
@@ -40450,7 +40474,7 @@
         <v>1235</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="M257" s="1" t="s">
         <v>774</v>
@@ -40482,13 +40506,13 @@
         <v>779</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>319</v>
@@ -40500,7 +40524,7 @@
         <v>1235</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="M258" s="1" t="s">
         <v>763</v>
@@ -40532,13 +40556,13 @@
         <v>784</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>319</v>
@@ -40550,7 +40574,7 @@
         <v>1235</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="M259" s="1" t="s">
         <v>753</v>
@@ -40559,7 +40583,7 @@
         <v>320</v>
       </c>
       <c r="AM259" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="AN259" s="1" t="s">
         <v>785</v>
@@ -40585,13 +40609,13 @@
         <v>789</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>319</v>
@@ -40603,7 +40627,7 @@
         <v>1235</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="M260" s="1" t="s">
         <v>790</v>
@@ -40612,7 +40636,7 @@
         <v>320</v>
       </c>
       <c r="AM260" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="AN260" s="1" t="s">
         <v>791</v>
@@ -40638,13 +40662,13 @@
         <v>795</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>319</v>
@@ -40656,7 +40680,7 @@
         <v>1235</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="M261" s="1" t="s">
         <v>796</v>
@@ -40665,7 +40689,7 @@
         <v>320</v>
       </c>
       <c r="AK261" s="1" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="AL261" s="1" t="s">
         <v>692</v>
@@ -40691,13 +40715,13 @@
         <v>800</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>319</v>
@@ -40709,7 +40733,7 @@
         <v>1235</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="M262" s="1" t="s">
         <v>796</v>
@@ -40718,7 +40742,7 @@
         <v>320</v>
       </c>
       <c r="AK262" s="1" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="AL262" s="1" t="s">
         <v>655</v>
@@ -40744,13 +40768,13 @@
         <v>804</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>319</v>
@@ -40762,7 +40786,7 @@
         <v>1235</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="M263" s="1" t="s">
         <v>796</v>
@@ -40771,7 +40795,7 @@
         <v>320</v>
       </c>
       <c r="AK263" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="AL263" s="1" t="s">
         <v>674</v>
@@ -40797,10 +40821,10 @@
         <v>808</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>1234</v>
@@ -40815,7 +40839,7 @@
         <v>1235</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="M264" s="1" t="s">
         <v>809</v>
@@ -40824,10 +40848,10 @@
         <v>320</v>
       </c>
       <c r="AJ264" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="AK264" s="1" t="s">
         <v>1690</v>
-      </c>
-      <c r="AK264" s="1" t="s">
-        <v>1691</v>
       </c>
       <c r="AL264" s="1" t="s">
         <v>640</v>
@@ -40853,13 +40877,13 @@
         <v>814</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>319</v>
@@ -40871,7 +40895,7 @@
         <v>1235</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="M265" s="1" t="s">
         <v>796</v>
@@ -40880,7 +40904,7 @@
         <v>320</v>
       </c>
       <c r="AK265" s="1" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="AL265" s="1" t="s">
         <v>815</v>
@@ -40906,10 +40930,10 @@
         <v>819</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>953</v>
@@ -40924,7 +40948,7 @@
         <v>1235</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="M266" s="1" t="s">
         <v>796</v>
@@ -40933,7 +40957,7 @@
         <v>320</v>
       </c>
       <c r="AK266" s="1" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="AL266" s="1" t="s">
         <v>820</v>
@@ -40959,13 +40983,13 @@
         <v>162</v>
       </c>
       <c r="C267" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E267" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="D267" s="1" t="s">
-        <v>1708</v>
-      </c>
-      <c r="E267" s="1" t="s">
-        <v>1397</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>319</v>
@@ -40977,7 +41001,7 @@
         <v>1235</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="M267" s="1" t="s">
         <v>824</v>
@@ -40986,7 +41010,7 @@
         <v>320</v>
       </c>
       <c r="AK267" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="AL267" s="1" t="s">
         <v>820</v>
@@ -41012,13 +41036,13 @@
         <v>828</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>319</v>
@@ -41045,7 +41069,7 @@
         <v>320</v>
       </c>
       <c r="AL268" s="1" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="AM268" s="1" t="s">
         <v>727</v>
@@ -41071,10 +41095,10 @@
         <v>832</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>1145</v>
@@ -41127,13 +41151,13 @@
         <v>837</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>319</v>
@@ -41157,13 +41181,13 @@
         <v>839</v>
       </c>
       <c r="AT270" s="1" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="AU270" s="1" t="s">
         <v>320</v>
       </c>
       <c r="AV270" s="1" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="AW270" s="1" t="s">
         <v>840</v>
@@ -41180,13 +41204,13 @@
         <v>842</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>319</v>
@@ -41230,10 +41254,10 @@
         <v>847</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>1113</v>
@@ -41260,13 +41284,13 @@
         <v>848</v>
       </c>
       <c r="AT272" s="1" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="AU272" s="1" t="s">
         <v>320</v>
       </c>
       <c r="AV272" s="1" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="AW272" s="1" t="s">
         <v>849</v>
@@ -41283,13 +41307,13 @@
         <v>851</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>319</v>
@@ -41301,7 +41325,7 @@
         <v>1235</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="M273" s="1" t="s">
         <v>725</v>
@@ -41313,7 +41337,7 @@
         <v>320</v>
       </c>
       <c r="AU273" s="1" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="AV273" s="1" t="s">
         <v>852</v>
@@ -41333,13 +41357,13 @@
         <v>855</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>319</v>
@@ -41351,7 +41375,7 @@
         <v>1235</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="M274" s="1" t="s">
         <v>738</v>
@@ -41386,10 +41410,10 @@
         <v>1307</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>319</v>
@@ -41407,13 +41431,13 @@
         <v>320</v>
       </c>
       <c r="AT275" s="1" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="AU275" s="1" t="s">
         <v>320</v>
       </c>
       <c r="AV275" s="1" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="AW275" s="1" t="s">
         <v>860</v>
@@ -41430,10 +41454,10 @@
         <v>862</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>1081</v>
@@ -41471,10 +41495,10 @@
         <v>1211</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>319</v>
@@ -41492,7 +41516,7 @@
         <v>320</v>
       </c>
       <c r="AT277" s="1" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="AU277" s="1" t="s">
         <v>320</v>
@@ -41515,13 +41539,13 @@
         <v>869</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>319</v>
@@ -41559,13 +41583,13 @@
         <v>874</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>319</v>
@@ -41603,13 +41627,13 @@
         <v>879</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>319</v>
@@ -41624,7 +41648,7 @@
         <v>320</v>
       </c>
       <c r="AV280" s="1" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="AW280" s="1" t="s">
         <v>880</v>
@@ -41641,13 +41665,13 @@
         <v>882</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>319</v>
@@ -41671,13 +41695,13 @@
         <v>843</v>
       </c>
       <c r="AT281" s="1" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="AU281" s="1" t="s">
         <v>320</v>
       </c>
       <c r="AV281" s="1" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="AW281" s="1" t="s">
         <v>883</v>
@@ -41694,13 +41718,13 @@
         <v>885</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>319</v>
@@ -41730,7 +41754,7 @@
         <v>320</v>
       </c>
       <c r="AV282" s="1" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="AW282" s="1" t="s">
         <v>887</v>
@@ -41747,13 +41771,13 @@
         <v>889</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>319</v>
@@ -41774,7 +41798,7 @@
         <v>320</v>
       </c>
       <c r="AV283" s="1" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="AW283" s="1" t="s">
         <v>891</v>
@@ -42442,12 +42466,12 @@
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="129" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
@@ -42587,12 +42611,12 @@
     </row>
     <row r="157" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
     </row>
   </sheetData>
@@ -42621,7 +42645,7 @@
         <v>907</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>908</v>
@@ -42630,16 +42654,16 @@
         <v>909</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>1782</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>1783</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>1784</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -47208,10 +47232,10 @@
         <v>153</v>
       </c>
       <c r="C132" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>491</v>
@@ -47239,13 +47263,13 @@
         <v>152</v>
       </c>
       <c r="B133" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>1375</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>964</v>
@@ -47273,13 +47297,13 @@
         <v>152</v>
       </c>
       <c r="B134" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>1376</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>970</v>
@@ -47307,13 +47331,13 @@
         <v>152</v>
       </c>
       <c r="B135" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>1377</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>577</v>
@@ -47341,13 +47365,13 @@
         <v>152</v>
       </c>
       <c r="B136" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>1378</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>982</v>
@@ -47375,13 +47399,13 @@
         <v>152</v>
       </c>
       <c r="B137" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>1380</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>504</v>
@@ -47409,13 +47433,13 @@
         <v>152</v>
       </c>
       <c r="B138" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>1371</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>1384</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>1372</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>994</v>
@@ -47484,7 +47508,7 @@
         <v>320</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>320</v>
@@ -47522,7 +47546,7 @@
         <v>320</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>320</v>
@@ -47560,10 +47584,10 @@
         <v>162</v>
       </c>
       <c r="C142" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>1397</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>491</v>
@@ -47591,13 +47615,13 @@
         <v>161</v>
       </c>
       <c r="B143" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>1400</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>1397</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>964</v>
@@ -47625,13 +47649,13 @@
         <v>161</v>
       </c>
       <c r="B144" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E144" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>1402</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>1397</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>970</v>
@@ -47659,13 +47683,13 @@
         <v>161</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>618</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>577</v>
@@ -47693,13 +47717,13 @@
         <v>161</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>619</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>982</v>
@@ -47727,13 +47751,13 @@
         <v>161</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>617</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>504</v>
@@ -47761,13 +47785,13 @@
         <v>161</v>
       </c>
       <c r="B148" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>1405</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>1397</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>994</v>
@@ -47836,7 +47860,7 @@
         <v>320</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>320</v>
@@ -47874,7 +47898,7 @@
         <v>320</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>320</v>
@@ -47912,10 +47936,10 @@
         <v>175</v>
       </c>
       <c r="C152" s="3" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>491</v>
@@ -47943,13 +47967,13 @@
         <v>174</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>1422</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>964</v>
@@ -47977,13 +48001,13 @@
         <v>174</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="C154" s="3" t="s">
-        <v>1423</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>970</v>
@@ -48011,13 +48035,13 @@
         <v>174</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>1425</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>577</v>
@@ -48045,13 +48069,13 @@
         <v>174</v>
       </c>
       <c r="B156" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E156" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>1426</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>982</v>
@@ -48079,13 +48103,13 @@
         <v>174</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>1428</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>504</v>
@@ -48113,13 +48137,13 @@
         <v>174</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>1418</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>1430</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>1419</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>994</v>
@@ -48150,7 +48174,7 @@
         <v>320</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>320</v>
@@ -48188,7 +48212,7 @@
         <v>320</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>320</v>
@@ -48226,7 +48250,7 @@
         <v>320</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>320</v>
@@ -48264,10 +48288,10 @@
         <v>187</v>
       </c>
       <c r="C162" s="3" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>1447</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>1448</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>491</v>
@@ -48295,13 +48319,13 @@
         <v>186</v>
       </c>
       <c r="B163" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>1447</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>1452</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>1448</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>964</v>
@@ -48329,13 +48353,13 @@
         <v>186</v>
       </c>
       <c r="B164" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>1447</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>1454</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>1448</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>970</v>
@@ -48363,13 +48387,13 @@
         <v>186</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>1447</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>1455</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>1448</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>577</v>
@@ -48397,13 +48421,13 @@
         <v>186</v>
       </c>
       <c r="B166" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>1447</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>1458</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>1448</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>982</v>
@@ -48431,13 +48455,13 @@
         <v>186</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E167" s="1" t="s">
         <v>1447</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>1459</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>1448</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>504</v>
@@ -48465,13 +48489,13 @@
         <v>186</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E168" s="1" t="s">
         <v>1447</v>
-      </c>
-      <c r="C168" s="3" t="s">
-        <v>1461</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>1448</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>994</v>
@@ -48578,7 +48602,7 @@
         <v>320</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>320</v>
@@ -48616,10 +48640,10 @@
         <v>200</v>
       </c>
       <c r="C172" s="3" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E172" s="1" t="s">
         <v>1476</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>1477</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>491</v>
@@ -48647,13 +48671,13 @@
         <v>199</v>
       </c>
       <c r="B173" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E173" s="1" t="s">
         <v>1476</v>
-      </c>
-      <c r="C173" s="3" t="s">
-        <v>1483</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>1477</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>964</v>
@@ -48681,13 +48705,13 @@
         <v>199</v>
       </c>
       <c r="B174" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E174" s="1" t="s">
         <v>1476</v>
-      </c>
-      <c r="C174" s="3" t="s">
-        <v>1486</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>1477</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>970</v>
@@ -48715,13 +48739,13 @@
         <v>199</v>
       </c>
       <c r="B175" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E175" s="1" t="s">
         <v>1476</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>1487</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>1477</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>577</v>
@@ -48749,13 +48773,13 @@
         <v>199</v>
       </c>
       <c r="B176" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E176" s="1" t="s">
         <v>1476</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>1489</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>1477</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>982</v>
@@ -48783,13 +48807,13 @@
         <v>199</v>
       </c>
       <c r="B177" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E177" s="1" t="s">
         <v>1476</v>
-      </c>
-      <c r="C177" s="3" t="s">
-        <v>1490</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>1477</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>504</v>
@@ -48817,13 +48841,13 @@
         <v>199</v>
       </c>
       <c r="B178" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>1476</v>
-      </c>
-      <c r="C178" s="3" t="s">
-        <v>1492</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>1477</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>994</v>
@@ -48854,7 +48878,7 @@
         <v>320</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>320</v>
@@ -48892,7 +48916,7 @@
         <v>320</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>320</v>
@@ -48930,7 +48954,7 @@
         <v>320</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>320</v>
@@ -48968,10 +48992,10 @@
         <v>213</v>
       </c>
       <c r="C182" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>491</v>
@@ -48999,13 +49023,13 @@
         <v>212</v>
       </c>
       <c r="B183" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="C183" s="3" t="s">
-        <v>1514</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>964</v>
@@ -49033,13 +49057,13 @@
         <v>212</v>
       </c>
       <c r="B184" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E184" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="C184" s="3" t="s">
-        <v>1517</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>970</v>
@@ -49067,13 +49091,13 @@
         <v>212</v>
       </c>
       <c r="B185" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E185" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="C185" s="3" t="s">
-        <v>1519</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>577</v>
@@ -49101,13 +49125,13 @@
         <v>212</v>
       </c>
       <c r="B186" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>1520</v>
+      </c>
+      <c r="E186" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="C186" s="3" t="s">
-        <v>1521</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>982</v>
@@ -49135,13 +49159,13 @@
         <v>212</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E187" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="C187" s="3" t="s">
-        <v>1523</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>504</v>
@@ -49169,13 +49193,13 @@
         <v>212</v>
       </c>
       <c r="B188" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E188" s="1" t="s">
         <v>1506</v>
-      </c>
-      <c r="C188" s="3" t="s">
-        <v>1524</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>1507</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>994</v>
@@ -49206,7 +49230,7 @@
         <v>320</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>320</v>
@@ -49282,7 +49306,7 @@
         <v>320</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>320</v>
@@ -49320,10 +49344,10 @@
         <v>222</v>
       </c>
       <c r="C192" s="3" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E192" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>491</v>
@@ -49351,13 +49375,13 @@
         <v>221</v>
       </c>
       <c r="B193" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E193" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="C193" s="3" t="s">
-        <v>1545</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>964</v>
@@ -49385,13 +49409,13 @@
         <v>221</v>
       </c>
       <c r="B194" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="E194" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="C194" s="3" t="s">
-        <v>1547</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>970</v>
@@ -49419,13 +49443,13 @@
         <v>221</v>
       </c>
       <c r="B195" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E195" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="C195" s="3" t="s">
-        <v>1549</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>577</v>
@@ -49453,13 +49477,13 @@
         <v>221</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>1551</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="C196" s="3" t="s">
-        <v>1552</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>982</v>
@@ -49487,13 +49511,13 @@
         <v>221</v>
       </c>
       <c r="B197" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="C197" s="3" t="s">
-        <v>1554</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>504</v>
@@ -49521,13 +49545,13 @@
         <v>221</v>
       </c>
       <c r="B198" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>1540</v>
-      </c>
-      <c r="C198" s="3" t="s">
-        <v>1556</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>1541</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>994</v>
@@ -49558,7 +49582,7 @@
         <v>320</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>320</v>
@@ -49595,7 +49619,7 @@
         <v>320</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>320</v>
@@ -49633,7 +49657,7 @@
         <v>320</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>320</v>
@@ -49671,10 +49695,10 @@
         <v>235</v>
       </c>
       <c r="C202" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E202" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>491</v>
@@ -49695,13 +49719,13 @@
         <v>234</v>
       </c>
       <c r="B203" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E203" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="C203" s="3" t="s">
-        <v>1575</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>964</v>
@@ -49722,13 +49746,13 @@
         <v>234</v>
       </c>
       <c r="B204" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E204" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="C204" s="3" t="s">
-        <v>1577</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>970</v>
@@ -49749,13 +49773,13 @@
         <v>234</v>
       </c>
       <c r="B205" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="C205" s="3" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>577</v>
@@ -49776,13 +49800,13 @@
         <v>234</v>
       </c>
       <c r="B206" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E206" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="C206" s="3" t="s">
-        <v>1581</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>982</v>
@@ -49803,13 +49827,13 @@
         <v>234</v>
       </c>
       <c r="B207" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E207" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="C207" s="3" t="s">
-        <v>1583</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>504</v>
@@ -49830,13 +49854,13 @@
         <v>234</v>
       </c>
       <c r="B208" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="C208" s="3" t="s">
-        <v>1587</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>1571</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>994</v>
@@ -49860,7 +49884,7 @@
         <v>320</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>320</v>
@@ -49891,7 +49915,7 @@
         <v>320</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>320</v>
@@ -49922,7 +49946,7 @@
         <v>320</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>320</v>
@@ -49953,10 +49977,10 @@
         <v>249</v>
       </c>
       <c r="C212" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>1599</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>1600</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>491</v>
@@ -49977,13 +50001,13 @@
         <v>248</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="E213" s="1" t="s">
         <v>1599</v>
-      </c>
-      <c r="C213" s="3" t="s">
-        <v>1602</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>1600</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>964</v>
@@ -50004,13 +50028,13 @@
         <v>248</v>
       </c>
       <c r="B214" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E214" s="1" t="s">
         <v>1599</v>
-      </c>
-      <c r="C214" s="3" t="s">
-        <v>1604</v>
-      </c>
-      <c r="E214" s="1" t="s">
-        <v>1600</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>970</v>
@@ -50031,13 +50055,13 @@
         <v>248</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="C215" s="3" t="s">
         <v>591</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>577</v>
@@ -50058,13 +50082,13 @@
         <v>248</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>571</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>982</v>
@@ -50085,13 +50109,13 @@
         <v>248</v>
       </c>
       <c r="B217" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E217" s="1" t="s">
         <v>1599</v>
-      </c>
-      <c r="C217" s="3" t="s">
-        <v>1609</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>1600</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>504</v>
@@ -50112,13 +50136,13 @@
         <v>248</v>
       </c>
       <c r="B218" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="E218" s="1" t="s">
         <v>1599</v>
-      </c>
-      <c r="C218" s="3" t="s">
-        <v>1611</v>
-      </c>
-      <c r="E218" s="1" t="s">
-        <v>1600</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>994</v>
@@ -50142,7 +50166,7 @@
         <v>320</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>320</v>
@@ -50173,7 +50197,7 @@
         <v>320</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>320</v>
@@ -50204,7 +50228,7 @@
         <v>320</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>320</v>
@@ -50234,10 +50258,10 @@
         <v>264</v>
       </c>
       <c r="C222" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="E222" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>491</v>
@@ -50258,13 +50282,13 @@
         <v>263</v>
       </c>
       <c r="B223" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="E223" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C223" s="3" t="s">
-        <v>1625</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>964</v>
@@ -50285,13 +50309,13 @@
         <v>263</v>
       </c>
       <c r="B224" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="E224" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>1626</v>
-      </c>
-      <c r="E224" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>970</v>
@@ -50312,13 +50336,13 @@
         <v>263</v>
       </c>
       <c r="B225" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E225" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C225" s="3" t="s">
-        <v>1628</v>
-      </c>
-      <c r="E225" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>577</v>
@@ -50339,13 +50363,13 @@
         <v>263</v>
       </c>
       <c r="B226" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E226" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>1631</v>
-      </c>
-      <c r="E226" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>982</v>
@@ -50366,13 +50390,13 @@
         <v>263</v>
       </c>
       <c r="B227" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E227" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C227" s="3" t="s">
-        <v>1632</v>
-      </c>
-      <c r="E227" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>504</v>
@@ -50393,13 +50417,13 @@
         <v>263</v>
       </c>
       <c r="B228" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E228" s="1" t="s">
         <v>1622</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>1634</v>
-      </c>
-      <c r="E228" s="1" t="s">
-        <v>1623</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>994</v>
@@ -50423,7 +50447,7 @@
         <v>320</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>320</v>
@@ -50454,7 +50478,7 @@
         <v>320</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>320</v>
@@ -50485,7 +50509,7 @@
         <v>320</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>320</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AAACFE8-E33F-48CE-9D52-2E3818B49EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4AB3AF-FC5C-465E-9958-F9EACC1392A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -6473,10 +6473,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>和同群夥伴之間拉出一條由一節一節火環扣成的橘黃火焰鎖鏈（鏈環數隨距離增減），持續到怪物死亡；每 3~6 秒隨機跑位，用火鏈掃過你。碰到或穿過火鏈會承受高頻率的連續火焰傷害。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>{"pool":"random","arch":"sparks","kind":"passive","color":"#8ad8ff","n":[2,4],"speed":8,"life":5,"r":1.2,"dmg":0.45,"gap":0.35,"cap":36,"bodyD":1.6}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -7578,6 +7574,10 @@
   </si>
   <si>
     <t>　earthguard 第 7 階（我方）：第 1 格 復活後減傷〔限屬性增減〕</t>
+  </si>
+  <si>
+    <t>和同群夥伴之間拉出由一節一節火環扣成的橘黃火焰鎖鏈（2 隻連一條線、3 隻連成三角形、4 隻連成四邊形，以此類推）（鏈環數隨距離增減），持續到怪物死亡；每 3~6 秒隨機跑位，用火鏈掃過你。碰到或穿過火鏈會承受高頻率的連續火焰傷害。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8357,7 +8357,7 @@
         <v>554</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="AX2" s="1" t="s">
         <v>30</v>
@@ -8491,7 +8491,7 @@
         <v>1023</v>
       </c>
       <c r="AW3" s="1" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="AX3" s="1" t="s">
         <v>31</v>
@@ -8625,7 +8625,7 @@
         <v>1025</v>
       </c>
       <c r="AW4" s="1" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="AX4" s="1" t="s">
         <v>32</v>
@@ -8759,7 +8759,7 @@
         <v>555</v>
       </c>
       <c r="AW5" s="1" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="AX5" s="1" t="s">
         <v>33</v>
@@ -8893,7 +8893,7 @@
         <v>556</v>
       </c>
       <c r="AW6" s="1" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="AX6" s="1" t="s">
         <v>34</v>
@@ -9027,7 +9027,7 @@
         <v>557</v>
       </c>
       <c r="AW7" s="1" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="AX7" s="1" t="s">
         <v>35</v>
@@ -9158,10 +9158,10 @@
         <v>314</v>
       </c>
       <c r="AV8" s="1" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="AW8" s="1" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="AX8" s="1" t="s">
         <v>36</v>
@@ -9295,7 +9295,7 @@
         <v>1036</v>
       </c>
       <c r="AW9" s="1" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="AX9" s="1" t="s">
         <v>37</v>
@@ -9435,7 +9435,7 @@
         <v>1040</v>
       </c>
       <c r="AW10" s="1" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="AX10" s="1" t="s">
         <v>38</v>
@@ -9569,7 +9569,7 @@
         <v>558</v>
       </c>
       <c r="AW11" s="1" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="AX11" s="1" t="s">
         <v>39</v>
@@ -9703,7 +9703,7 @@
         <v>554</v>
       </c>
       <c r="AW12" s="1" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="AX12" s="1" t="s">
         <v>9</v>
@@ -9837,7 +9837,7 @@
         <v>934</v>
       </c>
       <c r="AW13" s="1" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="AX13" s="1" t="s">
         <v>10</v>
@@ -9971,7 +9971,7 @@
         <v>941</v>
       </c>
       <c r="AW14" s="1" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="AX14" s="1" t="s">
         <v>11</v>
@@ -10105,7 +10105,7 @@
         <v>946</v>
       </c>
       <c r="AW15" s="1" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="AX15" s="1" t="s">
         <v>12</v>
@@ -10239,7 +10239,7 @@
         <v>953</v>
       </c>
       <c r="AW16" s="1" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="AX16" s="1" t="s">
         <v>13</v>
@@ -10373,7 +10373,7 @@
         <v>959</v>
       </c>
       <c r="AW17" s="1" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="AX17" s="1" t="s">
         <v>14</v>
@@ -10507,7 +10507,7 @@
         <v>551</v>
       </c>
       <c r="AW18" s="1" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="AX18" s="1" t="s">
         <v>964</v>
@@ -10647,7 +10647,7 @@
         <v>552</v>
       </c>
       <c r="AW19" s="1" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="AX19" s="1" t="s">
         <v>971</v>
@@ -10784,7 +10784,7 @@
         <v>978</v>
       </c>
       <c r="AW20" s="1" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="AX20" s="1" t="s">
         <v>15</v>
@@ -10918,7 +10918,7 @@
         <v>984</v>
       </c>
       <c r="AW21" s="1" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="AX21" s="1" t="s">
         <v>985</v>
@@ -11052,7 +11052,7 @@
         <v>990</v>
       </c>
       <c r="AW22" s="1" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="AX22" s="1" t="s">
         <v>18</v>
@@ -11186,7 +11186,7 @@
         <v>959</v>
       </c>
       <c r="AW23" s="1" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="AX23" s="1" t="s">
         <v>19</v>
@@ -11320,7 +11320,7 @@
         <v>994</v>
       </c>
       <c r="AW24" s="1" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="AX24" s="1" t="s">
         <v>20</v>
@@ -11454,7 +11454,7 @@
         <v>996</v>
       </c>
       <c r="AW25" s="1" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="AX25" s="1" t="s">
         <v>21</v>
@@ -11587,7 +11587,7 @@
         <v>1000</v>
       </c>
       <c r="AW26" s="1" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="AX26" s="1" t="s">
         <v>22</v>
@@ -11719,7 +11719,7 @@
         <v>959</v>
       </c>
       <c r="AW27" s="1" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="AX27" s="1" t="s">
         <v>23</v>
@@ -13750,7 +13750,7 @@
         <v>1082</v>
       </c>
       <c r="AV42" s="1" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="AW42" s="1" t="s">
         <v>54</v>
@@ -13880,7 +13880,7 @@
         <v>314</v>
       </c>
       <c r="AV43" s="1" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="AW43" s="1" t="s">
         <v>55</v>
@@ -14292,7 +14292,7 @@
         <v>314</v>
       </c>
       <c r="AV46" s="1" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="AW46" s="1" t="s">
         <v>59</v>
@@ -14563,7 +14563,7 @@
         <v>314</v>
       </c>
       <c r="AV48" s="1" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="AW48" s="1" t="s">
         <v>62</v>
@@ -14982,16 +14982,16 @@
         <v>314</v>
       </c>
       <c r="AV51" s="1" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="AW51" s="1" t="s">
+        <v>1878</v>
+      </c>
+      <c r="AX51" s="1" t="s">
         <v>1879</v>
       </c>
-      <c r="AX51" s="1" t="s">
-        <v>1880</v>
-      </c>
       <c r="AY51" s="1" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="AZ51" s="3" t="s">
         <v>1110</v>
@@ -15115,7 +15115,7 @@
         <v>1114</v>
       </c>
       <c r="AW52" s="1" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="AX52" s="1" t="s">
         <v>1115</v>
@@ -15247,7 +15247,7 @@
         <v>1117</v>
       </c>
       <c r="AW53" s="1" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="AX53" s="1" t="s">
         <v>1118</v>
@@ -15379,7 +15379,7 @@
         <v>1121</v>
       </c>
       <c r="AW54" s="1" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="AX54" s="1" t="s">
         <v>67</v>
@@ -15519,7 +15519,7 @@
         <v>1123</v>
       </c>
       <c r="AW55" s="1" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="AX55" s="1" t="s">
         <v>68</v>
@@ -15659,7 +15659,7 @@
         <v>345</v>
       </c>
       <c r="AW56" s="1" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="AX56" s="1" t="s">
         <v>69</v>
@@ -15793,7 +15793,7 @@
         <v>1128</v>
       </c>
       <c r="AW57" s="1" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="AX57" s="1" t="s">
         <v>70</v>
@@ -15931,7 +15931,7 @@
         <v>1130</v>
       </c>
       <c r="AW58" s="1" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="AX58" s="1" t="s">
         <v>1131</v>
@@ -16065,7 +16065,7 @@
         <v>444</v>
       </c>
       <c r="AW59" s="1" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="AX59" s="1" t="s">
         <v>1135</v>
@@ -16202,10 +16202,10 @@
         <v>594</v>
       </c>
       <c r="AW60" s="1" t="s">
+        <v>1898</v>
+      </c>
+      <c r="AX60" s="1" t="s">
         <v>1899</v>
-      </c>
-      <c r="AX60" s="1" t="s">
-        <v>1900</v>
       </c>
       <c r="AY60" s="1" t="s">
         <v>423</v>
@@ -16336,7 +16336,7 @@
         <v>1036</v>
       </c>
       <c r="AW61" s="1" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="AX61" s="1" t="s">
         <v>71</v>
@@ -16470,10 +16470,10 @@
         <v>1147</v>
       </c>
       <c r="AW62" s="1" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="AX62" s="1" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="AY62" s="1" t="s">
         <v>423</v>
@@ -16604,7 +16604,7 @@
         <v>1149</v>
       </c>
       <c r="AW63" s="1" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="AX63" s="1" t="s">
         <v>74</v>
@@ -16738,7 +16738,7 @@
         <v>1151</v>
       </c>
       <c r="AW64" s="1" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="AX64" s="1" t="s">
         <v>75</v>
@@ -16872,7 +16872,7 @@
         <v>525</v>
       </c>
       <c r="AW65" s="1" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="AX65" s="1" t="s">
         <v>76</v>
@@ -17009,7 +17009,7 @@
         <v>1157</v>
       </c>
       <c r="AW66" s="1" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="AX66" s="1" t="s">
         <v>78</v>
@@ -17143,7 +17143,7 @@
         <v>447</v>
       </c>
       <c r="AW67" s="1" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="AX67" s="1" t="s">
         <v>79</v>
@@ -17277,7 +17277,7 @@
         <v>448</v>
       </c>
       <c r="AW68" s="1" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="AX68" s="1" t="s">
         <v>80</v>
@@ -17417,10 +17417,10 @@
         <v>314</v>
       </c>
       <c r="AV69" s="1" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="AW69" s="1" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="AX69" s="1" t="s">
         <v>81</v>
@@ -17704,13 +17704,13 @@
         <v>314</v>
       </c>
       <c r="AV71" s="1" t="s">
+        <v>1900</v>
+      </c>
+      <c r="AW71" s="1" t="s">
+        <v>1903</v>
+      </c>
+      <c r="AX71" s="1" t="s">
         <v>1901</v>
-      </c>
-      <c r="AW71" s="1" t="s">
-        <v>1904</v>
-      </c>
-      <c r="AX71" s="1" t="s">
-        <v>1902</v>
       </c>
       <c r="AY71" s="1" t="s">
         <v>423</v>
@@ -17853,7 +17853,7 @@
         <v>1176</v>
       </c>
       <c r="AW72" s="1" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="AX72" s="1" t="s">
         <v>85</v>
@@ -17987,7 +17987,7 @@
         <v>1036</v>
       </c>
       <c r="AW73" s="1" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="AX73" s="1" t="s">
         <v>87</v>
@@ -18119,7 +18119,7 @@
         <v>1036</v>
       </c>
       <c r="AW74" s="1" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="AX74" s="1" t="s">
         <v>88</v>
@@ -18251,7 +18251,7 @@
         <v>1183</v>
       </c>
       <c r="AW75" s="1" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="AX75" s="1" t="s">
         <v>89</v>
@@ -18383,7 +18383,7 @@
         <v>1036</v>
       </c>
       <c r="AW76" s="1" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="AX76" s="1" t="s">
         <v>90</v>
@@ -18512,10 +18512,10 @@
         <v>314</v>
       </c>
       <c r="AV77" s="1" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="AW77" s="1" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="AX77" s="1" t="s">
         <v>91</v>
@@ -18651,13 +18651,13 @@
         <v>314</v>
       </c>
       <c r="AV78" s="1" t="s">
+        <v>1912</v>
+      </c>
+      <c r="AW78" s="1" t="s">
+        <v>1917</v>
+      </c>
+      <c r="AX78" s="1" t="s">
         <v>1913</v>
-      </c>
-      <c r="AW78" s="1" t="s">
-        <v>1918</v>
-      </c>
-      <c r="AX78" s="1" t="s">
-        <v>1914</v>
       </c>
       <c r="AY78" s="1" t="s">
         <v>1177</v>
@@ -18792,7 +18792,7 @@
         <v>1192</v>
       </c>
       <c r="AW79" s="1" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="AX79" s="1" t="s">
         <v>92</v>
@@ -18933,10 +18933,10 @@
         <v>314</v>
       </c>
       <c r="AV80" s="1" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="AW80" s="1" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="AX80" s="1" t="s">
         <v>451</v>
@@ -19077,13 +19077,13 @@
         <v>314</v>
       </c>
       <c r="AV81" s="1" t="s">
+        <v>1914</v>
+      </c>
+      <c r="AW81" s="1" t="s">
+        <v>1919</v>
+      </c>
+      <c r="AX81" s="1" t="s">
         <v>1915</v>
-      </c>
-      <c r="AW81" s="1" t="s">
-        <v>1920</v>
-      </c>
-      <c r="AX81" s="1" t="s">
-        <v>1916</v>
       </c>
       <c r="AY81" s="1" t="s">
         <v>1177</v>
@@ -19212,7 +19212,7 @@
         <v>1205</v>
       </c>
       <c r="AW82" s="1" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="AX82" s="1" t="s">
         <v>97</v>
@@ -19347,7 +19347,7 @@
         <v>1208</v>
       </c>
       <c r="AW83" s="1" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="AX83" s="1" t="s">
         <v>98</v>
@@ -19479,7 +19479,7 @@
         <v>1210</v>
       </c>
       <c r="AW84" s="1" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="AX84" s="1" t="s">
         <v>99</v>
@@ -19611,7 +19611,7 @@
         <v>959</v>
       </c>
       <c r="AW85" s="1" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="AX85" s="1" t="s">
         <v>100</v>
@@ -19743,7 +19743,7 @@
         <v>1096</v>
       </c>
       <c r="AW86" s="1" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="AX86" s="1" t="s">
         <v>102</v>
@@ -19878,13 +19878,13 @@
         <v>314</v>
       </c>
       <c r="AV87" s="1" t="s">
+        <v>1926</v>
+      </c>
+      <c r="AW87" s="1" t="s">
+        <v>1928</v>
+      </c>
+      <c r="AX87" s="1" t="s">
         <v>1927</v>
-      </c>
-      <c r="AW87" s="1" t="s">
-        <v>1929</v>
-      </c>
-      <c r="AX87" s="1" t="s">
-        <v>1928</v>
       </c>
       <c r="AY87" s="1" t="s">
         <v>423</v>
@@ -20013,7 +20013,7 @@
         <v>1220</v>
       </c>
       <c r="AW88" s="1" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="AX88" s="1" t="s">
         <v>104</v>
@@ -20145,7 +20145,7 @@
         <v>1224</v>
       </c>
       <c r="AW89" s="1" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="AX89" s="1" t="s">
         <v>105</v>
@@ -20289,7 +20289,7 @@
         <v>575</v>
       </c>
       <c r="AW90" s="1" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="AX90" s="1" t="s">
         <v>107</v>
@@ -20421,7 +20421,7 @@
         <v>574</v>
       </c>
       <c r="AW91" s="1" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="AX91" s="1" t="s">
         <v>108</v>
@@ -20556,7 +20556,7 @@
         <v>1235</v>
       </c>
       <c r="AW92" s="1" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="AX92" s="1" t="s">
         <v>112</v>
@@ -20688,7 +20688,7 @@
         <v>1086</v>
       </c>
       <c r="AW93" s="1" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="AX93" s="1" t="s">
         <v>113</v>
@@ -20817,10 +20817,10 @@
         <v>314</v>
       </c>
       <c r="AV94" s="1" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="AW94" s="1" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="AX94" s="1" t="s">
         <v>114</v>
@@ -20955,7 +20955,7 @@
         <v>1240</v>
       </c>
       <c r="AW95" s="1" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="AX95" s="1" t="s">
         <v>115</v>
@@ -21099,7 +21099,7 @@
         <v>1192</v>
       </c>
       <c r="AW96" s="1" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="AX96" s="1" t="s">
         <v>116</v>
@@ -21231,7 +21231,7 @@
         <v>1244</v>
       </c>
       <c r="AW97" s="1" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="AX97" s="1" t="s">
         <v>117</v>
@@ -21366,7 +21366,7 @@
         <v>1246</v>
       </c>
       <c r="AW98" s="1" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="AX98" s="1" t="s">
         <v>119</v>
@@ -21507,7 +21507,7 @@
         <v>1250</v>
       </c>
       <c r="AW99" s="1" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="AX99" s="1" t="s">
         <v>465</v>
@@ -21642,10 +21642,10 @@
         <v>314</v>
       </c>
       <c r="AV100" s="1" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="AW100" s="1" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="AX100" s="1" t="s">
         <v>121</v>
@@ -21783,7 +21783,7 @@
         <v>464</v>
       </c>
       <c r="AW101" s="1" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="AX101" s="1" t="s">
         <v>1258</v>
@@ -21921,7 +21921,7 @@
         <v>1265</v>
       </c>
       <c r="AW102" s="1" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="AX102" s="1" t="s">
         <v>124</v>
@@ -22053,7 +22053,7 @@
         <v>1267</v>
       </c>
       <c r="AW103" s="1" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="AX103" s="1" t="s">
         <v>125</v>
@@ -22191,7 +22191,7 @@
         <v>1269</v>
       </c>
       <c r="AW104" s="1" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="AX104" s="1" t="s">
         <v>127</v>
@@ -22323,7 +22323,7 @@
         <v>1271</v>
       </c>
       <c r="AW105" s="1" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="AX105" s="1" t="s">
         <v>128</v>
@@ -22455,7 +22455,7 @@
         <v>1036</v>
       </c>
       <c r="AW106" s="1" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="AX106" s="1" t="s">
         <v>129</v>
@@ -22584,10 +22584,10 @@
         <v>314</v>
       </c>
       <c r="AV107" s="1" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="AW107" s="1" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="AX107" s="1" t="s">
         <v>131</v>
@@ -22719,10 +22719,10 @@
         <v>1275</v>
       </c>
       <c r="AW108" s="1" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="AX108" s="1" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="AY108" s="1" t="s">
         <v>423</v>
@@ -22854,7 +22854,7 @@
         <v>314</v>
       </c>
       <c r="AV109" s="1" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="AW109" s="1" t="s">
         <v>132</v>
@@ -22992,13 +22992,13 @@
         <v>1207</v>
       </c>
       <c r="AV110" s="1" t="s">
+        <v>1954</v>
+      </c>
+      <c r="AW110" s="1" t="s">
         <v>1955</v>
       </c>
-      <c r="AW110" s="1" t="s">
+      <c r="AX110" s="1" t="s">
         <v>1956</v>
-      </c>
-      <c r="AX110" s="1" t="s">
-        <v>1957</v>
       </c>
       <c r="AY110" s="1" t="s">
         <v>472</v>
@@ -23139,7 +23139,7 @@
         <v>467</v>
       </c>
       <c r="AW111" s="1" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="AX111" s="1" t="s">
         <v>466</v>
@@ -23274,10 +23274,10 @@
         <v>314</v>
       </c>
       <c r="AV112" s="1" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="AW112" s="1" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="AX112" s="1" t="s">
         <v>136</v>
@@ -23409,7 +23409,7 @@
         <v>1036</v>
       </c>
       <c r="AW113" s="1" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="AX113" s="1" t="s">
         <v>137</v>
@@ -23541,7 +23541,7 @@
         <v>1289</v>
       </c>
       <c r="AW114" s="1" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="AX114" s="1" t="s">
         <v>138</v>
@@ -23673,10 +23673,10 @@
         <v>1267</v>
       </c>
       <c r="AW115" s="1" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="AX115" s="1" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="AY115" s="1" t="s">
         <v>423</v>
@@ -23805,7 +23805,7 @@
         <v>525</v>
       </c>
       <c r="AW116" s="1" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="AX116" s="1" t="s">
         <v>139</v>
@@ -23940,10 +23940,10 @@
         <v>314</v>
       </c>
       <c r="AV117" s="1" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="AW117" s="1" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="AX117" s="1" t="s">
         <v>140</v>
@@ -24075,7 +24075,7 @@
         <v>1294</v>
       </c>
       <c r="AW118" s="1" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="AX118" s="1" t="s">
         <v>142</v>
@@ -24225,7 +24225,7 @@
         <v>584</v>
       </c>
       <c r="AW119" s="1" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="AX119" s="1" t="s">
         <v>1299</v>
@@ -24354,10 +24354,10 @@
         <v>314</v>
       </c>
       <c r="AV120" s="1" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AW120" s="1" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="AX120" s="1" t="s">
         <v>143</v>
@@ -24492,13 +24492,13 @@
         <v>1308</v>
       </c>
       <c r="AV121" s="1" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="AW121" s="1" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="AX121" s="1" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="AY121" s="1" t="s">
         <v>423</v>
@@ -24627,13 +24627,13 @@
         <v>1313</v>
       </c>
       <c r="AV122" s="1" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="AW122" s="1" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="AX122" s="1" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="AY122" s="1" t="s">
         <v>423</v>
@@ -24762,10 +24762,10 @@
         <v>1267</v>
       </c>
       <c r="AW123" s="1" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="AX123" s="1" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="AY123" s="1" t="s">
         <v>423</v>
@@ -24897,7 +24897,7 @@
         <v>1318</v>
       </c>
       <c r="AW124" s="1" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="AX124" s="1" t="s">
         <v>146</v>
@@ -25161,7 +25161,7 @@
         <v>1321</v>
       </c>
       <c r="AW126" s="1" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="AX126" s="1" t="s">
         <v>148</v>
@@ -25293,10 +25293,10 @@
         <v>1323</v>
       </c>
       <c r="AW127" s="1" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="AX127" s="1" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="AY127" s="1" t="s">
         <v>423</v>
@@ -25428,7 +25428,7 @@
         <v>1327</v>
       </c>
       <c r="AW128" s="1" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="AX128" s="1" t="s">
         <v>149</v>
@@ -25563,7 +25563,7 @@
         <v>1331</v>
       </c>
       <c r="AW129" s="1" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="AX129" s="1" t="s">
         <v>150</v>
@@ -25695,7 +25695,7 @@
         <v>482</v>
       </c>
       <c r="AR130" s="1" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="AT130" s="1" t="s">
         <v>314</v>
@@ -25704,16 +25704,16 @@
         <v>314</v>
       </c>
       <c r="AV130" s="1" t="s">
+        <v>1983</v>
+      </c>
+      <c r="AW130" s="1" t="s">
+        <v>1988</v>
+      </c>
+      <c r="AX130" s="1" t="s">
         <v>1984</v>
       </c>
-      <c r="AW130" s="1" t="s">
-        <v>1989</v>
-      </c>
-      <c r="AX130" s="1" t="s">
+      <c r="AY130" s="1" t="s">
         <v>1985</v>
-      </c>
-      <c r="AY130" s="1" t="s">
-        <v>1986</v>
       </c>
       <c r="AZ130" s="3" t="s">
         <v>1276</v>
@@ -25836,10 +25836,10 @@
         <v>314</v>
       </c>
       <c r="AV131" s="1" t="s">
+        <v>1981</v>
+      </c>
+      <c r="AW131" s="1" t="s">
         <v>1982</v>
-      </c>
-      <c r="AW131" s="1" t="s">
-        <v>1983</v>
       </c>
       <c r="AX131" s="1" t="s">
         <v>151</v>
@@ -25968,10 +25968,10 @@
         <v>314</v>
       </c>
       <c r="AV132" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="AW132" s="1" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="AX132" s="1" t="s">
         <v>154</v>
@@ -26103,7 +26103,7 @@
         <v>1267</v>
       </c>
       <c r="AW133" s="1" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="AX133" s="1" t="s">
         <v>155</v>
@@ -26235,7 +26235,7 @@
         <v>499</v>
       </c>
       <c r="AW134" s="1" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="AX134" s="1" t="s">
         <v>156</v>
@@ -26367,7 +26367,7 @@
         <v>499</v>
       </c>
       <c r="AW135" s="1" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="AX135" s="1" t="s">
         <v>157</v>
@@ -26499,7 +26499,7 @@
         <v>587</v>
       </c>
       <c r="AW136" s="1" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="AX136" s="1" t="s">
         <v>1343</v>
@@ -26631,7 +26631,7 @@
         <v>1347</v>
       </c>
       <c r="AW137" s="1" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="AX137" s="1" t="s">
         <v>158</v>
@@ -26760,19 +26760,19 @@
         <v>314</v>
       </c>
       <c r="AT138" s="1" t="s">
+        <v>1996</v>
+      </c>
+      <c r="AU138" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AV138" s="1" t="s">
+        <v>1995</v>
+      </c>
+      <c r="AW138" s="1" t="s">
+        <v>1999</v>
+      </c>
+      <c r="AX138" s="1" t="s">
         <v>1997</v>
-      </c>
-      <c r="AU138" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AV138" s="1" t="s">
-        <v>1996</v>
-      </c>
-      <c r="AW138" s="1" t="s">
-        <v>2000</v>
-      </c>
-      <c r="AX138" s="1" t="s">
-        <v>1998</v>
       </c>
       <c r="AY138" s="1" t="s">
         <v>423</v>
@@ -26901,7 +26901,7 @@
         <v>595</v>
       </c>
       <c r="AW139" s="1" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="AX139" s="1" t="s">
         <v>1352</v>
@@ -27033,7 +27033,7 @@
         <v>484</v>
       </c>
       <c r="AW140" s="1" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="AX140" s="1" t="s">
         <v>159</v>
@@ -27165,7 +27165,7 @@
         <v>1358</v>
       </c>
       <c r="AW141" s="1" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="AX141" s="1" t="s">
         <v>160</v>
@@ -27295,7 +27295,7 @@
         <v>588</v>
       </c>
       <c r="AW142" s="1" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="AX142" s="1" t="s">
         <v>165</v>
@@ -27427,7 +27427,7 @@
         <v>560</v>
       </c>
       <c r="AW143" s="1" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="AX143" s="1" t="s">
         <v>166</v>
@@ -27559,7 +27559,7 @@
         <v>555</v>
       </c>
       <c r="AW144" s="1" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AX144" s="1" t="s">
         <v>167</v>
@@ -27691,7 +27691,7 @@
         <v>1117</v>
       </c>
       <c r="AW145" s="1" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="AX145" s="1" t="s">
         <v>168</v>
@@ -27823,7 +27823,7 @@
         <v>1366</v>
       </c>
       <c r="AW146" s="1" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="AX146" s="1" t="s">
         <v>169</v>
@@ -27955,7 +27955,7 @@
         <v>560</v>
       </c>
       <c r="AW147" s="1" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="AX147" s="1" t="s">
         <v>170</v>
@@ -28087,7 +28087,7 @@
         <v>596</v>
       </c>
       <c r="AW148" s="1" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="AX148" s="1" t="s">
         <v>171</v>
@@ -28234,7 +28234,7 @@
         <v>1374</v>
       </c>
       <c r="AW149" s="1" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="AX149" s="1" t="s">
         <v>172</v>
@@ -28372,7 +28372,7 @@
         <v>597</v>
       </c>
       <c r="AW150" s="1" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="AX150" s="1" t="s">
         <v>1379</v>
@@ -28392,7 +28392,7 @@
         <v>314</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>314</v>
@@ -28473,7 +28473,7 @@
         <v>314</v>
       </c>
       <c r="AE151" s="1" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="AF151" s="1" t="s">
         <v>314</v>
@@ -28501,10 +28501,10 @@
         <v>959</v>
       </c>
       <c r="AW151" s="1" t="s">
+        <v>2072</v>
+      </c>
+      <c r="AX151" s="1" t="s">
         <v>2073</v>
-      </c>
-      <c r="AX151" s="1" t="s">
-        <v>2074</v>
       </c>
       <c r="AY151" s="1" t="s">
         <v>423</v>
@@ -28633,7 +28633,7 @@
         <v>1384</v>
       </c>
       <c r="AW152" s="1" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="AX152" s="1" t="s">
         <v>175</v>
@@ -28765,7 +28765,7 @@
         <v>555</v>
       </c>
       <c r="AW153" s="1" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="AX153" s="1" t="s">
         <v>176</v>
@@ -28897,7 +28897,7 @@
         <v>555</v>
       </c>
       <c r="AW154" s="1" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="AX154" s="1" t="s">
         <v>177</v>
@@ -29029,7 +29029,7 @@
         <v>1192</v>
       </c>
       <c r="AW155" s="1" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="AX155" s="1" t="s">
         <v>178</v>
@@ -29164,7 +29164,7 @@
         <v>1390</v>
       </c>
       <c r="AW156" s="1" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="AX156" s="1" t="s">
         <v>179</v>
@@ -29296,7 +29296,7 @@
         <v>1392</v>
       </c>
       <c r="AW157" s="1" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="AX157" s="1" t="s">
         <v>180</v>
@@ -29316,7 +29316,7 @@
         <v>1381</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>1382</v>
@@ -29428,7 +29428,7 @@
         <v>1395</v>
       </c>
       <c r="AW158" s="1" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="AX158" s="1" t="s">
         <v>181</v>
@@ -29566,7 +29566,7 @@
         <v>494</v>
       </c>
       <c r="AW159" s="1" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="AX159" s="1" t="s">
         <v>1404</v>
@@ -29698,10 +29698,10 @@
         <v>556</v>
       </c>
       <c r="AW160" s="1" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="AX160" s="1" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="AY160" s="1" t="s">
         <v>423</v>
@@ -29827,10 +29827,10 @@
         <v>314</v>
       </c>
       <c r="AV161" s="1" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="AW161" s="1" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="AX161" s="1" t="s">
         <v>182</v>
@@ -29963,7 +29963,7 @@
         <v>1411</v>
       </c>
       <c r="AW162" s="1" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="AX162" s="1" t="s">
         <v>187</v>
@@ -30095,7 +30095,7 @@
         <v>1267</v>
       </c>
       <c r="AW163" s="1" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="AX163" s="1" t="s">
         <v>188</v>
@@ -30227,7 +30227,7 @@
         <v>555</v>
       </c>
       <c r="AW164" s="1" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="AX164" s="1" t="s">
         <v>189</v>
@@ -30363,7 +30363,7 @@
         <v>1417</v>
       </c>
       <c r="AW165" s="1" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="AX165" s="1" t="s">
         <v>191</v>
@@ -30495,7 +30495,7 @@
         <v>1294</v>
       </c>
       <c r="AW166" s="1" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="AX166" s="1" t="s">
         <v>192</v>
@@ -30628,7 +30628,7 @@
         <v>1421</v>
       </c>
       <c r="AW167" s="1" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="AX167" s="1" t="s">
         <v>193</v>
@@ -30770,7 +30770,7 @@
         <v>1425</v>
       </c>
       <c r="AW168" s="1" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="AX168" s="1" t="s">
         <v>195</v>
@@ -30905,7 +30905,7 @@
         <v>507</v>
       </c>
       <c r="AW169" s="1" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="AX169" s="1" t="s">
         <v>1428</v>
@@ -31046,7 +31046,7 @@
         <v>517</v>
       </c>
       <c r="AW170" s="1" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="AX170" s="1" t="s">
         <v>496</v>
@@ -31178,7 +31178,7 @@
         <v>1435</v>
       </c>
       <c r="AW171" s="1" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="AX171" s="1" t="s">
         <v>196</v>
@@ -31310,7 +31310,7 @@
         <v>1442</v>
       </c>
       <c r="AW172" s="1" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="AX172" s="1" t="s">
         <v>201</v>
@@ -31445,7 +31445,7 @@
         <v>1446</v>
       </c>
       <c r="AW173" s="1" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="AX173" s="1" t="s">
         <v>203</v>
@@ -31577,7 +31577,7 @@
         <v>1192</v>
       </c>
       <c r="AW174" s="1" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="AX174" s="1" t="s">
         <v>204</v>
@@ -31709,7 +31709,7 @@
         <v>959</v>
       </c>
       <c r="AW175" s="1" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="AX175" s="1" t="s">
         <v>205</v>
@@ -31841,7 +31841,7 @@
         <v>555</v>
       </c>
       <c r="AW176" s="1" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="AX176" s="1" t="s">
         <v>206</v>
@@ -31973,7 +31973,7 @@
         <v>1452</v>
       </c>
       <c r="AW177" s="1" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="AX177" s="1" t="s">
         <v>207</v>
@@ -32109,7 +32109,7 @@
         <v>521</v>
       </c>
       <c r="AW178" s="1" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="AX178" s="1" t="s">
         <v>209</v>
@@ -32241,7 +32241,7 @@
         <v>523</v>
       </c>
       <c r="AW179" s="1" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="AX179" s="1" t="s">
         <v>1459</v>
@@ -32373,7 +32373,7 @@
         <v>522</v>
       </c>
       <c r="AW180" s="1" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="AX180" s="1" t="s">
         <v>1462</v>
@@ -32514,7 +32514,7 @@
         <v>518</v>
       </c>
       <c r="AW181" s="1" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="AX181" s="1" t="s">
         <v>1465</v>
@@ -32644,7 +32644,7 @@
         <v>1472</v>
       </c>
       <c r="AW182" s="1" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="AX182" s="1" t="s">
         <v>1473</v>
@@ -32779,7 +32779,7 @@
         <v>1477</v>
       </c>
       <c r="AW183" s="1" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="AX183" s="1" t="s">
         <v>212</v>
@@ -32914,7 +32914,7 @@
         <v>1479</v>
       </c>
       <c r="AW184" s="1" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="AX184" s="1" t="s">
         <v>213</v>
@@ -33046,7 +33046,7 @@
         <v>1481</v>
       </c>
       <c r="AW185" s="1" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="AX185" s="1" t="s">
         <v>214</v>
@@ -33187,7 +33187,7 @@
         <v>447</v>
       </c>
       <c r="AW186" s="1" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="AX186" s="1" t="s">
         <v>215</v>
@@ -33319,7 +33319,7 @@
         <v>1117</v>
       </c>
       <c r="AW187" s="1" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="AX187" s="1" t="s">
         <v>216</v>
@@ -33457,7 +33457,7 @@
         <v>535</v>
       </c>
       <c r="AW188" s="1" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="AX188" s="1" t="s">
         <v>218</v>
@@ -33595,7 +33595,7 @@
         <v>524</v>
       </c>
       <c r="AW189" s="1" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="AX189" s="1" t="s">
         <v>1492</v>
@@ -33736,7 +33736,7 @@
         <v>534</v>
       </c>
       <c r="AW190" s="1" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="AX190" s="1" t="s">
         <v>1495</v>
@@ -33880,7 +33880,7 @@
         <v>527</v>
       </c>
       <c r="AW191" s="1" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="AX191" s="1" t="s">
         <v>1499</v>
@@ -34015,7 +34015,7 @@
         <v>1505</v>
       </c>
       <c r="AW192" s="1" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="AX192" s="1" t="s">
         <v>221</v>
@@ -34147,7 +34147,7 @@
         <v>560</v>
       </c>
       <c r="AW193" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="AX193" s="1" t="s">
         <v>222</v>
@@ -34285,7 +34285,7 @@
         <v>1509</v>
       </c>
       <c r="AW194" s="1" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="AX194" s="1" t="s">
         <v>223</v>
@@ -34417,7 +34417,7 @@
         <v>1512</v>
       </c>
       <c r="AW195" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="AX195" s="1" t="s">
         <v>224</v>
@@ -34549,7 +34549,7 @@
         <v>555</v>
       </c>
       <c r="AW196" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="AX196" s="1" t="s">
         <v>225</v>
@@ -34681,7 +34681,7 @@
         <v>1516</v>
       </c>
       <c r="AW197" s="1" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="AX197" s="1" t="s">
         <v>226</v>
@@ -34819,7 +34819,7 @@
         <v>1520</v>
       </c>
       <c r="AW198" s="1" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="AX198" s="1" t="s">
         <v>229</v>
@@ -34951,7 +34951,7 @@
         <v>560</v>
       </c>
       <c r="AW199" s="1" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="AX199" s="1" t="s">
         <v>230</v>
@@ -35087,7 +35087,7 @@
         <v>532</v>
       </c>
       <c r="AW200" s="1" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="AX200" s="1" t="s">
         <v>1525</v>
@@ -35225,7 +35225,7 @@
         <v>1529</v>
       </c>
       <c r="AW201" s="1" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="AX201" s="1" t="s">
         <v>231</v>
@@ -35357,7 +35357,7 @@
         <v>1472</v>
       </c>
       <c r="AW202" s="1" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="AX202" s="1" t="s">
         <v>236</v>
@@ -35489,7 +35489,7 @@
         <v>1537</v>
       </c>
       <c r="AW203" s="1" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="AX203" s="1" t="s">
         <v>237</v>
@@ -35621,7 +35621,7 @@
         <v>1539</v>
       </c>
       <c r="AW204" s="1" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="AX204" s="1" t="s">
         <v>238</v>
@@ -35762,7 +35762,7 @@
         <v>1294</v>
       </c>
       <c r="AW205" s="1" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="AX205" s="1" t="s">
         <v>239</v>
@@ -35903,7 +35903,7 @@
         <v>1543</v>
       </c>
       <c r="AW206" s="1" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="AX206" s="1" t="s">
         <v>241</v>
@@ -36047,16 +36047,16 @@
         <v>1545</v>
       </c>
       <c r="AV207" s="1" t="s">
+        <v>2074</v>
+      </c>
+      <c r="AW207" s="1" t="s">
         <v>2075</v>
       </c>
-      <c r="AW207" s="1" t="s">
+      <c r="AX207" s="1" t="s">
         <v>2076</v>
       </c>
-      <c r="AX207" s="1" t="s">
+      <c r="AY207" s="1" t="s">
         <v>2077</v>
-      </c>
-      <c r="AY207" s="1" t="s">
-        <v>2078</v>
       </c>
       <c r="AZ207" s="3" t="s">
         <v>1083</v>
@@ -36182,7 +36182,7 @@
         <v>1547</v>
       </c>
       <c r="AW208" s="1" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="AX208" s="1" t="s">
         <v>243</v>
@@ -36323,13 +36323,13 @@
         <v>539</v>
       </c>
       <c r="AW209" s="1" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="AX209" s="1" t="s">
         <v>1550</v>
       </c>
       <c r="AY209" s="1" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="AZ209" s="3" t="s">
         <v>1110</v>
@@ -36470,13 +36470,13 @@
         <v>598</v>
       </c>
       <c r="AW210" s="1" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="AX210" s="1" t="s">
         <v>1554</v>
       </c>
       <c r="AY210" s="1" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AZ210" s="3" t="s">
         <v>1252</v>
@@ -36611,7 +36611,7 @@
         <v>1557</v>
       </c>
       <c r="AW211" s="1" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="AX211" s="1" t="s">
         <v>244</v>
@@ -36743,7 +36743,7 @@
         <v>1220</v>
       </c>
       <c r="AW212" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="AX212" s="1" t="s">
         <v>247</v>
@@ -36881,7 +36881,7 @@
         <v>1562</v>
       </c>
       <c r="AW213" s="1" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="AX213" s="1" t="s">
         <v>249</v>
@@ -37016,7 +37016,7 @@
         <v>1565</v>
       </c>
       <c r="AW214" s="1" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="AX214" s="1" t="s">
         <v>250</v>
@@ -37148,7 +37148,7 @@
         <v>1294</v>
       </c>
       <c r="AW215" s="1" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="AX215" s="1" t="s">
         <v>252</v>
@@ -37280,7 +37280,7 @@
         <v>1567</v>
       </c>
       <c r="AW216" s="1" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="AX216" s="1" t="s">
         <v>253</v>
@@ -37412,7 +37412,7 @@
         <v>1569</v>
       </c>
       <c r="AW217" s="1" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="AX217" s="1" t="s">
         <v>254</v>
@@ -37565,13 +37565,13 @@
         <v>1572</v>
       </c>
       <c r="AW218" s="1" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="AX218" s="1" t="s">
         <v>257</v>
       </c>
       <c r="AY218" s="1" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="AZ218" s="3" t="s">
         <v>1046</v>
@@ -37844,13 +37844,13 @@
         <v>556</v>
       </c>
       <c r="AW220" s="1" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="AX220" s="1" t="s">
+        <v>2091</v>
+      </c>
+      <c r="AY220" s="1" t="s">
         <v>2092</v>
-      </c>
-      <c r="AY220" s="1" t="s">
-        <v>2093</v>
       </c>
       <c r="AZ220" s="3" t="s">
         <v>1578</v>
@@ -37976,7 +37976,7 @@
         <v>560</v>
       </c>
       <c r="AW221" s="1" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="AX221" s="1" t="s">
         <v>258</v>
@@ -38111,10 +38111,10 @@
         <v>314</v>
       </c>
       <c r="AV222" s="1" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="AW222" s="1" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="AX222" s="1" t="s">
         <v>261</v>
@@ -38255,7 +38255,7 @@
         <v>560</v>
       </c>
       <c r="AW223" s="1" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="AX223" s="1" t="s">
         <v>263</v>
@@ -38396,7 +38396,7 @@
         <v>556</v>
       </c>
       <c r="AW224" s="1" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="AX224" s="1" t="s">
         <v>264</v>
@@ -38537,7 +38537,7 @@
         <v>1587</v>
       </c>
       <c r="AW225" s="1" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="AX225" s="1" t="s">
         <v>265</v>
@@ -38678,7 +38678,7 @@
         <v>1585</v>
       </c>
       <c r="AW226" s="1" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="AX226" s="1" t="s">
         <v>266</v>
@@ -38807,13 +38807,13 @@
         <v>314</v>
       </c>
       <c r="AV227" s="1" t="s">
+        <v>2104</v>
+      </c>
+      <c r="AW227" s="1" t="s">
         <v>2105</v>
       </c>
-      <c r="AW227" s="1" t="s">
-        <v>2106</v>
-      </c>
       <c r="AX227" s="1" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="AY227" s="1" t="s">
         <v>423</v>
@@ -38945,10 +38945,10 @@
         <v>314</v>
       </c>
       <c r="AV228" s="1" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="AW228" s="1" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AX228" s="1" t="s">
         <v>267</v>
@@ -39077,13 +39077,13 @@
         <v>314</v>
       </c>
       <c r="AV229" s="1" t="s">
+        <v>2106</v>
+      </c>
+      <c r="AW229" s="1" t="s">
         <v>2107</v>
       </c>
-      <c r="AW229" s="1" t="s">
-        <v>2108</v>
-      </c>
       <c r="AX229" s="1" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="AY229" s="1" t="s">
         <v>423</v>
@@ -39227,7 +39227,7 @@
         <v>1596</v>
       </c>
       <c r="AW230" s="1" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="AX230" s="1" t="s">
         <v>268</v>
@@ -39374,7 +39374,7 @@
         <v>560</v>
       </c>
       <c r="AW231" s="1" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="AX231" s="1" t="s">
         <v>269</v>
@@ -39442,7 +39442,7 @@
         <v>1835</v>
       </c>
       <c r="AW232" s="1" t="s">
-        <v>1836</v>
+        <v>2113</v>
       </c>
       <c r="AY232" s="1" t="s">
         <v>314</v>
@@ -39566,10 +39566,10 @@
         <v>314</v>
       </c>
       <c r="AV234" s="1" t="s">
+        <v>2109</v>
+      </c>
+      <c r="AW234" s="1" t="s">
         <v>2110</v>
-      </c>
-      <c r="AW234" s="1" t="s">
-        <v>2111</v>
       </c>
       <c r="AY234" s="1" t="s">
         <v>314</v>
@@ -39678,10 +39678,10 @@
         <v>314</v>
       </c>
       <c r="AV236" s="1" t="s">
+        <v>1836</v>
+      </c>
+      <c r="AW236" s="1" t="s">
         <v>1837</v>
-      </c>
-      <c r="AW236" s="1" t="s">
-        <v>1838</v>
       </c>
       <c r="AY236" s="1" t="s">
         <v>314</v>
@@ -39734,10 +39734,10 @@
         <v>314</v>
       </c>
       <c r="AV237" s="1" t="s">
+        <v>1838</v>
+      </c>
+      <c r="AW237" s="1" t="s">
         <v>1839</v>
-      </c>
-      <c r="AW237" s="1" t="s">
-        <v>1840</v>
       </c>
       <c r="AY237" s="1" t="s">
         <v>314</v>
@@ -39967,16 +39967,16 @@
         <v>1620</v>
       </c>
       <c r="AN241" s="1" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="AU241" s="1" t="s">
         <v>314</v>
       </c>
       <c r="AV241" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="AW241" s="1" t="s">
         <v>1845</v>
-      </c>
-      <c r="AW241" s="1" t="s">
-        <v>1846</v>
       </c>
       <c r="AY241" s="1" t="s">
         <v>314</v>
@@ -42399,7 +42399,7 @@
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
@@ -42429,7 +42429,7 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
@@ -42809,12 +42809,12 @@
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
@@ -42954,7 +42954,7 @@
     </row>
     <row r="158" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4AB3AF-FC5C-465E-9958-F9EACC1392A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B20C528-7178-4110-BE9D-5C1ADA8DF89F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -6481,14 +6481,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"pool":"random","arch":"cross","kind":"active","color":"#7ee02a","repo":1,"throwRange":12,"dur":6,"balls":7,"ballR":1.8,"dmg":0.4,"tick":0.25,"warn":0.9,"dot":{"id":"poison","name":"中毒","pct":25,"dur":3},"len":36,"speed":12,"hubR":4}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>地面先生出一個綠色毒圈（半徑 4 米），隨後從中心向上下左右四個方向「長出」一排排毒水球（每秒 12 米、最長 36 米），持續 6 秒；碰到毒球或站在毒圈裡會受到高額毒素傷害。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>en-stone-wall-0</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -7577,6 +7569,14 @@
   </si>
   <si>
     <t>和同群夥伴之間拉出由一節一節火環扣成的橘黃火焰鎖鏈（2 隻連一條線、3 隻連成三角形、4 隻連成四邊形，以此類推）（鏈環數隨距離增減），持續到怪物死亡；每 3~6 秒隨機跑位，用火鏈掃過你。碰到或穿過火鏈會承受高頻率的連續火焰傷害。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"pool":"random","arch":"cross","kind":"active","color":"#7ee02a","repo":1,"throwRange":12,"dur":16,"balls":5,"ballR":4,"dmg":0.4,"tick":0.25,"warn":0.9,"dot":{"id":"poison","name":"中毒","pct":25,"dur":3},"len":36,"speed":12,"hubR":4}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地面先生出一個綠色毒圈（半徑 4 米），隨後從中心向上下左右四個方向「長出」一排排毒水球（每秒 12 米、最長 36 米），持續 16 秒；每顆毒水球和中心毒圈一樣大、相鄰兩顆略有重疊；碰到毒球或站在毒圈裡會受到高額毒素傷害。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -8357,7 +8357,7 @@
         <v>554</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="AX2" s="1" t="s">
         <v>30</v>
@@ -8491,7 +8491,7 @@
         <v>1023</v>
       </c>
       <c r="AW3" s="1" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="AX3" s="1" t="s">
         <v>31</v>
@@ -8625,7 +8625,7 @@
         <v>1025</v>
       </c>
       <c r="AW4" s="1" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="AX4" s="1" t="s">
         <v>32</v>
@@ -8759,7 +8759,7 @@
         <v>555</v>
       </c>
       <c r="AW5" s="1" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="AX5" s="1" t="s">
         <v>33</v>
@@ -8893,7 +8893,7 @@
         <v>556</v>
       </c>
       <c r="AW6" s="1" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="AX6" s="1" t="s">
         <v>34</v>
@@ -9027,7 +9027,7 @@
         <v>557</v>
       </c>
       <c r="AW7" s="1" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="AX7" s="1" t="s">
         <v>35</v>
@@ -9158,10 +9158,10 @@
         <v>314</v>
       </c>
       <c r="AV8" s="1" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AW8" s="1" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="AX8" s="1" t="s">
         <v>36</v>
@@ -9295,7 +9295,7 @@
         <v>1036</v>
       </c>
       <c r="AW9" s="1" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="AX9" s="1" t="s">
         <v>37</v>
@@ -9435,7 +9435,7 @@
         <v>1040</v>
       </c>
       <c r="AW10" s="1" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="AX10" s="1" t="s">
         <v>38</v>
@@ -9569,7 +9569,7 @@
         <v>558</v>
       </c>
       <c r="AW11" s="1" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="AX11" s="1" t="s">
         <v>39</v>
@@ -9703,7 +9703,7 @@
         <v>554</v>
       </c>
       <c r="AW12" s="1" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="AX12" s="1" t="s">
         <v>9</v>
@@ -9837,7 +9837,7 @@
         <v>934</v>
       </c>
       <c r="AW13" s="1" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="AX13" s="1" t="s">
         <v>10</v>
@@ -9971,7 +9971,7 @@
         <v>941</v>
       </c>
       <c r="AW14" s="1" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="AX14" s="1" t="s">
         <v>11</v>
@@ -10105,7 +10105,7 @@
         <v>946</v>
       </c>
       <c r="AW15" s="1" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="AX15" s="1" t="s">
         <v>12</v>
@@ -10239,7 +10239,7 @@
         <v>953</v>
       </c>
       <c r="AW16" s="1" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="AX16" s="1" t="s">
         <v>13</v>
@@ -10373,7 +10373,7 @@
         <v>959</v>
       </c>
       <c r="AW17" s="1" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
       <c r="AX17" s="1" t="s">
         <v>14</v>
@@ -10507,7 +10507,7 @@
         <v>551</v>
       </c>
       <c r="AW18" s="1" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="AX18" s="1" t="s">
         <v>964</v>
@@ -10647,7 +10647,7 @@
         <v>552</v>
       </c>
       <c r="AW19" s="1" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="AX19" s="1" t="s">
         <v>971</v>
@@ -10784,7 +10784,7 @@
         <v>978</v>
       </c>
       <c r="AW20" s="1" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="AX20" s="1" t="s">
         <v>15</v>
@@ -10918,7 +10918,7 @@
         <v>984</v>
       </c>
       <c r="AW21" s="1" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="AX21" s="1" t="s">
         <v>985</v>
@@ -11052,7 +11052,7 @@
         <v>990</v>
       </c>
       <c r="AW22" s="1" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="AX22" s="1" t="s">
         <v>18</v>
@@ -11186,7 +11186,7 @@
         <v>959</v>
       </c>
       <c r="AW23" s="1" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="AX23" s="1" t="s">
         <v>19</v>
@@ -11320,7 +11320,7 @@
         <v>994</v>
       </c>
       <c r="AW24" s="1" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="AX24" s="1" t="s">
         <v>20</v>
@@ -11454,7 +11454,7 @@
         <v>996</v>
       </c>
       <c r="AW25" s="1" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="AX25" s="1" t="s">
         <v>21</v>
@@ -11587,7 +11587,7 @@
         <v>1000</v>
       </c>
       <c r="AW26" s="1" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="AX26" s="1" t="s">
         <v>22</v>
@@ -11719,7 +11719,7 @@
         <v>959</v>
       </c>
       <c r="AW27" s="1" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
       <c r="AX27" s="1" t="s">
         <v>23</v>
@@ -13750,7 +13750,7 @@
         <v>1082</v>
       </c>
       <c r="AV42" s="1" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="AW42" s="1" t="s">
         <v>54</v>
@@ -13880,7 +13880,7 @@
         <v>314</v>
       </c>
       <c r="AV43" s="1" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AW43" s="1" t="s">
         <v>55</v>
@@ -14292,7 +14292,7 @@
         <v>314</v>
       </c>
       <c r="AV46" s="1" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="AW46" s="1" t="s">
         <v>59</v>
@@ -14563,7 +14563,7 @@
         <v>314</v>
       </c>
       <c r="AV48" s="1" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AW48" s="1" t="s">
         <v>62</v>
@@ -14982,16 +14982,16 @@
         <v>314</v>
       </c>
       <c r="AV51" s="1" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="AW51" s="1" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="AX51" s="1" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="AY51" s="1" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="AZ51" s="3" t="s">
         <v>1110</v>
@@ -15115,7 +15115,7 @@
         <v>1114</v>
       </c>
       <c r="AW52" s="1" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="AX52" s="1" t="s">
         <v>1115</v>
@@ -15247,7 +15247,7 @@
         <v>1117</v>
       </c>
       <c r="AW53" s="1" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="AX53" s="1" t="s">
         <v>1118</v>
@@ -15379,7 +15379,7 @@
         <v>1121</v>
       </c>
       <c r="AW54" s="1" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="AX54" s="1" t="s">
         <v>67</v>
@@ -15519,7 +15519,7 @@
         <v>1123</v>
       </c>
       <c r="AW55" s="1" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="AX55" s="1" t="s">
         <v>68</v>
@@ -15659,7 +15659,7 @@
         <v>345</v>
       </c>
       <c r="AW56" s="1" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="AX56" s="1" t="s">
         <v>69</v>
@@ -15793,7 +15793,7 @@
         <v>1128</v>
       </c>
       <c r="AW57" s="1" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="AX57" s="1" t="s">
         <v>70</v>
@@ -15931,7 +15931,7 @@
         <v>1130</v>
       </c>
       <c r="AW58" s="1" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="AX58" s="1" t="s">
         <v>1131</v>
@@ -16065,7 +16065,7 @@
         <v>444</v>
       </c>
       <c r="AW59" s="1" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="AX59" s="1" t="s">
         <v>1135</v>
@@ -16202,10 +16202,10 @@
         <v>594</v>
       </c>
       <c r="AW60" s="1" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="AX60" s="1" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="AY60" s="1" t="s">
         <v>423</v>
@@ -16336,7 +16336,7 @@
         <v>1036</v>
       </c>
       <c r="AW61" s="1" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="AX61" s="1" t="s">
         <v>71</v>
@@ -16470,10 +16470,10 @@
         <v>1147</v>
       </c>
       <c r="AW62" s="1" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="AX62" s="1" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="AY62" s="1" t="s">
         <v>423</v>
@@ -16604,7 +16604,7 @@
         <v>1149</v>
       </c>
       <c r="AW63" s="1" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="AX63" s="1" t="s">
         <v>74</v>
@@ -16738,7 +16738,7 @@
         <v>1151</v>
       </c>
       <c r="AW64" s="1" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="AX64" s="1" t="s">
         <v>75</v>
@@ -16872,7 +16872,7 @@
         <v>525</v>
       </c>
       <c r="AW65" s="1" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="AX65" s="1" t="s">
         <v>76</v>
@@ -17009,7 +17009,7 @@
         <v>1157</v>
       </c>
       <c r="AW66" s="1" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="AX66" s="1" t="s">
         <v>78</v>
@@ -17143,7 +17143,7 @@
         <v>447</v>
       </c>
       <c r="AW67" s="1" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="AX67" s="1" t="s">
         <v>79</v>
@@ -17277,7 +17277,7 @@
         <v>448</v>
       </c>
       <c r="AW68" s="1" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="AX68" s="1" t="s">
         <v>80</v>
@@ -17417,10 +17417,10 @@
         <v>314</v>
       </c>
       <c r="AV69" s="1" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="AW69" s="1" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="AX69" s="1" t="s">
         <v>81</v>
@@ -17704,13 +17704,13 @@
         <v>314</v>
       </c>
       <c r="AV71" s="1" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="AW71" s="1" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="AX71" s="1" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="AY71" s="1" t="s">
         <v>423</v>
@@ -17853,7 +17853,7 @@
         <v>1176</v>
       </c>
       <c r="AW72" s="1" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="AX72" s="1" t="s">
         <v>85</v>
@@ -17987,7 +17987,7 @@
         <v>1036</v>
       </c>
       <c r="AW73" s="1" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="AX73" s="1" t="s">
         <v>87</v>
@@ -18119,7 +18119,7 @@
         <v>1036</v>
       </c>
       <c r="AW74" s="1" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="AX74" s="1" t="s">
         <v>88</v>
@@ -18251,7 +18251,7 @@
         <v>1183</v>
       </c>
       <c r="AW75" s="1" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="AX75" s="1" t="s">
         <v>89</v>
@@ -18383,7 +18383,7 @@
         <v>1036</v>
       </c>
       <c r="AW76" s="1" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="AX76" s="1" t="s">
         <v>90</v>
@@ -18512,10 +18512,10 @@
         <v>314</v>
       </c>
       <c r="AV77" s="1" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="AW77" s="1" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="AX77" s="1" t="s">
         <v>91</v>
@@ -18651,13 +18651,13 @@
         <v>314</v>
       </c>
       <c r="AV78" s="1" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="AW78" s="1" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="AX78" s="1" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="AY78" s="1" t="s">
         <v>1177</v>
@@ -18792,7 +18792,7 @@
         <v>1192</v>
       </c>
       <c r="AW79" s="1" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="AX79" s="1" t="s">
         <v>92</v>
@@ -18933,10 +18933,10 @@
         <v>314</v>
       </c>
       <c r="AV80" s="1" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="AW80" s="1" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="AX80" s="1" t="s">
         <v>451</v>
@@ -19077,13 +19077,13 @@
         <v>314</v>
       </c>
       <c r="AV81" s="1" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="AW81" s="1" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="AX81" s="1" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="AY81" s="1" t="s">
         <v>1177</v>
@@ -19212,7 +19212,7 @@
         <v>1205</v>
       </c>
       <c r="AW82" s="1" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="AX82" s="1" t="s">
         <v>97</v>
@@ -19347,7 +19347,7 @@
         <v>1208</v>
       </c>
       <c r="AW83" s="1" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="AX83" s="1" t="s">
         <v>98</v>
@@ -19479,7 +19479,7 @@
         <v>1210</v>
       </c>
       <c r="AW84" s="1" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="AX84" s="1" t="s">
         <v>99</v>
@@ -19611,7 +19611,7 @@
         <v>959</v>
       </c>
       <c r="AW85" s="1" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="AX85" s="1" t="s">
         <v>100</v>
@@ -19743,7 +19743,7 @@
         <v>1096</v>
       </c>
       <c r="AW86" s="1" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="AX86" s="1" t="s">
         <v>102</v>
@@ -19878,13 +19878,13 @@
         <v>314</v>
       </c>
       <c r="AV87" s="1" t="s">
+        <v>1924</v>
+      </c>
+      <c r="AW87" s="1" t="s">
         <v>1926</v>
       </c>
-      <c r="AW87" s="1" t="s">
-        <v>1928</v>
-      </c>
       <c r="AX87" s="1" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="AY87" s="1" t="s">
         <v>423</v>
@@ -20013,7 +20013,7 @@
         <v>1220</v>
       </c>
       <c r="AW88" s="1" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="AX88" s="1" t="s">
         <v>104</v>
@@ -20145,7 +20145,7 @@
         <v>1224</v>
       </c>
       <c r="AW89" s="1" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="AX89" s="1" t="s">
         <v>105</v>
@@ -20289,7 +20289,7 @@
         <v>575</v>
       </c>
       <c r="AW90" s="1" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="AX90" s="1" t="s">
         <v>107</v>
@@ -20421,7 +20421,7 @@
         <v>574</v>
       </c>
       <c r="AW91" s="1" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
       <c r="AX91" s="1" t="s">
         <v>108</v>
@@ -20556,7 +20556,7 @@
         <v>1235</v>
       </c>
       <c r="AW92" s="1" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="AX92" s="1" t="s">
         <v>112</v>
@@ -20688,7 +20688,7 @@
         <v>1086</v>
       </c>
       <c r="AW93" s="1" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="AX93" s="1" t="s">
         <v>113</v>
@@ -20817,10 +20817,10 @@
         <v>314</v>
       </c>
       <c r="AV94" s="1" t="s">
+        <v>1931</v>
+      </c>
+      <c r="AW94" s="1" t="s">
         <v>1933</v>
-      </c>
-      <c r="AW94" s="1" t="s">
-        <v>1935</v>
       </c>
       <c r="AX94" s="1" t="s">
         <v>114</v>
@@ -20955,7 +20955,7 @@
         <v>1240</v>
       </c>
       <c r="AW95" s="1" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="AX95" s="1" t="s">
         <v>115</v>
@@ -21099,7 +21099,7 @@
         <v>1192</v>
       </c>
       <c r="AW96" s="1" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="AX96" s="1" t="s">
         <v>116</v>
@@ -21231,7 +21231,7 @@
         <v>1244</v>
       </c>
       <c r="AW97" s="1" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="AX97" s="1" t="s">
         <v>117</v>
@@ -21366,7 +21366,7 @@
         <v>1246</v>
       </c>
       <c r="AW98" s="1" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="AX98" s="1" t="s">
         <v>119</v>
@@ -21507,7 +21507,7 @@
         <v>1250</v>
       </c>
       <c r="AW99" s="1" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="AX99" s="1" t="s">
         <v>465</v>
@@ -21642,10 +21642,10 @@
         <v>314</v>
       </c>
       <c r="AV100" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="AW100" s="1" t="s">
         <v>1941</v>
-      </c>
-      <c r="AW100" s="1" t="s">
-        <v>1943</v>
       </c>
       <c r="AX100" s="1" t="s">
         <v>121</v>
@@ -21783,7 +21783,7 @@
         <v>464</v>
       </c>
       <c r="AW101" s="1" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="AX101" s="1" t="s">
         <v>1258</v>
@@ -21921,7 +21921,7 @@
         <v>1265</v>
       </c>
       <c r="AW102" s="1" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="AX102" s="1" t="s">
         <v>124</v>
@@ -22053,7 +22053,7 @@
         <v>1267</v>
       </c>
       <c r="AW103" s="1" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="AX103" s="1" t="s">
         <v>125</v>
@@ -22191,7 +22191,7 @@
         <v>1269</v>
       </c>
       <c r="AW104" s="1" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="AX104" s="1" t="s">
         <v>127</v>
@@ -22323,7 +22323,7 @@
         <v>1271</v>
       </c>
       <c r="AW105" s="1" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="AX105" s="1" t="s">
         <v>128</v>
@@ -22455,7 +22455,7 @@
         <v>1036</v>
       </c>
       <c r="AW106" s="1" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="AX106" s="1" t="s">
         <v>129</v>
@@ -22584,10 +22584,10 @@
         <v>314</v>
       </c>
       <c r="AV107" s="1" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="AW107" s="1" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="AX107" s="1" t="s">
         <v>131</v>
@@ -22719,10 +22719,10 @@
         <v>1275</v>
       </c>
       <c r="AW108" s="1" t="s">
+        <v>1949</v>
+      </c>
+      <c r="AX108" s="1" t="s">
         <v>1951</v>
-      </c>
-      <c r="AX108" s="1" t="s">
-        <v>1953</v>
       </c>
       <c r="AY108" s="1" t="s">
         <v>423</v>
@@ -22854,7 +22854,7 @@
         <v>314</v>
       </c>
       <c r="AV109" s="1" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="AW109" s="1" t="s">
         <v>132</v>
@@ -22992,13 +22992,13 @@
         <v>1207</v>
       </c>
       <c r="AV110" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="AW110" s="1" t="s">
+        <v>1953</v>
+      </c>
+      <c r="AX110" s="1" t="s">
         <v>1954</v>
-      </c>
-      <c r="AW110" s="1" t="s">
-        <v>1955</v>
-      </c>
-      <c r="AX110" s="1" t="s">
-        <v>1956</v>
       </c>
       <c r="AY110" s="1" t="s">
         <v>472</v>
@@ -23139,7 +23139,7 @@
         <v>467</v>
       </c>
       <c r="AW111" s="1" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="AX111" s="1" t="s">
         <v>466</v>
@@ -23274,10 +23274,10 @@
         <v>314</v>
       </c>
       <c r="AV112" s="1" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="AW112" s="1" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="AX112" s="1" t="s">
         <v>136</v>
@@ -23409,7 +23409,7 @@
         <v>1036</v>
       </c>
       <c r="AW113" s="1" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="AX113" s="1" t="s">
         <v>137</v>
@@ -23541,7 +23541,7 @@
         <v>1289</v>
       </c>
       <c r="AW114" s="1" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="AX114" s="1" t="s">
         <v>138</v>
@@ -23673,10 +23673,10 @@
         <v>1267</v>
       </c>
       <c r="AW115" s="1" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="AX115" s="1" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="AY115" s="1" t="s">
         <v>423</v>
@@ -23805,7 +23805,7 @@
         <v>525</v>
       </c>
       <c r="AW116" s="1" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="AX116" s="1" t="s">
         <v>139</v>
@@ -23940,10 +23940,10 @@
         <v>314</v>
       </c>
       <c r="AV117" s="1" t="s">
+        <v>1962</v>
+      </c>
+      <c r="AW117" s="1" t="s">
         <v>1964</v>
-      </c>
-      <c r="AW117" s="1" t="s">
-        <v>1966</v>
       </c>
       <c r="AX117" s="1" t="s">
         <v>140</v>
@@ -24075,7 +24075,7 @@
         <v>1294</v>
       </c>
       <c r="AW118" s="1" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="AX118" s="1" t="s">
         <v>142</v>
@@ -24225,7 +24225,7 @@
         <v>584</v>
       </c>
       <c r="AW119" s="1" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="AX119" s="1" t="s">
         <v>1299</v>
@@ -24354,10 +24354,10 @@
         <v>314</v>
       </c>
       <c r="AV120" s="1" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="AW120" s="1" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="AX120" s="1" t="s">
         <v>143</v>
@@ -24492,13 +24492,13 @@
         <v>1308</v>
       </c>
       <c r="AV121" s="1" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AW121" s="1" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="AX121" s="1" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="AY121" s="1" t="s">
         <v>423</v>
@@ -24627,13 +24627,13 @@
         <v>1313</v>
       </c>
       <c r="AV122" s="1" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="AW122" s="1" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="AX122" s="1" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="AY122" s="1" t="s">
         <v>423</v>
@@ -24762,10 +24762,10 @@
         <v>1267</v>
       </c>
       <c r="AW123" s="1" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="AX123" s="1" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="AY123" s="1" t="s">
         <v>423</v>
@@ -24897,7 +24897,7 @@
         <v>1318</v>
       </c>
       <c r="AW124" s="1" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="AX124" s="1" t="s">
         <v>146</v>
@@ -25161,7 +25161,7 @@
         <v>1321</v>
       </c>
       <c r="AW126" s="1" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="AX126" s="1" t="s">
         <v>148</v>
@@ -25293,10 +25293,10 @@
         <v>1323</v>
       </c>
       <c r="AW127" s="1" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="AX127" s="1" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AY127" s="1" t="s">
         <v>423</v>
@@ -25428,7 +25428,7 @@
         <v>1327</v>
       </c>
       <c r="AW128" s="1" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="AX128" s="1" t="s">
         <v>149</v>
@@ -25563,7 +25563,7 @@
         <v>1331</v>
       </c>
       <c r="AW129" s="1" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="AX129" s="1" t="s">
         <v>150</v>
@@ -25695,25 +25695,25 @@
         <v>482</v>
       </c>
       <c r="AR130" s="1" t="s">
+        <v>1984</v>
+      </c>
+      <c r="AT130" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AU130" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AV130" s="1" t="s">
+        <v>1981</v>
+      </c>
+      <c r="AW130" s="1" t="s">
         <v>1986</v>
       </c>
-      <c r="AT130" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AU130" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AV130" s="1" t="s">
+      <c r="AX130" s="1" t="s">
+        <v>1982</v>
+      </c>
+      <c r="AY130" s="1" t="s">
         <v>1983</v>
-      </c>
-      <c r="AW130" s="1" t="s">
-        <v>1988</v>
-      </c>
-      <c r="AX130" s="1" t="s">
-        <v>1984</v>
-      </c>
-      <c r="AY130" s="1" t="s">
-        <v>1985</v>
       </c>
       <c r="AZ130" s="3" t="s">
         <v>1276</v>
@@ -25836,10 +25836,10 @@
         <v>314</v>
       </c>
       <c r="AV131" s="1" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="AW131" s="1" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="AX131" s="1" t="s">
         <v>151</v>
@@ -25968,10 +25968,10 @@
         <v>314</v>
       </c>
       <c r="AV132" s="1" t="s">
+        <v>1985</v>
+      </c>
+      <c r="AW132" s="1" t="s">
         <v>1987</v>
-      </c>
-      <c r="AW132" s="1" t="s">
-        <v>1989</v>
       </c>
       <c r="AX132" s="1" t="s">
         <v>154</v>
@@ -26103,7 +26103,7 @@
         <v>1267</v>
       </c>
       <c r="AW133" s="1" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="AX133" s="1" t="s">
         <v>155</v>
@@ -26235,7 +26235,7 @@
         <v>499</v>
       </c>
       <c r="AW134" s="1" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="AX134" s="1" t="s">
         <v>156</v>
@@ -26367,7 +26367,7 @@
         <v>499</v>
       </c>
       <c r="AW135" s="1" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="AX135" s="1" t="s">
         <v>157</v>
@@ -26499,7 +26499,7 @@
         <v>587</v>
       </c>
       <c r="AW136" s="1" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="AX136" s="1" t="s">
         <v>1343</v>
@@ -26631,7 +26631,7 @@
         <v>1347</v>
       </c>
       <c r="AW137" s="1" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="AX137" s="1" t="s">
         <v>158</v>
@@ -26760,19 +26760,19 @@
         <v>314</v>
       </c>
       <c r="AT138" s="1" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="AU138" s="1" t="s">
         <v>314</v>
       </c>
       <c r="AV138" s="1" t="s">
+        <v>1993</v>
+      </c>
+      <c r="AW138" s="1" t="s">
+        <v>1997</v>
+      </c>
+      <c r="AX138" s="1" t="s">
         <v>1995</v>
-      </c>
-      <c r="AW138" s="1" t="s">
-        <v>1999</v>
-      </c>
-      <c r="AX138" s="1" t="s">
-        <v>1997</v>
       </c>
       <c r="AY138" s="1" t="s">
         <v>423</v>
@@ -26901,7 +26901,7 @@
         <v>595</v>
       </c>
       <c r="AW139" s="1" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="AX139" s="1" t="s">
         <v>1352</v>
@@ -27033,7 +27033,7 @@
         <v>484</v>
       </c>
       <c r="AW140" s="1" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="AX140" s="1" t="s">
         <v>159</v>
@@ -27165,7 +27165,7 @@
         <v>1358</v>
       </c>
       <c r="AW141" s="1" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="AX141" s="1" t="s">
         <v>160</v>
@@ -27295,7 +27295,7 @@
         <v>588</v>
       </c>
       <c r="AW142" s="1" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="AX142" s="1" t="s">
         <v>165</v>
@@ -27427,7 +27427,7 @@
         <v>560</v>
       </c>
       <c r="AW143" s="1" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="AX143" s="1" t="s">
         <v>166</v>
@@ -27559,7 +27559,7 @@
         <v>555</v>
       </c>
       <c r="AW144" s="1" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="AX144" s="1" t="s">
         <v>167</v>
@@ -27691,7 +27691,7 @@
         <v>1117</v>
       </c>
       <c r="AW145" s="1" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="AX145" s="1" t="s">
         <v>168</v>
@@ -27823,7 +27823,7 @@
         <v>1366</v>
       </c>
       <c r="AW146" s="1" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="AX146" s="1" t="s">
         <v>169</v>
@@ -27955,7 +27955,7 @@
         <v>560</v>
       </c>
       <c r="AW147" s="1" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AX147" s="1" t="s">
         <v>170</v>
@@ -28087,7 +28087,7 @@
         <v>596</v>
       </c>
       <c r="AW148" s="1" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="AX148" s="1" t="s">
         <v>171</v>
@@ -28234,7 +28234,7 @@
         <v>1374</v>
       </c>
       <c r="AW149" s="1" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="AX149" s="1" t="s">
         <v>172</v>
@@ -28372,7 +28372,7 @@
         <v>597</v>
       </c>
       <c r="AW150" s="1" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="AX150" s="1" t="s">
         <v>1379</v>
@@ -28392,7 +28392,7 @@
         <v>314</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>314</v>
@@ -28473,7 +28473,7 @@
         <v>314</v>
       </c>
       <c r="AE151" s="1" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="AF151" s="1" t="s">
         <v>314</v>
@@ -28501,10 +28501,10 @@
         <v>959</v>
       </c>
       <c r="AW151" s="1" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="AX151" s="1" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="AY151" s="1" t="s">
         <v>423</v>
@@ -28633,7 +28633,7 @@
         <v>1384</v>
       </c>
       <c r="AW152" s="1" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="AX152" s="1" t="s">
         <v>175</v>
@@ -28765,7 +28765,7 @@
         <v>555</v>
       </c>
       <c r="AW153" s="1" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="AX153" s="1" t="s">
         <v>176</v>
@@ -28897,7 +28897,7 @@
         <v>555</v>
       </c>
       <c r="AW154" s="1" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="AX154" s="1" t="s">
         <v>177</v>
@@ -29029,7 +29029,7 @@
         <v>1192</v>
       </c>
       <c r="AW155" s="1" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="AX155" s="1" t="s">
         <v>178</v>
@@ -29164,7 +29164,7 @@
         <v>1390</v>
       </c>
       <c r="AW156" s="1" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="AX156" s="1" t="s">
         <v>179</v>
@@ -29296,7 +29296,7 @@
         <v>1392</v>
       </c>
       <c r="AW157" s="1" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="AX157" s="1" t="s">
         <v>180</v>
@@ -29316,7 +29316,7 @@
         <v>1381</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>1382</v>
@@ -29428,7 +29428,7 @@
         <v>1395</v>
       </c>
       <c r="AW158" s="1" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="AX158" s="1" t="s">
         <v>181</v>
@@ -29566,7 +29566,7 @@
         <v>494</v>
       </c>
       <c r="AW159" s="1" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="AX159" s="1" t="s">
         <v>1404</v>
@@ -29698,10 +29698,10 @@
         <v>556</v>
       </c>
       <c r="AW160" s="1" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="AX160" s="1" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="AY160" s="1" t="s">
         <v>423</v>
@@ -29827,10 +29827,10 @@
         <v>314</v>
       </c>
       <c r="AV161" s="1" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="AW161" s="1" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="AX161" s="1" t="s">
         <v>182</v>
@@ -29963,7 +29963,7 @@
         <v>1411</v>
       </c>
       <c r="AW162" s="1" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AX162" s="1" t="s">
         <v>187</v>
@@ -30095,7 +30095,7 @@
         <v>1267</v>
       </c>
       <c r="AW163" s="1" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="AX163" s="1" t="s">
         <v>188</v>
@@ -30227,7 +30227,7 @@
         <v>555</v>
       </c>
       <c r="AW164" s="1" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="AX164" s="1" t="s">
         <v>189</v>
@@ -30363,7 +30363,7 @@
         <v>1417</v>
       </c>
       <c r="AW165" s="1" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="AX165" s="1" t="s">
         <v>191</v>
@@ -30495,7 +30495,7 @@
         <v>1294</v>
       </c>
       <c r="AW166" s="1" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="AX166" s="1" t="s">
         <v>192</v>
@@ -30628,7 +30628,7 @@
         <v>1421</v>
       </c>
       <c r="AW167" s="1" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="AX167" s="1" t="s">
         <v>193</v>
@@ -30770,7 +30770,7 @@
         <v>1425</v>
       </c>
       <c r="AW168" s="1" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="AX168" s="1" t="s">
         <v>195</v>
@@ -30905,7 +30905,7 @@
         <v>507</v>
       </c>
       <c r="AW169" s="1" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="AX169" s="1" t="s">
         <v>1428</v>
@@ -31046,7 +31046,7 @@
         <v>517</v>
       </c>
       <c r="AW170" s="1" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="AX170" s="1" t="s">
         <v>496</v>
@@ -31178,7 +31178,7 @@
         <v>1435</v>
       </c>
       <c r="AW171" s="1" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="AX171" s="1" t="s">
         <v>196</v>
@@ -31310,7 +31310,7 @@
         <v>1442</v>
       </c>
       <c r="AW172" s="1" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="AX172" s="1" t="s">
         <v>201</v>
@@ -31445,7 +31445,7 @@
         <v>1446</v>
       </c>
       <c r="AW173" s="1" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="AX173" s="1" t="s">
         <v>203</v>
@@ -31577,7 +31577,7 @@
         <v>1192</v>
       </c>
       <c r="AW174" s="1" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="AX174" s="1" t="s">
         <v>204</v>
@@ -31709,7 +31709,7 @@
         <v>959</v>
       </c>
       <c r="AW175" s="1" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="AX175" s="1" t="s">
         <v>205</v>
@@ -31841,7 +31841,7 @@
         <v>555</v>
       </c>
       <c r="AW176" s="1" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="AX176" s="1" t="s">
         <v>206</v>
@@ -31973,7 +31973,7 @@
         <v>1452</v>
       </c>
       <c r="AW177" s="1" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="AX177" s="1" t="s">
         <v>207</v>
@@ -32109,7 +32109,7 @@
         <v>521</v>
       </c>
       <c r="AW178" s="1" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="AX178" s="1" t="s">
         <v>209</v>
@@ -32241,7 +32241,7 @@
         <v>523</v>
       </c>
       <c r="AW179" s="1" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="AX179" s="1" t="s">
         <v>1459</v>
@@ -32373,7 +32373,7 @@
         <v>522</v>
       </c>
       <c r="AW180" s="1" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="AX180" s="1" t="s">
         <v>1462</v>
@@ -32514,7 +32514,7 @@
         <v>518</v>
       </c>
       <c r="AW181" s="1" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="AX181" s="1" t="s">
         <v>1465</v>
@@ -32644,7 +32644,7 @@
         <v>1472</v>
       </c>
       <c r="AW182" s="1" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="AX182" s="1" t="s">
         <v>1473</v>
@@ -32779,7 +32779,7 @@
         <v>1477</v>
       </c>
       <c r="AW183" s="1" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="AX183" s="1" t="s">
         <v>212</v>
@@ -32914,7 +32914,7 @@
         <v>1479</v>
       </c>
       <c r="AW184" s="1" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="AX184" s="1" t="s">
         <v>213</v>
@@ -33046,7 +33046,7 @@
         <v>1481</v>
       </c>
       <c r="AW185" s="1" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="AX185" s="1" t="s">
         <v>214</v>
@@ -33187,7 +33187,7 @@
         <v>447</v>
       </c>
       <c r="AW186" s="1" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="AX186" s="1" t="s">
         <v>215</v>
@@ -33319,7 +33319,7 @@
         <v>1117</v>
       </c>
       <c r="AW187" s="1" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="AX187" s="1" t="s">
         <v>216</v>
@@ -33457,7 +33457,7 @@
         <v>535</v>
       </c>
       <c r="AW188" s="1" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="AX188" s="1" t="s">
         <v>218</v>
@@ -33595,7 +33595,7 @@
         <v>524</v>
       </c>
       <c r="AW189" s="1" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="AX189" s="1" t="s">
         <v>1492</v>
@@ -33736,7 +33736,7 @@
         <v>534</v>
       </c>
       <c r="AW190" s="1" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="AX190" s="1" t="s">
         <v>1495</v>
@@ -33880,7 +33880,7 @@
         <v>527</v>
       </c>
       <c r="AW191" s="1" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="AX191" s="1" t="s">
         <v>1499</v>
@@ -34015,7 +34015,7 @@
         <v>1505</v>
       </c>
       <c r="AW192" s="1" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="AX192" s="1" t="s">
         <v>221</v>
@@ -34147,7 +34147,7 @@
         <v>560</v>
       </c>
       <c r="AW193" s="1" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="AX193" s="1" t="s">
         <v>222</v>
@@ -34285,7 +34285,7 @@
         <v>1509</v>
       </c>
       <c r="AW194" s="1" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="AX194" s="1" t="s">
         <v>223</v>
@@ -34417,7 +34417,7 @@
         <v>1512</v>
       </c>
       <c r="AW195" s="1" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="AX195" s="1" t="s">
         <v>224</v>
@@ -34549,7 +34549,7 @@
         <v>555</v>
       </c>
       <c r="AW196" s="1" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="AX196" s="1" t="s">
         <v>225</v>
@@ -34681,7 +34681,7 @@
         <v>1516</v>
       </c>
       <c r="AW197" s="1" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="AX197" s="1" t="s">
         <v>226</v>
@@ -34819,7 +34819,7 @@
         <v>1520</v>
       </c>
       <c r="AW198" s="1" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="AX198" s="1" t="s">
         <v>229</v>
@@ -34951,7 +34951,7 @@
         <v>560</v>
       </c>
       <c r="AW199" s="1" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="AX199" s="1" t="s">
         <v>230</v>
@@ -35087,7 +35087,7 @@
         <v>532</v>
       </c>
       <c r="AW200" s="1" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="AX200" s="1" t="s">
         <v>1525</v>
@@ -35225,7 +35225,7 @@
         <v>1529</v>
       </c>
       <c r="AW201" s="1" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="AX201" s="1" t="s">
         <v>231</v>
@@ -35357,7 +35357,7 @@
         <v>1472</v>
       </c>
       <c r="AW202" s="1" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="AX202" s="1" t="s">
         <v>236</v>
@@ -35489,7 +35489,7 @@
         <v>1537</v>
       </c>
       <c r="AW203" s="1" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="AX203" s="1" t="s">
         <v>237</v>
@@ -35621,7 +35621,7 @@
         <v>1539</v>
       </c>
       <c r="AW204" s="1" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="AX204" s="1" t="s">
         <v>238</v>
@@ -35762,7 +35762,7 @@
         <v>1294</v>
       </c>
       <c r="AW205" s="1" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="AX205" s="1" t="s">
         <v>239</v>
@@ -35903,7 +35903,7 @@
         <v>1543</v>
       </c>
       <c r="AW206" s="1" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="AX206" s="1" t="s">
         <v>241</v>
@@ -36047,16 +36047,16 @@
         <v>1545</v>
       </c>
       <c r="AV207" s="1" t="s">
+        <v>2072</v>
+      </c>
+      <c r="AW207" s="1" t="s">
+        <v>2073</v>
+      </c>
+      <c r="AX207" s="1" t="s">
         <v>2074</v>
       </c>
-      <c r="AW207" s="1" t="s">
+      <c r="AY207" s="1" t="s">
         <v>2075</v>
-      </c>
-      <c r="AX207" s="1" t="s">
-        <v>2076</v>
-      </c>
-      <c r="AY207" s="1" t="s">
-        <v>2077</v>
       </c>
       <c r="AZ207" s="3" t="s">
         <v>1083</v>
@@ -36182,7 +36182,7 @@
         <v>1547</v>
       </c>
       <c r="AW208" s="1" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="AX208" s="1" t="s">
         <v>243</v>
@@ -36323,13 +36323,13 @@
         <v>539</v>
       </c>
       <c r="AW209" s="1" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="AX209" s="1" t="s">
         <v>1550</v>
       </c>
       <c r="AY209" s="1" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="AZ209" s="3" t="s">
         <v>1110</v>
@@ -36470,13 +36470,13 @@
         <v>598</v>
       </c>
       <c r="AW210" s="1" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="AX210" s="1" t="s">
         <v>1554</v>
       </c>
       <c r="AY210" s="1" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="AZ210" s="3" t="s">
         <v>1252</v>
@@ -36611,7 +36611,7 @@
         <v>1557</v>
       </c>
       <c r="AW211" s="1" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="AX211" s="1" t="s">
         <v>244</v>
@@ -36743,7 +36743,7 @@
         <v>1220</v>
       </c>
       <c r="AW212" s="1" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="AX212" s="1" t="s">
         <v>247</v>
@@ -36881,7 +36881,7 @@
         <v>1562</v>
       </c>
       <c r="AW213" s="1" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="AX213" s="1" t="s">
         <v>249</v>
@@ -37016,7 +37016,7 @@
         <v>1565</v>
       </c>
       <c r="AW214" s="1" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="AX214" s="1" t="s">
         <v>250</v>
@@ -37148,7 +37148,7 @@
         <v>1294</v>
       </c>
       <c r="AW215" s="1" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
       <c r="AX215" s="1" t="s">
         <v>252</v>
@@ -37280,7 +37280,7 @@
         <v>1567</v>
       </c>
       <c r="AW216" s="1" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="AX216" s="1" t="s">
         <v>253</v>
@@ -37412,7 +37412,7 @@
         <v>1569</v>
       </c>
       <c r="AW217" s="1" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="AX217" s="1" t="s">
         <v>254</v>
@@ -37565,13 +37565,13 @@
         <v>1572</v>
       </c>
       <c r="AW218" s="1" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="AX218" s="1" t="s">
         <v>257</v>
       </c>
       <c r="AY218" s="1" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="AZ218" s="3" t="s">
         <v>1046</v>
@@ -37844,13 +37844,13 @@
         <v>556</v>
       </c>
       <c r="AW220" s="1" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="AX220" s="1" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="AY220" s="1" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="AZ220" s="3" t="s">
         <v>1578</v>
@@ -37976,7 +37976,7 @@
         <v>560</v>
       </c>
       <c r="AW221" s="1" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="AX221" s="1" t="s">
         <v>258</v>
@@ -38111,10 +38111,10 @@
         <v>314</v>
       </c>
       <c r="AV222" s="1" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="AW222" s="1" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="AX222" s="1" t="s">
         <v>261</v>
@@ -38255,7 +38255,7 @@
         <v>560</v>
       </c>
       <c r="AW223" s="1" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="AX223" s="1" t="s">
         <v>263</v>
@@ -38396,7 +38396,7 @@
         <v>556</v>
       </c>
       <c r="AW224" s="1" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="AX224" s="1" t="s">
         <v>264</v>
@@ -38537,7 +38537,7 @@
         <v>1587</v>
       </c>
       <c r="AW225" s="1" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="AX225" s="1" t="s">
         <v>265</v>
@@ -38678,7 +38678,7 @@
         <v>1585</v>
       </c>
       <c r="AW226" s="1" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="AX226" s="1" t="s">
         <v>266</v>
@@ -38807,13 +38807,13 @@
         <v>314</v>
       </c>
       <c r="AV227" s="1" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="AW227" s="1" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="AX227" s="1" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="AY227" s="1" t="s">
         <v>423</v>
@@ -38945,10 +38945,10 @@
         <v>314</v>
       </c>
       <c r="AV228" s="1" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="AW228" s="1" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="AX228" s="1" t="s">
         <v>267</v>
@@ -39077,13 +39077,13 @@
         <v>314</v>
       </c>
       <c r="AV229" s="1" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="AW229" s="1" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="AX229" s="1" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="AY229" s="1" t="s">
         <v>423</v>
@@ -39227,7 +39227,7 @@
         <v>1596</v>
       </c>
       <c r="AW230" s="1" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="AX230" s="1" t="s">
         <v>268</v>
@@ -39374,7 +39374,7 @@
         <v>560</v>
       </c>
       <c r="AW231" s="1" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="AX231" s="1" t="s">
         <v>269</v>
@@ -39442,7 +39442,7 @@
         <v>1835</v>
       </c>
       <c r="AW232" s="1" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="AY232" s="1" t="s">
         <v>314</v>
@@ -39566,10 +39566,10 @@
         <v>314</v>
       </c>
       <c r="AV234" s="1" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="AW234" s="1" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="AY234" s="1" t="s">
         <v>314</v>
@@ -39734,10 +39734,10 @@
         <v>314</v>
       </c>
       <c r="AV237" s="1" t="s">
-        <v>1838</v>
+        <v>2112</v>
       </c>
       <c r="AW237" s="1" t="s">
-        <v>1839</v>
+        <v>2113</v>
       </c>
       <c r="AY237" s="1" t="s">
         <v>314</v>
@@ -39967,16 +39967,16 @@
         <v>1620</v>
       </c>
       <c r="AN241" s="1" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="AU241" s="1" t="s">
         <v>314</v>
       </c>
       <c r="AV241" s="1" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AW241" s="1" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="AY241" s="1" t="s">
         <v>314</v>
@@ -42399,7 +42399,7 @@
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
@@ -42429,7 +42429,7 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
@@ -42809,12 +42809,12 @@
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
@@ -42954,7 +42954,7 @@
     </row>
     <row r="158" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B20C528-7178-4110-BE9D-5C1ADA8DF89F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C573E380-7559-479D-9402-22EA3F97562B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -6469,10 +6469,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{"pool":"random","arch":"chain","kind":"active","color":"#ff6a1a","needs":"group","repo":1,"dmg":0.3,"tick":0.25,"wid":1.4,"presets":["en-fire-chain-3","en-fire-chain-4","en-fire-chain-5","en-fire-chain-6","en-fire-chain-8","en-fire-chain-12","en-fire-chain-15","en-fire-chain-19","en-fire-chain-23"],"linkLen":1.5,"linkH":1.5}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>{"pool":"random","arch":"sparks","kind":"passive","color":"#8ad8ff","n":[2,4],"speed":8,"life":5,"r":1.2,"dmg":0.45,"gap":0.35,"cap":36,"bodyD":1.6}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -7568,15 +7564,19 @@
     <t>　earthguard 第 7 階（我方）：第 1 格 復活後減傷〔限屬性增減〕</t>
   </si>
   <si>
-    <t>和同群夥伴之間拉出由一節一節火環扣成的橘黃火焰鎖鏈（2 隻連一條線、3 隻連成三角形、4 隻連成四邊形，以此類推）（鏈環數隨距離增減），持續到怪物死亡；每 3~6 秒隨機跑位，用火鏈掃過你。碰到或穿過火鏈會承受高頻率的連續火焰傷害。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>{"pool":"random","arch":"cross","kind":"active","color":"#7ee02a","repo":1,"throwRange":12,"dur":16,"balls":5,"ballR":4,"dmg":0.4,"tick":0.25,"warn":0.9,"dot":{"id":"poison","name":"中毒","pct":25,"dur":3},"len":36,"speed":12,"hubR":4}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>地面先生出一個綠色毒圈（半徑 4 米），隨後從中心向上下左右四個方向「長出」一排排毒水球（每秒 12 米、最長 36 米），持續 16 秒；每顆毒水球和中心毒圈一樣大、相鄰兩顆略有重疊；碰到毒球或站在毒圈裡會受到高額毒素傷害。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"pool":"random","arch":"chain","kind":"active","color":"#ff6a1a","needs":"group","repo":1,"dmg":0.3,"tick":0.25,"wid":1.4,"presets":["en-fire-chain-3","en-fire-chain-4","en-fire-chain-5","en-fire-chain-6","en-fire-chain-8","en-fire-chain-12","en-fire-chain-15","en-fire-chain-19","en-fire-chain-23"],"linkLen":1.5,"linkH":1.5,"hover":8,"repoGap":[1.5,3]}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>和同群夥伴之間拉出由一節一節火環扣成的橘黃火焰鎖鏈（2 隻連一條線、3 隻連成三角形、4 隻連成四邊形，以此類推）（鏈環數隨距離增減），持續到怪物死亡；每 1.5~3 秒就跑位到你的另一側、讓火鏈掃過你；平時只守在你 8 米外，不貼臉近戰。碰到或穿過火鏈會承受高頻率的連續火焰傷害。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -8357,7 +8357,7 @@
         <v>554</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="AX2" s="1" t="s">
         <v>30</v>
@@ -8491,7 +8491,7 @@
         <v>1023</v>
       </c>
       <c r="AW3" s="1" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="AX3" s="1" t="s">
         <v>31</v>
@@ -8625,7 +8625,7 @@
         <v>1025</v>
       </c>
       <c r="AW4" s="1" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="AX4" s="1" t="s">
         <v>32</v>
@@ -8759,7 +8759,7 @@
         <v>555</v>
       </c>
       <c r="AW5" s="1" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="AX5" s="1" t="s">
         <v>33</v>
@@ -8893,7 +8893,7 @@
         <v>556</v>
       </c>
       <c r="AW6" s="1" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="AX6" s="1" t="s">
         <v>34</v>
@@ -9027,7 +9027,7 @@
         <v>557</v>
       </c>
       <c r="AW7" s="1" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="AX7" s="1" t="s">
         <v>35</v>
@@ -9158,10 +9158,10 @@
         <v>314</v>
       </c>
       <c r="AV8" s="1" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="AW8" s="1" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="AX8" s="1" t="s">
         <v>36</v>
@@ -9295,7 +9295,7 @@
         <v>1036</v>
       </c>
       <c r="AW9" s="1" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="AX9" s="1" t="s">
         <v>37</v>
@@ -9435,7 +9435,7 @@
         <v>1040</v>
       </c>
       <c r="AW10" s="1" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="AX10" s="1" t="s">
         <v>38</v>
@@ -9569,7 +9569,7 @@
         <v>558</v>
       </c>
       <c r="AW11" s="1" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="AX11" s="1" t="s">
         <v>39</v>
@@ -9703,7 +9703,7 @@
         <v>554</v>
       </c>
       <c r="AW12" s="1" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="AX12" s="1" t="s">
         <v>9</v>
@@ -9837,7 +9837,7 @@
         <v>934</v>
       </c>
       <c r="AW13" s="1" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="AX13" s="1" t="s">
         <v>10</v>
@@ -9971,7 +9971,7 @@
         <v>941</v>
       </c>
       <c r="AW14" s="1" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="AX14" s="1" t="s">
         <v>11</v>
@@ -10105,7 +10105,7 @@
         <v>946</v>
       </c>
       <c r="AW15" s="1" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="AX15" s="1" t="s">
         <v>12</v>
@@ -10239,7 +10239,7 @@
         <v>953</v>
       </c>
       <c r="AW16" s="1" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="AX16" s="1" t="s">
         <v>13</v>
@@ -10373,7 +10373,7 @@
         <v>959</v>
       </c>
       <c r="AW17" s="1" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="AX17" s="1" t="s">
         <v>14</v>
@@ -10507,7 +10507,7 @@
         <v>551</v>
       </c>
       <c r="AW18" s="1" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="AX18" s="1" t="s">
         <v>964</v>
@@ -10647,7 +10647,7 @@
         <v>552</v>
       </c>
       <c r="AW19" s="1" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="AX19" s="1" t="s">
         <v>971</v>
@@ -10784,7 +10784,7 @@
         <v>978</v>
       </c>
       <c r="AW20" s="1" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="AX20" s="1" t="s">
         <v>15</v>
@@ -10918,7 +10918,7 @@
         <v>984</v>
       </c>
       <c r="AW21" s="1" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="AX21" s="1" t="s">
         <v>985</v>
@@ -11052,7 +11052,7 @@
         <v>990</v>
       </c>
       <c r="AW22" s="1" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="AX22" s="1" t="s">
         <v>18</v>
@@ -11186,7 +11186,7 @@
         <v>959</v>
       </c>
       <c r="AW23" s="1" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="AX23" s="1" t="s">
         <v>19</v>
@@ -11320,7 +11320,7 @@
         <v>994</v>
       </c>
       <c r="AW24" s="1" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="AX24" s="1" t="s">
         <v>20</v>
@@ -11454,7 +11454,7 @@
         <v>996</v>
       </c>
       <c r="AW25" s="1" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="AX25" s="1" t="s">
         <v>21</v>
@@ -11587,7 +11587,7 @@
         <v>1000</v>
       </c>
       <c r="AW26" s="1" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="AX26" s="1" t="s">
         <v>22</v>
@@ -11719,7 +11719,7 @@
         <v>959</v>
       </c>
       <c r="AW27" s="1" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="AX27" s="1" t="s">
         <v>23</v>
@@ -13750,7 +13750,7 @@
         <v>1082</v>
       </c>
       <c r="AV42" s="1" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="AW42" s="1" t="s">
         <v>54</v>
@@ -13880,7 +13880,7 @@
         <v>314</v>
       </c>
       <c r="AV43" s="1" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="AW43" s="1" t="s">
         <v>55</v>
@@ -14292,7 +14292,7 @@
         <v>314</v>
       </c>
       <c r="AV46" s="1" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="AW46" s="1" t="s">
         <v>59</v>
@@ -14563,7 +14563,7 @@
         <v>314</v>
       </c>
       <c r="AV48" s="1" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="AW48" s="1" t="s">
         <v>62</v>
@@ -14982,16 +14982,16 @@
         <v>314</v>
       </c>
       <c r="AV51" s="1" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="AW51" s="1" t="s">
+        <v>1875</v>
+      </c>
+      <c r="AX51" s="1" t="s">
         <v>1876</v>
       </c>
-      <c r="AX51" s="1" t="s">
-        <v>1877</v>
-      </c>
       <c r="AY51" s="1" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="AZ51" s="3" t="s">
         <v>1110</v>
@@ -15115,7 +15115,7 @@
         <v>1114</v>
       </c>
       <c r="AW52" s="1" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="AX52" s="1" t="s">
         <v>1115</v>
@@ -15247,7 +15247,7 @@
         <v>1117</v>
       </c>
       <c r="AW53" s="1" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="AX53" s="1" t="s">
         <v>1118</v>
@@ -15379,7 +15379,7 @@
         <v>1121</v>
       </c>
       <c r="AW54" s="1" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="AX54" s="1" t="s">
         <v>67</v>
@@ -15519,7 +15519,7 @@
         <v>1123</v>
       </c>
       <c r="AW55" s="1" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="AX55" s="1" t="s">
         <v>68</v>
@@ -15659,7 +15659,7 @@
         <v>345</v>
       </c>
       <c r="AW56" s="1" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="AX56" s="1" t="s">
         <v>69</v>
@@ -15793,7 +15793,7 @@
         <v>1128</v>
       </c>
       <c r="AW57" s="1" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="AX57" s="1" t="s">
         <v>70</v>
@@ -15931,7 +15931,7 @@
         <v>1130</v>
       </c>
       <c r="AW58" s="1" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="AX58" s="1" t="s">
         <v>1131</v>
@@ -16065,7 +16065,7 @@
         <v>444</v>
       </c>
       <c r="AW59" s="1" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="AX59" s="1" t="s">
         <v>1135</v>
@@ -16202,10 +16202,10 @@
         <v>594</v>
       </c>
       <c r="AW60" s="1" t="s">
+        <v>1895</v>
+      </c>
+      <c r="AX60" s="1" t="s">
         <v>1896</v>
-      </c>
-      <c r="AX60" s="1" t="s">
-        <v>1897</v>
       </c>
       <c r="AY60" s="1" t="s">
         <v>423</v>
@@ -16336,7 +16336,7 @@
         <v>1036</v>
       </c>
       <c r="AW61" s="1" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="AX61" s="1" t="s">
         <v>71</v>
@@ -16470,10 +16470,10 @@
         <v>1147</v>
       </c>
       <c r="AW62" s="1" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="AX62" s="1" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="AY62" s="1" t="s">
         <v>423</v>
@@ -16604,7 +16604,7 @@
         <v>1149</v>
       </c>
       <c r="AW63" s="1" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="AX63" s="1" t="s">
         <v>74</v>
@@ -16738,7 +16738,7 @@
         <v>1151</v>
       </c>
       <c r="AW64" s="1" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="AX64" s="1" t="s">
         <v>75</v>
@@ -16872,7 +16872,7 @@
         <v>525</v>
       </c>
       <c r="AW65" s="1" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="AX65" s="1" t="s">
         <v>76</v>
@@ -17009,7 +17009,7 @@
         <v>1157</v>
       </c>
       <c r="AW66" s="1" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="AX66" s="1" t="s">
         <v>78</v>
@@ -17143,7 +17143,7 @@
         <v>447</v>
       </c>
       <c r="AW67" s="1" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="AX67" s="1" t="s">
         <v>79</v>
@@ -17277,7 +17277,7 @@
         <v>448</v>
       </c>
       <c r="AW68" s="1" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="AX68" s="1" t="s">
         <v>80</v>
@@ -17417,10 +17417,10 @@
         <v>314</v>
       </c>
       <c r="AV69" s="1" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="AW69" s="1" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="AX69" s="1" t="s">
         <v>81</v>
@@ -17704,13 +17704,13 @@
         <v>314</v>
       </c>
       <c r="AV71" s="1" t="s">
+        <v>1897</v>
+      </c>
+      <c r="AW71" s="1" t="s">
+        <v>1900</v>
+      </c>
+      <c r="AX71" s="1" t="s">
         <v>1898</v>
-      </c>
-      <c r="AW71" s="1" t="s">
-        <v>1901</v>
-      </c>
-      <c r="AX71" s="1" t="s">
-        <v>1899</v>
       </c>
       <c r="AY71" s="1" t="s">
         <v>423</v>
@@ -17853,7 +17853,7 @@
         <v>1176</v>
       </c>
       <c r="AW72" s="1" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="AX72" s="1" t="s">
         <v>85</v>
@@ -17987,7 +17987,7 @@
         <v>1036</v>
       </c>
       <c r="AW73" s="1" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="AX73" s="1" t="s">
         <v>87</v>
@@ -18119,7 +18119,7 @@
         <v>1036</v>
       </c>
       <c r="AW74" s="1" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="AX74" s="1" t="s">
         <v>88</v>
@@ -18251,7 +18251,7 @@
         <v>1183</v>
       </c>
       <c r="AW75" s="1" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="AX75" s="1" t="s">
         <v>89</v>
@@ -18383,7 +18383,7 @@
         <v>1036</v>
       </c>
       <c r="AW76" s="1" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="AX76" s="1" t="s">
         <v>90</v>
@@ -18512,10 +18512,10 @@
         <v>314</v>
       </c>
       <c r="AV77" s="1" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="AW77" s="1" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="AX77" s="1" t="s">
         <v>91</v>
@@ -18651,13 +18651,13 @@
         <v>314</v>
       </c>
       <c r="AV78" s="1" t="s">
+        <v>1909</v>
+      </c>
+      <c r="AW78" s="1" t="s">
+        <v>1914</v>
+      </c>
+      <c r="AX78" s="1" t="s">
         <v>1910</v>
-      </c>
-      <c r="AW78" s="1" t="s">
-        <v>1915</v>
-      </c>
-      <c r="AX78" s="1" t="s">
-        <v>1911</v>
       </c>
       <c r="AY78" s="1" t="s">
         <v>1177</v>
@@ -18792,7 +18792,7 @@
         <v>1192</v>
       </c>
       <c r="AW79" s="1" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="AX79" s="1" t="s">
         <v>92</v>
@@ -18933,10 +18933,10 @@
         <v>314</v>
       </c>
       <c r="AV80" s="1" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="AW80" s="1" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="AX80" s="1" t="s">
         <v>451</v>
@@ -19077,13 +19077,13 @@
         <v>314</v>
       </c>
       <c r="AV81" s="1" t="s">
+        <v>1911</v>
+      </c>
+      <c r="AW81" s="1" t="s">
+        <v>1916</v>
+      </c>
+      <c r="AX81" s="1" t="s">
         <v>1912</v>
-      </c>
-      <c r="AW81" s="1" t="s">
-        <v>1917</v>
-      </c>
-      <c r="AX81" s="1" t="s">
-        <v>1913</v>
       </c>
       <c r="AY81" s="1" t="s">
         <v>1177</v>
@@ -19212,7 +19212,7 @@
         <v>1205</v>
       </c>
       <c r="AW82" s="1" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="AX82" s="1" t="s">
         <v>97</v>
@@ -19347,7 +19347,7 @@
         <v>1208</v>
       </c>
       <c r="AW83" s="1" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="AX83" s="1" t="s">
         <v>98</v>
@@ -19479,7 +19479,7 @@
         <v>1210</v>
       </c>
       <c r="AW84" s="1" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="AX84" s="1" t="s">
         <v>99</v>
@@ -19611,7 +19611,7 @@
         <v>959</v>
       </c>
       <c r="AW85" s="1" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="AX85" s="1" t="s">
         <v>100</v>
@@ -19743,7 +19743,7 @@
         <v>1096</v>
       </c>
       <c r="AW86" s="1" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="AX86" s="1" t="s">
         <v>102</v>
@@ -19878,13 +19878,13 @@
         <v>314</v>
       </c>
       <c r="AV87" s="1" t="s">
+        <v>1923</v>
+      </c>
+      <c r="AW87" s="1" t="s">
+        <v>1925</v>
+      </c>
+      <c r="AX87" s="1" t="s">
         <v>1924</v>
-      </c>
-      <c r="AW87" s="1" t="s">
-        <v>1926</v>
-      </c>
-      <c r="AX87" s="1" t="s">
-        <v>1925</v>
       </c>
       <c r="AY87" s="1" t="s">
         <v>423</v>
@@ -20013,7 +20013,7 @@
         <v>1220</v>
       </c>
       <c r="AW88" s="1" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="AX88" s="1" t="s">
         <v>104</v>
@@ -20145,7 +20145,7 @@
         <v>1224</v>
       </c>
       <c r="AW89" s="1" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="AX89" s="1" t="s">
         <v>105</v>
@@ -20289,7 +20289,7 @@
         <v>575</v>
       </c>
       <c r="AW90" s="1" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="AX90" s="1" t="s">
         <v>107</v>
@@ -20421,7 +20421,7 @@
         <v>574</v>
       </c>
       <c r="AW91" s="1" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="AX91" s="1" t="s">
         <v>108</v>
@@ -20556,7 +20556,7 @@
         <v>1235</v>
       </c>
       <c r="AW92" s="1" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="AX92" s="1" t="s">
         <v>112</v>
@@ -20688,7 +20688,7 @@
         <v>1086</v>
       </c>
       <c r="AW93" s="1" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="AX93" s="1" t="s">
         <v>113</v>
@@ -20817,10 +20817,10 @@
         <v>314</v>
       </c>
       <c r="AV94" s="1" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="AW94" s="1" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="AX94" s="1" t="s">
         <v>114</v>
@@ -20955,7 +20955,7 @@
         <v>1240</v>
       </c>
       <c r="AW95" s="1" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="AX95" s="1" t="s">
         <v>115</v>
@@ -21099,7 +21099,7 @@
         <v>1192</v>
       </c>
       <c r="AW96" s="1" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="AX96" s="1" t="s">
         <v>116</v>
@@ -21231,7 +21231,7 @@
         <v>1244</v>
       </c>
       <c r="AW97" s="1" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="AX97" s="1" t="s">
         <v>117</v>
@@ -21366,7 +21366,7 @@
         <v>1246</v>
       </c>
       <c r="AW98" s="1" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="AX98" s="1" t="s">
         <v>119</v>
@@ -21507,7 +21507,7 @@
         <v>1250</v>
       </c>
       <c r="AW99" s="1" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="AX99" s="1" t="s">
         <v>465</v>
@@ -21642,10 +21642,10 @@
         <v>314</v>
       </c>
       <c r="AV100" s="1" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="AW100" s="1" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="AX100" s="1" t="s">
         <v>121</v>
@@ -21783,7 +21783,7 @@
         <v>464</v>
       </c>
       <c r="AW101" s="1" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="AX101" s="1" t="s">
         <v>1258</v>
@@ -21921,7 +21921,7 @@
         <v>1265</v>
       </c>
       <c r="AW102" s="1" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="AX102" s="1" t="s">
         <v>124</v>
@@ -22053,7 +22053,7 @@
         <v>1267</v>
       </c>
       <c r="AW103" s="1" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="AX103" s="1" t="s">
         <v>125</v>
@@ -22191,7 +22191,7 @@
         <v>1269</v>
       </c>
       <c r="AW104" s="1" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="AX104" s="1" t="s">
         <v>127</v>
@@ -22323,7 +22323,7 @@
         <v>1271</v>
       </c>
       <c r="AW105" s="1" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="AX105" s="1" t="s">
         <v>128</v>
@@ -22455,7 +22455,7 @@
         <v>1036</v>
       </c>
       <c r="AW106" s="1" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="AX106" s="1" t="s">
         <v>129</v>
@@ -22584,10 +22584,10 @@
         <v>314</v>
       </c>
       <c r="AV107" s="1" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="AW107" s="1" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="AX107" s="1" t="s">
         <v>131</v>
@@ -22719,10 +22719,10 @@
         <v>1275</v>
       </c>
       <c r="AW108" s="1" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="AX108" s="1" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="AY108" s="1" t="s">
         <v>423</v>
@@ -22854,7 +22854,7 @@
         <v>314</v>
       </c>
       <c r="AV109" s="1" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="AW109" s="1" t="s">
         <v>132</v>
@@ -22992,13 +22992,13 @@
         <v>1207</v>
       </c>
       <c r="AV110" s="1" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AW110" s="1" t="s">
         <v>1952</v>
       </c>
-      <c r="AW110" s="1" t="s">
+      <c r="AX110" s="1" t="s">
         <v>1953</v>
-      </c>
-      <c r="AX110" s="1" t="s">
-        <v>1954</v>
       </c>
       <c r="AY110" s="1" t="s">
         <v>472</v>
@@ -23139,7 +23139,7 @@
         <v>467</v>
       </c>
       <c r="AW111" s="1" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="AX111" s="1" t="s">
         <v>466</v>
@@ -23274,10 +23274,10 @@
         <v>314</v>
       </c>
       <c r="AV112" s="1" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="AW112" s="1" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="AX112" s="1" t="s">
         <v>136</v>
@@ -23409,7 +23409,7 @@
         <v>1036</v>
       </c>
       <c r="AW113" s="1" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="AX113" s="1" t="s">
         <v>137</v>
@@ -23541,7 +23541,7 @@
         <v>1289</v>
       </c>
       <c r="AW114" s="1" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="AX114" s="1" t="s">
         <v>138</v>
@@ -23673,10 +23673,10 @@
         <v>1267</v>
       </c>
       <c r="AW115" s="1" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="AX115" s="1" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="AY115" s="1" t="s">
         <v>423</v>
@@ -23805,7 +23805,7 @@
         <v>525</v>
       </c>
       <c r="AW116" s="1" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="AX116" s="1" t="s">
         <v>139</v>
@@ -23940,10 +23940,10 @@
         <v>314</v>
       </c>
       <c r="AV117" s="1" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="AW117" s="1" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="AX117" s="1" t="s">
         <v>140</v>
@@ -24075,7 +24075,7 @@
         <v>1294</v>
       </c>
       <c r="AW118" s="1" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="AX118" s="1" t="s">
         <v>142</v>
@@ -24225,7 +24225,7 @@
         <v>584</v>
       </c>
       <c r="AW119" s="1" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="AX119" s="1" t="s">
         <v>1299</v>
@@ -24354,10 +24354,10 @@
         <v>314</v>
       </c>
       <c r="AV120" s="1" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="AW120" s="1" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="AX120" s="1" t="s">
         <v>143</v>
@@ -24492,13 +24492,13 @@
         <v>1308</v>
       </c>
       <c r="AV121" s="1" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="AW121" s="1" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="AX121" s="1" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="AY121" s="1" t="s">
         <v>423</v>
@@ -24627,13 +24627,13 @@
         <v>1313</v>
       </c>
       <c r="AV122" s="1" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="AW122" s="1" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AX122" s="1" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AY122" s="1" t="s">
         <v>423</v>
@@ -24762,10 +24762,10 @@
         <v>1267</v>
       </c>
       <c r="AW123" s="1" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="AX123" s="1" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="AY123" s="1" t="s">
         <v>423</v>
@@ -24897,7 +24897,7 @@
         <v>1318</v>
       </c>
       <c r="AW124" s="1" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="AX124" s="1" t="s">
         <v>146</v>
@@ -25161,7 +25161,7 @@
         <v>1321</v>
       </c>
       <c r="AW126" s="1" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="AX126" s="1" t="s">
         <v>148</v>
@@ -25293,10 +25293,10 @@
         <v>1323</v>
       </c>
       <c r="AW127" s="1" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="AX127" s="1" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="AY127" s="1" t="s">
         <v>423</v>
@@ -25428,7 +25428,7 @@
         <v>1327</v>
       </c>
       <c r="AW128" s="1" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="AX128" s="1" t="s">
         <v>149</v>
@@ -25563,7 +25563,7 @@
         <v>1331</v>
       </c>
       <c r="AW129" s="1" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="AX129" s="1" t="s">
         <v>150</v>
@@ -25695,7 +25695,7 @@
         <v>482</v>
       </c>
       <c r="AR130" s="1" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="AT130" s="1" t="s">
         <v>314</v>
@@ -25704,16 +25704,16 @@
         <v>314</v>
       </c>
       <c r="AV130" s="1" t="s">
+        <v>1980</v>
+      </c>
+      <c r="AW130" s="1" t="s">
+        <v>1985</v>
+      </c>
+      <c r="AX130" s="1" t="s">
         <v>1981</v>
       </c>
-      <c r="AW130" s="1" t="s">
-        <v>1986</v>
-      </c>
-      <c r="AX130" s="1" t="s">
+      <c r="AY130" s="1" t="s">
         <v>1982</v>
-      </c>
-      <c r="AY130" s="1" t="s">
-        <v>1983</v>
       </c>
       <c r="AZ130" s="3" t="s">
         <v>1276</v>
@@ -25836,10 +25836,10 @@
         <v>314</v>
       </c>
       <c r="AV131" s="1" t="s">
+        <v>1978</v>
+      </c>
+      <c r="AW131" s="1" t="s">
         <v>1979</v>
-      </c>
-      <c r="AW131" s="1" t="s">
-        <v>1980</v>
       </c>
       <c r="AX131" s="1" t="s">
         <v>151</v>
@@ -25968,10 +25968,10 @@
         <v>314</v>
       </c>
       <c r="AV132" s="1" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="AW132" s="1" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="AX132" s="1" t="s">
         <v>154</v>
@@ -26103,7 +26103,7 @@
         <v>1267</v>
       </c>
       <c r="AW133" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="AX133" s="1" t="s">
         <v>155</v>
@@ -26235,7 +26235,7 @@
         <v>499</v>
       </c>
       <c r="AW134" s="1" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="AX134" s="1" t="s">
         <v>156</v>
@@ -26367,7 +26367,7 @@
         <v>499</v>
       </c>
       <c r="AW135" s="1" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="AX135" s="1" t="s">
         <v>157</v>
@@ -26499,7 +26499,7 @@
         <v>587</v>
       </c>
       <c r="AW136" s="1" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="AX136" s="1" t="s">
         <v>1343</v>
@@ -26631,7 +26631,7 @@
         <v>1347</v>
       </c>
       <c r="AW137" s="1" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="AX137" s="1" t="s">
         <v>158</v>
@@ -26760,19 +26760,19 @@
         <v>314</v>
       </c>
       <c r="AT138" s="1" t="s">
+        <v>1993</v>
+      </c>
+      <c r="AU138" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AV138" s="1" t="s">
+        <v>1992</v>
+      </c>
+      <c r="AW138" s="1" t="s">
+        <v>1996</v>
+      </c>
+      <c r="AX138" s="1" t="s">
         <v>1994</v>
-      </c>
-      <c r="AU138" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AV138" s="1" t="s">
-        <v>1993</v>
-      </c>
-      <c r="AW138" s="1" t="s">
-        <v>1997</v>
-      </c>
-      <c r="AX138" s="1" t="s">
-        <v>1995</v>
       </c>
       <c r="AY138" s="1" t="s">
         <v>423</v>
@@ -26901,7 +26901,7 @@
         <v>595</v>
       </c>
       <c r="AW139" s="1" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AX139" s="1" t="s">
         <v>1352</v>
@@ -27033,7 +27033,7 @@
         <v>484</v>
       </c>
       <c r="AW140" s="1" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="AX140" s="1" t="s">
         <v>159</v>
@@ -27165,7 +27165,7 @@
         <v>1358</v>
       </c>
       <c r="AW141" s="1" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="AX141" s="1" t="s">
         <v>160</v>
@@ -27295,7 +27295,7 @@
         <v>588</v>
       </c>
       <c r="AW142" s="1" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="AX142" s="1" t="s">
         <v>165</v>
@@ -27427,7 +27427,7 @@
         <v>560</v>
       </c>
       <c r="AW143" s="1" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="AX143" s="1" t="s">
         <v>166</v>
@@ -27559,7 +27559,7 @@
         <v>555</v>
       </c>
       <c r="AW144" s="1" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="AX144" s="1" t="s">
         <v>167</v>
@@ -27691,7 +27691,7 @@
         <v>1117</v>
       </c>
       <c r="AW145" s="1" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="AX145" s="1" t="s">
         <v>168</v>
@@ -27823,7 +27823,7 @@
         <v>1366</v>
       </c>
       <c r="AW146" s="1" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="AX146" s="1" t="s">
         <v>169</v>
@@ -27955,7 +27955,7 @@
         <v>560</v>
       </c>
       <c r="AW147" s="1" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AX147" s="1" t="s">
         <v>170</v>
@@ -28087,7 +28087,7 @@
         <v>596</v>
       </c>
       <c r="AW148" s="1" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="AX148" s="1" t="s">
         <v>171</v>
@@ -28234,7 +28234,7 @@
         <v>1374</v>
       </c>
       <c r="AW149" s="1" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="AX149" s="1" t="s">
         <v>172</v>
@@ -28372,7 +28372,7 @@
         <v>597</v>
       </c>
       <c r="AW150" s="1" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="AX150" s="1" t="s">
         <v>1379</v>
@@ -28392,7 +28392,7 @@
         <v>314</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>314</v>
@@ -28473,7 +28473,7 @@
         <v>314</v>
       </c>
       <c r="AE151" s="1" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="AF151" s="1" t="s">
         <v>314</v>
@@ -28501,10 +28501,10 @@
         <v>959</v>
       </c>
       <c r="AW151" s="1" t="s">
+        <v>2069</v>
+      </c>
+      <c r="AX151" s="1" t="s">
         <v>2070</v>
-      </c>
-      <c r="AX151" s="1" t="s">
-        <v>2071</v>
       </c>
       <c r="AY151" s="1" t="s">
         <v>423</v>
@@ -28633,7 +28633,7 @@
         <v>1384</v>
       </c>
       <c r="AW152" s="1" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="AX152" s="1" t="s">
         <v>175</v>
@@ -28765,7 +28765,7 @@
         <v>555</v>
       </c>
       <c r="AW153" s="1" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="AX153" s="1" t="s">
         <v>176</v>
@@ -28897,7 +28897,7 @@
         <v>555</v>
       </c>
       <c r="AW154" s="1" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="AX154" s="1" t="s">
         <v>177</v>
@@ -29029,7 +29029,7 @@
         <v>1192</v>
       </c>
       <c r="AW155" s="1" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="AX155" s="1" t="s">
         <v>178</v>
@@ -29164,7 +29164,7 @@
         <v>1390</v>
       </c>
       <c r="AW156" s="1" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="AX156" s="1" t="s">
         <v>179</v>
@@ -29296,7 +29296,7 @@
         <v>1392</v>
       </c>
       <c r="AW157" s="1" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="AX157" s="1" t="s">
         <v>180</v>
@@ -29316,7 +29316,7 @@
         <v>1381</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>1382</v>
@@ -29428,7 +29428,7 @@
         <v>1395</v>
       </c>
       <c r="AW158" s="1" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="AX158" s="1" t="s">
         <v>181</v>
@@ -29566,7 +29566,7 @@
         <v>494</v>
       </c>
       <c r="AW159" s="1" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="AX159" s="1" t="s">
         <v>1404</v>
@@ -29698,10 +29698,10 @@
         <v>556</v>
       </c>
       <c r="AW160" s="1" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="AX160" s="1" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="AY160" s="1" t="s">
         <v>423</v>
@@ -29827,10 +29827,10 @@
         <v>314</v>
       </c>
       <c r="AV161" s="1" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="AW161" s="1" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="AX161" s="1" t="s">
         <v>182</v>
@@ -29963,7 +29963,7 @@
         <v>1411</v>
       </c>
       <c r="AW162" s="1" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="AX162" s="1" t="s">
         <v>187</v>
@@ -30095,7 +30095,7 @@
         <v>1267</v>
       </c>
       <c r="AW163" s="1" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="AX163" s="1" t="s">
         <v>188</v>
@@ -30227,7 +30227,7 @@
         <v>555</v>
       </c>
       <c r="AW164" s="1" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="AX164" s="1" t="s">
         <v>189</v>
@@ -30363,7 +30363,7 @@
         <v>1417</v>
       </c>
       <c r="AW165" s="1" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="AX165" s="1" t="s">
         <v>191</v>
@@ -30495,7 +30495,7 @@
         <v>1294</v>
       </c>
       <c r="AW166" s="1" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="AX166" s="1" t="s">
         <v>192</v>
@@ -30628,7 +30628,7 @@
         <v>1421</v>
       </c>
       <c r="AW167" s="1" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="AX167" s="1" t="s">
         <v>193</v>
@@ -30770,7 +30770,7 @@
         <v>1425</v>
       </c>
       <c r="AW168" s="1" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="AX168" s="1" t="s">
         <v>195</v>
@@ -30905,7 +30905,7 @@
         <v>507</v>
       </c>
       <c r="AW169" s="1" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="AX169" s="1" t="s">
         <v>1428</v>
@@ -31046,7 +31046,7 @@
         <v>517</v>
       </c>
       <c r="AW170" s="1" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="AX170" s="1" t="s">
         <v>496</v>
@@ -31178,7 +31178,7 @@
         <v>1435</v>
       </c>
       <c r="AW171" s="1" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="AX171" s="1" t="s">
         <v>196</v>
@@ -31310,7 +31310,7 @@
         <v>1442</v>
       </c>
       <c r="AW172" s="1" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="AX172" s="1" t="s">
         <v>201</v>
@@ -31445,7 +31445,7 @@
         <v>1446</v>
       </c>
       <c r="AW173" s="1" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="AX173" s="1" t="s">
         <v>203</v>
@@ -31577,7 +31577,7 @@
         <v>1192</v>
       </c>
       <c r="AW174" s="1" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="AX174" s="1" t="s">
         <v>204</v>
@@ -31709,7 +31709,7 @@
         <v>959</v>
       </c>
       <c r="AW175" s="1" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="AX175" s="1" t="s">
         <v>205</v>
@@ -31841,7 +31841,7 @@
         <v>555</v>
       </c>
       <c r="AW176" s="1" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="AX176" s="1" t="s">
         <v>206</v>
@@ -31973,7 +31973,7 @@
         <v>1452</v>
       </c>
       <c r="AW177" s="1" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="AX177" s="1" t="s">
         <v>207</v>
@@ -32109,7 +32109,7 @@
         <v>521</v>
       </c>
       <c r="AW178" s="1" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="AX178" s="1" t="s">
         <v>209</v>
@@ -32241,7 +32241,7 @@
         <v>523</v>
       </c>
       <c r="AW179" s="1" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="AX179" s="1" t="s">
         <v>1459</v>
@@ -32373,7 +32373,7 @@
         <v>522</v>
       </c>
       <c r="AW180" s="1" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="AX180" s="1" t="s">
         <v>1462</v>
@@ -32514,7 +32514,7 @@
         <v>518</v>
       </c>
       <c r="AW181" s="1" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="AX181" s="1" t="s">
         <v>1465</v>
@@ -32644,7 +32644,7 @@
         <v>1472</v>
       </c>
       <c r="AW182" s="1" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="AX182" s="1" t="s">
         <v>1473</v>
@@ -32779,7 +32779,7 @@
         <v>1477</v>
       </c>
       <c r="AW183" s="1" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="AX183" s="1" t="s">
         <v>212</v>
@@ -32914,7 +32914,7 @@
         <v>1479</v>
       </c>
       <c r="AW184" s="1" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="AX184" s="1" t="s">
         <v>213</v>
@@ -33046,7 +33046,7 @@
         <v>1481</v>
       </c>
       <c r="AW185" s="1" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="AX185" s="1" t="s">
         <v>214</v>
@@ -33187,7 +33187,7 @@
         <v>447</v>
       </c>
       <c r="AW186" s="1" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="AX186" s="1" t="s">
         <v>215</v>
@@ -33319,7 +33319,7 @@
         <v>1117</v>
       </c>
       <c r="AW187" s="1" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="AX187" s="1" t="s">
         <v>216</v>
@@ -33457,7 +33457,7 @@
         <v>535</v>
       </c>
       <c r="AW188" s="1" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="AX188" s="1" t="s">
         <v>218</v>
@@ -33595,7 +33595,7 @@
         <v>524</v>
       </c>
       <c r="AW189" s="1" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="AX189" s="1" t="s">
         <v>1492</v>
@@ -33736,7 +33736,7 @@
         <v>534</v>
       </c>
       <c r="AW190" s="1" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="AX190" s="1" t="s">
         <v>1495</v>
@@ -33880,7 +33880,7 @@
         <v>527</v>
       </c>
       <c r="AW191" s="1" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="AX191" s="1" t="s">
         <v>1499</v>
@@ -34015,7 +34015,7 @@
         <v>1505</v>
       </c>
       <c r="AW192" s="1" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="AX192" s="1" t="s">
         <v>221</v>
@@ -34147,7 +34147,7 @@
         <v>560</v>
       </c>
       <c r="AW193" s="1" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="AX193" s="1" t="s">
         <v>222</v>
@@ -34285,7 +34285,7 @@
         <v>1509</v>
       </c>
       <c r="AW194" s="1" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="AX194" s="1" t="s">
         <v>223</v>
@@ -34417,7 +34417,7 @@
         <v>1512</v>
       </c>
       <c r="AW195" s="1" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="AX195" s="1" t="s">
         <v>224</v>
@@ -34549,7 +34549,7 @@
         <v>555</v>
       </c>
       <c r="AW196" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="AX196" s="1" t="s">
         <v>225</v>
@@ -34681,7 +34681,7 @@
         <v>1516</v>
       </c>
       <c r="AW197" s="1" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="AX197" s="1" t="s">
         <v>226</v>
@@ -34819,7 +34819,7 @@
         <v>1520</v>
       </c>
       <c r="AW198" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="AX198" s="1" t="s">
         <v>229</v>
@@ -34951,7 +34951,7 @@
         <v>560</v>
       </c>
       <c r="AW199" s="1" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="AX199" s="1" t="s">
         <v>230</v>
@@ -35087,7 +35087,7 @@
         <v>532</v>
       </c>
       <c r="AW200" s="1" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="AX200" s="1" t="s">
         <v>1525</v>
@@ -35225,7 +35225,7 @@
         <v>1529</v>
       </c>
       <c r="AW201" s="1" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="AX201" s="1" t="s">
         <v>231</v>
@@ -35357,7 +35357,7 @@
         <v>1472</v>
       </c>
       <c r="AW202" s="1" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="AX202" s="1" t="s">
         <v>236</v>
@@ -35489,7 +35489,7 @@
         <v>1537</v>
       </c>
       <c r="AW203" s="1" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="AX203" s="1" t="s">
         <v>237</v>
@@ -35621,7 +35621,7 @@
         <v>1539</v>
       </c>
       <c r="AW204" s="1" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="AX204" s="1" t="s">
         <v>238</v>
@@ -35762,7 +35762,7 @@
         <v>1294</v>
       </c>
       <c r="AW205" s="1" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="AX205" s="1" t="s">
         <v>239</v>
@@ -35903,7 +35903,7 @@
         <v>1543</v>
       </c>
       <c r="AW206" s="1" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="AX206" s="1" t="s">
         <v>241</v>
@@ -36047,16 +36047,16 @@
         <v>1545</v>
       </c>
       <c r="AV207" s="1" t="s">
+        <v>2071</v>
+      </c>
+      <c r="AW207" s="1" t="s">
         <v>2072</v>
       </c>
-      <c r="AW207" s="1" t="s">
+      <c r="AX207" s="1" t="s">
         <v>2073</v>
       </c>
-      <c r="AX207" s="1" t="s">
+      <c r="AY207" s="1" t="s">
         <v>2074</v>
-      </c>
-      <c r="AY207" s="1" t="s">
-        <v>2075</v>
       </c>
       <c r="AZ207" s="3" t="s">
         <v>1083</v>
@@ -36182,7 +36182,7 @@
         <v>1547</v>
       </c>
       <c r="AW208" s="1" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="AX208" s="1" t="s">
         <v>243</v>
@@ -36323,13 +36323,13 @@
         <v>539</v>
       </c>
       <c r="AW209" s="1" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AX209" s="1" t="s">
         <v>1550</v>
       </c>
       <c r="AY209" s="1" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AZ209" s="3" t="s">
         <v>1110</v>
@@ -36470,13 +36470,13 @@
         <v>598</v>
       </c>
       <c r="AW210" s="1" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="AX210" s="1" t="s">
         <v>1554</v>
       </c>
       <c r="AY210" s="1" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AZ210" s="3" t="s">
         <v>1252</v>
@@ -36611,7 +36611,7 @@
         <v>1557</v>
       </c>
       <c r="AW211" s="1" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AX211" s="1" t="s">
         <v>244</v>
@@ -36743,7 +36743,7 @@
         <v>1220</v>
       </c>
       <c r="AW212" s="1" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="AX212" s="1" t="s">
         <v>247</v>
@@ -36881,7 +36881,7 @@
         <v>1562</v>
       </c>
       <c r="AW213" s="1" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="AX213" s="1" t="s">
         <v>249</v>
@@ -37016,7 +37016,7 @@
         <v>1565</v>
       </c>
       <c r="AW214" s="1" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="AX214" s="1" t="s">
         <v>250</v>
@@ -37148,7 +37148,7 @@
         <v>1294</v>
       </c>
       <c r="AW215" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="AX215" s="1" t="s">
         <v>252</v>
@@ -37280,7 +37280,7 @@
         <v>1567</v>
       </c>
       <c r="AW216" s="1" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="AX216" s="1" t="s">
         <v>253</v>
@@ -37412,7 +37412,7 @@
         <v>1569</v>
       </c>
       <c r="AW217" s="1" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="AX217" s="1" t="s">
         <v>254</v>
@@ -37565,13 +37565,13 @@
         <v>1572</v>
       </c>
       <c r="AW218" s="1" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="AX218" s="1" t="s">
         <v>257</v>
       </c>
       <c r="AY218" s="1" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="AZ218" s="3" t="s">
         <v>1046</v>
@@ -37844,13 +37844,13 @@
         <v>556</v>
       </c>
       <c r="AW220" s="1" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="AX220" s="1" t="s">
+        <v>2088</v>
+      </c>
+      <c r="AY220" s="1" t="s">
         <v>2089</v>
-      </c>
-      <c r="AY220" s="1" t="s">
-        <v>2090</v>
       </c>
       <c r="AZ220" s="3" t="s">
         <v>1578</v>
@@ -37976,7 +37976,7 @@
         <v>560</v>
       </c>
       <c r="AW221" s="1" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="AX221" s="1" t="s">
         <v>258</v>
@@ -38111,10 +38111,10 @@
         <v>314</v>
       </c>
       <c r="AV222" s="1" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="AW222" s="1" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="AX222" s="1" t="s">
         <v>261</v>
@@ -38255,7 +38255,7 @@
         <v>560</v>
       </c>
       <c r="AW223" s="1" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="AX223" s="1" t="s">
         <v>263</v>
@@ -38396,7 +38396,7 @@
         <v>556</v>
       </c>
       <c r="AW224" s="1" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="AX224" s="1" t="s">
         <v>264</v>
@@ -38537,7 +38537,7 @@
         <v>1587</v>
       </c>
       <c r="AW225" s="1" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="AX225" s="1" t="s">
         <v>265</v>
@@ -38678,7 +38678,7 @@
         <v>1585</v>
       </c>
       <c r="AW226" s="1" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="AX226" s="1" t="s">
         <v>266</v>
@@ -38807,13 +38807,13 @@
         <v>314</v>
       </c>
       <c r="AV227" s="1" t="s">
+        <v>2101</v>
+      </c>
+      <c r="AW227" s="1" t="s">
         <v>2102</v>
       </c>
-      <c r="AW227" s="1" t="s">
-        <v>2103</v>
-      </c>
       <c r="AX227" s="1" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="AY227" s="1" t="s">
         <v>423</v>
@@ -38945,10 +38945,10 @@
         <v>314</v>
       </c>
       <c r="AV228" s="1" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="AW228" s="1" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AX228" s="1" t="s">
         <v>267</v>
@@ -39077,13 +39077,13 @@
         <v>314</v>
       </c>
       <c r="AV229" s="1" t="s">
+        <v>2103</v>
+      </c>
+      <c r="AW229" s="1" t="s">
         <v>2104</v>
       </c>
-      <c r="AW229" s="1" t="s">
-        <v>2105</v>
-      </c>
       <c r="AX229" s="1" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="AY229" s="1" t="s">
         <v>423</v>
@@ -39227,7 +39227,7 @@
         <v>1596</v>
       </c>
       <c r="AW230" s="1" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="AX230" s="1" t="s">
         <v>268</v>
@@ -39374,7 +39374,7 @@
         <v>560</v>
       </c>
       <c r="AW231" s="1" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="AX231" s="1" t="s">
         <v>269</v>
@@ -39439,10 +39439,10 @@
         <v>314</v>
       </c>
       <c r="AV232" s="1" t="s">
-        <v>1835</v>
+        <v>2112</v>
       </c>
       <c r="AW232" s="1" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="AY232" s="1" t="s">
         <v>314</v>
@@ -39566,10 +39566,10 @@
         <v>314</v>
       </c>
       <c r="AV234" s="1" t="s">
+        <v>2106</v>
+      </c>
+      <c r="AW234" s="1" t="s">
         <v>2107</v>
-      </c>
-      <c r="AW234" s="1" t="s">
-        <v>2108</v>
       </c>
       <c r="AY234" s="1" t="s">
         <v>314</v>
@@ -39678,10 +39678,10 @@
         <v>314</v>
       </c>
       <c r="AV236" s="1" t="s">
+        <v>1835</v>
+      </c>
+      <c r="AW236" s="1" t="s">
         <v>1836</v>
-      </c>
-      <c r="AW236" s="1" t="s">
-        <v>1837</v>
       </c>
       <c r="AY236" s="1" t="s">
         <v>314</v>
@@ -39734,10 +39734,10 @@
         <v>314</v>
       </c>
       <c r="AV237" s="1" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="AW237" s="1" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="AY237" s="1" t="s">
         <v>314</v>
@@ -39967,16 +39967,16 @@
         <v>1620</v>
       </c>
       <c r="AN241" s="1" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="AU241" s="1" t="s">
         <v>314</v>
       </c>
       <c r="AV241" s="1" t="s">
+        <v>1841</v>
+      </c>
+      <c r="AW241" s="1" t="s">
         <v>1842</v>
-      </c>
-      <c r="AW241" s="1" t="s">
-        <v>1843</v>
       </c>
       <c r="AY241" s="1" t="s">
         <v>314</v>
@@ -42399,7 +42399,7 @@
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
@@ -42429,7 +42429,7 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
@@ -42809,12 +42809,12 @@
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
@@ -42954,7 +42954,7 @@
     </row>
     <row r="158" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A47A622-E3ED-4461-8152-0CCC7A043CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3941C02A-4F2B-4252-9E2E-315A21246E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
+    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills2" sheetId="1" r:id="rId1"/>
@@ -7386,10 +7386,6 @@
     <t>　earthguard 第 7 階（我方）：第 1 格 復活後減傷〔限屬性增減〕</t>
   </si>
   <si>
-    <t>地面先生出一個綠色毒圈（半徑 4 米），隨後從中心向上下左右四個方向「長出」一排排毒水球（每秒 12 米、最長 36 米），持續 16 秒；每顆毒水球和中心毒圈一樣大、相鄰兩顆略有重疊；碰到毒球或站在毒圈裡會受到高額毒素傷害。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>和同群夥伴之間拉出由一節一節火環扣成的橘黃火焰鎖鏈（2 隻連一條線、3 隻連成三角形、4 隻連成四邊形，以此類推）（鏈環數隨距離增減），持續到怪物死亡；每 1.5~3 秒就跑位到你的另一側、讓火鏈掃過你；平時只守在你 8 米外，不貼臉近戰。碰到或穿過火鏈會承受高頻率的連續火焰傷害。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -7734,6 +7730,10 @@
   </si>
   <si>
     <t>【雷隕天落】的雷隕石體積增大 {scale}%、傷害額外 +{pct}%，並額外每 {gap} 秒不斷再降下 1 顆</t>
+  </si>
+  <si>
+    <t>地面先生出一個綠色毒圈（半徑 4 米），隨後從中心沿「敵人面對你的方向」與其垂直的方向（斜向來就是斜十字）四個方向「長出」一排排毒水球（每秒 12 米、最長 36 米），持續 16 秒；每顆毒水球和中心毒圈一樣大、相鄰兩顆略有重疊；碰到毒球或站在毒圈裡會受到高額毒素傷害。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -20057,7 +20057,7 @@
         <v>1166</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>1167</v>
@@ -20169,10 +20169,10 @@
         <v>1186</v>
       </c>
       <c r="AW88" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="AX88" s="1" t="s">
         <v>2143</v>
-      </c>
-      <c r="AX88" s="1" t="s">
-        <v>2144</v>
       </c>
       <c r="AY88" s="1" t="s">
         <v>417</v>
@@ -20189,7 +20189,7 @@
         <v>308</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>308</v>
@@ -20301,10 +20301,10 @@
         <v>1190</v>
       </c>
       <c r="AW89" s="1" t="s">
+        <v>2144</v>
+      </c>
+      <c r="AX89" s="1" t="s">
         <v>2145</v>
-      </c>
-      <c r="AX89" s="1" t="s">
-        <v>2146</v>
       </c>
       <c r="AY89" s="1" t="s">
         <v>417</v>
@@ -20445,13 +20445,13 @@
         <v>568</v>
       </c>
       <c r="AW90" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="AX90" s="1" t="s">
         <v>2147</v>
       </c>
-      <c r="AX90" s="1" t="s">
+      <c r="AY90" s="1" t="s">
         <v>2148</v>
-      </c>
-      <c r="AY90" s="1" t="s">
-        <v>2149</v>
       </c>
       <c r="AZ90" s="3" t="s">
         <v>980</v>
@@ -20577,10 +20577,10 @@
         <v>567</v>
       </c>
       <c r="AW91" s="1" t="s">
+        <v>2149</v>
+      </c>
+      <c r="AX91" s="1" t="s">
         <v>2150</v>
-      </c>
-      <c r="AX91" s="1" t="s">
-        <v>2151</v>
       </c>
       <c r="AY91" s="1" t="s">
         <v>417</v>
@@ -30804,7 +30804,7 @@
         <v>1373</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>1374</v>
@@ -30926,13 +30926,13 @@
         <v>1390</v>
       </c>
       <c r="AW168" s="1" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="AX168" s="1" t="s">
         <v>191</v>
       </c>
       <c r="AY168" s="1" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="AZ168" s="3" t="s">
         <v>1092</v>
@@ -31222,7 +31222,7 @@
         <v>308</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>308</v>
@@ -31334,10 +31334,10 @@
         <v>1399</v>
       </c>
       <c r="AW171" s="1" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="AX171" s="1" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="AY171" s="1" t="s">
         <v>417</v>
@@ -39383,13 +39383,13 @@
         <v>1560</v>
       </c>
       <c r="AW230" s="1" t="s">
+        <v>2153</v>
+      </c>
+      <c r="AX230" s="1" t="s">
+        <v>2153</v>
+      </c>
+      <c r="AY230" s="1" t="s">
         <v>2154</v>
-      </c>
-      <c r="AX230" s="1" t="s">
-        <v>2154</v>
-      </c>
-      <c r="AY230" s="1" t="s">
-        <v>2155</v>
       </c>
       <c r="AZ230" s="3" t="s">
         <v>1341</v>
@@ -39574,13 +39574,13 @@
         <v>599</v>
       </c>
       <c r="T232" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="X232" s="1" t="s">
         <v>2059</v>
       </c>
-      <c r="X232" s="1" t="s">
+      <c r="AE232" s="1" t="s">
         <v>2060</v>
-      </c>
-      <c r="AE232" s="1" t="s">
-        <v>2061</v>
       </c>
       <c r="AH232" s="1" t="s">
         <v>308</v>
@@ -39604,10 +39604,10 @@
         <v>308</v>
       </c>
       <c r="AV232" s="1" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="AW232" s="1" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="AY232" s="1" t="s">
         <v>308</v>
@@ -39645,13 +39645,13 @@
         <v>604</v>
       </c>
       <c r="Q233" s="1" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="AA233" s="1" t="s">
         <v>321</v>
       </c>
       <c r="AE233" s="1" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="AH233" s="1" t="s">
         <v>308</v>
@@ -39681,7 +39681,7 @@
         <v>308</v>
       </c>
       <c r="AV233" s="1" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="AW233" s="1" t="s">
         <v>1681</v>
@@ -39719,13 +39719,13 @@
         <v>95</v>
       </c>
       <c r="Q234" s="1" t="s">
+        <v>2065</v>
+      </c>
+      <c r="X234" s="1" t="s">
         <v>2066</v>
       </c>
-      <c r="X234" s="1" t="s">
+      <c r="AE234" s="1" t="s">
         <v>2067</v>
-      </c>
-      <c r="AE234" s="1" t="s">
-        <v>2068</v>
       </c>
       <c r="AI234" s="1" t="s">
         <v>308</v>
@@ -39749,7 +39749,7 @@
         <v>308</v>
       </c>
       <c r="AV234" s="1" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="AW234" s="1" t="s">
         <v>2054</v>
@@ -39793,7 +39793,7 @@
         <v>314</v>
       </c>
       <c r="AE235" s="1" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="AH235" s="1" t="s">
         <v>308</v>
@@ -39817,7 +39817,7 @@
         <v>308</v>
       </c>
       <c r="AV235" s="1" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="AW235" s="1" t="s">
         <v>617</v>
@@ -39855,13 +39855,13 @@
         <v>159</v>
       </c>
       <c r="Q236" s="1" t="s">
+        <v>2070</v>
+      </c>
+      <c r="T236" s="1" t="s">
         <v>2071</v>
       </c>
-      <c r="T236" s="1" t="s">
+      <c r="AE236" s="1" t="s">
         <v>2072</v>
-      </c>
-      <c r="AE236" s="1" t="s">
-        <v>2073</v>
       </c>
       <c r="AG236" s="1" t="s">
         <v>315</v>
@@ -39879,7 +39879,7 @@
         <v>308</v>
       </c>
       <c r="AV236" s="1" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="AW236" s="1" t="s">
         <v>1792</v>
@@ -39920,7 +39920,7 @@
         <v>604</v>
       </c>
       <c r="Q237" s="1" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="V237" s="1" t="s">
         <v>320</v>
@@ -39932,7 +39932,7 @@
         <v>319</v>
       </c>
       <c r="AE237" s="1" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="AK237" s="1" t="s">
         <v>308</v>
@@ -39950,10 +39950,10 @@
         <v>308</v>
       </c>
       <c r="AV237" s="1" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="AW237" s="1" t="s">
-        <v>2057</v>
+        <v>2160</v>
       </c>
       <c r="AY237" s="1" t="s">
         <v>308</v>
@@ -39991,7 +39991,7 @@
         <v>599</v>
       </c>
       <c r="Q238" s="1" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AA238" s="1" t="s">
         <v>315</v>
@@ -40015,7 +40015,7 @@
         <v>308</v>
       </c>
       <c r="AV238" s="1" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AW238" s="1" t="s">
         <v>628</v>
@@ -40056,13 +40056,13 @@
         <v>631</v>
       </c>
       <c r="Q239" s="1" t="s">
+        <v>2077</v>
+      </c>
+      <c r="AE239" s="1" t="s">
         <v>2078</v>
       </c>
-      <c r="AE239" s="1" t="s">
+      <c r="AG239" s="1" t="s">
         <v>2079</v>
-      </c>
-      <c r="AG239" s="1" t="s">
-        <v>2080</v>
       </c>
       <c r="AI239" s="1" t="s">
         <v>308</v>
@@ -40086,7 +40086,7 @@
         <v>308</v>
       </c>
       <c r="AV239" s="1" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AW239" s="1" t="s">
         <v>635</v>
@@ -40127,19 +40127,19 @@
         <v>638</v>
       </c>
       <c r="Q240" s="1" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="T240" s="1" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AA240" s="1" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="AB240" s="1" t="s">
+        <v>2081</v>
+      </c>
+      <c r="AE240" s="1" t="s">
         <v>2082</v>
-      </c>
-      <c r="AE240" s="1" t="s">
-        <v>2083</v>
       </c>
       <c r="AI240" s="1" t="s">
         <v>308</v>
@@ -40160,10 +40160,10 @@
         <v>308</v>
       </c>
       <c r="AV240" s="1" t="s">
+        <v>2139</v>
+      </c>
+      <c r="AW240" s="1" t="s">
         <v>2140</v>
-      </c>
-      <c r="AW240" s="1" t="s">
-        <v>2141</v>
       </c>
       <c r="AY240" s="1" t="s">
         <v>308</v>
@@ -40201,10 +40201,10 @@
         <v>643</v>
       </c>
       <c r="T241" s="1" t="s">
+        <v>2083</v>
+      </c>
+      <c r="AA241" s="1" t="s">
         <v>2084</v>
-      </c>
-      <c r="AA241" s="1" t="s">
-        <v>2085</v>
       </c>
       <c r="AI241" s="1" t="s">
         <v>308</v>
@@ -40225,7 +40225,7 @@
         <v>308</v>
       </c>
       <c r="AV241" s="1" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="AW241" s="1" t="s">
         <v>1797</v>
@@ -40269,7 +40269,7 @@
         <v>311</v>
       </c>
       <c r="AB242" s="1" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG242" s="1" t="s">
         <v>312</v>
@@ -40293,7 +40293,7 @@
         <v>308</v>
       </c>
       <c r="AV242" s="1" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="AW242" s="1" t="s">
         <v>1682</v>
@@ -40507,13 +40507,13 @@
         <v>670</v>
       </c>
       <c r="Q247" s="1" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="T247" s="1" t="s">
+        <v>2087</v>
+      </c>
+      <c r="V247" s="1" t="s">
         <v>2088</v>
-      </c>
-      <c r="V247" s="1" t="s">
-        <v>2089</v>
       </c>
       <c r="AI247" s="1" t="s">
         <v>308</v>
@@ -40531,7 +40531,7 @@
         <v>308</v>
       </c>
       <c r="AV247" s="1" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="AW247" s="1" t="s">
         <v>672</v>
@@ -40578,7 +40578,7 @@
         <v>314</v>
       </c>
       <c r="AE248" s="1" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="AI248" s="1" t="s">
         <v>308</v>
@@ -40605,7 +40605,7 @@
         <v>308</v>
       </c>
       <c r="AV248" s="1" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="AW248" s="1" t="s">
         <v>678</v>
@@ -40646,16 +40646,16 @@
         <v>681</v>
       </c>
       <c r="Q249" s="1" t="s">
+        <v>2091</v>
+      </c>
+      <c r="T249" s="1" t="s">
         <v>2092</v>
       </c>
-      <c r="T249" s="1" t="s">
+      <c r="AA249" s="1" t="s">
         <v>2093</v>
       </c>
-      <c r="AA249" s="1" t="s">
+      <c r="AE249" s="1" t="s">
         <v>2094</v>
-      </c>
-      <c r="AE249" s="1" t="s">
-        <v>2095</v>
       </c>
       <c r="AI249" s="1" t="s">
         <v>308</v>
@@ -40676,7 +40676,7 @@
         <v>308</v>
       </c>
       <c r="AV249" s="1" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="AW249" s="1" t="s">
         <v>684</v>
@@ -40717,7 +40717,7 @@
         <v>687</v>
       </c>
       <c r="Q250" s="1" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="AI250" s="1" t="s">
         <v>308</v>
@@ -40735,7 +40735,7 @@
         <v>308</v>
       </c>
       <c r="AV250" s="1" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="AW250" s="1" t="s">
         <v>690</v>
@@ -40776,7 +40776,7 @@
         <v>692</v>
       </c>
       <c r="Q251" s="1" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="AI251" s="1" t="s">
         <v>308</v>
@@ -40794,7 +40794,7 @@
         <v>308</v>
       </c>
       <c r="AV251" s="1" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="AW251" s="1" t="s">
         <v>695</v>
@@ -40835,7 +40835,7 @@
         <v>698</v>
       </c>
       <c r="Q252" s="1" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="AI252" s="1" t="s">
         <v>308</v>
@@ -40859,7 +40859,7 @@
         <v>308</v>
       </c>
       <c r="AV252" s="1" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="AW252" s="1" t="s">
         <v>702</v>
@@ -40918,7 +40918,7 @@
         <v>308</v>
       </c>
       <c r="AV253" s="1" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="AW253" s="1" t="s">
         <v>707</v>
@@ -40977,7 +40977,7 @@
         <v>308</v>
       </c>
       <c r="AV254" s="1" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="AW254" s="1" t="s">
         <v>711</v>
@@ -41018,10 +41018,10 @@
         <v>713</v>
       </c>
       <c r="Q255" s="1" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="AE255" s="1" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="AL255" s="1" t="s">
         <v>308</v>
@@ -41036,7 +41036,7 @@
         <v>308</v>
       </c>
       <c r="AV255" s="1" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="AW255" s="1" t="s">
         <v>715</v>
@@ -41077,10 +41077,10 @@
         <v>698</v>
       </c>
       <c r="Q256" s="1" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="AE256" s="1" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="AL256" s="1" t="s">
         <v>308</v>
@@ -41095,7 +41095,7 @@
         <v>308</v>
       </c>
       <c r="AV256" s="1" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="AW256" s="1" t="s">
         <v>719</v>
@@ -41136,13 +41136,13 @@
         <v>722</v>
       </c>
       <c r="Q257" s="1" t="s">
+        <v>2108</v>
+      </c>
+      <c r="AE257" s="1" t="s">
         <v>2109</v>
       </c>
-      <c r="AE257" s="1" t="s">
+      <c r="AG257" s="1" t="s">
         <v>2110</v>
-      </c>
-      <c r="AG257" s="1" t="s">
-        <v>2111</v>
       </c>
       <c r="AM257" s="1" t="s">
         <v>308</v>
@@ -41154,7 +41154,7 @@
         <v>308</v>
       </c>
       <c r="AV257" s="1" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="AW257" s="1" t="s">
         <v>724</v>
@@ -41195,10 +41195,10 @@
         <v>713</v>
       </c>
       <c r="Q258" s="1" t="s">
+        <v>2112</v>
+      </c>
+      <c r="AE258" s="1" t="s">
         <v>2113</v>
-      </c>
-      <c r="AE258" s="1" t="s">
-        <v>2114</v>
       </c>
       <c r="AG258" s="1" t="s">
         <v>316</v>
@@ -41213,7 +41213,7 @@
         <v>308</v>
       </c>
       <c r="AV258" s="1" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="AW258" s="1" t="s">
         <v>728</v>
@@ -41254,10 +41254,10 @@
         <v>705</v>
       </c>
       <c r="Q259" s="1" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="AE259" s="1" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="AL259" s="1" t="s">
         <v>308</v>
@@ -41272,7 +41272,7 @@
         <v>308</v>
       </c>
       <c r="AV259" s="1" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="AW259" s="1" t="s">
         <v>732</v>
@@ -41313,10 +41313,10 @@
         <v>735</v>
       </c>
       <c r="Q260" s="1" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="AE260" s="1" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="AL260" s="1" t="s">
         <v>308</v>
@@ -41331,7 +41331,7 @@
         <v>308</v>
       </c>
       <c r="AV260" s="1" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="AW260" s="1" t="s">
         <v>737</v>
@@ -41372,13 +41372,13 @@
         <v>740</v>
       </c>
       <c r="Q261" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="T261" s="1" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AE261" s="1" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="AJ261" s="1" t="s">
         <v>308</v>
@@ -41393,7 +41393,7 @@
         <v>308</v>
       </c>
       <c r="AV261" s="1" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="AW261" s="1" t="s">
         <v>741</v>
@@ -41434,10 +41434,10 @@
         <v>740</v>
       </c>
       <c r="Q262" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="AE262" s="1" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="AJ262" s="1" t="s">
         <v>308</v>
@@ -41452,7 +41452,7 @@
         <v>308</v>
       </c>
       <c r="AV262" s="1" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="AW262" s="1" t="s">
         <v>744</v>
@@ -41493,10 +41493,10 @@
         <v>740</v>
       </c>
       <c r="Q263" s="1" t="s">
+        <v>2120</v>
+      </c>
+      <c r="AE263" s="1" t="s">
         <v>2121</v>
-      </c>
-      <c r="AE263" s="1" t="s">
-        <v>2122</v>
       </c>
       <c r="AJ263" s="1" t="s">
         <v>308</v>
@@ -41511,7 +41511,7 @@
         <v>308</v>
       </c>
       <c r="AV263" s="1" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="AW263" s="1" t="s">
         <v>747</v>
@@ -41552,10 +41552,10 @@
         <v>750</v>
       </c>
       <c r="Q264" s="1" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="T264" s="1" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="AE264" s="1" t="s">
         <v>1111</v>
@@ -41576,7 +41576,7 @@
         <v>308</v>
       </c>
       <c r="AV264" s="1" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="AW264" s="1" t="s">
         <v>752</v>
@@ -41617,10 +41617,10 @@
         <v>740</v>
       </c>
       <c r="Q265" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="AE265" s="1" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="AJ265" s="1" t="s">
         <v>308</v>
@@ -41635,7 +41635,7 @@
         <v>308</v>
       </c>
       <c r="AV265" s="1" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="AW265" s="1" t="s">
         <v>756</v>
@@ -41676,10 +41676,10 @@
         <v>740</v>
       </c>
       <c r="Q266" s="1" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="AE266" s="1" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="AJ266" s="1" t="s">
         <v>308</v>
@@ -41694,7 +41694,7 @@
         <v>308</v>
       </c>
       <c r="AV266" s="1" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="AW266" s="1" t="s">
         <v>760</v>
@@ -41788,7 +41788,7 @@
         <v>681</v>
       </c>
       <c r="Q268" s="1" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="AG268" s="1" t="s">
         <v>1430</v>
@@ -41812,7 +41812,7 @@
         <v>308</v>
       </c>
       <c r="AV268" s="1" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="AW268" s="1" t="s">
         <v>767</v>
@@ -41856,7 +41856,7 @@
         <v>316</v>
       </c>
       <c r="AE269" s="1" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="AI269" s="1" t="s">
         <v>308</v>
@@ -41874,7 +41874,7 @@
         <v>308</v>
       </c>
       <c r="AV269" s="1" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="AW269" s="1" t="s">
         <v>771</v>
@@ -42121,7 +42121,7 @@
         <v>692</v>
       </c>
       <c r="T274" s="1" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="AJ274" s="1" t="s">
         <v>308</v>
@@ -42133,7 +42133,7 @@
         <v>308</v>
       </c>
       <c r="AV274" s="1" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="AW274" s="1" t="s">
         <v>793</v>
@@ -42482,7 +42482,7 @@
         <v>95</v>
       </c>
       <c r="Q282" s="1" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="AI282" s="1" t="s">
         <v>308</v>
@@ -42500,7 +42500,7 @@
         <v>308</v>
       </c>
       <c r="AV282" s="1" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="AW282" s="1" t="s">
         <v>822</v>
@@ -43337,22 +43337,22 @@
     </row>
     <row r="153" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="154" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="155" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="156" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="157" spans="1:1" ht="33" x14ac:dyDescent="0.25">
@@ -43377,7 +43377,7 @@
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A47A622-E3ED-4461-8152-0CCC7A043CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B212131-834A-4EDB-993F-39BF95968C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E9FFE87-213B-4B8E-BCB8-47D778A8CA93}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12504" uniqueCount="2161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12501" uniqueCount="2160">
   <si>
     <t>群組ID</t>
   </si>
@@ -5173,10 +5173,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>burst-frost-freeze</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>{"dmgPct":40,"dmgPctPer":4,"durPct":40,"durPctPer":4}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -7407,9 +7403,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>10.4*1.43</t>
-  </si>
-  <si>
     <t>0.2</t>
   </si>
   <si>
@@ -7734,6 +7727,10 @@
   </si>
   <si>
     <t>【雷隕天落】的雷隕石體積增大 {scale}%、傷害額外 +{pct}%，並額外每 {gap} 秒不斷再降下 1 顆</t>
+  </si>
+  <si>
+    <t>14*1.75</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8222,7 +8219,8 @@
     <col min="10" max="33" width="8.5" customWidth="1"/>
     <col min="34" max="34" width="7.625" customWidth="1"/>
     <col min="35" max="35" width="14.25" customWidth="1"/>
-    <col min="36" max="37" width="7.625" customWidth="1"/>
+    <col min="36" max="36" width="15.5" customWidth="1"/>
+    <col min="37" max="37" width="7.625" customWidth="1"/>
     <col min="38" max="38" width="20.5" customWidth="1"/>
     <col min="39" max="39" width="7.625" customWidth="1"/>
     <col min="40" max="44" width="7.625" style="1" customWidth="1"/>
@@ -8246,7 +8244,7 @@
         <v>840</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>841</v>
@@ -8255,7 +8253,7 @@
         <v>842</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>843</v>
@@ -8408,7 +8406,7 @@
         <v>477</v>
       </c>
       <c r="G2" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>887</v>
@@ -8513,7 +8511,7 @@
         <v>547</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="AX2" s="1" t="s">
         <v>30</v>
@@ -8542,7 +8540,7 @@
         <v>897</v>
       </c>
       <c r="G3" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>898</v>
@@ -8647,7 +8645,7 @@
         <v>989</v>
       </c>
       <c r="AW3" s="1" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="AX3" s="1" t="s">
         <v>31</v>
@@ -8676,7 +8674,7 @@
         <v>903</v>
       </c>
       <c r="G4" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>904</v>
@@ -8781,7 +8779,7 @@
         <v>991</v>
       </c>
       <c r="AW4" s="1" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="AX4" s="1" t="s">
         <v>32</v>
@@ -8810,7 +8808,7 @@
         <v>542</v>
       </c>
       <c r="G5" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>909</v>
@@ -8915,7 +8913,7 @@
         <v>548</v>
       </c>
       <c r="AW5" s="1" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="AX5" s="1" t="s">
         <v>33</v>
@@ -8944,7 +8942,7 @@
         <v>915</v>
       </c>
       <c r="G6" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>916</v>
@@ -9049,7 +9047,7 @@
         <v>549</v>
       </c>
       <c r="AW6" s="1" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="AX6" s="1" t="s">
         <v>34</v>
@@ -9078,7 +9076,7 @@
         <v>487</v>
       </c>
       <c r="G7" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>922</v>
@@ -9183,7 +9181,7 @@
         <v>550</v>
       </c>
       <c r="AW7" s="1" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="AX7" s="1" t="s">
         <v>35</v>
@@ -9212,7 +9210,7 @@
         <v>927</v>
       </c>
       <c r="G8" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>928</v>
@@ -9314,10 +9312,10 @@
         <v>308</v>
       </c>
       <c r="AV8" s="1" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="AW8" s="1" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="AX8" s="1" t="s">
         <v>36</v>
@@ -9346,7 +9344,7 @@
         <v>523</v>
       </c>
       <c r="G9" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>932</v>
@@ -9451,7 +9449,7 @@
         <v>1002</v>
       </c>
       <c r="AW9" s="1" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="AX9" s="1" t="s">
         <v>37</v>
@@ -9480,7 +9478,7 @@
         <v>940</v>
       </c>
       <c r="G10" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>932</v>
@@ -9591,7 +9589,7 @@
         <v>1006</v>
       </c>
       <c r="AW10" s="1" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="AX10" s="1" t="s">
         <v>38</v>
@@ -9620,7 +9618,7 @@
         <v>947</v>
       </c>
       <c r="G11" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>932</v>
@@ -9725,7 +9723,7 @@
         <v>551</v>
       </c>
       <c r="AW11" s="1" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="AX11" s="1" t="s">
         <v>39</v>
@@ -9754,7 +9752,7 @@
         <v>477</v>
       </c>
       <c r="G12" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>887</v>
@@ -9859,7 +9857,7 @@
         <v>547</v>
       </c>
       <c r="AW12" s="1" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="AX12" s="1" t="s">
         <v>9</v>
@@ -9888,7 +9886,7 @@
         <v>897</v>
       </c>
       <c r="G13" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>898</v>
@@ -9993,7 +9991,7 @@
         <v>900</v>
       </c>
       <c r="AW13" s="1" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="AX13" s="1" t="s">
         <v>10</v>
@@ -10022,7 +10020,7 @@
         <v>903</v>
       </c>
       <c r="G14" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>904</v>
@@ -10127,7 +10125,7 @@
         <v>907</v>
       </c>
       <c r="AW14" s="1" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="AX14" s="1" t="s">
         <v>11</v>
@@ -10156,7 +10154,7 @@
         <v>542</v>
       </c>
       <c r="G15" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>909</v>
@@ -10261,7 +10259,7 @@
         <v>912</v>
       </c>
       <c r="AW15" s="1" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="AX15" s="1" t="s">
         <v>12</v>
@@ -10290,7 +10288,7 @@
         <v>915</v>
       </c>
       <c r="G16" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>916</v>
@@ -10395,7 +10393,7 @@
         <v>919</v>
       </c>
       <c r="AW16" s="1" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="AX16" s="1" t="s">
         <v>13</v>
@@ -10424,7 +10422,7 @@
         <v>487</v>
       </c>
       <c r="G17" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>922</v>
@@ -10529,7 +10527,7 @@
         <v>925</v>
       </c>
       <c r="AW17" s="1" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="AX17" s="1" t="s">
         <v>14</v>
@@ -10558,7 +10556,7 @@
         <v>927</v>
       </c>
       <c r="G18" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>928</v>
@@ -10663,7 +10661,7 @@
         <v>544</v>
       </c>
       <c r="AW18" s="1" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="AX18" s="1" t="s">
         <v>930</v>
@@ -10692,7 +10690,7 @@
         <v>523</v>
       </c>
       <c r="G19" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>932</v>
@@ -10803,7 +10801,7 @@
         <v>545</v>
       </c>
       <c r="AW19" s="1" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="AX19" s="1" t="s">
         <v>937</v>
@@ -10832,7 +10830,7 @@
         <v>940</v>
       </c>
       <c r="G20" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>932</v>
@@ -10940,7 +10938,7 @@
         <v>944</v>
       </c>
       <c r="AW20" s="1" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="AX20" s="1" t="s">
         <v>15</v>
@@ -10969,7 +10967,7 @@
         <v>947</v>
       </c>
       <c r="G21" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>932</v>
@@ -11074,7 +11072,7 @@
         <v>950</v>
       </c>
       <c r="AW21" s="1" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="AX21" s="1" t="s">
         <v>951</v>
@@ -11103,7 +11101,7 @@
         <v>477</v>
       </c>
       <c r="G22" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>887</v>
@@ -11208,7 +11206,7 @@
         <v>956</v>
       </c>
       <c r="AW22" s="1" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="AX22" s="1" t="s">
         <v>18</v>
@@ -11237,7 +11235,7 @@
         <v>897</v>
       </c>
       <c r="G23" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>898</v>
@@ -11342,7 +11340,7 @@
         <v>925</v>
       </c>
       <c r="AW23" s="1" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="AX23" s="1" t="s">
         <v>19</v>
@@ -11371,7 +11369,7 @@
         <v>903</v>
       </c>
       <c r="G24" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>904</v>
@@ -11476,7 +11474,7 @@
         <v>960</v>
       </c>
       <c r="AW24" s="1" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="AX24" s="1" t="s">
         <v>20</v>
@@ -11505,7 +11503,7 @@
         <v>542</v>
       </c>
       <c r="G25" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>909</v>
@@ -11610,7 +11608,7 @@
         <v>962</v>
       </c>
       <c r="AW25" s="1" t="s">
-        <v>1826</v>
+        <v>1825</v>
      